--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-27 18:13:01 | Daily Audits Logged: 1</t>
+          <t>Generated On: 2026-08-28 10:21:14 | Daily Audits Logged: 1</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 10:08:30 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 10:14:17 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>
@@ -898,14 +898,14 @@
       </c>
       <c r="H3" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I3" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="21" t="n">
-        <v>141311</v>
+        <v>43936</v>
       </c>
       <c r="K3" s="21" t="n">
         <v>185247</v>
@@ -970,14 +970,14 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I4" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>46623</v>
+        <v>90566</v>
       </c>
       <c r="K4" s="14" t="n">
         <v>137189</v>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I5" s="20" t="n">
@@ -1114,14 +1114,14 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I6" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>12118</v>
+        <v>70990</v>
       </c>
       <c r="K6" s="14" t="n">
         <v>83108</v>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I7" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="21" t="n">
-        <v>51702</v>
+        <v>26080</v>
       </c>
       <c r="K7" s="21" t="n">
         <v>77782</v>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I8" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>36173</v>
+        <v>38584</v>
       </c>
       <c r="K8" s="14" t="n">
         <v>74757</v>
@@ -1402,14 +1402,14 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I10" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>26204</v>
+        <v>48086</v>
       </c>
       <c r="K10" s="14" t="n">
         <v>74290</v>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I18" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>28487</v>
+        <v>21925</v>
       </c>
       <c r="K18" s="14" t="n">
         <v>50412</v>
@@ -2050,14 +2050,14 @@
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I19" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>1245</v>
+        <v>47876</v>
       </c>
       <c r="K19" s="21" t="n">
         <v>49121</v>
@@ -2122,14 +2122,14 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I20" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>15950</v>
+        <v>31903</v>
       </c>
       <c r="K20" s="14" t="n">
         <v>47853</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I21" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>41270</v>
+        <v>5883</v>
       </c>
       <c r="K21" s="21" t="n">
         <v>47153</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I22" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>10245</v>
+        <v>36823</v>
       </c>
       <c r="K22" s="14" t="n">
         <v>47068</v>
@@ -2410,14 +2410,14 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I24" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>19795</v>
+        <v>26404</v>
       </c>
       <c r="K24" s="14" t="n">
         <v>46199</v>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I26" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>39193</v>
+        <v>3918</v>
       </c>
       <c r="K26" s="14" t="n">
         <v>43111</v>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I28" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>8225</v>
+        <v>33063</v>
       </c>
       <c r="K28" s="14" t="n">
         <v>41288</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="H31" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I31" s="20" t="n">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I32" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>23618</v>
+        <v>15271</v>
       </c>
       <c r="K32" s="14" t="n">
         <v>38889</v>
@@ -3058,14 +3058,14 @@
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I33" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J33" s="21" t="n">
-        <v>19232</v>
+        <v>18751</v>
       </c>
       <c r="K33" s="21" t="n">
         <v>37983</v>
@@ -3202,14 +3202,14 @@
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>27294</v>
+        <v>7808</v>
       </c>
       <c r="K35" s="21" t="n">
         <v>35102</v>
@@ -3346,14 +3346,14 @@
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I37" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J37" s="21" t="n">
-        <v>10508</v>
+        <v>22390</v>
       </c>
       <c r="K37" s="21" t="n">
         <v>32898</v>
@@ -3418,14 +3418,14 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>19075</v>
+        <v>13496</v>
       </c>
       <c r="K38" s="14" t="n">
         <v>32571</v>
@@ -3490,14 +3490,14 @@
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I39" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="21" t="n">
-        <v>21292</v>
+        <v>11179</v>
       </c>
       <c r="K39" s="21" t="n">
         <v>32471</v>
@@ -3562,14 +3562,14 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I40" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>7026</v>
+        <v>25120</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>32146</v>
@@ -4210,14 +4210,14 @@
       </c>
       <c r="H49" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I49" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J49" s="21" t="n">
-        <v>3293</v>
+        <v>23048</v>
       </c>
       <c r="K49" s="21" t="n">
         <v>26341</v>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I51" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J51" s="21" t="n">
-        <v>14604</v>
+        <v>11479</v>
       </c>
       <c r="K51" s="21" t="n">
         <v>26083</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I52" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>14387</v>
+        <v>11650</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>26037</v>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I54" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J54" s="14" t="n">
-        <v>11571</v>
+        <v>13185</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>24756</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="H55" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I55" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J55" s="21" t="n">
-        <v>8209</v>
+        <v>16409</v>
       </c>
       <c r="K55" s="21" t="n">
         <v>24618</v>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="H57" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I57" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J57" s="21" t="n">
-        <v>9221</v>
+        <v>14553</v>
       </c>
       <c r="K57" s="21" t="n">
         <v>23774</v>
@@ -4858,14 +4858,14 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I58" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="14" t="n">
-        <v>5305</v>
+        <v>17304</v>
       </c>
       <c r="K58" s="14" t="n">
         <v>22609</v>
@@ -4930,14 +4930,14 @@
       </c>
       <c r="H59" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I59" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J59" s="21" t="n">
-        <v>6874</v>
+        <v>15666</v>
       </c>
       <c r="K59" s="21" t="n">
         <v>22540</v>
@@ -5002,14 +5002,14 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I60" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>5264</v>
+        <v>16281</v>
       </c>
       <c r="K60" s="14" t="n">
         <v>21545</v>
@@ -5146,14 +5146,14 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I62" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="14" t="n">
-        <v>11763</v>
+        <v>9410</v>
       </c>
       <c r="K62" s="14" t="n">
         <v>21173</v>
@@ -5218,14 +5218,14 @@
       </c>
       <c r="H63" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I63" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="21" t="n">
-        <v>4880</v>
+        <v>16107</v>
       </c>
       <c r="K63" s="21" t="n">
         <v>20987</v>
@@ -5362,14 +5362,14 @@
       </c>
       <c r="H65" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I65" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J65" s="21" t="n">
-        <v>12786</v>
+        <v>7258</v>
       </c>
       <c r="K65" s="21" t="n">
         <v>20044</v>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I66" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J66" s="14" t="n">
-        <v>14153</v>
+        <v>5858</v>
       </c>
       <c r="K66" s="14" t="n">
         <v>20011</v>
@@ -5506,14 +5506,14 @@
       </c>
       <c r="H67" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I67" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J67" s="21" t="n">
-        <v>4893</v>
+        <v>14985</v>
       </c>
       <c r="K67" s="21" t="n">
         <v>19878</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I70" s="13" t="n">
@@ -5866,14 +5866,14 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I72" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>3293</v>
+        <v>15525</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>18818</v>
@@ -6010,14 +6010,14 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I74" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J74" s="14" t="n">
-        <v>4514</v>
+        <v>14018</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>18532</v>
@@ -6154,14 +6154,14 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I76" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J76" s="14" t="n">
-        <v>10316</v>
+        <v>7602</v>
       </c>
       <c r="K76" s="14" t="n">
         <v>17918</v>
@@ -6298,14 +6298,14 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I78" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J78" s="14" t="n">
-        <v>10620</v>
+        <v>6903</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>17523</v>
@@ -6514,14 +6514,14 @@
       </c>
       <c r="H81" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I81" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J81" s="21" t="n">
-        <v>1969</v>
+        <v>15119</v>
       </c>
       <c r="K81" s="21" t="n">
         <v>17088</v>
@@ -6658,14 +6658,14 @@
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I83" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J83" s="21" t="n">
-        <v>13666</v>
+        <v>2928</v>
       </c>
       <c r="K83" s="21" t="n">
         <v>16594</v>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="H85" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I85" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J85" s="21" t="n">
-        <v>5795</v>
+        <v>10644</v>
       </c>
       <c r="K85" s="21" t="n">
         <v>16439</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="H87" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I87" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J87" s="21" t="n">
-        <v>1223</v>
+        <v>14915</v>
       </c>
       <c r="K87" s="21" t="n">
         <v>16138</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I90" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J90" s="14" t="n">
-        <v>5758</v>
+        <v>9898</v>
       </c>
       <c r="K90" s="14" t="n">
         <v>15656</v>
@@ -7234,14 +7234,14 @@
       </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I91" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J91" s="21" t="n">
-        <v>6844</v>
+        <v>8746</v>
       </c>
       <c r="K91" s="21" t="n">
         <v>15590</v>
@@ -7306,14 +7306,14 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I92" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J92" s="14" t="n">
-        <v>9203</v>
+        <v>5751</v>
       </c>
       <c r="K92" s="14" t="n">
         <v>14954</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I94" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J94" s="14" t="n">
-        <v>12156</v>
+        <v>2440</v>
       </c>
       <c r="K94" s="14" t="n">
         <v>14596</v>
@@ -7810,14 +7810,14 @@
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I99" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J99" s="21" t="n">
-        <v>1968</v>
+        <v>11974</v>
       </c>
       <c r="K99" s="21" t="n">
         <v>13942</v>
@@ -7954,14 +7954,14 @@
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I101" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J101" s="21" t="n">
-        <v>6986</v>
+        <v>6859</v>
       </c>
       <c r="K101" s="21" t="n">
         <v>13845</v>
@@ -8026,14 +8026,14 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I102" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J102" s="14" t="n">
-        <v>9860</v>
+        <v>3904</v>
       </c>
       <c r="K102" s="14" t="n">
         <v>13764</v>
@@ -8098,14 +8098,14 @@
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I103" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J103" s="21" t="n">
-        <v>7197</v>
+        <v>6532</v>
       </c>
       <c r="K103" s="21" t="n">
         <v>13729</v>
@@ -8242,14 +8242,14 @@
       </c>
       <c r="H105" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I105" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J105" s="21" t="n">
-        <v>6891</v>
+        <v>6727</v>
       </c>
       <c r="K105" s="21" t="n">
         <v>13618</v>
@@ -8386,14 +8386,14 @@
       </c>
       <c r="H107" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I107" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J107" s="21" t="n">
-        <v>5660</v>
+        <v>7772</v>
       </c>
       <c r="K107" s="21" t="n">
         <v>13432</v>
@@ -8458,14 +8458,14 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I108" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J108" s="14" t="n">
-        <v>5142</v>
+        <v>8111</v>
       </c>
       <c r="K108" s="14" t="n">
         <v>13253</v>
@@ -8746,14 +8746,14 @@
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I112" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J112" s="14" t="n">
-        <v>4048</v>
+        <v>8847</v>
       </c>
       <c r="K112" s="14" t="n">
         <v>12895</v>
@@ -8818,14 +8818,14 @@
       </c>
       <c r="H113" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I113" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J113" s="21" t="n">
-        <v>2822</v>
+        <v>10066</v>
       </c>
       <c r="K113" s="21" t="n">
         <v>12888</v>
@@ -8890,14 +8890,14 @@
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I114" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J114" s="14" t="n">
-        <v>10127</v>
+        <v>2602</v>
       </c>
       <c r="K114" s="14" t="n">
         <v>12729</v>
@@ -9034,14 +9034,14 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I116" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>2442</v>
+        <v>10057</v>
       </c>
       <c r="K116" s="14" t="n">
         <v>12499</v>
@@ -9250,14 +9250,14 @@
       </c>
       <c r="H119" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I119" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J119" s="21" t="n">
-        <v>1339</v>
+        <v>10582</v>
       </c>
       <c r="K119" s="21" t="n">
         <v>11921</v>
@@ -9466,14 +9466,14 @@
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I122" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J122" s="14" t="n">
-        <v>2257</v>
+        <v>9470</v>
       </c>
       <c r="K122" s="14" t="n">
         <v>11727</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="H125" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I125" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J125" s="21" t="n">
-        <v>5295</v>
+        <v>6308</v>
       </c>
       <c r="K125" s="21" t="n">
         <v>11603</v>
@@ -9826,14 +9826,14 @@
       </c>
       <c r="H127" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I127" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J127" s="21" t="n">
-        <v>2893</v>
+        <v>8679</v>
       </c>
       <c r="K127" s="21" t="n">
         <v>11572</v>
@@ -9898,14 +9898,14 @@
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I128" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J128" s="14" t="n">
-        <v>8399</v>
+        <v>2964</v>
       </c>
       <c r="K128" s="14" t="n">
         <v>11363</v>
@@ -10042,14 +10042,14 @@
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I130" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J130" s="14" t="n">
-        <v>2911</v>
+        <v>8230</v>
       </c>
       <c r="K130" s="14" t="n">
         <v>11141</v>
@@ -10114,14 +10114,14 @@
       </c>
       <c r="H131" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I131" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J131" s="21" t="n">
-        <v>8643</v>
+        <v>2305</v>
       </c>
       <c r="K131" s="21" t="n">
         <v>10948</v>
@@ -10186,14 +10186,14 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I132" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J132" s="14" t="n">
-        <v>4721</v>
+        <v>6169</v>
       </c>
       <c r="K132" s="14" t="n">
         <v>10890</v>
@@ -10258,14 +10258,14 @@
       </c>
       <c r="H133" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I133" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J133" s="21" t="n">
-        <v>4940</v>
+        <v>5927</v>
       </c>
       <c r="K133" s="21" t="n">
         <v>10867</v>
@@ -10330,14 +10330,14 @@
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I134" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J134" s="14" t="n">
-        <v>4842</v>
+        <v>5891</v>
       </c>
       <c r="K134" s="14" t="n">
         <v>10733</v>
@@ -10402,14 +10402,14 @@
       </c>
       <c r="H135" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I135" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J135" s="21" t="n">
-        <v>2396</v>
+        <v>8254</v>
       </c>
       <c r="K135" s="21" t="n">
         <v>10650</v>
@@ -10762,14 +10762,14 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I140" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J140" s="14" t="n">
-        <v>1412</v>
+        <v>8610</v>
       </c>
       <c r="K140" s="14" t="n">
         <v>10022</v>
@@ -10978,14 +10978,14 @@
       </c>
       <c r="H143" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I143" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J143" s="21" t="n">
-        <v>5636</v>
+        <v>4227</v>
       </c>
       <c r="K143" s="21" t="n">
         <v>9863</v>
@@ -11050,14 +11050,14 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I144" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>6357</v>
+        <v>3423</v>
       </c>
       <c r="K144" s="14" t="n">
         <v>9780</v>
@@ -11482,14 +11482,14 @@
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I150" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J150" s="14" t="n">
-        <v>5680</v>
+        <v>3857</v>
       </c>
       <c r="K150" s="14" t="n">
         <v>9537</v>
@@ -11698,14 +11698,14 @@
       </c>
       <c r="H153" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I153" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J153" s="21" t="n">
-        <v>3715</v>
+        <v>5597</v>
       </c>
       <c r="K153" s="21" t="n">
         <v>9312</v>
@@ -12274,14 +12274,14 @@
       </c>
       <c r="H161" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I161" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J161" s="21" t="n">
-        <v>6568</v>
+        <v>1962</v>
       </c>
       <c r="K161" s="21" t="n">
         <v>8530</v>
@@ -12346,14 +12346,14 @@
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I162" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J162" s="14" t="n">
-        <v>2353</v>
+        <v>6022</v>
       </c>
       <c r="K162" s="14" t="n">
         <v>8375</v>
@@ -12418,14 +12418,14 @@
       </c>
       <c r="H163" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I163" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J163" s="21" t="n">
-        <v>3198</v>
+        <v>5174</v>
       </c>
       <c r="K163" s="21" t="n">
         <v>8372</v>
@@ -12850,14 +12850,14 @@
       </c>
       <c r="H169" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I169" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J169" s="21" t="n">
-        <v>3927</v>
+        <v>3868</v>
       </c>
       <c r="K169" s="21" t="n">
         <v>7795</v>
@@ -13282,14 +13282,14 @@
       </c>
       <c r="H175" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I175" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J175" s="21" t="n">
-        <v>3121</v>
+        <v>4373</v>
       </c>
       <c r="K175" s="21" t="n">
         <v>7494</v>
@@ -13354,14 +13354,14 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I176" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J176" s="14" t="n">
-        <v>1358</v>
+        <v>6014</v>
       </c>
       <c r="K176" s="14" t="n">
         <v>7372</v>
@@ -14218,14 +14218,14 @@
       </c>
       <c r="H188" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I188" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J188" s="14" t="n">
-        <v>3319</v>
+        <v>3321</v>
       </c>
       <c r="K188" s="14" t="n">
         <v>6640</v>
@@ -14722,14 +14722,14 @@
       </c>
       <c r="H195" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I195" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J195" s="21" t="n">
-        <v>1567</v>
+        <v>4798</v>
       </c>
       <c r="K195" s="21" t="n">
         <v>6365</v>
@@ -14866,14 +14866,14 @@
       </c>
       <c r="H197" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I197" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J197" s="21" t="n">
-        <v>3198</v>
+        <v>3104</v>
       </c>
       <c r="K197" s="21" t="n">
         <v>6302</v>
@@ -15082,14 +15082,14 @@
       </c>
       <c r="H200" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I200" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J200" s="14" t="n">
-        <v>4963</v>
+        <v>1304</v>
       </c>
       <c r="K200" s="14" t="n">
         <v>6267</v>
@@ -15154,14 +15154,14 @@
       </c>
       <c r="H201" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I201" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J201" s="21" t="n">
-        <v>4305</v>
+        <v>1916</v>
       </c>
       <c r="K201" s="21" t="n">
         <v>6221</v>
@@ -15226,14 +15226,14 @@
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I202" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J202" s="14" t="n">
-        <v>1905</v>
+        <v>4286</v>
       </c>
       <c r="K202" s="14" t="n">
         <v>6191</v>
@@ -15298,14 +15298,14 @@
       </c>
       <c r="H203" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I203" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J203" s="21" t="n">
-        <v>2250</v>
+        <v>3870</v>
       </c>
       <c r="K203" s="21" t="n">
         <v>6120</v>
@@ -15442,14 +15442,14 @@
       </c>
       <c r="H205" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I205" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J205" s="21" t="n">
-        <v>1426</v>
+        <v>4657</v>
       </c>
       <c r="K205" s="21" t="n">
         <v>6083</v>
@@ -15514,14 +15514,14 @@
       </c>
       <c r="H206" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I206" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J206" s="14" t="n">
-        <v>2783</v>
+        <v>3154</v>
       </c>
       <c r="K206" s="14" t="n">
         <v>5937</v>
@@ -15586,14 +15586,14 @@
       </c>
       <c r="H207" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I207" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J207" s="21" t="n">
-        <v>3101</v>
+        <v>2817</v>
       </c>
       <c r="K207" s="21" t="n">
         <v>5918</v>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="H210" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I210" s="13" t="n">
@@ -16306,14 +16306,14 @@
       </c>
       <c r="H217" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I217" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J217" s="21" t="n">
-        <v>1757</v>
+        <v>3513</v>
       </c>
       <c r="K217" s="21" t="n">
         <v>5270</v>
@@ -16378,14 +16378,14 @@
       </c>
       <c r="H218" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I218" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J218" s="14" t="n">
-        <v>2530</v>
+        <v>2730</v>
       </c>
       <c r="K218" s="14" t="n">
         <v>5260</v>
@@ -16450,14 +16450,14 @@
       </c>
       <c r="H219" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I219" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J219" s="21" t="n">
-        <v>2381</v>
+        <v>2857</v>
       </c>
       <c r="K219" s="21" t="n">
         <v>5238</v>
@@ -17026,14 +17026,14 @@
       </c>
       <c r="H227" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I227" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J227" s="21" t="n">
-        <v>1464</v>
+        <v>3417</v>
       </c>
       <c r="K227" s="21" t="n">
         <v>4881</v>
@@ -17530,14 +17530,14 @@
       </c>
       <c r="H234" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I234" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J234" s="14" t="n">
-        <v>3331</v>
+        <v>1462</v>
       </c>
       <c r="K234" s="14" t="n">
         <v>4793</v>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H243" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I243" s="20" t="n">
@@ -18394,14 +18394,14 @@
       </c>
       <c r="H246" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I246" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J246" s="14" t="n">
-        <v>1412</v>
+        <v>2823</v>
       </c>
       <c r="K246" s="14" t="n">
         <v>4235</v>
@@ -18466,7 +18466,7 @@
       </c>
       <c r="H247" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I247" s="20" t="n">
@@ -18538,14 +18538,14 @@
       </c>
       <c r="H248" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I248" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J248" s="14" t="n">
-        <v>2427</v>
+        <v>1749</v>
       </c>
       <c r="K248" s="14" t="n">
         <v>4176</v>
@@ -18610,14 +18610,14 @@
       </c>
       <c r="H249" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I249" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J249" s="21" t="n">
-        <v>1349</v>
+        <v>2698</v>
       </c>
       <c r="K249" s="21" t="n">
         <v>4047</v>
@@ -18754,14 +18754,14 @@
       </c>
       <c r="H251" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I251" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J251" s="21" t="n">
-        <v>2666</v>
+        <v>1329</v>
       </c>
       <c r="K251" s="21" t="n">
         <v>3995</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="H256" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I256" s="13" t="n">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="H258" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I258" s="13" t="n">
@@ -19690,14 +19690,14 @@
       </c>
       <c r="H264" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I264" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J264" s="14" t="n">
-        <v>2348</v>
+        <v>1409</v>
       </c>
       <c r="K264" s="14" t="n">
         <v>3757</v>
@@ -20482,14 +20482,14 @@
       </c>
       <c r="H275" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I275" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J275" s="21" t="n">
-        <v>1714</v>
+        <v>1524</v>
       </c>
       <c r="K275" s="21" t="n">
         <v>3238</v>
@@ -20554,14 +20554,14 @@
       </c>
       <c r="H276" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I276" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J276" s="14" t="n">
-        <v>1641</v>
+        <v>1552</v>
       </c>
       <c r="K276" s="14" t="n">
         <v>3193</v>
@@ -20626,14 +20626,14 @@
       </c>
       <c r="H277" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I277" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J277" s="21" t="n">
-        <v>1157</v>
+        <v>2025</v>
       </c>
       <c r="K277" s="21" t="n">
         <v>3182</v>
@@ -20842,14 +20842,14 @@
       </c>
       <c r="H280" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I280" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J280" s="14" t="n">
-        <v>1087</v>
+        <v>1979</v>
       </c>
       <c r="K280" s="14" t="n">
         <v>3066</v>
@@ -22354,14 +22354,14 @@
       </c>
       <c r="H301" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I301" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J301" s="21" t="n">
-        <v>1688</v>
+        <v>1061</v>
       </c>
       <c r="K301" s="21" t="n">
         <v>2749</v>
@@ -22858,14 +22858,14 @@
       </c>
       <c r="H308" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I308" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J308" s="14" t="n">
-        <v>1401</v>
+        <v>1134</v>
       </c>
       <c r="K308" s="14" t="n">
         <v>2535</v>
@@ -23002,14 +23002,14 @@
       </c>
       <c r="H310" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I310" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J310" s="14" t="n">
-        <v>1070</v>
+        <v>1457</v>
       </c>
       <c r="K310" s="14" t="n">
         <v>2527</v>
@@ -23506,14 +23506,14 @@
       </c>
       <c r="H317" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I317" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J317" s="21" t="n">
-        <v>1149</v>
+        <v>1261</v>
       </c>
       <c r="K317" s="21" t="n">
         <v>2410</v>
@@ -24298,7 +24298,7 @@
       </c>
       <c r="H328" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I328" s="13" t="n">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 10:17:21 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 04:48:56 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹5,303,053.00</t>
+          <t>₹5,317,843.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>300</v>
+        <v>204</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>3590595</v>
+        <v>3391731</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
@@ -1012,22 +1012,22 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>63e0416509bf7d00326f6ef9</t>
+          <t>641074ebef82f6001fb616b9</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>lws</t>
+          <t>careerintrading</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>omkar.vent@gmail.com</t>
+          <t>tusharjain100@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>9829012838</t>
+          <t>7224950865</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -1049,22 +1049,22 @@
         <v>2</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>46976</v>
+        <v>14790</v>
       </c>
       <c r="K5" s="21" t="n">
-        <v>93952</v>
+        <v>102129</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>46976</v>
+        <v>87339</v>
       </c>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>6a3e7980291f3d0013b550f9</t>
+          <t>649c358021ff91002bd79e9f</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3e7980291f3d0013b550f9</t>
+          <t>https://superprofile.bio/vig/649c358021ff91002bd79e9f</t>
         </is>
       </c>
       <c r="O5" s="24" t="inlineStr">
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>641074ebef82f6001fb616b9</t>
+          <t>63e0416509bf7d00326f6ef9</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>careerintrading</t>
+          <t>lws</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>tusharjain100@gmail.com</t>
+          <t>omkar.vent@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>7224950865</t>
+          <t>9829012838</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -1109,34 +1109,34 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I6" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>87339</v>
+        <v>46976</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>87339</v>
+        <v>93952</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>87339</v>
+        <v>46976</v>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>649c358021ff91002bd79e9f</t>
+          <t>6a3e7980291f3d0013b550f9</t>
         </is>
       </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/649c358021ff91002bd79e9f</t>
+          <t>https://superprofile.bio/vig/6a3e7980291f3d0013b550f9</t>
         </is>
       </c>
       <c r="O6" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 10:23:38 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 04:55:36 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>3386902</v>
+        <v>3391731</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3590595</v>
+        <v>3389553</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I13" s="20" t="n">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 04:55:36 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 04:57:26 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3389553</v>
+        <v>3379576</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 10:36:53 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 05:13:38 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>2156119</v>
+        <v>0</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-08-31 05:13:38 | Daily Audits Logged: 2</t>
+          <t>Generated On: 2026-08-31 10:07:03 | Daily Audits Logged: 2</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 10:11:27 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 04:47:48 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>4385088</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 04:47:48 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 10:33:03 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0</v>
+        <v>4385088</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 10:33:03 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 10:38:01 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 10:38:01 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 05:13:55 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 10:38:01 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 06:41:53 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 10:38:01 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 05:13:55 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 05:13:55 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 08:19:05 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-01 08:19:05 | Daily Audits Logged: 3</t>
+          <t>Generated On: 2026-09-01 08:57:03 | Daily Audits Logged: 3</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-02 09:54:20 | Daily Audits Logged: 4</t>
+          <t>Generated On: 2026-09-02 04:43:36 | Daily Audits Logged: 4</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-02 04:43:36 | Daily Audits Logged: 4</t>
+          <t>Generated On: 2026-09-02 07:46:05 | Daily Audits Logged: 4</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-02 07:46:05 | Daily Audits Logged: 4</t>
+          <t>Generated On: 2026-09-02 08:10:37 | Daily Audits Logged: 4</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-02 08:10:37 | Daily Audits Logged: 4</t>
+          <t>Generated On: 2026-09-02 08:36:11 | Daily Audits Logged: 4</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 10:51:04 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 05:29:19 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 05:29:19 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 07:55:17 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 07:55:17 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 08:19:52 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 08:19:52 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 08:45:01 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 10:51:04 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 16:06:23 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 16:06:23 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 16:10:51 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-03 16:10:51 | Daily Audits Logged: 5</t>
+          <t>Generated On: 2026-09-03 10:47:35 | Daily Audits Logged: 5</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-04 10:01:16 | Daily Audits Logged: 6</t>
+          <t>Generated On: 2026-09-04 04:36:56 | Daily Audits Logged: 6</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-04 04:36:56 | Daily Audits Logged: 6</t>
+          <t>Generated On: 2026-09-04 07:50:51 | Daily Audits Logged: 6</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-04 07:50:51 | Daily Audits Logged: 6</t>
+          <t>Generated On: 2026-09-04 08:15:45 | Daily Audits Logged: 6</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-04 08:15:45 | Daily Audits Logged: 6</t>
+          <t>Generated On: 2026-09-04 08:39:25 | Daily Audits Logged: 6</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:47:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 05:23:19 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:47:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 10:53:45 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:53:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 05:29:21 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:53:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 10:59:45 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:59:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 05:35:20 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:59:45 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 11:15:14 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 11:56:34 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 06:27:44 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>
@@ -593,11 +593,11 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹29,078,853.00</t>
+          <t>₹29,090,443.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>3777982</v>
+        <v>3789572</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P699"/>
+  <dimension ref="A1:P705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -785,7 +785,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
@@ -45166,59 +45166,59 @@
       </c>
       <c r="B617" s="20" t="inlineStr">
         <is>
-          <t>6856668cc5a2ba00132de15a</t>
+          <t>6a4bf7f1f111810013cba5ce</t>
         </is>
       </c>
       <c r="C617" s="20" t="inlineStr">
         <is>
-          <t>eaglesclub</t>
+          <t>insiderpedia</t>
         </is>
       </c>
       <c r="D617" s="19" t="inlineStr">
         <is>
-          <t>thelionstradingclub@gmail.com</t>
+          <t>insiderpedia@gmail.com</t>
         </is>
       </c>
       <c r="E617" s="19" t="inlineStr">
         <is>
-          <t>8708868105</t>
+          <t>8439150506</t>
         </is>
       </c>
       <c r="F617" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="G617" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H617" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I617" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J617" s="21" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="K617" s="21" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="L617" s="22" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="M617" s="19" t="inlineStr">
         <is>
-          <t>6857f6d6c357ae0013fa2b9d</t>
+          <t>68d3c6acdab36c001342c601</t>
         </is>
       </c>
       <c r="N617" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6857f6d6c357ae0013fa2b9d</t>
+          <t>https://superprofile.bio/vig/68d3c6acdab36c001342c601</t>
         </is>
       </c>
       <c r="O617" s="24" t="inlineStr">
@@ -45238,22 +45238,22 @@
       </c>
       <c r="B618" s="13" t="inlineStr">
         <is>
-          <t>65dedb00c9a3280013f2b031</t>
+          <t>6856668cc5a2ba00132de15a</t>
         </is>
       </c>
       <c r="C618" s="13" t="inlineStr">
         <is>
-          <t>rahulhans</t>
+          <t>eaglesclub</t>
         </is>
       </c>
       <c r="D618" s="12" t="inlineStr">
         <is>
-          <t>rahulhns41@gmail.com</t>
+          <t>thelionstradingclub@gmail.com</t>
         </is>
       </c>
       <c r="E618" s="12" t="inlineStr">
         <is>
-          <t>9138601433</t>
+          <t>8708868105</t>
         </is>
       </c>
       <c r="F618" s="12" t="inlineStr">
@@ -45268,29 +45268,29 @@
       </c>
       <c r="H618" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I618" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J618" s="14" t="n">
-        <v>1426</v>
+        <v>2857</v>
       </c>
       <c r="K618" s="14" t="n">
-        <v>2852</v>
+        <v>2857</v>
       </c>
       <c r="L618" s="15" t="n">
-        <v>1426</v>
+        <v>2857</v>
       </c>
       <c r="M618" s="12" t="inlineStr">
         <is>
-          <t>691966f3892ce60013fb6617</t>
+          <t>6857f6d6c357ae0013fa2b9d</t>
         </is>
       </c>
       <c r="N618" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/691966f3892ce60013fb6617</t>
+          <t>https://superprofile.bio/vig/6857f6d6c357ae0013fa2b9d</t>
         </is>
       </c>
       <c r="O618" s="17" t="inlineStr">
@@ -45310,22 +45310,22 @@
       </c>
       <c r="B619" s="20" t="inlineStr">
         <is>
-          <t>647d9398dd6b3d0020306128</t>
+          <t>65dedb00c9a3280013f2b031</t>
         </is>
       </c>
       <c r="C619" s="20" t="inlineStr">
         <is>
-          <t>kpinvestment</t>
+          <t>rahulhans</t>
         </is>
       </c>
       <c r="D619" s="19" t="inlineStr">
         <is>
-          <t>help.kpinvestment@gmail.com</t>
+          <t>rahulhns41@gmail.com</t>
         </is>
       </c>
       <c r="E619" s="19" t="inlineStr">
         <is>
-          <t>8160490424</t>
+          <t>9138601433</t>
         </is>
       </c>
       <c r="F619" s="19" t="inlineStr">
@@ -45335,34 +45335,34 @@
       </c>
       <c r="G619" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H619" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I619" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J619" s="21" t="n">
-        <v>2823</v>
+        <v>1426</v>
       </c>
       <c r="K619" s="21" t="n">
-        <v>2823</v>
+        <v>2852</v>
       </c>
       <c r="L619" s="22" t="n">
-        <v>2823</v>
+        <v>1426</v>
       </c>
       <c r="M619" s="19" t="inlineStr">
         <is>
-          <t>64d6fa8fedf0ae001ee54c49</t>
+          <t>691966f3892ce60013fb6617</t>
         </is>
       </c>
       <c r="N619" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64d6fa8fedf0ae001ee54c49</t>
+          <t>https://superprofile.bio/vig/691966f3892ce60013fb6617</t>
         </is>
       </c>
       <c r="O619" s="24" t="inlineStr">
@@ -45382,22 +45382,22 @@
       </c>
       <c r="B620" s="13" t="inlineStr">
         <is>
-          <t>65535c55ad8cfd001e27b0e3</t>
+          <t>647d9398dd6b3d0020306128</t>
         </is>
       </c>
       <c r="C620" s="13" t="inlineStr">
         <is>
-          <t>derivativetradersameer</t>
+          <t>kpinvestment</t>
         </is>
       </c>
       <c r="D620" s="12" t="inlineStr">
         <is>
-          <t>Samnit573@gmail.com</t>
+          <t>help.kpinvestment@gmail.com</t>
         </is>
       </c>
       <c r="E620" s="12" t="inlineStr">
         <is>
-          <t>7004760817</t>
+          <t>8160490424</t>
         </is>
       </c>
       <c r="F620" s="12" t="inlineStr">
@@ -45407,12 +45407,12 @@
       </c>
       <c r="G620" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H620" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I620" s="13" t="n">
@@ -45429,12 +45429,12 @@
       </c>
       <c r="M620" s="12" t="inlineStr">
         <is>
-          <t>681acdaf8684e10013d2bd41</t>
+          <t>64d6fa8fedf0ae001ee54c49</t>
         </is>
       </c>
       <c r="N620" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/681acdaf8684e10013d2bd41</t>
+          <t>https://superprofile.bio/vig/64d6fa8fedf0ae001ee54c49</t>
         </is>
       </c>
       <c r="O620" s="17" t="inlineStr">
@@ -45454,22 +45454,22 @@
       </c>
       <c r="B621" s="20" t="inlineStr">
         <is>
-          <t>6965edf1903a5c0013d1ccbc</t>
+          <t>65535c55ad8cfd001e27b0e3</t>
         </is>
       </c>
       <c r="C621" s="20" t="inlineStr">
         <is>
-          <t>presenttradingintelugu</t>
+          <t>derivativetradersameer</t>
         </is>
       </c>
       <c r="D621" s="19" t="inlineStr">
         <is>
-          <t>techrepresenttelugu@gmail.com</t>
+          <t>Samnit573@gmail.com</t>
         </is>
       </c>
       <c r="E621" s="19" t="inlineStr">
         <is>
-          <t>9640474466</t>
+          <t>7004760817</t>
         </is>
       </c>
       <c r="F621" s="19" t="inlineStr">
@@ -45479,34 +45479,34 @@
       </c>
       <c r="G621" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H621" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I621" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J621" s="21" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="K621" s="21" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="L621" s="22" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="M621" s="19" t="inlineStr">
         <is>
-          <t>6965f72391331700133f6bae</t>
+          <t>681acdaf8684e10013d2bd41</t>
         </is>
       </c>
       <c r="N621" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6965f72391331700133f6bae</t>
+          <t>https://superprofile.bio/vig/681acdaf8684e10013d2bd41</t>
         </is>
       </c>
       <c r="O621" s="24" t="inlineStr">
@@ -45526,22 +45526,22 @@
       </c>
       <c r="B622" s="13" t="inlineStr">
         <is>
-          <t>68fcd1a1390a76001310259f</t>
+          <t>6965edf1903a5c0013d1ccbc</t>
         </is>
       </c>
       <c r="C622" s="13" t="inlineStr">
         <is>
-          <t>hindustantrader985</t>
+          <t>presenttradingintelugu</t>
         </is>
       </c>
       <c r="D622" s="12" t="inlineStr">
         <is>
-          <t>vivekpatel75364@gmail.com</t>
+          <t>techrepresenttelugu@gmail.com</t>
         </is>
       </c>
       <c r="E622" s="12" t="inlineStr">
         <is>
-          <t>8003683727</t>
+          <t>9640474466</t>
         </is>
       </c>
       <c r="F622" s="12" t="inlineStr">
@@ -45551,12 +45551,12 @@
       </c>
       <c r="G622" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H622" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I622" s="13" t="n">
@@ -45573,12 +45573,12 @@
       </c>
       <c r="M622" s="12" t="inlineStr">
         <is>
-          <t>69328fb31485a2001397c7ac</t>
+          <t>6965f72391331700133f6bae</t>
         </is>
       </c>
       <c r="N622" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69328fb31485a2001397c7ac</t>
+          <t>https://superprofile.bio/vig/6965f72391331700133f6bae</t>
         </is>
       </c>
       <c r="O622" s="17" t="inlineStr">
@@ -45598,22 +45598,22 @@
       </c>
       <c r="B623" s="20" t="inlineStr">
         <is>
-          <t>6515aeec9433d3001ef9f2a2</t>
+          <t>68fcd1a1390a76001310259f</t>
         </is>
       </c>
       <c r="C623" s="20" t="inlineStr">
         <is>
-          <t>markethunterr</t>
+          <t>hindustantrader985</t>
         </is>
       </c>
       <c r="D623" s="19" t="inlineStr">
         <is>
-          <t>querymarketunterr@gmail.com</t>
+          <t>vivekpatel75364@gmail.com</t>
         </is>
       </c>
       <c r="E623" s="19" t="inlineStr">
         <is>
-          <t>9579525336</t>
+          <t>8003683727</t>
         </is>
       </c>
       <c r="F623" s="19" t="inlineStr">
@@ -45623,34 +45623,34 @@
       </c>
       <c r="G623" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H623" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I623" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J623" s="21" t="n">
-        <v>1411</v>
+        <v>2822</v>
       </c>
       <c r="K623" s="21" t="n">
         <v>2822</v>
       </c>
       <c r="L623" s="22" t="n">
-        <v>1411</v>
+        <v>2822</v>
       </c>
       <c r="M623" s="19" t="inlineStr">
         <is>
-          <t>6a9292ec59d38a00131346fa</t>
+          <t>69328fb31485a2001397c7ac</t>
         </is>
       </c>
       <c r="N623" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9292ec59d38a00131346fa</t>
+          <t>https://superprofile.bio/vig/69328fb31485a2001397c7ac</t>
         </is>
       </c>
       <c r="O623" s="24" t="inlineStr">
@@ -45670,22 +45670,22 @@
       </c>
       <c r="B624" s="13" t="inlineStr">
         <is>
-          <t>63d1296900efcd002c245c4d</t>
+          <t>6515aeec9433d3001ef9f2a2</t>
         </is>
       </c>
       <c r="C624" s="13" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>markethunterr</t>
         </is>
       </c>
       <c r="D624" s="12" t="inlineStr">
         <is>
-          <t>quicktrendindicator@gmail.com</t>
+          <t>querymarketunterr@gmail.com</t>
         </is>
       </c>
       <c r="E624" s="12" t="inlineStr">
         <is>
-          <t>9741745344</t>
+          <t>9579525336</t>
         </is>
       </c>
       <c r="F624" s="12" t="inlineStr">
@@ -45695,34 +45695,34 @@
       </c>
       <c r="G624" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H624" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I624" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J624" s="14" t="n">
-        <v>2796</v>
+        <v>1411</v>
       </c>
       <c r="K624" s="14" t="n">
-        <v>2796</v>
+        <v>2822</v>
       </c>
       <c r="L624" s="15" t="n">
-        <v>2796</v>
+        <v>1411</v>
       </c>
       <c r="M624" s="12" t="inlineStr">
         <is>
-          <t>6a1d0d0d66efb200138751ac</t>
+          <t>6a9292ec59d38a00131346fa</t>
         </is>
       </c>
       <c r="N624" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a1d0d0d66efb200138751ac</t>
+          <t>https://superprofile.bio/vig/6a9292ec59d38a00131346fa</t>
         </is>
       </c>
       <c r="O624" s="17" t="inlineStr">
@@ -45742,22 +45742,22 @@
       </c>
       <c r="B625" s="20" t="inlineStr">
         <is>
-          <t>64a1753cab80790020aadcfb</t>
+          <t>63d1296900efcd002c245c4d</t>
         </is>
       </c>
       <c r="C625" s="20" t="inlineStr">
         <is>
-          <t>Gourav2696</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="D625" s="19" t="inlineStr">
         <is>
-          <t>gouravdangi830@gmail.com</t>
+          <t>quicktrendindicator@gmail.com</t>
         </is>
       </c>
       <c r="E625" s="19" t="inlineStr">
         <is>
-          <t>9340549395</t>
+          <t>9741745344</t>
         </is>
       </c>
       <c r="F625" s="19" t="inlineStr">
@@ -45767,34 +45767,34 @@
       </c>
       <c r="G625" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H625" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I625" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J625" s="21" t="n">
-        <v>1539</v>
+        <v>2796</v>
       </c>
       <c r="K625" s="21" t="n">
-        <v>2790</v>
+        <v>2796</v>
       </c>
       <c r="L625" s="22" t="n">
-        <v>1539</v>
+        <v>2796</v>
       </c>
       <c r="M625" s="19" t="inlineStr">
         <is>
-          <t>6a463f963e42370013afb7f9</t>
+          <t>6a1d0d0d66efb200138751ac</t>
         </is>
       </c>
       <c r="N625" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a463f963e42370013afb7f9</t>
+          <t>https://superprofile.bio/vig/6a1d0d0d66efb200138751ac</t>
         </is>
       </c>
       <c r="O625" s="24" t="inlineStr">
@@ -45814,22 +45814,22 @@
       </c>
       <c r="B626" s="13" t="inlineStr">
         <is>
-          <t>69fb20dbfae26e0013229a6c</t>
+          <t>64a1753cab80790020aadcfb</t>
         </is>
       </c>
       <c r="C626" s="13" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>Gourav2696</t>
         </is>
       </c>
       <c r="D626" s="12" t="inlineStr">
         <is>
-          <t>rupeshbhagat1445@gmail.com</t>
+          <t>gouravdangi830@gmail.com</t>
         </is>
       </c>
       <c r="E626" s="12" t="inlineStr">
         <is>
-          <t>6397113270</t>
+          <t>9340549395</t>
         </is>
       </c>
       <c r="F626" s="12" t="inlineStr">
@@ -45839,34 +45839,34 @@
       </c>
       <c r="G626" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H626" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I626" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J626" s="14" t="n">
-        <v>1061</v>
+        <v>1539</v>
       </c>
       <c r="K626" s="14" t="n">
-        <v>2749</v>
+        <v>2790</v>
       </c>
       <c r="L626" s="15" t="n">
-        <v>1688</v>
+        <v>1539</v>
       </c>
       <c r="M626" s="12" t="inlineStr">
         <is>
-          <t>6a40e3e946bff60013350d9d</t>
+          <t>6a463f963e42370013afb7f9</t>
         </is>
       </c>
       <c r="N626" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
+          <t>https://superprofile.bio/vig/6a463f963e42370013afb7f9</t>
         </is>
       </c>
       <c r="O626" s="17" t="inlineStr">
@@ -45886,22 +45886,22 @@
       </c>
       <c r="B627" s="20" t="inlineStr">
         <is>
-          <t>6772d84a573cf00013c60e1b</t>
+          <t>69fb20dbfae26e0013229a6c</t>
         </is>
       </c>
       <c r="C627" s="20" t="inlineStr">
         <is>
-          <t>elliottmasti</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="D627" s="19" t="inlineStr">
         <is>
-          <t>vijayvsawant1997@gmail.com</t>
+          <t>rupeshbhagat1445@gmail.com</t>
         </is>
       </c>
       <c r="E627" s="19" t="inlineStr">
         <is>
-          <t>9766884324</t>
+          <t>6397113270</t>
         </is>
       </c>
       <c r="F627" s="19" t="inlineStr">
@@ -45911,34 +45911,34 @@
       </c>
       <c r="G627" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H627" s="19" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H627" s="19" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="I627" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J627" s="21" t="n">
-        <v>2700</v>
+        <v>1061</v>
       </c>
       <c r="K627" s="21" t="n">
-        <v>2700</v>
+        <v>2749</v>
       </c>
       <c r="L627" s="22" t="n">
-        <v>2700</v>
+        <v>1688</v>
       </c>
       <c r="M627" s="19" t="inlineStr">
         <is>
-          <t>69f1aa36808e890013cacb09</t>
+          <t>6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="N627" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f1aa36808e890013cacb09</t>
+          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="O627" s="24" t="inlineStr">
@@ -45958,22 +45958,22 @@
       </c>
       <c r="B628" s="13" t="inlineStr">
         <is>
-          <t>65ff2645cdd7340013f558ba</t>
+          <t>6772d84a573cf00013c60e1b</t>
         </is>
       </c>
       <c r="C628" s="13" t="inlineStr">
         <is>
-          <t>dgcametpapers</t>
+          <t>elliottmasti</t>
         </is>
       </c>
       <c r="D628" s="12" t="inlineStr">
         <is>
-          <t>examairways@gmail.com</t>
+          <t>vijayvsawant1997@gmail.com</t>
         </is>
       </c>
       <c r="E628" s="12" t="inlineStr">
         <is>
-          <t>9978638833</t>
+          <t>9766884324</t>
         </is>
       </c>
       <c r="F628" s="12" t="inlineStr">
@@ -45983,12 +45983,12 @@
       </c>
       <c r="G628" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H628" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I628" s="13" t="n">
@@ -46005,12 +46005,12 @@
       </c>
       <c r="M628" s="12" t="inlineStr">
         <is>
-          <t>65ff2831cf68d10013420bf5</t>
+          <t>69f1aa36808e890013cacb09</t>
         </is>
       </c>
       <c r="N628" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65ff2831cf68d10013420bf5</t>
+          <t>https://superprofile.bio/vig/69f1aa36808e890013cacb09</t>
         </is>
       </c>
       <c r="O628" s="17" t="inlineStr">
@@ -46030,22 +46030,22 @@
       </c>
       <c r="B629" s="20" t="inlineStr">
         <is>
-          <t>68c10b0bfe96b400137da7ed</t>
+          <t>65ff2645cdd7340013f558ba</t>
         </is>
       </c>
       <c r="C629" s="20" t="inlineStr">
         <is>
-          <t>tradewitharvind</t>
+          <t>dgcametpapers</t>
         </is>
       </c>
       <c r="D629" s="19" t="inlineStr">
         <is>
-          <t>dharmpalverma612@gmail.com</t>
+          <t>examairways@gmail.com</t>
         </is>
       </c>
       <c r="E629" s="19" t="inlineStr">
         <is>
-          <t>6375584399</t>
+          <t>9978638833</t>
         </is>
       </c>
       <c r="F629" s="19" t="inlineStr">
@@ -46055,34 +46055,34 @@
       </c>
       <c r="G629" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H629" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I629" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J629" s="21" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="K629" s="21" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="L629" s="22" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="M629" s="19" t="inlineStr">
         <is>
-          <t>68c11258fe96b400137e95cd</t>
+          <t>65ff2831cf68d10013420bf5</t>
         </is>
       </c>
       <c r="N629" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c11258fe96b400137e95cd</t>
+          <t>https://superprofile.bio/vig/65ff2831cf68d10013420bf5</t>
         </is>
       </c>
       <c r="O629" s="24" t="inlineStr">
@@ -46102,22 +46102,22 @@
       </c>
       <c r="B630" s="13" t="inlineStr">
         <is>
-          <t>68727633c835ab00139080d1</t>
+          <t>68c10b0bfe96b400137da7ed</t>
         </is>
       </c>
       <c r="C630" s="13" t="inlineStr">
         <is>
-          <t>disciplinetrader</t>
+          <t>tradewitharvind</t>
         </is>
       </c>
       <c r="D630" s="12" t="inlineStr">
         <is>
-          <t>rajesh25129@gmail.com</t>
+          <t>dharmpalverma612@gmail.com</t>
         </is>
       </c>
       <c r="E630" s="12" t="inlineStr">
         <is>
-          <t>7887205206</t>
+          <t>6375584399</t>
         </is>
       </c>
       <c r="F630" s="12" t="inlineStr">
@@ -46127,34 +46127,34 @@
       </c>
       <c r="G630" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H630" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I630" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J630" s="14" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="K630" s="14" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="L630" s="15" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="M630" s="12" t="inlineStr">
         <is>
-          <t>696b5f6c469b4600134e3e96</t>
+          <t>68c11258fe96b400137e95cd</t>
         </is>
       </c>
       <c r="N630" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696b5f6c469b4600134e3e96</t>
+          <t>https://superprofile.bio/vig/68c11258fe96b400137e95cd</t>
         </is>
       </c>
       <c r="O630" s="17" t="inlineStr">
@@ -46174,22 +46174,22 @@
       </c>
       <c r="B631" s="20" t="inlineStr">
         <is>
-          <t>6a8352777b63ce00137c8364</t>
+          <t>68727633c835ab00139080d1</t>
         </is>
       </c>
       <c r="C631" s="20" t="inlineStr">
         <is>
-          <t>bootcampadsfusionacademy</t>
+          <t>disciplinetrader</t>
         </is>
       </c>
       <c r="D631" s="19" t="inlineStr">
         <is>
-          <t>hakeemkp111@gmail.com</t>
+          <t>rajesh25129@gmail.com</t>
         </is>
       </c>
       <c r="E631" s="19" t="inlineStr">
         <is>
-          <t>7356250713</t>
+          <t>7887205206</t>
         </is>
       </c>
       <c r="F631" s="19" t="inlineStr">
@@ -46199,34 +46199,34 @@
       </c>
       <c r="G631" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H631" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I631" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J631" s="21" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="K631" s="21" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="L631" s="22" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="M631" s="19" t="inlineStr">
         <is>
-          <t>6a8463b0d51eef001369a03c</t>
+          <t>696b5f6c469b4600134e3e96</t>
         </is>
       </c>
       <c r="N631" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8463b0d51eef001369a03c</t>
+          <t>https://superprofile.bio/vig/696b5f6c469b4600134e3e96</t>
         </is>
       </c>
       <c r="O631" s="24" t="inlineStr">
@@ -46246,22 +46246,22 @@
       </c>
       <c r="B632" s="13" t="inlineStr">
         <is>
-          <t>65132965f4d0b1001eba9b70</t>
+          <t>6a8352777b63ce00137c8364</t>
         </is>
       </c>
       <c r="C632" s="13" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>bootcampadsfusionacademy</t>
         </is>
       </c>
       <c r="D632" s="12" t="inlineStr">
         <is>
-          <t>biswalfc@gmail.com</t>
+          <t>hakeemkp111@gmail.com</t>
         </is>
       </c>
       <c r="E632" s="12" t="inlineStr">
         <is>
-          <t>9658251426</t>
+          <t>7356250713</t>
         </is>
       </c>
       <c r="F632" s="12" t="inlineStr">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="G632" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H632" s="12" t="inlineStr">
@@ -46280,25 +46280,25 @@
         </is>
       </c>
       <c r="I632" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J632" s="14" t="n">
-        <v>1134</v>
+        <v>2538</v>
       </c>
       <c r="K632" s="14" t="n">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="L632" s="15" t="n">
-        <v>1401</v>
+        <v>2538</v>
       </c>
       <c r="M632" s="12" t="inlineStr">
         <is>
-          <t>6724fcbd76412b00139f3f43</t>
+          <t>6a8463b0d51eef001369a03c</t>
         </is>
       </c>
       <c r="N632" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
+          <t>https://superprofile.bio/vig/6a8463b0d51eef001369a03c</t>
         </is>
       </c>
       <c r="O632" s="17" t="inlineStr">
@@ -46318,22 +46318,22 @@
       </c>
       <c r="B633" s="20" t="inlineStr">
         <is>
-          <t>69157f06e3a0e3001373be01</t>
+          <t>65132965f4d0b1001eba9b70</t>
         </is>
       </c>
       <c r="C633" s="20" t="inlineStr">
         <is>
-          <t>ayushmarda</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="D633" s="19" t="inlineStr">
         <is>
-          <t>ayushmarda000@gmail.com</t>
+          <t>biswalfc@gmail.com</t>
         </is>
       </c>
       <c r="E633" s="19" t="inlineStr">
         <is>
-          <t>8007790099</t>
+          <t>9658251426</t>
         </is>
       </c>
       <c r="F633" s="19" t="inlineStr">
@@ -46343,34 +46343,34 @@
       </c>
       <c r="G633" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H633" s="19" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H633" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I633" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J633" s="21" t="n">
-        <v>1259</v>
+        <v>1134</v>
       </c>
       <c r="K633" s="21" t="n">
-        <v>2518</v>
+        <v>2535</v>
       </c>
       <c r="L633" s="22" t="n">
-        <v>1259</v>
+        <v>1401</v>
       </c>
       <c r="M633" s="19" t="inlineStr">
         <is>
-          <t>692e8f7a0454370012d339a1</t>
+          <t>6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="N633" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692e8f7a0454370012d339a1</t>
+          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="O633" s="24" t="inlineStr">
@@ -46390,22 +46390,22 @@
       </c>
       <c r="B634" s="13" t="inlineStr">
         <is>
-          <t>68496d1b267f07001316fae2</t>
+          <t>69157f06e3a0e3001373be01</t>
         </is>
       </c>
       <c r="C634" s="13" t="inlineStr">
         <is>
-          <t>Harsh3320</t>
+          <t>ayushmarda</t>
         </is>
       </c>
       <c r="D634" s="12" t="inlineStr">
         <is>
-          <t>harshchhura1998@gmail.com</t>
+          <t>ayushmarda000@gmail.com</t>
         </is>
       </c>
       <c r="E634" s="12" t="inlineStr">
         <is>
-          <t>9140171059</t>
+          <t>8007790099</t>
         </is>
       </c>
       <c r="F634" s="12" t="inlineStr">
@@ -46420,29 +46420,29 @@
       </c>
       <c r="H634" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I634" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J634" s="14" t="n">
-        <v>1048</v>
+        <v>1259</v>
       </c>
       <c r="K634" s="14" t="n">
-        <v>2494</v>
+        <v>2518</v>
       </c>
       <c r="L634" s="15" t="n">
-        <v>2096</v>
+        <v>1259</v>
       </c>
       <c r="M634" s="12" t="inlineStr">
         <is>
-          <t>695779059b6b5d00139242b9</t>
+          <t>692e8f7a0454370012d339a1</t>
         </is>
       </c>
       <c r="N634" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/695779059b6b5d00139242b9</t>
+          <t>https://superprofile.bio/vig/692e8f7a0454370012d339a1</t>
         </is>
       </c>
       <c r="O634" s="17" t="inlineStr">
@@ -46462,22 +46462,22 @@
       </c>
       <c r="B635" s="20" t="inlineStr">
         <is>
-          <t>667d25dd8fa7f30013731fe4</t>
+          <t>68496d1b267f07001316fae2</t>
         </is>
       </c>
       <c r="C635" s="20" t="inlineStr">
         <is>
-          <t>shivayindex</t>
+          <t>Harsh3320</t>
         </is>
       </c>
       <c r="D635" s="19" t="inlineStr">
         <is>
-          <t>shivayindex@gmail.com</t>
+          <t>harshchhura1998@gmail.com</t>
         </is>
       </c>
       <c r="E635" s="19" t="inlineStr">
         <is>
-          <t>7760026001</t>
+          <t>9140171059</t>
         </is>
       </c>
       <c r="F635" s="19" t="inlineStr">
@@ -46487,34 +46487,34 @@
       </c>
       <c r="G635" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H635" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I635" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J635" s="21" t="n">
-        <v>2471</v>
+        <v>1048</v>
       </c>
       <c r="K635" s="21" t="n">
-        <v>2471</v>
+        <v>2494</v>
       </c>
       <c r="L635" s="22" t="n">
-        <v>2471</v>
+        <v>2096</v>
       </c>
       <c r="M635" s="19" t="inlineStr">
         <is>
-          <t>667d3662cdab3f0014414ffe</t>
+          <t>695779059b6b5d00139242b9</t>
         </is>
       </c>
       <c r="N635" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/667d3662cdab3f0014414ffe</t>
+          <t>https://superprofile.bio/vig/695779059b6b5d00139242b9</t>
         </is>
       </c>
       <c r="O635" s="24" t="inlineStr">
@@ -46534,22 +46534,22 @@
       </c>
       <c r="B636" s="13" t="inlineStr">
         <is>
-          <t>69955dcab7a14d00134f6967</t>
+          <t>667d25dd8fa7f30013731fe4</t>
         </is>
       </c>
       <c r="C636" s="13" t="inlineStr">
         <is>
-          <t>Kapil4688</t>
+          <t>shivayindex</t>
         </is>
       </c>
       <c r="D636" s="12" t="inlineStr">
         <is>
-          <t>kapilchitroda6@gmail.com</t>
+          <t>shivayindex@gmail.com</t>
         </is>
       </c>
       <c r="E636" s="12" t="inlineStr">
         <is>
-          <t>9913641472</t>
+          <t>7760026001</t>
         </is>
       </c>
       <c r="F636" s="12" t="inlineStr">
@@ -46571,22 +46571,22 @@
         <v>1</v>
       </c>
       <c r="J636" s="14" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="K636" s="14" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="L636" s="15" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="M636" s="12" t="inlineStr">
         <is>
-          <t>69956ec366f1840013fb1972</t>
+          <t>667d3662cdab3f0014414ffe</t>
         </is>
       </c>
       <c r="N636" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69956ec366f1840013fb1972</t>
+          <t>https://superprofile.bio/vig/667d3662cdab3f0014414ffe</t>
         </is>
       </c>
       <c r="O636" s="17" t="inlineStr">
@@ -46606,22 +46606,22 @@
       </c>
       <c r="B637" s="20" t="inlineStr">
         <is>
-          <t>6497453f99a69e001f23154b</t>
+          <t>69955dcab7a14d00134f6967</t>
         </is>
       </c>
       <c r="C637" s="20" t="inlineStr">
         <is>
-          <t>abhaytrading</t>
+          <t>Kapil4688</t>
         </is>
       </c>
       <c r="D637" s="19" t="inlineStr">
         <is>
-          <t>abhaytradinglive@gmail.com</t>
+          <t>kapilchitroda6@gmail.com</t>
         </is>
       </c>
       <c r="E637" s="19" t="inlineStr">
         <is>
-          <t>6289427132</t>
+          <t>9913641472</t>
         </is>
       </c>
       <c r="F637" s="19" t="inlineStr">
@@ -46631,34 +46631,34 @@
       </c>
       <c r="G637" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H637" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I637" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J637" s="21" t="n">
-        <v>2434</v>
+        <v>2470</v>
       </c>
       <c r="K637" s="21" t="n">
-        <v>2434</v>
+        <v>2470</v>
       </c>
       <c r="L637" s="22" t="n">
-        <v>2434</v>
+        <v>2470</v>
       </c>
       <c r="M637" s="19" t="inlineStr">
         <is>
-          <t>69331b989bbbbf0013601185</t>
+          <t>69956ec366f1840013fb1972</t>
         </is>
       </c>
       <c r="N637" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69331b989bbbbf0013601185</t>
+          <t>https://superprofile.bio/vig/69956ec366f1840013fb1972</t>
         </is>
       </c>
       <c r="O637" s="24" t="inlineStr">
@@ -46678,22 +46678,22 @@
       </c>
       <c r="B638" s="13" t="inlineStr">
         <is>
-          <t>69c5265e2203a70013a81621</t>
+          <t>6497453f99a69e001f23154b</t>
         </is>
       </c>
       <c r="C638" s="13" t="inlineStr">
         <is>
-          <t>Haresh9504</t>
+          <t>abhaytrading</t>
         </is>
       </c>
       <c r="D638" s="12" t="inlineStr">
         <is>
-          <t>hareshbhata5623@gmail.com</t>
+          <t>abhaytradinglive@gmail.com</t>
         </is>
       </c>
       <c r="E638" s="12" t="inlineStr">
         <is>
-          <t>7046653069</t>
+          <t>6289427132</t>
         </is>
       </c>
       <c r="F638" s="12" t="inlineStr">
@@ -46703,34 +46703,34 @@
       </c>
       <c r="G638" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H638" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I638" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J638" s="14" t="n">
-        <v>2364</v>
+        <v>2434</v>
       </c>
       <c r="K638" s="14" t="n">
-        <v>2364</v>
+        <v>2434</v>
       </c>
       <c r="L638" s="15" t="n">
-        <v>2364</v>
+        <v>2434</v>
       </c>
       <c r="M638" s="12" t="inlineStr">
         <is>
-          <t>69ca1572e3c5910014470e51</t>
+          <t>69331b989bbbbf0013601185</t>
         </is>
       </c>
       <c r="N638" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca1572e3c5910014470e51</t>
+          <t>https://superprofile.bio/vig/69331b989bbbbf0013601185</t>
         </is>
       </c>
       <c r="O638" s="17" t="inlineStr">
@@ -46750,22 +46750,22 @@
       </c>
       <c r="B639" s="20" t="inlineStr">
         <is>
-          <t>6614c807442e34001b427d04</t>
+          <t>69c5265e2203a70013a81621</t>
         </is>
       </c>
       <c r="C639" s="20" t="inlineStr">
         <is>
-          <t>learningskills2024</t>
+          <t>Haresh9504</t>
         </is>
       </c>
       <c r="D639" s="19" t="inlineStr">
         <is>
-          <t>sureshbhobria@gmail.com</t>
+          <t>hareshbhata5623@gmail.com</t>
         </is>
       </c>
       <c r="E639" s="19" t="inlineStr">
         <is>
-          <t>9493980572</t>
+          <t>7046653069</t>
         </is>
       </c>
       <c r="F639" s="19" t="inlineStr">
@@ -46787,22 +46787,22 @@
         <v>1</v>
       </c>
       <c r="J639" s="21" t="n">
-        <v>2352</v>
+        <v>2364</v>
       </c>
       <c r="K639" s="21" t="n">
-        <v>2352</v>
+        <v>2364</v>
       </c>
       <c r="L639" s="22" t="n">
-        <v>2352</v>
+        <v>2364</v>
       </c>
       <c r="M639" s="19" t="inlineStr">
         <is>
-          <t>6625fc1f9ef1d500139994c9</t>
+          <t>69ca1572e3c5910014470e51</t>
         </is>
       </c>
       <c r="N639" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6625fc1f9ef1d500139994c9</t>
+          <t>https://superprofile.bio/vig/69ca1572e3c5910014470e51</t>
         </is>
       </c>
       <c r="O639" s="24" t="inlineStr">
@@ -46822,22 +46822,22 @@
       </c>
       <c r="B640" s="13" t="inlineStr">
         <is>
-          <t>68187755c1c1c000138da976</t>
+          <t>6614c807442e34001b427d04</t>
         </is>
       </c>
       <c r="C640" s="13" t="inlineStr">
         <is>
-          <t>swingandmomentum</t>
+          <t>learningskills2024</t>
         </is>
       </c>
       <c r="D640" s="12" t="inlineStr">
         <is>
-          <t>aroffical966@gmail.com</t>
+          <t>sureshbhobria@gmail.com</t>
         </is>
       </c>
       <c r="E640" s="12" t="inlineStr">
         <is>
-          <t>7568090936</t>
+          <t>9493980572</t>
         </is>
       </c>
       <c r="F640" s="12" t="inlineStr">
@@ -46859,22 +46859,22 @@
         <v>1</v>
       </c>
       <c r="J640" s="14" t="n">
-        <v>2266</v>
+        <v>2352</v>
       </c>
       <c r="K640" s="14" t="n">
-        <v>2266</v>
+        <v>2352</v>
       </c>
       <c r="L640" s="15" t="n">
-        <v>2266</v>
+        <v>2352</v>
       </c>
       <c r="M640" s="12" t="inlineStr">
         <is>
-          <t>6824337bd729e000139c8cad</t>
+          <t>6625fc1f9ef1d500139994c9</t>
         </is>
       </c>
       <c r="N640" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6824337bd729e000139c8cad</t>
+          <t>https://superprofile.bio/vig/6625fc1f9ef1d500139994c9</t>
         </is>
       </c>
       <c r="O640" s="17" t="inlineStr">
@@ -46894,22 +46894,22 @@
       </c>
       <c r="B641" s="20" t="inlineStr">
         <is>
-          <t>68538cf11838b3001339832b</t>
+          <t>68187755c1c1c000138da976</t>
         </is>
       </c>
       <c r="C641" s="20" t="inlineStr">
         <is>
-          <t>priyamysticpath</t>
+          <t>swingandmomentum</t>
         </is>
       </c>
       <c r="D641" s="19" t="inlineStr">
         <is>
-          <t>9priyaamishra@gmail.com</t>
+          <t>aroffical966@gmail.com</t>
         </is>
       </c>
       <c r="E641" s="19" t="inlineStr">
         <is>
-          <t>9118857790</t>
+          <t>7568090936</t>
         </is>
       </c>
       <c r="F641" s="19" t="inlineStr">
@@ -46919,34 +46919,34 @@
       </c>
       <c r="G641" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H641" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I641" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J641" s="21" t="n">
-        <v>1128</v>
+        <v>2266</v>
       </c>
       <c r="K641" s="21" t="n">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="L641" s="22" t="n">
-        <v>1128</v>
+        <v>2266</v>
       </c>
       <c r="M641" s="19" t="inlineStr">
         <is>
-          <t>6a08ab7d618c1400131e3293</t>
+          <t>6824337bd729e000139c8cad</t>
         </is>
       </c>
       <c r="N641" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a08ab7d618c1400131e3293</t>
+          <t>https://superprofile.bio/vig/6824337bd729e000139c8cad</t>
         </is>
       </c>
       <c r="O641" s="24" t="inlineStr">
@@ -46966,59 +46966,59 @@
       </c>
       <c r="B642" s="13" t="inlineStr">
         <is>
-          <t>6550fb1348d70d0a6565e5d3</t>
+          <t>67ad63172703020013099918</t>
         </is>
       </c>
       <c r="C642" s="13" t="inlineStr">
         <is>
-          <t>vibhor-aw</t>
+          <t>stockwithshreyash</t>
         </is>
       </c>
       <c r="D642" s="12" t="inlineStr">
         <is>
-          <t>vibhor.tomar@gmail.com</t>
+          <t>shreyashphanase@gmail.com</t>
         </is>
       </c>
       <c r="E642" s="12" t="inlineStr">
         <is>
-          <t>9986680598</t>
+          <t>7066533150</t>
         </is>
       </c>
       <c r="F642" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kkabir John</t>
         </is>
       </c>
       <c r="G642" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H642" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I642" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J642" s="14" t="n">
-        <v>2249</v>
+        <v>2256</v>
       </c>
       <c r="K642" s="14" t="n">
-        <v>2249</v>
+        <v>2256</v>
       </c>
       <c r="L642" s="15" t="n">
-        <v>2249</v>
+        <v>2256</v>
       </c>
       <c r="M642" s="12" t="inlineStr">
         <is>
-          <t>69db7be277163000147b374b</t>
+          <t>6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="N642" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69db7be277163000147b374b</t>
+          <t>https://superprofile.bio/vig/6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="O642" s="17" t="inlineStr">
@@ -47038,22 +47038,22 @@
       </c>
       <c r="B643" s="20" t="inlineStr">
         <is>
-          <t>637dc4e34f7c40002b76bbc0</t>
+          <t>68538cf11838b3001339832b</t>
         </is>
       </c>
       <c r="C643" s="20" t="inlineStr">
         <is>
-          <t>k989</t>
+          <t>priyamysticpath</t>
         </is>
       </c>
       <c r="D643" s="19" t="inlineStr">
         <is>
-          <t>limbachiyakaushik3@gmail.com</t>
+          <t>9priyaamishra@gmail.com</t>
         </is>
       </c>
       <c r="E643" s="19" t="inlineStr">
         <is>
-          <t>9879402061</t>
+          <t>9118857790</t>
         </is>
       </c>
       <c r="F643" s="19" t="inlineStr">
@@ -47063,34 +47063,34 @@
       </c>
       <c r="G643" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H643" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I643" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J643" s="21" t="n">
-        <v>2248</v>
+        <v>1128</v>
       </c>
       <c r="K643" s="21" t="n">
-        <v>2248</v>
+        <v>2256</v>
       </c>
       <c r="L643" s="22" t="n">
-        <v>2248</v>
+        <v>1128</v>
       </c>
       <c r="M643" s="19" t="inlineStr">
         <is>
-          <t>65b26a00d9f5df001eb963f4</t>
+          <t>6a08ab7d618c1400131e3293</t>
         </is>
       </c>
       <c r="N643" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65b26a00d9f5df001eb963f4</t>
+          <t>https://superprofile.bio/vig/6a08ab7d618c1400131e3293</t>
         </is>
       </c>
       <c r="O643" s="24" t="inlineStr">
@@ -47110,22 +47110,22 @@
       </c>
       <c r="B644" s="13" t="inlineStr">
         <is>
-          <t>67ec127cbca74f0013a6db1b</t>
+          <t>6550fb1348d70d0a6565e5d3</t>
         </is>
       </c>
       <c r="C644" s="13" t="inlineStr">
         <is>
-          <t>financewithajay</t>
+          <t>vibhor-aw</t>
         </is>
       </c>
       <c r="D644" s="12" t="inlineStr">
         <is>
-          <t>contact.financewithajay@gmail.com</t>
+          <t>vibhor.tomar@gmail.com</t>
         </is>
       </c>
       <c r="E644" s="12" t="inlineStr">
         <is>
-          <t>9772539711</t>
+          <t>9986680598</t>
         </is>
       </c>
       <c r="F644" s="12" t="inlineStr">
@@ -47135,34 +47135,34 @@
       </c>
       <c r="G644" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H644" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I644" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J644" s="14" t="n">
-        <v>2241</v>
+        <v>2249</v>
       </c>
       <c r="K644" s="14" t="n">
-        <v>2241</v>
+        <v>2249</v>
       </c>
       <c r="L644" s="15" t="n">
-        <v>2241</v>
+        <v>2249</v>
       </c>
       <c r="M644" s="12" t="inlineStr">
         <is>
-          <t>6a23e5e47e49330013137085</t>
+          <t>69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="N644" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a23e5e47e49330013137085</t>
+          <t>https://superprofile.bio/vig/69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="O644" s="17" t="inlineStr">
@@ -47182,22 +47182,22 @@
       </c>
       <c r="B645" s="20" t="inlineStr">
         <is>
-          <t>62fcd64e0031fa2b3302649b</t>
+          <t>637dc4e34f7c40002b76bbc0</t>
         </is>
       </c>
       <c r="C645" s="20" t="inlineStr">
         <is>
-          <t>nmta-</t>
+          <t>k989</t>
         </is>
       </c>
       <c r="D645" s="19" t="inlineStr">
         <is>
-          <t>Namdevmane23@gmail.com</t>
+          <t>limbachiyakaushik3@gmail.com</t>
         </is>
       </c>
       <c r="E645" s="19" t="inlineStr">
         <is>
-          <t>9850252283</t>
+          <t>9879402061</t>
         </is>
       </c>
       <c r="F645" s="19" t="inlineStr">
@@ -47207,34 +47207,34 @@
       </c>
       <c r="G645" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H645" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I645" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J645" s="21" t="n">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="K645" s="21" t="n">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="L645" s="22" t="n">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="M645" s="19" t="inlineStr">
         <is>
-          <t>62ff2e73bdd77b4291a5c288</t>
+          <t>65b26a00d9f5df001eb963f4</t>
         </is>
       </c>
       <c r="N645" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62ff2e73bdd77b4291a5c288</t>
+          <t>https://superprofile.bio/vig/65b26a00d9f5df001eb963f4</t>
         </is>
       </c>
       <c r="O645" s="24" t="inlineStr">
@@ -47254,22 +47254,22 @@
       </c>
       <c r="B646" s="13" t="inlineStr">
         <is>
-          <t>659208105c801e06f023a189</t>
+          <t>67ec127cbca74f0013a6db1b</t>
         </is>
       </c>
       <c r="C646" s="13" t="inlineStr">
         <is>
-          <t>upscnewspaper</t>
+          <t>financewithajay</t>
         </is>
       </c>
       <c r="D646" s="12" t="inlineStr">
         <is>
-          <t>lokizircon@gmail.com</t>
+          <t>contact.financewithajay@gmail.com</t>
         </is>
       </c>
       <c r="E646" s="12" t="inlineStr">
         <is>
-          <t>8076501613</t>
+          <t>9772539711</t>
         </is>
       </c>
       <c r="F646" s="12" t="inlineStr">
@@ -47284,29 +47284,29 @@
       </c>
       <c r="H646" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I646" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J646" s="14" t="n">
-        <v>1156</v>
+        <v>2241</v>
       </c>
       <c r="K646" s="14" t="n">
-        <v>2223</v>
+        <v>2241</v>
       </c>
       <c r="L646" s="15" t="n">
-        <v>1156</v>
+        <v>2241</v>
       </c>
       <c r="M646" s="12" t="inlineStr">
         <is>
-          <t>678b74430410b00014115634</t>
+          <t>6a23e5e47e49330013137085</t>
         </is>
       </c>
       <c r="N646" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/678b74430410b00014115634</t>
+          <t>https://superprofile.bio/vig/6a23e5e47e49330013137085</t>
         </is>
       </c>
       <c r="O646" s="17" t="inlineStr">
@@ -47326,22 +47326,22 @@
       </c>
       <c r="B647" s="20" t="inlineStr">
         <is>
-          <t>64a6df40de08fb0020605733</t>
+          <t>62fcd64e0031fa2b3302649b</t>
         </is>
       </c>
       <c r="C647" s="20" t="inlineStr">
         <is>
-          <t>priyanka8090</t>
+          <t>nmta-</t>
         </is>
       </c>
       <c r="D647" s="19" t="inlineStr">
         <is>
-          <t>drtarunkashyap123@gmail.com</t>
+          <t>Namdevmane23@gmail.com</t>
         </is>
       </c>
       <c r="E647" s="19" t="inlineStr">
         <is>
-          <t>9355701148</t>
+          <t>9850252283</t>
         </is>
       </c>
       <c r="F647" s="19" t="inlineStr">
@@ -47351,34 +47351,34 @@
       </c>
       <c r="G647" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H647" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I647" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J647" s="21" t="n">
-        <v>1080</v>
+        <v>2238</v>
       </c>
       <c r="K647" s="21" t="n">
-        <v>2160</v>
+        <v>2238</v>
       </c>
       <c r="L647" s="22" t="n">
-        <v>1080</v>
+        <v>2238</v>
       </c>
       <c r="M647" s="19" t="inlineStr">
         <is>
-          <t>64a8db7aee58cc002a13fe63</t>
+          <t>62ff2e73bdd77b4291a5c288</t>
         </is>
       </c>
       <c r="N647" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64a8db7aee58cc002a13fe63</t>
+          <t>https://superprofile.bio/vig/62ff2e73bdd77b4291a5c288</t>
         </is>
       </c>
       <c r="O647" s="24" t="inlineStr">
@@ -47398,22 +47398,22 @@
       </c>
       <c r="B648" s="13" t="inlineStr">
         <is>
-          <t>659b990d57f865001e1efa98</t>
+          <t>659208105c801e06f023a189</t>
         </is>
       </c>
       <c r="C648" s="13" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>upscnewspaper</t>
         </is>
       </c>
       <c r="D648" s="12" t="inlineStr">
         <is>
-          <t>vishalgaikwad91888@gmail.com</t>
+          <t>lokizircon@gmail.com</t>
         </is>
       </c>
       <c r="E648" s="12" t="inlineStr">
         <is>
-          <t>7040119684</t>
+          <t>8076501613</t>
         </is>
       </c>
       <c r="F648" s="12" t="inlineStr">
@@ -47423,34 +47423,34 @@
       </c>
       <c r="G648" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H648" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I648" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J648" s="14" t="n">
-        <v>1078</v>
+        <v>1156</v>
       </c>
       <c r="K648" s="14" t="n">
-        <v>2156</v>
+        <v>2223</v>
       </c>
       <c r="L648" s="15" t="n">
-        <v>1078</v>
+        <v>1156</v>
       </c>
       <c r="M648" s="12" t="inlineStr">
         <is>
-          <t>69f59765a8c2c60013505029</t>
+          <t>678b74430410b00014115634</t>
         </is>
       </c>
       <c r="N648" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
+          <t>https://superprofile.bio/vig/678b74430410b00014115634</t>
         </is>
       </c>
       <c r="O648" s="17" t="inlineStr">
@@ -47470,22 +47470,22 @@
       </c>
       <c r="B649" s="20" t="inlineStr">
         <is>
-          <t>6790d7e59cdd18001364c325</t>
+          <t>64a6df40de08fb0020605733</t>
         </is>
       </c>
       <c r="C649" s="20" t="inlineStr">
         <is>
-          <t>tga</t>
+          <t>priyanka8090</t>
         </is>
       </c>
       <c r="D649" s="19" t="inlineStr">
         <is>
-          <t>traders.guide2025@gmail.com</t>
+          <t>drtarunkashyap123@gmail.com</t>
         </is>
       </c>
       <c r="E649" s="19" t="inlineStr">
         <is>
-          <t>9106193633</t>
+          <t>9355701148</t>
         </is>
       </c>
       <c r="F649" s="19" t="inlineStr">
@@ -47495,34 +47495,34 @@
       </c>
       <c r="G649" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H649" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I649" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J649" s="21" t="n">
-        <v>2128</v>
+        <v>1080</v>
       </c>
       <c r="K649" s="21" t="n">
-        <v>2128</v>
+        <v>2160</v>
       </c>
       <c r="L649" s="22" t="n">
-        <v>2128</v>
+        <v>1080</v>
       </c>
       <c r="M649" s="19" t="inlineStr">
         <is>
-          <t>69e73f8208572d0014eb9576</t>
+          <t>64a8db7aee58cc002a13fe63</t>
         </is>
       </c>
       <c r="N649" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e73f8208572d0014eb9576</t>
+          <t>https://superprofile.bio/vig/64a8db7aee58cc002a13fe63</t>
         </is>
       </c>
       <c r="O649" s="24" t="inlineStr">
@@ -47542,22 +47542,22 @@
       </c>
       <c r="B650" s="13" t="inlineStr">
         <is>
-          <t>636c3a1fac6bc6003dbb97c3</t>
+          <t>659b990d57f865001e1efa98</t>
         </is>
       </c>
       <c r="C650" s="13" t="inlineStr">
         <is>
-          <t>pisignals</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="D650" s="12" t="inlineStr">
         <is>
-          <t>support@pisignals.com</t>
+          <t>vishalgaikwad91888@gmail.com</t>
         </is>
       </c>
       <c r="E650" s="12" t="inlineStr">
         <is>
-          <t>8087686830</t>
+          <t>7040119684</t>
         </is>
       </c>
       <c r="F650" s="12" t="inlineStr">
@@ -47567,34 +47567,34 @@
       </c>
       <c r="G650" s="12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H650" s="12" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H650" s="12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="I650" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J650" s="14" t="n">
-        <v>2100</v>
+        <v>1078</v>
       </c>
       <c r="K650" s="14" t="n">
-        <v>2100</v>
+        <v>2156</v>
       </c>
       <c r="L650" s="15" t="n">
-        <v>2100</v>
+        <v>1078</v>
       </c>
       <c r="M650" s="12" t="inlineStr">
         <is>
-          <t>6371e1aeb9bdd4003d6c0bdf</t>
+          <t>69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="N650" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6371e1aeb9bdd4003d6c0bdf</t>
+          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="O650" s="17" t="inlineStr">
@@ -47614,22 +47614,22 @@
       </c>
       <c r="B651" s="20" t="inlineStr">
         <is>
-          <t>699f1e6675134300132e01e6</t>
+          <t>6790d7e59cdd18001364c325</t>
         </is>
       </c>
       <c r="C651" s="20" t="inlineStr">
         <is>
-          <t>traderpihuu</t>
+          <t>tga</t>
         </is>
       </c>
       <c r="D651" s="19" t="inlineStr">
         <is>
-          <t>pihulearningjoin@gmail.com</t>
+          <t>traders.guide2025@gmail.com</t>
         </is>
       </c>
       <c r="E651" s="19" t="inlineStr">
         <is>
-          <t>6393912567</t>
+          <t>9106193633</t>
         </is>
       </c>
       <c r="F651" s="19" t="inlineStr">
@@ -47651,22 +47651,22 @@
         <v>1</v>
       </c>
       <c r="J651" s="21" t="n">
-        <v>2057</v>
+        <v>2128</v>
       </c>
       <c r="K651" s="21" t="n">
-        <v>2057</v>
+        <v>2128</v>
       </c>
       <c r="L651" s="22" t="n">
-        <v>2057</v>
+        <v>2128</v>
       </c>
       <c r="M651" s="19" t="inlineStr">
         <is>
-          <t>69bbaa83098b8c00135db027</t>
+          <t>69e73f8208572d0014eb9576</t>
         </is>
       </c>
       <c r="N651" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bbaa83098b8c00135db027</t>
+          <t>https://superprofile.bio/vig/69e73f8208572d0014eb9576</t>
         </is>
       </c>
       <c r="O651" s="24" t="inlineStr">
@@ -47686,22 +47686,22 @@
       </c>
       <c r="B652" s="13" t="inlineStr">
         <is>
-          <t>69b99c4bd4535b00137cb627</t>
+          <t>636c3a1fac6bc6003dbb97c3</t>
         </is>
       </c>
       <c r="C652" s="13" t="inlineStr">
         <is>
-          <t>lunarkio</t>
+          <t>pisignals</t>
         </is>
       </c>
       <c r="D652" s="12" t="inlineStr">
         <is>
-          <t>ahujadaksh2000@gmail.com</t>
+          <t>support@pisignals.com</t>
         </is>
       </c>
       <c r="E652" s="12" t="inlineStr">
         <is>
-          <t>7986554065</t>
+          <t>8087686830</t>
         </is>
       </c>
       <c r="F652" s="12" t="inlineStr">
@@ -47711,34 +47711,34 @@
       </c>
       <c r="G652" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H652" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I652" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J652" s="14" t="n">
-        <v>2021</v>
+        <v>2100</v>
       </c>
       <c r="K652" s="14" t="n">
-        <v>2021</v>
+        <v>2100</v>
       </c>
       <c r="L652" s="15" t="n">
-        <v>2021</v>
+        <v>2100</v>
       </c>
       <c r="M652" s="12" t="inlineStr">
         <is>
-          <t>6a5e8c86b4f0e8001420ee62</t>
+          <t>6371e1aeb9bdd4003d6c0bdf</t>
         </is>
       </c>
       <c r="N652" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5e8c86b4f0e8001420ee62</t>
+          <t>https://superprofile.bio/vig/6371e1aeb9bdd4003d6c0bdf</t>
         </is>
       </c>
       <c r="O652" s="17" t="inlineStr">
@@ -47758,22 +47758,22 @@
       </c>
       <c r="B653" s="20" t="inlineStr">
         <is>
-          <t>63257ee60a46af3e6e681d38</t>
+          <t>699f1e6675134300132e01e6</t>
         </is>
       </c>
       <c r="C653" s="20" t="inlineStr">
         <is>
-          <t>tradelikemantra</t>
+          <t>traderpihuu</t>
         </is>
       </c>
       <c r="D653" s="19" t="inlineStr">
         <is>
-          <t>kunwarvishal241@gmail.com</t>
+          <t>pihulearningjoin@gmail.com</t>
         </is>
       </c>
       <c r="E653" s="19" t="inlineStr">
         <is>
-          <t>8827370474</t>
+          <t>6393912567</t>
         </is>
       </c>
       <c r="F653" s="19" t="inlineStr">
@@ -47783,34 +47783,34 @@
       </c>
       <c r="G653" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H653" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I653" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J653" s="21" t="n">
-        <v>2001</v>
+        <v>2057</v>
       </c>
       <c r="K653" s="21" t="n">
-        <v>2001</v>
+        <v>2057</v>
       </c>
       <c r="L653" s="22" t="n">
-        <v>2001</v>
+        <v>2057</v>
       </c>
       <c r="M653" s="19" t="inlineStr">
         <is>
-          <t>632582d30a46af3e6e6822f1</t>
+          <t>69bbaa83098b8c00135db027</t>
         </is>
       </c>
       <c r="N653" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/632582d30a46af3e6e6822f1</t>
+          <t>https://superprofile.bio/vig/69bbaa83098b8c00135db027</t>
         </is>
       </c>
       <c r="O653" s="24" t="inlineStr">
@@ -47830,22 +47830,22 @@
       </c>
       <c r="B654" s="13" t="inlineStr">
         <is>
-          <t>69072bb4ae00150013d00d28</t>
+          <t>69b99c4bd4535b00137cb627</t>
         </is>
       </c>
       <c r="C654" s="13" t="inlineStr">
         <is>
-          <t>thelearning</t>
+          <t>lunarkio</t>
         </is>
       </c>
       <c r="D654" s="12" t="inlineStr">
         <is>
-          <t>xenik31898@lovleo.com</t>
+          <t>ahujadaksh2000@gmail.com</t>
         </is>
       </c>
       <c r="E654" s="12" t="inlineStr">
         <is>
-          <t>9669648431</t>
+          <t>7986554065</t>
         </is>
       </c>
       <c r="F654" s="12" t="inlineStr">
@@ -47855,34 +47855,34 @@
       </c>
       <c r="G654" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H654" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I654" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J654" s="14" t="n">
-        <v>1977</v>
+        <v>2021</v>
       </c>
       <c r="K654" s="14" t="n">
-        <v>1977</v>
+        <v>2021</v>
       </c>
       <c r="L654" s="15" t="n">
-        <v>1977</v>
+        <v>2021</v>
       </c>
       <c r="M654" s="12" t="inlineStr">
         <is>
-          <t>67ee600f6cfba0001396a350</t>
+          <t>6a5e8c86b4f0e8001420ee62</t>
         </is>
       </c>
       <c r="N654" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ee600f6cfba0001396a350</t>
+          <t>https://superprofile.bio/vig/6a5e8c86b4f0e8001420ee62</t>
         </is>
       </c>
       <c r="O654" s="17" t="inlineStr">
@@ -47902,22 +47902,22 @@
       </c>
       <c r="B655" s="20" t="inlineStr">
         <is>
-          <t>67dd417c2e848e001306dae2</t>
+          <t>63257ee60a46af3e6e681d38</t>
         </is>
       </c>
       <c r="C655" s="20" t="inlineStr">
         <is>
-          <t>kamakshiraheja</t>
+          <t>tradelikemantra</t>
         </is>
       </c>
       <c r="D655" s="19" t="inlineStr">
         <is>
-          <t>kamakshidhameja@gmail.com</t>
+          <t>kunwarvishal241@gmail.com</t>
         </is>
       </c>
       <c r="E655" s="19" t="inlineStr">
         <is>
-          <t>9819908232</t>
+          <t>8827370474</t>
         </is>
       </c>
       <c r="F655" s="19" t="inlineStr">
@@ -47939,22 +47939,22 @@
         <v>1</v>
       </c>
       <c r="J655" s="21" t="n">
-        <v>1976</v>
+        <v>2001</v>
       </c>
       <c r="K655" s="21" t="n">
-        <v>1976</v>
+        <v>2001</v>
       </c>
       <c r="L655" s="22" t="n">
-        <v>1976</v>
+        <v>2001</v>
       </c>
       <c r="M655" s="19" t="inlineStr">
         <is>
-          <t>693a7b20cd08d200134e762f</t>
+          <t>632582d30a46af3e6e6822f1</t>
         </is>
       </c>
       <c r="N655" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/693a7b20cd08d200134e762f</t>
+          <t>https://superprofile.bio/vig/632582d30a46af3e6e6822f1</t>
         </is>
       </c>
       <c r="O655" s="24" t="inlineStr">
@@ -47974,22 +47974,22 @@
       </c>
       <c r="B656" s="13" t="inlineStr">
         <is>
-          <t>66461a4a2526160013e088af</t>
+          <t>69072bb4ae00150013d00d28</t>
         </is>
       </c>
       <c r="C656" s="13" t="inlineStr">
         <is>
-          <t>vanaantmultiverse</t>
+          <t>thelearning</t>
         </is>
       </c>
       <c r="D656" s="12" t="inlineStr">
         <is>
-          <t>divinetarot808@gmail.com</t>
+          <t>xenik31898@lovleo.com</t>
         </is>
       </c>
       <c r="E656" s="12" t="inlineStr">
         <is>
-          <t>7017530919</t>
+          <t>9669648431</t>
         </is>
       </c>
       <c r="F656" s="12" t="inlineStr">
@@ -47999,34 +47999,34 @@
       </c>
       <c r="G656" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H656" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I656" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J656" s="14" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="K656" s="14" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="L656" s="15" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="M656" s="12" t="inlineStr">
         <is>
-          <t>66e80a09e49fa70013df7e9f</t>
+          <t>67ee600f6cfba0001396a350</t>
         </is>
       </c>
       <c r="N656" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66e80a09e49fa70013df7e9f</t>
+          <t>https://superprofile.bio/vig/67ee600f6cfba0001396a350</t>
         </is>
       </c>
       <c r="O656" s="17" t="inlineStr">
@@ -48046,22 +48046,22 @@
       </c>
       <c r="B657" s="20" t="inlineStr">
         <is>
-          <t>67fdc8680a272d0013949011</t>
+          <t>67dd417c2e848e001306dae2</t>
         </is>
       </c>
       <c r="C657" s="20" t="inlineStr">
         <is>
-          <t>madhavbanknifty</t>
+          <t>kamakshiraheja</t>
         </is>
       </c>
       <c r="D657" s="19" t="inlineStr">
         <is>
-          <t>ashvinbarot92@gmail.com</t>
+          <t>kamakshidhameja@gmail.com</t>
         </is>
       </c>
       <c r="E657" s="19" t="inlineStr">
         <is>
-          <t>7698089313</t>
+          <t>9819908232</t>
         </is>
       </c>
       <c r="F657" s="19" t="inlineStr">
@@ -48071,34 +48071,34 @@
       </c>
       <c r="G657" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H657" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I657" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J657" s="21" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="K657" s="21" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="L657" s="22" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="M657" s="19" t="inlineStr">
         <is>
-          <t>68073ef7f0df960013f5afe4</t>
+          <t>693a7b20cd08d200134e762f</t>
         </is>
       </c>
       <c r="N657" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68073ef7f0df960013f5afe4</t>
+          <t>https://superprofile.bio/vig/693a7b20cd08d200134e762f</t>
         </is>
       </c>
       <c r="O657" s="24" t="inlineStr">
@@ -48118,22 +48118,22 @@
       </c>
       <c r="B658" s="13" t="inlineStr">
         <is>
-          <t>650d7d75f8c83a001d1a9b22</t>
+          <t>66461a4a2526160013e088af</t>
         </is>
       </c>
       <c r="C658" s="13" t="inlineStr">
         <is>
-          <t>priceactioncourse</t>
+          <t>vanaantmultiverse</t>
         </is>
       </c>
       <c r="D658" s="12" t="inlineStr">
         <is>
-          <t>theplutotv@gmail.com</t>
+          <t>divinetarot808@gmail.com</t>
         </is>
       </c>
       <c r="E658" s="12" t="inlineStr">
         <is>
-          <t>9625222340</t>
+          <t>7017530919</t>
         </is>
       </c>
       <c r="F658" s="12" t="inlineStr">
@@ -48143,34 +48143,34 @@
       </c>
       <c r="G658" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H658" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I658" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J658" s="14" t="n">
-        <v>1940</v>
+        <v>1976</v>
       </c>
       <c r="K658" s="14" t="n">
-        <v>1940</v>
+        <v>1976</v>
       </c>
       <c r="L658" s="15" t="n">
-        <v>1940</v>
+        <v>1976</v>
       </c>
       <c r="M658" s="12" t="inlineStr">
         <is>
-          <t>6627984036843f001375093b</t>
+          <t>66e80a09e49fa70013df7e9f</t>
         </is>
       </c>
       <c r="N658" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6627984036843f001375093b</t>
+          <t>https://superprofile.bio/vig/66e80a09e49fa70013df7e9f</t>
         </is>
       </c>
       <c r="O658" s="17" t="inlineStr">
@@ -48190,22 +48190,22 @@
       </c>
       <c r="B659" s="20" t="inlineStr">
         <is>
-          <t>656404ed5929eb0029d9df20</t>
+          <t>67fdc8680a272d0013949011</t>
         </is>
       </c>
       <c r="C659" s="20" t="inlineStr">
         <is>
-          <t>TheOutlook</t>
+          <t>madhavbanknifty</t>
         </is>
       </c>
       <c r="D659" s="19" t="inlineStr">
         <is>
-          <t>Gdu1618@gmail.com</t>
+          <t>ashvinbarot92@gmail.com</t>
         </is>
       </c>
       <c r="E659" s="19" t="inlineStr">
         <is>
-          <t>8360942366</t>
+          <t>7698089313</t>
         </is>
       </c>
       <c r="F659" s="19" t="inlineStr">
@@ -48215,34 +48215,34 @@
       </c>
       <c r="G659" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H659" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I659" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J659" s="21" t="n">
-        <v>1928</v>
+        <v>1952</v>
       </c>
       <c r="K659" s="21" t="n">
-        <v>1928</v>
+        <v>1952</v>
       </c>
       <c r="L659" s="22" t="n">
-        <v>1928</v>
+        <v>1952</v>
       </c>
       <c r="M659" s="19" t="inlineStr">
         <is>
-          <t>6992e4fd0fc07c0013dceef5</t>
+          <t>68073ef7f0df960013f5afe4</t>
         </is>
       </c>
       <c r="N659" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6992e4fd0fc07c0013dceef5</t>
+          <t>https://superprofile.bio/vig/68073ef7f0df960013f5afe4</t>
         </is>
       </c>
       <c r="O659" s="24" t="inlineStr">
@@ -48262,59 +48262,59 @@
       </c>
       <c r="B660" s="13" t="inlineStr">
         <is>
-          <t>6799b5fe5229a200134ae372</t>
+          <t>69a2adacccc9e60013257a64</t>
         </is>
       </c>
       <c r="C660" s="13" t="inlineStr">
         <is>
-          <t>zerohero110</t>
+          <t>teyesi</t>
         </is>
       </c>
       <c r="D660" s="12" t="inlineStr">
         <is>
-          <t>zerheropremium230@gmail.com</t>
+          <t>stocktrader0050@gmail.com</t>
         </is>
       </c>
       <c r="E660" s="12" t="inlineStr">
         <is>
-          <t>9166230130</t>
+          <t>9096857617</t>
         </is>
       </c>
       <c r="F660" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mohit Singh</t>
         </is>
       </c>
       <c r="G660" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H660" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I660" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J660" s="14" t="n">
-        <v>1927</v>
+        <v>1951</v>
       </c>
       <c r="K660" s="14" t="n">
-        <v>1927</v>
+        <v>1951</v>
       </c>
       <c r="L660" s="15" t="n">
-        <v>1927</v>
+        <v>1951</v>
       </c>
       <c r="M660" s="12" t="inlineStr">
         <is>
-          <t>687e0fcb5399a5001312665f</t>
+          <t>6a133abc88bf0a0013e0af7b</t>
         </is>
       </c>
       <c r="N660" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687e0fcb5399a5001312665f</t>
+          <t>https://superprofile.bio/vig/6a133abc88bf0a0013e0af7b</t>
         </is>
       </c>
       <c r="O660" s="17" t="inlineStr">
@@ -48334,22 +48334,22 @@
       </c>
       <c r="B661" s="20" t="inlineStr">
         <is>
-          <t>66878b370bfc9f0013f8aab2</t>
+          <t>650d7d75f8c83a001d1a9b22</t>
         </is>
       </c>
       <c r="C661" s="20" t="inlineStr">
         <is>
-          <t>thattraderstories</t>
+          <t>priceactioncourse</t>
         </is>
       </c>
       <c r="D661" s="19" t="inlineStr">
         <is>
-          <t>giksongeorge@gmail.com</t>
+          <t>theplutotv@gmail.com</t>
         </is>
       </c>
       <c r="E661" s="19" t="inlineStr">
         <is>
-          <t>9910419041</t>
+          <t>9625222340</t>
         </is>
       </c>
       <c r="F661" s="19" t="inlineStr">
@@ -48359,34 +48359,34 @@
       </c>
       <c r="G661" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H661" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I661" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J661" s="21" t="n">
-        <v>1926</v>
+        <v>1940</v>
       </c>
       <c r="K661" s="21" t="n">
-        <v>1926</v>
+        <v>1940</v>
       </c>
       <c r="L661" s="22" t="n">
-        <v>1926</v>
+        <v>1940</v>
       </c>
       <c r="M661" s="19" t="inlineStr">
         <is>
-          <t>6a5f4719c1ef5e00131e7d17</t>
+          <t>6627984036843f001375093b</t>
         </is>
       </c>
       <c r="N661" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5f4719c1ef5e00131e7d17</t>
+          <t>https://superprofile.bio/vig/6627984036843f001375093b</t>
         </is>
       </c>
       <c r="O661" s="24" t="inlineStr">
@@ -48406,22 +48406,22 @@
       </c>
       <c r="B662" s="13" t="inlineStr">
         <is>
-          <t>67600b1b39b60f0013d996e2</t>
+          <t>656404ed5929eb0029d9df20</t>
         </is>
       </c>
       <c r="C662" s="13" t="inlineStr">
         <is>
-          <t>saima0786</t>
+          <t>TheOutlook</t>
         </is>
       </c>
       <c r="D662" s="12" t="inlineStr">
         <is>
-          <t>Saimashahnawaz130@gmail.com</t>
+          <t>Gdu1618@gmail.com</t>
         </is>
       </c>
       <c r="E662" s="12" t="inlineStr">
         <is>
-          <t>8100541237</t>
+          <t>8360942366</t>
         </is>
       </c>
       <c r="F662" s="12" t="inlineStr">
@@ -48431,34 +48431,34 @@
       </c>
       <c r="G662" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H662" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I662" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J662" s="14" t="n">
-        <v>1916</v>
+        <v>1928</v>
       </c>
       <c r="K662" s="14" t="n">
-        <v>1916</v>
+        <v>1928</v>
       </c>
       <c r="L662" s="15" t="n">
-        <v>1916</v>
+        <v>1928</v>
       </c>
       <c r="M662" s="12" t="inlineStr">
         <is>
-          <t>69c3dba01eb3cc001300f9a9</t>
+          <t>6992e4fd0fc07c0013dceef5</t>
         </is>
       </c>
       <c r="N662" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c3dba01eb3cc001300f9a9</t>
+          <t>https://superprofile.bio/vig/6992e4fd0fc07c0013dceef5</t>
         </is>
       </c>
       <c r="O662" s="17" t="inlineStr">
@@ -48478,22 +48478,22 @@
       </c>
       <c r="B663" s="20" t="inlineStr">
         <is>
-          <t>653d2bce423d4e001ee4dd1d</t>
+          <t>6799b5fe5229a200134ae372</t>
         </is>
       </c>
       <c r="C663" s="20" t="inlineStr">
         <is>
-          <t>cainvestor</t>
+          <t>zerohero110</t>
         </is>
       </c>
       <c r="D663" s="19" t="inlineStr">
         <is>
-          <t>multibaggerinvestor11@gmail.com</t>
+          <t>zerheropremium230@gmail.com</t>
         </is>
       </c>
       <c r="E663" s="19" t="inlineStr">
         <is>
-          <t>8830932954</t>
+          <t>9166230130</t>
         </is>
       </c>
       <c r="F663" s="19" t="inlineStr">
@@ -48515,22 +48515,22 @@
         <v>1</v>
       </c>
       <c r="J663" s="21" t="n">
-        <v>1904</v>
+        <v>1927</v>
       </c>
       <c r="K663" s="21" t="n">
-        <v>1904</v>
+        <v>1927</v>
       </c>
       <c r="L663" s="22" t="n">
-        <v>1904</v>
+        <v>1927</v>
       </c>
       <c r="M663" s="19" t="inlineStr">
         <is>
-          <t>6794368b20a3e90013310b49</t>
+          <t>687e0fcb5399a5001312665f</t>
         </is>
       </c>
       <c r="N663" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6794368b20a3e90013310b49</t>
+          <t>https://superprofile.bio/vig/687e0fcb5399a5001312665f</t>
         </is>
       </c>
       <c r="O663" s="24" t="inlineStr">
@@ -48550,22 +48550,22 @@
       </c>
       <c r="B664" s="13" t="inlineStr">
         <is>
-          <t>67506cec64fe550013dd58c8</t>
+          <t>66878b370bfc9f0013f8aab2</t>
         </is>
       </c>
       <c r="C664" s="13" t="inlineStr">
         <is>
-          <t>level2traders</t>
+          <t>thattraderstories</t>
         </is>
       </c>
       <c r="D664" s="12" t="inlineStr">
         <is>
-          <t>renjuu.pais@gmail.com</t>
+          <t>giksongeorge@gmail.com</t>
         </is>
       </c>
       <c r="E664" s="12" t="inlineStr">
         <is>
-          <t>9995015768</t>
+          <t>9910419041</t>
         </is>
       </c>
       <c r="F664" s="12" t="inlineStr">
@@ -48587,22 +48587,22 @@
         <v>1</v>
       </c>
       <c r="J664" s="14" t="n">
-        <v>1899</v>
+        <v>1926</v>
       </c>
       <c r="K664" s="14" t="n">
-        <v>1899</v>
+        <v>1926</v>
       </c>
       <c r="L664" s="15" t="n">
-        <v>1899</v>
+        <v>1926</v>
       </c>
       <c r="M664" s="12" t="inlineStr">
         <is>
-          <t>69035024a37225001314a9b9</t>
+          <t>6a5f4719c1ef5e00131e7d17</t>
         </is>
       </c>
       <c r="N664" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69035024a37225001314a9b9</t>
+          <t>https://superprofile.bio/vig/6a5f4719c1ef5e00131e7d17</t>
         </is>
       </c>
       <c r="O664" s="17" t="inlineStr">
@@ -48622,22 +48622,22 @@
       </c>
       <c r="B665" s="20" t="inlineStr">
         <is>
-          <t>64c7f6aa009c3c001e206fa4</t>
+          <t>67600b1b39b60f0013d996e2</t>
         </is>
       </c>
       <c r="C665" s="20" t="inlineStr">
         <is>
-          <t>deepakwadhwaguruji</t>
+          <t>saima0786</t>
         </is>
       </c>
       <c r="D665" s="19" t="inlineStr">
         <is>
-          <t>monumee966085@gmail.com</t>
+          <t>Saimashahnawaz130@gmail.com</t>
         </is>
       </c>
       <c r="E665" s="19" t="inlineStr">
         <is>
-          <t>9772977600</t>
+          <t>8100541237</t>
         </is>
       </c>
       <c r="F665" s="19" t="inlineStr">
@@ -48647,34 +48647,34 @@
       </c>
       <c r="G665" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H665" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I665" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J665" s="21" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="K665" s="21" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="L665" s="22" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="M665" s="19" t="inlineStr">
         <is>
-          <t>6a5c7ae2002e310013423007</t>
+          <t>69c3dba01eb3cc001300f9a9</t>
         </is>
       </c>
       <c r="N665" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5c7ae2002e310013423007</t>
+          <t>https://superprofile.bio/vig/69c3dba01eb3cc001300f9a9</t>
         </is>
       </c>
       <c r="O665" s="24" t="inlineStr">
@@ -48694,22 +48694,22 @@
       </c>
       <c r="B666" s="13" t="inlineStr">
         <is>
-          <t>64d0b757596d8a001d266a41</t>
+          <t>653d2bce423d4e001ee4dd1d</t>
         </is>
       </c>
       <c r="C666" s="13" t="inlineStr">
         <is>
-          <t>kkstockbtacademy</t>
+          <t>cainvestor</t>
         </is>
       </c>
       <c r="D666" s="12" t="inlineStr">
         <is>
-          <t>prasunb34@gmail.com</t>
+          <t>multibaggerinvestor11@gmail.com</t>
         </is>
       </c>
       <c r="E666" s="12" t="inlineStr">
         <is>
-          <t>8348726471</t>
+          <t>8830932954</t>
         </is>
       </c>
       <c r="F666" s="12" t="inlineStr">
@@ -48719,34 +48719,34 @@
       </c>
       <c r="G666" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H666" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I666" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J666" s="14" t="n">
-        <v>1881</v>
+        <v>1904</v>
       </c>
       <c r="K666" s="14" t="n">
-        <v>1881</v>
+        <v>1904</v>
       </c>
       <c r="L666" s="15" t="n">
-        <v>1881</v>
+        <v>1904</v>
       </c>
       <c r="M666" s="12" t="inlineStr">
         <is>
-          <t>6a91e241282ef200131da755</t>
+          <t>6794368b20a3e90013310b49</t>
         </is>
       </c>
       <c r="N666" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a91e241282ef200131da755</t>
+          <t>https://superprofile.bio/vig/6794368b20a3e90013310b49</t>
         </is>
       </c>
       <c r="O666" s="17" t="inlineStr">
@@ -48766,22 +48766,22 @@
       </c>
       <c r="B667" s="20" t="inlineStr">
         <is>
-          <t>65cd763e8b84610029a550ab</t>
+          <t>67506cec64fe550013dd58c8</t>
         </is>
       </c>
       <c r="C667" s="20" t="inlineStr">
         <is>
-          <t>pioneerws</t>
+          <t>level2traders</t>
         </is>
       </c>
       <c r="D667" s="19" t="inlineStr">
         <is>
-          <t>shetevaibhav@gmail.com</t>
+          <t>renjuu.pais@gmail.com</t>
         </is>
       </c>
       <c r="E667" s="19" t="inlineStr">
         <is>
-          <t>9820489820</t>
+          <t>9995015768</t>
         </is>
       </c>
       <c r="F667" s="19" t="inlineStr">
@@ -48803,22 +48803,22 @@
         <v>1</v>
       </c>
       <c r="J667" s="21" t="n">
-        <v>1881</v>
+        <v>1899</v>
       </c>
       <c r="K667" s="21" t="n">
-        <v>1881</v>
+        <v>1899</v>
       </c>
       <c r="L667" s="22" t="n">
-        <v>1881</v>
+        <v>1899</v>
       </c>
       <c r="M667" s="19" t="inlineStr">
         <is>
-          <t>65d8fcd412af0500144f83cc</t>
+          <t>69035024a37225001314a9b9</t>
         </is>
       </c>
       <c r="N667" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65d8fcd412af0500144f83cc</t>
+          <t>https://superprofile.bio/vig/69035024a37225001314a9b9</t>
         </is>
       </c>
       <c r="O667" s="24" t="inlineStr">
@@ -48838,22 +48838,22 @@
       </c>
       <c r="B668" s="13" t="inlineStr">
         <is>
-          <t>6880988ef959ac0013076234</t>
+          <t>64c7f6aa009c3c001e206fa4</t>
         </is>
       </c>
       <c r="C668" s="13" t="inlineStr">
         <is>
-          <t>heyitspriyankasingh</t>
+          <t>deepakwadhwaguruji</t>
         </is>
       </c>
       <c r="D668" s="12" t="inlineStr">
         <is>
-          <t>priyanka.singhmgnt@gmail.com</t>
+          <t>monumee966085@gmail.com</t>
         </is>
       </c>
       <c r="E668" s="12" t="inlineStr">
         <is>
-          <t>9399019263</t>
+          <t>9772977600</t>
         </is>
       </c>
       <c r="F668" s="12" t="inlineStr">
@@ -48863,34 +48863,34 @@
       </c>
       <c r="G668" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H668" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I668" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J668" s="14" t="n">
-        <v>1873</v>
+        <v>1890</v>
       </c>
       <c r="K668" s="14" t="n">
-        <v>1873</v>
+        <v>1890</v>
       </c>
       <c r="L668" s="15" t="n">
-        <v>1873</v>
+        <v>1890</v>
       </c>
       <c r="M668" s="12" t="inlineStr">
         <is>
-          <t>6a92e2b6f6013c00133e3e5d</t>
+          <t>6a5c7ae2002e310013423007</t>
         </is>
       </c>
       <c r="N668" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a92e2b6f6013c00133e3e5d</t>
+          <t>https://superprofile.bio/vig/6a5c7ae2002e310013423007</t>
         </is>
       </c>
       <c r="O668" s="17" t="inlineStr">
@@ -48910,22 +48910,22 @@
       </c>
       <c r="B669" s="20" t="inlineStr">
         <is>
-          <t>6478b051107b57001f86f918</t>
+          <t>64d0b757596d8a001d266a41</t>
         </is>
       </c>
       <c r="C669" s="20" t="inlineStr">
         <is>
-          <t>srptrader</t>
+          <t>kkstockbtacademy</t>
         </is>
       </c>
       <c r="D669" s="19" t="inlineStr">
         <is>
-          <t>jaymaajaymaa330@gmail.com</t>
+          <t>prasunb34@gmail.com</t>
         </is>
       </c>
       <c r="E669" s="19" t="inlineStr">
         <is>
-          <t>6377083526</t>
+          <t>8348726471</t>
         </is>
       </c>
       <c r="F669" s="19" t="inlineStr">
@@ -48935,34 +48935,34 @@
       </c>
       <c r="G669" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H669" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I669" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J669" s="21" t="n">
-        <v>1799</v>
+        <v>1881</v>
       </c>
       <c r="K669" s="21" t="n">
-        <v>1799</v>
+        <v>1881</v>
       </c>
       <c r="L669" s="22" t="n">
-        <v>1799</v>
+        <v>1881</v>
       </c>
       <c r="M669" s="19" t="inlineStr">
         <is>
-          <t>66f2e10389f9ce0013483dc0</t>
+          <t>6a91e241282ef200131da755</t>
         </is>
       </c>
       <c r="N669" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66f2e10389f9ce0013483dc0</t>
+          <t>https://superprofile.bio/vig/6a91e241282ef200131da755</t>
         </is>
       </c>
       <c r="O669" s="24" t="inlineStr">
@@ -48982,22 +48982,22 @@
       </c>
       <c r="B670" s="13" t="inlineStr">
         <is>
-          <t>656776a2d7de9b001e22044a</t>
+          <t>65cd763e8b84610029a550ab</t>
         </is>
       </c>
       <c r="C670" s="13" t="inlineStr">
         <is>
-          <t>tsunami07</t>
+          <t>pioneerws</t>
         </is>
       </c>
       <c r="D670" s="12" t="inlineStr">
         <is>
-          <t>shubh050701@gmail.com</t>
+          <t>shetevaibhav@gmail.com</t>
         </is>
       </c>
       <c r="E670" s="12" t="inlineStr">
         <is>
-          <t>8765220711</t>
+          <t>9820489820</t>
         </is>
       </c>
       <c r="F670" s="12" t="inlineStr">
@@ -49007,34 +49007,34 @@
       </c>
       <c r="G670" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H670" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I670" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J670" s="14" t="n">
-        <v>1786</v>
+        <v>1881</v>
       </c>
       <c r="K670" s="14" t="n">
-        <v>1786</v>
+        <v>1881</v>
       </c>
       <c r="L670" s="15" t="n">
-        <v>1786</v>
+        <v>1881</v>
       </c>
       <c r="M670" s="12" t="inlineStr">
         <is>
-          <t>6a0a982b37a61300137fcec1</t>
+          <t>65d8fcd412af0500144f83cc</t>
         </is>
       </c>
       <c r="N670" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a0a982b37a61300137fcec1</t>
+          <t>https://superprofile.bio/vig/65d8fcd412af0500144f83cc</t>
         </is>
       </c>
       <c r="O670" s="17" t="inlineStr">
@@ -49054,22 +49054,22 @@
       </c>
       <c r="B671" s="20" t="inlineStr">
         <is>
-          <t>6475a085f68c8e0020340ef5</t>
+          <t>6880988ef959ac0013076234</t>
         </is>
       </c>
       <c r="C671" s="20" t="inlineStr">
         <is>
-          <t>jd24education</t>
+          <t>heyitspriyankasingh</t>
         </is>
       </c>
       <c r="D671" s="19" t="inlineStr">
         <is>
-          <t>jd24education@gmail.com</t>
+          <t>priyanka.singhmgnt@gmail.com</t>
         </is>
       </c>
       <c r="E671" s="19" t="inlineStr">
         <is>
-          <t>8002550026</t>
+          <t>9399019263</t>
         </is>
       </c>
       <c r="F671" s="19" t="inlineStr">
@@ -49079,34 +49079,34 @@
       </c>
       <c r="G671" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H671" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I671" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J671" s="21" t="n">
-        <v>1773</v>
+        <v>1873</v>
       </c>
       <c r="K671" s="21" t="n">
-        <v>1773</v>
+        <v>1873</v>
       </c>
       <c r="L671" s="22" t="n">
-        <v>1773</v>
+        <v>1873</v>
       </c>
       <c r="M671" s="19" t="inlineStr">
         <is>
-          <t>6582cd2325f8a7001ebe8d03</t>
+          <t>6a92e2b6f6013c00133e3e5d</t>
         </is>
       </c>
       <c r="N671" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6582cd2325f8a7001ebe8d03</t>
+          <t>https://superprofile.bio/vig/6a92e2b6f6013c00133e3e5d</t>
         </is>
       </c>
       <c r="O671" s="24" t="inlineStr">
@@ -49126,22 +49126,22 @@
       </c>
       <c r="B672" s="13" t="inlineStr">
         <is>
-          <t>650ff72bf8c83a001d33ca7c</t>
+          <t>6478b051107b57001f86f918</t>
         </is>
       </c>
       <c r="C672" s="13" t="inlineStr">
         <is>
-          <t>optionmaster02</t>
+          <t>srptrader</t>
         </is>
       </c>
       <c r="D672" s="12" t="inlineStr">
         <is>
-          <t>kaushikmekdar@gmail.com</t>
+          <t>jaymaajaymaa330@gmail.com</t>
         </is>
       </c>
       <c r="E672" s="12" t="inlineStr">
         <is>
-          <t>9599339897</t>
+          <t>6377083526</t>
         </is>
       </c>
       <c r="F672" s="12" t="inlineStr">
@@ -49163,22 +49163,22 @@
         <v>1</v>
       </c>
       <c r="J672" s="14" t="n">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="K672" s="14" t="n">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="L672" s="15" t="n">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="M672" s="12" t="inlineStr">
         <is>
-          <t>69ca0c4617aeb10013e7d804</t>
+          <t>66f2e10389f9ce0013483dc0</t>
         </is>
       </c>
       <c r="N672" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca0c4617aeb10013e7d804</t>
+          <t>https://superprofile.bio/vig/66f2e10389f9ce0013483dc0</t>
         </is>
       </c>
       <c r="O672" s="17" t="inlineStr">
@@ -49198,22 +49198,22 @@
       </c>
       <c r="B673" s="20" t="inlineStr">
         <is>
-          <t>64d31140b49711001ee4cb72</t>
+          <t>656776a2d7de9b001e22044a</t>
         </is>
       </c>
       <c r="C673" s="20" t="inlineStr">
         <is>
-          <t>Learningtrade</t>
+          <t>tsunami07</t>
         </is>
       </c>
       <c r="D673" s="19" t="inlineStr">
         <is>
-          <t>vishallakhvara@email.com</t>
+          <t>shubh050701@gmail.com</t>
         </is>
       </c>
       <c r="E673" s="19" t="inlineStr">
         <is>
-          <t>9427664410</t>
+          <t>8765220711</t>
         </is>
       </c>
       <c r="F673" s="19" t="inlineStr">
@@ -49223,34 +49223,34 @@
       </c>
       <c r="G673" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H673" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I673" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J673" s="21" t="n">
-        <v>1744</v>
+        <v>1786</v>
       </c>
       <c r="K673" s="21" t="n">
-        <v>1744</v>
+        <v>1786</v>
       </c>
       <c r="L673" s="22" t="n">
-        <v>1744</v>
+        <v>1786</v>
       </c>
       <c r="M673" s="19" t="inlineStr">
         <is>
-          <t>64f20be95b9b46001fea4819</t>
+          <t>6a0a982b37a61300137fcec1</t>
         </is>
       </c>
       <c r="N673" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64f20be95b9b46001fea4819</t>
+          <t>https://superprofile.bio/vig/6a0a982b37a61300137fcec1</t>
         </is>
       </c>
       <c r="O673" s="24" t="inlineStr">
@@ -49270,22 +49270,22 @@
       </c>
       <c r="B674" s="13" t="inlineStr">
         <is>
-          <t>63bab66e73a489003e7526c9</t>
+          <t>6475a085f68c8e0020340ef5</t>
         </is>
       </c>
       <c r="C674" s="13" t="inlineStr">
         <is>
-          <t>stockpremium</t>
+          <t>jd24education</t>
         </is>
       </c>
       <c r="D674" s="12" t="inlineStr">
         <is>
-          <t>kaish3185@gmail.com</t>
+          <t>jd24education@gmail.com</t>
         </is>
       </c>
       <c r="E674" s="12" t="inlineStr">
         <is>
-          <t>9811477947</t>
+          <t>8002550026</t>
         </is>
       </c>
       <c r="F674" s="12" t="inlineStr">
@@ -49295,34 +49295,34 @@
       </c>
       <c r="G674" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H674" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I674" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J674" s="14" t="n">
-        <v>1715</v>
+        <v>1773</v>
       </c>
       <c r="K674" s="14" t="n">
-        <v>1715</v>
+        <v>1773</v>
       </c>
       <c r="L674" s="15" t="n">
-        <v>1715</v>
+        <v>1773</v>
       </c>
       <c r="M674" s="12" t="inlineStr">
         <is>
-          <t>63baba5c8a32b9003d4baae2</t>
+          <t>6582cd2325f8a7001ebe8d03</t>
         </is>
       </c>
       <c r="N674" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63baba5c8a32b9003d4baae2</t>
+          <t>https://superprofile.bio/vig/6582cd2325f8a7001ebe8d03</t>
         </is>
       </c>
       <c r="O674" s="17" t="inlineStr">
@@ -49342,22 +49342,22 @@
       </c>
       <c r="B675" s="20" t="inlineStr">
         <is>
-          <t>69da8fd221153d0013f28a7a</t>
+          <t>650ff72bf8c83a001d33ca7c</t>
         </is>
       </c>
       <c r="C675" s="20" t="inlineStr">
         <is>
-          <t>helpdesk11</t>
+          <t>optionmaster02</t>
         </is>
       </c>
       <c r="D675" s="19" t="inlineStr">
         <is>
-          <t>lkmeena6272@gmail.com</t>
+          <t>kaushikmekdar@gmail.com</t>
         </is>
       </c>
       <c r="E675" s="19" t="inlineStr">
         <is>
-          <t>6377995024</t>
+          <t>9599339897</t>
         </is>
       </c>
       <c r="F675" s="19" t="inlineStr">
@@ -49367,34 +49367,34 @@
       </c>
       <c r="G675" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H675" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I675" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J675" s="21" t="n">
-        <v>1671</v>
+        <v>1757</v>
       </c>
       <c r="K675" s="21" t="n">
-        <v>1671</v>
+        <v>1757</v>
       </c>
       <c r="L675" s="22" t="n">
-        <v>1671</v>
+        <v>1757</v>
       </c>
       <c r="M675" s="19" t="inlineStr">
         <is>
-          <t>69eb0cccaa5f62001331a4ce</t>
+          <t>69ca0c4617aeb10013e7d804</t>
         </is>
       </c>
       <c r="N675" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69eb0cccaa5f62001331a4ce</t>
+          <t>https://superprofile.bio/vig/69ca0c4617aeb10013e7d804</t>
         </is>
       </c>
       <c r="O675" s="24" t="inlineStr">
@@ -49414,22 +49414,22 @@
       </c>
       <c r="B676" s="13" t="inlineStr">
         <is>
-          <t>670a35a446b3f5001315f409</t>
+          <t>64d31140b49711001ee4cb72</t>
         </is>
       </c>
       <c r="C676" s="13" t="inlineStr">
         <is>
-          <t>tradewithshiv00</t>
+          <t>Learningtrade</t>
         </is>
       </c>
       <c r="D676" s="12" t="inlineStr">
         <is>
-          <t>sonu3322111@gmail.com</t>
+          <t>vishallakhvara@email.com</t>
         </is>
       </c>
       <c r="E676" s="12" t="inlineStr">
         <is>
-          <t>7419333111</t>
+          <t>9427664410</t>
         </is>
       </c>
       <c r="F676" s="12" t="inlineStr">
@@ -49451,22 +49451,22 @@
         <v>1</v>
       </c>
       <c r="J676" s="14" t="n">
-        <v>1669</v>
+        <v>1744</v>
       </c>
       <c r="K676" s="14" t="n">
-        <v>1669</v>
+        <v>1744</v>
       </c>
       <c r="L676" s="15" t="n">
-        <v>1669</v>
+        <v>1744</v>
       </c>
       <c r="M676" s="12" t="inlineStr">
         <is>
-          <t>67c06d2dd4e3b4001314d20c</t>
+          <t>64f20be95b9b46001fea4819</t>
         </is>
       </c>
       <c r="N676" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67c06d2dd4e3b4001314d20c</t>
+          <t>https://superprofile.bio/vig/64f20be95b9b46001fea4819</t>
         </is>
       </c>
       <c r="O676" s="17" t="inlineStr">
@@ -49486,22 +49486,22 @@
       </c>
       <c r="B677" s="20" t="inlineStr">
         <is>
-          <t>68b03fb7687f420013c3f18b</t>
+          <t>63bab66e73a489003e7526c9</t>
         </is>
       </c>
       <c r="C677" s="20" t="inlineStr">
         <is>
-          <t>sy01</t>
+          <t>stockpremium</t>
         </is>
       </c>
       <c r="D677" s="19" t="inlineStr">
         <is>
-          <t>saurabhydv856@gmail.com</t>
+          <t>kaish3185@gmail.com</t>
         </is>
       </c>
       <c r="E677" s="19" t="inlineStr">
         <is>
-          <t>6398689318</t>
+          <t>9811477947</t>
         </is>
       </c>
       <c r="F677" s="19" t="inlineStr">
@@ -49511,34 +49511,34 @@
       </c>
       <c r="G677" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H677" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I677" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J677" s="21" t="n">
-        <v>1646</v>
+        <v>1715</v>
       </c>
       <c r="K677" s="21" t="n">
-        <v>1646</v>
+        <v>1715</v>
       </c>
       <c r="L677" s="22" t="n">
-        <v>1646</v>
+        <v>1715</v>
       </c>
       <c r="M677" s="19" t="inlineStr">
         <is>
-          <t>6734586c512491001324475c</t>
+          <t>63baba5c8a32b9003d4baae2</t>
         </is>
       </c>
       <c r="N677" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6734586c512491001324475c</t>
+          <t>https://superprofile.bio/vig/63baba5c8a32b9003d4baae2</t>
         </is>
       </c>
       <c r="O677" s="24" t="inlineStr">
@@ -49558,22 +49558,22 @@
       </c>
       <c r="B678" s="13" t="inlineStr">
         <is>
-          <t>62dd3018f83d933bcd5bd23c</t>
+          <t>69da8fd221153d0013f28a7a</t>
         </is>
       </c>
       <c r="C678" s="13" t="inlineStr">
         <is>
-          <t>bullbearpremium</t>
+          <t>helpdesk11</t>
         </is>
       </c>
       <c r="D678" s="12" t="inlineStr">
         <is>
-          <t>pradip.gund9@gmail.com</t>
+          <t>lkmeena6272@gmail.com</t>
         </is>
       </c>
       <c r="E678" s="12" t="inlineStr">
         <is>
-          <t>9503876571</t>
+          <t>6377995024</t>
         </is>
       </c>
       <c r="F678" s="12" t="inlineStr">
@@ -49583,34 +49583,34 @@
       </c>
       <c r="G678" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H678" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I678" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J678" s="14" t="n">
-        <v>1620</v>
+        <v>1671</v>
       </c>
       <c r="K678" s="14" t="n">
-        <v>1620</v>
+        <v>1671</v>
       </c>
       <c r="L678" s="15" t="n">
-        <v>1620</v>
+        <v>1671</v>
       </c>
       <c r="M678" s="12" t="inlineStr">
         <is>
-          <t>68e7cafb27f3a100139ee425</t>
+          <t>69eb0cccaa5f62001331a4ce</t>
         </is>
       </c>
       <c r="N678" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68e7cafb27f3a100139ee425</t>
+          <t>https://superprofile.bio/vig/69eb0cccaa5f62001331a4ce</t>
         </is>
       </c>
       <c r="O678" s="17" t="inlineStr">
@@ -49630,22 +49630,22 @@
       </c>
       <c r="B679" s="20" t="inlineStr">
         <is>
-          <t>65e556ff75a641001a90bf56</t>
+          <t>670a35a446b3f5001315f409</t>
         </is>
       </c>
       <c r="C679" s="20" t="inlineStr">
         <is>
-          <t>tradewithraj</t>
+          <t>tradewithshiv00</t>
         </is>
       </c>
       <c r="D679" s="19" t="inlineStr">
         <is>
-          <t>cmsprimesuport@gmail.com</t>
+          <t>sonu3322111@gmail.com</t>
         </is>
       </c>
       <c r="E679" s="19" t="inlineStr">
         <is>
-          <t>6367105395</t>
+          <t>7419333111</t>
         </is>
       </c>
       <c r="F679" s="19" t="inlineStr">
@@ -49655,34 +49655,34 @@
       </c>
       <c r="G679" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H679" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I679" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J679" s="21" t="n">
-        <v>1599</v>
+        <v>1669</v>
       </c>
       <c r="K679" s="21" t="n">
-        <v>1599</v>
+        <v>1669</v>
       </c>
       <c r="L679" s="22" t="n">
-        <v>1599</v>
+        <v>1669</v>
       </c>
       <c r="M679" s="19" t="inlineStr">
         <is>
-          <t>68fde49cad2e290012df50ba</t>
+          <t>67c06d2dd4e3b4001314d20c</t>
         </is>
       </c>
       <c r="N679" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68fde49cad2e290012df50ba</t>
+          <t>https://superprofile.bio/vig/67c06d2dd4e3b4001314d20c</t>
         </is>
       </c>
       <c r="O679" s="24" t="inlineStr">
@@ -49702,22 +49702,22 @@
       </c>
       <c r="B680" s="13" t="inlineStr">
         <is>
-          <t>63398a142e52d546d6af08e9</t>
+          <t>68b03fb7687f420013c3f18b</t>
         </is>
       </c>
       <c r="C680" s="13" t="inlineStr">
         <is>
-          <t>tigerstrading</t>
+          <t>sy01</t>
         </is>
       </c>
       <c r="D680" s="12" t="inlineStr">
         <is>
-          <t>tigertrading921@gmail.com</t>
+          <t>saurabhydv856@gmail.com</t>
         </is>
       </c>
       <c r="E680" s="12" t="inlineStr">
         <is>
-          <t>9209860503</t>
+          <t>6398689318</t>
         </is>
       </c>
       <c r="F680" s="12" t="inlineStr">
@@ -49739,22 +49739,22 @@
         <v>1</v>
       </c>
       <c r="J680" s="14" t="n">
-        <v>1591</v>
+        <v>1646</v>
       </c>
       <c r="K680" s="14" t="n">
-        <v>1591</v>
+        <v>1646</v>
       </c>
       <c r="L680" s="15" t="n">
-        <v>1591</v>
+        <v>1646</v>
       </c>
       <c r="M680" s="12" t="inlineStr">
         <is>
-          <t>6976addf599433001336b54b</t>
+          <t>6734586c512491001324475c</t>
         </is>
       </c>
       <c r="N680" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6976addf599433001336b54b</t>
+          <t>https://superprofile.bio/vig/6734586c512491001324475c</t>
         </is>
       </c>
       <c r="O680" s="17" t="inlineStr">
@@ -49774,22 +49774,22 @@
       </c>
       <c r="B681" s="20" t="inlineStr">
         <is>
-          <t>69eeed4b09e8f10012d998bb</t>
+          <t>62dd3018f83d933bcd5bd23c</t>
         </is>
       </c>
       <c r="C681" s="20" t="inlineStr">
         <is>
-          <t>preparationkit</t>
+          <t>bullbearpremium</t>
         </is>
       </c>
       <c r="D681" s="19" t="inlineStr">
         <is>
-          <t>pranavvpatel25@gmail.com</t>
+          <t>pradip.gund9@gmail.com</t>
         </is>
       </c>
       <c r="E681" s="19" t="inlineStr">
         <is>
-          <t>8469655210</t>
+          <t>9503876571</t>
         </is>
       </c>
       <c r="F681" s="19" t="inlineStr">
@@ -49799,34 +49799,34 @@
       </c>
       <c r="G681" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H681" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I681" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J681" s="21" t="n">
-        <v>1572</v>
+        <v>1620</v>
       </c>
       <c r="K681" s="21" t="n">
-        <v>1572</v>
+        <v>1620</v>
       </c>
       <c r="L681" s="22" t="n">
-        <v>1572</v>
+        <v>1620</v>
       </c>
       <c r="M681" s="19" t="inlineStr">
         <is>
-          <t>6a90770994d8730013b824d6</t>
+          <t>68e7cafb27f3a100139ee425</t>
         </is>
       </c>
       <c r="N681" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a90770994d8730013b824d6</t>
+          <t>https://superprofile.bio/vig/68e7cafb27f3a100139ee425</t>
         </is>
       </c>
       <c r="O681" s="24" t="inlineStr">
@@ -49846,22 +49846,22 @@
       </c>
       <c r="B682" s="13" t="inlineStr">
         <is>
-          <t>6613ee30d6ac80001afadce9</t>
+          <t>65e556ff75a641001a90bf56</t>
         </is>
       </c>
       <c r="C682" s="13" t="inlineStr">
         <is>
-          <t>httpstmet1uilphv4taxymm1</t>
+          <t>tradewithraj</t>
         </is>
       </c>
       <c r="D682" s="12" t="inlineStr">
         <is>
-          <t>abinash543211@gmail.com</t>
+          <t>cmsprimesuport@gmail.com</t>
         </is>
       </c>
       <c r="E682" s="12" t="inlineStr">
         <is>
-          <t>9589592337</t>
+          <t>6367105395</t>
         </is>
       </c>
       <c r="F682" s="12" t="inlineStr">
@@ -49871,34 +49871,34 @@
       </c>
       <c r="G682" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H682" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I682" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J682" s="14" t="n">
-        <v>1515</v>
+        <v>1599</v>
       </c>
       <c r="K682" s="14" t="n">
-        <v>1515</v>
+        <v>1599</v>
       </c>
       <c r="L682" s="15" t="n">
-        <v>1515</v>
+        <v>1599</v>
       </c>
       <c r="M682" s="12" t="inlineStr">
         <is>
-          <t>6994990e6e580f00133a8ce5</t>
+          <t>68fde49cad2e290012df50ba</t>
         </is>
       </c>
       <c r="N682" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6994990e6e580f00133a8ce5</t>
+          <t>https://superprofile.bio/vig/68fde49cad2e290012df50ba</t>
         </is>
       </c>
       <c r="O682" s="17" t="inlineStr">
@@ -49918,22 +49918,22 @@
       </c>
       <c r="B683" s="20" t="inlineStr">
         <is>
-          <t>62bad2a8dc07ec6e742c8cd2</t>
+          <t>63398a142e52d546d6af08e9</t>
         </is>
       </c>
       <c r="C683" s="20" t="inlineStr">
         <is>
-          <t>tradexculture</t>
+          <t>tigerstrading</t>
         </is>
       </c>
       <c r="D683" s="19" t="inlineStr">
         <is>
-          <t>itstradeculture@gmail.com</t>
+          <t>tigertrading921@gmail.com</t>
         </is>
       </c>
       <c r="E683" s="19" t="inlineStr">
         <is>
-          <t>9098432281</t>
+          <t>9209860503</t>
         </is>
       </c>
       <c r="F683" s="19" t="inlineStr">
@@ -49943,34 +49943,34 @@
       </c>
       <c r="G683" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H683" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I683" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J683" s="21" t="n">
-        <v>1464</v>
+        <v>1591</v>
       </c>
       <c r="K683" s="21" t="n">
-        <v>1464</v>
+        <v>1591</v>
       </c>
       <c r="L683" s="22" t="n">
-        <v>1464</v>
+        <v>1591</v>
       </c>
       <c r="M683" s="19" t="inlineStr">
         <is>
-          <t>63515a0aa785512f19f504e7</t>
+          <t>6976addf599433001336b54b</t>
         </is>
       </c>
       <c r="N683" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
+          <t>https://superprofile.bio/vig/6976addf599433001336b54b</t>
         </is>
       </c>
       <c r="O683" s="24" t="inlineStr">
@@ -49990,22 +49990,22 @@
       </c>
       <c r="B684" s="13" t="inlineStr">
         <is>
-          <t>65f03772c3be0800137389f9</t>
+          <t>69eeed4b09e8f10012d998bb</t>
         </is>
       </c>
       <c r="C684" s="13" t="inlineStr">
         <is>
-          <t>evergreenprofit1</t>
+          <t>preparationkit</t>
         </is>
       </c>
       <c r="D684" s="12" t="inlineStr">
         <is>
-          <t>jtinvestment@yahoo.com</t>
+          <t>pranavvpatel25@gmail.com</t>
         </is>
       </c>
       <c r="E684" s="12" t="inlineStr">
         <is>
-          <t>9811359531</t>
+          <t>8469655210</t>
         </is>
       </c>
       <c r="F684" s="12" t="inlineStr">
@@ -50015,34 +50015,34 @@
       </c>
       <c r="G684" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H684" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I684" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J684" s="14" t="n">
-        <v>1455</v>
+        <v>1572</v>
       </c>
       <c r="K684" s="14" t="n">
-        <v>1455</v>
+        <v>1572</v>
       </c>
       <c r="L684" s="15" t="n">
-        <v>1455</v>
+        <v>1572</v>
       </c>
       <c r="M684" s="12" t="inlineStr">
         <is>
-          <t>68821d571a62d00013d94752</t>
+          <t>6a90770994d8730013b824d6</t>
         </is>
       </c>
       <c r="N684" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68821d571a62d00013d94752</t>
+          <t>https://superprofile.bio/vig/6a90770994d8730013b824d6</t>
         </is>
       </c>
       <c r="O684" s="17" t="inlineStr">
@@ -50062,59 +50062,59 @@
       </c>
       <c r="B685" s="20" t="inlineStr">
         <is>
-          <t>6788ca6493df9b001313bee5</t>
+          <t>63f5178f135a2c0020ebd0de</t>
         </is>
       </c>
       <c r="C685" s="20" t="inlineStr">
         <is>
-          <t>compoundly</t>
+          <t>dropouttradergaurav</t>
         </is>
       </c>
       <c r="D685" s="19" t="inlineStr">
         <is>
-          <t>shiwanilegal31@gmail.com</t>
+          <t>dropouttradergaurav@gmail.com</t>
         </is>
       </c>
       <c r="E685" s="19" t="inlineStr">
         <is>
-          <t>9821037875</t>
+          <t>8003506141</t>
         </is>
       </c>
       <c r="F685" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Baljeet Singh</t>
         </is>
       </c>
       <c r="G685" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H685" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I685" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J685" s="21" t="n">
-        <v>1448</v>
+        <v>1551</v>
       </c>
       <c r="K685" s="21" t="n">
-        <v>1448</v>
+        <v>1551</v>
       </c>
       <c r="L685" s="22" t="n">
-        <v>1448</v>
+        <v>1551</v>
       </c>
       <c r="M685" s="19" t="inlineStr">
         <is>
-          <t>68f764d5f9db6f0013225489</t>
+          <t>69e45d2b5275a70013bdf54d</t>
         </is>
       </c>
       <c r="N685" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f764d5f9db6f0013225489</t>
+          <t>https://superprofile.bio/vig/69e45d2b5275a70013bdf54d</t>
         </is>
       </c>
       <c r="O685" s="24" t="inlineStr">
@@ -50134,59 +50134,59 @@
       </c>
       <c r="B686" s="13" t="inlineStr">
         <is>
-          <t>65c05cddd5ea93001f37a5b4</t>
+          <t>68cf7b40aaa4c30013596288</t>
         </is>
       </c>
       <c r="C686" s="13" t="inlineStr">
         <is>
-          <t>vlogsbysachinn</t>
+          <t>httpswwwcareerswavein</t>
         </is>
       </c>
       <c r="D686" s="12" t="inlineStr">
         <is>
-          <t>sachinprsnl12@gmail.com</t>
+          <t>njawaharrenuka@gmail.com</t>
         </is>
       </c>
       <c r="E686" s="12" t="inlineStr">
         <is>
-          <t>9315724186</t>
+          <t>9010106560</t>
         </is>
       </c>
       <c r="F686" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aayush Sethi</t>
         </is>
       </c>
       <c r="G686" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H686" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I686" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J686" s="14" t="n">
-        <v>1411</v>
+        <v>1529</v>
       </c>
       <c r="K686" s="14" t="n">
-        <v>1411</v>
+        <v>1529</v>
       </c>
       <c r="L686" s="15" t="n">
-        <v>1411</v>
+        <v>1529</v>
       </c>
       <c r="M686" s="12" t="inlineStr">
         <is>
-          <t>68c2b6158f67740013f45471</t>
+          <t>68d0ed81287cca00135e7910</t>
         </is>
       </c>
       <c r="N686" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c2b6158f67740013f45471</t>
+          <t>https://superprofile.bio/vig/68d0ed81287cca00135e7910</t>
         </is>
       </c>
       <c r="O686" s="17" t="inlineStr">
@@ -50206,22 +50206,22 @@
       </c>
       <c r="B687" s="20" t="inlineStr">
         <is>
-          <t>6a364acc4cf49e001251bd8d</t>
+          <t>6613ee30d6ac80001afadce9</t>
         </is>
       </c>
       <c r="C687" s="20" t="inlineStr">
         <is>
-          <t>vishaltradingx</t>
+          <t>httpstmet1uilphv4taxymm1</t>
         </is>
       </c>
       <c r="D687" s="19" t="inlineStr">
         <is>
-          <t>vishalgupta992005@gmail.com</t>
+          <t>abinash543211@gmail.com</t>
         </is>
       </c>
       <c r="E687" s="19" t="inlineStr">
         <is>
-          <t>8882180982</t>
+          <t>9589592337</t>
         </is>
       </c>
       <c r="F687" s="19" t="inlineStr">
@@ -50231,34 +50231,34 @@
       </c>
       <c r="G687" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H687" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I687" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J687" s="21" t="n">
-        <v>1411</v>
+        <v>1515</v>
       </c>
       <c r="K687" s="21" t="n">
-        <v>1411</v>
+        <v>1515</v>
       </c>
       <c r="L687" s="22" t="n">
-        <v>1411</v>
+        <v>1515</v>
       </c>
       <c r="M687" s="19" t="inlineStr">
         <is>
-          <t>6a95d78d71d63e00139088dc</t>
+          <t>6994990e6e580f00133a8ce5</t>
         </is>
       </c>
       <c r="N687" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a95d78d71d63e00139088dc</t>
+          <t>https://superprofile.bio/vig/6994990e6e580f00133a8ce5</t>
         </is>
       </c>
       <c r="O687" s="24" t="inlineStr">
@@ -50278,22 +50278,22 @@
       </c>
       <c r="B688" s="13" t="inlineStr">
         <is>
-          <t>67c5f49ae74b1d0013ea0111</t>
+          <t>62bad2a8dc07ec6e742c8cd2</t>
         </is>
       </c>
       <c r="C688" s="13" t="inlineStr">
         <is>
-          <t>jayb2427</t>
+          <t>tradexculture</t>
         </is>
       </c>
       <c r="D688" s="12" t="inlineStr">
         <is>
-          <t>astutetrader24@gmail.com</t>
+          <t>itstradeculture@gmail.com</t>
         </is>
       </c>
       <c r="E688" s="12" t="inlineStr">
         <is>
-          <t>9879002427</t>
+          <t>9098432281</t>
         </is>
       </c>
       <c r="F688" s="12" t="inlineStr">
@@ -50303,34 +50303,34 @@
       </c>
       <c r="G688" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H688" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I688" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J688" s="14" t="n">
-        <v>1350</v>
+        <v>1464</v>
       </c>
       <c r="K688" s="14" t="n">
-        <v>1350</v>
+        <v>1464</v>
       </c>
       <c r="L688" s="15" t="n">
-        <v>1350</v>
+        <v>1464</v>
       </c>
       <c r="M688" s="12" t="inlineStr">
         <is>
-          <t>67ecc370d9f0a5001309bd71</t>
+          <t>63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="N688" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
+          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="O688" s="17" t="inlineStr">
@@ -50350,22 +50350,22 @@
       </c>
       <c r="B689" s="20" t="inlineStr">
         <is>
-          <t>6652f73e17ab4600138327bc</t>
+          <t>65f03772c3be0800137389f9</t>
         </is>
       </c>
       <c r="C689" s="20" t="inlineStr">
         <is>
-          <t>aryashah</t>
+          <t>evergreenprofit1</t>
         </is>
       </c>
       <c r="D689" s="19" t="inlineStr">
         <is>
-          <t>arya80226@gmail.com</t>
+          <t>jtinvestment@yahoo.com</t>
         </is>
       </c>
       <c r="E689" s="19" t="inlineStr">
         <is>
-          <t>9316096699</t>
+          <t>9811359531</t>
         </is>
       </c>
       <c r="F689" s="19" t="inlineStr">
@@ -50375,34 +50375,34 @@
       </c>
       <c r="G689" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H689" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I689" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J689" s="21" t="n">
-        <v>1349</v>
+        <v>1455</v>
       </c>
       <c r="K689" s="21" t="n">
-        <v>1349</v>
+        <v>1455</v>
       </c>
       <c r="L689" s="22" t="n">
-        <v>1349</v>
+        <v>1455</v>
       </c>
       <c r="M689" s="19" t="inlineStr">
         <is>
-          <t>6a3fac03f608d4001316288a</t>
+          <t>68821d571a62d00013d94752</t>
         </is>
       </c>
       <c r="N689" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3fac03f608d4001316288a</t>
+          <t>https://superprofile.bio/vig/68821d571a62d00013d94752</t>
         </is>
       </c>
       <c r="O689" s="24" t="inlineStr">
@@ -50422,22 +50422,22 @@
       </c>
       <c r="B690" s="13" t="inlineStr">
         <is>
-          <t>64c5ffb8cabc14001e87cfb9</t>
+          <t>6788ca6493df9b001313bee5</t>
         </is>
       </c>
       <c r="C690" s="13" t="inlineStr">
         <is>
-          <t>StudyNiftyMalayalam</t>
+          <t>compoundly</t>
         </is>
       </c>
       <c r="D690" s="12" t="inlineStr">
         <is>
-          <t>nairjkrishnan@gmail.com</t>
+          <t>shiwanilegal31@gmail.com</t>
         </is>
       </c>
       <c r="E690" s="12" t="inlineStr">
         <is>
-          <t>7200822228</t>
+          <t>9821037875</t>
         </is>
       </c>
       <c r="F690" s="12" t="inlineStr">
@@ -50447,34 +50447,34 @@
       </c>
       <c r="G690" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H690" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I690" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J690" s="14" t="n">
-        <v>1261</v>
+        <v>1448</v>
       </c>
       <c r="K690" s="14" t="n">
-        <v>1261</v>
+        <v>1448</v>
       </c>
       <c r="L690" s="15" t="n">
-        <v>1261</v>
+        <v>1448</v>
       </c>
       <c r="M690" s="12" t="inlineStr">
         <is>
-          <t>64c60188903653001d97606e</t>
+          <t>68f764d5f9db6f0013225489</t>
         </is>
       </c>
       <c r="N690" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64c60188903653001d97606e</t>
+          <t>https://superprofile.bio/vig/68f764d5f9db6f0013225489</t>
         </is>
       </c>
       <c r="O690" s="17" t="inlineStr">
@@ -50494,59 +50494,59 @@
       </c>
       <c r="B691" s="20" t="inlineStr">
         <is>
-          <t>64c10e82985f36002a91518a</t>
+          <t>673aeaa4e09ab900136b0f69</t>
         </is>
       </c>
       <c r="C691" s="20" t="inlineStr">
         <is>
-          <t>investwithsoumyadeep</t>
+          <t>tradetuition</t>
         </is>
       </c>
       <c r="D691" s="19" t="inlineStr">
         <is>
-          <t>soumyadeepsp@gmail.com</t>
+          <t>valueinvestor713@gmail.com</t>
         </is>
       </c>
       <c r="E691" s="19" t="inlineStr">
         <is>
-          <t>7042006372</t>
+          <t>7488638311</t>
         </is>
       </c>
       <c r="F691" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ujjwal Bakshi</t>
         </is>
       </c>
       <c r="G691" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H691" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I691" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J691" s="21" t="n">
-        <v>1260</v>
+        <v>1429</v>
       </c>
       <c r="K691" s="21" t="n">
-        <v>1260</v>
+        <v>1429</v>
       </c>
       <c r="L691" s="22" t="n">
-        <v>1260</v>
+        <v>1429</v>
       </c>
       <c r="M691" s="19" t="inlineStr">
         <is>
-          <t>66ffe626e0ec7e0013a396d5</t>
+          <t>6a1fbfcd62b0ef0013bb7063</t>
         </is>
       </c>
       <c r="N691" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ffe626e0ec7e0013a396d5</t>
+          <t>https://superprofile.bio/vig/6a1fbfcd62b0ef0013bb7063</t>
         </is>
       </c>
       <c r="O691" s="24" t="inlineStr">
@@ -50566,22 +50566,22 @@
       </c>
       <c r="B692" s="13" t="inlineStr">
         <is>
-          <t>655c2b17f2c0c5001e80dc5c</t>
+          <t>65c05cddd5ea93001f37a5b4</t>
         </is>
       </c>
       <c r="C692" s="13" t="inlineStr">
         <is>
-          <t>uday08</t>
+          <t>vlogsbysachinn</t>
         </is>
       </c>
       <c r="D692" s="12" t="inlineStr">
         <is>
-          <t>joguudaykiran4i@gmail.com</t>
+          <t>sachinprsnl12@gmail.com</t>
         </is>
       </c>
       <c r="E692" s="12" t="inlineStr">
         <is>
-          <t>7569057147</t>
+          <t>9315724186</t>
         </is>
       </c>
       <c r="F692" s="12" t="inlineStr">
@@ -50591,34 +50591,34 @@
       </c>
       <c r="G692" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H692" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I692" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J692" s="14" t="n">
-        <v>1259</v>
+        <v>1411</v>
       </c>
       <c r="K692" s="14" t="n">
-        <v>1259</v>
+        <v>1411</v>
       </c>
       <c r="L692" s="15" t="n">
-        <v>1259</v>
+        <v>1411</v>
       </c>
       <c r="M692" s="12" t="inlineStr">
         <is>
-          <t>6a97085d5a0b9a00134a57d9</t>
+          <t>68c2b6158f67740013f45471</t>
         </is>
       </c>
       <c r="N692" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
+          <t>https://superprofile.bio/vig/68c2b6158f67740013f45471</t>
         </is>
       </c>
       <c r="O692" s="17" t="inlineStr">
@@ -50638,22 +50638,22 @@
       </c>
       <c r="B693" s="20" t="inlineStr">
         <is>
-          <t>6520f7847a624b001e93bb99</t>
+          <t>6a364acc4cf49e001251bd8d</t>
         </is>
       </c>
       <c r="C693" s="20" t="inlineStr">
         <is>
-          <t>studyniftymalayalam</t>
+          <t>vishaltradingx</t>
         </is>
       </c>
       <c r="D693" s="19" t="inlineStr">
         <is>
-          <t>aidotechindia@gmail.com</t>
+          <t>vishalgupta992005@gmail.com</t>
         </is>
       </c>
       <c r="E693" s="19" t="inlineStr">
         <is>
-          <t>8848066533</t>
+          <t>8882180982</t>
         </is>
       </c>
       <c r="F693" s="19" t="inlineStr">
@@ -50663,34 +50663,34 @@
       </c>
       <c r="G693" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H693" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I693" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J693" s="21" t="n">
-        <v>1245</v>
+        <v>1411</v>
       </c>
       <c r="K693" s="21" t="n">
-        <v>1245</v>
+        <v>1411</v>
       </c>
       <c r="L693" s="22" t="n">
-        <v>1245</v>
+        <v>1411</v>
       </c>
       <c r="M693" s="19" t="inlineStr">
         <is>
-          <t>6909a2491e2589001342a886</t>
+          <t>6a95d78d71d63e00139088dc</t>
         </is>
       </c>
       <c r="N693" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6909a2491e2589001342a886</t>
+          <t>https://superprofile.bio/vig/6a95d78d71d63e00139088dc</t>
         </is>
       </c>
       <c r="O693" s="24" t="inlineStr">
@@ -50710,22 +50710,22 @@
       </c>
       <c r="B694" s="13" t="inlineStr">
         <is>
-          <t>6a2a3b18739da100136db6f1</t>
+          <t>67c5f49ae74b1d0013ea0111</t>
         </is>
       </c>
       <c r="C694" s="13" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>jayb2427</t>
         </is>
       </c>
       <c r="D694" s="12" t="inlineStr">
         <is>
-          <t>mr.perfect.official018@gmail.com</t>
+          <t>astutetrader24@gmail.com</t>
         </is>
       </c>
       <c r="E694" s="12" t="inlineStr">
         <is>
-          <t>9116087897</t>
+          <t>9879002427</t>
         </is>
       </c>
       <c r="F694" s="12" t="inlineStr">
@@ -50735,34 +50735,34 @@
       </c>
       <c r="G694" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H694" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I694" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J694" s="14" t="n">
-        <v>1172</v>
+        <v>1350</v>
       </c>
       <c r="K694" s="14" t="n">
-        <v>1220</v>
+        <v>1350</v>
       </c>
       <c r="L694" s="15" t="n">
-        <v>1220</v>
+        <v>1350</v>
       </c>
       <c r="M694" s="12" t="inlineStr">
         <is>
-          <t>6a7d364eb62576001374f10c</t>
+          <t>67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="N694" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
+          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="O694" s="17" t="inlineStr">
@@ -50782,22 +50782,22 @@
       </c>
       <c r="B695" s="20" t="inlineStr">
         <is>
-          <t>64bbeb37cd861f002058b8c2</t>
+          <t>6652f73e17ab4600138327bc</t>
         </is>
       </c>
       <c r="C695" s="20" t="inlineStr">
         <is>
-          <t>SBTrader123</t>
+          <t>aryashah</t>
         </is>
       </c>
       <c r="D695" s="19" t="inlineStr">
         <is>
-          <t>safeexit2022@gmail.com</t>
+          <t>arya80226@gmail.com</t>
         </is>
       </c>
       <c r="E695" s="19" t="inlineStr">
         <is>
-          <t>9340517160</t>
+          <t>9316096699</t>
         </is>
       </c>
       <c r="F695" s="19" t="inlineStr">
@@ -50807,34 +50807,34 @@
       </c>
       <c r="G695" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H695" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I695" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J695" s="21" t="n">
-        <v>1161</v>
+        <v>1349</v>
       </c>
       <c r="K695" s="21" t="n">
-        <v>1161</v>
+        <v>1349</v>
       </c>
       <c r="L695" s="22" t="n">
-        <v>1161</v>
+        <v>1349</v>
       </c>
       <c r="M695" s="19" t="inlineStr">
         <is>
-          <t>64bbed001a03ba0021a80161</t>
+          <t>6a3fac03f608d4001316288a</t>
         </is>
       </c>
       <c r="N695" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64bbed001a03ba0021a80161</t>
+          <t>https://superprofile.bio/vig/6a3fac03f608d4001316288a</t>
         </is>
       </c>
       <c r="O695" s="24" t="inlineStr">
@@ -50854,22 +50854,22 @@
       </c>
       <c r="B696" s="13" t="inlineStr">
         <is>
-          <t>6436d5892b2028001fbf607b</t>
+          <t>64c5ffb8cabc14001e87cfb9</t>
         </is>
       </c>
       <c r="C696" s="13" t="inlineStr">
         <is>
-          <t>Livelonghari</t>
+          <t>StudyNiftyMalayalam</t>
         </is>
       </c>
       <c r="D696" s="12" t="inlineStr">
         <is>
-          <t>livelongwealth@gmail.com</t>
+          <t>nairjkrishnan@gmail.com</t>
         </is>
       </c>
       <c r="E696" s="12" t="inlineStr">
         <is>
-          <t>9544085264</t>
+          <t>7200822228</t>
         </is>
       </c>
       <c r="F696" s="12" t="inlineStr">
@@ -50879,34 +50879,34 @@
       </c>
       <c r="G696" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H696" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I696" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J696" s="14" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="K696" s="14" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="L696" s="15" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="M696" s="12" t="inlineStr">
         <is>
-          <t>653e68ea423d4e001eef5b19</t>
+          <t>64c60188903653001d97606e</t>
         </is>
       </c>
       <c r="N696" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
+          <t>https://superprofile.bio/vig/64c60188903653001d97606e</t>
         </is>
       </c>
       <c r="O696" s="17" t="inlineStr">
@@ -50926,22 +50926,22 @@
       </c>
       <c r="B697" s="20" t="inlineStr">
         <is>
-          <t>67e424ccab747f00135495b4</t>
+          <t>64c10e82985f36002a91518a</t>
         </is>
       </c>
       <c r="C697" s="20" t="inlineStr">
         <is>
-          <t>jobposting</t>
+          <t>investwithsoumyadeep</t>
         </is>
       </c>
       <c r="D697" s="19" t="inlineStr">
         <is>
-          <t>sagarruttare@gmail.com</t>
+          <t>soumyadeepsp@gmail.com</t>
         </is>
       </c>
       <c r="E697" s="19" t="inlineStr">
         <is>
-          <t>7796716569</t>
+          <t>7042006372</t>
         </is>
       </c>
       <c r="F697" s="19" t="inlineStr">
@@ -50951,34 +50951,34 @@
       </c>
       <c r="G697" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H697" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I697" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J697" s="21" t="n">
-        <v>1078</v>
+        <v>1260</v>
       </c>
       <c r="K697" s="21" t="n">
-        <v>1078</v>
+        <v>1260</v>
       </c>
       <c r="L697" s="22" t="n">
-        <v>1078</v>
+        <v>1260</v>
       </c>
       <c r="M697" s="19" t="inlineStr">
         <is>
-          <t>692dae30d42b600013b13d78</t>
+          <t>66ffe626e0ec7e0013a396d5</t>
         </is>
       </c>
       <c r="N697" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
+          <t>https://superprofile.bio/vig/66ffe626e0ec7e0013a396d5</t>
         </is>
       </c>
       <c r="O697" s="24" t="inlineStr">
@@ -50998,22 +50998,22 @@
       </c>
       <c r="B698" s="13" t="inlineStr">
         <is>
-          <t>69ad496eafc0e100130d7f09</t>
+          <t>655c2b17f2c0c5001e80dc5c</t>
         </is>
       </c>
       <c r="C698" s="13" t="inlineStr">
         <is>
-          <t>sunoaudiobook</t>
+          <t>uday08</t>
         </is>
       </c>
       <c r="D698" s="12" t="inlineStr">
         <is>
-          <t>devrajstudio09@gmail.com</t>
+          <t>joguudaykiran4i@gmail.com</t>
         </is>
       </c>
       <c r="E698" s="12" t="inlineStr">
         <is>
-          <t>7869490714</t>
+          <t>7569057147</t>
         </is>
       </c>
       <c r="F698" s="12" t="inlineStr">
@@ -51023,34 +51023,34 @@
       </c>
       <c r="G698" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H698" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I698" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J698" s="14" t="n">
-        <v>1031</v>
+        <v>1259</v>
       </c>
       <c r="K698" s="14" t="n">
-        <v>1031</v>
+        <v>1259</v>
       </c>
       <c r="L698" s="15" t="n">
-        <v>1031</v>
+        <v>1259</v>
       </c>
       <c r="M698" s="12" t="inlineStr">
         <is>
-          <t>6a4684b13604a700135096e1</t>
+          <t>6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="N698" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4684b13604a700135096e1</t>
+          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="O698" s="17" t="inlineStr">
@@ -51070,22 +51070,22 @@
       </c>
       <c r="B699" s="20" t="inlineStr">
         <is>
-          <t>68efa32deb549e001385d2c4</t>
+          <t>6520f7847a624b001e93bb99</t>
         </is>
       </c>
       <c r="C699" s="20" t="inlineStr">
         <is>
-          <t>Mahbub0954</t>
+          <t>studyniftymalayalam</t>
         </is>
       </c>
       <c r="D699" s="19" t="inlineStr">
         <is>
-          <t>helperofficial786@gmail.com</t>
+          <t>aidotechindia@gmail.com</t>
         </is>
       </c>
       <c r="E699" s="19" t="inlineStr">
         <is>
-          <t>7667937751</t>
+          <t>8848066533</t>
         </is>
       </c>
       <c r="F699" s="19" t="inlineStr">
@@ -51095,42 +51095,474 @@
       </c>
       <c r="G699" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H699" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I699" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J699" s="21" t="n">
+        <v>1245</v>
+      </c>
+      <c r="K699" s="21" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L699" s="22" t="n">
+        <v>1245</v>
+      </c>
+      <c r="M699" s="19" t="inlineStr">
+        <is>
+          <t>6909a2491e2589001342a886</t>
+        </is>
+      </c>
+      <c r="N699" s="23" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/6909a2491e2589001342a886</t>
+        </is>
+      </c>
+      <c r="O699" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P699" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="12" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" s="13" t="inlineStr">
+        <is>
+          <t>6a2a3b18739da100136db6f1</t>
+        </is>
+      </c>
+      <c r="C700" s="13" t="inlineStr">
+        <is>
+          <t>mr-perfectofficial</t>
+        </is>
+      </c>
+      <c r="D700" s="12" t="inlineStr">
+        <is>
+          <t>mr.perfect.official018@gmail.com</t>
+        </is>
+      </c>
+      <c r="E700" s="12" t="inlineStr">
+        <is>
+          <t>9116087897</t>
+        </is>
+      </c>
+      <c r="F700" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G700" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H700" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I700" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J700" s="14" t="n">
+        <v>1172</v>
+      </c>
+      <c r="K700" s="14" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L700" s="15" t="n">
+        <v>1220</v>
+      </c>
+      <c r="M700" s="12" t="inlineStr">
+        <is>
+          <t>6a7d364eb62576001374f10c</t>
+        </is>
+      </c>
+      <c r="N700" s="16" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
+        </is>
+      </c>
+      <c r="O700" s="17" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P700" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" s="20" t="inlineStr">
+        <is>
+          <t>64bbeb37cd861f002058b8c2</t>
+        </is>
+      </c>
+      <c r="C701" s="20" t="inlineStr">
+        <is>
+          <t>SBTrader123</t>
+        </is>
+      </c>
+      <c r="D701" s="19" t="inlineStr">
+        <is>
+          <t>safeexit2022@gmail.com</t>
+        </is>
+      </c>
+      <c r="E701" s="19" t="inlineStr">
+        <is>
+          <t>9340517160</t>
+        </is>
+      </c>
+      <c r="F701" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G701" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H701" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I701" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J701" s="21" t="n">
+        <v>1161</v>
+      </c>
+      <c r="K701" s="21" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L701" s="22" t="n">
+        <v>1161</v>
+      </c>
+      <c r="M701" s="19" t="inlineStr">
+        <is>
+          <t>64bbed001a03ba0021a80161</t>
+        </is>
+      </c>
+      <c r="N701" s="23" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/64bbed001a03ba0021a80161</t>
+        </is>
+      </c>
+      <c r="O701" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P701" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="12" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" s="13" t="inlineStr">
+        <is>
+          <t>6436d5892b2028001fbf607b</t>
+        </is>
+      </c>
+      <c r="C702" s="13" t="inlineStr">
+        <is>
+          <t>Livelonghari</t>
+        </is>
+      </c>
+      <c r="D702" s="12" t="inlineStr">
+        <is>
+          <t>livelongwealth@gmail.com</t>
+        </is>
+      </c>
+      <c r="E702" s="12" t="inlineStr">
+        <is>
+          <t>9544085264</t>
+        </is>
+      </c>
+      <c r="F702" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G702" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H702" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I702" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J702" s="14" t="n">
+        <v>1080</v>
+      </c>
+      <c r="K702" s="14" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L702" s="15" t="n">
+        <v>1080</v>
+      </c>
+      <c r="M702" s="12" t="inlineStr">
+        <is>
+          <t>653e68ea423d4e001eef5b19</t>
+        </is>
+      </c>
+      <c r="N702" s="16" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
+        </is>
+      </c>
+      <c r="O702" s="17" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P702" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="19" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" s="20" t="inlineStr">
+        <is>
+          <t>67e424ccab747f00135495b4</t>
+        </is>
+      </c>
+      <c r="C703" s="20" t="inlineStr">
+        <is>
+          <t>jobposting</t>
+        </is>
+      </c>
+      <c r="D703" s="19" t="inlineStr">
+        <is>
+          <t>sagarruttare@gmail.com</t>
+        </is>
+      </c>
+      <c r="E703" s="19" t="inlineStr">
+        <is>
+          <t>7796716569</t>
+        </is>
+      </c>
+      <c r="F703" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G703" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H703" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I703" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J703" s="21" t="n">
+        <v>1078</v>
+      </c>
+      <c r="K703" s="21" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L703" s="22" t="n">
+        <v>1078</v>
+      </c>
+      <c r="M703" s="19" t="inlineStr">
+        <is>
+          <t>692dae30d42b600013b13d78</t>
+        </is>
+      </c>
+      <c r="N703" s="23" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
+        </is>
+      </c>
+      <c r="O703" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P703" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="12" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" s="13" t="inlineStr">
+        <is>
+          <t>69ad496eafc0e100130d7f09</t>
+        </is>
+      </c>
+      <c r="C704" s="13" t="inlineStr">
+        <is>
+          <t>sunoaudiobook</t>
+        </is>
+      </c>
+      <c r="D704" s="12" t="inlineStr">
+        <is>
+          <t>devrajstudio09@gmail.com</t>
+        </is>
+      </c>
+      <c r="E704" s="12" t="inlineStr">
+        <is>
+          <t>7869490714</t>
+        </is>
+      </c>
+      <c r="F704" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G704" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H704" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I704" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J704" s="14" t="n">
+        <v>1031</v>
+      </c>
+      <c r="K704" s="14" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L704" s="15" t="n">
+        <v>1031</v>
+      </c>
+      <c r="M704" s="12" t="inlineStr">
+        <is>
+          <t>6a4684b13604a700135096e1</t>
+        </is>
+      </c>
+      <c r="N704" s="16" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/6a4684b13604a700135096e1</t>
+        </is>
+      </c>
+      <c r="O704" s="17" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P704" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="19" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" s="20" t="inlineStr">
+        <is>
+          <t>68efa32deb549e001385d2c4</t>
+        </is>
+      </c>
+      <c r="C705" s="20" t="inlineStr">
+        <is>
+          <t>Mahbub0954</t>
+        </is>
+      </c>
+      <c r="D705" s="19" t="inlineStr">
+        <is>
+          <t>helperofficial786@gmail.com</t>
+        </is>
+      </c>
+      <c r="E705" s="19" t="inlineStr">
+        <is>
+          <t>7667937751</t>
+        </is>
+      </c>
+      <c r="F705" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G705" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H705" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I705" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J705" s="21" t="n">
         <v>1017</v>
       </c>
-      <c r="K699" s="21" t="n">
+      <c r="K705" s="21" t="n">
         <v>1017</v>
       </c>
-      <c r="L699" s="22" t="n">
+      <c r="L705" s="22" t="n">
         <v>1017</v>
       </c>
-      <c r="M699" s="19" t="inlineStr">
+      <c r="M705" s="19" t="inlineStr">
         <is>
           <t>68f1b5ebaacf8d0013e01c1e</t>
         </is>
       </c>
-      <c r="N699" s="23" t="inlineStr">
+      <c r="N705" s="23" t="inlineStr">
         <is>
           <t>https://superprofile.bio/vig/68f1b5ebaacf8d0013e01c1e</t>
         </is>
       </c>
-      <c r="O699" s="24" t="inlineStr">
-        <is>
-          <t>Not Verified</t>
-        </is>
-      </c>
-      <c r="P699" s="18" t="inlineStr">
+      <c r="O705" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P705" s="18" t="inlineStr">
         <is>
           <t>HOLD - RELEASE RESTRICTED</t>
         </is>
@@ -51836,6 +52268,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N697" r:id="rId696"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N698" r:id="rId697"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N705" r:id="rId704"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 06:27:44 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 08:51:34 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 08:51:34 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 10:07:43 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:07:43 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 10:24:34 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:24:34 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 10:36:01 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 10:36:01 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 11:03:58 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 11:03:58 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 13:18:54 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 13:18:54 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 14:31:44 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 14:31:44 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 16:42:01 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-05 16:42:01 | Daily Audits Logged: 7</t>
+          <t>Generated On: 2026-09-05 17:44:50 | Daily Audits Logged: 7</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 02:22:31 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 05:33:07 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 05:33:07 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 06:27:04 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 06:27:04 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 06:54:36 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 06:54:36 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 08:18:15 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 08:18:15 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 10:19:17 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 10:19:17 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 11:59:11 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 11:59:11 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 13:28:09 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 13:28:09 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 14:03:11 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 14:03:11 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 14:14:04 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 14:14:04 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 14:53:17 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 14:53:17 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 16:48:40 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-06 16:48:40 | Daily Audits Logged: 8</t>
+          <t>Generated On: 2026-09-06 17:48:19 | Daily Audits Logged: 8</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 02:20:03 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 05:43:51 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 05:43:51 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 06:35:21 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹34,137,362.00</t>
+          <t>₹34,167,992.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2694467</v>
+        <v>2737539</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>8</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>50852</v>
+        <v>8574</v>
       </c>
       <c r="K22" s="14" t="n">
         <v>250816</v>
@@ -5999,7 +5999,7 @@
         <v>8</v>
       </c>
       <c r="J72" s="14" t="n">
-        <v>21455</v>
+        <v>15997</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>122989</v>
@@ -8842,22 +8842,22 @@
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>667da0645d2c340013656ad7</t>
+          <t>648f53edccfdc8002aff354d</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>learninggroup01</t>
+          <t>stockmarketdetails</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>education61859586@gmail.com</t>
+          <t>aronsaif008@GMAIL.COM</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>8650198055</t>
+          <t>9079835137</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -8872,29 +8872,29 @@
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I112" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J112" s="14" t="n">
-        <v>18018</v>
+        <v>4029</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>85062</v>
+        <v>85407</v>
       </c>
       <c r="L112" s="15" t="n">
-        <v>21410</v>
+        <v>15947</v>
       </c>
       <c r="M112" s="12" t="inlineStr">
         <is>
-          <t>668b4f3db5c64700139c7370</t>
+          <t>64ddb6a847ac1d001e9857b1</t>
         </is>
       </c>
       <c r="N112" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/668b4f3db5c64700139c7370</t>
+          <t>https://superprofile.bio/vig/64ddb6a847ac1d001e9857b1</t>
         </is>
       </c>
       <c r="O112" s="17" t="inlineStr">
@@ -8914,22 +8914,22 @@
       </c>
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>64191cd926d3cc0020071427</t>
+          <t>667da0645d2c340013656ad7</t>
         </is>
       </c>
       <c r="C113" s="20" t="inlineStr">
         <is>
-          <t>optionexpert</t>
+          <t>learninggroup01</t>
         </is>
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t>marketexpert112@gmail.com</t>
+          <t>education61859586@gmail.com</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t>9669385977</t>
+          <t>8650198055</t>
         </is>
       </c>
       <c r="F113" s="19" t="inlineStr">
@@ -8939,34 +8939,34 @@
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H113" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I113" s="20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J113" s="21" t="n">
-        <v>23967</v>
+        <v>18018</v>
       </c>
       <c r="K113" s="21" t="n">
-        <v>83703</v>
+        <v>85062</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>37702</v>
+        <v>21410</v>
       </c>
       <c r="M113" s="19" t="inlineStr">
         <is>
-          <t>652764d7fc8f0200282c0577</t>
+          <t>668b4f3db5c64700139c7370</t>
         </is>
       </c>
       <c r="N113" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/652764d7fc8f0200282c0577</t>
+          <t>https://superprofile.bio/vig/668b4f3db5c64700139c7370</t>
         </is>
       </c>
       <c r="O113" s="24" t="inlineStr">
@@ -8986,22 +8986,22 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>65b5bc2daa6275001da0c01d</t>
+          <t>64191cd926d3cc0020071427</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>vikramsinh8788</t>
+          <t>optionexpert</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>maverai08@gmail.com</t>
+          <t>marketexpert112@gmail.com</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>9879027469</t>
+          <t>9669385977</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
@@ -9011,34 +9011,34 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I114" s="13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J114" s="14" t="n">
-        <v>4777</v>
+        <v>23967</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>82987</v>
+        <v>83703</v>
       </c>
       <c r="L114" s="15" t="n">
-        <v>18517</v>
+        <v>37702</v>
       </c>
       <c r="M114" s="12" t="inlineStr">
         <is>
-          <t>69d6441f287bd70013f90e8c</t>
+          <t>652764d7fc8f0200282c0577</t>
         </is>
       </c>
       <c r="N114" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d6441f287bd70013f90e8c</t>
+          <t>https://superprofile.bio/vig/652764d7fc8f0200282c0577</t>
         </is>
       </c>
       <c r="O114" s="17" t="inlineStr">
@@ -9058,22 +9058,22 @@
       </c>
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>69be3238b2f3ae0013f126bd</t>
+          <t>65b5bc2daa6275001da0c01d</t>
         </is>
       </c>
       <c r="C115" s="20" t="inlineStr">
         <is>
-          <t>thestocksmania81</t>
+          <t>vikramsinh8788</t>
         </is>
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t>thestocksmania08@gmail.com</t>
+          <t>maverai08@gmail.com</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t>9038883253</t>
+          <t>9879027469</t>
         </is>
       </c>
       <c r="F115" s="19" t="inlineStr">
@@ -9095,22 +9095,22 @@
         <v>8</v>
       </c>
       <c r="J115" s="21" t="n">
-        <v>2425</v>
+        <v>4777</v>
       </c>
       <c r="K115" s="21" t="n">
-        <v>82918</v>
+        <v>82987</v>
       </c>
       <c r="L115" s="22" t="n">
-        <v>68460</v>
+        <v>18517</v>
       </c>
       <c r="M115" s="19" t="inlineStr">
         <is>
-          <t>66045dc58fe788104551632f</t>
+          <t>69d6441f287bd70013f90e8c</t>
         </is>
       </c>
       <c r="N115" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66045dc58fe788104551632f</t>
+          <t>https://superprofile.bio/vig/69d6441f287bd70013f90e8c</t>
         </is>
       </c>
       <c r="O115" s="24" t="inlineStr">
@@ -9130,22 +9130,22 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>64a520adc6f02f00209d9697</t>
+          <t>69be3238b2f3ae0013f126bd</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>learnbasic</t>
+          <t>thestocksmania81</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>nageshwarankit23@gmail.com</t>
+          <t>thestocksmania08@gmail.com</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>7840922465</t>
+          <t>9038883253</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
@@ -9164,25 +9164,25 @@
         </is>
       </c>
       <c r="I116" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>2857</v>
+        <v>2425</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>82765</v>
+        <v>82918</v>
       </c>
       <c r="L116" s="15" t="n">
-        <v>17124</v>
+        <v>68460</v>
       </c>
       <c r="M116" s="12" t="inlineStr">
         <is>
-          <t>647c894870fe91002b0f4c8f</t>
+          <t>66045dc58fe788104551632f</t>
         </is>
       </c>
       <c r="N116" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647c894870fe91002b0f4c8f</t>
+          <t>https://superprofile.bio/vig/66045dc58fe788104551632f</t>
         </is>
       </c>
       <c r="O116" s="17" t="inlineStr">
@@ -9202,22 +9202,22 @@
       </c>
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>68c028c79760310013afe186</t>
+          <t>64a520adc6f02f00209d9697</t>
         </is>
       </c>
       <c r="C117" s="20" t="inlineStr">
         <is>
-          <t>everydaytrading</t>
+          <t>learnbasic</t>
         </is>
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t>herobee7223@gmail.com</t>
+          <t>nageshwarankit23@gmail.com</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>6269583123</t>
+          <t>7840922465</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
@@ -9232,29 +9232,29 @@
       </c>
       <c r="H117" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I117" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J117" s="21" t="n">
-        <v>11762</v>
+        <v>2857</v>
       </c>
       <c r="K117" s="21" t="n">
-        <v>82151</v>
+        <v>82765</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>23055</v>
+        <v>17124</v>
       </c>
       <c r="M117" s="19" t="inlineStr">
         <is>
-          <t>68c67381e4826a00139bb5cf</t>
+          <t>647c894870fe91002b0f4c8f</t>
         </is>
       </c>
       <c r="N117" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c67381e4826a00139bb5cf</t>
+          <t>https://superprofile.bio/vig/647c894870fe91002b0f4c8f</t>
         </is>
       </c>
       <c r="O117" s="24" t="inlineStr">
@@ -9274,22 +9274,22 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>65f40b7084681c00130db00f</t>
+          <t>68c028c79760310013afe186</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>zerotoheroexpert</t>
+          <t>everydaytrading</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>zerotoherotrading057@gmail.com</t>
+          <t>herobee7223@gmail.com</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>8003373805</t>
+          <t>6269583123</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
@@ -9308,25 +9308,25 @@
         </is>
       </c>
       <c r="I118" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J118" s="14" t="n">
-        <v>2911</v>
+        <v>11762</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>81442</v>
+        <v>82151</v>
       </c>
       <c r="L118" s="15" t="n">
-        <v>26168</v>
+        <v>23055</v>
       </c>
       <c r="M118" s="12" t="inlineStr">
         <is>
-          <t>672856f13fbd59001317deea</t>
+          <t>68c67381e4826a00139bb5cf</t>
         </is>
       </c>
       <c r="N118" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/672856f13fbd59001317deea</t>
+          <t>https://superprofile.bio/vig/68c67381e4826a00139bb5cf</t>
         </is>
       </c>
       <c r="O118" s="17" t="inlineStr">
@@ -9346,22 +9346,22 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>648f53edccfdc8002aff354d</t>
+          <t>65f40b7084681c00130db00f</t>
         </is>
       </c>
       <c r="C119" s="20" t="inlineStr">
         <is>
-          <t>stockmarketdetails</t>
+          <t>zerotoheroexpert</t>
         </is>
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t>aronsaif008@GMAIL.COM</t>
+          <t>zerotoherotrading057@gmail.com</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t>9079835137</t>
+          <t>8003373805</t>
         </is>
       </c>
       <c r="F119" s="19" t="inlineStr">
@@ -9376,29 +9376,29 @@
       </c>
       <c r="H119" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I119" s="20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J119" s="21" t="n">
-        <v>4029</v>
+        <v>2911</v>
       </c>
       <c r="K119" s="21" t="n">
-        <v>81378</v>
+        <v>81442</v>
       </c>
       <c r="L119" s="22" t="n">
-        <v>15947</v>
+        <v>26168</v>
       </c>
       <c r="M119" s="19" t="inlineStr">
         <is>
-          <t>64ddb6a847ac1d001e9857b1</t>
+          <t>672856f13fbd59001317deea</t>
         </is>
       </c>
       <c r="N119" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64ddb6a847ac1d001e9857b1</t>
+          <t>https://superprofile.bio/vig/672856f13fbd59001317deea</t>
         </is>
       </c>
       <c r="O119" s="24" t="inlineStr">
@@ -11362,22 +11362,22 @@
       </c>
       <c r="B147" s="20" t="inlineStr">
         <is>
-          <t>64cc9ae0500648001d42e01c</t>
+          <t>68384fb7f6fecd0013930afc</t>
         </is>
       </c>
       <c r="C147" s="20" t="inlineStr">
         <is>
-          <t>stoxup</t>
+          <t>pihu00</t>
         </is>
       </c>
       <c r="D147" s="19" t="inlineStr">
         <is>
-          <t>dinesh060799@gmail.com</t>
+          <t>suryanshsakshi26@gmail.com</t>
         </is>
       </c>
       <c r="E147" s="19" t="inlineStr">
         <is>
-          <t>7568442454</t>
+          <t>8439752930</t>
         </is>
       </c>
       <c r="F147" s="19" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G147" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H147" s="19" t="inlineStr">
@@ -11399,22 +11399,22 @@
         <v>7</v>
       </c>
       <c r="J147" s="21" t="n">
-        <v>22466</v>
+        <v>10240</v>
       </c>
       <c r="K147" s="21" t="n">
-        <v>61168</v>
+        <v>61569</v>
       </c>
       <c r="L147" s="22" t="n">
-        <v>28077</v>
+        <v>12340</v>
       </c>
       <c r="M147" s="19" t="inlineStr">
         <is>
-          <t>68d11c79211346001339d1fc</t>
+          <t>69bb9a626bc32b00132d43af</t>
         </is>
       </c>
       <c r="N147" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d11c79211346001339d1fc</t>
+          <t>https://superprofile.bio/vig/69bb9a626bc32b00132d43af</t>
         </is>
       </c>
       <c r="O147" s="24" t="inlineStr">
@@ -11434,22 +11434,22 @@
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>6391d53d8e6bc3002c0f7105</t>
+          <t>64cc9ae0500648001d42e01c</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>secretsystem</t>
+          <t>stoxup</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>mahendrasankhala760@gmail.com</t>
+          <t>dinesh060799@gmail.com</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>8302154371</t>
+          <t>7568442454</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -11471,22 +11471,22 @@
         <v>7</v>
       </c>
       <c r="J148" s="14" t="n">
-        <v>10063</v>
+        <v>22466</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>60433</v>
+        <v>61168</v>
       </c>
       <c r="L148" s="15" t="n">
-        <v>14410</v>
+        <v>28077</v>
       </c>
       <c r="M148" s="12" t="inlineStr">
         <is>
-          <t>66feba7d2a7c600013944424</t>
+          <t>68d11c79211346001339d1fc</t>
         </is>
       </c>
       <c r="N148" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66feba7d2a7c600013944424</t>
+          <t>https://superprofile.bio/vig/68d11c79211346001339d1fc</t>
         </is>
       </c>
       <c r="O148" s="17" t="inlineStr">
@@ -11506,22 +11506,22 @@
       </c>
       <c r="B149" s="20" t="inlineStr">
         <is>
-          <t>63c7cee4ed193700365233cd</t>
+          <t>6391d53d8e6bc3002c0f7105</t>
         </is>
       </c>
       <c r="C149" s="20" t="inlineStr">
         <is>
-          <t>tradingstarofficial</t>
+          <t>secretsystem</t>
         </is>
       </c>
       <c r="D149" s="19" t="inlineStr">
         <is>
-          <t>helptradingstar@gmail.com</t>
+          <t>mahendrasankhala760@gmail.com</t>
         </is>
       </c>
       <c r="E149" s="19" t="inlineStr">
         <is>
-          <t>9288070016</t>
+          <t>8302154371</t>
         </is>
       </c>
       <c r="F149" s="19" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="G149" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H149" s="19" t="inlineStr">
@@ -11540,25 +11540,25 @@
         </is>
       </c>
       <c r="I149" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J149" s="21" t="n">
-        <v>10732</v>
+        <v>10063</v>
       </c>
       <c r="K149" s="21" t="n">
-        <v>60392</v>
+        <v>60433</v>
       </c>
       <c r="L149" s="22" t="n">
-        <v>16531</v>
+        <v>14410</v>
       </c>
       <c r="M149" s="19" t="inlineStr">
         <is>
-          <t>6a01481246724b0013a2614c</t>
+          <t>66feba7d2a7c600013944424</t>
         </is>
       </c>
       <c r="N149" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a01481246724b0013a2614c</t>
+          <t>https://superprofile.bio/vig/66feba7d2a7c600013944424</t>
         </is>
       </c>
       <c r="O149" s="24" t="inlineStr">
@@ -11578,22 +11578,22 @@
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>649330ea3b6d6900200fdb05</t>
+          <t>63c7cee4ed193700365233cd</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>fando</t>
+          <t>tradingstarofficial</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>shashihk0@gmail.com</t>
+          <t>helptradingstar@gmail.com</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>9343949080</t>
+          <t>9288070016</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
@@ -11612,25 +11612,25 @@
         </is>
       </c>
       <c r="I150" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J150" s="14" t="n">
-        <v>3437</v>
+        <v>10732</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>60289</v>
+        <v>60392</v>
       </c>
       <c r="L150" s="15" t="n">
-        <v>26050</v>
+        <v>16531</v>
       </c>
       <c r="M150" s="12" t="inlineStr">
         <is>
-          <t>68da766ae5d1d00013cfb6d7</t>
+          <t>6a01481246724b0013a2614c</t>
         </is>
       </c>
       <c r="N150" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68da766ae5d1d00013cfb6d7</t>
+          <t>https://superprofile.bio/vig/6a01481246724b0013a2614c</t>
         </is>
       </c>
       <c r="O150" s="17" t="inlineStr">
@@ -11650,22 +11650,22 @@
       </c>
       <c r="B151" s="20" t="inlineStr">
         <is>
-          <t>64ab6b8673ab82002b92ef6a</t>
+          <t>68fc64086d7f7b00132e8664</t>
         </is>
       </c>
       <c r="C151" s="20" t="inlineStr">
         <is>
-          <t>swastiktrading</t>
+          <t>bulishbe</t>
         </is>
       </c>
       <c r="D151" s="19" t="inlineStr">
         <is>
-          <t>yashv.business@gmail.com</t>
+          <t>shivamsomani360@gmail.com</t>
         </is>
       </c>
       <c r="E151" s="19" t="inlineStr">
         <is>
-          <t>8839218332</t>
+          <t>7413942083</t>
         </is>
       </c>
       <c r="F151" s="19" t="inlineStr">
@@ -11675,34 +11675,34 @@
       </c>
       <c r="G151" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H151" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I151" s="20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J151" s="21" t="n">
-        <v>3882</v>
+        <v>2946</v>
       </c>
       <c r="K151" s="21" t="n">
-        <v>60174</v>
+        <v>60329</v>
       </c>
       <c r="L151" s="22" t="n">
-        <v>58230</v>
+        <v>20067</v>
       </c>
       <c r="M151" s="19" t="inlineStr">
         <is>
-          <t>6a87e124014dfe0013676114</t>
+          <t>670500b24509b400132cb385</t>
         </is>
       </c>
       <c r="N151" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a87e124014dfe0013676114</t>
+          <t>https://superprofile.bio/vig/670500b24509b400132cb385</t>
         </is>
       </c>
       <c r="O151" s="24" t="inlineStr">
@@ -11722,22 +11722,22 @@
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>6443c3c058544c002035fae3</t>
+          <t>649330ea3b6d6900200fdb05</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>profitmillionaire</t>
+          <t>fando</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>profitmillionairegroup@gmail.com</t>
+          <t>shashihk0@gmail.com</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>8446865866</t>
+          <t>9343949080</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -11756,25 +11756,25 @@
         </is>
       </c>
       <c r="I152" s="13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J152" s="14" t="n">
-        <v>9526</v>
+        <v>3437</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>60093</v>
+        <v>60289</v>
       </c>
       <c r="L152" s="15" t="n">
-        <v>16849</v>
+        <v>26050</v>
       </c>
       <c r="M152" s="12" t="inlineStr">
         <is>
-          <t>6a58249222d9b50013a45019</t>
+          <t>68da766ae5d1d00013cfb6d7</t>
         </is>
       </c>
       <c r="N152" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a58249222d9b50013a45019</t>
+          <t>https://superprofile.bio/vig/68da766ae5d1d00013cfb6d7</t>
         </is>
       </c>
       <c r="O152" s="17" t="inlineStr">
@@ -11794,22 +11794,22 @@
       </c>
       <c r="B153" s="20" t="inlineStr">
         <is>
-          <t>66842a747c9daa001273da10</t>
+          <t>64ab6b8673ab82002b92ef6a</t>
         </is>
       </c>
       <c r="C153" s="20" t="inlineStr">
         <is>
-          <t>bulllions</t>
+          <t>swastiktrading</t>
         </is>
       </c>
       <c r="D153" s="19" t="inlineStr">
         <is>
-          <t>thestockmarket1111@gmail.com</t>
+          <t>yashv.business@gmail.com</t>
         </is>
       </c>
       <c r="E153" s="19" t="inlineStr">
         <is>
-          <t>8448709939</t>
+          <t>8839218332</t>
         </is>
       </c>
       <c r="F153" s="19" t="inlineStr">
@@ -11824,29 +11824,29 @@
       </c>
       <c r="H153" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I153" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J153" s="21" t="n">
-        <v>15654</v>
+        <v>3882</v>
       </c>
       <c r="K153" s="21" t="n">
-        <v>60001</v>
+        <v>60174</v>
       </c>
       <c r="L153" s="22" t="n">
-        <v>21393</v>
+        <v>58230</v>
       </c>
       <c r="M153" s="19" t="inlineStr">
         <is>
-          <t>67ac62ef81438f00127c43bb</t>
+          <t>6a87e124014dfe0013676114</t>
         </is>
       </c>
       <c r="N153" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ac62ef81438f00127c43bb</t>
+          <t>https://superprofile.bio/vig/6a87e124014dfe0013676114</t>
         </is>
       </c>
       <c r="O153" s="24" t="inlineStr">
@@ -11866,22 +11866,22 @@
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>65473a7f3fad8004611cb71e</t>
+          <t>6443c3c058544c002035fae3</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>mahesh3009</t>
+          <t>profitmillionaire</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>Wadhwahosiery@gmail.com</t>
+          <t>profitmillionairegroup@gmail.com</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>9213297755</t>
+          <t>8446865866</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
@@ -11900,25 +11900,25 @@
         </is>
       </c>
       <c r="I154" s="13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J154" s="14" t="n">
-        <v>4882</v>
+        <v>9526</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>58442</v>
+        <v>60093</v>
       </c>
       <c r="L154" s="15" t="n">
-        <v>13563</v>
+        <v>16849</v>
       </c>
       <c r="M154" s="12" t="inlineStr">
         <is>
-          <t>6620bca29f96c2435e02b516</t>
+          <t>6a58249222d9b50013a45019</t>
         </is>
       </c>
       <c r="N154" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6620bca29f96c2435e02b516</t>
+          <t>https://superprofile.bio/vig/6a58249222d9b50013a45019</t>
         </is>
       </c>
       <c r="O154" s="17" t="inlineStr">
@@ -11938,22 +11938,22 @@
       </c>
       <c r="B155" s="20" t="inlineStr">
         <is>
-          <t>68b8146651190f0013db1745</t>
+          <t>66842a747c9daa001273da10</t>
         </is>
       </c>
       <c r="C155" s="20" t="inlineStr">
         <is>
-          <t>vedicjyotishsanar</t>
+          <t>bulllions</t>
         </is>
       </c>
       <c r="D155" s="19" t="inlineStr">
         <is>
-          <t>vikramsinghvedang@gmail.com</t>
+          <t>thestockmarket1111@gmail.com</t>
         </is>
       </c>
       <c r="E155" s="19" t="inlineStr">
         <is>
-          <t>7078397050</t>
+          <t>8448709939</t>
         </is>
       </c>
       <c r="F155" s="19" t="inlineStr">
@@ -11968,29 +11968,29 @@
       </c>
       <c r="H155" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I155" s="20" t="n">
         <v>6</v>
       </c>
       <c r="J155" s="21" t="n">
-        <v>11646</v>
+        <v>15654</v>
       </c>
       <c r="K155" s="21" t="n">
-        <v>58041</v>
+        <v>60001</v>
       </c>
       <c r="L155" s="22" t="n">
-        <v>30867</v>
+        <v>21393</v>
       </c>
       <c r="M155" s="19" t="inlineStr">
         <is>
-          <t>69df0b935a89b70013ccc651</t>
+          <t>67ac62ef81438f00127c43bb</t>
         </is>
       </c>
       <c r="N155" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69df0b935a89b70013ccc651</t>
+          <t>https://superprofile.bio/vig/67ac62ef81438f00127c43bb</t>
         </is>
       </c>
       <c r="O155" s="24" t="inlineStr">
@@ -12010,22 +12010,22 @@
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>68fc64086d7f7b00132e8664</t>
+          <t>698960d575efa100133dc34a</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>bulishbe</t>
+          <t>mbtrading</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>shivamsomani360@gmail.com</t>
+          <t>brijeshshah898@gmail.com</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>7413942083</t>
+          <t>7388327183</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
@@ -12035,34 +12035,34 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I156" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J156" s="14" t="n">
-        <v>2946</v>
+        <v>13415</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>57383</v>
+        <v>58957</v>
       </c>
       <c r="L156" s="15" t="n">
-        <v>20067</v>
+        <v>13415</v>
       </c>
       <c r="M156" s="12" t="inlineStr">
         <is>
-          <t>670500b24509b400132cb385</t>
+          <t>69a63a3b0035f00013abc48a</t>
         </is>
       </c>
       <c r="N156" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/670500b24509b400132cb385</t>
+          <t>https://superprofile.bio/vig/69a63a3b0035f00013abc48a</t>
         </is>
       </c>
       <c r="O156" s="17" t="inlineStr">
@@ -12082,22 +12082,22 @@
       </c>
       <c r="B157" s="20" t="inlineStr">
         <is>
-          <t>6700b5b72a57240013df898e</t>
+          <t>65473a7f3fad8004611cb71e</t>
         </is>
       </c>
       <c r="C157" s="20" t="inlineStr">
         <is>
-          <t>drmayukhhazra</t>
+          <t>mahesh3009</t>
         </is>
       </c>
       <c r="D157" s="19" t="inlineStr">
         <is>
-          <t>mayukhhazra1998@gmail.com</t>
+          <t>Wadhwahosiery@gmail.com</t>
         </is>
       </c>
       <c r="E157" s="19" t="inlineStr">
         <is>
-          <t>8250554404</t>
+          <t>9213297755</t>
         </is>
       </c>
       <c r="F157" s="19" t="inlineStr">
@@ -12119,22 +12119,22 @@
         <v>9</v>
       </c>
       <c r="J157" s="21" t="n">
-        <v>4163</v>
+        <v>4882</v>
       </c>
       <c r="K157" s="21" t="n">
-        <v>57135</v>
+        <v>58442</v>
       </c>
       <c r="L157" s="22" t="n">
-        <v>13541</v>
+        <v>13563</v>
       </c>
       <c r="M157" s="19" t="inlineStr">
         <is>
-          <t>6905e814429e060013ff74f2</t>
+          <t>6620bca29f96c2435e02b516</t>
         </is>
       </c>
       <c r="N157" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6905e814429e060013ff74f2</t>
+          <t>https://superprofile.bio/vig/6620bca29f96c2435e02b516</t>
         </is>
       </c>
       <c r="O157" s="24" t="inlineStr">
@@ -12154,22 +12154,22 @@
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>65d0bb030524d90012989f5b</t>
+          <t>68b8146651190f0013db1745</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>stockmarket89</t>
+          <t>vedicjyotishsanar</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>Shyamkalani95@gmail.com</t>
+          <t>vikramsinghvedang@gmail.com</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>8955931195</t>
+          <t>7078397050</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
@@ -12179,34 +12179,34 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I158" s="13" t="n">
         <v>6</v>
       </c>
       <c r="J158" s="14" t="n">
-        <v>3154</v>
+        <v>11646</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>56968</v>
+        <v>58041</v>
       </c>
       <c r="L158" s="15" t="n">
-        <v>34616</v>
+        <v>30867</v>
       </c>
       <c r="M158" s="12" t="inlineStr">
         <is>
-          <t>6485e8894454f1002a688918</t>
+          <t>69df0b935a89b70013ccc651</t>
         </is>
       </c>
       <c r="N158" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6485e8894454f1002a688918</t>
+          <t>https://superprofile.bio/vig/69df0b935a89b70013ccc651</t>
         </is>
       </c>
       <c r="O158" s="17" t="inlineStr">
@@ -12226,22 +12226,22 @@
       </c>
       <c r="B159" s="20" t="inlineStr">
         <is>
-          <t>687a07838aeacf0013a9f58c</t>
+          <t>6700b5b72a57240013df898e</t>
         </is>
       </c>
       <c r="C159" s="20" t="inlineStr">
         <is>
-          <t>trendwolf2326</t>
+          <t>drmayukhhazra</t>
         </is>
       </c>
       <c r="D159" s="19" t="inlineStr">
         <is>
-          <t>technox.trade@gmail.com</t>
+          <t>mayukhhazra1998@gmail.com</t>
         </is>
       </c>
       <c r="E159" s="19" t="inlineStr">
         <is>
-          <t>8160628197</t>
+          <t>8250554404</t>
         </is>
       </c>
       <c r="F159" s="19" t="inlineStr">
@@ -12256,29 +12256,29 @@
       </c>
       <c r="H159" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I159" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J159" s="21" t="n">
-        <v>1952</v>
+        <v>4163</v>
       </c>
       <c r="K159" s="21" t="n">
-        <v>56821</v>
+        <v>57135</v>
       </c>
       <c r="L159" s="22" t="n">
-        <v>34556</v>
+        <v>13541</v>
       </c>
       <c r="M159" s="19" t="inlineStr">
         <is>
-          <t>6944ec21d0013e00134d24e0</t>
+          <t>6905e814429e060013ff74f2</t>
         </is>
       </c>
       <c r="N159" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6944ec21d0013e00134d24e0</t>
+          <t>https://superprofile.bio/vig/6905e814429e060013ff74f2</t>
         </is>
       </c>
       <c r="O159" s="24" t="inlineStr">
@@ -12298,22 +12298,22 @@
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>64c7e110671a83001de0239f</t>
+          <t>65d0bb030524d90012989f5b</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>wealthcreator24</t>
+          <t>stockmarket89</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>shivamrathour1993@gmail.com</t>
+          <t>Shyamkalani95@gmail.com</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>9236003812</t>
+          <t>8955931195</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
@@ -12323,34 +12323,34 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I160" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J160" s="14" t="n">
-        <v>1954</v>
+        <v>3154</v>
       </c>
       <c r="K160" s="14" t="n">
-        <v>56715</v>
+        <v>56968</v>
       </c>
       <c r="L160" s="15" t="n">
-        <v>56639</v>
+        <v>34616</v>
       </c>
       <c r="M160" s="12" t="inlineStr">
         <is>
-          <t>6594509a02521d001db86770</t>
+          <t>6485e8894454f1002a688918</t>
         </is>
       </c>
       <c r="N160" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6594509a02521d001db86770</t>
+          <t>https://superprofile.bio/vig/6485e8894454f1002a688918</t>
         </is>
       </c>
       <c r="O160" s="17" t="inlineStr">
@@ -12370,22 +12370,22 @@
       </c>
       <c r="B161" s="20" t="inlineStr">
         <is>
-          <t>65bf8c50336354001e3003a3</t>
+          <t>687a07838aeacf0013a9f58c</t>
         </is>
       </c>
       <c r="C161" s="20" t="inlineStr">
         <is>
-          <t>amansharma85</t>
+          <t>trendwolf2326</t>
         </is>
       </c>
       <c r="D161" s="19" t="inlineStr">
         <is>
-          <t>Tradeteam.in@gmail.com</t>
+          <t>technox.trade@gmail.com</t>
         </is>
       </c>
       <c r="E161" s="19" t="inlineStr">
         <is>
-          <t>8699882116</t>
+          <t>8160628197</t>
         </is>
       </c>
       <c r="F161" s="19" t="inlineStr">
@@ -12400,29 +12400,29 @@
       </c>
       <c r="H161" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I161" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J161" s="21" t="n">
-        <v>27760</v>
+        <v>1952</v>
       </c>
       <c r="K161" s="21" t="n">
-        <v>55520</v>
+        <v>56821</v>
       </c>
       <c r="L161" s="22" t="n">
-        <v>27760</v>
+        <v>34556</v>
       </c>
       <c r="M161" s="19" t="inlineStr">
         <is>
-          <t>67495145098ae7001338559a</t>
+          <t>6944ec21d0013e00134d24e0</t>
         </is>
       </c>
       <c r="N161" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67495145098ae7001338559a</t>
+          <t>https://superprofile.bio/vig/6944ec21d0013e00134d24e0</t>
         </is>
       </c>
       <c r="O161" s="24" t="inlineStr">
@@ -12442,22 +12442,22 @@
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>66541c97ca30a000133c3bed</t>
+          <t>64c7e110671a83001de0239f</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>optionsparadise</t>
+          <t>wealthcreator24</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>Ratnadipgaikwad34@gmail.com</t>
+          <t>shivamrathour1993@gmail.com</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>9091025927</t>
+          <t>9236003812</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
@@ -12467,34 +12467,34 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I162" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J162" s="14" t="n">
-        <v>4871</v>
+        <v>1954</v>
       </c>
       <c r="K162" s="14" t="n">
-        <v>55338</v>
+        <v>56715</v>
       </c>
       <c r="L162" s="15" t="n">
-        <v>19421</v>
+        <v>56639</v>
       </c>
       <c r="M162" s="12" t="inlineStr">
         <is>
-          <t>675fb2c06244d90013ffd569</t>
+          <t>6594509a02521d001db86770</t>
         </is>
       </c>
       <c r="N162" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/675fb2c06244d90013ffd569</t>
+          <t>https://superprofile.bio/vig/6594509a02521d001db86770</t>
         </is>
       </c>
       <c r="O162" s="17" t="inlineStr">
@@ -12514,22 +12514,22 @@
       </c>
       <c r="B163" s="20" t="inlineStr">
         <is>
-          <t>677934d39aeb4b0013816267</t>
+          <t>65bf8c50336354001e3003a3</t>
         </is>
       </c>
       <c r="C163" s="20" t="inlineStr">
         <is>
-          <t>cosmofeedsuper</t>
+          <t>amansharma85</t>
         </is>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>rhushimane.ca@gmail.com</t>
+          <t>Tradeteam.in@gmail.com</t>
         </is>
       </c>
       <c r="E163" s="19" t="inlineStr">
         <is>
-          <t>8928549145</t>
+          <t>8699882116</t>
         </is>
       </c>
       <c r="F163" s="19" t="inlineStr">
@@ -12539,34 +12539,34 @@
       </c>
       <c r="G163" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H163" s="19" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H163" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="I163" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J163" s="21" t="n">
-        <v>34011</v>
+        <v>27760</v>
       </c>
       <c r="K163" s="21" t="n">
-        <v>55265</v>
+        <v>55520</v>
       </c>
       <c r="L163" s="22" t="n">
-        <v>34011</v>
+        <v>27760</v>
       </c>
       <c r="M163" s="19" t="inlineStr">
         <is>
-          <t>6901f529874dda0013d7e8f9</t>
+          <t>67495145098ae7001338559a</t>
         </is>
       </c>
       <c r="N163" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6901f529874dda0013d7e8f9</t>
+          <t>https://superprofile.bio/vig/67495145098ae7001338559a</t>
         </is>
       </c>
       <c r="O163" s="24" t="inlineStr">
@@ -12586,22 +12586,22 @@
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>63e79efafb1d710033a11eab</t>
+          <t>66541c97ca30a000133c3bed</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>deepdubey09</t>
+          <t>optionsparadise</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>deepdubeys24@gmail.com</t>
+          <t>Ratnadipgaikwad34@gmail.com</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>9456251468</t>
+          <t>9091025927</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
@@ -12611,34 +12611,34 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I164" s="13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J164" s="14" t="n">
-        <v>1861</v>
+        <v>4871</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>54904</v>
+        <v>55338</v>
       </c>
       <c r="L164" s="15" t="n">
-        <v>12786</v>
+        <v>19421</v>
       </c>
       <c r="M164" s="12" t="inlineStr">
         <is>
-          <t>6a87d76979d74e0013d98462</t>
+          <t>675fb2c06244d90013ffd569</t>
         </is>
       </c>
       <c r="N164" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a87d76979d74e0013d98462</t>
+          <t>https://superprofile.bio/vig/675fb2c06244d90013ffd569</t>
         </is>
       </c>
       <c r="O164" s="17" t="inlineStr">
@@ -12658,22 +12658,22 @@
       </c>
       <c r="B165" s="20" t="inlineStr">
         <is>
-          <t>656f190c85e895001e492ba2</t>
+          <t>677934d39aeb4b0013816267</t>
         </is>
       </c>
       <c r="C165" s="20" t="inlineStr">
         <is>
-          <t>mts3949</t>
+          <t>cosmofeedsuper</t>
         </is>
       </c>
       <c r="D165" s="19" t="inlineStr">
         <is>
-          <t>shivaniprashant77@gmail.com</t>
+          <t>rhushimane.ca@gmail.com</t>
         </is>
       </c>
       <c r="E165" s="19" t="inlineStr">
         <is>
-          <t>9284394639</t>
+          <t>8928549145</t>
         </is>
       </c>
       <c r="F165" s="19" t="inlineStr">
@@ -12683,34 +12683,34 @@
       </c>
       <c r="G165" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H165" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I165" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J165" s="21" t="n">
-        <v>1552</v>
+        <v>34011</v>
       </c>
       <c r="K165" s="21" t="n">
-        <v>54201</v>
+        <v>55265</v>
       </c>
       <c r="L165" s="22" t="n">
-        <v>24263</v>
+        <v>34011</v>
       </c>
       <c r="M165" s="19" t="inlineStr">
         <is>
-          <t>698f2450859ceb00130815a3</t>
+          <t>6901f529874dda0013d7e8f9</t>
         </is>
       </c>
       <c r="N165" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
+          <t>https://superprofile.bio/vig/6901f529874dda0013d7e8f9</t>
         </is>
       </c>
       <c r="O165" s="24" t="inlineStr">
@@ -12730,22 +12730,22 @@
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>67e62ed2f90398001392f46a</t>
+          <t>63e79efafb1d710033a11eab</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>dailylivetrade</t>
+          <t>deepdubey09</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>smdv.digital@gmail.com</t>
+          <t>deepdubeys24@gmail.com</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>8290268460</t>
+          <t>9456251468</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
@@ -12755,34 +12755,34 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I166" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J166" s="14" t="n">
-        <v>2534</v>
+        <v>1861</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>54190</v>
+        <v>54904</v>
       </c>
       <c r="L166" s="15" t="n">
-        <v>30200</v>
+        <v>12786</v>
       </c>
       <c r="M166" s="12" t="inlineStr">
         <is>
-          <t>69043d63a68ca50013eaf6ea</t>
+          <t>6a87d76979d74e0013d98462</t>
         </is>
       </c>
       <c r="N166" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69043d63a68ca50013eaf6ea</t>
+          <t>https://superprofile.bio/vig/6a87d76979d74e0013d98462</t>
         </is>
       </c>
       <c r="O166" s="17" t="inlineStr">
@@ -12802,22 +12802,22 @@
       </c>
       <c r="B167" s="20" t="inlineStr">
         <is>
-          <t>647afc6cbc5c8a0020c85fa7</t>
+          <t>656f190c85e895001e492ba2</t>
         </is>
       </c>
       <c r="C167" s="20" t="inlineStr">
         <is>
-          <t>Cbkhasiya</t>
+          <t>mts3949</t>
         </is>
       </c>
       <c r="D167" s="19" t="inlineStr">
         <is>
-          <t>cbkhasiya@gmail.com</t>
+          <t>shivaniprashant77@gmail.com</t>
         </is>
       </c>
       <c r="E167" s="19" t="inlineStr">
         <is>
-          <t>9081188188</t>
+          <t>9284394639</t>
         </is>
       </c>
       <c r="F167" s="19" t="inlineStr">
@@ -12836,25 +12836,25 @@
         </is>
       </c>
       <c r="I167" s="20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J167" s="21" t="n">
-        <v>3157</v>
+        <v>1552</v>
       </c>
       <c r="K167" s="21" t="n">
-        <v>54104</v>
+        <v>54201</v>
       </c>
       <c r="L167" s="22" t="n">
-        <v>9470</v>
+        <v>24263</v>
       </c>
       <c r="M167" s="19" t="inlineStr">
         <is>
-          <t>647df876e96cba002128da30</t>
+          <t>698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="N167" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647df876e96cba002128da30</t>
+          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="O167" s="24" t="inlineStr">
@@ -12874,22 +12874,22 @@
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>68132601762e3100137b966e</t>
+          <t>67e62ed2f90398001392f46a</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>pihumam</t>
+          <t>dailylivetrade</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>suryanshnothing@gmail.com</t>
+          <t>smdv.digital@gmail.com</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>6393374083</t>
+          <t>8290268460</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
@@ -12899,34 +12899,34 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I168" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J168" s="14" t="n">
-        <v>6127</v>
+        <v>2534</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>53385</v>
+        <v>54190</v>
       </c>
       <c r="L168" s="15" t="n">
-        <v>18466</v>
+        <v>30200</v>
       </c>
       <c r="M168" s="12" t="inlineStr">
         <is>
-          <t>69d377a9036ec1001305c793</t>
+          <t>69043d63a68ca50013eaf6ea</t>
         </is>
       </c>
       <c r="N168" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d377a9036ec1001305c793</t>
+          <t>https://superprofile.bio/vig/69043d63a68ca50013eaf6ea</t>
         </is>
       </c>
       <c r="O168" s="17" t="inlineStr">
@@ -12946,22 +12946,22 @@
       </c>
       <c r="B169" s="20" t="inlineStr">
         <is>
-          <t>66a498181f30df00135dcc9c</t>
+          <t>647afc6cbc5c8a0020c85fa7</t>
         </is>
       </c>
       <c r="C169" s="20" t="inlineStr">
         <is>
-          <t>docnifty</t>
+          <t>Cbkhasiya</t>
         </is>
       </c>
       <c r="D169" s="19" t="inlineStr">
         <is>
-          <t>dramit1403@gmail.com</t>
+          <t>cbkhasiya@gmail.com</t>
         </is>
       </c>
       <c r="E169" s="19" t="inlineStr">
         <is>
-          <t>8780933053</t>
+          <t>9081188188</t>
         </is>
       </c>
       <c r="F169" s="19" t="inlineStr">
@@ -12976,29 +12976,29 @@
       </c>
       <c r="H169" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I169" s="20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J169" s="21" t="n">
-        <v>26611</v>
+        <v>3157</v>
       </c>
       <c r="K169" s="21" t="n">
-        <v>53222</v>
+        <v>54104</v>
       </c>
       <c r="L169" s="22" t="n">
-        <v>26611</v>
+        <v>9470</v>
       </c>
       <c r="M169" s="19" t="inlineStr">
         <is>
-          <t>68c56332f0b046001379deb9</t>
+          <t>647df876e96cba002128da30</t>
         </is>
       </c>
       <c r="N169" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c56332f0b046001379deb9</t>
+          <t>https://superprofile.bio/vig/647df876e96cba002128da30</t>
         </is>
       </c>
       <c r="O169" s="24" t="inlineStr">
@@ -13018,22 +13018,22 @@
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>68384fb7f6fecd0013930afc</t>
+          <t>68132601762e3100137b966e</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>pihu00</t>
+          <t>pihumam</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>suryanshsakshi26@gmail.com</t>
+          <t>suryanshnothing@gmail.com</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>8439752930</t>
+          <t>6393374083</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -13043,34 +13043,34 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I170" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J170" s="14" t="n">
-        <v>10240</v>
+        <v>6127</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>51329</v>
+        <v>53385</v>
       </c>
       <c r="L170" s="15" t="n">
-        <v>12340</v>
+        <v>18466</v>
       </c>
       <c r="M170" s="12" t="inlineStr">
         <is>
-          <t>69bb9a626bc32b00132d43af</t>
+          <t>69d377a9036ec1001305c793</t>
         </is>
       </c>
       <c r="N170" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bb9a626bc32b00132d43af</t>
+          <t>https://superprofile.bio/vig/69d377a9036ec1001305c793</t>
         </is>
       </c>
       <c r="O170" s="17" t="inlineStr">
@@ -13090,22 +13090,22 @@
       </c>
       <c r="B171" s="20" t="inlineStr">
         <is>
-          <t>65427462316da7001e52ce0e</t>
+          <t>66a498181f30df00135dcc9c</t>
         </is>
       </c>
       <c r="C171" s="20" t="inlineStr">
         <is>
-          <t>panchalhitesh</t>
+          <t>docnifty</t>
         </is>
       </c>
       <c r="D171" s="19" t="inlineStr">
         <is>
-          <t>Panchalripal800@gmail.com</t>
+          <t>dramit1403@gmail.com</t>
         </is>
       </c>
       <c r="E171" s="19" t="inlineStr">
         <is>
-          <t>6353018497</t>
+          <t>8780933053</t>
         </is>
       </c>
       <c r="F171" s="19" t="inlineStr">
@@ -13115,34 +13115,34 @@
       </c>
       <c r="G171" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H171" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I171" s="20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J171" s="21" t="n">
-        <v>4822</v>
+        <v>26611</v>
       </c>
       <c r="K171" s="21" t="n">
-        <v>49838</v>
+        <v>53222</v>
       </c>
       <c r="L171" s="22" t="n">
-        <v>15275</v>
+        <v>26611</v>
       </c>
       <c r="M171" s="19" t="inlineStr">
         <is>
-          <t>65d87f56b799230013f6bcf7</t>
+          <t>68c56332f0b046001379deb9</t>
         </is>
       </c>
       <c r="N171" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65d87f56b799230013f6bcf7</t>
+          <t>https://superprofile.bio/vig/68c56332f0b046001379deb9</t>
         </is>
       </c>
       <c r="O171" s="24" t="inlineStr">
@@ -13162,22 +13162,22 @@
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>6474cf7ef2fde40020e45748</t>
+          <t>65427462316da7001e52ce0e</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>bestoption3001</t>
+          <t>panchalhitesh</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>mohitwadhwa321@gmail.com</t>
+          <t>Panchalripal800@gmail.com</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>9895468931</t>
+          <t>6353018497</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
@@ -13187,34 +13187,34 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I172" s="13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J172" s="14" t="n">
-        <v>1953</v>
+        <v>4822</v>
       </c>
       <c r="K172" s="14" t="n">
-        <v>49762</v>
+        <v>49838</v>
       </c>
       <c r="L172" s="15" t="n">
-        <v>14646</v>
+        <v>15275</v>
       </c>
       <c r="M172" s="12" t="inlineStr">
         <is>
-          <t>6576f37de497b978f8596a2b</t>
+          <t>65d87f56b799230013f6bcf7</t>
         </is>
       </c>
       <c r="N172" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6576f37de497b978f8596a2b</t>
+          <t>https://superprofile.bio/vig/65d87f56b799230013f6bcf7</t>
         </is>
       </c>
       <c r="O172" s="17" t="inlineStr">
@@ -13234,22 +13234,22 @@
       </c>
       <c r="B173" s="20" t="inlineStr">
         <is>
-          <t>659d2da99c7837001e53f781</t>
+          <t>6474cf7ef2fde40020e45748</t>
         </is>
       </c>
       <c r="C173" s="20" t="inlineStr">
         <is>
-          <t>cliffcapital</t>
+          <t>bestoption3001</t>
         </is>
       </c>
       <c r="D173" s="19" t="inlineStr">
         <is>
-          <t>courseswithmani@gmail.com</t>
+          <t>mohitwadhwa321@gmail.com</t>
         </is>
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>9289334952</t>
+          <t>9895468931</t>
         </is>
       </c>
       <c r="F173" s="19" t="inlineStr">
@@ -13259,34 +13259,34 @@
       </c>
       <c r="G173" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H173" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I173" s="20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J173" s="21" t="n">
-        <v>5216</v>
+        <v>1953</v>
       </c>
       <c r="K173" s="21" t="n">
-        <v>49625</v>
+        <v>49762</v>
       </c>
       <c r="L173" s="22" t="n">
-        <v>23733</v>
+        <v>14646</v>
       </c>
       <c r="M173" s="19" t="inlineStr">
         <is>
-          <t>659d30c79c7837001e544bb8</t>
+          <t>6576f37de497b978f8596a2b</t>
         </is>
       </c>
       <c r="N173" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/659d30c79c7837001e544bb8</t>
+          <t>https://superprofile.bio/vig/6576f37de497b978f8596a2b</t>
         </is>
       </c>
       <c r="O173" s="24" t="inlineStr">
@@ -13306,22 +13306,22 @@
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>662f4af96d60c800135f73d3</t>
+          <t>659d2da99c7837001e53f781</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>8875192746</t>
+          <t>cliffcapital</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>Princemeena887519@gmail.com</t>
+          <t>courseswithmani@gmail.com</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>8875192746</t>
+          <t>9289334952</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
@@ -13331,34 +13331,34 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I174" s="13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J174" s="14" t="n">
-        <v>2069</v>
+        <v>5216</v>
       </c>
       <c r="K174" s="14" t="n">
-        <v>48849</v>
+        <v>49625</v>
       </c>
       <c r="L174" s="15" t="n">
-        <v>8847</v>
+        <v>23733</v>
       </c>
       <c r="M174" s="12" t="inlineStr">
         <is>
-          <t>6933a91311b9460013934702</t>
+          <t>659d30c79c7837001e544bb8</t>
         </is>
       </c>
       <c r="N174" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6933a91311b9460013934702</t>
+          <t>https://superprofile.bio/vig/659d30c79c7837001e544bb8</t>
         </is>
       </c>
       <c r="O174" s="17" t="inlineStr">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="B175" s="20" t="inlineStr">
         <is>
-          <t>6a6843cc298f960014a01d85</t>
+          <t>662f4af96d60c800135f73d3</t>
         </is>
       </c>
       <c r="C175" s="20" t="inlineStr">
         <is>
-          <t>thetradeverse</t>
+          <t>8875192746</t>
         </is>
       </c>
       <c r="D175" s="19" t="inlineStr">
         <is>
-          <t>vramrakhiyani0@gmail.com</t>
+          <t>Princemeena887519@gmail.com</t>
         </is>
       </c>
       <c r="E175" s="19" t="inlineStr">
         <is>
-          <t>9574183683</t>
+          <t>8875192746</t>
         </is>
       </c>
       <c r="F175" s="19" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G175" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H175" s="19" t="inlineStr">
@@ -13412,25 +13412,25 @@
         </is>
       </c>
       <c r="I175" s="20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J175" s="21" t="n">
-        <v>12552</v>
+        <v>2069</v>
       </c>
       <c r="K175" s="21" t="n">
-        <v>48804</v>
+        <v>48849</v>
       </c>
       <c r="L175" s="22" t="n">
-        <v>17393</v>
+        <v>8847</v>
       </c>
       <c r="M175" s="19" t="inlineStr">
         <is>
-          <t>6a7d4c4b7a273200136aa8e5</t>
+          <t>6933a91311b9460013934702</t>
         </is>
       </c>
       <c r="N175" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7d4c4b7a273200136aa8e5</t>
+          <t>https://superprofile.bio/vig/6933a91311b9460013934702</t>
         </is>
       </c>
       <c r="O175" s="24" t="inlineStr">
@@ -13450,22 +13450,22 @@
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>624f0396ccc9ef0fa78281b0</t>
+          <t>6a6843cc298f960014a01d85</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>Darshuj10</t>
+          <t>thetradeverse</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>Dinuj10@gmail.com</t>
+          <t>vramrakhiyani0@gmail.com</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>9892492682</t>
+          <t>9574183683</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I176" s="13" t="n">
         <v>5</v>
       </c>
       <c r="J176" s="14" t="n">
-        <v>21969</v>
+        <v>12552</v>
       </c>
       <c r="K176" s="14" t="n">
-        <v>48725</v>
+        <v>48804</v>
       </c>
       <c r="L176" s="15" t="n">
-        <v>21969</v>
+        <v>17393</v>
       </c>
       <c r="M176" s="12" t="inlineStr">
         <is>
-          <t>6a66cd860a242e00131b0ba2</t>
+          <t>6a7d4c4b7a273200136aa8e5</t>
         </is>
       </c>
       <c r="N176" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a66cd860a242e00131b0ba2</t>
+          <t>https://superprofile.bio/vig/6a7d4c4b7a273200136aa8e5</t>
         </is>
       </c>
       <c r="O176" s="17" t="inlineStr">
@@ -13522,22 +13522,22 @@
       </c>
       <c r="B177" s="20" t="inlineStr">
         <is>
-          <t>6545f8d94b4aeb001f659e30</t>
+          <t>624f0396ccc9ef0fa78281b0</t>
         </is>
       </c>
       <c r="C177" s="20" t="inlineStr">
         <is>
-          <t>Awdhesh</t>
+          <t>Darshuj10</t>
         </is>
       </c>
       <c r="D177" s="19" t="inlineStr">
         <is>
-          <t>awdheshkumar022@gmail.com</t>
+          <t>Dinuj10@gmail.com</t>
         </is>
       </c>
       <c r="E177" s="19" t="inlineStr">
         <is>
-          <t>7870153559</t>
+          <t>9892492682</t>
         </is>
       </c>
       <c r="F177" s="19" t="inlineStr">
@@ -13547,34 +13547,34 @@
       </c>
       <c r="G177" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H177" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I177" s="20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J177" s="21" t="n">
-        <v>8152</v>
+        <v>21969</v>
       </c>
       <c r="K177" s="21" t="n">
-        <v>48436</v>
+        <v>48725</v>
       </c>
       <c r="L177" s="22" t="n">
-        <v>19981</v>
+        <v>21969</v>
       </c>
       <c r="M177" s="19" t="inlineStr">
         <is>
-          <t>66d6f2a06e56ec001373f81c</t>
+          <t>6a66cd860a242e00131b0ba2</t>
         </is>
       </c>
       <c r="N177" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66d6f2a06e56ec001373f81c</t>
+          <t>https://superprofile.bio/vig/6a66cd860a242e00131b0ba2</t>
         </is>
       </c>
       <c r="O177" s="24" t="inlineStr">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>675ab45e058432001308f3bd</t>
+          <t>6545f8d94b4aeb001f659e30</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>tradingsky</t>
+          <t>Awdhesh</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>support@tradingsky.in</t>
+          <t>awdheshkumar022@gmail.com</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
         <is>
-          <t>8287436828</t>
+          <t>7870153559</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
@@ -13619,34 +13619,34 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I178" s="13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J178" s="14" t="n">
-        <v>48318</v>
+        <v>8152</v>
       </c>
       <c r="K178" s="14" t="n">
-        <v>48318</v>
+        <v>48436</v>
       </c>
       <c r="L178" s="15" t="n">
-        <v>48318</v>
+        <v>19981</v>
       </c>
       <c r="M178" s="12" t="inlineStr">
         <is>
-          <t>69fc37eb1b03b900133f0a74</t>
+          <t>66d6f2a06e56ec001373f81c</t>
         </is>
       </c>
       <c r="N178" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69fc37eb1b03b900133f0a74</t>
+          <t>https://superprofile.bio/vig/66d6f2a06e56ec001373f81c</t>
         </is>
       </c>
       <c r="O178" s="17" t="inlineStr">
@@ -13666,22 +13666,22 @@
       </c>
       <c r="B179" s="20" t="inlineStr">
         <is>
-          <t>68f097f508edc40013780862</t>
+          <t>675ab45e058432001308f3bd</t>
         </is>
       </c>
       <c r="C179" s="20" t="inlineStr">
         <is>
-          <t>officialstockbeast</t>
+          <t>tradingsky</t>
         </is>
       </c>
       <c r="D179" s="19" t="inlineStr">
         <is>
-          <t>officialstockbeast@gmail.com</t>
+          <t>support@tradingsky.in</t>
         </is>
       </c>
       <c r="E179" s="19" t="inlineStr">
         <is>
-          <t>9930080512</t>
+          <t>8287436828</t>
         </is>
       </c>
       <c r="F179" s="19" t="inlineStr">
@@ -13691,34 +13691,34 @@
       </c>
       <c r="G179" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H179" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I179" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J179" s="21" t="n">
-        <v>5927</v>
+        <v>48318</v>
       </c>
       <c r="K179" s="21" t="n">
-        <v>48305</v>
+        <v>48318</v>
       </c>
       <c r="L179" s="22" t="n">
-        <v>17677</v>
+        <v>48318</v>
       </c>
       <c r="M179" s="19" t="inlineStr">
         <is>
-          <t>6a889a264d598800131abbcf</t>
+          <t>69fc37eb1b03b900133f0a74</t>
         </is>
       </c>
       <c r="N179" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a889a264d598800131abbcf</t>
+          <t>https://superprofile.bio/vig/69fc37eb1b03b900133f0a74</t>
         </is>
       </c>
       <c r="O179" s="24" t="inlineStr">
@@ -13738,22 +13738,22 @@
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>63ad25d5e0023900370deae4</t>
+          <t>68f097f508edc40013780862</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>shortermswing</t>
+          <t>officialstockbeast</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>justfornirmal@gmail.com</t>
+          <t>officialstockbeast@gmail.com</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>6379601124</t>
+          <t>9930080512</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
@@ -13768,29 +13768,29 @@
       </c>
       <c r="H180" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I180" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J180" s="14" t="n">
-        <v>6418</v>
+        <v>5927</v>
       </c>
       <c r="K180" s="14" t="n">
-        <v>48240</v>
+        <v>48305</v>
       </c>
       <c r="L180" s="15" t="n">
-        <v>11619</v>
+        <v>17677</v>
       </c>
       <c r="M180" s="12" t="inlineStr">
         <is>
-          <t>63c90951b6cd3f003d489395</t>
+          <t>6a889a264d598800131abbcf</t>
         </is>
       </c>
       <c r="N180" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63c90951b6cd3f003d489395</t>
+          <t>https://superprofile.bio/vig/6a889a264d598800131abbcf</t>
         </is>
       </c>
       <c r="O180" s="17" t="inlineStr">
@@ -13810,22 +13810,22 @@
       </c>
       <c r="B181" s="20" t="inlineStr">
         <is>
-          <t>693d2567c5d4f600137fdbb6</t>
+          <t>63ad25d5e0023900370deae4</t>
         </is>
       </c>
       <c r="C181" s="20" t="inlineStr">
         <is>
-          <t>stockwaves01</t>
+          <t>shortermswing</t>
         </is>
       </c>
       <c r="D181" s="19" t="inlineStr">
         <is>
-          <t>stockwaves555@gmail.com</t>
+          <t>justfornirmal@gmail.com</t>
         </is>
       </c>
       <c r="E181" s="19" t="inlineStr">
         <is>
-          <t>8920556522</t>
+          <t>6379601124</t>
         </is>
       </c>
       <c r="F181" s="19" t="inlineStr">
@@ -13844,25 +13844,25 @@
         </is>
       </c>
       <c r="I181" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J181" s="21" t="n">
-        <v>12926</v>
+        <v>6418</v>
       </c>
       <c r="K181" s="21" t="n">
-        <v>47072</v>
+        <v>48240</v>
       </c>
       <c r="L181" s="22" t="n">
-        <v>13890</v>
+        <v>11619</v>
       </c>
       <c r="M181" s="19" t="inlineStr">
         <is>
-          <t>67fcf46d31bbb20013338235</t>
+          <t>63c90951b6cd3f003d489395</t>
         </is>
       </c>
       <c r="N181" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67fcf46d31bbb20013338235</t>
+          <t>https://superprofile.bio/vig/63c90951b6cd3f003d489395</t>
         </is>
       </c>
       <c r="O181" s="24" t="inlineStr">
@@ -13882,22 +13882,22 @@
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>6a1d7ae12f3971001304d6f9</t>
+          <t>693d2567c5d4f600137fdbb6</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>dhs</t>
+          <t>stockwaves01</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>yixogiy851@fixscal.com</t>
+          <t>stockwaves555@gmail.com</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
         <is>
-          <t>9691393926</t>
+          <t>8920556522</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
@@ -13912,29 +13912,29 @@
       </c>
       <c r="H182" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I182" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J182" s="14" t="n">
-        <v>36823</v>
+        <v>12926</v>
       </c>
       <c r="K182" s="14" t="n">
-        <v>47068</v>
+        <v>47072</v>
       </c>
       <c r="L182" s="15" t="n">
-        <v>36823</v>
+        <v>13890</v>
       </c>
       <c r="M182" s="12" t="inlineStr">
         <is>
-          <t>697aeb756fa9030013e878ea</t>
+          <t>67fcf46d31bbb20013338235</t>
         </is>
       </c>
       <c r="N182" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697aeb756fa9030013e878ea</t>
+          <t>https://superprofile.bio/vig/67fcf46d31bbb20013338235</t>
         </is>
       </c>
       <c r="O182" s="17" t="inlineStr">
@@ -13954,22 +13954,22 @@
       </c>
       <c r="B183" s="20" t="inlineStr">
         <is>
-          <t>6708183b3a97c6001355987d</t>
+          <t>6a1d7ae12f3971001304d6f9</t>
         </is>
       </c>
       <c r="C183" s="20" t="inlineStr">
         <is>
-          <t>stockvsipoin</t>
+          <t>dhs</t>
         </is>
       </c>
       <c r="D183" s="19" t="inlineStr">
         <is>
-          <t>D33pak29@gmail.com</t>
+          <t>yixogiy851@fixscal.com</t>
         </is>
       </c>
       <c r="E183" s="19" t="inlineStr">
         <is>
-          <t>9589660300</t>
+          <t>9691393926</t>
         </is>
       </c>
       <c r="F183" s="19" t="inlineStr">
@@ -13984,29 +13984,29 @@
       </c>
       <c r="H183" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I183" s="20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J183" s="21" t="n">
-        <v>8341</v>
+        <v>36823</v>
       </c>
       <c r="K183" s="21" t="n">
-        <v>46639</v>
+        <v>47068</v>
       </c>
       <c r="L183" s="22" t="n">
-        <v>19107</v>
+        <v>36823</v>
       </c>
       <c r="M183" s="19" t="inlineStr">
         <is>
-          <t>67738686f9e9a000134df3d2</t>
+          <t>697aeb756fa9030013e878ea</t>
         </is>
       </c>
       <c r="N183" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67738686f9e9a000134df3d2</t>
+          <t>https://superprofile.bio/vig/697aeb756fa9030013e878ea</t>
         </is>
       </c>
       <c r="O183" s="24" t="inlineStr">
@@ -14026,22 +14026,22 @@
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>67332673160fd900139f7de9</t>
+          <t>6708183b3a97c6001355987d</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>drguptamd</t>
+          <t>stockvsipoin</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>dr.rajat95gupta@gmail.com</t>
+          <t>D33pak29@gmail.com</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>8894577818</t>
+          <t>9589660300</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -14063,22 +14063,22 @@
         <v>8</v>
       </c>
       <c r="J184" s="14" t="n">
-        <v>13271</v>
+        <v>8341</v>
       </c>
       <c r="K184" s="14" t="n">
-        <v>46555</v>
+        <v>46639</v>
       </c>
       <c r="L184" s="15" t="n">
-        <v>13271</v>
+        <v>19107</v>
       </c>
       <c r="M184" s="12" t="inlineStr">
         <is>
-          <t>67f8cb86a5f4410013979220</t>
+          <t>67738686f9e9a000134df3d2</t>
         </is>
       </c>
       <c r="N184" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67f8cb86a5f4410013979220</t>
+          <t>https://superprofile.bio/vig/67738686f9e9a000134df3d2</t>
         </is>
       </c>
       <c r="O184" s="17" t="inlineStr">
@@ -14098,22 +14098,22 @@
       </c>
       <c r="B185" s="20" t="inlineStr">
         <is>
-          <t>65c07da823d6a606da382bcd</t>
+          <t>67332673160fd900139f7de9</t>
         </is>
       </c>
       <c r="C185" s="20" t="inlineStr">
         <is>
-          <t>zerotohero001</t>
+          <t>drguptamd</t>
         </is>
       </c>
       <c r="D185" s="19" t="inlineStr">
         <is>
-          <t>zerotoherotrading562@gmail.com</t>
+          <t>dr.rajat95gupta@gmail.com</t>
         </is>
       </c>
       <c r="E185" s="19" t="inlineStr">
         <is>
-          <t>8696606766</t>
+          <t>8894577818</t>
         </is>
       </c>
       <c r="F185" s="19" t="inlineStr">
@@ -14123,34 +14123,34 @@
       </c>
       <c r="G185" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H185" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I185" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J185" s="21" t="n">
-        <v>5786</v>
+        <v>8124</v>
       </c>
       <c r="K185" s="21" t="n">
-        <v>46268</v>
+        <v>46555</v>
       </c>
       <c r="L185" s="22" t="n">
-        <v>19271</v>
+        <v>13271</v>
       </c>
       <c r="M185" s="19" t="inlineStr">
         <is>
-          <t>6798ae8a9c89a4001358d7a1</t>
+          <t>67f8cb86a5f4410013979220</t>
         </is>
       </c>
       <c r="N185" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6798ae8a9c89a4001358d7a1</t>
+          <t>https://superprofile.bio/vig/67f8cb86a5f4410013979220</t>
         </is>
       </c>
       <c r="O185" s="24" t="inlineStr">
@@ -14170,22 +14170,22 @@
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>62e2324735c9e35b636f78f4</t>
+          <t>65c07da823d6a606da382bcd</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>tradeindiaofficial</t>
+          <t>zerotohero001</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>ziactcom@gmail.com</t>
+          <t>zerotoherotrading562@gmail.com</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>8760001106</t>
+          <t>8696606766</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
@@ -14200,29 +14200,29 @@
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I186" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J186" s="14" t="n">
-        <v>8822</v>
+        <v>5786</v>
       </c>
       <c r="K186" s="14" t="n">
-        <v>46257</v>
+        <v>46268</v>
       </c>
       <c r="L186" s="15" t="n">
-        <v>13233</v>
+        <v>19271</v>
       </c>
       <c r="M186" s="12" t="inlineStr">
         <is>
-          <t>660d1a78b66cbb0012f68180</t>
+          <t>6798ae8a9c89a4001358d7a1</t>
         </is>
       </c>
       <c r="N186" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/660d1a78b66cbb0012f68180</t>
+          <t>https://superprofile.bio/vig/6798ae8a9c89a4001358d7a1</t>
         </is>
       </c>
       <c r="O186" s="17" t="inlineStr">
@@ -14242,22 +14242,22 @@
       </c>
       <c r="B187" s="20" t="inlineStr">
         <is>
-          <t>6a884edc0011bc001397087d</t>
+          <t>62e2324735c9e35b636f78f4</t>
         </is>
       </c>
       <c r="C187" s="20" t="inlineStr">
         <is>
-          <t>bullixtrader</t>
+          <t>tradeindiaofficial</t>
         </is>
       </c>
       <c r="D187" s="19" t="inlineStr">
         <is>
-          <t>manwanichirag9@gmail.com</t>
+          <t>ziactcom@gmail.com</t>
         </is>
       </c>
       <c r="E187" s="19" t="inlineStr">
         <is>
-          <t>9638960188</t>
+          <t>8760001106</t>
         </is>
       </c>
       <c r="F187" s="19" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="G187" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H187" s="19" t="inlineStr">
@@ -14276,25 +14276,25 @@
         </is>
       </c>
       <c r="I187" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J187" s="21" t="n">
-        <v>4822</v>
+        <v>8822</v>
       </c>
       <c r="K187" s="21" t="n">
-        <v>46077</v>
+        <v>46257</v>
       </c>
       <c r="L187" s="22" t="n">
-        <v>8982</v>
+        <v>13233</v>
       </c>
       <c r="M187" s="19" t="inlineStr">
         <is>
-          <t>6a93e1f2f65d170012d3ac78</t>
+          <t>660d1a78b66cbb0012f68180</t>
         </is>
       </c>
       <c r="N187" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a93e1f2f65d170012d3ac78</t>
+          <t>https://superprofile.bio/vig/660d1a78b66cbb0012f68180</t>
         </is>
       </c>
       <c r="O187" s="24" t="inlineStr">
@@ -14314,22 +14314,22 @@
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>64759be6ab41f2001fa930a9</t>
+          <t>6a884edc0011bc001397087d</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>msingh17</t>
+          <t>bullixtrader</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>nishu_kool17@yahoo.com</t>
+          <t>manwanichirag9@gmail.com</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>7493064834</t>
+          <t>9638960188</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -14348,25 +14348,25 @@
         </is>
       </c>
       <c r="I188" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J188" s="14" t="n">
-        <v>2946</v>
+        <v>4822</v>
       </c>
       <c r="K188" s="14" t="n">
-        <v>45948</v>
+        <v>46077</v>
       </c>
       <c r="L188" s="15" t="n">
-        <v>14042</v>
+        <v>8982</v>
       </c>
       <c r="M188" s="12" t="inlineStr">
         <is>
-          <t>64759f2e526648002079e864</t>
+          <t>6a93e1f2f65d170012d3ac78</t>
         </is>
       </c>
       <c r="N188" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64759f2e526648002079e864</t>
+          <t>https://superprofile.bio/vig/6a93e1f2f65d170012d3ac78</t>
         </is>
       </c>
       <c r="O188" s="17" t="inlineStr">
@@ -14386,22 +14386,22 @@
       </c>
       <c r="B189" s="20" t="inlineStr">
         <is>
-          <t>640d10371bcf9e0020296ad8</t>
+          <t>64759be6ab41f2001fa930a9</t>
         </is>
       </c>
       <c r="C189" s="20" t="inlineStr">
         <is>
-          <t>stockscannerin</t>
+          <t>msingh17</t>
         </is>
       </c>
       <c r="D189" s="19" t="inlineStr">
         <is>
-          <t>iamrajesh2du@gmail.com</t>
+          <t>nishu_kool17@yahoo.com</t>
         </is>
       </c>
       <c r="E189" s="19" t="inlineStr">
         <is>
-          <t>7717760693</t>
+          <t>7493064834</t>
         </is>
       </c>
       <c r="F189" s="19" t="inlineStr">
@@ -14416,29 +14416,29 @@
       </c>
       <c r="H189" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I189" s="20" t="n">
         <v>7</v>
       </c>
       <c r="J189" s="21" t="n">
-        <v>4679</v>
+        <v>2946</v>
       </c>
       <c r="K189" s="21" t="n">
-        <v>45765</v>
+        <v>45948</v>
       </c>
       <c r="L189" s="22" t="n">
-        <v>13768</v>
+        <v>14042</v>
       </c>
       <c r="M189" s="19" t="inlineStr">
         <is>
-          <t>66544e6da5123900130b90ad</t>
+          <t>64759f2e526648002079e864</t>
         </is>
       </c>
       <c r="N189" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66544e6da5123900130b90ad</t>
+          <t>https://superprofile.bio/vig/64759f2e526648002079e864</t>
         </is>
       </c>
       <c r="O189" s="24" t="inlineStr">
@@ -14458,22 +14458,22 @@
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>698960d575efa100133dc34a</t>
+          <t>640d10371bcf9e0020296ad8</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>mbtrading</t>
+          <t>stockscannerin</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>brijeshshah898@gmail.com</t>
+          <t>iamrajesh2du@gmail.com</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>7388327183</t>
+          <t>7717760693</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
@@ -14483,34 +14483,34 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I190" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J190" s="14" t="n">
-        <v>13415</v>
+        <v>4679</v>
       </c>
       <c r="K190" s="14" t="n">
-        <v>45542</v>
+        <v>45765</v>
       </c>
       <c r="L190" s="15" t="n">
-        <v>13415</v>
+        <v>13768</v>
       </c>
       <c r="M190" s="12" t="inlineStr">
         <is>
-          <t>69a63a3b0035f00013abc48a</t>
+          <t>66544e6da5123900130b90ad</t>
         </is>
       </c>
       <c r="N190" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a63a3b0035f00013abc48a</t>
+          <t>https://superprofile.bio/vig/66544e6da5123900130b90ad</t>
         </is>
       </c>
       <c r="O190" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 06:35:21 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 07:04:05 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 07:04:05 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 08:50:49 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2737539</v>
+        <v>2739420</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 08:50:49 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 11:40:04 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 11:40:04 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 13:59:58 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 13:59:58 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 15:37:04 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 15:37:04 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 17:11:01 | Daily Audits Logged: 9</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 17:11:01 | Daily Audits Logged: 9</t>
+          <t>Generated On: 2026-09-07 18:40:16 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹34,167,992.00</t>
+          <t>₹34,170,347.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -794,6 +794,24 @@
         <v>2739420</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Logged &amp; Deduplicated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Logged &amp; Deduplicated</t>
         </is>
@@ -29650,22 +29668,22 @@
       </c>
       <c r="B401" s="20" t="inlineStr">
         <is>
-          <t>64b0ea441e6e1b002a2b2802</t>
+          <t>62115e4a6bd738258707c0e9</t>
         </is>
       </c>
       <c r="C401" s="20" t="inlineStr">
         <is>
-          <t>alfaearning</t>
+          <t>aditya</t>
         </is>
       </c>
       <c r="D401" s="19" t="inlineStr">
         <is>
-          <t>tcmall9987@gmail.com</t>
+          <t>imavschoudhary@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="19" t="inlineStr">
         <is>
-          <t>7668471271</t>
+          <t>9717115749</t>
         </is>
       </c>
       <c r="F401" s="19" t="inlineStr">
@@ -29675,34 +29693,34 @@
       </c>
       <c r="G401" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H401" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I401" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J401" s="21" t="n">
-        <v>14646</v>
+        <v>2355</v>
       </c>
       <c r="K401" s="21" t="n">
-        <v>14646</v>
+        <v>14655</v>
       </c>
       <c r="L401" s="22" t="n">
-        <v>14646</v>
+        <v>3795</v>
       </c>
       <c r="M401" s="19" t="inlineStr">
         <is>
-          <t>66596deaeec07b001310d2df</t>
+          <t>6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="N401" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66596deaeec07b001310d2df</t>
+          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="O401" s="24" t="inlineStr">
@@ -29722,22 +29740,22 @@
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>67222b9c5ea5240013ca5e36</t>
+          <t>64b0ea441e6e1b002a2b2802</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
         <is>
-          <t>nidhishah9366</t>
+          <t>alfaearning</t>
         </is>
       </c>
       <c r="D402" s="12" t="inlineStr">
         <is>
-          <t>nidhishah9366@gmail.com</t>
+          <t>tcmall9987@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr">
         <is>
-          <t>9427741411</t>
+          <t>7668471271</t>
         </is>
       </c>
       <c r="F402" s="12" t="inlineStr">
@@ -29747,34 +29765,34 @@
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I402" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J402" s="14" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="K402" s="14" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="L402" s="15" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="M402" s="12" t="inlineStr">
         <is>
-          <t>674947b2098ae70013379485</t>
+          <t>66596deaeec07b001310d2df</t>
         </is>
       </c>
       <c r="N402" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/674947b2098ae70013379485</t>
+          <t>https://superprofile.bio/vig/66596deaeec07b001310d2df</t>
         </is>
       </c>
       <c r="O402" s="17" t="inlineStr">
@@ -29794,22 +29812,22 @@
       </c>
       <c r="B403" s="20" t="inlineStr">
         <is>
-          <t>62fd0aaed7f1067b018a5ebf</t>
+          <t>67222b9c5ea5240013ca5e36</t>
         </is>
       </c>
       <c r="C403" s="20" t="inlineStr">
         <is>
-          <t>hareem1</t>
+          <t>nidhishah9366</t>
         </is>
       </c>
       <c r="D403" s="19" t="inlineStr">
         <is>
-          <t>justowais8@gmail.com</t>
+          <t>nidhishah9366@gmail.com</t>
         </is>
       </c>
       <c r="E403" s="19" t="inlineStr">
         <is>
-          <t>9797189866</t>
+          <t>9427741411</t>
         </is>
       </c>
       <c r="F403" s="19" t="inlineStr">
@@ -29819,34 +29837,34 @@
       </c>
       <c r="G403" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H403" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I403" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J403" s="21" t="n">
-        <v>1509</v>
+        <v>14628</v>
       </c>
       <c r="K403" s="21" t="n">
-        <v>14564</v>
+        <v>14628</v>
       </c>
       <c r="L403" s="22" t="n">
-        <v>5839</v>
+        <v>14628</v>
       </c>
       <c r="M403" s="19" t="inlineStr">
         <is>
-          <t>62fd101cda86187f12419fa8</t>
+          <t>674947b2098ae70013379485</t>
         </is>
       </c>
       <c r="N403" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62fd101cda86187f12419fa8</t>
+          <t>https://superprofile.bio/vig/674947b2098ae70013379485</t>
         </is>
       </c>
       <c r="O403" s="24" t="inlineStr">
@@ -29866,22 +29884,22 @@
       </c>
       <c r="B404" s="13" t="inlineStr">
         <is>
-          <t>61b633d2efcfd46e56495985</t>
+          <t>62fd0aaed7f1067b018a5ebf</t>
         </is>
       </c>
       <c r="C404" s="13" t="inlineStr">
         <is>
-          <t>thetradingclub</t>
+          <t>hareem1</t>
         </is>
       </c>
       <c r="D404" s="12" t="inlineStr">
         <is>
-          <t>sumitjain61830@gmail.com</t>
+          <t>justowais8@gmail.com</t>
         </is>
       </c>
       <c r="E404" s="12" t="inlineStr">
         <is>
-          <t>8975698992</t>
+          <t>9797189866</t>
         </is>
       </c>
       <c r="F404" s="12" t="inlineStr">
@@ -29891,34 +29909,34 @@
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H404" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I404" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>1239</v>
+        <v>1509</v>
       </c>
       <c r="K404" s="14" t="n">
-        <v>14540</v>
+        <v>14564</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>10410</v>
+        <v>5839</v>
       </c>
       <c r="M404" s="12" t="inlineStr">
         <is>
-          <t>6a4bf40725aaf10013aee750</t>
+          <t>62fd101cda86187f12419fa8</t>
         </is>
       </c>
       <c r="N404" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4bf40725aaf10013aee750</t>
+          <t>https://superprofile.bio/vig/62fd101cda86187f12419fa8</t>
         </is>
       </c>
       <c r="O404" s="17" t="inlineStr">
@@ -29938,22 +29956,22 @@
       </c>
       <c r="B405" s="20" t="inlineStr">
         <is>
-          <t>63cf83e4603a1c00332a3516</t>
+          <t>61b633d2efcfd46e56495985</t>
         </is>
       </c>
       <c r="C405" s="20" t="inlineStr">
         <is>
-          <t>repleteequities</t>
+          <t>thetradingclub</t>
         </is>
       </c>
       <c r="D405" s="19" t="inlineStr">
         <is>
-          <t>sachin@repleteequities.com</t>
+          <t>sumitjain61830@gmail.com</t>
         </is>
       </c>
       <c r="E405" s="19" t="inlineStr">
         <is>
-          <t>7229945555</t>
+          <t>8975698992</t>
         </is>
       </c>
       <c r="F405" s="19" t="inlineStr">
@@ -29968,29 +29986,29 @@
       </c>
       <c r="H405" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I405" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J405" s="21" t="n">
-        <v>14468</v>
+        <v>1239</v>
       </c>
       <c r="K405" s="21" t="n">
-        <v>14468</v>
+        <v>14540</v>
       </c>
       <c r="L405" s="22" t="n">
-        <v>14468</v>
+        <v>10410</v>
       </c>
       <c r="M405" s="19" t="inlineStr">
         <is>
-          <t>695e07b1813efa0013b5b56c</t>
+          <t>6a4bf40725aaf10013aee750</t>
         </is>
       </c>
       <c r="N405" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/695e07b1813efa0013b5b56c</t>
+          <t>https://superprofile.bio/vig/6a4bf40725aaf10013aee750</t>
         </is>
       </c>
       <c r="O405" s="24" t="inlineStr">
@@ -30010,22 +30028,22 @@
       </c>
       <c r="B406" s="13" t="inlineStr">
         <is>
-          <t>654f049b0ce920001de81c27</t>
+          <t>63cf83e4603a1c00332a3516</t>
         </is>
       </c>
       <c r="C406" s="13" t="inlineStr">
         <is>
-          <t>Shiv09</t>
+          <t>repleteequities</t>
         </is>
       </c>
       <c r="D406" s="12" t="inlineStr">
         <is>
-          <t>shivrajdangi63@gmail.com</t>
+          <t>sachin@repleteequities.com</t>
         </is>
       </c>
       <c r="E406" s="12" t="inlineStr">
         <is>
-          <t>9301596441</t>
+          <t>7229945555</t>
         </is>
       </c>
       <c r="F406" s="12" t="inlineStr">
@@ -30035,7 +30053,7 @@
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H406" s="12" t="inlineStr">
@@ -30044,25 +30062,25 @@
         </is>
       </c>
       <c r="I406" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J406" s="14" t="n">
-        <v>4822</v>
+        <v>14468</v>
       </c>
       <c r="K406" s="14" t="n">
-        <v>14466</v>
+        <v>14468</v>
       </c>
       <c r="L406" s="15" t="n">
-        <v>4822</v>
+        <v>14468</v>
       </c>
       <c r="M406" s="12" t="inlineStr">
         <is>
-          <t>69ecbffeaa29900013b94540</t>
+          <t>695e07b1813efa0013b5b56c</t>
         </is>
       </c>
       <c r="N406" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ecbffeaa29900013b94540</t>
+          <t>https://superprofile.bio/vig/695e07b1813efa0013b5b56c</t>
         </is>
       </c>
       <c r="O406" s="17" t="inlineStr">
@@ -30082,22 +30100,22 @@
       </c>
       <c r="B407" s="20" t="inlineStr">
         <is>
-          <t>6513d6f6fa59f9001e0df913</t>
+          <t>654f049b0ce920001de81c27</t>
         </is>
       </c>
       <c r="C407" s="20" t="inlineStr">
         <is>
-          <t>stockvip</t>
+          <t>Shiv09</t>
         </is>
       </c>
       <c r="D407" s="19" t="inlineStr">
         <is>
-          <t>nky0998765@gmail.com</t>
+          <t>shivrajdangi63@gmail.com</t>
         </is>
       </c>
       <c r="E407" s="19" t="inlineStr">
         <is>
-          <t>9651479360</t>
+          <t>9301596441</t>
         </is>
       </c>
       <c r="F407" s="19" t="inlineStr">
@@ -30107,34 +30125,34 @@
       </c>
       <c r="G407" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H407" s="19" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="H407" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="I407" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J407" s="21" t="n">
-        <v>4002</v>
+        <v>4822</v>
       </c>
       <c r="K407" s="21" t="n">
-        <v>14427</v>
+        <v>14466</v>
       </c>
       <c r="L407" s="22" t="n">
-        <v>4002</v>
+        <v>4822</v>
       </c>
       <c r="M407" s="19" t="inlineStr">
         <is>
-          <t>69bbe0da3d80fd0013eac43d</t>
+          <t>69ecbffeaa29900013b94540</t>
         </is>
       </c>
       <c r="N407" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bbe0da3d80fd0013eac43d</t>
+          <t>https://superprofile.bio/vig/69ecbffeaa29900013b94540</t>
         </is>
       </c>
       <c r="O407" s="24" t="inlineStr">
@@ -30154,22 +30172,22 @@
       </c>
       <c r="B408" s="13" t="inlineStr">
         <is>
-          <t>6a07df7c7c5fcd00133a6e3b</t>
+          <t>6513d6f6fa59f9001e0df913</t>
         </is>
       </c>
       <c r="C408" s="13" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>stockvip</t>
         </is>
       </c>
       <c r="D408" s="12" t="inlineStr">
         <is>
-          <t>experttrading874@gmail.com</t>
+          <t>nky0998765@gmail.com</t>
         </is>
       </c>
       <c r="E408" s="12" t="inlineStr">
         <is>
-          <t>6377727003</t>
+          <t>9651479360</t>
         </is>
       </c>
       <c r="F408" s="12" t="inlineStr">
@@ -30179,34 +30197,34 @@
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H408" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I408" s="13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J408" s="14" t="n">
-        <v>1127</v>
+        <v>4002</v>
       </c>
       <c r="K408" s="14" t="n">
-        <v>14288</v>
+        <v>14427</v>
       </c>
       <c r="L408" s="15" t="n">
-        <v>3762</v>
+        <v>4002</v>
       </c>
       <c r="M408" s="12" t="inlineStr">
         <is>
-          <t>6a088c367c5fcd00135ca723</t>
+          <t>69bbe0da3d80fd0013eac43d</t>
         </is>
       </c>
       <c r="N408" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
+          <t>https://superprofile.bio/vig/69bbe0da3d80fd0013eac43d</t>
         </is>
       </c>
       <c r="O408" s="17" t="inlineStr">
@@ -30226,22 +30244,22 @@
       </c>
       <c r="B409" s="20" t="inlineStr">
         <is>
-          <t>6693e8299527ae0013ffcb9e</t>
+          <t>6a07df7c7c5fcd00133a6e3b</t>
         </is>
       </c>
       <c r="C409" s="20" t="inlineStr">
         <is>
-          <t>bigbull2025</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="D409" s="19" t="inlineStr">
         <is>
-          <t>bjisrk80@gmail.com</t>
+          <t>experttrading874@gmail.com</t>
         </is>
       </c>
       <c r="E409" s="19" t="inlineStr">
         <is>
-          <t>7568977191</t>
+          <t>6377727003</t>
         </is>
       </c>
       <c r="F409" s="19" t="inlineStr">
@@ -30256,29 +30274,29 @@
       </c>
       <c r="H409" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I409" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J409" s="21" t="n">
-        <v>3238</v>
+        <v>1127</v>
       </c>
       <c r="K409" s="21" t="n">
-        <v>14285</v>
+        <v>14288</v>
       </c>
       <c r="L409" s="22" t="n">
-        <v>6285</v>
+        <v>3762</v>
       </c>
       <c r="M409" s="19" t="inlineStr">
         <is>
-          <t>66ee6de8d79b930013987bd6</t>
+          <t>6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="N409" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
+          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="O409" s="24" t="inlineStr">
@@ -30298,22 +30316,22 @@
       </c>
       <c r="B410" s="13" t="inlineStr">
         <is>
-          <t>69c024131e4a31001362ea2c</t>
+          <t>6693e8299527ae0013ffcb9e</t>
         </is>
       </c>
       <c r="C410" s="13" t="inlineStr">
         <is>
-          <t>khokon2004</t>
+          <t>bigbull2025</t>
         </is>
       </c>
       <c r="D410" s="12" t="inlineStr">
         <is>
-          <t>mrtraderbusiness03@gmail.com</t>
+          <t>bjisrk80@gmail.com</t>
         </is>
       </c>
       <c r="E410" s="12" t="inlineStr">
         <is>
-          <t>9832288446</t>
+          <t>7568977191</t>
         </is>
       </c>
       <c r="F410" s="12" t="inlineStr">
@@ -30328,29 +30346,29 @@
       </c>
       <c r="H410" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I410" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J410" s="14" t="n">
-        <v>2353</v>
+        <v>3238</v>
       </c>
       <c r="K410" s="14" t="n">
-        <v>14116</v>
+        <v>14285</v>
       </c>
       <c r="L410" s="15" t="n">
-        <v>4705</v>
+        <v>6285</v>
       </c>
       <c r="M410" s="12" t="inlineStr">
         <is>
-          <t>6a53c2ea94c4f30013f521be</t>
+          <t>66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="N410" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a53c2ea94c4f30013f521be</t>
+          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="O410" s="17" t="inlineStr">
@@ -30370,22 +30388,22 @@
       </c>
       <c r="B411" s="20" t="inlineStr">
         <is>
-          <t>64d2675c94b053001d508b71</t>
+          <t>69c024131e4a31001362ea2c</t>
         </is>
       </c>
       <c r="C411" s="20" t="inlineStr">
         <is>
-          <t>stocktrade007</t>
+          <t>khokon2004</t>
         </is>
       </c>
       <c r="D411" s="19" t="inlineStr">
         <is>
-          <t>tradewithme4999@gmail.com</t>
+          <t>mrtraderbusiness03@gmail.com</t>
         </is>
       </c>
       <c r="E411" s="19" t="inlineStr">
         <is>
-          <t>8380029432</t>
+          <t>9832288446</t>
         </is>
       </c>
       <c r="F411" s="19" t="inlineStr">
@@ -30395,34 +30413,34 @@
       </c>
       <c r="G411" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H411" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I411" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J411" s="21" t="n">
-        <v>14114</v>
+        <v>2353</v>
       </c>
       <c r="K411" s="21" t="n">
-        <v>14114</v>
+        <v>14116</v>
       </c>
       <c r="L411" s="22" t="n">
-        <v>14114</v>
+        <v>4705</v>
       </c>
       <c r="M411" s="19" t="inlineStr">
         <is>
-          <t>6708475d1f46ee001371cb20</t>
+          <t>6a53c2ea94c4f30013f521be</t>
         </is>
       </c>
       <c r="N411" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6708475d1f46ee001371cb20</t>
+          <t>https://superprofile.bio/vig/6a53c2ea94c4f30013f521be</t>
         </is>
       </c>
       <c r="O411" s="24" t="inlineStr">
@@ -30442,22 +30460,22 @@
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>6961cac5209b3d00137110a2</t>
+          <t>64d2675c94b053001d508b71</t>
         </is>
       </c>
       <c r="C412" s="13" t="inlineStr">
         <is>
-          <t>tradingexpert02</t>
+          <t>stocktrade007</t>
         </is>
       </c>
       <c r="D412" s="12" t="inlineStr">
         <is>
-          <t>tradingexpert7180@gmail.com</t>
+          <t>tradewithme4999@gmail.com</t>
         </is>
       </c>
       <c r="E412" s="12" t="inlineStr">
         <is>
-          <t>9784944154</t>
+          <t>8380029432</t>
         </is>
       </c>
       <c r="F412" s="12" t="inlineStr">
@@ -30467,34 +30485,34 @@
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H412" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I412" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J412" s="14" t="n">
-        <v>5644</v>
+        <v>14114</v>
       </c>
       <c r="K412" s="14" t="n">
-        <v>14110</v>
+        <v>14114</v>
       </c>
       <c r="L412" s="15" t="n">
-        <v>5644</v>
+        <v>14114</v>
       </c>
       <c r="M412" s="12" t="inlineStr">
         <is>
-          <t>696641d77445fa001320e5e2</t>
+          <t>6708475d1f46ee001371cb20</t>
         </is>
       </c>
       <c r="N412" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696641d77445fa001320e5e2</t>
+          <t>https://superprofile.bio/vig/6708475d1f46ee001371cb20</t>
         </is>
       </c>
       <c r="O412" s="17" t="inlineStr">
@@ -30514,22 +30532,22 @@
       </c>
       <c r="B413" s="20" t="inlineStr">
         <is>
-          <t>654e35d70ce920001de26234</t>
+          <t>6961cac5209b3d00137110a2</t>
         </is>
       </c>
       <c r="C413" s="20" t="inlineStr">
         <is>
-          <t>radiobabaa</t>
+          <t>tradingexpert02</t>
         </is>
       </c>
       <c r="D413" s="19" t="inlineStr">
         <is>
-          <t>bairaagilokam@gmail.com</t>
+          <t>tradingexpert7180@gmail.com</t>
         </is>
       </c>
       <c r="E413" s="19" t="inlineStr">
         <is>
-          <t>9000090942</t>
+          <t>9784944154</t>
         </is>
       </c>
       <c r="F413" s="19" t="inlineStr">
@@ -30539,34 +30557,34 @@
       </c>
       <c r="G413" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H413" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I413" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J413" s="21" t="n">
-        <v>3531</v>
+        <v>5644</v>
       </c>
       <c r="K413" s="21" t="n">
-        <v>14106</v>
+        <v>14110</v>
       </c>
       <c r="L413" s="22" t="n">
-        <v>4710</v>
+        <v>5644</v>
       </c>
       <c r="M413" s="19" t="inlineStr">
         <is>
-          <t>6a92b996b3a738001366c2fc</t>
+          <t>696641d77445fa001320e5e2</t>
         </is>
       </c>
       <c r="N413" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a92b996b3a738001366c2fc</t>
+          <t>https://superprofile.bio/vig/696641d77445fa001320e5e2</t>
         </is>
       </c>
       <c r="O413" s="24" t="inlineStr">
@@ -30586,22 +30604,22 @@
       </c>
       <c r="B414" s="13" t="inlineStr">
         <is>
-          <t>649510441a32ba0020928c2d</t>
+          <t>654e35d70ce920001de26234</t>
         </is>
       </c>
       <c r="C414" s="13" t="inlineStr">
         <is>
-          <t>OmiSakhalkar</t>
+          <t>radiobabaa</t>
         </is>
       </c>
       <c r="D414" s="12" t="inlineStr">
         <is>
-          <t>sakhalkaronkar@gmail.com</t>
+          <t>bairaagilokam@gmail.com</t>
         </is>
       </c>
       <c r="E414" s="12" t="inlineStr">
         <is>
-          <t>9011099529</t>
+          <t>9000090942</t>
         </is>
       </c>
       <c r="F414" s="12" t="inlineStr">
@@ -30611,34 +30629,34 @@
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H414" s="12" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="H414" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="I414" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J414" s="14" t="n">
-        <v>14070</v>
+        <v>3531</v>
       </c>
       <c r="K414" s="14" t="n">
-        <v>14070</v>
+        <v>14106</v>
       </c>
       <c r="L414" s="15" t="n">
-        <v>14070</v>
+        <v>4710</v>
       </c>
       <c r="M414" s="12" t="inlineStr">
         <is>
-          <t>6579601dc879dd001d37904a</t>
+          <t>6a92b996b3a738001366c2fc</t>
         </is>
       </c>
       <c r="N414" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6579601dc879dd001d37904a</t>
+          <t>https://superprofile.bio/vig/6a92b996b3a738001366c2fc</t>
         </is>
       </c>
       <c r="O414" s="17" t="inlineStr">
@@ -30658,22 +30676,22 @@
       </c>
       <c r="B415" s="20" t="inlineStr">
         <is>
-          <t>66f153fcbce5f30013159b4a</t>
+          <t>649510441a32ba0020928c2d</t>
         </is>
       </c>
       <c r="C415" s="20" t="inlineStr">
         <is>
-          <t>investway</t>
+          <t>OmiSakhalkar</t>
         </is>
       </c>
       <c r="D415" s="19" t="inlineStr">
         <is>
-          <t>harickstewart@gmail.com</t>
+          <t>sakhalkaronkar@gmail.com</t>
         </is>
       </c>
       <c r="E415" s="19" t="inlineStr">
         <is>
-          <t>9724245588</t>
+          <t>9011099529</t>
         </is>
       </c>
       <c r="F415" s="19" t="inlineStr">
@@ -30683,34 +30701,34 @@
       </c>
       <c r="G415" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H415" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I415" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J415" s="21" t="n">
-        <v>10117</v>
+        <v>14070</v>
       </c>
       <c r="K415" s="21" t="n">
-        <v>14055</v>
+        <v>14070</v>
       </c>
       <c r="L415" s="22" t="n">
-        <v>10117</v>
+        <v>14070</v>
       </c>
       <c r="M415" s="19" t="inlineStr">
         <is>
-          <t>66f26b26befc8e0013688a1f</t>
+          <t>6579601dc879dd001d37904a</t>
         </is>
       </c>
       <c r="N415" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66f26b26befc8e0013688a1f</t>
+          <t>https://superprofile.bio/vig/6579601dc879dd001d37904a</t>
         </is>
       </c>
       <c r="O415" s="24" t="inlineStr">
@@ -30730,22 +30748,22 @@
       </c>
       <c r="B416" s="13" t="inlineStr">
         <is>
-          <t>687f538e23947700130cd9cc</t>
+          <t>66f153fcbce5f30013159b4a</t>
         </is>
       </c>
       <c r="C416" s="13" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>investway</t>
         </is>
       </c>
       <c r="D416" s="12" t="inlineStr">
         <is>
-          <t>mastermindteam051@gmail.com</t>
+          <t>harickstewart@gmail.com</t>
         </is>
       </c>
       <c r="E416" s="12" t="inlineStr">
         <is>
-          <t>9936556941</t>
+          <t>9724245588</t>
         </is>
       </c>
       <c r="F416" s="12" t="inlineStr">
@@ -30755,34 +30773,34 @@
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H416" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I416" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J416" s="14" t="n">
-        <v>5267</v>
+        <v>10117</v>
       </c>
       <c r="K416" s="14" t="n">
-        <v>14014</v>
+        <v>14055</v>
       </c>
       <c r="L416" s="15" t="n">
-        <v>5267</v>
+        <v>10117</v>
       </c>
       <c r="M416" s="12" t="inlineStr">
         <is>
-          <t>697998f47fac9d0013f74dfe</t>
+          <t>66f26b26befc8e0013688a1f</t>
         </is>
       </c>
       <c r="N416" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
+          <t>https://superprofile.bio/vig/66f26b26befc8e0013688a1f</t>
         </is>
       </c>
       <c r="O416" s="17" t="inlineStr">
@@ -30802,22 +30820,22 @@
       </c>
       <c r="B417" s="20" t="inlineStr">
         <is>
-          <t>644f511bb09d34001fdba603</t>
+          <t>687f538e23947700130cd9cc</t>
         </is>
       </c>
       <c r="C417" s="20" t="inlineStr">
         <is>
-          <t>manju235</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="D417" s="19" t="inlineStr">
         <is>
-          <t>sapnakanwarr2004@gmail.com</t>
+          <t>mastermindteam051@gmail.com</t>
         </is>
       </c>
       <c r="E417" s="19" t="inlineStr">
         <is>
-          <t>7877492320</t>
+          <t>9936556941</t>
         </is>
       </c>
       <c r="F417" s="19" t="inlineStr">
@@ -30827,7 +30845,7 @@
       </c>
       <c r="G417" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H417" s="19" t="inlineStr">
@@ -30839,22 +30857,22 @@
         <v>4</v>
       </c>
       <c r="J417" s="21" t="n">
-        <v>2250</v>
+        <v>5267</v>
       </c>
       <c r="K417" s="21" t="n">
-        <v>13658</v>
+        <v>14014</v>
       </c>
       <c r="L417" s="22" t="n">
-        <v>9608</v>
+        <v>5267</v>
       </c>
       <c r="M417" s="19" t="inlineStr">
         <is>
-          <t>6a887a1347d8100013f8b797</t>
+          <t>697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="N417" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a887a1347d8100013f8b797</t>
+          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="O417" s="24" t="inlineStr">
@@ -30874,22 +30892,22 @@
       </c>
       <c r="B418" s="13" t="inlineStr">
         <is>
-          <t>6a2036382888a500137bb912</t>
+          <t>644f511bb09d34001fdba603</t>
         </is>
       </c>
       <c r="C418" s="13" t="inlineStr">
         <is>
-          <t>yvstocks</t>
+          <t>manju235</t>
         </is>
       </c>
       <c r="D418" s="12" t="inlineStr">
         <is>
-          <t>yogeshmalviya1313@gmail.com</t>
+          <t>sapnakanwarr2004@gmail.com</t>
         </is>
       </c>
       <c r="E418" s="12" t="inlineStr">
         <is>
-          <t>8989262596</t>
+          <t>7877492320</t>
         </is>
       </c>
       <c r="F418" s="12" t="inlineStr">
@@ -30899,7 +30917,7 @@
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H418" s="12" t="inlineStr">
@@ -30908,25 +30926,25 @@
         </is>
       </c>
       <c r="I418" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J418" s="14" t="n">
-        <v>1778</v>
+        <v>2250</v>
       </c>
       <c r="K418" s="14" t="n">
-        <v>13634</v>
+        <v>13658</v>
       </c>
       <c r="L418" s="15" t="n">
-        <v>3952</v>
+        <v>9608</v>
       </c>
       <c r="M418" s="12" t="inlineStr">
         <is>
-          <t>6a20398f997af1001360a84c</t>
+          <t>6a887a1347d8100013f8b797</t>
         </is>
       </c>
       <c r="N418" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a20398f997af1001360a84c</t>
+          <t>https://superprofile.bio/vig/6a887a1347d8100013f8b797</t>
         </is>
       </c>
       <c r="O418" s="17" t="inlineStr">
@@ -30946,22 +30964,22 @@
       </c>
       <c r="B419" s="20" t="inlineStr">
         <is>
-          <t>64ac146aa698af0020798bce</t>
+          <t>6a2036382888a500137bb912</t>
         </is>
       </c>
       <c r="C419" s="20" t="inlineStr">
         <is>
-          <t>TheBigBullPremium</t>
+          <t>yvstocks</t>
         </is>
       </c>
       <c r="D419" s="19" t="inlineStr">
         <is>
-          <t>Paymentqoohoo@gmail.com</t>
+          <t>yogeshmalviya1313@gmail.com</t>
         </is>
       </c>
       <c r="E419" s="19" t="inlineStr">
         <is>
-          <t>8115825949</t>
+          <t>8989262596</t>
         </is>
       </c>
       <c r="F419" s="19" t="inlineStr">
@@ -30976,29 +30994,29 @@
       </c>
       <c r="H419" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I419" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J419" s="21" t="n">
-        <v>6727</v>
+        <v>1778</v>
       </c>
       <c r="K419" s="21" t="n">
-        <v>13618</v>
+        <v>13634</v>
       </c>
       <c r="L419" s="22" t="n">
-        <v>6891</v>
+        <v>3952</v>
       </c>
       <c r="M419" s="19" t="inlineStr">
         <is>
-          <t>67d96fae1b910100136f52e2</t>
+          <t>6a20398f997af1001360a84c</t>
         </is>
       </c>
       <c r="N419" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67d96fae1b910100136f52e2</t>
+          <t>https://superprofile.bio/vig/6a20398f997af1001360a84c</t>
         </is>
       </c>
       <c r="O419" s="24" t="inlineStr">
@@ -31018,22 +31036,22 @@
       </c>
       <c r="B420" s="13" t="inlineStr">
         <is>
-          <t>652966b0de6af5001d3dda25</t>
+          <t>64ac146aa698af0020798bce</t>
         </is>
       </c>
       <c r="C420" s="13" t="inlineStr">
         <is>
-          <t>maruticonsultancy</t>
+          <t>TheBigBullPremium</t>
         </is>
       </c>
       <c r="D420" s="12" t="inlineStr">
         <is>
-          <t>maruticonsultancy98@gmail.com</t>
+          <t>Paymentqoohoo@gmail.com</t>
         </is>
       </c>
       <c r="E420" s="12" t="inlineStr">
         <is>
-          <t>8901668662</t>
+          <t>8115825949</t>
         </is>
       </c>
       <c r="F420" s="12" t="inlineStr">
@@ -31048,29 +31066,29 @@
       </c>
       <c r="H420" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I420" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J420" s="14" t="n">
-        <v>3881</v>
+        <v>6727</v>
       </c>
       <c r="K420" s="14" t="n">
-        <v>13585</v>
+        <v>13618</v>
       </c>
       <c r="L420" s="15" t="n">
-        <v>4852</v>
+        <v>6891</v>
       </c>
       <c r="M420" s="12" t="inlineStr">
         <is>
-          <t>652a3033de6af5001d436363</t>
+          <t>67d96fae1b910100136f52e2</t>
         </is>
       </c>
       <c r="N420" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/652a3033de6af5001d436363</t>
+          <t>https://superprofile.bio/vig/67d96fae1b910100136f52e2</t>
         </is>
       </c>
       <c r="O420" s="17" t="inlineStr">
@@ -31090,22 +31108,22 @@
       </c>
       <c r="B421" s="20" t="inlineStr">
         <is>
-          <t>67a5b6121602340013351a38</t>
+          <t>652966b0de6af5001d3dda25</t>
         </is>
       </c>
       <c r="C421" s="20" t="inlineStr">
         <is>
-          <t>sharemarketstudies</t>
+          <t>maruticonsultancy</t>
         </is>
       </c>
       <c r="D421" s="19" t="inlineStr">
         <is>
-          <t>sharemarketstudies@gmail.com</t>
+          <t>maruticonsultancy98@gmail.com</t>
         </is>
       </c>
       <c r="E421" s="19" t="inlineStr">
         <is>
-          <t>7020684526</t>
+          <t>8901668662</t>
         </is>
       </c>
       <c r="F421" s="19" t="inlineStr">
@@ -31120,29 +31138,29 @@
       </c>
       <c r="H421" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I421" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J421" s="21" t="n">
-        <v>1939</v>
+        <v>3881</v>
       </c>
       <c r="K421" s="21" t="n">
-        <v>13573</v>
+        <v>13585</v>
       </c>
       <c r="L421" s="22" t="n">
-        <v>3878</v>
+        <v>4852</v>
       </c>
       <c r="M421" s="19" t="inlineStr">
         <is>
-          <t>687790a8beb3cd001320bdd5</t>
+          <t>652a3033de6af5001d436363</t>
         </is>
       </c>
       <c r="N421" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687790a8beb3cd001320bdd5</t>
+          <t>https://superprofile.bio/vig/652a3033de6af5001d436363</t>
         </is>
       </c>
       <c r="O421" s="24" t="inlineStr">
@@ -31162,22 +31180,22 @@
       </c>
       <c r="B422" s="13" t="inlineStr">
         <is>
-          <t>67a6163b2add040013b0ce0f</t>
+          <t>67a5b6121602340013351a38</t>
         </is>
       </c>
       <c r="C422" s="13" t="inlineStr">
         <is>
-          <t>aadavan</t>
+          <t>sharemarketstudies</t>
         </is>
       </c>
       <c r="D422" s="12" t="inlineStr">
         <is>
-          <t>jishanmaalik@gmail.com</t>
+          <t>sharemarketstudies@gmail.com</t>
         </is>
       </c>
       <c r="E422" s="12" t="inlineStr">
         <is>
-          <t>8088654150</t>
+          <t>7020684526</t>
         </is>
       </c>
       <c r="F422" s="12" t="inlineStr">
@@ -31192,29 +31210,29 @@
       </c>
       <c r="H422" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I422" s="13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J422" s="14" t="n">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="K422" s="14" t="n">
-        <v>13543</v>
+        <v>13573</v>
       </c>
       <c r="L422" s="15" t="n">
-        <v>6308</v>
+        <v>3878</v>
       </c>
       <c r="M422" s="12" t="inlineStr">
         <is>
-          <t>67a8c6045ee5520012250762</t>
+          <t>687790a8beb3cd001320bdd5</t>
         </is>
       </c>
       <c r="N422" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
+          <t>https://superprofile.bio/vig/687790a8beb3cd001320bdd5</t>
         </is>
       </c>
       <c r="O422" s="17" t="inlineStr">
@@ -31234,22 +31252,22 @@
       </c>
       <c r="B423" s="20" t="inlineStr">
         <is>
-          <t>695fc2d673169a001320fcf5</t>
+          <t>67a6163b2add040013b0ce0f</t>
         </is>
       </c>
       <c r="C423" s="20" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>aadavan</t>
         </is>
       </c>
       <c r="D423" s="19" t="inlineStr">
         <is>
-          <t>shivamshiva7870@gmail.com</t>
+          <t>jishanmaalik@gmail.com</t>
         </is>
       </c>
       <c r="E423" s="19" t="inlineStr">
         <is>
-          <t>9534598557</t>
+          <t>8088654150</t>
         </is>
       </c>
       <c r="F423" s="19" t="inlineStr">
@@ -31264,29 +31282,29 @@
       </c>
       <c r="H423" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I423" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J423" s="21" t="n">
-        <v>2453</v>
+        <v>1940</v>
       </c>
       <c r="K423" s="21" t="n">
-        <v>13535</v>
+        <v>13543</v>
       </c>
       <c r="L423" s="22" t="n">
-        <v>5389</v>
+        <v>6308</v>
       </c>
       <c r="M423" s="19" t="inlineStr">
         <is>
-          <t>6961fea2c0dd9a00126d58b1</t>
+          <t>67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="N423" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
+          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="O423" s="24" t="inlineStr">
@@ -31306,22 +31324,22 @@
       </c>
       <c r="B424" s="13" t="inlineStr">
         <is>
-          <t>66ba3fd39dbbdf001363534e</t>
+          <t>695fc2d673169a001320fcf5</t>
         </is>
       </c>
       <c r="C424" s="13" t="inlineStr">
         <is>
-          <t>psyterade</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="D424" s="12" t="inlineStr">
         <is>
-          <t>dasrupendra890@gmail.com</t>
+          <t>shivamshiva7870@gmail.com</t>
         </is>
       </c>
       <c r="E424" s="12" t="inlineStr">
         <is>
-          <t>8797313767</t>
+          <t>9534598557</t>
         </is>
       </c>
       <c r="F424" s="12" t="inlineStr">
@@ -31340,25 +31358,25 @@
         </is>
       </c>
       <c r="I424" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J424" s="14" t="n">
-        <v>11573</v>
+        <v>2453</v>
       </c>
       <c r="K424" s="14" t="n">
-        <v>13500</v>
+        <v>13535</v>
       </c>
       <c r="L424" s="15" t="n">
-        <v>11573</v>
+        <v>5389</v>
       </c>
       <c r="M424" s="12" t="inlineStr">
         <is>
-          <t>6a8d2a214fd9fb0013631358</t>
+          <t>6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="N424" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8d2a214fd9fb0013631358</t>
+          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="O424" s="17" t="inlineStr">
@@ -31378,22 +31396,22 @@
       </c>
       <c r="B425" s="20" t="inlineStr">
         <is>
-          <t>66d337800616ad00136e01e3</t>
+          <t>66ba3fd39dbbdf001363534e</t>
         </is>
       </c>
       <c r="C425" s="20" t="inlineStr">
         <is>
-          <t>optionanalysiswithyg</t>
+          <t>psyterade</t>
         </is>
       </c>
       <c r="D425" s="19" t="inlineStr">
         <is>
-          <t>prachidubey8149@gmail.com</t>
+          <t>dasrupendra890@gmail.com</t>
         </is>
       </c>
       <c r="E425" s="19" t="inlineStr">
         <is>
-          <t>9569472350</t>
+          <t>8797313767</t>
         </is>
       </c>
       <c r="F425" s="19" t="inlineStr">
@@ -31403,34 +31421,34 @@
       </c>
       <c r="G425" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H425" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I425" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J425" s="21" t="n">
-        <v>13499</v>
+        <v>11573</v>
       </c>
       <c r="K425" s="21" t="n">
-        <v>13499</v>
+        <v>13500</v>
       </c>
       <c r="L425" s="22" t="n">
-        <v>13499</v>
+        <v>11573</v>
       </c>
       <c r="M425" s="19" t="inlineStr">
         <is>
-          <t>69e7a0a8b9c4b70013bb3c26</t>
+          <t>6a8d2a214fd9fb0013631358</t>
         </is>
       </c>
       <c r="N425" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e7a0a8b9c4b70013bb3c26</t>
+          <t>https://superprofile.bio/vig/6a8d2a214fd9fb0013631358</t>
         </is>
       </c>
       <c r="O425" s="24" t="inlineStr">
@@ -31450,22 +31468,22 @@
       </c>
       <c r="B426" s="13" t="inlineStr">
         <is>
-          <t>632a9399c6a1534e767e54ed</t>
+          <t>66d337800616ad00136e01e3</t>
         </is>
       </c>
       <c r="C426" s="13" t="inlineStr">
         <is>
-          <t>twptechnology</t>
+          <t>optionanalysiswithyg</t>
         </is>
       </c>
       <c r="D426" s="12" t="inlineStr">
         <is>
-          <t>pratiksen537@gmail.com</t>
+          <t>prachidubey8149@gmail.com</t>
         </is>
       </c>
       <c r="E426" s="12" t="inlineStr">
         <is>
-          <t>9660741167</t>
+          <t>9569472350</t>
         </is>
       </c>
       <c r="F426" s="12" t="inlineStr">
@@ -31480,29 +31498,29 @@
       </c>
       <c r="H426" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I426" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J426" s="14" t="n">
-        <v>5399</v>
+        <v>13499</v>
       </c>
       <c r="K426" s="14" t="n">
-        <v>13497</v>
+        <v>13499</v>
       </c>
       <c r="L426" s="15" t="n">
-        <v>5399</v>
+        <v>13499</v>
       </c>
       <c r="M426" s="12" t="inlineStr">
         <is>
-          <t>6730b09e6f82800014f08ebd</t>
+          <t>69e7a0a8b9c4b70013bb3c26</t>
         </is>
       </c>
       <c r="N426" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6730b09e6f82800014f08ebd</t>
+          <t>https://superprofile.bio/vig/69e7a0a8b9c4b70013bb3c26</t>
         </is>
       </c>
       <c r="O426" s="17" t="inlineStr">
@@ -31522,22 +31540,22 @@
       </c>
       <c r="B427" s="20" t="inlineStr">
         <is>
-          <t>66926a105d82bc0013c1229c</t>
+          <t>632a9399c6a1534e767e54ed</t>
         </is>
       </c>
       <c r="C427" s="20" t="inlineStr">
         <is>
-          <t>aactiveetraders</t>
+          <t>twptechnology</t>
         </is>
       </c>
       <c r="D427" s="19" t="inlineStr">
         <is>
-          <t>rshinde7057@gmail.com</t>
+          <t>pratiksen537@gmail.com</t>
         </is>
       </c>
       <c r="E427" s="19" t="inlineStr">
         <is>
-          <t>8104421373</t>
+          <t>9660741167</t>
         </is>
       </c>
       <c r="F427" s="19" t="inlineStr">
@@ -31547,7 +31565,7 @@
       </c>
       <c r="G427" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H427" s="19" t="inlineStr">
@@ -31556,25 +31574,25 @@
         </is>
       </c>
       <c r="I427" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J427" s="21" t="n">
-        <v>2893</v>
+        <v>5399</v>
       </c>
       <c r="K427" s="21" t="n">
-        <v>13496</v>
+        <v>13497</v>
       </c>
       <c r="L427" s="22" t="n">
-        <v>3856</v>
+        <v>5399</v>
       </c>
       <c r="M427" s="19" t="inlineStr">
         <is>
-          <t>67cab3644e87bf0013f15f65</t>
+          <t>6730b09e6f82800014f08ebd</t>
         </is>
       </c>
       <c r="N427" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
+          <t>https://superprofile.bio/vig/6730b09e6f82800014f08ebd</t>
         </is>
       </c>
       <c r="O427" s="24" t="inlineStr">
@@ -31594,22 +31612,22 @@
       </c>
       <c r="B428" s="13" t="inlineStr">
         <is>
-          <t>65237580a4e730001df28da0</t>
+          <t>66926a105d82bc0013c1229c</t>
         </is>
       </c>
       <c r="C428" s="13" t="inlineStr">
         <is>
-          <t>chinmayonniftyy</t>
+          <t>aactiveetraders</t>
         </is>
       </c>
       <c r="D428" s="12" t="inlineStr">
         <is>
-          <t>chinmaypattanaik81@gmail.com</t>
+          <t>rshinde7057@gmail.com</t>
         </is>
       </c>
       <c r="E428" s="12" t="inlineStr">
         <is>
-          <t>8018863337</t>
+          <t>8104421373</t>
         </is>
       </c>
       <c r="F428" s="12" t="inlineStr">
@@ -31619,34 +31637,34 @@
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H428" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I428" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J428" s="14" t="n">
-        <v>1349</v>
+        <v>2893</v>
       </c>
       <c r="K428" s="14" t="n">
-        <v>13492</v>
+        <v>13496</v>
       </c>
       <c r="L428" s="15" t="n">
-        <v>5397</v>
+        <v>3856</v>
       </c>
       <c r="M428" s="12" t="inlineStr">
         <is>
-          <t>68b414cc3eef9400133fcbfd</t>
+          <t>67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="N428" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b414cc3eef9400133fcbfd</t>
+          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="O428" s="17" t="inlineStr">
@@ -31666,22 +31684,22 @@
       </c>
       <c r="B429" s="20" t="inlineStr">
         <is>
-          <t>6570843bf00260001e4d51c0</t>
+          <t>65237580a4e730001df28da0</t>
         </is>
       </c>
       <c r="C429" s="20" t="inlineStr">
         <is>
-          <t>SHARESHARK7</t>
+          <t>chinmayonniftyy</t>
         </is>
       </c>
       <c r="D429" s="19" t="inlineStr">
         <is>
-          <t>Shareshark7@gmail.com</t>
+          <t>chinmaypattanaik81@gmail.com</t>
         </is>
       </c>
       <c r="E429" s="19" t="inlineStr">
         <is>
-          <t>9289228409</t>
+          <t>8018863337</t>
         </is>
       </c>
       <c r="F429" s="19" t="inlineStr">
@@ -31691,7 +31709,7 @@
       </c>
       <c r="G429" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H429" s="19" t="inlineStr">
@@ -31700,25 +31718,25 @@
         </is>
       </c>
       <c r="I429" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J429" s="21" t="n">
-        <v>4593</v>
+        <v>1349</v>
       </c>
       <c r="K429" s="21" t="n">
-        <v>13381</v>
+        <v>13492</v>
       </c>
       <c r="L429" s="22" t="n">
-        <v>8788</v>
+        <v>5397</v>
       </c>
       <c r="M429" s="19" t="inlineStr">
         <is>
-          <t>6570860cbcd285001db72761</t>
+          <t>68b414cc3eef9400133fcbfd</t>
         </is>
       </c>
       <c r="N429" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6570860cbcd285001db72761</t>
+          <t>https://superprofile.bio/vig/68b414cc3eef9400133fcbfd</t>
         </is>
       </c>
       <c r="O429" s="24" t="inlineStr">
@@ -31738,22 +31756,22 @@
       </c>
       <c r="B430" s="13" t="inlineStr">
         <is>
-          <t>65f92f6ac022090013a05e2f</t>
+          <t>6570843bf00260001e4d51c0</t>
         </is>
       </c>
       <c r="C430" s="13" t="inlineStr">
         <is>
-          <t>brokerntreder09</t>
+          <t>SHARESHARK7</t>
         </is>
       </c>
       <c r="D430" s="12" t="inlineStr">
         <is>
-          <t>moaakilsandhi786@gmail.com</t>
+          <t>Shareshark7@gmail.com</t>
         </is>
       </c>
       <c r="E430" s="12" t="inlineStr">
         <is>
-          <t>9316693141</t>
+          <t>9289228409</t>
         </is>
       </c>
       <c r="F430" s="12" t="inlineStr">
@@ -31763,34 +31781,34 @@
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H430" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I430" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J430" s="14" t="n">
-        <v>2540</v>
+        <v>4593</v>
       </c>
       <c r="K430" s="14" t="n">
-        <v>13263</v>
+        <v>13381</v>
       </c>
       <c r="L430" s="15" t="n">
-        <v>8748</v>
+        <v>8788</v>
       </c>
       <c r="M430" s="12" t="inlineStr">
         <is>
-          <t>69786236017be60013a65fc2</t>
+          <t>6570860cbcd285001db72761</t>
         </is>
       </c>
       <c r="N430" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69786236017be60013a65fc2</t>
+          <t>https://superprofile.bio/vig/6570860cbcd285001db72761</t>
         </is>
       </c>
       <c r="O430" s="17" t="inlineStr">
@@ -31810,22 +31828,22 @@
       </c>
       <c r="B431" s="20" t="inlineStr">
         <is>
-          <t>64b0fcd06794f2002a008a24</t>
+          <t>65f92f6ac022090013a05e2f</t>
         </is>
       </c>
       <c r="C431" s="20" t="inlineStr">
         <is>
-          <t>tradelikealph</t>
+          <t>brokerntreder09</t>
         </is>
       </c>
       <c r="D431" s="19" t="inlineStr">
         <is>
-          <t>Bhupendradevda88@gmail.com</t>
+          <t>moaakilsandhi786@gmail.com</t>
         </is>
       </c>
       <c r="E431" s="19" t="inlineStr">
         <is>
-          <t>9724755466</t>
+          <t>9316693141</t>
         </is>
       </c>
       <c r="F431" s="19" t="inlineStr">
@@ -31835,34 +31853,34 @@
       </c>
       <c r="G431" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H431" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I431" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J431" s="21" t="n">
-        <v>6627</v>
+        <v>2540</v>
       </c>
       <c r="K431" s="21" t="n">
-        <v>13254</v>
+        <v>13263</v>
       </c>
       <c r="L431" s="22" t="n">
-        <v>6627</v>
+        <v>8748</v>
       </c>
       <c r="M431" s="19" t="inlineStr">
         <is>
-          <t>683ef78254f0f6001337b0b7</t>
+          <t>69786236017be60013a65fc2</t>
         </is>
       </c>
       <c r="N431" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/683ef78254f0f6001337b0b7</t>
+          <t>https://superprofile.bio/vig/69786236017be60013a65fc2</t>
         </is>
       </c>
       <c r="O431" s="24" t="inlineStr">
@@ -31882,22 +31900,22 @@
       </c>
       <c r="B432" s="13" t="inlineStr">
         <is>
-          <t>6a100cef9fe3f3001288dbfc</t>
+          <t>64b0fcd06794f2002a008a24</t>
         </is>
       </c>
       <c r="C432" s="13" t="inlineStr">
         <is>
-          <t>tyagi01018h</t>
+          <t>tradelikealph</t>
         </is>
       </c>
       <c r="D432" s="12" t="inlineStr">
         <is>
-          <t>taruntyagi9519@gmail.com</t>
+          <t>Bhupendradevda88@gmail.com</t>
         </is>
       </c>
       <c r="E432" s="12" t="inlineStr">
         <is>
-          <t>9634039110</t>
+          <t>9724755466</t>
         </is>
       </c>
       <c r="F432" s="12" t="inlineStr">
@@ -31912,29 +31930,29 @@
       </c>
       <c r="H432" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I432" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J432" s="14" t="n">
-        <v>3763</v>
+        <v>6627</v>
       </c>
       <c r="K432" s="14" t="n">
-        <v>13170</v>
+        <v>13254</v>
       </c>
       <c r="L432" s="15" t="n">
-        <v>3763</v>
+        <v>6627</v>
       </c>
       <c r="M432" s="12" t="inlineStr">
         <is>
-          <t>6a1aa5ef98a0930013839311</t>
+          <t>683ef78254f0f6001337b0b7</t>
         </is>
       </c>
       <c r="N432" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a1aa5ef98a0930013839311</t>
+          <t>https://superprofile.bio/vig/683ef78254f0f6001337b0b7</t>
         </is>
       </c>
       <c r="O432" s="17" t="inlineStr">
@@ -31954,22 +31972,22 @@
       </c>
       <c r="B433" s="20" t="inlineStr">
         <is>
-          <t>68edde8bd4a4db0013530331</t>
+          <t>6a100cef9fe3f3001288dbfc</t>
         </is>
       </c>
       <c r="C433" s="20" t="inlineStr">
         <is>
-          <t>httpstmetheforexfund</t>
+          <t>tyagi01018h</t>
         </is>
       </c>
       <c r="D433" s="19" t="inlineStr">
         <is>
-          <t>salimjadu90@gmail.com</t>
+          <t>taruntyagi9519@gmail.com</t>
         </is>
       </c>
       <c r="E433" s="19" t="inlineStr">
         <is>
-          <t>8279903733</t>
+          <t>9634039110</t>
         </is>
       </c>
       <c r="F433" s="19" t="inlineStr">
@@ -31979,34 +31997,34 @@
       </c>
       <c r="G433" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H433" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I433" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J433" s="21" t="n">
-        <v>1881</v>
+        <v>3763</v>
       </c>
       <c r="K433" s="21" t="n">
-        <v>13168</v>
+        <v>13170</v>
       </c>
       <c r="L433" s="22" t="n">
-        <v>2822</v>
+        <v>3763</v>
       </c>
       <c r="M433" s="19" t="inlineStr">
         <is>
-          <t>69974b6011c3e90013a068fc</t>
+          <t>6a1aa5ef98a0930013839311</t>
         </is>
       </c>
       <c r="N433" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69974b6011c3e90013a068fc</t>
+          <t>https://superprofile.bio/vig/6a1aa5ef98a0930013839311</t>
         </is>
       </c>
       <c r="O433" s="24" t="inlineStr">
@@ -32026,22 +32044,22 @@
       </c>
       <c r="B434" s="13" t="inlineStr">
         <is>
-          <t>69e89b0ed9ffde0013e31879</t>
+          <t>68edde8bd4a4db0013530331</t>
         </is>
       </c>
       <c r="C434" s="13" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>httpstmetheforexfund</t>
         </is>
       </c>
       <c r="D434" s="12" t="inlineStr">
         <is>
-          <t>nitindhandre42@gmail.com</t>
+          <t>salimjadu90@gmail.com</t>
         </is>
       </c>
       <c r="E434" s="12" t="inlineStr">
         <is>
-          <t>7977913010</t>
+          <t>8279903733</t>
         </is>
       </c>
       <c r="F434" s="12" t="inlineStr">
@@ -32051,34 +32069,34 @@
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H434" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I434" s="13" t="n">
         <v>6</v>
       </c>
       <c r="J434" s="14" t="n">
-        <v>1714</v>
+        <v>1881</v>
       </c>
       <c r="K434" s="14" t="n">
-        <v>13140</v>
+        <v>13168</v>
       </c>
       <c r="L434" s="15" t="n">
-        <v>3428</v>
+        <v>2822</v>
       </c>
       <c r="M434" s="12" t="inlineStr">
         <is>
-          <t>6a787fec62ca790013c3fe57</t>
+          <t>69974b6011c3e90013a068fc</t>
         </is>
       </c>
       <c r="N434" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
+          <t>https://superprofile.bio/vig/69974b6011c3e90013a068fc</t>
         </is>
       </c>
       <c r="O434" s="17" t="inlineStr">
@@ -32098,22 +32116,22 @@
       </c>
       <c r="B435" s="20" t="inlineStr">
         <is>
-          <t>62fded2fc251165bd614c60b</t>
+          <t>69e89b0ed9ffde0013e31879</t>
         </is>
       </c>
       <c r="C435" s="20" t="inlineStr">
         <is>
-          <t>Eagles</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="D435" s="19" t="inlineStr">
         <is>
-          <t>abhi120302378@gmail.com</t>
+          <t>nitindhandre42@gmail.com</t>
         </is>
       </c>
       <c r="E435" s="19" t="inlineStr">
         <is>
-          <t>8115000004</t>
+          <t>7977913010</t>
         </is>
       </c>
       <c r="F435" s="19" t="inlineStr">
@@ -32128,29 +32146,29 @@
       </c>
       <c r="H435" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I435" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J435" s="21" t="n">
-        <v>3902</v>
+        <v>1714</v>
       </c>
       <c r="K435" s="21" t="n">
-        <v>13136</v>
+        <v>13140</v>
       </c>
       <c r="L435" s="22" t="n">
-        <v>4373</v>
+        <v>3428</v>
       </c>
       <c r="M435" s="19" t="inlineStr">
         <is>
-          <t>68a590a3342f1300132334fa</t>
+          <t>6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="N435" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68a590a3342f1300132334fa</t>
+          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="O435" s="24" t="inlineStr">
@@ -32170,22 +32188,22 @@
       </c>
       <c r="B436" s="13" t="inlineStr">
         <is>
-          <t>6a131bb7d14a790012e11a6f</t>
+          <t>62fded2fc251165bd614c60b</t>
         </is>
       </c>
       <c r="C436" s="13" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>Eagles</t>
         </is>
       </c>
       <c r="D436" s="12" t="inlineStr">
         <is>
-          <t>ffkatarka@gmail.com</t>
+          <t>abhi120302378@gmail.com</t>
         </is>
       </c>
       <c r="E436" s="12" t="inlineStr">
         <is>
-          <t>9101299533</t>
+          <t>8115000004</t>
         </is>
       </c>
       <c r="F436" s="12" t="inlineStr">
@@ -32204,25 +32222,25 @@
         </is>
       </c>
       <c r="I436" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J436" s="14" t="n">
-        <v>1976</v>
+        <v>3902</v>
       </c>
       <c r="K436" s="14" t="n">
-        <v>13081</v>
+        <v>13136</v>
       </c>
       <c r="L436" s="15" t="n">
-        <v>5834</v>
+        <v>4373</v>
       </c>
       <c r="M436" s="12" t="inlineStr">
         <is>
-          <t>6a6d9d5033211a001319c244</t>
+          <t>68a590a3342f1300132334fa</t>
         </is>
       </c>
       <c r="N436" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
+          <t>https://superprofile.bio/vig/68a590a3342f1300132334fa</t>
         </is>
       </c>
       <c r="O436" s="17" t="inlineStr">
@@ -32242,22 +32260,22 @@
       </c>
       <c r="B437" s="20" t="inlineStr">
         <is>
-          <t>66ab4182042051001366042b</t>
+          <t>6a131bb7d14a790012e11a6f</t>
         </is>
       </c>
       <c r="C437" s="20" t="inlineStr">
         <is>
-          <t>swingedge</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="D437" s="19" t="inlineStr">
         <is>
-          <t>sumannatani8586@gmail.com</t>
+          <t>ffkatarka@gmail.com</t>
         </is>
       </c>
       <c r="E437" s="19" t="inlineStr">
         <is>
-          <t>8905901899</t>
+          <t>9101299533</t>
         </is>
       </c>
       <c r="F437" s="19" t="inlineStr">
@@ -32267,7 +32285,7 @@
       </c>
       <c r="G437" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H437" s="19" t="inlineStr">
@@ -32276,25 +32294,25 @@
         </is>
       </c>
       <c r="I437" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J437" s="21" t="n">
-        <v>1778</v>
+        <v>1976</v>
       </c>
       <c r="K437" s="21" t="n">
-        <v>13058</v>
+        <v>13081</v>
       </c>
       <c r="L437" s="22" t="n">
-        <v>7520</v>
+        <v>5834</v>
       </c>
       <c r="M437" s="19" t="inlineStr">
         <is>
-          <t>68b5d44bdb108f0013354a5e</t>
+          <t>6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="N437" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b5d44bdb108f0013354a5e</t>
+          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="O437" s="24" t="inlineStr">
@@ -32314,22 +32332,22 @@
       </c>
       <c r="B438" s="13" t="inlineStr">
         <is>
-          <t>64e5ae617f68ef001ea74131</t>
+          <t>66ab4182042051001366042b</t>
         </is>
       </c>
       <c r="C438" s="13" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>swingedge</t>
         </is>
       </c>
       <c r="D438" s="12" t="inlineStr">
         <is>
-          <t>dalalmihir81@gmail.com</t>
+          <t>sumannatani8586@gmail.com</t>
         </is>
       </c>
       <c r="E438" s="12" t="inlineStr">
         <is>
-          <t>9879558198</t>
+          <t>8905901899</t>
         </is>
       </c>
       <c r="F438" s="12" t="inlineStr">
@@ -32339,34 +32357,34 @@
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H438" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I438" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J438" s="14" t="n">
-        <v>1996</v>
+        <v>1778</v>
       </c>
       <c r="K438" s="14" t="n">
-        <v>13000</v>
+        <v>13058</v>
       </c>
       <c r="L438" s="15" t="n">
-        <v>5004</v>
+        <v>7520</v>
       </c>
       <c r="M438" s="12" t="inlineStr">
         <is>
-          <t>66c871cfc6acc2001368e5a3</t>
+          <t>68b5d44bdb108f0013354a5e</t>
         </is>
       </c>
       <c r="N438" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
+          <t>https://superprofile.bio/vig/68b5d44bdb108f0013354a5e</t>
         </is>
       </c>
       <c r="O438" s="17" t="inlineStr">
@@ -32386,22 +32404,22 @@
       </c>
       <c r="B439" s="20" t="inlineStr">
         <is>
-          <t>6325d0f3770ec476f4cfc1f7</t>
+          <t>64e5ae617f68ef001ea74131</t>
         </is>
       </c>
       <c r="C439" s="20" t="inlineStr">
         <is>
-          <t>investhealthy07</t>
+          <t>dalalmihir81</t>
         </is>
       </c>
       <c r="D439" s="19" t="inlineStr">
         <is>
-          <t>ganrraj@gmail.com</t>
+          <t>dalalmihir81@gmail.com</t>
         </is>
       </c>
       <c r="E439" s="19" t="inlineStr">
         <is>
-          <t>9372871592</t>
+          <t>9879558198</t>
         </is>
       </c>
       <c r="F439" s="19" t="inlineStr">
@@ -32416,29 +32434,29 @@
       </c>
       <c r="H439" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I439" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J439" s="21" t="n">
-        <v>6575</v>
+        <v>1996</v>
       </c>
       <c r="K439" s="21" t="n">
-        <v>12954</v>
+        <v>13000</v>
       </c>
       <c r="L439" s="22" t="n">
-        <v>6575</v>
+        <v>5004</v>
       </c>
       <c r="M439" s="19" t="inlineStr">
         <is>
-          <t>66d9cb296ef79f00130ac417</t>
+          <t>66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="N439" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66d9cb296ef79f00130ac417</t>
+          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="O439" s="24" t="inlineStr">
@@ -32458,22 +32476,22 @@
       </c>
       <c r="B440" s="13" t="inlineStr">
         <is>
-          <t>659d87354540b4001dc9c97a</t>
+          <t>6325d0f3770ec476f4cfc1f7</t>
         </is>
       </c>
       <c r="C440" s="13" t="inlineStr">
         <is>
-          <t>worldmosttrader</t>
+          <t>investhealthy07</t>
         </is>
       </c>
       <c r="D440" s="12" t="inlineStr">
         <is>
-          <t>rakeshkumar890529@gmail.com</t>
+          <t>ganrraj@gmail.com</t>
         </is>
       </c>
       <c r="E440" s="12" t="inlineStr">
         <is>
-          <t>8955640502</t>
+          <t>9372871592</t>
         </is>
       </c>
       <c r="F440" s="12" t="inlineStr">
@@ -32488,29 +32506,29 @@
       </c>
       <c r="H440" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I440" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J440" s="14" t="n">
-        <v>6471</v>
+        <v>6575</v>
       </c>
       <c r="K440" s="14" t="n">
-        <v>12942</v>
+        <v>12954</v>
       </c>
       <c r="L440" s="15" t="n">
-        <v>6471</v>
+        <v>6575</v>
       </c>
       <c r="M440" s="12" t="inlineStr">
         <is>
-          <t>67a988222b922d00136fd091</t>
+          <t>66d9cb296ef79f00130ac417</t>
         </is>
       </c>
       <c r="N440" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a988222b922d00136fd091</t>
+          <t>https://superprofile.bio/vig/66d9cb296ef79f00130ac417</t>
         </is>
       </c>
       <c r="O440" s="17" t="inlineStr">
@@ -32530,22 +32548,22 @@
       </c>
       <c r="B441" s="20" t="inlineStr">
         <is>
-          <t>693319d6f3052a00135857d9</t>
+          <t>659d87354540b4001dc9c97a</t>
         </is>
       </c>
       <c r="C441" s="20" t="inlineStr">
         <is>
-          <t>gurusharemarket</t>
+          <t>worldmosttrader</t>
         </is>
       </c>
       <c r="D441" s="19" t="inlineStr">
         <is>
-          <t>gurusharemarket01@gmail.com</t>
+          <t>rakeshkumar890529@gmail.com</t>
         </is>
       </c>
       <c r="E441" s="19" t="inlineStr">
         <is>
-          <t>9911995213</t>
+          <t>8955640502</t>
         </is>
       </c>
       <c r="F441" s="19" t="inlineStr">
@@ -32555,34 +32573,34 @@
       </c>
       <c r="G441" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H441" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I441" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J441" s="21" t="n">
-        <v>12702</v>
+        <v>6471</v>
       </c>
       <c r="K441" s="21" t="n">
-        <v>12702</v>
+        <v>12942</v>
       </c>
       <c r="L441" s="22" t="n">
-        <v>12702</v>
+        <v>6471</v>
       </c>
       <c r="M441" s="19" t="inlineStr">
         <is>
-          <t>69331ed7c65ec80013b53645</t>
+          <t>67a988222b922d00136fd091</t>
         </is>
       </c>
       <c r="N441" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
+          <t>https://superprofile.bio/vig/67a988222b922d00136fd091</t>
         </is>
       </c>
       <c r="O441" s="24" t="inlineStr">
@@ -32602,22 +32620,22 @@
       </c>
       <c r="B442" s="13" t="inlineStr">
         <is>
-          <t>6541dfbbc8b47a001ec7f9ae</t>
+          <t>693319d6f3052a00135857d9</t>
         </is>
       </c>
       <c r="C442" s="13" t="inlineStr">
         <is>
-          <t>imock101</t>
+          <t>gurusharemarket</t>
         </is>
       </c>
       <c r="D442" s="12" t="inlineStr">
         <is>
-          <t>mrmchandsamota@gmail.com</t>
+          <t>gurusharemarket01@gmail.com</t>
         </is>
       </c>
       <c r="E442" s="12" t="inlineStr">
         <is>
-          <t>8505065646</t>
+          <t>9911995213</t>
         </is>
       </c>
       <c r="F442" s="12" t="inlineStr">
@@ -32627,34 +32645,34 @@
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H442" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I442" s="13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J442" s="14" t="n">
-        <v>1127</v>
+        <v>12702</v>
       </c>
       <c r="K442" s="14" t="n">
-        <v>12512</v>
+        <v>12702</v>
       </c>
       <c r="L442" s="15" t="n">
-        <v>5160</v>
+        <v>12702</v>
       </c>
       <c r="M442" s="12" t="inlineStr">
         <is>
-          <t>69eccd685fe24c0013aef1e2</t>
+          <t>69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="N442" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69eccd685fe24c0013aef1e2</t>
+          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="O442" s="17" t="inlineStr">
@@ -32674,22 +32692,22 @@
       </c>
       <c r="B443" s="20" t="inlineStr">
         <is>
-          <t>6466fe894600ce00214fabd6</t>
+          <t>6541dfbbc8b47a001ec7f9ae</t>
         </is>
       </c>
       <c r="C443" s="20" t="inlineStr">
         <is>
-          <t>daytraders247</t>
+          <t>imock101</t>
         </is>
       </c>
       <c r="D443" s="19" t="inlineStr">
         <is>
-          <t>dj025820@gmail.com</t>
+          <t>mrmchandsamota@gmail.com</t>
         </is>
       </c>
       <c r="E443" s="19" t="inlineStr">
         <is>
-          <t>9587744549</t>
+          <t>8505065646</t>
         </is>
       </c>
       <c r="F443" s="19" t="inlineStr">
@@ -32699,7 +32717,7 @@
       </c>
       <c r="G443" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H443" s="19" t="inlineStr">
@@ -32708,25 +32726,25 @@
         </is>
       </c>
       <c r="I443" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J443" s="21" t="n">
-        <v>5716</v>
+        <v>1127</v>
       </c>
       <c r="K443" s="21" t="n">
-        <v>12370</v>
+        <v>12512</v>
       </c>
       <c r="L443" s="22" t="n">
-        <v>5716</v>
+        <v>5160</v>
       </c>
       <c r="M443" s="19" t="inlineStr">
         <is>
-          <t>67d8393615497c0013a8e740</t>
+          <t>69eccd685fe24c0013aef1e2</t>
         </is>
       </c>
       <c r="N443" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67d8393615497c0013a8e740</t>
+          <t>https://superprofile.bio/vig/69eccd685fe24c0013aef1e2</t>
         </is>
       </c>
       <c r="O443" s="24" t="inlineStr">
@@ -32746,22 +32764,22 @@
       </c>
       <c r="B444" s="13" t="inlineStr">
         <is>
-          <t>62115e4a6bd738258707c0e9</t>
+          <t>6466fe894600ce00214fabd6</t>
         </is>
       </c>
       <c r="C444" s="13" t="inlineStr">
         <is>
-          <t>aditya</t>
+          <t>daytraders247</t>
         </is>
       </c>
       <c r="D444" s="12" t="inlineStr">
         <is>
-          <t>imavschoudhary@gmail.com</t>
+          <t>dj025820@gmail.com</t>
         </is>
       </c>
       <c r="E444" s="12" t="inlineStr">
         <is>
-          <t>9717115749</t>
+          <t>9587744549</t>
         </is>
       </c>
       <c r="F444" s="12" t="inlineStr">
@@ -32776,29 +32794,29 @@
       </c>
       <c r="H444" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I444" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J444" s="14" t="n">
-        <v>2355</v>
+        <v>5716</v>
       </c>
       <c r="K444" s="14" t="n">
-        <v>12300</v>
+        <v>12370</v>
       </c>
       <c r="L444" s="15" t="n">
-        <v>3795</v>
+        <v>5716</v>
       </c>
       <c r="M444" s="12" t="inlineStr">
         <is>
-          <t>6511690d55ae1b0058703c86</t>
+          <t>67d8393615497c0013a8e740</t>
         </is>
       </c>
       <c r="N444" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
+          <t>https://superprofile.bio/vig/67d8393615497c0013a8e740</t>
         </is>
       </c>
       <c r="O444" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-07 19:38:42 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 02:20:47 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 02:20:47 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 05:39:29 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹38,616,205.00</t>
+          <t>₹38,664,040.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4450568</v>
+        <v>4498403</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>63e0416509bf7d00326f6ef9</t>
+          <t>67038e07eda36800133f37cc</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>lws</t>
+          <t>topstocker24</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>omkar.vent@gmail.com</t>
+          <t>k4vaibhav17@gmail.com</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>9829012838</t>
+          <t>7060035920</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -2414,25 +2414,25 @@
         </is>
       </c>
       <c r="I22" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>46976</v>
+        <v>47835</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>281857</v>
+        <v>283768</v>
       </c>
       <c r="L22" s="15" t="n">
-        <v>93953</v>
+        <v>78026</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
-          <t>6a3e7980291f3d0013b550f9</t>
+          <t>670391811232fa0013fdf36b</t>
         </is>
       </c>
       <c r="N22" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3e7980291f3d0013b550f9</t>
+          <t>https://superprofile.bio/vig/670391811232fa0013fdf36b</t>
         </is>
       </c>
       <c r="O22" s="17" t="inlineStr">
@@ -2452,22 +2452,22 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>65e953798a133b0013814853</t>
+          <t>63e0416509bf7d00326f6ef9</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>samirpradhan</t>
+          <t>lws</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>samirkumarpradhan9@gmail.com</t>
+          <t>omkar.vent@gmail.com</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>9178074088</t>
+          <t>9829012838</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -2486,25 +2486,25 @@
         </is>
       </c>
       <c r="I23" s="20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>22589</v>
+        <v>46976</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>277969</v>
+        <v>281857</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>60916</v>
+        <v>93953</v>
       </c>
       <c r="M23" s="19" t="inlineStr">
         <is>
-          <t>65e9543e9451aa0012fe0644</t>
+          <t>6a3e7980291f3d0013b550f9</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
+          <t>https://superprofile.bio/vig/6a3e7980291f3d0013b550f9</t>
         </is>
       </c>
       <c r="O23" s="24" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>6a85a273ac3621001354cbf3</t>
+          <t>65e953798a133b0013814853</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>ketan6618</t>
+          <t>samirpradhan</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>consultancysimplified28@gmail.com</t>
+          <t>samirkumarpradhan9@gmail.com</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>7000078224</t>
+          <t>9178074088</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2554,29 +2554,29 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I24" s="13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>92003</v>
+        <v>22589</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>277250</v>
+        <v>277969</v>
       </c>
       <c r="L24" s="15" t="n">
-        <v>141311</v>
+        <v>60916</v>
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
-          <t>6865592c338056001322e55e</t>
+          <t>65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6865592c338056001322e55e</t>
+          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="O24" s="17" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>67e1a6a720f70200135afe0a</t>
+          <t>6a85a273ac3621001354cbf3</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>tradesatyamsharma</t>
+          <t>ketan6618</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>indexinsiders@gmail.com</t>
+          <t>consultancysimplified28@gmail.com</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>7015946114</t>
+          <t>7000078224</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -2626,29 +2626,29 @@
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I25" s="20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>30822</v>
+        <v>92003</v>
       </c>
       <c r="K25" s="21" t="n">
-        <v>276343</v>
+        <v>277250</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>51674</v>
+        <v>141311</v>
       </c>
       <c r="M25" s="19" t="inlineStr">
         <is>
-          <t>6a76f4a37590c2001315562c</t>
+          <t>6865592c338056001322e55e</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a76f4a37590c2001315562c</t>
+          <t>https://superprofile.bio/vig/6865592c338056001322e55e</t>
         </is>
       </c>
       <c r="O25" s="24" t="inlineStr">
@@ -2668,22 +2668,22 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>62d954abba10293040ccce13</t>
+          <t>67e1a6a720f70200135afe0a</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>lalitkishoresharma</t>
+          <t>tradesatyamsharma</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Lalitkishoresharma1989@gmail.com</t>
+          <t>indexinsiders@gmail.com</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>8745857356</t>
+          <t>7015946114</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -2702,25 +2702,25 @@
         </is>
       </c>
       <c r="I26" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>14469</v>
+        <v>30822</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>272020</v>
+        <v>276343</v>
       </c>
       <c r="L26" s="15" t="n">
-        <v>65111</v>
+        <v>51674</v>
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
-          <t>62d958779656df7a57f42227</t>
+          <t>6a76f4a37590c2001315562c</t>
         </is>
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62d958779656df7a57f42227</t>
+          <t>https://superprofile.bio/vig/6a76f4a37590c2001315562c</t>
         </is>
       </c>
       <c r="O26" s="17" t="inlineStr">
@@ -2740,22 +2740,22 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>69bcddef6d730800132e6d04</t>
+          <t>62d954abba10293040ccce13</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>akshay5894</t>
+          <t>lalitkishoresharma</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>maharashtrafamily288@gmail.com</t>
+          <t>Lalitkishoresharma1989@gmail.com</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>8855978736</t>
+          <t>8745857356</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
@@ -2765,34 +2765,34 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="I27" s="20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>269734</v>
+        <v>14469</v>
       </c>
       <c r="K27" s="21" t="n">
-        <v>269734</v>
+        <v>272020</v>
       </c>
       <c r="L27" s="22" t="n">
-        <v>269734</v>
+        <v>65111</v>
       </c>
       <c r="M27" s="19" t="inlineStr">
         <is>
-          <t>6a9918f052d28b0013b473cf</t>
+          <t>62d958779656df7a57f42227</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9918f052d28b0013b473cf</t>
+          <t>https://superprofile.bio/vig/62d958779656df7a57f42227</t>
         </is>
       </c>
       <c r="O27" s="24" t="inlineStr">
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>686213a26baad500137e5ae3</t>
+          <t>69bcddef6d730800132e6d04</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>45mohitsharma</t>
+          <t>akshay5894</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>anileducation01@gmail.com</t>
+          <t>maharashtrafamily288@gmail.com</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>9352686018</t>
+          <t>8855978736</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -2846,25 +2846,25 @@
         </is>
       </c>
       <c r="I28" s="13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>23674</v>
+        <v>269734</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>268874</v>
+        <v>269734</v>
       </c>
       <c r="L28" s="15" t="n">
-        <v>51138</v>
+        <v>269734</v>
       </c>
       <c r="M28" s="12" t="inlineStr">
         <is>
-          <t>6998149536c51700132c3f93</t>
+          <t>6a9918f052d28b0013b473cf</t>
         </is>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6998149536c51700132c3f93</t>
+          <t>https://superprofile.bio/vig/6a9918f052d28b0013b473cf</t>
         </is>
       </c>
       <c r="O28" s="17" t="inlineStr">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>6a8fb6f61559b900134d4ae8</t>
+          <t>686213a26baad500137e5ae3</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>Banknifty9888</t>
+          <t>45mohitsharma</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>studyking736@gmail.com</t>
+          <t>anileducation01@gmail.com</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>8092600241</t>
+          <t>9352686018</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
@@ -2918,25 +2918,25 @@
         </is>
       </c>
       <c r="I29" s="20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29" s="21" t="n">
-        <v>39274</v>
+        <v>23674</v>
       </c>
       <c r="K29" s="21" t="n">
-        <v>258778</v>
+        <v>268874</v>
       </c>
       <c r="L29" s="22" t="n">
-        <v>57276</v>
+        <v>51138</v>
       </c>
       <c r="M29" s="19" t="inlineStr">
         <is>
-          <t>697aeb756fa9030013e878ea</t>
+          <t>6998149536c51700132c3f93</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697aeb756fa9030013e878ea</t>
+          <t>https://superprofile.bio/vig/6998149536c51700132c3f93</t>
         </is>
       </c>
       <c r="O29" s="24" t="inlineStr">
@@ -2956,22 +2956,22 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>64cbcd3b93d7e4001d11fdb6</t>
+          <t>6a8fb6f61559b900134d4ae8</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>signaledge</t>
+          <t>Banknifty9888</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>signaledge161@gmail.com</t>
+          <t>studyking736@gmail.com</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>7022381539</t>
+          <t>8092600241</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -2993,22 +2993,22 @@
         <v>9</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>7366</v>
+        <v>39274</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>258182</v>
+        <v>258778</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>50852</v>
+        <v>57276</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
-          <t>6a6b4ce6f6cdba0013dadec2</t>
+          <t>697aeb756fa9030013e878ea</t>
         </is>
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6b4ce6f6cdba0013dadec2</t>
+          <t>https://superprofile.bio/vig/697aeb756fa9030013e878ea</t>
         </is>
       </c>
       <c r="O30" s="17" t="inlineStr">
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>6799ba66ece5b90013e713fc</t>
+          <t>64cbcd3b93d7e4001d11fdb6</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>stockshubofficial</t>
+          <t>signaledge</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>stockshubofficial@gmail.com</t>
+          <t>signaledge161@gmail.com</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>9974731343</t>
+          <t>7022381539</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
@@ -3065,22 +3065,22 @@
         <v>9</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>71948</v>
+        <v>7366</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>250292</v>
+        <v>258182</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>114194</v>
+        <v>50852</v>
       </c>
       <c r="M31" s="19" t="inlineStr">
         <is>
-          <t>699be7236bc2f10013b21da1</t>
+          <t>6a6b4ce6f6cdba0013dadec2</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/699be7236bc2f10013b21da1</t>
+          <t>https://superprofile.bio/vig/6a6b4ce6f6cdba0013dadec2</t>
         </is>
       </c>
       <c r="O31" s="24" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>62b9a085bfba080a0feea73d</t>
+          <t>6799ba66ece5b90013e713fc</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>cavivekjoshi</t>
+          <t>stockshubofficial</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>vivekjoshiweb@gmail.com</t>
+          <t>stockshubofficial@gmail.com</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>8655698288</t>
+          <t>9974731343</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -3134,25 +3134,25 @@
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>22811</v>
+        <v>71948</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>238280</v>
+        <v>250292</v>
       </c>
       <c r="L32" s="15" t="n">
-        <v>54825</v>
+        <v>114194</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
-          <t>62c825b50e230419663e4fe0</t>
+          <t>699be7236bc2f10013b21da1</t>
         </is>
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62c825b50e230419663e4fe0</t>
+          <t>https://superprofile.bio/vig/699be7236bc2f10013b21da1</t>
         </is>
       </c>
       <c r="O32" s="17" t="inlineStr">
@@ -3172,22 +3172,22 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>67038e07eda36800133f37cc</t>
+          <t>62b9a085bfba080a0feea73d</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>topstocker24</t>
+          <t>cavivekjoshi</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>k4vaibhav17@gmail.com</t>
+          <t>vivekjoshiweb@gmail.com</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>7060035920</t>
+          <t>8655698288</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -3197,34 +3197,34 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I33" s="20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J33" s="21" t="n">
-        <v>77262</v>
+        <v>22811</v>
       </c>
       <c r="K33" s="21" t="n">
-        <v>235933</v>
+        <v>238280</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>78026</v>
+        <v>54825</v>
       </c>
       <c r="M33" s="19" t="inlineStr">
         <is>
-          <t>670391811232fa0013fdf36b</t>
+          <t>62c825b50e230419663e4fe0</t>
         </is>
       </c>
       <c r="N33" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/670391811232fa0013fdf36b</t>
+          <t>https://superprofile.bio/vig/62c825b50e230419663e4fe0</t>
         </is>
       </c>
       <c r="O33" s="24" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 05:39:29 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 06:28:01 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4498403</v>
+        <v>4472800</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>47835</v>
+        <v>11116</v>
       </c>
       <c r="K22" s="14" t="n">
         <v>283768</v>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 06:28:01 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 06:58:45 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 06:58:45 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 08:31:20 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 08:31:20 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 10:39:05 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 10:39:05 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 12:38:46 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 12:38:46 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 14:14:50 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 14:14:50 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 15:56:40 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-08 15:56:40 | Daily Audits Logged: 10</t>
+          <t>Generated On: 2026-09-08 17:51:43 | Daily Audits Logged: 10</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 02:35:41 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 05:45:28 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 05:45:28 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 06:34:28 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 06:34:28 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 07:08:07 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 07:08:07 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 08:33:51 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 08:33:51 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 10:49:06 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 10:49:06 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 12:45:22 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 12:45:22 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 14:15:09 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 14:15:09 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 15:52:28 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 15:52:28 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 17:44:25 | Daily Audits Logged: 11</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-09 17:44:25 | Daily Audits Logged: 11</t>
+          <t>Generated On: 2026-09-09 18:53:13 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹43,077,536.00</t>
+          <t>₹43,079,891.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -830,6 +830,24 @@
         <v>4574958</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Logged &amp; Deduplicated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Logged &amp; Deduplicated</t>
         </is>
@@ -29326,22 +29344,22 @@
       </c>
       <c r="B396" s="13" t="inlineStr">
         <is>
-          <t>68945e14ec57170013be06f1</t>
+          <t>62115e4a6bd738258707c0e9</t>
         </is>
       </c>
       <c r="C396" s="13" t="inlineStr">
         <is>
-          <t>manifestwithsruthi</t>
+          <t>aditya</t>
         </is>
       </c>
       <c r="D396" s="12" t="inlineStr">
         <is>
-          <t>sruthimuthu12@gmail.com</t>
+          <t>imavschoudhary@gmail.com</t>
         </is>
       </c>
       <c r="E396" s="12" t="inlineStr">
         <is>
-          <t>7305697145</t>
+          <t>9717115749</t>
         </is>
       </c>
       <c r="F396" s="12" t="inlineStr">
@@ -29351,34 +29369,34 @@
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H396" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I396" s="13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J396" s="14" t="n">
-        <v>19292</v>
+        <v>2355</v>
       </c>
       <c r="K396" s="14" t="n">
-        <v>19292</v>
+        <v>19365</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>19292</v>
+        <v>4379</v>
       </c>
       <c r="M396" s="12" t="inlineStr">
         <is>
-          <t>6a291defb236c60013e452c2</t>
+          <t>6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="N396" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a291defb236c60013e452c2</t>
+          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="O396" s="17" t="inlineStr">
@@ -29398,22 +29416,22 @@
       </c>
       <c r="B397" s="20" t="inlineStr">
         <is>
-          <t>693319d6f3052a00135857d9</t>
+          <t>68945e14ec57170013be06f1</t>
         </is>
       </c>
       <c r="C397" s="20" t="inlineStr">
         <is>
-          <t>gurusharemarket</t>
+          <t>manifestwithsruthi</t>
         </is>
       </c>
       <c r="D397" s="19" t="inlineStr">
         <is>
-          <t>gurusharemarket01@gmail.com</t>
+          <t>sruthimuthu12@gmail.com</t>
         </is>
       </c>
       <c r="E397" s="19" t="inlineStr">
         <is>
-          <t>9911995213</t>
+          <t>7305697145</t>
         </is>
       </c>
       <c r="F397" s="19" t="inlineStr">
@@ -29423,34 +29441,34 @@
       </c>
       <c r="G397" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H397" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I397" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J397" s="21" t="n">
-        <v>6351</v>
+        <v>19292</v>
       </c>
       <c r="K397" s="21" t="n">
-        <v>19053</v>
+        <v>19292</v>
       </c>
       <c r="L397" s="22" t="n">
-        <v>12702</v>
+        <v>19292</v>
       </c>
       <c r="M397" s="19" t="inlineStr">
         <is>
-          <t>69331ed7c65ec80013b53645</t>
+          <t>6a291defb236c60013e452c2</t>
         </is>
       </c>
       <c r="N397" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
+          <t>https://superprofile.bio/vig/6a291defb236c60013e452c2</t>
         </is>
       </c>
       <c r="O397" s="24" t="inlineStr">
@@ -29470,22 +29488,22 @@
       </c>
       <c r="B398" s="13" t="inlineStr">
         <is>
-          <t>66c4934ed4a9f8001370ea72</t>
+          <t>693319d6f3052a00135857d9</t>
         </is>
       </c>
       <c r="C398" s="13" t="inlineStr">
         <is>
-          <t>radhetradingofficial</t>
+          <t>gurusharemarket</t>
         </is>
       </c>
       <c r="D398" s="12" t="inlineStr">
         <is>
-          <t>educationmatlabradhetrading@gmail.com</t>
+          <t>gurusharemarket01@gmail.com</t>
         </is>
       </c>
       <c r="E398" s="12" t="inlineStr">
         <is>
-          <t>9138133306</t>
+          <t>9911995213</t>
         </is>
       </c>
       <c r="F398" s="12" t="inlineStr">
@@ -29495,34 +29513,34 @@
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H398" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I398" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J398" s="14" t="n">
-        <v>4750</v>
+        <v>6351</v>
       </c>
       <c r="K398" s="14" t="n">
-        <v>19047</v>
+        <v>19053</v>
       </c>
       <c r="L398" s="15" t="n">
-        <v>7172</v>
+        <v>12702</v>
       </c>
       <c r="M398" s="12" t="inlineStr">
         <is>
-          <t>67e292aee26d1e0013dec776</t>
+          <t>69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="N398" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67e292aee26d1e0013dec776</t>
+          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="O398" s="17" t="inlineStr">
@@ -29542,22 +29560,22 @@
       </c>
       <c r="B399" s="20" t="inlineStr">
         <is>
-          <t>64e5ae617f68ef001ea74131</t>
+          <t>66c4934ed4a9f8001370ea72</t>
         </is>
       </c>
       <c r="C399" s="20" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>radhetradingofficial</t>
         </is>
       </c>
       <c r="D399" s="19" t="inlineStr">
         <is>
-          <t>dalalmihir81@gmail.com</t>
+          <t>educationmatlabradhetrading@gmail.com</t>
         </is>
       </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
-          <t>9879558198</t>
+          <t>9138133306</t>
         </is>
       </c>
       <c r="F399" s="19" t="inlineStr">
@@ -29567,34 +29585,34 @@
       </c>
       <c r="G399" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H399" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I399" s="20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J399" s="21" t="n">
-        <v>1001</v>
+        <v>4750</v>
       </c>
       <c r="K399" s="21" t="n">
-        <v>19005</v>
+        <v>19047</v>
       </c>
       <c r="L399" s="22" t="n">
-        <v>5004</v>
+        <v>7172</v>
       </c>
       <c r="M399" s="19" t="inlineStr">
         <is>
-          <t>66c871cfc6acc2001368e5a3</t>
+          <t>67e292aee26d1e0013dec776</t>
         </is>
       </c>
       <c r="N399" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
+          <t>https://superprofile.bio/vig/67e292aee26d1e0013dec776</t>
         </is>
       </c>
       <c r="O399" s="24" t="inlineStr">
@@ -29614,22 +29632,22 @@
       </c>
       <c r="B400" s="13" t="inlineStr">
         <is>
-          <t>693ff14b339ef300132c00dd</t>
+          <t>64e5ae617f68ef001ea74131</t>
         </is>
       </c>
       <c r="C400" s="13" t="inlineStr">
         <is>
-          <t>themanifestationqueen</t>
+          <t>dalalmihir81</t>
         </is>
       </c>
       <c r="D400" s="12" t="inlineStr">
         <is>
-          <t>mannuthapa2381@gmail.com</t>
+          <t>dalalmihir81@gmail.com</t>
         </is>
       </c>
       <c r="E400" s="12" t="inlineStr">
         <is>
-          <t>9068457199</t>
+          <t>9879558198</t>
         </is>
       </c>
       <c r="F400" s="12" t="inlineStr">
@@ -29639,34 +29657,34 @@
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H400" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I400" s="13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J400" s="14" t="n">
-        <v>18820</v>
+        <v>1001</v>
       </c>
       <c r="K400" s="14" t="n">
-        <v>18820</v>
+        <v>19005</v>
       </c>
       <c r="L400" s="15" t="n">
-        <v>18820</v>
+        <v>5004</v>
       </c>
       <c r="M400" s="12" t="inlineStr">
         <is>
-          <t>69fda9af23cc6f00135df515</t>
+          <t>66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="N400" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69fda9af23cc6f00135df515</t>
+          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="O400" s="17" t="inlineStr">
@@ -29686,22 +29704,22 @@
       </c>
       <c r="B401" s="20" t="inlineStr">
         <is>
-          <t>6a523589f2a63c0013c8594d</t>
+          <t>693ff14b339ef300132c00dd</t>
         </is>
       </c>
       <c r="C401" s="20" t="inlineStr">
         <is>
-          <t>NITIN9239</t>
+          <t>themanifestationqueen</t>
         </is>
       </c>
       <c r="D401" s="19" t="inlineStr">
         <is>
-          <t>tradingspell@gmail.com</t>
+          <t>mannuthapa2381@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="19" t="inlineStr">
         <is>
-          <t>6395657006</t>
+          <t>9068457199</t>
         </is>
       </c>
       <c r="F401" s="19" t="inlineStr">
@@ -29711,34 +29729,34 @@
       </c>
       <c r="G401" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H401" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I401" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J401" s="21" t="n">
-        <v>4763</v>
+        <v>18820</v>
       </c>
       <c r="K401" s="21" t="n">
-        <v>18671</v>
+        <v>18820</v>
       </c>
       <c r="L401" s="22" t="n">
-        <v>6954</v>
+        <v>18820</v>
       </c>
       <c r="M401" s="19" t="inlineStr">
         <is>
-          <t>6a69b38a2519b6001380e5e0</t>
+          <t>69fda9af23cc6f00135df515</t>
         </is>
       </c>
       <c r="N401" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a69b38a2519b6001380e5e0</t>
+          <t>https://superprofile.bio/vig/69fda9af23cc6f00135df515</t>
         </is>
       </c>
       <c r="O401" s="24" t="inlineStr">
@@ -29758,22 +29776,22 @@
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>6986dbd1350e1a0014cdbba8</t>
+          <t>6a523589f2a63c0013c8594d</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>NITIN9239</t>
         </is>
       </c>
       <c r="D402" s="12" t="inlineStr">
         <is>
-          <t>kumarshubham857208@gmail.com</t>
+          <t>tradingspell@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr">
         <is>
-          <t>9253166725</t>
+          <t>6395657006</t>
         </is>
       </c>
       <c r="F402" s="12" t="inlineStr">
@@ -29783,34 +29801,34 @@
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I402" s="13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J402" s="14" t="n">
-        <v>1411</v>
+        <v>4763</v>
       </c>
       <c r="K402" s="14" t="n">
-        <v>18340</v>
+        <v>18671</v>
       </c>
       <c r="L402" s="15" t="n">
-        <v>2821</v>
+        <v>6954</v>
       </c>
       <c r="M402" s="12" t="inlineStr">
         <is>
-          <t>69a90448ce8bdc00125c31a5</t>
+          <t>6a69b38a2519b6001380e5e0</t>
         </is>
       </c>
       <c r="N402" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
+          <t>https://superprofile.bio/vig/6a69b38a2519b6001380e5e0</t>
         </is>
       </c>
       <c r="O402" s="17" t="inlineStr">
@@ -29830,22 +29848,22 @@
       </c>
       <c r="B403" s="20" t="inlineStr">
         <is>
-          <t>65951378bbebcf001d4651a6</t>
+          <t>6986dbd1350e1a0014cdbba8</t>
         </is>
       </c>
       <c r="C403" s="20" t="inlineStr">
         <is>
-          <t>nonstops</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="D403" s="19" t="inlineStr">
         <is>
-          <t>devanshsirvaiya@gmail.com</t>
+          <t>kumarshubham857208@gmail.com</t>
         </is>
       </c>
       <c r="E403" s="19" t="inlineStr">
         <is>
-          <t>9303185128</t>
+          <t>9253166725</t>
         </is>
       </c>
       <c r="F403" s="19" t="inlineStr">
@@ -29860,29 +29878,29 @@
       </c>
       <c r="H403" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I403" s="20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J403" s="21" t="n">
-        <v>5787</v>
+        <v>1411</v>
       </c>
       <c r="K403" s="21" t="n">
-        <v>18325</v>
+        <v>18340</v>
       </c>
       <c r="L403" s="22" t="n">
-        <v>6269</v>
+        <v>2821</v>
       </c>
       <c r="M403" s="19" t="inlineStr">
         <is>
-          <t>672f09c2cb504b00130e1071</t>
+          <t>69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="N403" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/672f09c2cb504b00130e1071</t>
+          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="O403" s="24" t="inlineStr">
@@ -29902,22 +29920,22 @@
       </c>
       <c r="B404" s="13" t="inlineStr">
         <is>
-          <t>6a0739870374d70013f4a6da</t>
+          <t>65951378bbebcf001d4651a6</t>
         </is>
       </c>
       <c r="C404" s="13" t="inlineStr">
         <is>
-          <t>algoxofficial</t>
+          <t>nonstops</t>
         </is>
       </c>
       <c r="D404" s="12" t="inlineStr">
         <is>
-          <t>sayhelloplux@gmail.com</t>
+          <t>devanshsirvaiya@gmail.com</t>
         </is>
       </c>
       <c r="E404" s="12" t="inlineStr">
         <is>
-          <t>8529451480</t>
+          <t>9303185128</t>
         </is>
       </c>
       <c r="F404" s="12" t="inlineStr">
@@ -29927,34 +29945,34 @@
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H404" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I404" s="13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>3754</v>
+        <v>5787</v>
       </c>
       <c r="K404" s="14" t="n">
-        <v>18286</v>
+        <v>18325</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>6554</v>
+        <v>6269</v>
       </c>
       <c r="M404" s="12" t="inlineStr">
         <is>
-          <t>6a40b76b8552d90013a86043</t>
+          <t>672f09c2cb504b00130e1071</t>
         </is>
       </c>
       <c r="N404" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
+          <t>https://superprofile.bio/vig/672f09c2cb504b00130e1071</t>
         </is>
       </c>
       <c r="O404" s="17" t="inlineStr">
@@ -29974,22 +29992,22 @@
       </c>
       <c r="B405" s="20" t="inlineStr">
         <is>
-          <t>676cf61fae833e001322e4d4</t>
+          <t>6a0739870374d70013f4a6da</t>
         </is>
       </c>
       <c r="C405" s="20" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>algoxofficial</t>
         </is>
       </c>
       <c r="D405" s="19" t="inlineStr">
         <is>
-          <t>rahulstock11@gmail.com</t>
+          <t>sayhelloplux@gmail.com</t>
         </is>
       </c>
       <c r="E405" s="19" t="inlineStr">
         <is>
-          <t>8305763595</t>
+          <t>8529451480</t>
         </is>
       </c>
       <c r="F405" s="19" t="inlineStr">
@@ -29999,34 +30017,34 @@
       </c>
       <c r="G405" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H405" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I405" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J405" s="21" t="n">
-        <v>4374</v>
+        <v>3754</v>
       </c>
       <c r="K405" s="21" t="n">
-        <v>18275</v>
+        <v>18286</v>
       </c>
       <c r="L405" s="22" t="n">
-        <v>4374</v>
+        <v>6554</v>
       </c>
       <c r="M405" s="19" t="inlineStr">
         <is>
-          <t>676d0ccf8e79b600130eb896</t>
+          <t>6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="N405" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
+          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="O405" s="24" t="inlineStr">
@@ -30046,22 +30064,22 @@
       </c>
       <c r="B406" s="13" t="inlineStr">
         <is>
-          <t>6788e1865e03e800132c5ed6</t>
+          <t>676cf61fae833e001322e4d4</t>
         </is>
       </c>
       <c r="C406" s="13" t="inlineStr">
         <is>
-          <t>tmestockdealbanknifty</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="D406" s="12" t="inlineStr">
         <is>
-          <t>kubavatbiz@gmail.com</t>
+          <t>rahulstock11@gmail.com</t>
         </is>
       </c>
       <c r="E406" s="12" t="inlineStr">
         <is>
-          <t>9824960130</t>
+          <t>8305763595</t>
         </is>
       </c>
       <c r="F406" s="12" t="inlineStr">
@@ -30071,34 +30089,34 @@
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H406" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I406" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J406" s="14" t="n">
-        <v>2636</v>
+        <v>4374</v>
       </c>
       <c r="K406" s="14" t="n">
-        <v>18253</v>
+        <v>18275</v>
       </c>
       <c r="L406" s="15" t="n">
-        <v>6833</v>
+        <v>4374</v>
       </c>
       <c r="M406" s="12" t="inlineStr">
         <is>
-          <t>6789ff3d8329cd0015c842bc</t>
+          <t>676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="N406" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6789ff3d8329cd0015c842bc</t>
+          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="O406" s="17" t="inlineStr">
@@ -30118,22 +30136,22 @@
       </c>
       <c r="B407" s="20" t="inlineStr">
         <is>
-          <t>65fd7074e04d92001271989a</t>
+          <t>6788e1865e03e800132c5ed6</t>
         </is>
       </c>
       <c r="C407" s="20" t="inlineStr">
         <is>
-          <t>indexhub</t>
+          <t>tmestockdealbanknifty</t>
         </is>
       </c>
       <c r="D407" s="19" t="inlineStr">
         <is>
-          <t>kajalbasodha1998@gmail.com</t>
+          <t>kubavatbiz@gmail.com</t>
         </is>
       </c>
       <c r="E407" s="19" t="inlineStr">
         <is>
-          <t>9913545157</t>
+          <t>9824960130</t>
         </is>
       </c>
       <c r="F407" s="19" t="inlineStr">
@@ -30143,34 +30161,34 @@
       </c>
       <c r="G407" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H407" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I407" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J407" s="21" t="n">
-        <v>2928</v>
+        <v>2636</v>
       </c>
       <c r="K407" s="21" t="n">
-        <v>18251</v>
+        <v>18253</v>
       </c>
       <c r="L407" s="22" t="n">
-        <v>4880</v>
+        <v>6833</v>
       </c>
       <c r="M407" s="19" t="inlineStr">
         <is>
-          <t>647830094112cd001f144fd5</t>
+          <t>6789ff3d8329cd0015c842bc</t>
         </is>
       </c>
       <c r="N407" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647830094112cd001f144fd5</t>
+          <t>https://superprofile.bio/vig/6789ff3d8329cd0015c842bc</t>
         </is>
       </c>
       <c r="O407" s="24" t="inlineStr">
@@ -30190,22 +30208,22 @@
       </c>
       <c r="B408" s="13" t="inlineStr">
         <is>
-          <t>677d0628221dc40013a45c7c</t>
+          <t>65fd7074e04d92001271989a</t>
         </is>
       </c>
       <c r="C408" s="13" t="inlineStr">
         <is>
-          <t>httpstmesmarttraders179</t>
+          <t>indexhub</t>
         </is>
       </c>
       <c r="D408" s="12" t="inlineStr">
         <is>
-          <t>gh1785739@gmail.com</t>
+          <t>kajalbasodha1998@gmail.com</t>
         </is>
       </c>
       <c r="E408" s="12" t="inlineStr">
         <is>
-          <t>9839748557</t>
+          <t>9913545157</t>
         </is>
       </c>
       <c r="F408" s="12" t="inlineStr">
@@ -30215,34 +30233,34 @@
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H408" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I408" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J408" s="14" t="n">
-        <v>1437</v>
+        <v>2928</v>
       </c>
       <c r="K408" s="14" t="n">
-        <v>18249</v>
+        <v>18251</v>
       </c>
       <c r="L408" s="15" t="n">
-        <v>3736</v>
+        <v>4880</v>
       </c>
       <c r="M408" s="12" t="inlineStr">
         <is>
-          <t>68807b5d6aec320013f7f836</t>
+          <t>647830094112cd001f144fd5</t>
         </is>
       </c>
       <c r="N408" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68807b5d6aec320013f7f836</t>
+          <t>https://superprofile.bio/vig/647830094112cd001f144fd5</t>
         </is>
       </c>
       <c r="O408" s="17" t="inlineStr">
@@ -30262,22 +30280,22 @@
       </c>
       <c r="B409" s="20" t="inlineStr">
         <is>
-          <t>663dd24d61f04800142f8ce8</t>
+          <t>677d0628221dc40013a45c7c</t>
         </is>
       </c>
       <c r="C409" s="20" t="inlineStr">
         <is>
-          <t>ikhushii-rajput</t>
+          <t>httpstmesmarttraders179</t>
         </is>
       </c>
       <c r="D409" s="19" t="inlineStr">
         <is>
-          <t>theamelia5705@gmail.com</t>
+          <t>gh1785739@gmail.com</t>
         </is>
       </c>
       <c r="E409" s="19" t="inlineStr">
         <is>
-          <t>9266867307</t>
+          <t>9839748557</t>
         </is>
       </c>
       <c r="F409" s="19" t="inlineStr">
@@ -30292,29 +30310,29 @@
       </c>
       <c r="H409" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I409" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J409" s="21" t="n">
-        <v>1222</v>
+        <v>1437</v>
       </c>
       <c r="K409" s="21" t="n">
-        <v>18127</v>
+        <v>18249</v>
       </c>
       <c r="L409" s="22" t="n">
-        <v>5597</v>
+        <v>3736</v>
       </c>
       <c r="M409" s="19" t="inlineStr">
         <is>
-          <t>69ebc141f28b8500138e14f8</t>
+          <t>68807b5d6aec320013f7f836</t>
         </is>
       </c>
       <c r="N409" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ebc141f28b8500138e14f8</t>
+          <t>https://superprofile.bio/vig/68807b5d6aec320013f7f836</t>
         </is>
       </c>
       <c r="O409" s="24" t="inlineStr">
@@ -30334,22 +30352,22 @@
       </c>
       <c r="B410" s="13" t="inlineStr">
         <is>
-          <t>6a0493243a48f800134b7d4b</t>
+          <t>663dd24d61f04800142f8ce8</t>
         </is>
       </c>
       <c r="C410" s="13" t="inlineStr">
         <is>
-          <t>meenarahulzz</t>
+          <t>ikhushii-rajput</t>
         </is>
       </c>
       <c r="D410" s="12" t="inlineStr">
         <is>
-          <t>tmind4460@gmail.com</t>
+          <t>theamelia5705@gmail.com</t>
         </is>
       </c>
       <c r="E410" s="12" t="inlineStr">
         <is>
-          <t>9672238460</t>
+          <t>9266867307</t>
         </is>
       </c>
       <c r="F410" s="12" t="inlineStr">
@@ -30359,34 +30377,34 @@
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H410" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I410" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J410" s="14" t="n">
-        <v>1619</v>
+        <v>1222</v>
       </c>
       <c r="K410" s="14" t="n">
-        <v>17905</v>
+        <v>18127</v>
       </c>
       <c r="L410" s="15" t="n">
-        <v>7428</v>
+        <v>5597</v>
       </c>
       <c r="M410" s="12" t="inlineStr">
         <is>
-          <t>68d0ebe0adc9cb00133eccaf</t>
+          <t>69ebc141f28b8500138e14f8</t>
         </is>
       </c>
       <c r="N410" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
+          <t>https://superprofile.bio/vig/69ebc141f28b8500138e14f8</t>
         </is>
       </c>
       <c r="O410" s="17" t="inlineStr">
@@ -30406,22 +30424,22 @@
       </c>
       <c r="B411" s="20" t="inlineStr">
         <is>
-          <t>66926a105d82bc0013c1229c</t>
+          <t>6a0493243a48f800134b7d4b</t>
         </is>
       </c>
       <c r="C411" s="20" t="inlineStr">
         <is>
-          <t>aactiveetraders</t>
+          <t>meenarahulzz</t>
         </is>
       </c>
       <c r="D411" s="19" t="inlineStr">
         <is>
-          <t>rshinde7057@gmail.com</t>
+          <t>tmind4460@gmail.com</t>
         </is>
       </c>
       <c r="E411" s="19" t="inlineStr">
         <is>
-          <t>8104421373</t>
+          <t>9672238460</t>
         </is>
       </c>
       <c r="F411" s="19" t="inlineStr">
@@ -30431,34 +30449,34 @@
       </c>
       <c r="G411" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H411" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I411" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J411" s="21" t="n">
-        <v>2411</v>
+        <v>1619</v>
       </c>
       <c r="K411" s="21" t="n">
-        <v>17800</v>
+        <v>17905</v>
       </c>
       <c r="L411" s="22" t="n">
-        <v>3856</v>
+        <v>7428</v>
       </c>
       <c r="M411" s="19" t="inlineStr">
         <is>
-          <t>67cab3644e87bf0013f15f65</t>
+          <t>68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="N411" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
+          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="O411" s="24" t="inlineStr">
@@ -30478,22 +30496,22 @@
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>67a6163b2add040013b0ce0f</t>
+          <t>66926a105d82bc0013c1229c</t>
         </is>
       </c>
       <c r="C412" s="13" t="inlineStr">
         <is>
-          <t>aadavan</t>
+          <t>aactiveetraders</t>
         </is>
       </c>
       <c r="D412" s="12" t="inlineStr">
         <is>
-          <t>jishanmaalik@gmail.com</t>
+          <t>rshinde7057@gmail.com</t>
         </is>
       </c>
       <c r="E412" s="12" t="inlineStr">
         <is>
-          <t>8088654150</t>
+          <t>8104421373</t>
         </is>
       </c>
       <c r="F412" s="12" t="inlineStr">
@@ -30503,7 +30521,7 @@
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H412" s="12" t="inlineStr">
@@ -30512,25 +30530,25 @@
         </is>
       </c>
       <c r="I412" s="13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J412" s="14" t="n">
-        <v>3880</v>
+        <v>2411</v>
       </c>
       <c r="K412" s="14" t="n">
-        <v>17423</v>
+        <v>17800</v>
       </c>
       <c r="L412" s="15" t="n">
-        <v>6308</v>
+        <v>3856</v>
       </c>
       <c r="M412" s="12" t="inlineStr">
         <is>
-          <t>67a8c6045ee5520012250762</t>
+          <t>67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="N412" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
+          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="O412" s="17" t="inlineStr">
@@ -30550,22 +30568,22 @@
       </c>
       <c r="B413" s="20" t="inlineStr">
         <is>
-          <t>62115e4a6bd738258707c0e9</t>
+          <t>67a6163b2add040013b0ce0f</t>
         </is>
       </c>
       <c r="C413" s="20" t="inlineStr">
         <is>
-          <t>aditya</t>
+          <t>aadavan</t>
         </is>
       </c>
       <c r="D413" s="19" t="inlineStr">
         <is>
-          <t>imavschoudhary@gmail.com</t>
+          <t>jishanmaalik@gmail.com</t>
         </is>
       </c>
       <c r="E413" s="19" t="inlineStr">
         <is>
-          <t>9717115749</t>
+          <t>8088654150</t>
         </is>
       </c>
       <c r="F413" s="19" t="inlineStr">
@@ -30575,7 +30593,7 @@
       </c>
       <c r="G413" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H413" s="19" t="inlineStr">
@@ -30584,25 +30602,25 @@
         </is>
       </c>
       <c r="I413" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J413" s="21" t="n">
-        <v>1752</v>
+        <v>3880</v>
       </c>
       <c r="K413" s="21" t="n">
-        <v>17010</v>
+        <v>17423</v>
       </c>
       <c r="L413" s="22" t="n">
-        <v>4379</v>
+        <v>6308</v>
       </c>
       <c r="M413" s="19" t="inlineStr">
         <is>
-          <t>6511690d55ae1b0058703c86</t>
+          <t>67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="N413" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
+          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="O413" s="24" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 02:34:41 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 05:39:35 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 05:39:35 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 06:34:03 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹47,488,012.00</t>
+          <t>₹47,496,375.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>4412831</v>
+        <v>4417779</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -30712,22 +30712,22 @@
       </c>
       <c r="B415" s="20" t="inlineStr">
         <is>
-          <t>693319d6f3052a00135857d9</t>
+          <t>6a9c25a3213bce0014ff2b98</t>
         </is>
       </c>
       <c r="C415" s="20" t="inlineStr">
         <is>
-          <t>gurusharemarket</t>
+          <t>priyasharma71284</t>
         </is>
       </c>
       <c r="D415" s="19" t="inlineStr">
         <is>
-          <t>gurusharemarket01@gmail.com</t>
+          <t>zerotohero941376@gmail.com</t>
         </is>
       </c>
       <c r="E415" s="19" t="inlineStr">
         <is>
-          <t>9911995213</t>
+          <t>9351444938</t>
         </is>
       </c>
       <c r="F415" s="19" t="inlineStr">
@@ -30742,29 +30742,29 @@
       </c>
       <c r="H415" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I415" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J415" s="21" t="n">
-        <v>6351</v>
+        <v>2474</v>
       </c>
       <c r="K415" s="21" t="n">
-        <v>19053</v>
+        <v>19200</v>
       </c>
       <c r="L415" s="22" t="n">
-        <v>12702</v>
+        <v>8363</v>
       </c>
       <c r="M415" s="19" t="inlineStr">
         <is>
-          <t>69331ed7c65ec80013b53645</t>
+          <t>6a9c330b213bce001402122a</t>
         </is>
       </c>
       <c r="N415" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
+          <t>https://superprofile.bio/vig/6a9c330b213bce001402122a</t>
         </is>
       </c>
       <c r="O415" s="24" t="inlineStr">
@@ -30784,22 +30784,22 @@
       </c>
       <c r="B416" s="13" t="inlineStr">
         <is>
-          <t>66c4934ed4a9f8001370ea72</t>
+          <t>693319d6f3052a00135857d9</t>
         </is>
       </c>
       <c r="C416" s="13" t="inlineStr">
         <is>
-          <t>radhetradingofficial</t>
+          <t>gurusharemarket</t>
         </is>
       </c>
       <c r="D416" s="12" t="inlineStr">
         <is>
-          <t>educationmatlabradhetrading@gmail.com</t>
+          <t>gurusharemarket01@gmail.com</t>
         </is>
       </c>
       <c r="E416" s="12" t="inlineStr">
         <is>
-          <t>9138133306</t>
+          <t>9911995213</t>
         </is>
       </c>
       <c r="F416" s="12" t="inlineStr">
@@ -30809,34 +30809,34 @@
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H416" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I416" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J416" s="14" t="n">
-        <v>4750</v>
+        <v>6351</v>
       </c>
       <c r="K416" s="14" t="n">
-        <v>19047</v>
+        <v>19053</v>
       </c>
       <c r="L416" s="15" t="n">
-        <v>7172</v>
+        <v>12702</v>
       </c>
       <c r="M416" s="12" t="inlineStr">
         <is>
-          <t>67e292aee26d1e0013dec776</t>
+          <t>69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="N416" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67e292aee26d1e0013dec776</t>
+          <t>https://superprofile.bio/vig/69331ed7c65ec80013b53645</t>
         </is>
       </c>
       <c r="O416" s="17" t="inlineStr">
@@ -30856,22 +30856,22 @@
       </c>
       <c r="B417" s="20" t="inlineStr">
         <is>
-          <t>64e5ae617f68ef001ea74131</t>
+          <t>66c4934ed4a9f8001370ea72</t>
         </is>
       </c>
       <c r="C417" s="20" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>radhetradingofficial</t>
         </is>
       </c>
       <c r="D417" s="19" t="inlineStr">
         <is>
-          <t>dalalmihir81@gmail.com</t>
+          <t>educationmatlabradhetrading@gmail.com</t>
         </is>
       </c>
       <c r="E417" s="19" t="inlineStr">
         <is>
-          <t>9879558198</t>
+          <t>9138133306</t>
         </is>
       </c>
       <c r="F417" s="19" t="inlineStr">
@@ -30881,34 +30881,34 @@
       </c>
       <c r="G417" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H417" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I417" s="20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J417" s="21" t="n">
-        <v>1001</v>
+        <v>4750</v>
       </c>
       <c r="K417" s="21" t="n">
-        <v>19005</v>
+        <v>19047</v>
       </c>
       <c r="L417" s="22" t="n">
-        <v>5004</v>
+        <v>7172</v>
       </c>
       <c r="M417" s="19" t="inlineStr">
         <is>
-          <t>66c871cfc6acc2001368e5a3</t>
+          <t>67e292aee26d1e0013dec776</t>
         </is>
       </c>
       <c r="N417" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
+          <t>https://superprofile.bio/vig/67e292aee26d1e0013dec776</t>
         </is>
       </c>
       <c r="O417" s="24" t="inlineStr">
@@ -30928,22 +30928,22 @@
       </c>
       <c r="B418" s="13" t="inlineStr">
         <is>
-          <t>693ff14b339ef300132c00dd</t>
+          <t>64e5ae617f68ef001ea74131</t>
         </is>
       </c>
       <c r="C418" s="13" t="inlineStr">
         <is>
-          <t>themanifestationqueen</t>
+          <t>dalalmihir81</t>
         </is>
       </c>
       <c r="D418" s="12" t="inlineStr">
         <is>
-          <t>mannuthapa2381@gmail.com</t>
+          <t>dalalmihir81@gmail.com</t>
         </is>
       </c>
       <c r="E418" s="12" t="inlineStr">
         <is>
-          <t>9068457199</t>
+          <t>9879558198</t>
         </is>
       </c>
       <c r="F418" s="12" t="inlineStr">
@@ -30953,34 +30953,34 @@
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H418" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I418" s="13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J418" s="14" t="n">
-        <v>18820</v>
+        <v>1001</v>
       </c>
       <c r="K418" s="14" t="n">
-        <v>18820</v>
+        <v>19005</v>
       </c>
       <c r="L418" s="15" t="n">
-        <v>18820</v>
+        <v>5004</v>
       </c>
       <c r="M418" s="12" t="inlineStr">
         <is>
-          <t>69fda9af23cc6f00135df515</t>
+          <t>66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="N418" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69fda9af23cc6f00135df515</t>
+          <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
       <c r="O418" s="17" t="inlineStr">
@@ -31000,22 +31000,22 @@
       </c>
       <c r="B419" s="20" t="inlineStr">
         <is>
-          <t>65f92f6ac022090013a05e2f</t>
+          <t>693ff14b339ef300132c00dd</t>
         </is>
       </c>
       <c r="C419" s="20" t="inlineStr">
         <is>
-          <t>brokerntreder09</t>
+          <t>themanifestationqueen</t>
         </is>
       </c>
       <c r="D419" s="19" t="inlineStr">
         <is>
-          <t>moaakilsandhi786@gmail.com</t>
+          <t>mannuthapa2381@gmail.com</t>
         </is>
       </c>
       <c r="E419" s="19" t="inlineStr">
         <is>
-          <t>9316693141</t>
+          <t>9068457199</t>
         </is>
       </c>
       <c r="F419" s="19" t="inlineStr">
@@ -31030,29 +31030,29 @@
       </c>
       <c r="H419" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I419" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J419" s="21" t="n">
-        <v>3762</v>
+        <v>18820</v>
       </c>
       <c r="K419" s="21" t="n">
-        <v>18718</v>
+        <v>18820</v>
       </c>
       <c r="L419" s="22" t="n">
-        <v>8748</v>
+        <v>18820</v>
       </c>
       <c r="M419" s="19" t="inlineStr">
         <is>
-          <t>69786236017be60013a65fc2</t>
+          <t>69fda9af23cc6f00135df515</t>
         </is>
       </c>
       <c r="N419" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69786236017be60013a65fc2</t>
+          <t>https://superprofile.bio/vig/69fda9af23cc6f00135df515</t>
         </is>
       </c>
       <c r="O419" s="24" t="inlineStr">
@@ -31072,22 +31072,22 @@
       </c>
       <c r="B420" s="13" t="inlineStr">
         <is>
-          <t>674826081e9bbd0013ea67fa</t>
+          <t>65f92f6ac022090013a05e2f</t>
         </is>
       </c>
       <c r="C420" s="13" t="inlineStr">
         <is>
-          <t>zerotoheroo</t>
+          <t>brokerntreder09</t>
         </is>
       </c>
       <c r="D420" s="12" t="inlineStr">
         <is>
-          <t>anilgoswami7414@gmail.com</t>
+          <t>moaakilsandhi786@gmail.com</t>
         </is>
       </c>
       <c r="E420" s="12" t="inlineStr">
         <is>
-          <t>7414801390</t>
+          <t>9316693141</t>
         </is>
       </c>
       <c r="F420" s="12" t="inlineStr">
@@ -31097,7 +31097,7 @@
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H420" s="12" t="inlineStr">
@@ -31106,25 +31106,25 @@
         </is>
       </c>
       <c r="I420" s="13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J420" s="14" t="n">
-        <v>1746</v>
+        <v>3762</v>
       </c>
       <c r="K420" s="14" t="n">
-        <v>18699</v>
+        <v>18718</v>
       </c>
       <c r="L420" s="15" t="n">
-        <v>6962</v>
+        <v>8748</v>
       </c>
       <c r="M420" s="12" t="inlineStr">
         <is>
-          <t>67b591e63f09ef001372f8c6</t>
+          <t>69786236017be60013a65fc2</t>
         </is>
       </c>
       <c r="N420" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67b591e63f09ef001372f8c6</t>
+          <t>https://superprofile.bio/vig/69786236017be60013a65fc2</t>
         </is>
       </c>
       <c r="O420" s="17" t="inlineStr">
@@ -31144,22 +31144,22 @@
       </c>
       <c r="B421" s="20" t="inlineStr">
         <is>
-          <t>6a523589f2a63c0013c8594d</t>
+          <t>674826081e9bbd0013ea67fa</t>
         </is>
       </c>
       <c r="C421" s="20" t="inlineStr">
         <is>
-          <t>NITIN9239</t>
+          <t>zerotoheroo</t>
         </is>
       </c>
       <c r="D421" s="19" t="inlineStr">
         <is>
-          <t>tradingspell@gmail.com</t>
+          <t>anilgoswami7414@gmail.com</t>
         </is>
       </c>
       <c r="E421" s="19" t="inlineStr">
         <is>
-          <t>6395657006</t>
+          <t>7414801390</t>
         </is>
       </c>
       <c r="F421" s="19" t="inlineStr">
@@ -31174,29 +31174,29 @@
       </c>
       <c r="H421" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I421" s="20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J421" s="21" t="n">
-        <v>4763</v>
+        <v>1746</v>
       </c>
       <c r="K421" s="21" t="n">
-        <v>18671</v>
+        <v>18699</v>
       </c>
       <c r="L421" s="22" t="n">
-        <v>6954</v>
+        <v>6962</v>
       </c>
       <c r="M421" s="19" t="inlineStr">
         <is>
-          <t>6a69b38a2519b6001380e5e0</t>
+          <t>67b591e63f09ef001372f8c6</t>
         </is>
       </c>
       <c r="N421" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a69b38a2519b6001380e5e0</t>
+          <t>https://superprofile.bio/vig/67b591e63f09ef001372f8c6</t>
         </is>
       </c>
       <c r="O421" s="24" t="inlineStr">
@@ -31216,22 +31216,22 @@
       </c>
       <c r="B422" s="13" t="inlineStr">
         <is>
-          <t>6986dbd1350e1a0014cdbba8</t>
+          <t>6a523589f2a63c0013c8594d</t>
         </is>
       </c>
       <c r="C422" s="13" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>NITIN9239</t>
         </is>
       </c>
       <c r="D422" s="12" t="inlineStr">
         <is>
-          <t>kumarshubham857208@gmail.com</t>
+          <t>tradingspell@gmail.com</t>
         </is>
       </c>
       <c r="E422" s="12" t="inlineStr">
         <is>
-          <t>9253166725</t>
+          <t>6395657006</t>
         </is>
       </c>
       <c r="F422" s="12" t="inlineStr">
@@ -31241,34 +31241,34 @@
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H422" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I422" s="13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J422" s="14" t="n">
-        <v>1411</v>
+        <v>4763</v>
       </c>
       <c r="K422" s="14" t="n">
-        <v>18340</v>
+        <v>18671</v>
       </c>
       <c r="L422" s="15" t="n">
-        <v>2821</v>
+        <v>6954</v>
       </c>
       <c r="M422" s="12" t="inlineStr">
         <is>
-          <t>69a90448ce8bdc00125c31a5</t>
+          <t>6a69b38a2519b6001380e5e0</t>
         </is>
       </c>
       <c r="N422" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
+          <t>https://superprofile.bio/vig/6a69b38a2519b6001380e5e0</t>
         </is>
       </c>
       <c r="O422" s="17" t="inlineStr">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="B423" s="20" t="inlineStr">
         <is>
-          <t>65951378bbebcf001d4651a6</t>
+          <t>6986dbd1350e1a0014cdbba8</t>
         </is>
       </c>
       <c r="C423" s="20" t="inlineStr">
         <is>
-          <t>nonstops</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="D423" s="19" t="inlineStr">
         <is>
-          <t>devanshsirvaiya@gmail.com</t>
+          <t>kumarshubham857208@gmail.com</t>
         </is>
       </c>
       <c r="E423" s="19" t="inlineStr">
         <is>
-          <t>9303185128</t>
+          <t>9253166725</t>
         </is>
       </c>
       <c r="F423" s="19" t="inlineStr">
@@ -31318,29 +31318,29 @@
       </c>
       <c r="H423" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I423" s="20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J423" s="21" t="n">
-        <v>5787</v>
+        <v>1411</v>
       </c>
       <c r="K423" s="21" t="n">
-        <v>18325</v>
+        <v>18340</v>
       </c>
       <c r="L423" s="22" t="n">
-        <v>6269</v>
+        <v>2821</v>
       </c>
       <c r="M423" s="19" t="inlineStr">
         <is>
-          <t>672f09c2cb504b00130e1071</t>
+          <t>69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="N423" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/672f09c2cb504b00130e1071</t>
+          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="O423" s="24" t="inlineStr">
@@ -31360,22 +31360,22 @@
       </c>
       <c r="B424" s="13" t="inlineStr">
         <is>
-          <t>65fd7074e04d92001271989a</t>
+          <t>65951378bbebcf001d4651a6</t>
         </is>
       </c>
       <c r="C424" s="13" t="inlineStr">
         <is>
-          <t>indexhub</t>
+          <t>nonstops</t>
         </is>
       </c>
       <c r="D424" s="12" t="inlineStr">
         <is>
-          <t>kajalbasodha1998@gmail.com</t>
+          <t>devanshsirvaiya@gmail.com</t>
         </is>
       </c>
       <c r="E424" s="12" t="inlineStr">
         <is>
-          <t>9913545157</t>
+          <t>9303185128</t>
         </is>
       </c>
       <c r="F424" s="12" t="inlineStr">
@@ -31385,34 +31385,34 @@
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H424" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I424" s="13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J424" s="14" t="n">
-        <v>2928</v>
+        <v>5787</v>
       </c>
       <c r="K424" s="14" t="n">
-        <v>18251</v>
+        <v>18325</v>
       </c>
       <c r="L424" s="15" t="n">
-        <v>4880</v>
+        <v>6269</v>
       </c>
       <c r="M424" s="12" t="inlineStr">
         <is>
-          <t>647830094112cd001f144fd5</t>
+          <t>672f09c2cb504b00130e1071</t>
         </is>
       </c>
       <c r="N424" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647830094112cd001f144fd5</t>
+          <t>https://superprofile.bio/vig/672f09c2cb504b00130e1071</t>
         </is>
       </c>
       <c r="O424" s="17" t="inlineStr">
@@ -31432,22 +31432,22 @@
       </c>
       <c r="B425" s="20" t="inlineStr">
         <is>
-          <t>677d0628221dc40013a45c7c</t>
+          <t>65fd7074e04d92001271989a</t>
         </is>
       </c>
       <c r="C425" s="20" t="inlineStr">
         <is>
-          <t>httpstmesmarttraders179</t>
+          <t>indexhub</t>
         </is>
       </c>
       <c r="D425" s="19" t="inlineStr">
         <is>
-          <t>gh1785739@gmail.com</t>
+          <t>kajalbasodha1998@gmail.com</t>
         </is>
       </c>
       <c r="E425" s="19" t="inlineStr">
         <is>
-          <t>9839748557</t>
+          <t>9913545157</t>
         </is>
       </c>
       <c r="F425" s="19" t="inlineStr">
@@ -31457,34 +31457,34 @@
       </c>
       <c r="G425" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H425" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I425" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J425" s="21" t="n">
-        <v>1437</v>
+        <v>2928</v>
       </c>
       <c r="K425" s="21" t="n">
-        <v>18249</v>
+        <v>18251</v>
       </c>
       <c r="L425" s="22" t="n">
-        <v>3736</v>
+        <v>4880</v>
       </c>
       <c r="M425" s="19" t="inlineStr">
         <is>
-          <t>68807b5d6aec320013f7f836</t>
+          <t>647830094112cd001f144fd5</t>
         </is>
       </c>
       <c r="N425" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68807b5d6aec320013f7f836</t>
+          <t>https://superprofile.bio/vig/647830094112cd001f144fd5</t>
         </is>
       </c>
       <c r="O425" s="24" t="inlineStr">
@@ -31504,22 +31504,22 @@
       </c>
       <c r="B426" s="13" t="inlineStr">
         <is>
-          <t>6798f85f9c782900139f3bb6</t>
+          <t>677d0628221dc40013a45c7c</t>
         </is>
       </c>
       <c r="C426" s="13" t="inlineStr">
         <is>
-          <t>finostocks</t>
+          <t>httpstmesmarttraders179</t>
         </is>
       </c>
       <c r="D426" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS.FINOMEDIA@GMAIL.COM</t>
+          <t>gh1785739@gmail.com</t>
         </is>
       </c>
       <c r="E426" s="12" t="inlineStr">
         <is>
-          <t>8595499642</t>
+          <t>9839748557</t>
         </is>
       </c>
       <c r="F426" s="12" t="inlineStr">
@@ -31534,29 +31534,29 @@
       </c>
       <c r="H426" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I426" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J426" s="14" t="n">
-        <v>2156</v>
+        <v>1437</v>
       </c>
       <c r="K426" s="14" t="n">
-        <v>18181</v>
+        <v>18249</v>
       </c>
       <c r="L426" s="15" t="n">
-        <v>5283</v>
+        <v>3736</v>
       </c>
       <c r="M426" s="12" t="inlineStr">
         <is>
-          <t>6841acade1ef5a0013eb5faa</t>
+          <t>68807b5d6aec320013f7f836</t>
         </is>
       </c>
       <c r="N426" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6841acade1ef5a0013eb5faa</t>
+          <t>https://superprofile.bio/vig/68807b5d6aec320013f7f836</t>
         </is>
       </c>
       <c r="O426" s="17" t="inlineStr">
@@ -31576,22 +31576,22 @@
       </c>
       <c r="B427" s="20" t="inlineStr">
         <is>
-          <t>663dd24d61f04800142f8ce8</t>
+          <t>6798f85f9c782900139f3bb6</t>
         </is>
       </c>
       <c r="C427" s="20" t="inlineStr">
         <is>
-          <t>ikhushii-rajput</t>
+          <t>finostocks</t>
         </is>
       </c>
       <c r="D427" s="19" t="inlineStr">
         <is>
-          <t>theamelia5705@gmail.com</t>
+          <t>BUSINESS.FINOMEDIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="E427" s="19" t="inlineStr">
         <is>
-          <t>9266867307</t>
+          <t>8595499642</t>
         </is>
       </c>
       <c r="F427" s="19" t="inlineStr">
@@ -31606,29 +31606,29 @@
       </c>
       <c r="H427" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I427" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J427" s="21" t="n">
-        <v>1222</v>
+        <v>2156</v>
       </c>
       <c r="K427" s="21" t="n">
-        <v>18127</v>
+        <v>18181</v>
       </c>
       <c r="L427" s="22" t="n">
-        <v>5597</v>
+        <v>5283</v>
       </c>
       <c r="M427" s="19" t="inlineStr">
         <is>
-          <t>69ebc141f28b8500138e14f8</t>
+          <t>6841acade1ef5a0013eb5faa</t>
         </is>
       </c>
       <c r="N427" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ebc141f28b8500138e14f8</t>
+          <t>https://superprofile.bio/vig/6841acade1ef5a0013eb5faa</t>
         </is>
       </c>
       <c r="O427" s="24" t="inlineStr">
@@ -31648,22 +31648,22 @@
       </c>
       <c r="B428" s="13" t="inlineStr">
         <is>
-          <t>648c4b2fa1f806002b0e5672</t>
+          <t>663dd24d61f04800142f8ce8</t>
         </is>
       </c>
       <c r="C428" s="13" t="inlineStr">
         <is>
-          <t>shalvi4</t>
+          <t>ikhushii-rajput</t>
         </is>
       </c>
       <c r="D428" s="12" t="inlineStr">
         <is>
-          <t>Shalvi93@gmail.com</t>
+          <t>theamelia5705@gmail.com</t>
         </is>
       </c>
       <c r="E428" s="12" t="inlineStr">
         <is>
-          <t>7986152551</t>
+          <t>9266867307</t>
         </is>
       </c>
       <c r="F428" s="12" t="inlineStr">
@@ -31673,34 +31673,34 @@
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H428" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I428" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J428" s="14" t="n">
-        <v>2811</v>
+        <v>1222</v>
       </c>
       <c r="K428" s="14" t="n">
-        <v>18089</v>
+        <v>18127</v>
       </c>
       <c r="L428" s="15" t="n">
-        <v>9518</v>
+        <v>5597</v>
       </c>
       <c r="M428" s="12" t="inlineStr">
         <is>
-          <t>65d3524e4fdd200013ff1d18</t>
+          <t>69ebc141f28b8500138e14f8</t>
         </is>
       </c>
       <c r="N428" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65d3524e4fdd200013ff1d18</t>
+          <t>https://superprofile.bio/vig/69ebc141f28b8500138e14f8</t>
         </is>
       </c>
       <c r="O428" s="17" t="inlineStr">
@@ -31720,22 +31720,22 @@
       </c>
       <c r="B429" s="20" t="inlineStr">
         <is>
-          <t>65866f50ea8865001e422cfa</t>
+          <t>648c4b2fa1f806002b0e5672</t>
         </is>
       </c>
       <c r="C429" s="20" t="inlineStr">
         <is>
-          <t>beinglimitless</t>
+          <t>shalvi4</t>
         </is>
       </c>
       <c r="D429" s="19" t="inlineStr">
         <is>
-          <t>beinglimitless43@gmail.com</t>
+          <t>Shalvi93@gmail.com</t>
         </is>
       </c>
       <c r="E429" s="19" t="inlineStr">
         <is>
-          <t>9695670665</t>
+          <t>7986152551</t>
         </is>
       </c>
       <c r="F429" s="19" t="inlineStr">
@@ -31745,7 +31745,7 @@
       </c>
       <c r="G429" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H429" s="19" t="inlineStr">
@@ -31754,25 +31754,25 @@
         </is>
       </c>
       <c r="I429" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J429" s="21" t="n">
-        <v>5400</v>
+        <v>2811</v>
       </c>
       <c r="K429" s="21" t="n">
-        <v>18000</v>
+        <v>18089</v>
       </c>
       <c r="L429" s="22" t="n">
-        <v>12600</v>
+        <v>9518</v>
       </c>
       <c r="M429" s="19" t="inlineStr">
         <is>
-          <t>658ff10c177387001df8af49</t>
+          <t>65d3524e4fdd200013ff1d18</t>
         </is>
       </c>
       <c r="N429" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/658ff10c177387001df8af49</t>
+          <t>https://superprofile.bio/vig/65d3524e4fdd200013ff1d18</t>
         </is>
       </c>
       <c r="O429" s="24" t="inlineStr">
@@ -31792,22 +31792,22 @@
       </c>
       <c r="B430" s="13" t="inlineStr">
         <is>
-          <t>6a0493243a48f800134b7d4b</t>
+          <t>65866f50ea8865001e422cfa</t>
         </is>
       </c>
       <c r="C430" s="13" t="inlineStr">
         <is>
-          <t>meenarahulzz</t>
+          <t>beinglimitless</t>
         </is>
       </c>
       <c r="D430" s="12" t="inlineStr">
         <is>
-          <t>tmind4460@gmail.com</t>
+          <t>beinglimitless43@gmail.com</t>
         </is>
       </c>
       <c r="E430" s="12" t="inlineStr">
         <is>
-          <t>9672238460</t>
+          <t>9695670665</t>
         </is>
       </c>
       <c r="F430" s="12" t="inlineStr">
@@ -31817,34 +31817,34 @@
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H430" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I430" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J430" s="14" t="n">
-        <v>1619</v>
+        <v>5400</v>
       </c>
       <c r="K430" s="14" t="n">
-        <v>17905</v>
+        <v>18000</v>
       </c>
       <c r="L430" s="15" t="n">
-        <v>7428</v>
+        <v>12600</v>
       </c>
       <c r="M430" s="12" t="inlineStr">
         <is>
-          <t>68d0ebe0adc9cb00133eccaf</t>
+          <t>658ff10c177387001df8af49</t>
         </is>
       </c>
       <c r="N430" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
+          <t>https://superprofile.bio/vig/658ff10c177387001df8af49</t>
         </is>
       </c>
       <c r="O430" s="17" t="inlineStr">
@@ -31864,22 +31864,22 @@
       </c>
       <c r="B431" s="20" t="inlineStr">
         <is>
-          <t>66926a105d82bc0013c1229c</t>
+          <t>6a0493243a48f800134b7d4b</t>
         </is>
       </c>
       <c r="C431" s="20" t="inlineStr">
         <is>
-          <t>aactiveetraders</t>
+          <t>meenarahulzz</t>
         </is>
       </c>
       <c r="D431" s="19" t="inlineStr">
         <is>
-          <t>rshinde7057@gmail.com</t>
+          <t>tmind4460@gmail.com</t>
         </is>
       </c>
       <c r="E431" s="19" t="inlineStr">
         <is>
-          <t>8104421373</t>
+          <t>9672238460</t>
         </is>
       </c>
       <c r="F431" s="19" t="inlineStr">
@@ -31889,34 +31889,34 @@
       </c>
       <c r="G431" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H431" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I431" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J431" s="21" t="n">
-        <v>2411</v>
+        <v>1619</v>
       </c>
       <c r="K431" s="21" t="n">
-        <v>17800</v>
+        <v>17905</v>
       </c>
       <c r="L431" s="22" t="n">
-        <v>3856</v>
+        <v>7428</v>
       </c>
       <c r="M431" s="19" t="inlineStr">
         <is>
-          <t>67cab3644e87bf0013f15f65</t>
+          <t>68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="N431" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
+          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="O431" s="24" t="inlineStr">
@@ -31936,22 +31936,22 @@
       </c>
       <c r="B432" s="13" t="inlineStr">
         <is>
-          <t>66b0a52105f9600013e59686</t>
+          <t>66926a105d82bc0013c1229c</t>
         </is>
       </c>
       <c r="C432" s="13" t="inlineStr">
         <is>
-          <t>swingwithdip</t>
+          <t>aactiveetraders</t>
         </is>
       </c>
       <c r="D432" s="12" t="inlineStr">
         <is>
-          <t>patildipak2106@gmail.com</t>
+          <t>rshinde7057@gmail.com</t>
         </is>
       </c>
       <c r="E432" s="12" t="inlineStr">
         <is>
-          <t>9545849301</t>
+          <t>8104421373</t>
         </is>
       </c>
       <c r="F432" s="12" t="inlineStr">
@@ -31961,34 +31961,34 @@
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H432" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I432" s="13" t="n">
         <v>7</v>
       </c>
       <c r="J432" s="14" t="n">
-        <v>2961</v>
+        <v>2411</v>
       </c>
       <c r="K432" s="14" t="n">
-        <v>17484</v>
+        <v>17800</v>
       </c>
       <c r="L432" s="15" t="n">
-        <v>4371</v>
+        <v>3856</v>
       </c>
       <c r="M432" s="12" t="inlineStr">
         <is>
-          <t>6a22b9a8c0c8d2001388c89e</t>
+          <t>67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="N432" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a22b9a8c0c8d2001388c89e</t>
+          <t>https://superprofile.bio/vig/67cab3644e87bf0013f15f65</t>
         </is>
       </c>
       <c r="O432" s="17" t="inlineStr">
@@ -32008,22 +32008,22 @@
       </c>
       <c r="B433" s="20" t="inlineStr">
         <is>
-          <t>64a936996a2973002b10c7f6</t>
+          <t>66b0a52105f9600013e59686</t>
         </is>
       </c>
       <c r="C433" s="20" t="inlineStr">
         <is>
-          <t>tmg</t>
+          <t>swingwithdip</t>
         </is>
       </c>
       <c r="D433" s="19" t="inlineStr">
         <is>
-          <t>rohanfriends29@gmail.com</t>
+          <t>patildipak2106@gmail.com</t>
         </is>
       </c>
       <c r="E433" s="19" t="inlineStr">
         <is>
-          <t>6350084025</t>
+          <t>9545849301</t>
         </is>
       </c>
       <c r="F433" s="19" t="inlineStr">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="G433" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H433" s="19" t="inlineStr">
@@ -32045,22 +32045,22 @@
         <v>7</v>
       </c>
       <c r="J433" s="21" t="n">
-        <v>2456</v>
+        <v>2961</v>
       </c>
       <c r="K433" s="21" t="n">
-        <v>17015</v>
+        <v>17484</v>
       </c>
       <c r="L433" s="22" t="n">
-        <v>4912</v>
+        <v>4371</v>
       </c>
       <c r="M433" s="19" t="inlineStr">
         <is>
-          <t>64f420086fadd99da766809d</t>
+          <t>6a22b9a8c0c8d2001388c89e</t>
         </is>
       </c>
       <c r="N433" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64f420086fadd99da766809d</t>
+          <t>https://superprofile.bio/vig/6a22b9a8c0c8d2001388c89e</t>
         </is>
       </c>
       <c r="O433" s="24" t="inlineStr">
@@ -32080,22 +32080,22 @@
       </c>
       <c r="B434" s="13" t="inlineStr">
         <is>
-          <t>64dc627649d054001e7dcd8d</t>
+          <t>64a936996a2973002b10c7f6</t>
         </is>
       </c>
       <c r="C434" s="13" t="inlineStr">
         <is>
-          <t>moresuccess</t>
+          <t>tmg</t>
         </is>
       </c>
       <c r="D434" s="12" t="inlineStr">
         <is>
-          <t>moresuccessofficiall@gmail.com</t>
+          <t>rohanfriends29@gmail.com</t>
         </is>
       </c>
       <c r="E434" s="12" t="inlineStr">
         <is>
-          <t>9415548937</t>
+          <t>6350084025</t>
         </is>
       </c>
       <c r="F434" s="12" t="inlineStr">
@@ -32105,34 +32105,34 @@
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H434" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I434" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J434" s="14" t="n">
-        <v>1409</v>
+        <v>2456</v>
       </c>
       <c r="K434" s="14" t="n">
-        <v>16938</v>
+        <v>17015</v>
       </c>
       <c r="L434" s="15" t="n">
-        <v>3469</v>
+        <v>4912</v>
       </c>
       <c r="M434" s="12" t="inlineStr">
         <is>
-          <t>6a89777c9ac5d90013d4f1dc</t>
+          <t>64f420086fadd99da766809d</t>
         </is>
       </c>
       <c r="N434" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a89777c9ac5d90013d4f1dc</t>
+          <t>https://superprofile.bio/vig/64f420086fadd99da766809d</t>
         </is>
       </c>
       <c r="O434" s="17" t="inlineStr">
@@ -32152,22 +32152,22 @@
       </c>
       <c r="B435" s="20" t="inlineStr">
         <is>
-          <t>66310a2d8235ac00139e18a0</t>
+          <t>64dc627649d054001e7dcd8d</t>
         </is>
       </c>
       <c r="C435" s="20" t="inlineStr">
         <is>
-          <t>thesonicbull</t>
+          <t>moresuccess</t>
         </is>
       </c>
       <c r="D435" s="19" t="inlineStr">
         <is>
-          <t>yomrbrown.in@gmail.com</t>
+          <t>moresuccessofficiall@gmail.com</t>
         </is>
       </c>
       <c r="E435" s="19" t="inlineStr">
         <is>
-          <t>9643006948</t>
+          <t>9415548937</t>
         </is>
       </c>
       <c r="F435" s="19" t="inlineStr">
@@ -32177,34 +32177,34 @@
       </c>
       <c r="G435" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H435" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I435" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J435" s="21" t="n">
-        <v>1973</v>
+        <v>1409</v>
       </c>
       <c r="K435" s="21" t="n">
-        <v>16913</v>
+        <v>16938</v>
       </c>
       <c r="L435" s="22" t="n">
-        <v>3289</v>
+        <v>3469</v>
       </c>
       <c r="M435" s="19" t="inlineStr">
         <is>
-          <t>69e337a24b855e0013361a30</t>
+          <t>6a89777c9ac5d90013d4f1dc</t>
         </is>
       </c>
       <c r="N435" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e337a24b855e0013361a30</t>
+          <t>https://superprofile.bio/vig/6a89777c9ac5d90013d4f1dc</t>
         </is>
       </c>
       <c r="O435" s="24" t="inlineStr">
@@ -32224,22 +32224,22 @@
       </c>
       <c r="B436" s="13" t="inlineStr">
         <is>
-          <t>6a27eb1c70bfd600133e21ab</t>
+          <t>66310a2d8235ac00139e18a0</t>
         </is>
       </c>
       <c r="C436" s="13" t="inlineStr">
         <is>
-          <t>saurabh8454</t>
+          <t>thesonicbull</t>
         </is>
       </c>
       <c r="D436" s="12" t="inlineStr">
         <is>
-          <t>vijaykarne18@gmail.com</t>
+          <t>yomrbrown.in@gmail.com</t>
         </is>
       </c>
       <c r="E436" s="12" t="inlineStr">
         <is>
-          <t>8793758084</t>
+          <t>9643006948</t>
         </is>
       </c>
       <c r="F436" s="12" t="inlineStr">
@@ -32254,29 +32254,29 @@
       </c>
       <c r="H436" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I436" s="13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J436" s="14" t="n">
-        <v>1750</v>
+        <v>1973</v>
       </c>
       <c r="K436" s="14" t="n">
-        <v>16898</v>
+        <v>16913</v>
       </c>
       <c r="L436" s="15" t="n">
-        <v>6117</v>
+        <v>3289</v>
       </c>
       <c r="M436" s="12" t="inlineStr">
         <is>
-          <t>6a70de5a833cbc00130a4f09</t>
+          <t>69e337a24b855e0013361a30</t>
         </is>
       </c>
       <c r="N436" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a70de5a833cbc00130a4f09</t>
+          <t>https://superprofile.bio/vig/69e337a24b855e0013361a30</t>
         </is>
       </c>
       <c r="O436" s="17" t="inlineStr">
@@ -32296,22 +32296,22 @@
       </c>
       <c r="B437" s="20" t="inlineStr">
         <is>
-          <t>66ab4182042051001366042b</t>
+          <t>6a27eb1c70bfd600133e21ab</t>
         </is>
       </c>
       <c r="C437" s="20" t="inlineStr">
         <is>
-          <t>swingedge</t>
+          <t>saurabh8454</t>
         </is>
       </c>
       <c r="D437" s="19" t="inlineStr">
         <is>
-          <t>sumannatani8586@gmail.com</t>
+          <t>vijaykarne18@gmail.com</t>
         </is>
       </c>
       <c r="E437" s="19" t="inlineStr">
         <is>
-          <t>8905901899</t>
+          <t>8793758084</t>
         </is>
       </c>
       <c r="F437" s="19" t="inlineStr">
@@ -32321,34 +32321,34 @@
       </c>
       <c r="G437" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H437" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I437" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J437" s="21" t="n">
-        <v>3760</v>
+        <v>1750</v>
       </c>
       <c r="K437" s="21" t="n">
-        <v>16818</v>
+        <v>16898</v>
       </c>
       <c r="L437" s="22" t="n">
-        <v>7520</v>
+        <v>6117</v>
       </c>
       <c r="M437" s="19" t="inlineStr">
         <is>
-          <t>68b5d44bdb108f0013354a5e</t>
+          <t>6a70de5a833cbc00130a4f09</t>
         </is>
       </c>
       <c r="N437" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b5d44bdb108f0013354a5e</t>
+          <t>https://superprofile.bio/vig/6a70de5a833cbc00130a4f09</t>
         </is>
       </c>
       <c r="O437" s="24" t="inlineStr">
@@ -32368,22 +32368,22 @@
       </c>
       <c r="B438" s="13" t="inlineStr">
         <is>
-          <t>648d294f6becf40020f34b85</t>
+          <t>66ab4182042051001366042b</t>
         </is>
       </c>
       <c r="C438" s="13" t="inlineStr">
         <is>
-          <t>NeelkanthTraining</t>
+          <t>swingedge</t>
         </is>
       </c>
       <c r="D438" s="12" t="inlineStr">
         <is>
-          <t>krissh.a.shiva@gmail.com</t>
+          <t>sumannatani8586@gmail.com</t>
         </is>
       </c>
       <c r="E438" s="12" t="inlineStr">
         <is>
-          <t>9822224364</t>
+          <t>8905901899</t>
         </is>
       </c>
       <c r="F438" s="12" t="inlineStr">
@@ -32393,34 +32393,34 @@
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H438" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I438" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J438" s="14" t="n">
-        <v>8299</v>
+        <v>3760</v>
       </c>
       <c r="K438" s="14" t="n">
-        <v>16598</v>
+        <v>16818</v>
       </c>
       <c r="L438" s="15" t="n">
-        <v>8299</v>
+        <v>7520</v>
       </c>
       <c r="M438" s="12" t="inlineStr">
         <is>
-          <t>6a8314dafb1cde0013c920fe</t>
+          <t>68b5d44bdb108f0013354a5e</t>
         </is>
       </c>
       <c r="N438" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8314dafb1cde0013c920fe</t>
+          <t>https://superprofile.bio/vig/68b5d44bdb108f0013354a5e</t>
         </is>
       </c>
       <c r="O438" s="17" t="inlineStr">
@@ -32440,22 +32440,22 @@
       </c>
       <c r="B439" s="20" t="inlineStr">
         <is>
-          <t>6a1fc44c997af10013463341</t>
+          <t>648d294f6becf40020f34b85</t>
         </is>
       </c>
       <c r="C439" s="20" t="inlineStr">
         <is>
-          <t>httpstmeequitytigerbh</t>
+          <t>NeelkanthTraining</t>
         </is>
       </c>
       <c r="D439" s="19" t="inlineStr">
         <is>
-          <t>equitytigerbh@gmail.com</t>
+          <t>krissh.a.shiva@gmail.com</t>
         </is>
       </c>
       <c r="E439" s="19" t="inlineStr">
         <is>
-          <t>9225536379</t>
+          <t>9822224364</t>
         </is>
       </c>
       <c r="F439" s="19" t="inlineStr">
@@ -32465,34 +32465,34 @@
       </c>
       <c r="G439" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H439" s="19" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H439" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="I439" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J439" s="21" t="n">
-        <v>1424</v>
+        <v>8299</v>
       </c>
       <c r="K439" s="21" t="n">
-        <v>16563</v>
+        <v>16598</v>
       </c>
       <c r="L439" s="22" t="n">
-        <v>8069</v>
+        <v>8299</v>
       </c>
       <c r="M439" s="19" t="inlineStr">
         <is>
-          <t>6a267c24adb94f00130df22e</t>
+          <t>6a8314dafb1cde0013c920fe</t>
         </is>
       </c>
       <c r="N439" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a267c24adb94f00130df22e</t>
+          <t>https://superprofile.bio/vig/6a8314dafb1cde0013c920fe</t>
         </is>
       </c>
       <c r="O439" s="24" t="inlineStr">
@@ -32512,22 +32512,22 @@
       </c>
       <c r="B440" s="13" t="inlineStr">
         <is>
-          <t>6748015fe2edb40013d1b7dd</t>
+          <t>6a1fc44c997af10013463341</t>
         </is>
       </c>
       <c r="C440" s="13" t="inlineStr">
         <is>
-          <t>Rishee6830</t>
+          <t>httpstmeequitytigerbh</t>
         </is>
       </c>
       <c r="D440" s="12" t="inlineStr">
         <is>
-          <t>rishibaweja@gmail.com</t>
+          <t>equitytigerbh@gmail.com</t>
         </is>
       </c>
       <c r="E440" s="12" t="inlineStr">
         <is>
-          <t>7217713027</t>
+          <t>9225536379</t>
         </is>
       </c>
       <c r="F440" s="12" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H440" s="12" t="inlineStr">
@@ -32546,25 +32546,25 @@
         </is>
       </c>
       <c r="I440" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J440" s="14" t="n">
-        <v>3011</v>
+        <v>1424</v>
       </c>
       <c r="K440" s="14" t="n">
-        <v>16561</v>
+        <v>16563</v>
       </c>
       <c r="L440" s="15" t="n">
-        <v>10539</v>
+        <v>8069</v>
       </c>
       <c r="M440" s="12" t="inlineStr">
         <is>
-          <t>698c7ad4dc89350013d7d312</t>
+          <t>6a267c24adb94f00130df22e</t>
         </is>
       </c>
       <c r="N440" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698c7ad4dc89350013d7d312</t>
+          <t>https://superprofile.bio/vig/6a267c24adb94f00130df22e</t>
         </is>
       </c>
       <c r="O440" s="17" t="inlineStr">
@@ -32584,22 +32584,22 @@
       </c>
       <c r="B441" s="20" t="inlineStr">
         <is>
-          <t>69a7e81242b689001318c2c7</t>
+          <t>6748015fe2edb40013d1b7dd</t>
         </is>
       </c>
       <c r="C441" s="20" t="inlineStr">
         <is>
-          <t>vippremiuimgrouo</t>
+          <t>Rishee6830</t>
         </is>
       </c>
       <c r="D441" s="19" t="inlineStr">
         <is>
-          <t>a1618202224@gmail.com</t>
+          <t>rishibaweja@gmail.com</t>
         </is>
       </c>
       <c r="E441" s="19" t="inlineStr">
         <is>
-          <t>8409761034</t>
+          <t>7217713027</t>
         </is>
       </c>
       <c r="F441" s="19" t="inlineStr">
@@ -32609,34 +32609,34 @@
       </c>
       <c r="G441" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H441" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I441" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J441" s="21" t="n">
-        <v>5624</v>
+        <v>3011</v>
       </c>
       <c r="K441" s="21" t="n">
-        <v>16483</v>
+        <v>16561</v>
       </c>
       <c r="L441" s="22" t="n">
-        <v>5624</v>
+        <v>10539</v>
       </c>
       <c r="M441" s="19" t="inlineStr">
         <is>
-          <t>6707a608a68141001380937c</t>
+          <t>698c7ad4dc89350013d7d312</t>
         </is>
       </c>
       <c r="N441" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6707a608a68141001380937c</t>
+          <t>https://superprofile.bio/vig/698c7ad4dc89350013d7d312</t>
         </is>
       </c>
       <c r="O441" s="24" t="inlineStr">
@@ -32656,22 +32656,22 @@
       </c>
       <c r="B442" s="13" t="inlineStr">
         <is>
-          <t>6822dab726bcaa0013d8c13b</t>
+          <t>69a7e81242b689001318c2c7</t>
         </is>
       </c>
       <c r="C442" s="13" t="inlineStr">
         <is>
-          <t>marketarchitect</t>
+          <t>vippremiuimgrouo</t>
         </is>
       </c>
       <c r="D442" s="12" t="inlineStr">
         <is>
-          <t>kingofstockmarket16925@gmail.com</t>
+          <t>a1618202224@gmail.com</t>
         </is>
       </c>
       <c r="E442" s="12" t="inlineStr">
         <is>
-          <t>9377882007</t>
+          <t>8409761034</t>
         </is>
       </c>
       <c r="F442" s="12" t="inlineStr">
@@ -32681,34 +32681,34 @@
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H442" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I442" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J442" s="14" t="n">
-        <v>1916</v>
+        <v>5624</v>
       </c>
       <c r="K442" s="14" t="n">
-        <v>16403</v>
+        <v>16483</v>
       </c>
       <c r="L442" s="15" t="n">
-        <v>3373</v>
+        <v>5624</v>
       </c>
       <c r="M442" s="12" t="inlineStr">
         <is>
-          <t>699587d32a02000013112058</t>
+          <t>6707a608a68141001380937c</t>
         </is>
       </c>
       <c r="N442" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/699587d32a02000013112058</t>
+          <t>https://superprofile.bio/vig/6707a608a68141001380937c</t>
         </is>
       </c>
       <c r="O442" s="17" t="inlineStr">
@@ -32728,22 +32728,22 @@
       </c>
       <c r="B443" s="20" t="inlineStr">
         <is>
-          <t>69e89b0ed9ffde0013e31879</t>
+          <t>6822dab726bcaa0013d8c13b</t>
         </is>
       </c>
       <c r="C443" s="20" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>marketarchitect</t>
         </is>
       </c>
       <c r="D443" s="19" t="inlineStr">
         <is>
-          <t>nitindhandre42@gmail.com</t>
+          <t>kingofstockmarket16925@gmail.com</t>
         </is>
       </c>
       <c r="E443" s="19" t="inlineStr">
         <is>
-          <t>7977913010</t>
+          <t>9377882007</t>
         </is>
       </c>
       <c r="F443" s="19" t="inlineStr">
@@ -32753,34 +32753,34 @@
       </c>
       <c r="G443" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H443" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I443" s="20" t="n">
         <v>7</v>
       </c>
       <c r="J443" s="21" t="n">
-        <v>3142</v>
+        <v>1916</v>
       </c>
       <c r="K443" s="21" t="n">
-        <v>16282</v>
+        <v>16403</v>
       </c>
       <c r="L443" s="22" t="n">
-        <v>3428</v>
+        <v>3373</v>
       </c>
       <c r="M443" s="19" t="inlineStr">
         <is>
-          <t>6a787fec62ca790013c3fe57</t>
+          <t>699587d32a02000013112058</t>
         </is>
       </c>
       <c r="N443" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
+          <t>https://superprofile.bio/vig/699587d32a02000013112058</t>
         </is>
       </c>
       <c r="O443" s="24" t="inlineStr">
@@ -32800,22 +32800,22 @@
       </c>
       <c r="B444" s="13" t="inlineStr">
         <is>
-          <t>64528400df151f002061d5de</t>
+          <t>69e89b0ed9ffde0013e31879</t>
         </is>
       </c>
       <c r="C444" s="13" t="inlineStr">
         <is>
-          <t>Piyushlodhabhl</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="D444" s="12" t="inlineStr">
         <is>
-          <t>salesmnccare@gmail.com</t>
+          <t>nitindhandre42@gmail.com</t>
         </is>
       </c>
       <c r="E444" s="12" t="inlineStr">
         <is>
-          <t>9649688666</t>
+          <t>7977913010</t>
         </is>
       </c>
       <c r="F444" s="12" t="inlineStr">
@@ -32825,34 +32825,34 @@
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H444" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I444" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J444" s="14" t="n">
-        <v>8100</v>
+        <v>3142</v>
       </c>
       <c r="K444" s="14" t="n">
-        <v>16200</v>
+        <v>16282</v>
       </c>
       <c r="L444" s="15" t="n">
-        <v>8100</v>
+        <v>3428</v>
       </c>
       <c r="M444" s="12" t="inlineStr">
         <is>
-          <t>67f9faff3518250013513aea</t>
+          <t>6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="N444" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67f9faff3518250013513aea</t>
+          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="O444" s="17" t="inlineStr">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="B445" s="20" t="inlineStr">
         <is>
-          <t>67783e8e9b28020013239bcb</t>
+          <t>64528400df151f002061d5de</t>
         </is>
       </c>
       <c r="C445" s="20" t="inlineStr">
         <is>
-          <t>therankerss</t>
+          <t>Piyushlodhabhl</t>
         </is>
       </c>
       <c r="D445" s="19" t="inlineStr">
         <is>
-          <t>kumanikhil54@gmail.com</t>
+          <t>salesmnccare@gmail.com</t>
         </is>
       </c>
       <c r="E445" s="19" t="inlineStr">
         <is>
-          <t>9142451230</t>
+          <t>9649688666</t>
         </is>
       </c>
       <c r="F445" s="19" t="inlineStr">
@@ -32897,34 +32897,34 @@
       </c>
       <c r="G445" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H445" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I445" s="20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J445" s="21" t="n">
-        <v>1218</v>
+        <v>8100</v>
       </c>
       <c r="K445" s="21" t="n">
-        <v>16119</v>
+        <v>16200</v>
       </c>
       <c r="L445" s="22" t="n">
-        <v>2898</v>
+        <v>8100</v>
       </c>
       <c r="M445" s="19" t="inlineStr">
         <is>
-          <t>6779192938e13e00133b7cc4</t>
+          <t>67f9faff3518250013513aea</t>
         </is>
       </c>
       <c r="N445" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6779192938e13e00133b7cc4</t>
+          <t>https://superprofile.bio/vig/67f9faff3518250013513aea</t>
         </is>
       </c>
       <c r="O445" s="24" t="inlineStr">
@@ -32944,22 +32944,22 @@
       </c>
       <c r="B446" s="13" t="inlineStr">
         <is>
-          <t>66eecfcebce5f30013f7e375</t>
+          <t>67783e8e9b28020013239bcb</t>
         </is>
       </c>
       <c r="C446" s="13" t="inlineStr">
         <is>
-          <t>tradinghubtelugu</t>
+          <t>therankerss</t>
         </is>
       </c>
       <c r="D446" s="12" t="inlineStr">
         <is>
-          <t>earnwithrajj@gmail.com</t>
+          <t>kumanikhil54@gmail.com</t>
         </is>
       </c>
       <c r="E446" s="12" t="inlineStr">
         <is>
-          <t>9177326947</t>
+          <t>9142451230</t>
         </is>
       </c>
       <c r="F446" s="12" t="inlineStr">
@@ -32969,34 +32969,34 @@
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H446" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I446" s="13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J446" s="14" t="n">
-        <v>8010</v>
+        <v>1218</v>
       </c>
       <c r="K446" s="14" t="n">
-        <v>16020</v>
+        <v>16119</v>
       </c>
       <c r="L446" s="15" t="n">
-        <v>8010</v>
+        <v>2898</v>
       </c>
       <c r="M446" s="12" t="inlineStr">
         <is>
-          <t>678ffeab68ed970013dc33a0</t>
+          <t>6779192938e13e00133b7cc4</t>
         </is>
       </c>
       <c r="N446" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/678ffeab68ed970013dc33a0</t>
+          <t>https://superprofile.bio/vig/6779192938e13e00133b7cc4</t>
         </is>
       </c>
       <c r="O446" s="17" t="inlineStr">
@@ -33016,22 +33016,22 @@
       </c>
       <c r="B447" s="20" t="inlineStr">
         <is>
-          <t>695fc2d673169a001320fcf5</t>
+          <t>66eecfcebce5f30013f7e375</t>
         </is>
       </c>
       <c r="C447" s="20" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>tradinghubtelugu</t>
         </is>
       </c>
       <c r="D447" s="19" t="inlineStr">
         <is>
-          <t>shivamshiva7870@gmail.com</t>
+          <t>earnwithrajj@gmail.com</t>
         </is>
       </c>
       <c r="E447" s="19" t="inlineStr">
         <is>
-          <t>9534598557</t>
+          <t>9177326947</t>
         </is>
       </c>
       <c r="F447" s="19" t="inlineStr">
@@ -33046,29 +33046,29 @@
       </c>
       <c r="H447" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I447" s="20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J447" s="21" t="n">
-        <v>1227</v>
+        <v>8010</v>
       </c>
       <c r="K447" s="21" t="n">
-        <v>15989</v>
+        <v>16020</v>
       </c>
       <c r="L447" s="22" t="n">
-        <v>5389</v>
+        <v>8010</v>
       </c>
       <c r="M447" s="19" t="inlineStr">
         <is>
-          <t>6961fea2c0dd9a00126d58b1</t>
+          <t>678ffeab68ed970013dc33a0</t>
         </is>
       </c>
       <c r="N447" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
+          <t>https://superprofile.bio/vig/678ffeab68ed970013dc33a0</t>
         </is>
       </c>
       <c r="O447" s="24" t="inlineStr">
@@ -33088,22 +33088,22 @@
       </c>
       <c r="B448" s="13" t="inlineStr">
         <is>
-          <t>633c3e226b661153706c2919</t>
+          <t>695fc2d673169a001320fcf5</t>
         </is>
       </c>
       <c r="C448" s="13" t="inlineStr">
         <is>
-          <t>bankniftyplatinum01</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="D448" s="12" t="inlineStr">
         <is>
-          <t>savitapawaskar72@gmail.com</t>
+          <t>shivamshiva7870@gmail.com</t>
         </is>
       </c>
       <c r="E448" s="12" t="inlineStr">
         <is>
-          <t>7483798461</t>
+          <t>9534598557</t>
         </is>
       </c>
       <c r="F448" s="12" t="inlineStr">
@@ -33113,34 +33113,34 @@
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H448" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I448" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J448" s="14" t="n">
-        <v>6924</v>
+        <v>1227</v>
       </c>
       <c r="K448" s="14" t="n">
-        <v>15825</v>
+        <v>15989</v>
       </c>
       <c r="L448" s="15" t="n">
-        <v>6924</v>
+        <v>5389</v>
       </c>
       <c r="M448" s="12" t="inlineStr">
         <is>
-          <t>63be7286b9f01e002c13f34a</t>
+          <t>6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="N448" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63be7286b9f01e002c13f34a</t>
+          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="O448" s="17" t="inlineStr">
@@ -33160,22 +33160,22 @@
       </c>
       <c r="B449" s="20" t="inlineStr">
         <is>
-          <t>61b633d2efcfd46e56495985</t>
+          <t>633c3e226b661153706c2919</t>
         </is>
       </c>
       <c r="C449" s="20" t="inlineStr">
         <is>
-          <t>thetradingclub</t>
+          <t>bankniftyplatinum01</t>
         </is>
       </c>
       <c r="D449" s="19" t="inlineStr">
         <is>
-          <t>sumitjain61830@gmail.com</t>
+          <t>savitapawaskar72@gmail.com</t>
         </is>
       </c>
       <c r="E449" s="19" t="inlineStr">
         <is>
-          <t>8975698992</t>
+          <t>7483798461</t>
         </is>
       </c>
       <c r="F449" s="19" t="inlineStr">
@@ -33190,29 +33190,29 @@
       </c>
       <c r="H449" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I449" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J449" s="21" t="n">
-        <v>1239</v>
+        <v>6924</v>
       </c>
       <c r="K449" s="21" t="n">
-        <v>15779</v>
+        <v>15825</v>
       </c>
       <c r="L449" s="22" t="n">
-        <v>10410</v>
+        <v>6924</v>
       </c>
       <c r="M449" s="19" t="inlineStr">
         <is>
-          <t>6a4bf40725aaf10013aee750</t>
+          <t>63be7286b9f01e002c13f34a</t>
         </is>
       </c>
       <c r="N449" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4bf40725aaf10013aee750</t>
+          <t>https://superprofile.bio/vig/63be7286b9f01e002c13f34a</t>
         </is>
       </c>
       <c r="O449" s="24" t="inlineStr">
@@ -33232,22 +33232,22 @@
       </c>
       <c r="B450" s="13" t="inlineStr">
         <is>
-          <t>68dccb22e1910c00138b515f</t>
+          <t>61b633d2efcfd46e56495985</t>
         </is>
       </c>
       <c r="C450" s="13" t="inlineStr">
         <is>
-          <t>badshaitrading</t>
+          <t>thetradingclub</t>
         </is>
       </c>
       <c r="D450" s="12" t="inlineStr">
         <is>
-          <t>badshaitrading@gmail.com</t>
+          <t>sumitjain61830@gmail.com</t>
         </is>
       </c>
       <c r="E450" s="12" t="inlineStr">
         <is>
-          <t>7076697666</t>
+          <t>8975698992</t>
         </is>
       </c>
       <c r="F450" s="12" t="inlineStr">
@@ -33257,34 +33257,34 @@
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H450" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I450" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J450" s="14" t="n">
-        <v>3975</v>
+        <v>1239</v>
       </c>
       <c r="K450" s="14" t="n">
-        <v>15726</v>
+        <v>15779</v>
       </c>
       <c r="L450" s="15" t="n">
-        <v>3975</v>
+        <v>10410</v>
       </c>
       <c r="M450" s="12" t="inlineStr">
         <is>
-          <t>68e12bede32be1001304d591</t>
+          <t>6a4bf40725aaf10013aee750</t>
         </is>
       </c>
       <c r="N450" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68e12bede32be1001304d591</t>
+          <t>https://superprofile.bio/vig/6a4bf40725aaf10013aee750</t>
         </is>
       </c>
       <c r="O450" s="17" t="inlineStr">
@@ -33304,22 +33304,22 @@
       </c>
       <c r="B451" s="20" t="inlineStr">
         <is>
-          <t>6468b4144600ce0021548f80</t>
+          <t>68dccb22e1910c00138b515f</t>
         </is>
       </c>
       <c r="C451" s="20" t="inlineStr">
         <is>
-          <t>buyingexpert</t>
+          <t>badshaitrading</t>
         </is>
       </c>
       <c r="D451" s="19" t="inlineStr">
         <is>
-          <t>abhiscalping2625@gmail.com</t>
+          <t>badshaitrading@gmail.com</t>
         </is>
       </c>
       <c r="E451" s="19" t="inlineStr">
         <is>
-          <t>7905666582</t>
+          <t>7076697666</t>
         </is>
       </c>
       <c r="F451" s="19" t="inlineStr">
@@ -33329,34 +33329,34 @@
       </c>
       <c r="G451" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H451" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I451" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J451" s="21" t="n">
-        <v>4230</v>
+        <v>3975</v>
       </c>
       <c r="K451" s="21" t="n">
-        <v>15660</v>
+        <v>15726</v>
       </c>
       <c r="L451" s="22" t="n">
-        <v>4230</v>
+        <v>3975</v>
       </c>
       <c r="M451" s="19" t="inlineStr">
         <is>
-          <t>69d4de9898622b0013d1d543</t>
+          <t>68e12bede32be1001304d591</t>
         </is>
       </c>
       <c r="N451" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d4de9898622b0013d1d543</t>
+          <t>https://superprofile.bio/vig/68e12bede32be1001304d591</t>
         </is>
       </c>
       <c r="O451" s="24" t="inlineStr">
@@ -33376,22 +33376,22 @@
       </c>
       <c r="B452" s="13" t="inlineStr">
         <is>
-          <t>6a2036382888a500137bb912</t>
+          <t>6468b4144600ce0021548f80</t>
         </is>
       </c>
       <c r="C452" s="13" t="inlineStr">
         <is>
-          <t>yvstocks</t>
+          <t>buyingexpert</t>
         </is>
       </c>
       <c r="D452" s="12" t="inlineStr">
         <is>
-          <t>yogeshmalviya1313@gmail.com</t>
+          <t>abhiscalping2625@gmail.com</t>
         </is>
       </c>
       <c r="E452" s="12" t="inlineStr">
         <is>
-          <t>8989262596</t>
+          <t>7905666582</t>
         </is>
       </c>
       <c r="F452" s="12" t="inlineStr">
@@ -33401,34 +33401,34 @@
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H452" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I452" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J452" s="14" t="n">
-        <v>1976</v>
+        <v>4230</v>
       </c>
       <c r="K452" s="14" t="n">
-        <v>15610</v>
+        <v>15660</v>
       </c>
       <c r="L452" s="15" t="n">
-        <v>3952</v>
+        <v>4230</v>
       </c>
       <c r="M452" s="12" t="inlineStr">
         <is>
-          <t>6a20398f997af1001360a84c</t>
+          <t>69d4de9898622b0013d1d543</t>
         </is>
       </c>
       <c r="N452" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a20398f997af1001360a84c</t>
+          <t>https://superprofile.bio/vig/69d4de9898622b0013d1d543</t>
         </is>
       </c>
       <c r="O452" s="17" t="inlineStr">
@@ -33448,22 +33448,22 @@
       </c>
       <c r="B453" s="20" t="inlineStr">
         <is>
-          <t>65d57aff5bdff5001412cd90</t>
+          <t>6a2036382888a500137bb912</t>
         </is>
       </c>
       <c r="C453" s="20" t="inlineStr">
         <is>
-          <t>finpranjal</t>
+          <t>yvstocks</t>
         </is>
       </c>
       <c r="D453" s="19" t="inlineStr">
         <is>
-          <t>rajan.pdy7@gmail.com</t>
+          <t>yogeshmalviya1313@gmail.com</t>
         </is>
       </c>
       <c r="E453" s="19" t="inlineStr">
         <is>
-          <t>9140134121</t>
+          <t>8989262596</t>
         </is>
       </c>
       <c r="F453" s="19" t="inlineStr">
@@ -33478,29 +33478,29 @@
       </c>
       <c r="H453" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I453" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J453" s="21" t="n">
-        <v>1964</v>
+        <v>1976</v>
       </c>
       <c r="K453" s="21" t="n">
-        <v>15516</v>
+        <v>15610</v>
       </c>
       <c r="L453" s="22" t="n">
-        <v>3732</v>
+        <v>3952</v>
       </c>
       <c r="M453" s="19" t="inlineStr">
         <is>
-          <t>69b6b0c5b8fa0b0014df6f9a</t>
+          <t>6a20398f997af1001360a84c</t>
         </is>
       </c>
       <c r="N453" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b6b0c5b8fa0b0014df6f9a</t>
+          <t>https://superprofile.bio/vig/6a20398f997af1001360a84c</t>
         </is>
       </c>
       <c r="O453" s="24" t="inlineStr">
@@ -33520,22 +33520,22 @@
       </c>
       <c r="B454" s="13" t="inlineStr">
         <is>
-          <t>63b5b2f786e809002c31628f</t>
+          <t>65d57aff5bdff5001412cd90</t>
         </is>
       </c>
       <c r="C454" s="13" t="inlineStr">
         <is>
-          <t>stock1ndex</t>
+          <t>finpranjal</t>
         </is>
       </c>
       <c r="D454" s="12" t="inlineStr">
         <is>
-          <t>raopreet208@gmail.com</t>
+          <t>rajan.pdy7@gmail.com</t>
         </is>
       </c>
       <c r="E454" s="12" t="inlineStr">
         <is>
-          <t>9518180694</t>
+          <t>9140134121</t>
         </is>
       </c>
       <c r="F454" s="12" t="inlineStr">
@@ -33545,7 +33545,7 @@
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H454" s="12" t="inlineStr">
@@ -33554,25 +33554,25 @@
         </is>
       </c>
       <c r="I454" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J454" s="14" t="n">
-        <v>2249</v>
+        <v>1964</v>
       </c>
       <c r="K454" s="14" t="n">
-        <v>15471</v>
+        <v>15516</v>
       </c>
       <c r="L454" s="15" t="n">
-        <v>3058</v>
+        <v>3732</v>
       </c>
       <c r="M454" s="12" t="inlineStr">
         <is>
-          <t>64772c61a5e1ac0020b87a6b</t>
+          <t>69b6b0c5b8fa0b0014df6f9a</t>
         </is>
       </c>
       <c r="N454" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64772c61a5e1ac0020b87a6b</t>
+          <t>https://superprofile.bio/vig/69b6b0c5b8fa0b0014df6f9a</t>
         </is>
       </c>
       <c r="O454" s="17" t="inlineStr">
@@ -33592,22 +33592,22 @@
       </c>
       <c r="B455" s="20" t="inlineStr">
         <is>
-          <t>6a0489783a48f8001349af38</t>
+          <t>63b5b2f786e809002c31628f</t>
         </is>
       </c>
       <c r="C455" s="20" t="inlineStr">
         <is>
-          <t>traderharneet</t>
+          <t>stock1ndex</t>
         </is>
       </c>
       <c r="D455" s="19" t="inlineStr">
         <is>
-          <t>coolhoney1988@gmail.com</t>
+          <t>raopreet208@gmail.com</t>
         </is>
       </c>
       <c r="E455" s="19" t="inlineStr">
         <is>
-          <t>7838700608</t>
+          <t>9518180694</t>
         </is>
       </c>
       <c r="F455" s="19" t="inlineStr">
@@ -33617,34 +33617,34 @@
       </c>
       <c r="G455" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H455" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I455" s="20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J455" s="21" t="n">
-        <v>10004</v>
+        <v>2249</v>
       </c>
       <c r="K455" s="21" t="n">
-        <v>15434</v>
+        <v>15471</v>
       </c>
       <c r="L455" s="22" t="n">
-        <v>10004</v>
+        <v>3058</v>
       </c>
       <c r="M455" s="19" t="inlineStr">
         <is>
-          <t>6a3e5b90c5eee700135eeea8</t>
+          <t>64772c61a5e1ac0020b87a6b</t>
         </is>
       </c>
       <c r="N455" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3e5b90c5eee700135eeea8</t>
+          <t>https://superprofile.bio/vig/64772c61a5e1ac0020b87a6b</t>
         </is>
       </c>
       <c r="O455" s="24" t="inlineStr">
@@ -33664,22 +33664,22 @@
       </c>
       <c r="B456" s="13" t="inlineStr">
         <is>
-          <t>6a07df7c7c5fcd00133a6e3b</t>
+          <t>6a0489783a48f8001349af38</t>
         </is>
       </c>
       <c r="C456" s="13" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>traderharneet</t>
         </is>
       </c>
       <c r="D456" s="12" t="inlineStr">
         <is>
-          <t>experttrading874@gmail.com</t>
+          <t>coolhoney1988@gmail.com</t>
         </is>
       </c>
       <c r="E456" s="12" t="inlineStr">
         <is>
-          <t>6377727003</t>
+          <t>7838700608</t>
         </is>
       </c>
       <c r="F456" s="12" t="inlineStr">
@@ -33689,34 +33689,34 @@
       </c>
       <c r="G456" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H456" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I456" s="13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J456" s="14" t="n">
-        <v>1127</v>
+        <v>10004</v>
       </c>
       <c r="K456" s="14" t="n">
-        <v>15415</v>
+        <v>15434</v>
       </c>
       <c r="L456" s="15" t="n">
-        <v>3762</v>
+        <v>10004</v>
       </c>
       <c r="M456" s="12" t="inlineStr">
         <is>
-          <t>6a088c367c5fcd00135ca723</t>
+          <t>6a3e5b90c5eee700135eeea8</t>
         </is>
       </c>
       <c r="N456" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
+          <t>https://superprofile.bio/vig/6a3e5b90c5eee700135eeea8</t>
         </is>
       </c>
       <c r="O456" s="17" t="inlineStr">
@@ -33736,22 +33736,22 @@
       </c>
       <c r="B457" s="20" t="inlineStr">
         <is>
-          <t>67113f1b17d5ab001325c3a7</t>
+          <t>6a07df7c7c5fcd00133a6e3b</t>
         </is>
       </c>
       <c r="C457" s="20" t="inlineStr">
         <is>
-          <t>anshika7566</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="D457" s="19" t="inlineStr">
         <is>
-          <t>suhani93991@gmail.com</t>
+          <t>experttrading874@gmail.com</t>
         </is>
       </c>
       <c r="E457" s="19" t="inlineStr">
         <is>
-          <t>9399158129</t>
+          <t>6377727003</t>
         </is>
       </c>
       <c r="F457" s="19" t="inlineStr">
@@ -33761,34 +33761,34 @@
       </c>
       <c r="G457" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H457" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I457" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J457" s="21" t="n">
-        <v>11982</v>
+        <v>1127</v>
       </c>
       <c r="K457" s="21" t="n">
-        <v>15337</v>
+        <v>15415</v>
       </c>
       <c r="L457" s="22" t="n">
-        <v>11982</v>
+        <v>3762</v>
       </c>
       <c r="M457" s="19" t="inlineStr">
         <is>
-          <t>676154f99babf600134329a6</t>
+          <t>6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="N457" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676154f99babf600134329a6</t>
+          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="O457" s="24" t="inlineStr">
@@ -33808,22 +33808,22 @@
       </c>
       <c r="B458" s="13" t="inlineStr">
         <is>
-          <t>68edde8bd4a4db0013530331</t>
+          <t>67113f1b17d5ab001325c3a7</t>
         </is>
       </c>
       <c r="C458" s="13" t="inlineStr">
         <is>
-          <t>httpstmetheforexfund</t>
+          <t>anshika7566</t>
         </is>
       </c>
       <c r="D458" s="12" t="inlineStr">
         <is>
-          <t>salimjadu90@gmail.com</t>
+          <t>suhani93991@gmail.com</t>
         </is>
       </c>
       <c r="E458" s="12" t="inlineStr">
         <is>
-          <t>8279903733</t>
+          <t>9399158129</t>
         </is>
       </c>
       <c r="F458" s="12" t="inlineStr">
@@ -33833,34 +33833,34 @@
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H458" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I458" s="13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J458" s="14" t="n">
-        <v>1881</v>
+        <v>11982</v>
       </c>
       <c r="K458" s="14" t="n">
-        <v>15049</v>
+        <v>15337</v>
       </c>
       <c r="L458" s="15" t="n">
-        <v>2822</v>
+        <v>11982</v>
       </c>
       <c r="M458" s="12" t="inlineStr">
         <is>
-          <t>69974b6011c3e90013a068fc</t>
+          <t>676154f99babf600134329a6</t>
         </is>
       </c>
       <c r="N458" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69974b6011c3e90013a068fc</t>
+          <t>https://superprofile.bio/vig/676154f99babf600134329a6</t>
         </is>
       </c>
       <c r="O458" s="17" t="inlineStr">
@@ -33880,22 +33880,22 @@
       </c>
       <c r="B459" s="20" t="inlineStr">
         <is>
-          <t>677a802db8a1e400132a1a88</t>
+          <t>68edde8bd4a4db0013530331</t>
         </is>
       </c>
       <c r="C459" s="20" t="inlineStr">
         <is>
-          <t>likithprasadbn6343</t>
+          <t>httpstmetheforexfund</t>
         </is>
       </c>
       <c r="D459" s="19" t="inlineStr">
         <is>
-          <t>likithprasadbn@gmail.com</t>
+          <t>salimjadu90@gmail.com</t>
         </is>
       </c>
       <c r="E459" s="19" t="inlineStr">
         <is>
-          <t>8123114047</t>
+          <t>8279903733</t>
         </is>
       </c>
       <c r="F459" s="19" t="inlineStr">
@@ -33905,34 +33905,34 @@
       </c>
       <c r="G459" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H459" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I459" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J459" s="21" t="n">
-        <v>7520</v>
+        <v>1881</v>
       </c>
       <c r="K459" s="21" t="n">
-        <v>15040</v>
+        <v>15049</v>
       </c>
       <c r="L459" s="22" t="n">
-        <v>7520</v>
+        <v>2822</v>
       </c>
       <c r="M459" s="19" t="inlineStr">
         <is>
-          <t>6a2ef7b6e7feae001338a244</t>
+          <t>69974b6011c3e90013a068fc</t>
         </is>
       </c>
       <c r="N459" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a2ef7b6e7feae001338a244</t>
+          <t>https://superprofile.bio/vig/69974b6011c3e90013a068fc</t>
         </is>
       </c>
       <c r="O459" s="24" t="inlineStr">
@@ -33952,22 +33952,22 @@
       </c>
       <c r="B460" s="13" t="inlineStr">
         <is>
-          <t>68f5e1cdf03b9000131c0fc2</t>
+          <t>677a802db8a1e400132a1a88</t>
         </is>
       </c>
       <c r="C460" s="13" t="inlineStr">
         <is>
-          <t>dampro4</t>
+          <t>likithprasadbn6343</t>
         </is>
       </c>
       <c r="D460" s="12" t="inlineStr">
         <is>
-          <t>damu.tanishq@gmail.com</t>
+          <t>likithprasadbn@gmail.com</t>
         </is>
       </c>
       <c r="E460" s="12" t="inlineStr">
         <is>
-          <t>9789853922</t>
+          <t>8123114047</t>
         </is>
       </c>
       <c r="F460" s="12" t="inlineStr">
@@ -33982,29 +33982,29 @@
       </c>
       <c r="H460" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I460" s="13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J460" s="14" t="n">
-        <v>3214</v>
+        <v>7520</v>
       </c>
       <c r="K460" s="14" t="n">
-        <v>14876</v>
+        <v>15040</v>
       </c>
       <c r="L460" s="15" t="n">
-        <v>3214</v>
+        <v>7520</v>
       </c>
       <c r="M460" s="12" t="inlineStr">
         <is>
-          <t>6a1fd35f62b0ef0013c02680</t>
+          <t>6a2ef7b6e7feae001338a244</t>
         </is>
       </c>
       <c r="N460" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a1fd35f62b0ef0013c02680</t>
+          <t>https://superprofile.bio/vig/6a2ef7b6e7feae001338a244</t>
         </is>
       </c>
       <c r="O460" s="17" t="inlineStr">
@@ -34024,22 +34024,22 @@
       </c>
       <c r="B461" s="20" t="inlineStr">
         <is>
-          <t>64b0ea441e6e1b002a2b2802</t>
+          <t>68f5e1cdf03b9000131c0fc2</t>
         </is>
       </c>
       <c r="C461" s="20" t="inlineStr">
         <is>
-          <t>alfaearning</t>
+          <t>dampro4</t>
         </is>
       </c>
       <c r="D461" s="19" t="inlineStr">
         <is>
-          <t>tcmall9987@gmail.com</t>
+          <t>damu.tanishq@gmail.com</t>
         </is>
       </c>
       <c r="E461" s="19" t="inlineStr">
         <is>
-          <t>7668471271</t>
+          <t>9789853922</t>
         </is>
       </c>
       <c r="F461" s="19" t="inlineStr">
@@ -34049,34 +34049,34 @@
       </c>
       <c r="G461" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H461" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I461" s="20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J461" s="21" t="n">
-        <v>14646</v>
+        <v>3214</v>
       </c>
       <c r="K461" s="21" t="n">
-        <v>14646</v>
+        <v>14876</v>
       </c>
       <c r="L461" s="22" t="n">
-        <v>14646</v>
+        <v>3214</v>
       </c>
       <c r="M461" s="19" t="inlineStr">
         <is>
-          <t>66596deaeec07b001310d2df</t>
+          <t>6a1fd35f62b0ef0013c02680</t>
         </is>
       </c>
       <c r="N461" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66596deaeec07b001310d2df</t>
+          <t>https://superprofile.bio/vig/6a1fd35f62b0ef0013c02680</t>
         </is>
       </c>
       <c r="O461" s="24" t="inlineStr">
@@ -34096,22 +34096,22 @@
       </c>
       <c r="B462" s="13" t="inlineStr">
         <is>
-          <t>67222b9c5ea5240013ca5e36</t>
+          <t>64b0ea441e6e1b002a2b2802</t>
         </is>
       </c>
       <c r="C462" s="13" t="inlineStr">
         <is>
-          <t>nidhishah9366</t>
+          <t>alfaearning</t>
         </is>
       </c>
       <c r="D462" s="12" t="inlineStr">
         <is>
-          <t>nidhishah9366@gmail.com</t>
+          <t>tcmall9987@gmail.com</t>
         </is>
       </c>
       <c r="E462" s="12" t="inlineStr">
         <is>
-          <t>9427741411</t>
+          <t>7668471271</t>
         </is>
       </c>
       <c r="F462" s="12" t="inlineStr">
@@ -34121,34 +34121,34 @@
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H462" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I462" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J462" s="14" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="K462" s="14" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="L462" s="15" t="n">
-        <v>14628</v>
+        <v>14646</v>
       </c>
       <c r="M462" s="12" t="inlineStr">
         <is>
-          <t>674947b2098ae70013379485</t>
+          <t>66596deaeec07b001310d2df</t>
         </is>
       </c>
       <c r="N462" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/674947b2098ae70013379485</t>
+          <t>https://superprofile.bio/vig/66596deaeec07b001310d2df</t>
         </is>
       </c>
       <c r="O462" s="17" t="inlineStr">
@@ -34168,22 +34168,22 @@
       </c>
       <c r="B463" s="20" t="inlineStr">
         <is>
-          <t>65c8c3e0e0e11f001e86446f</t>
+          <t>67222b9c5ea5240013ca5e36</t>
         </is>
       </c>
       <c r="C463" s="20" t="inlineStr">
         <is>
-          <t>edgeadmin</t>
+          <t>nidhishah9366</t>
         </is>
       </c>
       <c r="D463" s="19" t="inlineStr">
         <is>
-          <t>nimmii5151@gmail.com</t>
+          <t>nidhishah9366@gmail.com</t>
         </is>
       </c>
       <c r="E463" s="19" t="inlineStr">
         <is>
-          <t>8085115151</t>
+          <t>9427741411</t>
         </is>
       </c>
       <c r="F463" s="19" t="inlineStr">
@@ -34193,34 +34193,34 @@
       </c>
       <c r="G463" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H463" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I463" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J463" s="21" t="n">
-        <v>2907</v>
+        <v>14628</v>
       </c>
       <c r="K463" s="21" t="n">
-        <v>14535</v>
+        <v>14628</v>
       </c>
       <c r="L463" s="22" t="n">
-        <v>4845</v>
+        <v>14628</v>
       </c>
       <c r="M463" s="19" t="inlineStr">
         <is>
-          <t>66371b2d0b57770013e4942f</t>
+          <t>674947b2098ae70013379485</t>
         </is>
       </c>
       <c r="N463" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
+          <t>https://superprofile.bio/vig/674947b2098ae70013379485</t>
         </is>
       </c>
       <c r="O463" s="24" t="inlineStr">
@@ -34240,22 +34240,22 @@
       </c>
       <c r="B464" s="13" t="inlineStr">
         <is>
-          <t>63cf83e4603a1c00332a3516</t>
+          <t>65c8c3e0e0e11f001e86446f</t>
         </is>
       </c>
       <c r="C464" s="13" t="inlineStr">
         <is>
-          <t>repleteequities</t>
+          <t>edgeadmin</t>
         </is>
       </c>
       <c r="D464" s="12" t="inlineStr">
         <is>
-          <t>sachin@repleteequities.com</t>
+          <t>nimmii5151@gmail.com</t>
         </is>
       </c>
       <c r="E464" s="12" t="inlineStr">
         <is>
-          <t>7229945555</t>
+          <t>8085115151</t>
         </is>
       </c>
       <c r="F464" s="12" t="inlineStr">
@@ -34265,34 +34265,34 @@
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H464" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I464" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J464" s="14" t="n">
-        <v>14468</v>
+        <v>2907</v>
       </c>
       <c r="K464" s="14" t="n">
-        <v>14468</v>
+        <v>14535</v>
       </c>
       <c r="L464" s="15" t="n">
-        <v>14468</v>
+        <v>4845</v>
       </c>
       <c r="M464" s="12" t="inlineStr">
         <is>
-          <t>695e07b1813efa0013b5b56c</t>
+          <t>66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="N464" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/695e07b1813efa0013b5b56c</t>
+          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="O464" s="17" t="inlineStr">
@@ -34312,22 +34312,22 @@
       </c>
       <c r="B465" s="20" t="inlineStr">
         <is>
-          <t>654f049b0ce920001de81c27</t>
+          <t>63cf83e4603a1c00332a3516</t>
         </is>
       </c>
       <c r="C465" s="20" t="inlineStr">
         <is>
-          <t>Shiv09</t>
+          <t>repleteequities</t>
         </is>
       </c>
       <c r="D465" s="19" t="inlineStr">
         <is>
-          <t>shivrajdangi63@gmail.com</t>
+          <t>sachin@repleteequities.com</t>
         </is>
       </c>
       <c r="E465" s="19" t="inlineStr">
         <is>
-          <t>9301596441</t>
+          <t>7229945555</t>
         </is>
       </c>
       <c r="F465" s="19" t="inlineStr">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="G465" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H465" s="19" t="inlineStr">
@@ -34346,25 +34346,25 @@
         </is>
       </c>
       <c r="I465" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J465" s="21" t="n">
-        <v>4822</v>
+        <v>14468</v>
       </c>
       <c r="K465" s="21" t="n">
-        <v>14466</v>
+        <v>14468</v>
       </c>
       <c r="L465" s="22" t="n">
-        <v>4822</v>
+        <v>14468</v>
       </c>
       <c r="M465" s="19" t="inlineStr">
         <is>
-          <t>69ecbffeaa29900013b94540</t>
+          <t>695e07b1813efa0013b5b56c</t>
         </is>
       </c>
       <c r="N465" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ecbffeaa29900013b94540</t>
+          <t>https://superprofile.bio/vig/695e07b1813efa0013b5b56c</t>
         </is>
       </c>
       <c r="O465" s="24" t="inlineStr">
@@ -34384,22 +34384,22 @@
       </c>
       <c r="B466" s="13" t="inlineStr">
         <is>
-          <t>6513d6f6fa59f9001e0df913</t>
+          <t>654f049b0ce920001de81c27</t>
         </is>
       </c>
       <c r="C466" s="13" t="inlineStr">
         <is>
-          <t>stockvip</t>
+          <t>Shiv09</t>
         </is>
       </c>
       <c r="D466" s="12" t="inlineStr">
         <is>
-          <t>nky0998765@gmail.com</t>
+          <t>shivrajdangi63@gmail.com</t>
         </is>
       </c>
       <c r="E466" s="12" t="inlineStr">
         <is>
-          <t>9651479360</t>
+          <t>9301596441</t>
         </is>
       </c>
       <c r="F466" s="12" t="inlineStr">
@@ -34409,34 +34409,34 @@
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H466" s="12" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="H466" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
       <c r="I466" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J466" s="14" t="n">
-        <v>4002</v>
+        <v>4822</v>
       </c>
       <c r="K466" s="14" t="n">
-        <v>14427</v>
+        <v>14466</v>
       </c>
       <c r="L466" s="15" t="n">
-        <v>4002</v>
+        <v>4822</v>
       </c>
       <c r="M466" s="12" t="inlineStr">
         <is>
-          <t>69bbe0da3d80fd0013eac43d</t>
+          <t>69ecbffeaa29900013b94540</t>
         </is>
       </c>
       <c r="N466" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bbe0da3d80fd0013eac43d</t>
+          <t>https://superprofile.bio/vig/69ecbffeaa29900013b94540</t>
         </is>
       </c>
       <c r="O466" s="17" t="inlineStr">
@@ -34456,22 +34456,22 @@
       </c>
       <c r="B467" s="20" t="inlineStr">
         <is>
-          <t>6a817ca94329a10013f863c7</t>
+          <t>6513d6f6fa59f9001e0df913</t>
         </is>
       </c>
       <c r="C467" s="20" t="inlineStr">
         <is>
-          <t>Kamakshi4651</t>
+          <t>stockvip</t>
         </is>
       </c>
       <c r="D467" s="19" t="inlineStr">
         <is>
-          <t>kamakshisharma010897@gmail.com</t>
+          <t>nky0998765@gmail.com</t>
         </is>
       </c>
       <c r="E467" s="19" t="inlineStr">
         <is>
-          <t>7982384935</t>
+          <t>9651479360</t>
         </is>
       </c>
       <c r="F467" s="19" t="inlineStr">
@@ -34486,29 +34486,29 @@
       </c>
       <c r="H467" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I467" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J467" s="21" t="n">
-        <v>4239</v>
+        <v>4002</v>
       </c>
       <c r="K467" s="21" t="n">
-        <v>14374</v>
+        <v>14427</v>
       </c>
       <c r="L467" s="22" t="n">
-        <v>6737</v>
+        <v>4002</v>
       </c>
       <c r="M467" s="19" t="inlineStr">
         <is>
-          <t>69d5fd9e6bc2960013708810</t>
+          <t>69bbe0da3d80fd0013eac43d</t>
         </is>
       </c>
       <c r="N467" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d5fd9e6bc2960013708810</t>
+          <t>https://superprofile.bio/vig/69bbe0da3d80fd0013eac43d</t>
         </is>
       </c>
       <c r="O467" s="24" t="inlineStr">
@@ -34528,22 +34528,22 @@
       </c>
       <c r="B468" s="13" t="inlineStr">
         <is>
-          <t>6466fe894600ce00214fabd6</t>
+          <t>6a817ca94329a10013f863c7</t>
         </is>
       </c>
       <c r="C468" s="13" t="inlineStr">
         <is>
-          <t>daytraders247</t>
+          <t>Kamakshi4651</t>
         </is>
       </c>
       <c r="D468" s="12" t="inlineStr">
         <is>
-          <t>dj025820@gmail.com</t>
+          <t>kamakshisharma010897@gmail.com</t>
         </is>
       </c>
       <c r="E468" s="12" t="inlineStr">
         <is>
-          <t>9587744549</t>
+          <t>7982384935</t>
         </is>
       </c>
       <c r="F468" s="12" t="inlineStr">
@@ -34553,7 +34553,7 @@
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H468" s="12" t="inlineStr">
@@ -34562,25 +34562,25 @@
         </is>
       </c>
       <c r="I468" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J468" s="14" t="n">
-        <v>1996</v>
+        <v>4239</v>
       </c>
       <c r="K468" s="14" t="n">
-        <v>14366</v>
+        <v>14374</v>
       </c>
       <c r="L468" s="15" t="n">
-        <v>5716</v>
+        <v>6737</v>
       </c>
       <c r="M468" s="12" t="inlineStr">
         <is>
-          <t>67d8393615497c0013a8e740</t>
+          <t>69d5fd9e6bc2960013708810</t>
         </is>
       </c>
       <c r="N468" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67d8393615497c0013a8e740</t>
+          <t>https://superprofile.bio/vig/69d5fd9e6bc2960013708810</t>
         </is>
       </c>
       <c r="O468" s="17" t="inlineStr">
@@ -34600,22 +34600,22 @@
       </c>
       <c r="B469" s="20" t="inlineStr">
         <is>
-          <t>6862c79da533ea0013816c2b</t>
+          <t>6466fe894600ce00214fabd6</t>
         </is>
       </c>
       <c r="C469" s="20" t="inlineStr">
         <is>
-          <t>ayaan044</t>
+          <t>daytraders247</t>
         </is>
       </c>
       <c r="D469" s="19" t="inlineStr">
         <is>
-          <t>ac.ajay2007@gmail.com</t>
+          <t>dj025820@gmail.com</t>
         </is>
       </c>
       <c r="E469" s="19" t="inlineStr">
         <is>
-          <t>7382965826</t>
+          <t>9587744549</t>
         </is>
       </c>
       <c r="F469" s="19" t="inlineStr">
@@ -34625,34 +34625,34 @@
       </c>
       <c r="G469" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H469" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I469" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J469" s="21" t="n">
-        <v>3200</v>
+        <v>1996</v>
       </c>
       <c r="K469" s="21" t="n">
-        <v>14300</v>
+        <v>14366</v>
       </c>
       <c r="L469" s="22" t="n">
-        <v>3200</v>
+        <v>5716</v>
       </c>
       <c r="M469" s="19" t="inlineStr">
         <is>
-          <t>686308ad4f94d1001380bc13</t>
+          <t>67d8393615497c0013a8e740</t>
         </is>
       </c>
       <c r="N469" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/686308ad4f94d1001380bc13</t>
+          <t>https://superprofile.bio/vig/67d8393615497c0013a8e740</t>
         </is>
       </c>
       <c r="O469" s="24" t="inlineStr">
@@ -34672,22 +34672,22 @@
       </c>
       <c r="B470" s="13" t="inlineStr">
         <is>
-          <t>64d2675c94b053001d508b71</t>
+          <t>6862c79da533ea0013816c2b</t>
         </is>
       </c>
       <c r="C470" s="13" t="inlineStr">
         <is>
-          <t>stocktrade007</t>
+          <t>ayaan044</t>
         </is>
       </c>
       <c r="D470" s="12" t="inlineStr">
         <is>
-          <t>tradewithme4999@gmail.com</t>
+          <t>ac.ajay2007@gmail.com</t>
         </is>
       </c>
       <c r="E470" s="12" t="inlineStr">
         <is>
-          <t>8380029432</t>
+          <t>7382965826</t>
         </is>
       </c>
       <c r="F470" s="12" t="inlineStr">
@@ -34697,34 +34697,34 @@
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H470" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I470" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J470" s="14" t="n">
-        <v>14114</v>
+        <v>3200</v>
       </c>
       <c r="K470" s="14" t="n">
-        <v>14114</v>
+        <v>14300</v>
       </c>
       <c r="L470" s="15" t="n">
-        <v>14114</v>
+        <v>3200</v>
       </c>
       <c r="M470" s="12" t="inlineStr">
         <is>
-          <t>6708475d1f46ee001371cb20</t>
+          <t>686308ad4f94d1001380bc13</t>
         </is>
       </c>
       <c r="N470" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6708475d1f46ee001371cb20</t>
+          <t>https://superprofile.bio/vig/686308ad4f94d1001380bc13</t>
         </is>
       </c>
       <c r="O470" s="17" t="inlineStr">
@@ -34744,22 +34744,22 @@
       </c>
       <c r="B471" s="20" t="inlineStr">
         <is>
-          <t>6961cac5209b3d00137110a2</t>
+          <t>64d2675c94b053001d508b71</t>
         </is>
       </c>
       <c r="C471" s="20" t="inlineStr">
         <is>
-          <t>tradingexpert02</t>
+          <t>stocktrade007</t>
         </is>
       </c>
       <c r="D471" s="19" t="inlineStr">
         <is>
-          <t>tradingexpert7180@gmail.com</t>
+          <t>tradewithme4999@gmail.com</t>
         </is>
       </c>
       <c r="E471" s="19" t="inlineStr">
         <is>
-          <t>9784944154</t>
+          <t>8380029432</t>
         </is>
       </c>
       <c r="F471" s="19" t="inlineStr">
@@ -34769,34 +34769,34 @@
       </c>
       <c r="G471" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H471" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I471" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J471" s="21" t="n">
-        <v>5644</v>
+        <v>14114</v>
       </c>
       <c r="K471" s="21" t="n">
-        <v>14110</v>
+        <v>14114</v>
       </c>
       <c r="L471" s="22" t="n">
-        <v>5644</v>
+        <v>14114</v>
       </c>
       <c r="M471" s="19" t="inlineStr">
         <is>
-          <t>696641d77445fa001320e5e2</t>
+          <t>6708475d1f46ee001371cb20</t>
         </is>
       </c>
       <c r="N471" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696641d77445fa001320e5e2</t>
+          <t>https://superprofile.bio/vig/6708475d1f46ee001371cb20</t>
         </is>
       </c>
       <c r="O471" s="24" t="inlineStr">
@@ -34816,22 +34816,22 @@
       </c>
       <c r="B472" s="13" t="inlineStr">
         <is>
-          <t>649510441a32ba0020928c2d</t>
+          <t>6961cac5209b3d00137110a2</t>
         </is>
       </c>
       <c r="C472" s="13" t="inlineStr">
         <is>
-          <t>OmiSakhalkar</t>
+          <t>tradingexpert02</t>
         </is>
       </c>
       <c r="D472" s="12" t="inlineStr">
         <is>
-          <t>sakhalkaronkar@gmail.com</t>
+          <t>tradingexpert7180@gmail.com</t>
         </is>
       </c>
       <c r="E472" s="12" t="inlineStr">
         <is>
-          <t>9011099529</t>
+          <t>9784944154</t>
         </is>
       </c>
       <c r="F472" s="12" t="inlineStr">
@@ -34841,34 +34841,34 @@
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H472" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I472" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J472" s="14" t="n">
-        <v>14070</v>
+        <v>5644</v>
       </c>
       <c r="K472" s="14" t="n">
-        <v>14070</v>
+        <v>14110</v>
       </c>
       <c r="L472" s="15" t="n">
-        <v>14070</v>
+        <v>5644</v>
       </c>
       <c r="M472" s="12" t="inlineStr">
         <is>
-          <t>6579601dc879dd001d37904a</t>
+          <t>696641d77445fa001320e5e2</t>
         </is>
       </c>
       <c r="N472" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6579601dc879dd001d37904a</t>
+          <t>https://superprofile.bio/vig/696641d77445fa001320e5e2</t>
         </is>
       </c>
       <c r="O472" s="17" t="inlineStr">
@@ -34888,22 +34888,22 @@
       </c>
       <c r="B473" s="20" t="inlineStr">
         <is>
-          <t>62c5bb24f712d10f2dd7bc09</t>
+          <t>649510441a32ba0020928c2d</t>
         </is>
       </c>
       <c r="C473" s="20" t="inlineStr">
         <is>
-          <t>elliottbabaacademy</t>
+          <t>OmiSakhalkar</t>
         </is>
       </c>
       <c r="D473" s="19" t="inlineStr">
         <is>
-          <t>Adarshrai82@gmail.com</t>
+          <t>sakhalkaronkar@gmail.com</t>
         </is>
       </c>
       <c r="E473" s="19" t="inlineStr">
         <is>
-          <t>8707812455</t>
+          <t>9011099529</t>
         </is>
       </c>
       <c r="F473" s="19" t="inlineStr">
@@ -34913,34 +34913,34 @@
       </c>
       <c r="G473" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H473" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I473" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J473" s="21" t="n">
-        <v>8679</v>
+        <v>14070</v>
       </c>
       <c r="K473" s="21" t="n">
-        <v>13983</v>
+        <v>14070</v>
       </c>
       <c r="L473" s="22" t="n">
-        <v>8679</v>
+        <v>14070</v>
       </c>
       <c r="M473" s="19" t="inlineStr">
         <is>
-          <t>65b158ed3b1a56001d47377e</t>
+          <t>6579601dc879dd001d37904a</t>
         </is>
       </c>
       <c r="N473" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65b158ed3b1a56001d47377e</t>
+          <t>https://superprofile.bio/vig/6579601dc879dd001d37904a</t>
         </is>
       </c>
       <c r="O473" s="24" t="inlineStr">
@@ -34960,22 +34960,22 @@
       </c>
       <c r="B474" s="13" t="inlineStr">
         <is>
-          <t>644f511bb09d34001fdba603</t>
+          <t>62c5bb24f712d10f2dd7bc09</t>
         </is>
       </c>
       <c r="C474" s="13" t="inlineStr">
         <is>
-          <t>manju235</t>
+          <t>elliottbabaacademy</t>
         </is>
       </c>
       <c r="D474" s="12" t="inlineStr">
         <is>
-          <t>sapnakanwarr2004@gmail.com</t>
+          <t>Adarshrai82@gmail.com</t>
         </is>
       </c>
       <c r="E474" s="12" t="inlineStr">
         <is>
-          <t>7877492320</t>
+          <t>8707812455</t>
         </is>
       </c>
       <c r="F474" s="12" t="inlineStr">
@@ -34990,29 +34990,29 @@
       </c>
       <c r="H474" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I474" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J474" s="14" t="n">
-        <v>2250</v>
+        <v>8679</v>
       </c>
       <c r="K474" s="14" t="n">
-        <v>13658</v>
+        <v>13983</v>
       </c>
       <c r="L474" s="15" t="n">
-        <v>9608</v>
+        <v>8679</v>
       </c>
       <c r="M474" s="12" t="inlineStr">
         <is>
-          <t>6a887a1347d8100013f8b797</t>
+          <t>65b158ed3b1a56001d47377e</t>
         </is>
       </c>
       <c r="N474" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a887a1347d8100013f8b797</t>
+          <t>https://superprofile.bio/vig/65b158ed3b1a56001d47377e</t>
         </is>
       </c>
       <c r="O474" s="17" t="inlineStr">
@@ -35032,22 +35032,22 @@
       </c>
       <c r="B475" s="20" t="inlineStr">
         <is>
-          <t>656af629903568001e5d9687</t>
+          <t>644f511bb09d34001fdba603</t>
         </is>
       </c>
       <c r="C475" s="20" t="inlineStr">
         <is>
-          <t>chartify</t>
+          <t>manju235</t>
         </is>
       </c>
       <c r="D475" s="19" t="inlineStr">
         <is>
-          <t>thedatafolder.in@gmail.com</t>
+          <t>sapnakanwarr2004@gmail.com</t>
         </is>
       </c>
       <c r="E475" s="19" t="inlineStr">
         <is>
-          <t>7250156505</t>
+          <t>7877492320</t>
         </is>
       </c>
       <c r="F475" s="19" t="inlineStr">
@@ -35057,34 +35057,34 @@
       </c>
       <c r="G475" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H475" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I475" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J475" s="21" t="n">
-        <v>1411</v>
+        <v>2250</v>
       </c>
       <c r="K475" s="21" t="n">
-        <v>13642</v>
+        <v>13658</v>
       </c>
       <c r="L475" s="22" t="n">
-        <v>9409</v>
+        <v>9608</v>
       </c>
       <c r="M475" s="19" t="inlineStr">
         <is>
-          <t>65aad20085e8b0001e15dd40</t>
+          <t>6a887a1347d8100013f8b797</t>
         </is>
       </c>
       <c r="N475" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65aad20085e8b0001e15dd40</t>
+          <t>https://superprofile.bio/vig/6a887a1347d8100013f8b797</t>
         </is>
       </c>
       <c r="O475" s="24" t="inlineStr">
@@ -35104,22 +35104,22 @@
       </c>
       <c r="B476" s="13" t="inlineStr">
         <is>
-          <t>64ac146aa698af0020798bce</t>
+          <t>656af629903568001e5d9687</t>
         </is>
       </c>
       <c r="C476" s="13" t="inlineStr">
         <is>
-          <t>TheBigBullPremium</t>
+          <t>chartify</t>
         </is>
       </c>
       <c r="D476" s="12" t="inlineStr">
         <is>
-          <t>Paymentqoohoo@gmail.com</t>
+          <t>thedatafolder.in@gmail.com</t>
         </is>
       </c>
       <c r="E476" s="12" t="inlineStr">
         <is>
-          <t>8115825949</t>
+          <t>7250156505</t>
         </is>
       </c>
       <c r="F476" s="12" t="inlineStr">
@@ -35129,34 +35129,34 @@
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H476" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I476" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J476" s="14" t="n">
-        <v>6727</v>
+        <v>1411</v>
       </c>
       <c r="K476" s="14" t="n">
-        <v>13618</v>
+        <v>13642</v>
       </c>
       <c r="L476" s="15" t="n">
-        <v>6891</v>
+        <v>9409</v>
       </c>
       <c r="M476" s="12" t="inlineStr">
         <is>
-          <t>67d96fae1b910100136f52e2</t>
+          <t>65aad20085e8b0001e15dd40</t>
         </is>
       </c>
       <c r="N476" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67d96fae1b910100136f52e2</t>
+          <t>https://superprofile.bio/vig/65aad20085e8b0001e15dd40</t>
         </is>
       </c>
       <c r="O476" s="17" t="inlineStr">
@@ -35176,22 +35176,22 @@
       </c>
       <c r="B477" s="20" t="inlineStr">
         <is>
-          <t>67a5b6121602340013351a38</t>
+          <t>64ac146aa698af0020798bce</t>
         </is>
       </c>
       <c r="C477" s="20" t="inlineStr">
         <is>
-          <t>sharemarketstudies</t>
+          <t>TheBigBullPremium</t>
         </is>
       </c>
       <c r="D477" s="19" t="inlineStr">
         <is>
-          <t>sharemarketstudies@gmail.com</t>
+          <t>Paymentqoohoo@gmail.com</t>
         </is>
       </c>
       <c r="E477" s="19" t="inlineStr">
         <is>
-          <t>7020684526</t>
+          <t>8115825949</t>
         </is>
       </c>
       <c r="F477" s="19" t="inlineStr">
@@ -35206,29 +35206,29 @@
       </c>
       <c r="H477" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I477" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J477" s="21" t="n">
-        <v>1939</v>
+        <v>6727</v>
       </c>
       <c r="K477" s="21" t="n">
-        <v>13573</v>
+        <v>13618</v>
       </c>
       <c r="L477" s="22" t="n">
-        <v>3878</v>
+        <v>6891</v>
       </c>
       <c r="M477" s="19" t="inlineStr">
         <is>
-          <t>687790a8beb3cd001320bdd5</t>
+          <t>67d96fae1b910100136f52e2</t>
         </is>
       </c>
       <c r="N477" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687790a8beb3cd001320bdd5</t>
+          <t>https://superprofile.bio/vig/67d96fae1b910100136f52e2</t>
         </is>
       </c>
       <c r="O477" s="24" t="inlineStr">
@@ -35248,22 +35248,22 @@
       </c>
       <c r="B478" s="13" t="inlineStr">
         <is>
-          <t>66d337800616ad00136e01e3</t>
+          <t>67a5b6121602340013351a38</t>
         </is>
       </c>
       <c r="C478" s="13" t="inlineStr">
         <is>
-          <t>optionanalysiswithyg</t>
+          <t>sharemarketstudies</t>
         </is>
       </c>
       <c r="D478" s="12" t="inlineStr">
         <is>
-          <t>prachidubey8149@gmail.com</t>
+          <t>sharemarketstudies@gmail.com</t>
         </is>
       </c>
       <c r="E478" s="12" t="inlineStr">
         <is>
-          <t>9569472350</t>
+          <t>7020684526</t>
         </is>
       </c>
       <c r="F478" s="12" t="inlineStr">
@@ -35273,34 +35273,34 @@
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H478" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I478" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J478" s="14" t="n">
-        <v>13499</v>
+        <v>1939</v>
       </c>
       <c r="K478" s="14" t="n">
-        <v>13499</v>
+        <v>13573</v>
       </c>
       <c r="L478" s="15" t="n">
-        <v>13499</v>
+        <v>3878</v>
       </c>
       <c r="M478" s="12" t="inlineStr">
         <is>
-          <t>69e7a0a8b9c4b70013bb3c26</t>
+          <t>687790a8beb3cd001320bdd5</t>
         </is>
       </c>
       <c r="N478" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e7a0a8b9c4b70013bb3c26</t>
+          <t>https://superprofile.bio/vig/687790a8beb3cd001320bdd5</t>
         </is>
       </c>
       <c r="O478" s="17" t="inlineStr">
@@ -35320,22 +35320,22 @@
       </c>
       <c r="B479" s="20" t="inlineStr">
         <is>
-          <t>632a9399c6a1534e767e54ed</t>
+          <t>66d337800616ad00136e01e3</t>
         </is>
       </c>
       <c r="C479" s="20" t="inlineStr">
         <is>
-          <t>twptechnology</t>
+          <t>optionanalysiswithyg</t>
         </is>
       </c>
       <c r="D479" s="19" t="inlineStr">
         <is>
-          <t>pratiksen537@gmail.com</t>
+          <t>prachidubey8149@gmail.com</t>
         </is>
       </c>
       <c r="E479" s="19" t="inlineStr">
         <is>
-          <t>9660741167</t>
+          <t>9569472350</t>
         </is>
       </c>
       <c r="F479" s="19" t="inlineStr">
@@ -35350,29 +35350,29 @@
       </c>
       <c r="H479" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I479" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J479" s="21" t="n">
-        <v>5399</v>
+        <v>13499</v>
       </c>
       <c r="K479" s="21" t="n">
-        <v>13497</v>
+        <v>13499</v>
       </c>
       <c r="L479" s="22" t="n">
-        <v>5399</v>
+        <v>13499</v>
       </c>
       <c r="M479" s="19" t="inlineStr">
         <is>
-          <t>6730b09e6f82800014f08ebd</t>
+          <t>69e7a0a8b9c4b70013bb3c26</t>
         </is>
       </c>
       <c r="N479" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6730b09e6f82800014f08ebd</t>
+          <t>https://superprofile.bio/vig/69e7a0a8b9c4b70013bb3c26</t>
         </is>
       </c>
       <c r="O479" s="24" t="inlineStr">
@@ -35392,22 +35392,22 @@
       </c>
       <c r="B480" s="13" t="inlineStr">
         <is>
-          <t>65237580a4e730001df28da0</t>
+          <t>632a9399c6a1534e767e54ed</t>
         </is>
       </c>
       <c r="C480" s="13" t="inlineStr">
         <is>
-          <t>chinmayonniftyy</t>
+          <t>twptechnology</t>
         </is>
       </c>
       <c r="D480" s="12" t="inlineStr">
         <is>
-          <t>chinmaypattanaik81@gmail.com</t>
+          <t>pratiksen537@gmail.com</t>
         </is>
       </c>
       <c r="E480" s="12" t="inlineStr">
         <is>
-          <t>8018863337</t>
+          <t>9660741167</t>
         </is>
       </c>
       <c r="F480" s="12" t="inlineStr">
@@ -35417,34 +35417,34 @@
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H480" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I480" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J480" s="14" t="n">
-        <v>1349</v>
+        <v>5399</v>
       </c>
       <c r="K480" s="14" t="n">
-        <v>13492</v>
+        <v>13497</v>
       </c>
       <c r="L480" s="15" t="n">
-        <v>5397</v>
+        <v>5399</v>
       </c>
       <c r="M480" s="12" t="inlineStr">
         <is>
-          <t>68b414cc3eef9400133fcbfd</t>
+          <t>6730b09e6f82800014f08ebd</t>
         </is>
       </c>
       <c r="N480" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b414cc3eef9400133fcbfd</t>
+          <t>https://superprofile.bio/vig/6730b09e6f82800014f08ebd</t>
         </is>
       </c>
       <c r="O480" s="17" t="inlineStr">
@@ -35464,22 +35464,22 @@
       </c>
       <c r="B481" s="20" t="inlineStr">
         <is>
-          <t>6621d37589535b0013f61137</t>
+          <t>65237580a4e730001df28da0</t>
         </is>
       </c>
       <c r="C481" s="20" t="inlineStr">
         <is>
-          <t>profitpulsetc</t>
+          <t>chinmayonniftyy</t>
         </is>
       </c>
       <c r="D481" s="19" t="inlineStr">
         <is>
-          <t>hs878365@gmail.com</t>
+          <t>chinmaypattanaik81@gmail.com</t>
         </is>
       </c>
       <c r="E481" s="19" t="inlineStr">
         <is>
-          <t>9915506472</t>
+          <t>8018863337</t>
         </is>
       </c>
       <c r="F481" s="19" t="inlineStr">
@@ -35489,34 +35489,34 @@
       </c>
       <c r="G481" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H481" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I481" s="20" t="n">
         <v>4</v>
       </c>
       <c r="J481" s="21" t="n">
-        <v>4047</v>
+        <v>1349</v>
       </c>
       <c r="K481" s="21" t="n">
-        <v>13490</v>
+        <v>13492</v>
       </c>
       <c r="L481" s="22" t="n">
-        <v>5396</v>
+        <v>5397</v>
       </c>
       <c r="M481" s="19" t="inlineStr">
         <is>
-          <t>6a6ee4c799878a00137be792</t>
+          <t>68b414cc3eef9400133fcbfd</t>
         </is>
       </c>
       <c r="N481" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6ee4c799878a00137be792</t>
+          <t>https://superprofile.bio/vig/68b414cc3eef9400133fcbfd</t>
         </is>
       </c>
       <c r="O481" s="24" t="inlineStr">
@@ -35536,22 +35536,22 @@
       </c>
       <c r="B482" s="13" t="inlineStr">
         <is>
-          <t>6242e87cb3d6b2171643fc96</t>
+          <t>6621d37589535b0013f61137</t>
         </is>
       </c>
       <c r="C482" s="13" t="inlineStr">
         <is>
-          <t>tradersush</t>
+          <t>profitpulsetc</t>
         </is>
       </c>
       <c r="D482" s="12" t="inlineStr">
         <is>
-          <t>sushanth.reddy14@gmail.com</t>
+          <t>hs878365@gmail.com</t>
         </is>
       </c>
       <c r="E482" s="12" t="inlineStr">
         <is>
-          <t>9502619211</t>
+          <t>9915506472</t>
         </is>
       </c>
       <c r="F482" s="12" t="inlineStr">
@@ -35561,7 +35561,7 @@
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H482" s="12" t="inlineStr">
@@ -35573,22 +35573,22 @@
         <v>4</v>
       </c>
       <c r="J482" s="14" t="n">
-        <v>3667</v>
+        <v>4047</v>
       </c>
       <c r="K482" s="14" t="n">
-        <v>13447</v>
+        <v>13490</v>
       </c>
       <c r="L482" s="15" t="n">
-        <v>3668</v>
+        <v>5396</v>
       </c>
       <c r="M482" s="12" t="inlineStr">
         <is>
-          <t>6a5935459f9db90013c93c33</t>
+          <t>6a6ee4c799878a00137be792</t>
         </is>
       </c>
       <c r="N482" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5935459f9db90013c93c33</t>
+          <t>https://superprofile.bio/vig/6a6ee4c799878a00137be792</t>
         </is>
       </c>
       <c r="O482" s="17" t="inlineStr">
@@ -35608,22 +35608,22 @@
       </c>
       <c r="B483" s="20" t="inlineStr">
         <is>
-          <t>6570843bf00260001e4d51c0</t>
+          <t>6242e87cb3d6b2171643fc96</t>
         </is>
       </c>
       <c r="C483" s="20" t="inlineStr">
         <is>
-          <t>SHARESHARK7</t>
+          <t>tradersush</t>
         </is>
       </c>
       <c r="D483" s="19" t="inlineStr">
         <is>
-          <t>Shareshark7@gmail.com</t>
+          <t>sushanth.reddy14@gmail.com</t>
         </is>
       </c>
       <c r="E483" s="19" t="inlineStr">
         <is>
-          <t>9289228409</t>
+          <t>9502619211</t>
         </is>
       </c>
       <c r="F483" s="19" t="inlineStr">
@@ -35633,34 +35633,34 @@
       </c>
       <c r="G483" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H483" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I483" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J483" s="21" t="n">
-        <v>4593</v>
+        <v>3667</v>
       </c>
       <c r="K483" s="21" t="n">
-        <v>13381</v>
+        <v>13447</v>
       </c>
       <c r="L483" s="22" t="n">
-        <v>8788</v>
+        <v>3668</v>
       </c>
       <c r="M483" s="19" t="inlineStr">
         <is>
-          <t>6570860cbcd285001db72761</t>
+          <t>6a5935459f9db90013c93c33</t>
         </is>
       </c>
       <c r="N483" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6570860cbcd285001db72761</t>
+          <t>https://superprofile.bio/vig/6a5935459f9db90013c93c33</t>
         </is>
       </c>
       <c r="O483" s="24" t="inlineStr">
@@ -35680,22 +35680,22 @@
       </c>
       <c r="B484" s="13" t="inlineStr">
         <is>
-          <t>641d5f230b2bd4001f31f7e2</t>
+          <t>6570843bf00260001e4d51c0</t>
         </is>
       </c>
       <c r="C484" s="13" t="inlineStr">
         <is>
-          <t>digitalgigz</t>
+          <t>SHARESHARK7</t>
         </is>
       </c>
       <c r="D484" s="12" t="inlineStr">
         <is>
-          <t>kataraanshuman@gmail.com</t>
+          <t>Shareshark7@gmail.com</t>
         </is>
       </c>
       <c r="E484" s="12" t="inlineStr">
         <is>
-          <t>9352895763</t>
+          <t>9289228409</t>
         </is>
       </c>
       <c r="F484" s="12" t="inlineStr">
@@ -35705,34 +35705,34 @@
       </c>
       <c r="G484" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H484" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I484" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J484" s="14" t="n">
-        <v>1039</v>
+        <v>4593</v>
       </c>
       <c r="K484" s="14" t="n">
-        <v>13272</v>
+        <v>13381</v>
       </c>
       <c r="L484" s="15" t="n">
-        <v>5176</v>
+        <v>8788</v>
       </c>
       <c r="M484" s="12" t="inlineStr">
         <is>
-          <t>6487f9b2910548002b45d51e</t>
+          <t>6570860cbcd285001db72761</t>
         </is>
       </c>
       <c r="N484" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6487f9b2910548002b45d51e</t>
+          <t>https://superprofile.bio/vig/6570860cbcd285001db72761</t>
         </is>
       </c>
       <c r="O484" s="17" t="inlineStr">
@@ -35752,22 +35752,22 @@
       </c>
       <c r="B485" s="20" t="inlineStr">
         <is>
-          <t>64b0fcd06794f2002a008a24</t>
+          <t>641d5f230b2bd4001f31f7e2</t>
         </is>
       </c>
       <c r="C485" s="20" t="inlineStr">
         <is>
-          <t>tradelikealph</t>
+          <t>digitalgigz</t>
         </is>
       </c>
       <c r="D485" s="19" t="inlineStr">
         <is>
-          <t>Bhupendradevda88@gmail.com</t>
+          <t>kataraanshuman@gmail.com</t>
         </is>
       </c>
       <c r="E485" s="19" t="inlineStr">
         <is>
-          <t>9724755466</t>
+          <t>9352895763</t>
         </is>
       </c>
       <c r="F485" s="19" t="inlineStr">
@@ -35782,29 +35782,29 @@
       </c>
       <c r="H485" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I485" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J485" s="21" t="n">
-        <v>6627</v>
+        <v>1039</v>
       </c>
       <c r="K485" s="21" t="n">
-        <v>13254</v>
+        <v>13272</v>
       </c>
       <c r="L485" s="22" t="n">
-        <v>6627</v>
+        <v>5176</v>
       </c>
       <c r="M485" s="19" t="inlineStr">
         <is>
-          <t>683ef78254f0f6001337b0b7</t>
+          <t>6487f9b2910548002b45d51e</t>
         </is>
       </c>
       <c r="N485" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/683ef78254f0f6001337b0b7</t>
+          <t>https://superprofile.bio/vig/6487f9b2910548002b45d51e</t>
         </is>
       </c>
       <c r="O485" s="24" t="inlineStr">
@@ -35824,22 +35824,22 @@
       </c>
       <c r="B486" s="13" t="inlineStr">
         <is>
-          <t>65f98afec189e300129e5a9b</t>
+          <t>64b0fcd06794f2002a008a24</t>
         </is>
       </c>
       <c r="C486" s="13" t="inlineStr">
         <is>
-          <t>lakhbirsingh</t>
+          <t>tradelikealph</t>
         </is>
       </c>
       <c r="D486" s="12" t="inlineStr">
         <is>
-          <t>lslsgill1@gmail.com</t>
+          <t>Bhupendradevda88@gmail.com</t>
         </is>
       </c>
       <c r="E486" s="12" t="inlineStr">
         <is>
-          <t>6284544022</t>
+          <t>9724755466</t>
         </is>
       </c>
       <c r="F486" s="12" t="inlineStr">
@@ -35849,34 +35849,34 @@
       </c>
       <c r="G486" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H486" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I486" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J486" s="14" t="n">
-        <v>13237</v>
+        <v>6627</v>
       </c>
       <c r="K486" s="14" t="n">
-        <v>13237</v>
+        <v>13254</v>
       </c>
       <c r="L486" s="15" t="n">
-        <v>13237</v>
+        <v>6627</v>
       </c>
       <c r="M486" s="12" t="inlineStr">
         <is>
-          <t>687dbec0e23517001389aaae</t>
+          <t>683ef78254f0f6001337b0b7</t>
         </is>
       </c>
       <c r="N486" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687dbec0e23517001389aaae</t>
+          <t>https://superprofile.bio/vig/683ef78254f0f6001337b0b7</t>
         </is>
       </c>
       <c r="O486" s="17" t="inlineStr">
@@ -35896,22 +35896,22 @@
       </c>
       <c r="B487" s="20" t="inlineStr">
         <is>
-          <t>66dfde423f7d89001324eb00</t>
+          <t>65f98afec189e300129e5a9b</t>
         </is>
       </c>
       <c r="C487" s="20" t="inlineStr">
         <is>
-          <t>raj4predict</t>
+          <t>lakhbirsingh</t>
         </is>
       </c>
       <c r="D487" s="19" t="inlineStr">
         <is>
-          <t>raj4predict@gmail.com</t>
+          <t>lslsgill1@gmail.com</t>
         </is>
       </c>
       <c r="E487" s="19" t="inlineStr">
         <is>
-          <t>8005726206</t>
+          <t>6284544022</t>
         </is>
       </c>
       <c r="F487" s="19" t="inlineStr">
@@ -35921,34 +35921,34 @@
       </c>
       <c r="G487" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H487" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I487" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J487" s="21" t="n">
-        <v>1439</v>
+        <v>13237</v>
       </c>
       <c r="K487" s="21" t="n">
-        <v>13163</v>
+        <v>13237</v>
       </c>
       <c r="L487" s="22" t="n">
-        <v>2939</v>
+        <v>13237</v>
       </c>
       <c r="M487" s="19" t="inlineStr">
         <is>
-          <t>68b7029fd08c8e0013da9b34</t>
+          <t>687dbec0e23517001389aaae</t>
         </is>
       </c>
       <c r="N487" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b7029fd08c8e0013da9b34</t>
+          <t>https://superprofile.bio/vig/687dbec0e23517001389aaae</t>
         </is>
       </c>
       <c r="O487" s="24" t="inlineStr">
@@ -35968,22 +35968,22 @@
       </c>
       <c r="B488" s="13" t="inlineStr">
         <is>
-          <t>62fded2fc251165bd614c60b</t>
+          <t>66dfde423f7d89001324eb00</t>
         </is>
       </c>
       <c r="C488" s="13" t="inlineStr">
         <is>
-          <t>Eagles</t>
+          <t>raj4predict</t>
         </is>
       </c>
       <c r="D488" s="12" t="inlineStr">
         <is>
-          <t>abhi120302378@gmail.com</t>
+          <t>raj4predict@gmail.com</t>
         </is>
       </c>
       <c r="E488" s="12" t="inlineStr">
         <is>
-          <t>8115000004</t>
+          <t>8005726206</t>
         </is>
       </c>
       <c r="F488" s="12" t="inlineStr">
@@ -35993,34 +35993,34 @@
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H488" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I488" s="13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J488" s="14" t="n">
-        <v>3902</v>
+        <v>1439</v>
       </c>
       <c r="K488" s="14" t="n">
-        <v>13136</v>
+        <v>13163</v>
       </c>
       <c r="L488" s="15" t="n">
-        <v>4373</v>
+        <v>2939</v>
       </c>
       <c r="M488" s="12" t="inlineStr">
         <is>
-          <t>68a590a3342f1300132334fa</t>
+          <t>68b7029fd08c8e0013da9b34</t>
         </is>
       </c>
       <c r="N488" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68a590a3342f1300132334fa</t>
+          <t>https://superprofile.bio/vig/68b7029fd08c8e0013da9b34</t>
         </is>
       </c>
       <c r="O488" s="17" t="inlineStr">
@@ -36040,22 +36040,22 @@
       </c>
       <c r="B489" s="20" t="inlineStr">
         <is>
-          <t>6a131bb7d14a790012e11a6f</t>
+          <t>62fded2fc251165bd614c60b</t>
         </is>
       </c>
       <c r="C489" s="20" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>Eagles</t>
         </is>
       </c>
       <c r="D489" s="19" t="inlineStr">
         <is>
-          <t>ffkatarka@gmail.com</t>
+          <t>abhi120302378@gmail.com</t>
         </is>
       </c>
       <c r="E489" s="19" t="inlineStr">
         <is>
-          <t>9101299533</t>
+          <t>8115000004</t>
         </is>
       </c>
       <c r="F489" s="19" t="inlineStr">
@@ -36074,25 +36074,25 @@
         </is>
       </c>
       <c r="I489" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J489" s="21" t="n">
-        <v>1976</v>
+        <v>3902</v>
       </c>
       <c r="K489" s="21" t="n">
-        <v>13081</v>
+        <v>13136</v>
       </c>
       <c r="L489" s="22" t="n">
-        <v>5834</v>
+        <v>4373</v>
       </c>
       <c r="M489" s="19" t="inlineStr">
         <is>
-          <t>6a6d9d5033211a001319c244</t>
+          <t>68a590a3342f1300132334fa</t>
         </is>
       </c>
       <c r="N489" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
+          <t>https://superprofile.bio/vig/68a590a3342f1300132334fa</t>
         </is>
       </c>
       <c r="O489" s="24" t="inlineStr">
@@ -36112,22 +36112,22 @@
       </c>
       <c r="B490" s="13" t="inlineStr">
         <is>
-          <t>67b1ea9ed639a7001338f759</t>
+          <t>6a131bb7d14a790012e11a6f</t>
         </is>
       </c>
       <c r="C490" s="13" t="inlineStr">
         <is>
-          <t>stockabc</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="D490" s="12" t="inlineStr">
         <is>
-          <t>pawankulkarni44@gmail.com</t>
+          <t>ffkatarka@gmail.com</t>
         </is>
       </c>
       <c r="E490" s="12" t="inlineStr">
         <is>
-          <t>8799004354</t>
+          <t>9101299533</t>
         </is>
       </c>
       <c r="F490" s="12" t="inlineStr">
@@ -36137,34 +36137,34 @@
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H490" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I490" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J490" s="14" t="n">
-        <v>3834</v>
+        <v>1976</v>
       </c>
       <c r="K490" s="14" t="n">
-        <v>13038</v>
+        <v>13081</v>
       </c>
       <c r="L490" s="15" t="n">
-        <v>3834</v>
+        <v>5834</v>
       </c>
       <c r="M490" s="12" t="inlineStr">
         <is>
-          <t>67b833993185250013a00cae</t>
+          <t>6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="N490" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67b833993185250013a00cae</t>
+          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="O490" s="17" t="inlineStr">
@@ -36184,22 +36184,22 @@
       </c>
       <c r="B491" s="20" t="inlineStr">
         <is>
-          <t>6325d0f3770ec476f4cfc1f7</t>
+          <t>67b1ea9ed639a7001338f759</t>
         </is>
       </c>
       <c r="C491" s="20" t="inlineStr">
         <is>
-          <t>investhealthy07</t>
+          <t>stockabc</t>
         </is>
       </c>
       <c r="D491" s="19" t="inlineStr">
         <is>
-          <t>ganrraj@gmail.com</t>
+          <t>pawankulkarni44@gmail.com</t>
         </is>
       </c>
       <c r="E491" s="19" t="inlineStr">
         <is>
-          <t>9372871592</t>
+          <t>8799004354</t>
         </is>
       </c>
       <c r="F491" s="19" t="inlineStr">
@@ -36209,34 +36209,34 @@
       </c>
       <c r="G491" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H491" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I491" s="20" t="n">
         <v>4</v>
       </c>
       <c r="J491" s="21" t="n">
-        <v>6575</v>
+        <v>3834</v>
       </c>
       <c r="K491" s="21" t="n">
-        <v>12954</v>
+        <v>13038</v>
       </c>
       <c r="L491" s="22" t="n">
-        <v>6575</v>
+        <v>3834</v>
       </c>
       <c r="M491" s="19" t="inlineStr">
         <is>
-          <t>66d9cb296ef79f00130ac417</t>
+          <t>67b833993185250013a00cae</t>
         </is>
       </c>
       <c r="N491" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66d9cb296ef79f00130ac417</t>
+          <t>https://superprofile.bio/vig/67b833993185250013a00cae</t>
         </is>
       </c>
       <c r="O491" s="24" t="inlineStr">
@@ -36256,22 +36256,22 @@
       </c>
       <c r="B492" s="13" t="inlineStr">
         <is>
-          <t>659d87354540b4001dc9c97a</t>
+          <t>6325d0f3770ec476f4cfc1f7</t>
         </is>
       </c>
       <c r="C492" s="13" t="inlineStr">
         <is>
-          <t>worldmosttrader</t>
+          <t>investhealthy07</t>
         </is>
       </c>
       <c r="D492" s="12" t="inlineStr">
         <is>
-          <t>rakeshkumar890529@gmail.com</t>
+          <t>ganrraj@gmail.com</t>
         </is>
       </c>
       <c r="E492" s="12" t="inlineStr">
         <is>
-          <t>8955640502</t>
+          <t>9372871592</t>
         </is>
       </c>
       <c r="F492" s="12" t="inlineStr">
@@ -36286,29 +36286,29 @@
       </c>
       <c r="H492" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I492" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J492" s="14" t="n">
-        <v>6471</v>
+        <v>6575</v>
       </c>
       <c r="K492" s="14" t="n">
-        <v>12942</v>
+        <v>12954</v>
       </c>
       <c r="L492" s="15" t="n">
-        <v>6471</v>
+        <v>6575</v>
       </c>
       <c r="M492" s="12" t="inlineStr">
         <is>
-          <t>67a988222b922d00136fd091</t>
+          <t>66d9cb296ef79f00130ac417</t>
         </is>
       </c>
       <c r="N492" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a988222b922d00136fd091</t>
+          <t>https://superprofile.bio/vig/66d9cb296ef79f00130ac417</t>
         </is>
       </c>
       <c r="O492" s="17" t="inlineStr">
@@ -36328,59 +36328,59 @@
       </c>
       <c r="B493" s="20" t="inlineStr">
         <is>
-          <t>63f5178f135a2c0020ebd0de</t>
+          <t>659d87354540b4001dc9c97a</t>
         </is>
       </c>
       <c r="C493" s="20" t="inlineStr">
         <is>
-          <t>dropouttradergaurav</t>
+          <t>worldmosttrader</t>
         </is>
       </c>
       <c r="D493" s="19" t="inlineStr">
         <is>
-          <t>dropouttradergaurav@gmail.com</t>
+          <t>rakeshkumar890529@gmail.com</t>
         </is>
       </c>
       <c r="E493" s="19" t="inlineStr">
         <is>
-          <t>8003506141</t>
+          <t>8955640502</t>
         </is>
       </c>
       <c r="F493" s="19" t="inlineStr">
         <is>
-          <t>Baljeet Singh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G493" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H493" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I493" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J493" s="21" t="n">
-        <v>9835</v>
+        <v>6471</v>
       </c>
       <c r="K493" s="21" t="n">
-        <v>12937</v>
+        <v>12942</v>
       </c>
       <c r="L493" s="22" t="n">
-        <v>9835</v>
+        <v>6471</v>
       </c>
       <c r="M493" s="19" t="inlineStr">
         <is>
-          <t>69e45d2b5275a70013bdf54d</t>
+          <t>67a988222b922d00136fd091</t>
         </is>
       </c>
       <c r="N493" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e45d2b5275a70013bdf54d</t>
+          <t>https://superprofile.bio/vig/67a988222b922d00136fd091</t>
         </is>
       </c>
       <c r="O493" s="24" t="inlineStr">
@@ -36400,59 +36400,59 @@
       </c>
       <c r="B494" s="13" t="inlineStr">
         <is>
-          <t>6a706f7f833cbc0013f492ff</t>
+          <t>63f5178f135a2c0020ebd0de</t>
         </is>
       </c>
       <c r="C494" s="13" t="inlineStr">
         <is>
-          <t>up14trader</t>
+          <t>dropouttradergaurav</t>
         </is>
       </c>
       <c r="D494" s="12" t="inlineStr">
         <is>
-          <t>vishal5882gupta@gmail.com</t>
+          <t>dropouttradergaurav@gmail.com</t>
         </is>
       </c>
       <c r="E494" s="12" t="inlineStr">
         <is>
-          <t>9958827936</t>
+          <t>8003506141</t>
         </is>
       </c>
       <c r="F494" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Baljeet Singh</t>
         </is>
       </c>
       <c r="G494" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H494" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I494" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J494" s="14" t="n">
-        <v>1060</v>
+        <v>9835</v>
       </c>
       <c r="K494" s="14" t="n">
-        <v>12762</v>
+        <v>12937</v>
       </c>
       <c r="L494" s="15" t="n">
-        <v>6402</v>
+        <v>9835</v>
       </c>
       <c r="M494" s="12" t="inlineStr">
         <is>
-          <t>6a71ae2b9b236b00138135f0</t>
+          <t>69e45d2b5275a70013bdf54d</t>
         </is>
       </c>
       <c r="N494" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a71ae2b9b236b00138135f0</t>
+          <t>https://superprofile.bio/vig/69e45d2b5275a70013bdf54d</t>
         </is>
       </c>
       <c r="O494" s="17" t="inlineStr">
@@ -36472,22 +36472,22 @@
       </c>
       <c r="B495" s="20" t="inlineStr">
         <is>
-          <t>6772b8406eb176001311b230</t>
+          <t>6a706f7f833cbc0013f492ff</t>
         </is>
       </c>
       <c r="C495" s="20" t="inlineStr">
         <is>
-          <t>stockmarathi</t>
+          <t>up14trader</t>
         </is>
       </c>
       <c r="D495" s="19" t="inlineStr">
         <is>
-          <t>sunilphule111@gmail.com</t>
+          <t>vishal5882gupta@gmail.com</t>
         </is>
       </c>
       <c r="E495" s="19" t="inlineStr">
         <is>
-          <t>8888898782</t>
+          <t>9958827936</t>
         </is>
       </c>
       <c r="F495" s="19" t="inlineStr">
@@ -36497,7 +36497,7 @@
       </c>
       <c r="G495" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H495" s="19" t="inlineStr">
@@ -36509,22 +36509,22 @@
         <v>5</v>
       </c>
       <c r="J495" s="21" t="n">
-        <v>2944</v>
+        <v>1060</v>
       </c>
       <c r="K495" s="21" t="n">
-        <v>12758</v>
+        <v>12762</v>
       </c>
       <c r="L495" s="22" t="n">
-        <v>3925</v>
+        <v>6402</v>
       </c>
       <c r="M495" s="19" t="inlineStr">
         <is>
-          <t>6a1e625c7efba80013fcdbc8</t>
+          <t>6a71ae2b9b236b00138135f0</t>
         </is>
       </c>
       <c r="N495" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a1e625c7efba80013fcdbc8</t>
+          <t>https://superprofile.bio/vig/6a71ae2b9b236b00138135f0</t>
         </is>
       </c>
       <c r="O495" s="24" t="inlineStr">
@@ -36544,22 +36544,22 @@
       </c>
       <c r="B496" s="13" t="inlineStr">
         <is>
-          <t>67d06a60fac4900013f6e7c8</t>
+          <t>6772b8406eb176001311b230</t>
         </is>
       </c>
       <c r="C496" s="13" t="inlineStr">
         <is>
-          <t>gainyourselfofficial</t>
+          <t>stockmarathi</t>
         </is>
       </c>
       <c r="D496" s="12" t="inlineStr">
         <is>
-          <t>dp540503@gmail.com</t>
+          <t>sunilphule111@gmail.com</t>
         </is>
       </c>
       <c r="E496" s="12" t="inlineStr">
         <is>
-          <t>8897083372</t>
+          <t>8888898782</t>
         </is>
       </c>
       <c r="F496" s="12" t="inlineStr">
@@ -36569,34 +36569,34 @@
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H496" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I496" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J496" s="14" t="n">
-        <v>1411</v>
+        <v>2944</v>
       </c>
       <c r="K496" s="14" t="n">
-        <v>12698</v>
+        <v>12758</v>
       </c>
       <c r="L496" s="15" t="n">
-        <v>5643</v>
+        <v>3925</v>
       </c>
       <c r="M496" s="12" t="inlineStr">
         <is>
-          <t>6a4bdb749abd7300134a20f7</t>
+          <t>6a1e625c7efba80013fcdbc8</t>
         </is>
       </c>
       <c r="N496" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
+          <t>https://superprofile.bio/vig/6a1e625c7efba80013fcdbc8</t>
         </is>
       </c>
       <c r="O496" s="17" t="inlineStr">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="B497" s="20" t="inlineStr">
         <is>
-          <t>66537525ca30a0001338502e</t>
+          <t>67d06a60fac4900013f6e7c8</t>
         </is>
       </c>
       <c r="C497" s="20" t="inlineStr">
         <is>
-          <t>traderscommunity</t>
+          <t>gainyourselfofficial</t>
         </is>
       </c>
       <c r="D497" s="19" t="inlineStr">
         <is>
-          <t>bullinvestors748@gmail.com</t>
+          <t>dp540503@gmail.com</t>
         </is>
       </c>
       <c r="E497" s="19" t="inlineStr">
         <is>
-          <t>7487831947</t>
+          <t>8897083372</t>
         </is>
       </c>
       <c r="F497" s="19" t="inlineStr">
@@ -36641,34 +36641,34 @@
       </c>
       <c r="G497" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H497" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I497" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J497" s="21" t="n">
-        <v>5857</v>
+        <v>1411</v>
       </c>
       <c r="K497" s="21" t="n">
-        <v>12689</v>
+        <v>12698</v>
       </c>
       <c r="L497" s="22" t="n">
-        <v>5857</v>
+        <v>5643</v>
       </c>
       <c r="M497" s="19" t="inlineStr">
         <is>
-          <t>67b41e23bd83f70013950cf8</t>
+          <t>6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="N497" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67b41e23bd83f70013950cf8</t>
+          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="O497" s="24" t="inlineStr">
@@ -36688,22 +36688,22 @@
       </c>
       <c r="B498" s="13" t="inlineStr">
         <is>
-          <t>65aa4e493c74f1001e4eab0f</t>
+          <t>66537525ca30a0001338502e</t>
         </is>
       </c>
       <c r="C498" s="13" t="inlineStr">
         <is>
-          <t>Menariyatrader</t>
+          <t>traderscommunity</t>
         </is>
       </c>
       <c r="D498" s="12" t="inlineStr">
         <is>
-          <t>menariyatrader@gmail.com</t>
+          <t>bullinvestors748@gmail.com</t>
         </is>
       </c>
       <c r="E498" s="12" t="inlineStr">
         <is>
-          <t>8078666589</t>
+          <t>7487831947</t>
         </is>
       </c>
       <c r="F498" s="12" t="inlineStr">
@@ -36713,34 +36713,34 @@
       </c>
       <c r="G498" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H498" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I498" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J498" s="14" t="n">
-        <v>2928</v>
+        <v>5857</v>
       </c>
       <c r="K498" s="14" t="n">
-        <v>12688</v>
+        <v>12689</v>
       </c>
       <c r="L498" s="15" t="n">
-        <v>2928</v>
+        <v>5857</v>
       </c>
       <c r="M498" s="12" t="inlineStr">
         <is>
-          <t>6475ea4a9c04530020d235b7</t>
+          <t>67b41e23bd83f70013950cf8</t>
         </is>
       </c>
       <c r="N498" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6475ea4a9c04530020d235b7</t>
+          <t>https://superprofile.bio/vig/67b41e23bd83f70013950cf8</t>
         </is>
       </c>
       <c r="O498" s="17" t="inlineStr">
@@ -36760,22 +36760,22 @@
       </c>
       <c r="B499" s="20" t="inlineStr">
         <is>
-          <t>653aa2aed87cd0001e6f4b77</t>
+          <t>65aa4e493c74f1001e4eab0f</t>
         </is>
       </c>
       <c r="C499" s="20" t="inlineStr">
         <is>
-          <t>SMTEDUCATION</t>
+          <t>Menariyatrader</t>
         </is>
       </c>
       <c r="D499" s="19" t="inlineStr">
         <is>
-          <t>Nagaichsandeep088@gmail.com</t>
+          <t>menariyatrader@gmail.com</t>
         </is>
       </c>
       <c r="E499" s="19" t="inlineStr">
         <is>
-          <t>7860426229</t>
+          <t>8078666589</t>
         </is>
       </c>
       <c r="F499" s="19" t="inlineStr">
@@ -36794,25 +36794,25 @@
         </is>
       </c>
       <c r="I499" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J499" s="21" t="n">
-        <v>1157</v>
+        <v>2928</v>
       </c>
       <c r="K499" s="21" t="n">
-        <v>12610</v>
+        <v>12688</v>
       </c>
       <c r="L499" s="22" t="n">
-        <v>3953</v>
+        <v>2928</v>
       </c>
       <c r="M499" s="19" t="inlineStr">
         <is>
-          <t>653b62f0e24744a9699b63c6</t>
+          <t>6475ea4a9c04530020d235b7</t>
         </is>
       </c>
       <c r="N499" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/653b62f0e24744a9699b63c6</t>
+          <t>https://superprofile.bio/vig/6475ea4a9c04530020d235b7</t>
         </is>
       </c>
       <c r="O499" s="24" t="inlineStr">
@@ -36832,22 +36832,22 @@
       </c>
       <c r="B500" s="13" t="inlineStr">
         <is>
-          <t>6541dfbbc8b47a001ec7f9ae</t>
+          <t>653aa2aed87cd0001e6f4b77</t>
         </is>
       </c>
       <c r="C500" s="13" t="inlineStr">
         <is>
-          <t>imock101</t>
+          <t>SMTEDUCATION</t>
         </is>
       </c>
       <c r="D500" s="12" t="inlineStr">
         <is>
-          <t>mrmchandsamota@gmail.com</t>
+          <t>Nagaichsandeep088@gmail.com</t>
         </is>
       </c>
       <c r="E500" s="12" t="inlineStr">
         <is>
-          <t>8505065646</t>
+          <t>7860426229</t>
         </is>
       </c>
       <c r="F500" s="12" t="inlineStr">
@@ -36857,34 +36857,34 @@
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H500" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I500" s="13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J500" s="14" t="n">
-        <v>1127</v>
+        <v>1157</v>
       </c>
       <c r="K500" s="14" t="n">
-        <v>12512</v>
+        <v>12610</v>
       </c>
       <c r="L500" s="15" t="n">
-        <v>5160</v>
+        <v>3953</v>
       </c>
       <c r="M500" s="12" t="inlineStr">
         <is>
-          <t>69eccd685fe24c0013aef1e2</t>
+          <t>653b62f0e24744a9699b63c6</t>
         </is>
       </c>
       <c r="N500" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69eccd685fe24c0013aef1e2</t>
+          <t>https://superprofile.bio/vig/653b62f0e24744a9699b63c6</t>
         </is>
       </c>
       <c r="O500" s="17" t="inlineStr">
@@ -36904,22 +36904,22 @@
       </c>
       <c r="B501" s="20" t="inlineStr">
         <is>
-          <t>62c3cb33b1e08041dcff0860</t>
+          <t>6541dfbbc8b47a001ec7f9ae</t>
         </is>
       </c>
       <c r="C501" s="20" t="inlineStr">
         <is>
-          <t>robotradehub</t>
+          <t>imock101</t>
         </is>
       </c>
       <c r="D501" s="19" t="inlineStr">
         <is>
-          <t>devdj.sidana@gmail.com</t>
+          <t>mrmchandsamota@gmail.com</t>
         </is>
       </c>
       <c r="E501" s="19" t="inlineStr">
         <is>
-          <t>9876112334</t>
+          <t>8505065646</t>
         </is>
       </c>
       <c r="F501" s="19" t="inlineStr">
@@ -36934,29 +36934,29 @@
       </c>
       <c r="H501" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I501" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J501" s="21" t="n">
-        <v>6347</v>
+        <v>1127</v>
       </c>
       <c r="K501" s="21" t="n">
-        <v>12450</v>
+        <v>12512</v>
       </c>
       <c r="L501" s="22" t="n">
-        <v>6347</v>
+        <v>5160</v>
       </c>
       <c r="M501" s="19" t="inlineStr">
         <is>
-          <t>682dbea97f92d2001340e1bf</t>
+          <t>69eccd685fe24c0013aef1e2</t>
         </is>
       </c>
       <c r="N501" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/682dbea97f92d2001340e1bf</t>
+          <t>https://superprofile.bio/vig/69eccd685fe24c0013aef1e2</t>
         </is>
       </c>
       <c r="O501" s="24" t="inlineStr">
@@ -36976,22 +36976,22 @@
       </c>
       <c r="B502" s="13" t="inlineStr">
         <is>
-          <t>6a5344a9b05af20013c2744e</t>
+          <t>62c3cb33b1e08041dcff0860</t>
         </is>
       </c>
       <c r="C502" s="13" t="inlineStr">
         <is>
-          <t>tradewithmrrathore</t>
+          <t>robotradehub</t>
         </is>
       </c>
       <c r="D502" s="12" t="inlineStr">
         <is>
-          <t>tradewithmrrathoreofficial@gmail.com</t>
+          <t>devdj.sidana@gmail.com</t>
         </is>
       </c>
       <c r="E502" s="12" t="inlineStr">
         <is>
-          <t>9179125919</t>
+          <t>9876112334</t>
         </is>
       </c>
       <c r="F502" s="12" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="G502" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H502" s="12" t="inlineStr">
@@ -37010,25 +37010,25 @@
         </is>
       </c>
       <c r="I502" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J502" s="14" t="n">
-        <v>7527</v>
+        <v>6347</v>
       </c>
       <c r="K502" s="14" t="n">
-        <v>12416</v>
+        <v>12450</v>
       </c>
       <c r="L502" s="15" t="n">
-        <v>7527</v>
+        <v>6347</v>
       </c>
       <c r="M502" s="12" t="inlineStr">
         <is>
-          <t>6a5352f6e2e0070014b37086</t>
+          <t>682dbea97f92d2001340e1bf</t>
         </is>
       </c>
       <c r="N502" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5352f6e2e0070014b37086</t>
+          <t>https://superprofile.bio/vig/682dbea97f92d2001340e1bf</t>
         </is>
       </c>
       <c r="O502" s="17" t="inlineStr">
@@ -37048,22 +37048,22 @@
       </c>
       <c r="B503" s="20" t="inlineStr">
         <is>
-          <t>647c264b14366b002a85f133</t>
+          <t>6a5344a9b05af20013c2744e</t>
         </is>
       </c>
       <c r="C503" s="20" t="inlineStr">
         <is>
-          <t>thekaranpaid</t>
+          <t>tradewithmrrathore</t>
         </is>
       </c>
       <c r="D503" s="19" t="inlineStr">
         <is>
-          <t>amitdhamecha5@gmail.com</t>
+          <t>tradewithmrrathoreofficial@gmail.com</t>
         </is>
       </c>
       <c r="E503" s="19" t="inlineStr">
         <is>
-          <t>9033997421</t>
+          <t>9179125919</t>
         </is>
       </c>
       <c r="F503" s="19" t="inlineStr">
@@ -37078,29 +37078,29 @@
       </c>
       <c r="H503" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I503" s="20" t="n">
         <v>4</v>
       </c>
       <c r="J503" s="21" t="n">
-        <v>1972</v>
+        <v>7527</v>
       </c>
       <c r="K503" s="21" t="n">
-        <v>12281</v>
+        <v>12416</v>
       </c>
       <c r="L503" s="22" t="n">
-        <v>6365</v>
+        <v>7527</v>
       </c>
       <c r="M503" s="19" t="inlineStr">
         <is>
-          <t>69c77b6f8c802f00131a9b15</t>
+          <t>6a5352f6e2e0070014b37086</t>
         </is>
       </c>
       <c r="N503" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c77b6f8c802f00131a9b15</t>
+          <t>https://superprofile.bio/vig/6a5352f6e2e0070014b37086</t>
         </is>
       </c>
       <c r="O503" s="24" t="inlineStr">
@@ -37120,22 +37120,22 @@
       </c>
       <c r="B504" s="13" t="inlineStr">
         <is>
-          <t>695b6683d844f50012770a60</t>
+          <t>647c264b14366b002a85f133</t>
         </is>
       </c>
       <c r="C504" s="13" t="inlineStr">
         <is>
-          <t>starresearch</t>
+          <t>thekaranpaid</t>
         </is>
       </c>
       <c r="D504" s="12" t="inlineStr">
         <is>
-          <t>bhatudeore01@gmail.com</t>
+          <t>amitdhamecha5@gmail.com</t>
         </is>
       </c>
       <c r="E504" s="12" t="inlineStr">
         <is>
-          <t>7770002905</t>
+          <t>9033997421</t>
         </is>
       </c>
       <c r="F504" s="12" t="inlineStr">
@@ -37145,34 +37145,34 @@
       </c>
       <c r="G504" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H504" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I504" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J504" s="14" t="n">
-        <v>2440</v>
+        <v>1972</v>
       </c>
       <c r="K504" s="14" t="n">
-        <v>12201</v>
+        <v>12281</v>
       </c>
       <c r="L504" s="15" t="n">
-        <v>3905</v>
+        <v>6365</v>
       </c>
       <c r="M504" s="12" t="inlineStr">
         <is>
-          <t>6854f18a698fd4001305e686</t>
+          <t>69c77b6f8c802f00131a9b15</t>
         </is>
       </c>
       <c r="N504" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6854f18a698fd4001305e686</t>
+          <t>https://superprofile.bio/vig/69c77b6f8c802f00131a9b15</t>
         </is>
       </c>
       <c r="O504" s="17" t="inlineStr">
@@ -37192,22 +37192,22 @@
       </c>
       <c r="B505" s="20" t="inlineStr">
         <is>
-          <t>69482c860e733100134ed141</t>
+          <t>695b6683d844f50012770a60</t>
         </is>
       </c>
       <c r="C505" s="20" t="inlineStr">
         <is>
-          <t>stalkerhere</t>
+          <t>starresearch</t>
         </is>
       </c>
       <c r="D505" s="19" t="inlineStr">
         <is>
-          <t>dubeyarjun864@gmail.com</t>
+          <t>bhatudeore01@gmail.com</t>
         </is>
       </c>
       <c r="E505" s="19" t="inlineStr">
         <is>
-          <t>9137141331</t>
+          <t>7770002905</t>
         </is>
       </c>
       <c r="F505" s="19" t="inlineStr">
@@ -37217,34 +37217,34 @@
       </c>
       <c r="G505" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H505" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I505" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J505" s="21" t="n">
-        <v>1059</v>
+        <v>2440</v>
       </c>
       <c r="K505" s="21" t="n">
-        <v>12128</v>
+        <v>12201</v>
       </c>
       <c r="L505" s="22" t="n">
-        <v>4297</v>
+        <v>3905</v>
       </c>
       <c r="M505" s="19" t="inlineStr">
         <is>
-          <t>6a22d8b21346840013786206</t>
+          <t>6854f18a698fd4001305e686</t>
         </is>
       </c>
       <c r="N505" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a22d8b21346840013786206</t>
+          <t>https://superprofile.bio/vig/6854f18a698fd4001305e686</t>
         </is>
       </c>
       <c r="O505" s="24" t="inlineStr">
@@ -37264,22 +37264,22 @@
       </c>
       <c r="B506" s="13" t="inlineStr">
         <is>
-          <t>65ec0e3a8760a10013f1f989</t>
+          <t>69482c860e733100134ed141</t>
         </is>
       </c>
       <c r="C506" s="13" t="inlineStr">
         <is>
-          <t>mdrasalclasses</t>
+          <t>stalkerhere</t>
         </is>
       </c>
       <c r="D506" s="12" t="inlineStr">
         <is>
-          <t>monalirasal2510@gmail.com</t>
+          <t>dubeyarjun864@gmail.com</t>
         </is>
       </c>
       <c r="E506" s="12" t="inlineStr">
         <is>
-          <t>9881073331</t>
+          <t>9137141331</t>
         </is>
       </c>
       <c r="F506" s="12" t="inlineStr">
@@ -37289,34 +37289,34 @@
       </c>
       <c r="G506" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H506" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I506" s="13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J506" s="14" t="n">
-        <v>1125</v>
+        <v>1059</v>
       </c>
       <c r="K506" s="14" t="n">
-        <v>11923</v>
+        <v>12128</v>
       </c>
       <c r="L506" s="15" t="n">
-        <v>2744</v>
+        <v>4297</v>
       </c>
       <c r="M506" s="12" t="inlineStr">
         <is>
-          <t>698967292d273700127ba1b6</t>
+          <t>6a22d8b21346840013786206</t>
         </is>
       </c>
       <c r="N506" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698967292d273700127ba1b6</t>
+          <t>https://superprofile.bio/vig/6a22d8b21346840013786206</t>
         </is>
       </c>
       <c r="O506" s="17" t="inlineStr">
@@ -37336,22 +37336,22 @@
       </c>
       <c r="B507" s="20" t="inlineStr">
         <is>
-          <t>6360eaa132e4cd003667b28b</t>
+          <t>65ec0e3a8760a10013f1f989</t>
         </is>
       </c>
       <c r="C507" s="20" t="inlineStr">
         <is>
-          <t>ahtrends</t>
+          <t>mdrasalclasses</t>
         </is>
       </c>
       <c r="D507" s="19" t="inlineStr">
         <is>
-          <t>afjalhussainsaudi@gmail.com</t>
+          <t>monalirasal2510@gmail.com</t>
         </is>
       </c>
       <c r="E507" s="19" t="inlineStr">
         <is>
-          <t>9864714356</t>
+          <t>9881073331</t>
         </is>
       </c>
       <c r="F507" s="19" t="inlineStr">
@@ -37361,34 +37361,34 @@
       </c>
       <c r="G507" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H507" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I507" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J507" s="21" t="n">
-        <v>2096</v>
+        <v>1125</v>
       </c>
       <c r="K507" s="21" t="n">
-        <v>11910</v>
+        <v>11923</v>
       </c>
       <c r="L507" s="22" t="n">
-        <v>3144</v>
+        <v>2744</v>
       </c>
       <c r="M507" s="19" t="inlineStr">
         <is>
-          <t>6519c635535371001d421f8d</t>
+          <t>698967292d273700127ba1b6</t>
         </is>
       </c>
       <c r="N507" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6519c635535371001d421f8d</t>
+          <t>https://superprofile.bio/vig/698967292d273700127ba1b6</t>
         </is>
       </c>
       <c r="O507" s="24" t="inlineStr">
@@ -37408,22 +37408,22 @@
       </c>
       <c r="B508" s="13" t="inlineStr">
         <is>
-          <t>672913158d956b00139de083</t>
+          <t>6360eaa132e4cd003667b28b</t>
         </is>
       </c>
       <c r="C508" s="13" t="inlineStr">
         <is>
-          <t>swingtraders</t>
+          <t>ahtrends</t>
         </is>
       </c>
       <c r="D508" s="12" t="inlineStr">
         <is>
-          <t>hemakhune11@gmail.com</t>
+          <t>afjalhussainsaudi@gmail.com</t>
         </is>
       </c>
       <c r="E508" s="12" t="inlineStr">
         <is>
-          <t>8788693747</t>
+          <t>9864714356</t>
         </is>
       </c>
       <c r="F508" s="12" t="inlineStr">
@@ -37433,34 +37433,34 @@
       </c>
       <c r="G508" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H508" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I508" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J508" s="14" t="n">
-        <v>5894</v>
+        <v>2096</v>
       </c>
       <c r="K508" s="14" t="n">
-        <v>11717</v>
+        <v>11910</v>
       </c>
       <c r="L508" s="15" t="n">
-        <v>5894</v>
+        <v>3144</v>
       </c>
       <c r="M508" s="12" t="inlineStr">
         <is>
-          <t>67725a9c02b8330013737888</t>
+          <t>6519c635535371001d421f8d</t>
         </is>
       </c>
       <c r="N508" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67725a9c02b8330013737888</t>
+          <t>https://superprofile.bio/vig/6519c635535371001d421f8d</t>
         </is>
       </c>
       <c r="O508" s="17" t="inlineStr">
@@ -37480,22 +37480,22 @@
       </c>
       <c r="B509" s="20" t="inlineStr">
         <is>
-          <t>6784b631154f750013a08f96</t>
+          <t>672913158d956b00139de083</t>
         </is>
       </c>
       <c r="C509" s="20" t="inlineStr">
         <is>
-          <t>creativetradingcompany</t>
+          <t>swingtraders</t>
         </is>
       </c>
       <c r="D509" s="19" t="inlineStr">
         <is>
-          <t>rupanwardipak658@gmail.com</t>
+          <t>hemakhune11@gmail.com</t>
         </is>
       </c>
       <c r="E509" s="19" t="inlineStr">
         <is>
-          <t>9175857543</t>
+          <t>8788693747</t>
         </is>
       </c>
       <c r="F509" s="19" t="inlineStr">
@@ -37505,34 +37505,34 @@
       </c>
       <c r="G509" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H509" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I509" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J509" s="21" t="n">
-        <v>5853</v>
+        <v>5894</v>
       </c>
       <c r="K509" s="21" t="n">
-        <v>11706</v>
+        <v>11717</v>
       </c>
       <c r="L509" s="22" t="n">
-        <v>5853</v>
+        <v>5894</v>
       </c>
       <c r="M509" s="19" t="inlineStr">
         <is>
-          <t>6a6769888d035c0013651076</t>
+          <t>67725a9c02b8330013737888</t>
         </is>
       </c>
       <c r="N509" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6769888d035c0013651076</t>
+          <t>https://superprofile.bio/vig/67725a9c02b8330013737888</t>
         </is>
       </c>
       <c r="O509" s="24" t="inlineStr">
@@ -37552,22 +37552,22 @@
       </c>
       <c r="B510" s="13" t="inlineStr">
         <is>
-          <t>6524ef62cb7ef5001e914ff4</t>
+          <t>6784b631154f750013a08f96</t>
         </is>
       </c>
       <c r="C510" s="13" t="inlineStr">
         <is>
-          <t>Ratan2128</t>
+          <t>creativetradingcompany</t>
         </is>
       </c>
       <c r="D510" s="12" t="inlineStr">
         <is>
-          <t>ratansiyol002@gmail.com</t>
+          <t>rupanwardipak658@gmail.com</t>
         </is>
       </c>
       <c r="E510" s="12" t="inlineStr">
         <is>
-          <t>9116635172</t>
+          <t>9175857543</t>
         </is>
       </c>
       <c r="F510" s="12" t="inlineStr">
@@ -37577,34 +37577,34 @@
       </c>
       <c r="G510" s="12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H510" s="12" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H510" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="I510" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J510" s="14" t="n">
-        <v>2893</v>
+        <v>5853</v>
       </c>
       <c r="K510" s="14" t="n">
-        <v>11669</v>
+        <v>11706</v>
       </c>
       <c r="L510" s="15" t="n">
-        <v>5642</v>
+        <v>5853</v>
       </c>
       <c r="M510" s="12" t="inlineStr">
         <is>
-          <t>68bb102336262a0013e87744</t>
+          <t>6a6769888d035c0013651076</t>
         </is>
       </c>
       <c r="N510" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68bb102336262a0013e87744</t>
+          <t>https://superprofile.bio/vig/6a6769888d035c0013651076</t>
         </is>
       </c>
       <c r="O510" s="17" t="inlineStr">
@@ -37624,22 +37624,22 @@
       </c>
       <c r="B511" s="20" t="inlineStr">
         <is>
-          <t>62d77bd19422e201cc3af7c7</t>
+          <t>6524ef62cb7ef5001e914ff4</t>
         </is>
       </c>
       <c r="C511" s="20" t="inlineStr">
         <is>
-          <t>OptionsExperts</t>
+          <t>Ratan2128</t>
         </is>
       </c>
       <c r="D511" s="19" t="inlineStr">
         <is>
-          <t>parassadhu27@gmail.com</t>
+          <t>ratansiyol002@gmail.com</t>
         </is>
       </c>
       <c r="E511" s="19" t="inlineStr">
         <is>
-          <t>7069132800</t>
+          <t>9116635172</t>
         </is>
       </c>
       <c r="F511" s="19" t="inlineStr">
@@ -37649,34 +37649,34 @@
       </c>
       <c r="G511" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H511" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I511" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J511" s="21" t="n">
-        <v>2911</v>
+        <v>2893</v>
       </c>
       <c r="K511" s="21" t="n">
-        <v>11644</v>
+        <v>11669</v>
       </c>
       <c r="L511" s="22" t="n">
-        <v>2911</v>
+        <v>5642</v>
       </c>
       <c r="M511" s="19" t="inlineStr">
         <is>
-          <t>64758a8f788d15002037b098</t>
+          <t>68bb102336262a0013e87744</t>
         </is>
       </c>
       <c r="N511" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64758a8f788d15002037b098</t>
+          <t>https://superprofile.bio/vig/68bb102336262a0013e87744</t>
         </is>
       </c>
       <c r="O511" s="24" t="inlineStr">
@@ -37696,22 +37696,22 @@
       </c>
       <c r="B512" s="13" t="inlineStr">
         <is>
-          <t>680cbbd5828a580013dd5a2d</t>
+          <t>62d77bd19422e201cc3af7c7</t>
         </is>
       </c>
       <c r="C512" s="13" t="inlineStr">
         <is>
-          <t>profitgainer098</t>
+          <t>OptionsExperts</t>
         </is>
       </c>
       <c r="D512" s="12" t="inlineStr">
         <is>
-          <t>profitgainer098@gmail.com</t>
+          <t>parassadhu27@gmail.com</t>
         </is>
       </c>
       <c r="E512" s="12" t="inlineStr">
         <is>
-          <t>7412954802</t>
+          <t>7069132800</t>
         </is>
       </c>
       <c r="F512" s="12" t="inlineStr">
@@ -37726,29 +37726,29 @@
       </c>
       <c r="H512" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I512" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J512" s="14" t="n">
-        <v>1940</v>
+        <v>2911</v>
       </c>
       <c r="K512" s="14" t="n">
-        <v>11642</v>
+        <v>11644</v>
       </c>
       <c r="L512" s="15" t="n">
         <v>2911</v>
       </c>
       <c r="M512" s="12" t="inlineStr">
         <is>
-          <t>680cc43d56fedc0013eb8243</t>
+          <t>64758a8f788d15002037b098</t>
         </is>
       </c>
       <c r="N512" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/680cc43d56fedc0013eb8243</t>
+          <t>https://superprofile.bio/vig/64758a8f788d15002037b098</t>
         </is>
       </c>
       <c r="O512" s="17" t="inlineStr">
@@ -37768,22 +37768,22 @@
       </c>
       <c r="B513" s="20" t="inlineStr">
         <is>
-          <t>633c3a1bc0fe3f7289d32460</t>
+          <t>680cbbd5828a580013dd5a2d</t>
         </is>
       </c>
       <c r="C513" s="20" t="inlineStr">
         <is>
-          <t>herozero</t>
+          <t>profitgainer098</t>
         </is>
       </c>
       <c r="D513" s="19" t="inlineStr">
         <is>
-          <t>sorathiyaakshay7524@gmail.com</t>
+          <t>profitgainer098@gmail.com</t>
         </is>
       </c>
       <c r="E513" s="19" t="inlineStr">
         <is>
-          <t>6351545433</t>
+          <t>7412954802</t>
         </is>
       </c>
       <c r="F513" s="19" t="inlineStr">
@@ -37798,29 +37798,29 @@
       </c>
       <c r="H513" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I513" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J513" s="21" t="n">
-        <v>1621</v>
+        <v>1940</v>
       </c>
       <c r="K513" s="21" t="n">
-        <v>11572</v>
+        <v>11642</v>
       </c>
       <c r="L513" s="22" t="n">
-        <v>2744</v>
+        <v>2911</v>
       </c>
       <c r="M513" s="19" t="inlineStr">
         <is>
-          <t>6479e2590f8b6a002003d39a</t>
+          <t>680cc43d56fedc0013eb8243</t>
         </is>
       </c>
       <c r="N513" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6479e2590f8b6a002003d39a</t>
+          <t>https://superprofile.bio/vig/680cc43d56fedc0013eb8243</t>
         </is>
       </c>
       <c r="O513" s="24" t="inlineStr">
@@ -37840,22 +37840,22 @@
       </c>
       <c r="B514" s="13" t="inlineStr">
         <is>
-          <t>647761847e024f001ffe9d9d</t>
+          <t>633c3a1bc0fe3f7289d32460</t>
         </is>
       </c>
       <c r="C514" s="13" t="inlineStr">
         <is>
-          <t>mentorshipgenius007</t>
+          <t>herozero</t>
         </is>
       </c>
       <c r="D514" s="12" t="inlineStr">
         <is>
-          <t>rajkumarrakhunde9@gmail.com</t>
+          <t>sorathiyaakshay7524@gmail.com</t>
         </is>
       </c>
       <c r="E514" s="12" t="inlineStr">
         <is>
-          <t>9689988583</t>
+          <t>6351545433</t>
         </is>
       </c>
       <c r="F514" s="12" t="inlineStr">
@@ -37865,7 +37865,7 @@
       </c>
       <c r="G514" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H514" s="12" t="inlineStr">
@@ -37874,25 +37874,25 @@
         </is>
       </c>
       <c r="I514" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J514" s="14" t="n">
-        <v>8187</v>
+        <v>1621</v>
       </c>
       <c r="K514" s="14" t="n">
-        <v>11537</v>
+        <v>11572</v>
       </c>
       <c r="L514" s="15" t="n">
-        <v>8187</v>
+        <v>2744</v>
       </c>
       <c r="M514" s="12" t="inlineStr">
         <is>
-          <t>647888d4254df9002037a2ef</t>
+          <t>6479e2590f8b6a002003d39a</t>
         </is>
       </c>
       <c r="N514" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647888d4254df9002037a2ef</t>
+          <t>https://superprofile.bio/vig/6479e2590f8b6a002003d39a</t>
         </is>
       </c>
       <c r="O514" s="17" t="inlineStr">
@@ -37912,22 +37912,22 @@
       </c>
       <c r="B515" s="20" t="inlineStr">
         <is>
-          <t>64db9841857b64001ebb5534</t>
+          <t>647761847e024f001ffe9d9d</t>
         </is>
       </c>
       <c r="C515" s="20" t="inlineStr">
         <is>
-          <t>stockmarketwithawdhesh</t>
+          <t>mentorshipgenius007</t>
         </is>
       </c>
       <c r="D515" s="19" t="inlineStr">
         <is>
-          <t>investinstock26@gmail.com</t>
+          <t>rajkumarrakhunde9@gmail.com</t>
         </is>
       </c>
       <c r="E515" s="19" t="inlineStr">
         <is>
-          <t>7050619397</t>
+          <t>9689988583</t>
         </is>
       </c>
       <c r="F515" s="19" t="inlineStr">
@@ -37937,34 +37937,34 @@
       </c>
       <c r="G515" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H515" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I515" s="20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J515" s="21" t="n">
-        <v>1080</v>
+        <v>8187</v>
       </c>
       <c r="K515" s="21" t="n">
-        <v>11340</v>
+        <v>11537</v>
       </c>
       <c r="L515" s="22" t="n">
-        <v>3060</v>
+        <v>8187</v>
       </c>
       <c r="M515" s="19" t="inlineStr">
         <is>
-          <t>674304608358d800139decda</t>
+          <t>647888d4254df9002037a2ef</t>
         </is>
       </c>
       <c r="N515" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/674304608358d800139decda</t>
+          <t>https://superprofile.bio/vig/647888d4254df9002037a2ef</t>
         </is>
       </c>
       <c r="O515" s="24" t="inlineStr">
@@ -37984,22 +37984,22 @@
       </c>
       <c r="B516" s="13" t="inlineStr">
         <is>
-          <t>6a72c84e2b3c700013473c40</t>
+          <t>64db9841857b64001ebb5534</t>
         </is>
       </c>
       <c r="C516" s="13" t="inlineStr">
         <is>
-          <t>Ankit3741</t>
+          <t>stockmarketwithawdhesh</t>
         </is>
       </c>
       <c r="D516" s="12" t="inlineStr">
         <is>
-          <t>jaat1472580@gmail.com</t>
+          <t>investinstock26@gmail.com</t>
         </is>
       </c>
       <c r="E516" s="12" t="inlineStr">
         <is>
-          <t>6367055358</t>
+          <t>7050619397</t>
         </is>
       </c>
       <c r="F516" s="12" t="inlineStr">
@@ -38009,34 +38009,34 @@
       </c>
       <c r="G516" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H516" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I516" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J516" s="14" t="n">
-        <v>2822</v>
+        <v>1080</v>
       </c>
       <c r="K516" s="14" t="n">
-        <v>11308</v>
+        <v>11340</v>
       </c>
       <c r="L516" s="15" t="n">
-        <v>5645</v>
+        <v>3060</v>
       </c>
       <c r="M516" s="12" t="inlineStr">
         <is>
-          <t>6a889aaccf18c7001341f552</t>
+          <t>674304608358d800139decda</t>
         </is>
       </c>
       <c r="N516" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a889aaccf18c7001341f552</t>
+          <t>https://superprofile.bio/vig/674304608358d800139decda</t>
         </is>
       </c>
       <c r="O516" s="17" t="inlineStr">
@@ -38056,22 +38056,22 @@
       </c>
       <c r="B517" s="20" t="inlineStr">
         <is>
-          <t>644bf3523e20660020c9b69d</t>
+          <t>6a72c84e2b3c700013473c40</t>
         </is>
       </c>
       <c r="C517" s="20" t="inlineStr">
         <is>
-          <t>drgann</t>
+          <t>Ankit3741</t>
         </is>
       </c>
       <c r="D517" s="19" t="inlineStr">
         <is>
-          <t>amitkkkk@yahoo.com</t>
+          <t>jaat1472580@gmail.com</t>
         </is>
       </c>
       <c r="E517" s="19" t="inlineStr">
         <is>
-          <t>9435475680</t>
+          <t>6367055358</t>
         </is>
       </c>
       <c r="F517" s="19" t="inlineStr">
@@ -38081,34 +38081,34 @@
       </c>
       <c r="G517" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H517" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I517" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J517" s="21" t="n">
-        <v>3622</v>
+        <v>2822</v>
       </c>
       <c r="K517" s="21" t="n">
-        <v>11296</v>
+        <v>11308</v>
       </c>
       <c r="L517" s="22" t="n">
-        <v>3622</v>
+        <v>5645</v>
       </c>
       <c r="M517" s="19" t="inlineStr">
         <is>
-          <t>68f3a1239e3ce90013e78440</t>
+          <t>6a889aaccf18c7001341f552</t>
         </is>
       </c>
       <c r="N517" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f3a1239e3ce90013e78440</t>
+          <t>https://superprofile.bio/vig/6a889aaccf18c7001341f552</t>
         </is>
       </c>
       <c r="O517" s="24" t="inlineStr">
@@ -38128,22 +38128,22 @@
       </c>
       <c r="B518" s="13" t="inlineStr">
         <is>
-          <t>627ca99791125d5ba8a34b41</t>
+          <t>644bf3523e20660020c9b69d</t>
         </is>
       </c>
       <c r="C518" s="13" t="inlineStr">
         <is>
-          <t>mamoon</t>
+          <t>drgann</t>
         </is>
       </c>
       <c r="D518" s="12" t="inlineStr">
         <is>
-          <t>Mamoon4sindia@gmail.com</t>
+          <t>amitkkkk@yahoo.com</t>
         </is>
       </c>
       <c r="E518" s="12" t="inlineStr">
         <is>
-          <t>7903542731</t>
+          <t>9435475680</t>
         </is>
       </c>
       <c r="F518" s="12" t="inlineStr">
@@ -38158,29 +38158,29 @@
       </c>
       <c r="H518" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I518" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J518" s="14" t="n">
-        <v>1832</v>
+        <v>3622</v>
       </c>
       <c r="K518" s="14" t="n">
-        <v>11184</v>
+        <v>11296</v>
       </c>
       <c r="L518" s="15" t="n">
-        <v>3856</v>
+        <v>3622</v>
       </c>
       <c r="M518" s="12" t="inlineStr">
         <is>
-          <t>66eaae246c05200013bace75</t>
+          <t>68f3a1239e3ce90013e78440</t>
         </is>
       </c>
       <c r="N518" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
+          <t>https://superprofile.bio/vig/68f3a1239e3ce90013e78440</t>
         </is>
       </c>
       <c r="O518" s="17" t="inlineStr">
@@ -38200,22 +38200,22 @@
       </c>
       <c r="B519" s="20" t="inlineStr">
         <is>
-          <t>64f06b56cea5ab001f870948</t>
+          <t>627ca99791125d5ba8a34b41</t>
         </is>
       </c>
       <c r="C519" s="20" t="inlineStr">
         <is>
-          <t>optiontradingpoint</t>
+          <t>mamoon</t>
         </is>
       </c>
       <c r="D519" s="19" t="inlineStr">
         <is>
-          <t>deepkids19@gmail.com</t>
+          <t>Mamoon4sindia@gmail.com</t>
         </is>
       </c>
       <c r="E519" s="19" t="inlineStr">
         <is>
-          <t>7798151419</t>
+          <t>7903542731</t>
         </is>
       </c>
       <c r="F519" s="19" t="inlineStr">
@@ -38225,34 +38225,34 @@
       </c>
       <c r="G519" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H519" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I519" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J519" s="21" t="n">
-        <v>2910</v>
+        <v>1832</v>
       </c>
       <c r="K519" s="21" t="n">
-        <v>11047</v>
+        <v>11184</v>
       </c>
       <c r="L519" s="22" t="n">
-        <v>8137</v>
+        <v>3856</v>
       </c>
       <c r="M519" s="19" t="inlineStr">
         <is>
-          <t>65dafd37442a0f001325f1a7</t>
+          <t>66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="N519" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65dafd37442a0f001325f1a7</t>
+          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="O519" s="24" t="inlineStr">
@@ -38272,22 +38272,22 @@
       </c>
       <c r="B520" s="13" t="inlineStr">
         <is>
-          <t>6a9c25a3213bce0014ff2b98</t>
+          <t>64f06b56cea5ab001f870948</t>
         </is>
       </c>
       <c r="C520" s="13" t="inlineStr">
         <is>
-          <t>priyasharma71284</t>
+          <t>optiontradingpoint</t>
         </is>
       </c>
       <c r="D520" s="12" t="inlineStr">
         <is>
-          <t>zerotohero941376@gmail.com</t>
+          <t>deepkids19@gmail.com</t>
         </is>
       </c>
       <c r="E520" s="12" t="inlineStr">
         <is>
-          <t>9351444938</t>
+          <t>7798151419</t>
         </is>
       </c>
       <c r="F520" s="12" t="inlineStr">
@@ -38297,7 +38297,7 @@
       </c>
       <c r="G520" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H520" s="12" t="inlineStr">
@@ -38309,22 +38309,22 @@
         <v>2</v>
       </c>
       <c r="J520" s="14" t="n">
-        <v>8363</v>
+        <v>2910</v>
       </c>
       <c r="K520" s="14" t="n">
-        <v>10837</v>
+        <v>11047</v>
       </c>
       <c r="L520" s="15" t="n">
-        <v>8363</v>
+        <v>8137</v>
       </c>
       <c r="M520" s="12" t="inlineStr">
         <is>
-          <t>6a9c330b213bce001402122a</t>
+          <t>65dafd37442a0f001325f1a7</t>
         </is>
       </c>
       <c r="N520" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9c330b213bce001402122a</t>
+          <t>https://superprofile.bio/vig/65dafd37442a0f001325f1a7</t>
         </is>
       </c>
       <c r="O520" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 06:34:03 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 07:04:00 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹47,496,375.00</t>
+          <t>₹47,528,761.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>4417779</v>
+        <v>4425697</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -1984,22 +1984,22 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>6903094d47fdf40013e5a517</t>
+          <t>6a54b9ee478445001378e580</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>novawealthcapital</t>
+          <t>himanshi09</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>novawealthcap@gmail.com</t>
+          <t>himanshisharma88888@gmail.com</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>9998885486</t>
+          <t>6375733270</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -2018,25 +2018,25 @@
         </is>
       </c>
       <c r="I16" s="13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>28478</v>
+        <v>3959</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>364806</v>
+        <v>371985</v>
       </c>
       <c r="L16" s="15" t="n">
-        <v>69504</v>
+        <v>70572</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>689ad183b8ec0600136a3748</t>
+          <t>6a59b780bf6f01001379f602</t>
         </is>
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/689ad183b8ec0600136a3748</t>
+          <t>https://superprofile.bio/vig/6a59b780bf6f01001379f602</t>
         </is>
       </c>
       <c r="O16" s="17" t="inlineStr">
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>6718ef2cc3ab9800132644dd</t>
+          <t>6903094d47fdf40013e5a517</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>dtcommunity</t>
+          <t>novawealthcapital</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>helpdtpulse@gmail.com</t>
+          <t>novawealthcap@gmail.com</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>9828680440</t>
+          <t>9998885486</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -2086,29 +2086,29 @@
       </c>
       <c r="H17" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I17" s="20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>19283</v>
+        <v>28478</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>360966</v>
+        <v>364806</v>
       </c>
       <c r="L17" s="22" t="n">
-        <v>65645</v>
+        <v>69504</v>
       </c>
       <c r="M17" s="19" t="inlineStr">
         <is>
-          <t>6984f394797e090013c86e06</t>
+          <t>689ad183b8ec0600136a3748</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6984f394797e090013c86e06</t>
+          <t>https://superprofile.bio/vig/689ad183b8ec0600136a3748</t>
         </is>
       </c>
       <c r="O17" s="24" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>64e72fbf78136a001ea47a90</t>
+          <t>6718ef2cc3ab9800132644dd</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>babita8766</t>
+          <t>dtcommunity</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>babitakumari9r@gmail.com</t>
+          <t>helpdtpulse@gmail.com</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>7534846575</t>
+          <t>9828680440</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -2158,29 +2158,29 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I18" s="13" t="n">
         <v>11</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>8697</v>
+        <v>19283</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>357938</v>
+        <v>360966</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>63293</v>
+        <v>65645</v>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>648053c3588ff00020d20472</t>
+          <t>6984f394797e090013c86e06</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/648053c3588ff00020d20472</t>
+          <t>https://superprofile.bio/vig/6984f394797e090013c86e06</t>
         </is>
       </c>
       <c r="O18" s="17" t="inlineStr">
@@ -2200,22 +2200,22 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>6792105c1ca4f90013d8d22a</t>
+          <t>64e72fbf78136a001ea47a90</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>admin14</t>
+          <t>babita8766</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>datadazzle@zuperone.com</t>
+          <t>babitakumari9r@gmail.com</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>6361783958</t>
+          <t>7534846575</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
@@ -2225,34 +2225,34 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I19" s="20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>18996</v>
+        <v>8697</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>349910</v>
+        <v>357938</v>
       </c>
       <c r="L19" s="22" t="n">
-        <v>102168</v>
+        <v>63293</v>
       </c>
       <c r="M19" s="19" t="inlineStr">
         <is>
-          <t>67933373930de200137d8bc3</t>
+          <t>648053c3588ff00020d20472</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67933373930de200137d8bc3</t>
+          <t>https://superprofile.bio/vig/648053c3588ff00020d20472</t>
         </is>
       </c>
       <c r="O19" s="24" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>6a5daef8336dff00131581e1</t>
+          <t>6792105c1ca4f90013d8d22a</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>ishitamajumder</t>
+          <t>admin14</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>financewithishita00@gmail.com</t>
+          <t>datadazzle@zuperone.com</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>9903733648</t>
+          <t>6361783958</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2297,34 +2297,34 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I20" s="13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>21533</v>
+        <v>18996</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>340840</v>
+        <v>349910</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>59307</v>
+        <v>102168</v>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>6a66dadb0a242e00131d5d8b</t>
+          <t>67933373930de200137d8bc3</t>
         </is>
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a66dadb0a242e00131d5d8b</t>
+          <t>https://superprofile.bio/vig/67933373930de200137d8bc3</t>
         </is>
       </c>
       <c r="O20" s="17" t="inlineStr">
@@ -2344,22 +2344,22 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>6a54b9ee478445001378e580</t>
+          <t>6a5daef8336dff00131581e1</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>himanshi09</t>
+          <t>ishitamajumder</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>himanshisharma88888@gmail.com</t>
+          <t>financewithishita00@gmail.com</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>6375733270</t>
+          <t>9903733648</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -2374,29 +2374,29 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I21" s="20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>32386</v>
+        <v>21533</v>
       </c>
       <c r="K21" s="21" t="n">
-        <v>339599</v>
+        <v>340840</v>
       </c>
       <c r="L21" s="22" t="n">
-        <v>70572</v>
+        <v>59307</v>
       </c>
       <c r="M21" s="19" t="inlineStr">
         <is>
-          <t>6a59b780bf6f01001379f602</t>
+          <t>6a66dadb0a242e00131d5d8b</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a59b780bf6f01001379f602</t>
+          <t>https://superprofile.bio/vig/6a66dadb0a242e00131d5d8b</t>
         </is>
       </c>
       <c r="O21" s="24" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 07:04:00 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 08:35:45 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 08:35:45 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 10:41:34 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 10:41:34 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 12:43:39 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 12:43:39 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 14:09:03 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 14:09:03 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 15:47:40 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 15:47:40 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 17:37:00 | Daily Audits Logged: 12</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-10 17:37:00 | Daily Audits Logged: 12</t>
+          <t>Generated On: 2026-09-10 18:43:28 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹47,528,761.00</t>
+          <t>₹47,531,116.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -848,6 +848,24 @@
         <v>4425697</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Logged &amp; Deduplicated</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Logged &amp; Deduplicated</t>
         </is>
@@ -28696,22 +28714,22 @@
       </c>
       <c r="B387" s="20" t="inlineStr">
         <is>
-          <t>63dca2cc1bea38002cfb3221</t>
+          <t>62115e4a6bd738258707c0e9</t>
         </is>
       </c>
       <c r="C387" s="20" t="inlineStr">
         <is>
-          <t>equityforearning</t>
+          <t>aditya</t>
         </is>
       </c>
       <c r="D387" s="19" t="inlineStr">
         <is>
-          <t>equityforearning@gmail.com</t>
+          <t>imavschoudhary@gmail.com</t>
         </is>
       </c>
       <c r="E387" s="19" t="inlineStr">
         <is>
-          <t>7396962062</t>
+          <t>9717115749</t>
         </is>
       </c>
       <c r="F387" s="19" t="inlineStr">
@@ -28721,34 +28739,34 @@
       </c>
       <c r="G387" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H387" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I387" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J387" s="21" t="n">
-        <v>2412</v>
+        <v>2355</v>
       </c>
       <c r="K387" s="21" t="n">
-        <v>21705</v>
+        <v>21720</v>
       </c>
       <c r="L387" s="22" t="n">
-        <v>6752</v>
+        <v>4379</v>
       </c>
       <c r="M387" s="19" t="inlineStr">
         <is>
-          <t>663b5821b5a80a00130d0dd2</t>
+          <t>6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="N387" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/663b5821b5a80a00130d0dd2</t>
+          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="O387" s="24" t="inlineStr">
@@ -28768,22 +28786,22 @@
       </c>
       <c r="B388" s="13" t="inlineStr">
         <is>
-          <t>63df9c3c934d930033d43fa0</t>
+          <t>63dca2cc1bea38002cfb3221</t>
         </is>
       </c>
       <c r="C388" s="13" t="inlineStr">
         <is>
-          <t>darshan9323</t>
+          <t>equityforearning</t>
         </is>
       </c>
       <c r="D388" s="12" t="inlineStr">
         <is>
-          <t>varsanidarsh18@gmail.com</t>
+          <t>equityforearning@gmail.com</t>
         </is>
       </c>
       <c r="E388" s="12" t="inlineStr">
         <is>
-          <t>7016885381</t>
+          <t>7396962062</t>
         </is>
       </c>
       <c r="F388" s="12" t="inlineStr">
@@ -28793,34 +28811,34 @@
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H388" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I388" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J388" s="14" t="n">
-        <v>2964</v>
+        <v>2412</v>
       </c>
       <c r="K388" s="14" t="n">
-        <v>21689</v>
+        <v>21705</v>
       </c>
       <c r="L388" s="15" t="n">
-        <v>11315</v>
+        <v>6752</v>
       </c>
       <c r="M388" s="12" t="inlineStr">
         <is>
-          <t>684658da217aa40013f62f9a</t>
+          <t>663b5821b5a80a00130d0dd2</t>
         </is>
       </c>
       <c r="N388" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/684658da217aa40013f62f9a</t>
+          <t>https://superprofile.bio/vig/663b5821b5a80a00130d0dd2</t>
         </is>
       </c>
       <c r="O388" s="17" t="inlineStr">
@@ -28840,22 +28858,22 @@
       </c>
       <c r="B389" s="20" t="inlineStr">
         <is>
-          <t>6479fda68f1411002042115e</t>
+          <t>63df9c3c934d930033d43fa0</t>
         </is>
       </c>
       <c r="C389" s="20" t="inlineStr">
         <is>
-          <t>tradewithca</t>
+          <t>darshan9323</t>
         </is>
       </c>
       <c r="D389" s="19" t="inlineStr">
         <is>
-          <t>tarun199325@gmail.com</t>
+          <t>varsanidarsh18@gmail.com</t>
         </is>
       </c>
       <c r="E389" s="19" t="inlineStr">
         <is>
-          <t>7668256291</t>
+          <t>7016885381</t>
         </is>
       </c>
       <c r="F389" s="19" t="inlineStr">
@@ -28865,34 +28883,34 @@
       </c>
       <c r="G389" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H389" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I389" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J389" s="21" t="n">
-        <v>2352</v>
+        <v>2964</v>
       </c>
       <c r="K389" s="21" t="n">
-        <v>21636</v>
+        <v>21689</v>
       </c>
       <c r="L389" s="22" t="n">
-        <v>4703</v>
+        <v>11315</v>
       </c>
       <c r="M389" s="19" t="inlineStr">
         <is>
-          <t>69c8ae92ea59ad001490f2cd</t>
+          <t>684658da217aa40013f62f9a</t>
         </is>
       </c>
       <c r="N389" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c8ae92ea59ad001490f2cd</t>
+          <t>https://superprofile.bio/vig/684658da217aa40013f62f9a</t>
         </is>
       </c>
       <c r="O389" s="24" t="inlineStr">
@@ -28912,22 +28930,22 @@
       </c>
       <c r="B390" s="13" t="inlineStr">
         <is>
-          <t>6a701de79d1a120013ff6188</t>
+          <t>6479fda68f1411002042115e</t>
         </is>
       </c>
       <c r="C390" s="13" t="inlineStr">
         <is>
-          <t>NIL3017</t>
+          <t>tradewithca</t>
         </is>
       </c>
       <c r="D390" s="12" t="inlineStr">
         <is>
-          <t>nilbedmutha121@gmail.com</t>
+          <t>tarun199325@gmail.com</t>
         </is>
       </c>
       <c r="E390" s="12" t="inlineStr">
         <is>
-          <t>7719850602</t>
+          <t>7668256291</t>
         </is>
       </c>
       <c r="F390" s="12" t="inlineStr">
@@ -28937,34 +28955,34 @@
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H390" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I390" s="13" t="n">
         <v>7</v>
       </c>
       <c r="J390" s="14" t="n">
-        <v>1971</v>
+        <v>2352</v>
       </c>
       <c r="K390" s="14" t="n">
-        <v>21623</v>
+        <v>21636</v>
       </c>
       <c r="L390" s="15" t="n">
-        <v>5912</v>
+        <v>4703</v>
       </c>
       <c r="M390" s="12" t="inlineStr">
         <is>
-          <t>6a703a0899878a0013b796ba</t>
+          <t>69c8ae92ea59ad001490f2cd</t>
         </is>
       </c>
       <c r="N390" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a703a0899878a0013b796ba</t>
+          <t>https://superprofile.bio/vig/69c8ae92ea59ad001490f2cd</t>
         </is>
       </c>
       <c r="O390" s="17" t="inlineStr">
@@ -28984,22 +29002,22 @@
       </c>
       <c r="B391" s="20" t="inlineStr">
         <is>
-          <t>6a0739870374d70013f4a6da</t>
+          <t>6a701de79d1a120013ff6188</t>
         </is>
       </c>
       <c r="C391" s="20" t="inlineStr">
         <is>
-          <t>algoxofficial</t>
+          <t>NIL3017</t>
         </is>
       </c>
       <c r="D391" s="19" t="inlineStr">
         <is>
-          <t>sayhelloplux@gmail.com</t>
+          <t>nilbedmutha121@gmail.com</t>
         </is>
       </c>
       <c r="E391" s="19" t="inlineStr">
         <is>
-          <t>8529451480</t>
+          <t>7719850602</t>
         </is>
       </c>
       <c r="F391" s="19" t="inlineStr">
@@ -29009,7 +29027,7 @@
       </c>
       <c r="G391" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H391" s="19" t="inlineStr">
@@ -29018,25 +29036,25 @@
         </is>
       </c>
       <c r="I391" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J391" s="21" t="n">
-        <v>3281</v>
+        <v>1971</v>
       </c>
       <c r="K391" s="21" t="n">
-        <v>21567</v>
+        <v>21623</v>
       </c>
       <c r="L391" s="22" t="n">
-        <v>6554</v>
+        <v>5912</v>
       </c>
       <c r="M391" s="19" t="inlineStr">
         <is>
-          <t>6a40b76b8552d90013a86043</t>
+          <t>6a703a0899878a0013b796ba</t>
         </is>
       </c>
       <c r="N391" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
+          <t>https://superprofile.bio/vig/6a703a0899878a0013b796ba</t>
         </is>
       </c>
       <c r="O391" s="24" t="inlineStr">
@@ -29056,22 +29074,22 @@
       </c>
       <c r="B392" s="13" t="inlineStr">
         <is>
-          <t>6475ef47a3c3a8002022a30b</t>
+          <t>6a0739870374d70013f4a6da</t>
         </is>
       </c>
       <c r="C392" s="13" t="inlineStr">
         <is>
-          <t>NIFTYBYJADEJA</t>
+          <t>algoxofficial</t>
         </is>
       </c>
       <c r="D392" s="12" t="inlineStr">
         <is>
-          <t>Kanbhaj8@gmail.com</t>
+          <t>sayhelloplux@gmail.com</t>
         </is>
       </c>
       <c r="E392" s="12" t="inlineStr">
         <is>
-          <t>9712330345</t>
+          <t>8529451480</t>
         </is>
       </c>
       <c r="F392" s="12" t="inlineStr">
@@ -29081,34 +29099,34 @@
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H392" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I392" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J392" s="14" t="n">
-        <v>2700</v>
+        <v>3281</v>
       </c>
       <c r="K392" s="14" t="n">
-        <v>21464</v>
+        <v>21567</v>
       </c>
       <c r="L392" s="15" t="n">
-        <v>8932</v>
+        <v>6554</v>
       </c>
       <c r="M392" s="12" t="inlineStr">
         <is>
-          <t>65dd70e9dd17c100134be7ab</t>
+          <t>6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="N392" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65dd70e9dd17c100134be7ab</t>
+          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="O392" s="17" t="inlineStr">
@@ -29128,22 +29146,22 @@
       </c>
       <c r="B393" s="20" t="inlineStr">
         <is>
-          <t>67a6163b2add040013b0ce0f</t>
+          <t>6475ef47a3c3a8002022a30b</t>
         </is>
       </c>
       <c r="C393" s="20" t="inlineStr">
         <is>
-          <t>aadavan</t>
+          <t>NIFTYBYJADEJA</t>
         </is>
       </c>
       <c r="D393" s="19" t="inlineStr">
         <is>
-          <t>jishanmaalik@gmail.com</t>
+          <t>Kanbhaj8@gmail.com</t>
         </is>
       </c>
       <c r="E393" s="19" t="inlineStr">
         <is>
-          <t>8088654150</t>
+          <t>9712330345</t>
         </is>
       </c>
       <c r="F393" s="19" t="inlineStr">
@@ -29153,34 +29171,34 @@
       </c>
       <c r="G393" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H393" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I393" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J393" s="21" t="n">
-        <v>3880</v>
+        <v>2700</v>
       </c>
       <c r="K393" s="21" t="n">
-        <v>21303</v>
+        <v>21464</v>
       </c>
       <c r="L393" s="22" t="n">
-        <v>6308</v>
+        <v>8932</v>
       </c>
       <c r="M393" s="19" t="inlineStr">
         <is>
-          <t>67a8c6045ee5520012250762</t>
+          <t>65dd70e9dd17c100134be7ab</t>
         </is>
       </c>
       <c r="N393" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
+          <t>https://superprofile.bio/vig/65dd70e9dd17c100134be7ab</t>
         </is>
       </c>
       <c r="O393" s="24" t="inlineStr">
@@ -29200,22 +29218,22 @@
       </c>
       <c r="B394" s="13" t="inlineStr">
         <is>
-          <t>653537f0500ece001e141c9c</t>
+          <t>67a6163b2add040013b0ce0f</t>
         </is>
       </c>
       <c r="C394" s="13" t="inlineStr">
         <is>
-          <t>sizzdeep</t>
+          <t>aadavan</t>
         </is>
       </c>
       <c r="D394" s="12" t="inlineStr">
         <is>
-          <t>deepakbhard199@gmail.com</t>
+          <t>jishanmaalik@gmail.com</t>
         </is>
       </c>
       <c r="E394" s="12" t="inlineStr">
         <is>
-          <t>6230232721</t>
+          <t>8088654150</t>
         </is>
       </c>
       <c r="F394" s="12" t="inlineStr">
@@ -29225,34 +29243,34 @@
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H394" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I394" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J394" s="14" t="n">
-        <v>21220</v>
+        <v>3880</v>
       </c>
       <c r="K394" s="14" t="n">
-        <v>21220</v>
+        <v>21303</v>
       </c>
       <c r="L394" s="15" t="n">
-        <v>21220</v>
+        <v>6308</v>
       </c>
       <c r="M394" s="12" t="inlineStr">
         <is>
-          <t>6696419a36f0990013d6945a</t>
+          <t>67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="N394" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6696419a36f0990013d6945a</t>
+          <t>https://superprofile.bio/vig/67a8c6045ee5520012250762</t>
         </is>
       </c>
       <c r="O394" s="17" t="inlineStr">
@@ -29272,22 +29290,22 @@
       </c>
       <c r="B395" s="20" t="inlineStr">
         <is>
-          <t>6788e1865e03e800132c5ed6</t>
+          <t>653537f0500ece001e141c9c</t>
         </is>
       </c>
       <c r="C395" s="20" t="inlineStr">
         <is>
-          <t>tmestockdealbanknifty</t>
+          <t>sizzdeep</t>
         </is>
       </c>
       <c r="D395" s="19" t="inlineStr">
         <is>
-          <t>kubavatbiz@gmail.com</t>
+          <t>deepakbhard199@gmail.com</t>
         </is>
       </c>
       <c r="E395" s="19" t="inlineStr">
         <is>
-          <t>9824960130</t>
+          <t>6230232721</t>
         </is>
       </c>
       <c r="F395" s="19" t="inlineStr">
@@ -29297,34 +29315,34 @@
       </c>
       <c r="G395" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H395" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I395" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J395" s="21" t="n">
-        <v>2928</v>
+        <v>21220</v>
       </c>
       <c r="K395" s="21" t="n">
-        <v>21181</v>
+        <v>21220</v>
       </c>
       <c r="L395" s="22" t="n">
-        <v>6833</v>
+        <v>21220</v>
       </c>
       <c r="M395" s="19" t="inlineStr">
         <is>
-          <t>6789ff3d8329cd0015c842bc</t>
+          <t>6696419a36f0990013d6945a</t>
         </is>
       </c>
       <c r="N395" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6789ff3d8329cd0015c842bc</t>
+          <t>https://superprofile.bio/vig/6696419a36f0990013d6945a</t>
         </is>
       </c>
       <c r="O395" s="24" t="inlineStr">
@@ -29344,22 +29362,22 @@
       </c>
       <c r="B396" s="13" t="inlineStr">
         <is>
-          <t>69c024131e4a31001362ea2c</t>
+          <t>6788e1865e03e800132c5ed6</t>
         </is>
       </c>
       <c r="C396" s="13" t="inlineStr">
         <is>
-          <t>khokon2004</t>
+          <t>tmestockdealbanknifty</t>
         </is>
       </c>
       <c r="D396" s="12" t="inlineStr">
         <is>
-          <t>mrtraderbusiness03@gmail.com</t>
+          <t>kubavatbiz@gmail.com</t>
         </is>
       </c>
       <c r="E396" s="12" t="inlineStr">
         <is>
-          <t>9832288446</t>
+          <t>9824960130</t>
         </is>
       </c>
       <c r="F396" s="12" t="inlineStr">
@@ -29369,34 +29387,34 @@
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H396" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I396" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J396" s="14" t="n">
-        <v>7058</v>
+        <v>2928</v>
       </c>
       <c r="K396" s="14" t="n">
-        <v>21174</v>
+        <v>21181</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>7058</v>
+        <v>6833</v>
       </c>
       <c r="M396" s="12" t="inlineStr">
         <is>
-          <t>6a53c2ea94c4f30013f521be</t>
+          <t>6789ff3d8329cd0015c842bc</t>
         </is>
       </c>
       <c r="N396" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a53c2ea94c4f30013f521be</t>
+          <t>https://superprofile.bio/vig/6789ff3d8329cd0015c842bc</t>
         </is>
       </c>
       <c r="O396" s="17" t="inlineStr">
@@ -29416,22 +29434,22 @@
       </c>
       <c r="B397" s="20" t="inlineStr">
         <is>
-          <t>63b156cd65033900334ec0e7</t>
+          <t>69c024131e4a31001362ea2c</t>
         </is>
       </c>
       <c r="C397" s="20" t="inlineStr">
         <is>
-          <t>trade555</t>
+          <t>khokon2004</t>
         </is>
       </c>
       <c r="D397" s="19" t="inlineStr">
         <is>
-          <t>suryanshvishnoi5@gmail.com</t>
+          <t>mrtraderbusiness03@gmail.com</t>
         </is>
       </c>
       <c r="E397" s="19" t="inlineStr">
         <is>
-          <t>9084242427</t>
+          <t>9832288446</t>
         </is>
       </c>
       <c r="F397" s="19" t="inlineStr">
@@ -29441,34 +29459,34 @@
       </c>
       <c r="G397" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H397" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I397" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J397" s="21" t="n">
-        <v>6924</v>
+        <v>7058</v>
       </c>
       <c r="K397" s="21" t="n">
-        <v>20921</v>
+        <v>21174</v>
       </c>
       <c r="L397" s="22" t="n">
-        <v>7073</v>
+        <v>7058</v>
       </c>
       <c r="M397" s="19" t="inlineStr">
         <is>
-          <t>69c768f29ff8560012a56967</t>
+          <t>6a53c2ea94c4f30013f521be</t>
         </is>
       </c>
       <c r="N397" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c768f29ff8560012a56967</t>
+          <t>https://superprofile.bio/vig/6a53c2ea94c4f30013f521be</t>
         </is>
       </c>
       <c r="O397" s="24" t="inlineStr">
@@ -29488,22 +29506,22 @@
       </c>
       <c r="B398" s="13" t="inlineStr">
         <is>
-          <t>682368f50efed700131d7266</t>
+          <t>63b156cd65033900334ec0e7</t>
         </is>
       </c>
       <c r="C398" s="13" t="inlineStr">
         <is>
-          <t>tezimandi</t>
+          <t>trade555</t>
         </is>
       </c>
       <c r="D398" s="12" t="inlineStr">
         <is>
-          <t>tezimandibhaibhai@gmail.com</t>
+          <t>suryanshvishnoi5@gmail.com</t>
         </is>
       </c>
       <c r="E398" s="12" t="inlineStr">
         <is>
-          <t>9883118215</t>
+          <t>9084242427</t>
         </is>
       </c>
       <c r="F398" s="12" t="inlineStr">
@@ -29513,34 +29531,34 @@
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H398" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I398" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J398" s="14" t="n">
-        <v>3764</v>
+        <v>6924</v>
       </c>
       <c r="K398" s="14" t="n">
-        <v>20890</v>
+        <v>20921</v>
       </c>
       <c r="L398" s="15" t="n">
-        <v>6681</v>
+        <v>7073</v>
       </c>
       <c r="M398" s="12" t="inlineStr">
         <is>
-          <t>689dc7cba17ac90013e4012c</t>
+          <t>69c768f29ff8560012a56967</t>
         </is>
       </c>
       <c r="N398" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/689dc7cba17ac90013e4012c</t>
+          <t>https://superprofile.bio/vig/69c768f29ff8560012a56967</t>
         </is>
       </c>
       <c r="O398" s="17" t="inlineStr">
@@ -29560,22 +29578,22 @@
       </c>
       <c r="B399" s="20" t="inlineStr">
         <is>
-          <t>6411ac9a255671001f4b83f0</t>
+          <t>682368f50efed700131d7266</t>
         </is>
       </c>
       <c r="C399" s="20" t="inlineStr">
         <is>
-          <t>prakasheee</t>
+          <t>tezimandi</t>
         </is>
       </c>
       <c r="D399" s="19" t="inlineStr">
         <is>
-          <t>pmcinematography@gmail.com</t>
+          <t>tezimandibhaibhai@gmail.com</t>
         </is>
       </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
-          <t>7874519419</t>
+          <t>9883118215</t>
         </is>
       </c>
       <c r="F399" s="19" t="inlineStr">
@@ -29585,34 +29603,34 @@
       </c>
       <c r="G399" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H399" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I399" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J399" s="21" t="n">
-        <v>4940</v>
+        <v>3764</v>
       </c>
       <c r="K399" s="21" t="n">
-        <v>20747</v>
+        <v>20890</v>
       </c>
       <c r="L399" s="22" t="n">
-        <v>5927</v>
+        <v>6681</v>
       </c>
       <c r="M399" s="19" t="inlineStr">
         <is>
-          <t>69f9e4e9abc3bf00138986d8</t>
+          <t>689dc7cba17ac90013e4012c</t>
         </is>
       </c>
       <c r="N399" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f9e4e9abc3bf00138986d8</t>
+          <t>https://superprofile.bio/vig/689dc7cba17ac90013e4012c</t>
         </is>
       </c>
       <c r="O399" s="24" t="inlineStr">
@@ -29632,22 +29650,22 @@
       </c>
       <c r="B400" s="13" t="inlineStr">
         <is>
-          <t>64af7262460c89001f61e10f</t>
+          <t>6411ac9a255671001f4b83f0</t>
         </is>
       </c>
       <c r="C400" s="13" t="inlineStr">
         <is>
-          <t>alphawavetrader</t>
+          <t>prakasheee</t>
         </is>
       </c>
       <c r="D400" s="12" t="inlineStr">
         <is>
-          <t>traderalphawave@gmail.com</t>
+          <t>pmcinematography@gmail.com</t>
         </is>
       </c>
       <c r="E400" s="12" t="inlineStr">
         <is>
-          <t>8807423126</t>
+          <t>7874519419</t>
         </is>
       </c>
       <c r="F400" s="12" t="inlineStr">
@@ -29657,34 +29675,34 @@
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H400" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I400" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J400" s="14" t="n">
-        <v>20702</v>
+        <v>4940</v>
       </c>
       <c r="K400" s="14" t="n">
-        <v>20702</v>
+        <v>20747</v>
       </c>
       <c r="L400" s="15" t="n">
-        <v>20702</v>
+        <v>5927</v>
       </c>
       <c r="M400" s="12" t="inlineStr">
         <is>
-          <t>67f637996919960013fa64fd</t>
+          <t>69f9e4e9abc3bf00138986d8</t>
         </is>
       </c>
       <c r="N400" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67f637996919960013fa64fd</t>
+          <t>https://superprofile.bio/vig/69f9e4e9abc3bf00138986d8</t>
         </is>
       </c>
       <c r="O400" s="17" t="inlineStr">
@@ -29704,22 +29722,22 @@
       </c>
       <c r="B401" s="20" t="inlineStr">
         <is>
-          <t>67c94e21f8f7120014c00900</t>
+          <t>64af7262460c89001f61e10f</t>
         </is>
       </c>
       <c r="C401" s="20" t="inlineStr">
         <is>
-          <t>httpstme4xrkpkvzmi82mtzl</t>
+          <t>alphawavetrader</t>
         </is>
       </c>
       <c r="D401" s="19" t="inlineStr">
         <is>
-          <t>tradingwithvivek.87@gmail.com</t>
+          <t>traderalphawave@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="19" t="inlineStr">
         <is>
-          <t>9106562524</t>
+          <t>8807423126</t>
         </is>
       </c>
       <c r="F401" s="19" t="inlineStr">
@@ -29729,34 +29747,34 @@
       </c>
       <c r="G401" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H401" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I401" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J401" s="21" t="n">
-        <v>1619</v>
+        <v>20702</v>
       </c>
       <c r="K401" s="21" t="n">
-        <v>20620</v>
+        <v>20702</v>
       </c>
       <c r="L401" s="22" t="n">
-        <v>8132</v>
+        <v>20702</v>
       </c>
       <c r="M401" s="19" t="inlineStr">
         <is>
-          <t>6a7ac8e844ab5300132d194a</t>
+          <t>67f637996919960013fa64fd</t>
         </is>
       </c>
       <c r="N401" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
+          <t>https://superprofile.bio/vig/67f637996919960013fa64fd</t>
         </is>
       </c>
       <c r="O401" s="24" t="inlineStr">
@@ -29776,22 +29794,22 @@
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>6788df9652dd2b00134ab463</t>
+          <t>67c94e21f8f7120014c00900</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
         <is>
-          <t>tradelikeunstoppable</t>
+          <t>httpstme4xrkpkvzmi82mtzl</t>
         </is>
       </c>
       <c r="D402" s="12" t="inlineStr">
         <is>
-          <t>dhruvalk8@gmail.com</t>
+          <t>tradingwithvivek.87@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr">
         <is>
-          <t>6354517180</t>
+          <t>9106562524</t>
         </is>
       </c>
       <c r="F402" s="12" t="inlineStr">
@@ -29801,7 +29819,7 @@
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H402" s="12" t="inlineStr">
@@ -29810,25 +29828,25 @@
         </is>
       </c>
       <c r="I402" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J402" s="14" t="n">
-        <v>3001</v>
+        <v>1619</v>
       </c>
       <c r="K402" s="14" t="n">
-        <v>20484</v>
+        <v>20620</v>
       </c>
       <c r="L402" s="15" t="n">
-        <v>12715</v>
+        <v>8132</v>
       </c>
       <c r="M402" s="12" t="inlineStr">
         <is>
-          <t>6a44e4c03b46b900134e50be</t>
+          <t>6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="N402" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a44e4c03b46b900134e50be</t>
+          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="O402" s="17" t="inlineStr">
@@ -29848,22 +29866,22 @@
       </c>
       <c r="B403" s="20" t="inlineStr">
         <is>
-          <t>654e35d70ce920001de26234</t>
+          <t>6788df9652dd2b00134ab463</t>
         </is>
       </c>
       <c r="C403" s="20" t="inlineStr">
         <is>
-          <t>radiobabaa</t>
+          <t>tradelikeunstoppable</t>
         </is>
       </c>
       <c r="D403" s="19" t="inlineStr">
         <is>
-          <t>bairaagilokam@gmail.com</t>
+          <t>dhruvalk8@gmail.com</t>
         </is>
       </c>
       <c r="E403" s="19" t="inlineStr">
         <is>
-          <t>9000090942</t>
+          <t>6354517180</t>
         </is>
       </c>
       <c r="F403" s="19" t="inlineStr">
@@ -29873,7 +29891,7 @@
       </c>
       <c r="G403" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H403" s="19" t="inlineStr">
@@ -29882,25 +29900,25 @@
         </is>
       </c>
       <c r="I403" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J403" s="21" t="n">
-        <v>2038</v>
+        <v>3001</v>
       </c>
       <c r="K403" s="21" t="n">
-        <v>20331</v>
+        <v>20484</v>
       </c>
       <c r="L403" s="22" t="n">
-        <v>4710</v>
+        <v>12715</v>
       </c>
       <c r="M403" s="19" t="inlineStr">
         <is>
-          <t>6a92b996b3a738001366c2fc</t>
+          <t>6a44e4c03b46b900134e50be</t>
         </is>
       </c>
       <c r="N403" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a92b996b3a738001366c2fc</t>
+          <t>https://superprofile.bio/vig/6a44e4c03b46b900134e50be</t>
         </is>
       </c>
       <c r="O403" s="24" t="inlineStr">
@@ -29920,22 +29938,22 @@
       </c>
       <c r="B404" s="13" t="inlineStr">
         <is>
-          <t>647632b25fce500020877642</t>
+          <t>654e35d70ce920001de26234</t>
         </is>
       </c>
       <c r="C404" s="13" t="inlineStr">
         <is>
-          <t>educationhub2030</t>
+          <t>radiobabaa</t>
         </is>
       </c>
       <c r="D404" s="12" t="inlineStr">
         <is>
-          <t>sarojneeraj172@gmail.com</t>
+          <t>bairaagilokam@gmail.com</t>
         </is>
       </c>
       <c r="E404" s="12" t="inlineStr">
         <is>
-          <t>9628057757</t>
+          <t>9000090942</t>
         </is>
       </c>
       <c r="F404" s="12" t="inlineStr">
@@ -29945,7 +29963,7 @@
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H404" s="12" t="inlineStr">
@@ -29954,25 +29972,25 @@
         </is>
       </c>
       <c r="I404" s="13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J404" s="14" t="n">
-        <v>2987</v>
+        <v>2038</v>
       </c>
       <c r="K404" s="14" t="n">
-        <v>20319</v>
+        <v>20331</v>
       </c>
       <c r="L404" s="15" t="n">
-        <v>3392</v>
+        <v>4710</v>
       </c>
       <c r="M404" s="12" t="inlineStr">
         <is>
-          <t>6a6f1f484c5b83001337bf67</t>
+          <t>6a92b996b3a738001366c2fc</t>
         </is>
       </c>
       <c r="N404" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6f1f484c5b83001337bf67</t>
+          <t>https://superprofile.bio/vig/6a92b996b3a738001366c2fc</t>
         </is>
       </c>
       <c r="O404" s="17" t="inlineStr">
@@ -29992,22 +30010,22 @@
       </c>
       <c r="B405" s="20" t="inlineStr">
         <is>
-          <t>6645fe15c68305001322e7a6</t>
+          <t>647632b25fce500020877642</t>
         </is>
       </c>
       <c r="C405" s="20" t="inlineStr">
         <is>
-          <t>garyan400</t>
+          <t>educationhub2030</t>
         </is>
       </c>
       <c r="D405" s="19" t="inlineStr">
         <is>
-          <t>garyan400@gmail.com</t>
+          <t>sarojneeraj172@gmail.com</t>
         </is>
       </c>
       <c r="E405" s="19" t="inlineStr">
         <is>
-          <t>8963864273</t>
+          <t>9628057757</t>
         </is>
       </c>
       <c r="F405" s="19" t="inlineStr">
@@ -30017,34 +30035,34 @@
       </c>
       <c r="G405" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H405" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I405" s="20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J405" s="21" t="n">
-        <v>6008</v>
+        <v>2987</v>
       </c>
       <c r="K405" s="21" t="n">
-        <v>20165</v>
+        <v>20319</v>
       </c>
       <c r="L405" s="22" t="n">
-        <v>14157</v>
+        <v>3392</v>
       </c>
       <c r="M405" s="19" t="inlineStr">
         <is>
-          <t>667eafdc90ab6900137c23d2</t>
+          <t>6a6f1f484c5b83001337bf67</t>
         </is>
       </c>
       <c r="N405" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/667eafdc90ab6900137c23d2</t>
+          <t>https://superprofile.bio/vig/6a6f1f484c5b83001337bf67</t>
         </is>
       </c>
       <c r="O405" s="24" t="inlineStr">
@@ -30064,22 +30082,22 @@
       </c>
       <c r="B406" s="13" t="inlineStr">
         <is>
-          <t>658720a2a2c6b0001ecbed39</t>
+          <t>6645fe15c68305001322e7a6</t>
         </is>
       </c>
       <c r="C406" s="13" t="inlineStr">
         <is>
-          <t>bestbuyselldignalstratigy</t>
+          <t>garyan400</t>
         </is>
       </c>
       <c r="D406" s="12" t="inlineStr">
         <is>
-          <t>ramankumarsgg74@gmail.com</t>
+          <t>garyan400@gmail.com</t>
         </is>
       </c>
       <c r="E406" s="12" t="inlineStr">
         <is>
-          <t>7352035747</t>
+          <t>8963864273</t>
         </is>
       </c>
       <c r="F406" s="12" t="inlineStr">
@@ -30101,22 +30119,22 @@
         <v>2</v>
       </c>
       <c r="J406" s="14" t="n">
-        <v>10069</v>
+        <v>6008</v>
       </c>
       <c r="K406" s="14" t="n">
-        <v>20138</v>
+        <v>20165</v>
       </c>
       <c r="L406" s="15" t="n">
-        <v>10069</v>
+        <v>14157</v>
       </c>
       <c r="M406" s="12" t="inlineStr">
         <is>
-          <t>6a8a0949a752420013868b9f</t>
+          <t>667eafdc90ab6900137c23d2</t>
         </is>
       </c>
       <c r="N406" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8a0949a752420013868b9f</t>
+          <t>https://superprofile.bio/vig/667eafdc90ab6900137c23d2</t>
         </is>
       </c>
       <c r="O406" s="17" t="inlineStr">
@@ -30136,22 +30154,22 @@
       </c>
       <c r="B407" s="20" t="inlineStr">
         <is>
-          <t>6384e99de7291200319784c0</t>
+          <t>658720a2a2c6b0001ecbed39</t>
         </is>
       </c>
       <c r="C407" s="20" t="inlineStr">
         <is>
-          <t>traderlakshya1</t>
+          <t>bestbuyselldignalstratigy</t>
         </is>
       </c>
       <c r="D407" s="19" t="inlineStr">
         <is>
-          <t>bhedjeetsinghparihar@gmail.com</t>
+          <t>ramankumarsgg74@gmail.com</t>
         </is>
       </c>
       <c r="E407" s="19" t="inlineStr">
         <is>
-          <t>9412025083</t>
+          <t>7352035747</t>
         </is>
       </c>
       <c r="F407" s="19" t="inlineStr">
@@ -30161,34 +30179,34 @@
       </c>
       <c r="G407" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H407" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I407" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J407" s="21" t="n">
-        <v>19716</v>
+        <v>10069</v>
       </c>
       <c r="K407" s="21" t="n">
-        <v>19716</v>
+        <v>20138</v>
       </c>
       <c r="L407" s="22" t="n">
-        <v>19716</v>
+        <v>10069</v>
       </c>
       <c r="M407" s="19" t="inlineStr">
         <is>
-          <t>68f36b1663e0410013ae9462</t>
+          <t>6a8a0949a752420013868b9f</t>
         </is>
       </c>
       <c r="N407" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f36b1663e0410013ae9462</t>
+          <t>https://superprofile.bio/vig/6a8a0949a752420013868b9f</t>
         </is>
       </c>
       <c r="O407" s="24" t="inlineStr">
@@ -30208,22 +30226,22 @@
       </c>
       <c r="B408" s="13" t="inlineStr">
         <is>
-          <t>66e9b755945e660013f4e02a</t>
+          <t>6384e99de7291200319784c0</t>
         </is>
       </c>
       <c r="C408" s="13" t="inlineStr">
         <is>
-          <t>traderlakshya</t>
+          <t>traderlakshya1</t>
         </is>
       </c>
       <c r="D408" s="12" t="inlineStr">
         <is>
-          <t>jaykaranupstox@gmail.com</t>
+          <t>bhedjeetsinghparihar@gmail.com</t>
         </is>
       </c>
       <c r="E408" s="12" t="inlineStr">
         <is>
-          <t>8053113104</t>
+          <t>9412025083</t>
         </is>
       </c>
       <c r="F408" s="12" t="inlineStr">
@@ -30233,12 +30251,12 @@
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H408" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I408" s="13" t="n">
@@ -30255,12 +30273,12 @@
       </c>
       <c r="M408" s="12" t="inlineStr">
         <is>
-          <t>685418fa8e054b0013a1974d</t>
+          <t>68f36b1663e0410013ae9462</t>
         </is>
       </c>
       <c r="N408" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/685418fa8e054b0013a1974d</t>
+          <t>https://superprofile.bio/vig/68f36b1663e0410013ae9462</t>
         </is>
       </c>
       <c r="O408" s="17" t="inlineStr">
@@ -30280,22 +30298,22 @@
       </c>
       <c r="B409" s="20" t="inlineStr">
         <is>
-          <t>6a982bce919b22001319d7ea</t>
+          <t>66e9b755945e660013f4e02a</t>
         </is>
       </c>
       <c r="C409" s="20" t="inlineStr">
         <is>
-          <t>tradinngguru33</t>
+          <t>traderlakshya</t>
         </is>
       </c>
       <c r="D409" s="19" t="inlineStr">
         <is>
-          <t>monukumari7770@gmail.com</t>
+          <t>jaykaranupstox@gmail.com</t>
         </is>
       </c>
       <c r="E409" s="19" t="inlineStr">
         <is>
-          <t>6376056680</t>
+          <t>8053113104</t>
         </is>
       </c>
       <c r="F409" s="19" t="inlineStr">
@@ -30305,34 +30323,34 @@
       </c>
       <c r="G409" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H409" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I409" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J409" s="21" t="n">
-        <v>3896</v>
+        <v>19716</v>
       </c>
       <c r="K409" s="21" t="n">
-        <v>19685</v>
+        <v>19716</v>
       </c>
       <c r="L409" s="22" t="n">
-        <v>5263</v>
+        <v>19716</v>
       </c>
       <c r="M409" s="19" t="inlineStr">
         <is>
-          <t>6a982d3d14976c0013e3405c</t>
+          <t>685418fa8e054b0013a1974d</t>
         </is>
       </c>
       <c r="N409" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a982d3d14976c0013e3405c</t>
+          <t>https://superprofile.bio/vig/685418fa8e054b0013a1974d</t>
         </is>
       </c>
       <c r="O409" s="24" t="inlineStr">
@@ -30352,22 +30370,22 @@
       </c>
       <c r="B410" s="13" t="inlineStr">
         <is>
-          <t>69e5cb3ddd64680013de5fdb</t>
+          <t>6a982bce919b22001319d7ea</t>
         </is>
       </c>
       <c r="C410" s="13" t="inlineStr">
         <is>
-          <t>officialadmiiin</t>
+          <t>tradinngguru33</t>
         </is>
       </c>
       <c r="D410" s="12" t="inlineStr">
         <is>
-          <t>parthpartil1994@gmail.com</t>
+          <t>monukumari7770@gmail.com</t>
         </is>
       </c>
       <c r="E410" s="12" t="inlineStr">
         <is>
-          <t>9509105085</t>
+          <t>6376056680</t>
         </is>
       </c>
       <c r="F410" s="12" t="inlineStr">
@@ -30377,34 +30395,34 @@
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H410" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I410" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J410" s="14" t="n">
-        <v>19512</v>
+        <v>3896</v>
       </c>
       <c r="K410" s="14" t="n">
-        <v>19512</v>
+        <v>19685</v>
       </c>
       <c r="L410" s="15" t="n">
-        <v>19512</v>
+        <v>5263</v>
       </c>
       <c r="M410" s="12" t="inlineStr">
         <is>
-          <t>6a50527f6affe90013bbf659</t>
+          <t>6a982d3d14976c0013e3405c</t>
         </is>
       </c>
       <c r="N410" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a50527f6affe90013bbf659</t>
+          <t>https://superprofile.bio/vig/6a982d3d14976c0013e3405c</t>
         </is>
       </c>
       <c r="O410" s="17" t="inlineStr">
@@ -30424,22 +30442,22 @@
       </c>
       <c r="B411" s="20" t="inlineStr">
         <is>
-          <t>648dfce161a63800204d58c4</t>
+          <t>69e5cb3ddd64680013de5fdb</t>
         </is>
       </c>
       <c r="C411" s="20" t="inlineStr">
         <is>
-          <t>pallavtradetactics17</t>
+          <t>officialadmiiin</t>
         </is>
       </c>
       <c r="D411" s="19" t="inlineStr">
         <is>
-          <t>thinkcrypto17@gmail.com</t>
+          <t>parthpartil1994@gmail.com</t>
         </is>
       </c>
       <c r="E411" s="19" t="inlineStr">
         <is>
-          <t>8979574556</t>
+          <t>9509105085</t>
         </is>
       </c>
       <c r="F411" s="19" t="inlineStr">
@@ -30449,34 +30467,34 @@
       </c>
       <c r="G411" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H411" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I411" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J411" s="21" t="n">
-        <v>7716</v>
+        <v>19512</v>
       </c>
       <c r="K411" s="21" t="n">
-        <v>19430</v>
+        <v>19512</v>
       </c>
       <c r="L411" s="22" t="n">
-        <v>7716</v>
+        <v>19512</v>
       </c>
       <c r="M411" s="19" t="inlineStr">
         <is>
-          <t>660a49448b1e55001a0cc5a4</t>
+          <t>6a50527f6affe90013bbf659</t>
         </is>
       </c>
       <c r="N411" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/660a49448b1e55001a0cc5a4</t>
+          <t>https://superprofile.bio/vig/6a50527f6affe90013bbf659</t>
         </is>
       </c>
       <c r="O411" s="24" t="inlineStr">
@@ -30496,22 +30514,22 @@
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>62115e4a6bd738258707c0e9</t>
+          <t>648dfce161a63800204d58c4</t>
         </is>
       </c>
       <c r="C412" s="13" t="inlineStr">
         <is>
-          <t>aditya</t>
+          <t>pallavtradetactics17</t>
         </is>
       </c>
       <c r="D412" s="12" t="inlineStr">
         <is>
-          <t>imavschoudhary@gmail.com</t>
+          <t>thinkcrypto17@gmail.com</t>
         </is>
       </c>
       <c r="E412" s="12" t="inlineStr">
         <is>
-          <t>9717115749</t>
+          <t>8979574556</t>
         </is>
       </c>
       <c r="F412" s="12" t="inlineStr">
@@ -30530,25 +30548,25 @@
         </is>
       </c>
       <c r="I412" s="13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J412" s="14" t="n">
-        <v>2355</v>
+        <v>7716</v>
       </c>
       <c r="K412" s="14" t="n">
-        <v>19365</v>
+        <v>19430</v>
       </c>
       <c r="L412" s="15" t="n">
-        <v>4379</v>
+        <v>7716</v>
       </c>
       <c r="M412" s="12" t="inlineStr">
         <is>
-          <t>6511690d55ae1b0058703c86</t>
+          <t>660a49448b1e55001a0cc5a4</t>
         </is>
       </c>
       <c r="N412" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
+          <t>https://superprofile.bio/vig/660a49448b1e55001a0cc5a4</t>
         </is>
       </c>
       <c r="O412" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 02:29:51 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 05:39:31 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 05:39:31 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 06:34:04 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 06:34:04 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 07:03:26 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 07:03:26 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 08:30:03 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 08:30:03 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 10:40:46 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹51,007,586.00</t>
+          <t>₹51,011,186.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>3480558</v>
+        <v>3482918</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>2</v>
       </c>
       <c r="J514" s="14" t="n">
-        <v>8860</v>
+        <v>3810</v>
       </c>
       <c r="K514" s="14" t="n">
         <v>12670</v>
@@ -43618,22 +43618,22 @@
       </c>
       <c r="B594" s="13" t="inlineStr">
         <is>
-          <t>6478b051107b57001f86f918</t>
+          <t>66d329848007d20013cda7e5</t>
         </is>
       </c>
       <c r="C594" s="13" t="inlineStr">
         <is>
-          <t>srptrader</t>
+          <t>madan21</t>
         </is>
       </c>
       <c r="D594" s="12" t="inlineStr">
         <is>
-          <t>jaymaajaymaa330@gmail.com</t>
+          <t>madanlal010123@gmail.com</t>
         </is>
       </c>
       <c r="E594" s="12" t="inlineStr">
         <is>
-          <t>6377083526</t>
+          <t>9140204389</t>
         </is>
       </c>
       <c r="F594" s="12" t="inlineStr">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="G594" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H594" s="12" t="inlineStr">
@@ -43652,25 +43652,25 @@
         </is>
       </c>
       <c r="I594" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J594" s="14" t="n">
-        <v>1799</v>
+        <v>3600</v>
       </c>
       <c r="K594" s="14" t="n">
-        <v>7196</v>
+        <v>7200</v>
       </c>
       <c r="L594" s="15" t="n">
-        <v>1799</v>
+        <v>3600</v>
       </c>
       <c r="M594" s="12" t="inlineStr">
         <is>
-          <t>66f2e10389f9ce0013483dc0</t>
+          <t>6a5737d04ca9e200136e06b8</t>
         </is>
       </c>
       <c r="N594" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66f2e10389f9ce0013483dc0</t>
+          <t>https://superprofile.bio/vig/6a5737d04ca9e200136e06b8</t>
         </is>
       </c>
       <c r="O594" s="17" t="inlineStr">
@@ -43690,22 +43690,22 @@
       </c>
       <c r="B595" s="20" t="inlineStr">
         <is>
-          <t>68187755c1c1c000138da976</t>
+          <t>6478b051107b57001f86f918</t>
         </is>
       </c>
       <c r="C595" s="20" t="inlineStr">
         <is>
-          <t>swingandmomentum</t>
+          <t>srptrader</t>
         </is>
       </c>
       <c r="D595" s="19" t="inlineStr">
         <is>
-          <t>aroffical966@gmail.com</t>
+          <t>jaymaajaymaa330@gmail.com</t>
         </is>
       </c>
       <c r="E595" s="19" t="inlineStr">
         <is>
-          <t>7568090936</t>
+          <t>6377083526</t>
         </is>
       </c>
       <c r="F595" s="19" t="inlineStr">
@@ -43720,29 +43720,29 @@
       </c>
       <c r="H595" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I595" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J595" s="21" t="n">
-        <v>4816</v>
+        <v>1799</v>
       </c>
       <c r="K595" s="21" t="n">
-        <v>7082</v>
+        <v>7196</v>
       </c>
       <c r="L595" s="22" t="n">
-        <v>4816</v>
+        <v>1799</v>
       </c>
       <c r="M595" s="19" t="inlineStr">
         <is>
-          <t>6824337bd729e000139c8cad</t>
+          <t>66f2e10389f9ce0013483dc0</t>
         </is>
       </c>
       <c r="N595" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6824337bd729e000139c8cad</t>
+          <t>https://superprofile.bio/vig/66f2e10389f9ce0013483dc0</t>
         </is>
       </c>
       <c r="O595" s="24" t="inlineStr">
@@ -43762,22 +43762,22 @@
       </c>
       <c r="B596" s="13" t="inlineStr">
         <is>
-          <t>64ae2db27c3a37001f2b6465</t>
+          <t>68187755c1c1c000138da976</t>
         </is>
       </c>
       <c r="C596" s="13" t="inlineStr">
         <is>
-          <t>rameshwarpatilfx</t>
+          <t>swingandmomentum</t>
         </is>
       </c>
       <c r="D596" s="12" t="inlineStr">
         <is>
-          <t>bittuoptiktok@gmail.com</t>
+          <t>aroffical966@gmail.com</t>
         </is>
       </c>
       <c r="E596" s="12" t="inlineStr">
         <is>
-          <t>8446564801</t>
+          <t>7568090936</t>
         </is>
       </c>
       <c r="F596" s="12" t="inlineStr">
@@ -43787,34 +43787,34 @@
       </c>
       <c r="G596" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H596" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I596" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J596" s="14" t="n">
-        <v>2352</v>
+        <v>4816</v>
       </c>
       <c r="K596" s="14" t="n">
-        <v>7056</v>
+        <v>7082</v>
       </c>
       <c r="L596" s="15" t="n">
-        <v>2352</v>
+        <v>4816</v>
       </c>
       <c r="M596" s="12" t="inlineStr">
         <is>
-          <t>6a588470ea73100013db8b8a</t>
+          <t>6824337bd729e000139c8cad</t>
         </is>
       </c>
       <c r="N596" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a588470ea73100013db8b8a</t>
+          <t>https://superprofile.bio/vig/6824337bd729e000139c8cad</t>
         </is>
       </c>
       <c r="O596" s="17" t="inlineStr">
@@ -43834,22 +43834,22 @@
       </c>
       <c r="B597" s="20" t="inlineStr">
         <is>
-          <t>66e912fe20ed2200137c17da</t>
+          <t>64ae2db27c3a37001f2b6465</t>
         </is>
       </c>
       <c r="C597" s="20" t="inlineStr">
         <is>
-          <t>zerotohero24</t>
+          <t>rameshwarpatilfx</t>
         </is>
       </c>
       <c r="D597" s="19" t="inlineStr">
         <is>
-          <t>pp1765948@gmail.com</t>
+          <t>bittuoptiktok@gmail.com</t>
         </is>
       </c>
       <c r="E597" s="19" t="inlineStr">
         <is>
-          <t>6378516328</t>
+          <t>8446564801</t>
         </is>
       </c>
       <c r="F597" s="19" t="inlineStr">
@@ -43859,34 +43859,34 @@
       </c>
       <c r="G597" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H597" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I597" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J597" s="21" t="n">
-        <v>1757</v>
+        <v>2352</v>
       </c>
       <c r="K597" s="21" t="n">
-        <v>7028</v>
+        <v>7056</v>
       </c>
       <c r="L597" s="22" t="n">
-        <v>1757</v>
+        <v>2352</v>
       </c>
       <c r="M597" s="19" t="inlineStr">
         <is>
-          <t>67ee67726cfba00013977e25</t>
+          <t>6a588470ea73100013db8b8a</t>
         </is>
       </c>
       <c r="N597" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ee67726cfba00013977e25</t>
+          <t>https://superprofile.bio/vig/6a588470ea73100013db8b8a</t>
         </is>
       </c>
       <c r="O597" s="24" t="inlineStr">
@@ -43906,22 +43906,22 @@
       </c>
       <c r="B598" s="13" t="inlineStr">
         <is>
-          <t>691b32dfef1f1c0013cb196d</t>
+          <t>66e912fe20ed2200137c17da</t>
         </is>
       </c>
       <c r="C598" s="13" t="inlineStr">
         <is>
-          <t>krishnamckenzie</t>
+          <t>zerotohero24</t>
         </is>
       </c>
       <c r="D598" s="12" t="inlineStr">
         <is>
-          <t>emergencemusic@gmail.com</t>
+          <t>pp1765948@gmail.com</t>
         </is>
       </c>
       <c r="E598" s="12" t="inlineStr">
         <is>
-          <t>8072053484</t>
+          <t>6378516328</t>
         </is>
       </c>
       <c r="F598" s="12" t="inlineStr">
@@ -43931,34 +43931,34 @@
       </c>
       <c r="G598" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H598" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I598" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J598" s="14" t="n">
-        <v>1407</v>
+        <v>1757</v>
       </c>
       <c r="K598" s="14" t="n">
-        <v>6940</v>
+        <v>7028</v>
       </c>
       <c r="L598" s="15" t="n">
-        <v>5533</v>
+        <v>1757</v>
       </c>
       <c r="M598" s="12" t="inlineStr">
         <is>
-          <t>696f773e4386d6001250fdfe</t>
+          <t>67ee67726cfba00013977e25</t>
         </is>
       </c>
       <c r="N598" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696f773e4386d6001250fdfe</t>
+          <t>https://superprofile.bio/vig/67ee67726cfba00013977e25</t>
         </is>
       </c>
       <c r="O598" s="17" t="inlineStr">
@@ -43978,22 +43978,22 @@
       </c>
       <c r="B599" s="20" t="inlineStr">
         <is>
-          <t>62d051bc0178fa29153b140b</t>
+          <t>691b32dfef1f1c0013cb196d</t>
         </is>
       </c>
       <c r="C599" s="20" t="inlineStr">
         <is>
-          <t>vinayharwani</t>
+          <t>krishnamckenzie</t>
         </is>
       </c>
       <c r="D599" s="19" t="inlineStr">
         <is>
-          <t>vinayharwani999@gmail.com</t>
+          <t>emergencemusic@gmail.com</t>
         </is>
       </c>
       <c r="E599" s="19" t="inlineStr">
         <is>
-          <t>9664681811</t>
+          <t>8072053484</t>
         </is>
       </c>
       <c r="F599" s="19" t="inlineStr">
@@ -44003,34 +44003,34 @@
       </c>
       <c r="G599" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H599" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I599" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J599" s="21" t="n">
-        <v>3420</v>
+        <v>1407</v>
       </c>
       <c r="K599" s="21" t="n">
-        <v>6840</v>
+        <v>6940</v>
       </c>
       <c r="L599" s="22" t="n">
-        <v>3420</v>
+        <v>5533</v>
       </c>
       <c r="M599" s="19" t="inlineStr">
         <is>
-          <t>6a8eb09f58670a0013e9aa35</t>
+          <t>696f773e4386d6001250fdfe</t>
         </is>
       </c>
       <c r="N599" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8eb09f58670a0013e9aa35</t>
+          <t>https://superprofile.bio/vig/696f773e4386d6001250fdfe</t>
         </is>
       </c>
       <c r="O599" s="24" t="inlineStr">
@@ -44050,22 +44050,22 @@
       </c>
       <c r="B600" s="13" t="inlineStr">
         <is>
-          <t>641586bcd065950020804127</t>
+          <t>62d051bc0178fa29153b140b</t>
         </is>
       </c>
       <c r="C600" s="13" t="inlineStr">
         <is>
-          <t>tjpremium</t>
+          <t>vinayharwani</t>
         </is>
       </c>
       <c r="D600" s="12" t="inlineStr">
         <is>
-          <t>tj38473@gmail.com</t>
+          <t>vinayharwani999@gmail.com</t>
         </is>
       </c>
       <c r="E600" s="12" t="inlineStr">
         <is>
-          <t>8530949550</t>
+          <t>9664681811</t>
         </is>
       </c>
       <c r="F600" s="12" t="inlineStr">
@@ -44075,34 +44075,34 @@
       </c>
       <c r="G600" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H600" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I600" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J600" s="14" t="n">
-        <v>2928</v>
+        <v>3420</v>
       </c>
       <c r="K600" s="14" t="n">
-        <v>6832</v>
+        <v>6840</v>
       </c>
       <c r="L600" s="15" t="n">
-        <v>2928</v>
+        <v>3420</v>
       </c>
       <c r="M600" s="12" t="inlineStr">
         <is>
-          <t>6415820693799f001f43e13c</t>
+          <t>6a8eb09f58670a0013e9aa35</t>
         </is>
       </c>
       <c r="N600" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6415820693799f001f43e13c</t>
+          <t>https://superprofile.bio/vig/6a8eb09f58670a0013e9aa35</t>
         </is>
       </c>
       <c r="O600" s="17" t="inlineStr">
@@ -44122,22 +44122,22 @@
       </c>
       <c r="B601" s="20" t="inlineStr">
         <is>
-          <t>6790b09868ed970013e5c99b</t>
+          <t>641586bcd065950020804127</t>
         </is>
       </c>
       <c r="C601" s="20" t="inlineStr">
         <is>
-          <t>punamdevi</t>
+          <t>tjpremium</t>
         </is>
       </c>
       <c r="D601" s="19" t="inlineStr">
         <is>
-          <t>Kchaupal@gmail.com</t>
+          <t>tj38473@gmail.com</t>
         </is>
       </c>
       <c r="E601" s="19" t="inlineStr">
         <is>
-          <t>8652585763</t>
+          <t>8530949550</t>
         </is>
       </c>
       <c r="F601" s="19" t="inlineStr">
@@ -44147,34 +44147,34 @@
       </c>
       <c r="G601" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H601" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I601" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J601" s="21" t="n">
-        <v>1941</v>
+        <v>2928</v>
       </c>
       <c r="K601" s="21" t="n">
-        <v>6794</v>
+        <v>6832</v>
       </c>
       <c r="L601" s="22" t="n">
-        <v>4853</v>
+        <v>2928</v>
       </c>
       <c r="M601" s="19" t="inlineStr">
         <is>
-          <t>670fd912c79ae80013702ac6</t>
+          <t>6415820693799f001f43e13c</t>
         </is>
       </c>
       <c r="N601" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/670fd912c79ae80013702ac6</t>
+          <t>https://superprofile.bio/vig/6415820693799f001f43e13c</t>
         </is>
       </c>
       <c r="O601" s="24" t="inlineStr">
@@ -44194,22 +44194,22 @@
       </c>
       <c r="B602" s="13" t="inlineStr">
         <is>
-          <t>6669b7bbb2f9520013e6b8d7</t>
+          <t>6790b09868ed970013e5c99b</t>
         </is>
       </c>
       <c r="C602" s="13" t="inlineStr">
         <is>
-          <t>sonalitrades</t>
+          <t>punamdevi</t>
         </is>
       </c>
       <c r="D602" s="12" t="inlineStr">
         <is>
-          <t>sohamtalekar24@gmail.com</t>
+          <t>Kchaupal@gmail.com</t>
         </is>
       </c>
       <c r="E602" s="12" t="inlineStr">
         <is>
-          <t>7777071598</t>
+          <t>8652585763</t>
         </is>
       </c>
       <c r="F602" s="12" t="inlineStr">
@@ -44219,34 +44219,34 @@
       </c>
       <c r="G602" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H602" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I602" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J602" s="14" t="n">
-        <v>6749</v>
+        <v>1941</v>
       </c>
       <c r="K602" s="14" t="n">
-        <v>6749</v>
+        <v>6794</v>
       </c>
       <c r="L602" s="15" t="n">
-        <v>6749</v>
+        <v>4853</v>
       </c>
       <c r="M602" s="12" t="inlineStr">
         <is>
-          <t>66aa04eb0c2dc60013ac0e24</t>
+          <t>670fd912c79ae80013702ac6</t>
         </is>
       </c>
       <c r="N602" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66aa04eb0c2dc60013ac0e24</t>
+          <t>https://superprofile.bio/vig/670fd912c79ae80013702ac6</t>
         </is>
       </c>
       <c r="O602" s="17" t="inlineStr">
@@ -44266,22 +44266,22 @@
       </c>
       <c r="B603" s="20" t="inlineStr">
         <is>
-          <t>676eb3758806e70013ff25c0</t>
+          <t>6669b7bbb2f9520013e6b8d7</t>
         </is>
       </c>
       <c r="C603" s="20" t="inlineStr">
         <is>
-          <t>yuvrajdangi389</t>
+          <t>sonalitrades</t>
         </is>
       </c>
       <c r="D603" s="19" t="inlineStr">
         <is>
-          <t>dangiyuvraj576@gmail.com</t>
+          <t>sohamtalekar24@gmail.com</t>
         </is>
       </c>
       <c r="E603" s="19" t="inlineStr">
         <is>
-          <t>9244544652</t>
+          <t>7777071598</t>
         </is>
       </c>
       <c r="F603" s="19" t="inlineStr">
@@ -44291,34 +44291,34 @@
       </c>
       <c r="G603" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H603" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I603" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J603" s="21" t="n">
-        <v>1440</v>
+        <v>6749</v>
       </c>
       <c r="K603" s="21" t="n">
-        <v>6660</v>
+        <v>6749</v>
       </c>
       <c r="L603" s="22" t="n">
-        <v>1440</v>
+        <v>6749</v>
       </c>
       <c r="M603" s="19" t="inlineStr">
         <is>
-          <t>69fabe798248fc0013ab1190</t>
+          <t>66aa04eb0c2dc60013ac0e24</t>
         </is>
       </c>
       <c r="N603" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69fabe798248fc0013ab1190</t>
+          <t>https://superprofile.bio/vig/66aa04eb0c2dc60013ac0e24</t>
         </is>
       </c>
       <c r="O603" s="24" t="inlineStr">
@@ -44338,22 +44338,22 @@
       </c>
       <c r="B604" s="13" t="inlineStr">
         <is>
-          <t>6a27d380afc4cf0013f8bdcb</t>
+          <t>676eb3758806e70013ff25c0</t>
         </is>
       </c>
       <c r="C604" s="13" t="inlineStr">
         <is>
-          <t>vcpequitytrader1</t>
+          <t>yuvrajdangi389</t>
         </is>
       </c>
       <c r="D604" s="12" t="inlineStr">
         <is>
-          <t>xenosdante886@gmail.com</t>
+          <t>dangiyuvraj576@gmail.com</t>
         </is>
       </c>
       <c r="E604" s="12" t="inlineStr">
         <is>
-          <t>9706034931</t>
+          <t>9244544652</t>
         </is>
       </c>
       <c r="F604" s="12" t="inlineStr">
@@ -44363,34 +44363,34 @@
       </c>
       <c r="G604" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H604" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I604" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J604" s="14" t="n">
-        <v>1647</v>
+        <v>1440</v>
       </c>
       <c r="K604" s="14" t="n">
-        <v>6588</v>
+        <v>6660</v>
       </c>
       <c r="L604" s="15" t="n">
-        <v>1647</v>
+        <v>1440</v>
       </c>
       <c r="M604" s="12" t="inlineStr">
         <is>
-          <t>6a28f8f00bd2e80014533656</t>
+          <t>69fabe798248fc0013ab1190</t>
         </is>
       </c>
       <c r="N604" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a28f8f00bd2e80014533656</t>
+          <t>https://superprofile.bio/vig/69fabe798248fc0013ab1190</t>
         </is>
       </c>
       <c r="O604" s="17" t="inlineStr">
@@ -44410,22 +44410,22 @@
       </c>
       <c r="B605" s="20" t="inlineStr">
         <is>
-          <t>6a5f0754cbc2ff00131a7ae9</t>
+          <t>6a27d380afc4cf0013f8bdcb</t>
         </is>
       </c>
       <c r="C605" s="20" t="inlineStr">
         <is>
-          <t>vippremiummembership</t>
+          <t>vcpequitytrader1</t>
         </is>
       </c>
       <c r="D605" s="19" t="inlineStr">
         <is>
-          <t>jaibajarangbali9079@gmail.com</t>
+          <t>xenosdante886@gmail.com</t>
         </is>
       </c>
       <c r="E605" s="19" t="inlineStr">
         <is>
-          <t>9784700662</t>
+          <t>9706034931</t>
         </is>
       </c>
       <c r="F605" s="19" t="inlineStr">
@@ -44435,34 +44435,34 @@
       </c>
       <c r="G605" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H605" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I605" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J605" s="21" t="n">
-        <v>3292</v>
+        <v>1647</v>
       </c>
       <c r="K605" s="21" t="n">
-        <v>6584</v>
+        <v>6588</v>
       </c>
       <c r="L605" s="22" t="n">
-        <v>3292</v>
+        <v>1647</v>
       </c>
       <c r="M605" s="19" t="inlineStr">
         <is>
-          <t>6a5f90330f3a3c0014f14885</t>
+          <t>6a28f8f00bd2e80014533656</t>
         </is>
       </c>
       <c r="N605" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5f90330f3a3c0014f14885</t>
+          <t>https://superprofile.bio/vig/6a28f8f00bd2e80014533656</t>
         </is>
       </c>
       <c r="O605" s="24" t="inlineStr">
@@ -44482,22 +44482,22 @@
       </c>
       <c r="B606" s="13" t="inlineStr">
         <is>
-          <t>64f7f2c441cc54001fbe7491</t>
+          <t>6a5f0754cbc2ff00131a7ae9</t>
         </is>
       </c>
       <c r="C606" s="13" t="inlineStr">
         <is>
-          <t>xtellar</t>
+          <t>vippremiummembership</t>
         </is>
       </c>
       <c r="D606" s="12" t="inlineStr">
         <is>
-          <t>theartbraingokul@gmail.com</t>
+          <t>jaibajarangbali9079@gmail.com</t>
         </is>
       </c>
       <c r="E606" s="12" t="inlineStr">
         <is>
-          <t>8848757632</t>
+          <t>9784700662</t>
         </is>
       </c>
       <c r="F606" s="12" t="inlineStr">
@@ -44507,7 +44507,7 @@
       </c>
       <c r="G606" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H606" s="12" t="inlineStr">
@@ -44516,25 +44516,25 @@
         </is>
       </c>
       <c r="I606" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J606" s="14" t="n">
-        <v>1528</v>
+        <v>3292</v>
       </c>
       <c r="K606" s="14" t="n">
-        <v>6560</v>
+        <v>6584</v>
       </c>
       <c r="L606" s="15" t="n">
-        <v>1887</v>
+        <v>3292</v>
       </c>
       <c r="M606" s="12" t="inlineStr">
         <is>
-          <t>6a4773ece345050013f142db</t>
+          <t>6a5f90330f3a3c0014f14885</t>
         </is>
       </c>
       <c r="N606" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
+          <t>https://superprofile.bio/vig/6a5f90330f3a3c0014f14885</t>
         </is>
       </c>
       <c r="O606" s="17" t="inlineStr">
@@ -44554,22 +44554,22 @@
       </c>
       <c r="B607" s="20" t="inlineStr">
         <is>
-          <t>62eba544f479155041e30334</t>
+          <t>64f7f2c441cc54001fbe7491</t>
         </is>
       </c>
       <c r="C607" s="20" t="inlineStr">
         <is>
-          <t>paisabantahain</t>
+          <t>xtellar</t>
         </is>
       </c>
       <c r="D607" s="19" t="inlineStr">
         <is>
-          <t>paisabantahain@gmail.com</t>
+          <t>theartbraingokul@gmail.com</t>
         </is>
       </c>
       <c r="E607" s="19" t="inlineStr">
         <is>
-          <t>7549728896</t>
+          <t>8848757632</t>
         </is>
       </c>
       <c r="F607" s="19" t="inlineStr">
@@ -44579,34 +44579,34 @@
       </c>
       <c r="G607" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H607" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I607" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J607" s="21" t="n">
-        <v>6500</v>
+        <v>1528</v>
       </c>
       <c r="K607" s="21" t="n">
-        <v>6500</v>
+        <v>6560</v>
       </c>
       <c r="L607" s="22" t="n">
-        <v>6500</v>
+        <v>1887</v>
       </c>
       <c r="M607" s="19" t="inlineStr">
         <is>
-          <t>62f10b65c5736a11eac78582</t>
+          <t>6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="N607" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62f10b65c5736a11eac78582</t>
+          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="O607" s="24" t="inlineStr">
@@ -44626,22 +44626,22 @@
       </c>
       <c r="B608" s="13" t="inlineStr">
         <is>
-          <t>670e064c742ab00013bcdf08</t>
+          <t>62eba544f479155041e30334</t>
         </is>
       </c>
       <c r="C608" s="13" t="inlineStr">
         <is>
-          <t>winners2025</t>
+          <t>paisabantahain</t>
         </is>
       </c>
       <c r="D608" s="12" t="inlineStr">
         <is>
-          <t>theakbusiness05@gmail.com</t>
+          <t>paisabantahain@gmail.com</t>
         </is>
       </c>
       <c r="E608" s="12" t="inlineStr">
         <is>
-          <t>9958862700</t>
+          <t>7549728896</t>
         </is>
       </c>
       <c r="F608" s="12" t="inlineStr">
@@ -44651,34 +44651,34 @@
       </c>
       <c r="G608" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H608" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I608" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J608" s="14" t="n">
-        <v>1616</v>
+        <v>6500</v>
       </c>
       <c r="K608" s="14" t="n">
-        <v>6464</v>
+        <v>6500</v>
       </c>
       <c r="L608" s="15" t="n">
-        <v>3232</v>
+        <v>6500</v>
       </c>
       <c r="M608" s="12" t="inlineStr">
         <is>
-          <t>6992af5fc67b780013bf746b</t>
+          <t>62f10b65c5736a11eac78582</t>
         </is>
       </c>
       <c r="N608" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6992af5fc67b780013bf746b</t>
+          <t>https://superprofile.bio/vig/62f10b65c5736a11eac78582</t>
         </is>
       </c>
       <c r="O608" s="17" t="inlineStr">
@@ -44698,22 +44698,22 @@
       </c>
       <c r="B609" s="20" t="inlineStr">
         <is>
-          <t>6528b36ede6af5001d302839</t>
+          <t>670e064c742ab00013bcdf08</t>
         </is>
       </c>
       <c r="C609" s="20" t="inlineStr">
         <is>
-          <t>rahul851</t>
+          <t>winners2025</t>
         </is>
       </c>
       <c r="D609" s="19" t="inlineStr">
         <is>
-          <t>rahulmeena851@gmail.com</t>
+          <t>theakbusiness05@gmail.com</t>
         </is>
       </c>
       <c r="E609" s="19" t="inlineStr">
         <is>
-          <t>9887611761</t>
+          <t>9958862700</t>
         </is>
       </c>
       <c r="F609" s="19" t="inlineStr">
@@ -44723,7 +44723,7 @@
       </c>
       <c r="G609" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H609" s="19" t="inlineStr">
@@ -44732,25 +44732,25 @@
         </is>
       </c>
       <c r="I609" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J609" s="21" t="n">
-        <v>3210</v>
+        <v>1616</v>
       </c>
       <c r="K609" s="21" t="n">
-        <v>6420</v>
+        <v>6464</v>
       </c>
       <c r="L609" s="22" t="n">
-        <v>3210</v>
+        <v>3232</v>
       </c>
       <c r="M609" s="19" t="inlineStr">
         <is>
-          <t>673a2caf9124d20013ddb85b</t>
+          <t>6992af5fc67b780013bf746b</t>
         </is>
       </c>
       <c r="N609" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/673a2caf9124d20013ddb85b</t>
+          <t>https://superprofile.bio/vig/6992af5fc67b780013bf746b</t>
         </is>
       </c>
       <c r="O609" s="24" t="inlineStr">
@@ -44770,22 +44770,22 @@
       </c>
       <c r="B610" s="13" t="inlineStr">
         <is>
-          <t>6324958cc41a79755468f531</t>
+          <t>6528b36ede6af5001d302839</t>
         </is>
       </c>
       <c r="C610" s="13" t="inlineStr">
         <is>
-          <t>nityaanalyst</t>
+          <t>rahul851</t>
         </is>
       </c>
       <c r="D610" s="12" t="inlineStr">
         <is>
-          <t>hiteshsharma136@gmail.com</t>
+          <t>rahulmeena851@gmail.com</t>
         </is>
       </c>
       <c r="E610" s="12" t="inlineStr">
         <is>
-          <t>8755543444</t>
+          <t>9887611761</t>
         </is>
       </c>
       <c r="F610" s="12" t="inlineStr">
@@ -44795,34 +44795,34 @@
       </c>
       <c r="G610" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H610" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I610" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J610" s="14" t="n">
-        <v>6402</v>
+        <v>3210</v>
       </c>
       <c r="K610" s="14" t="n">
-        <v>6402</v>
+        <v>6420</v>
       </c>
       <c r="L610" s="15" t="n">
-        <v>6402</v>
+        <v>3210</v>
       </c>
       <c r="M610" s="12" t="inlineStr">
         <is>
-          <t>63249943c41a79755468f965</t>
+          <t>673a2caf9124d20013ddb85b</t>
         </is>
       </c>
       <c r="N610" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63249943c41a79755468f965</t>
+          <t>https://superprofile.bio/vig/673a2caf9124d20013ddb85b</t>
         </is>
       </c>
       <c r="O610" s="17" t="inlineStr">
@@ -44842,22 +44842,22 @@
       </c>
       <c r="B611" s="20" t="inlineStr">
         <is>
-          <t>67d0f64dfac4900013face06</t>
+          <t>6324958cc41a79755468f531</t>
         </is>
       </c>
       <c r="C611" s="20" t="inlineStr">
         <is>
-          <t>traderswealth1</t>
+          <t>nityaanalyst</t>
         </is>
       </c>
       <c r="D611" s="19" t="inlineStr">
         <is>
-          <t>traderswealth1@gmail.com</t>
+          <t>hiteshsharma136@gmail.com</t>
         </is>
       </c>
       <c r="E611" s="19" t="inlineStr">
         <is>
-          <t>9492340656</t>
+          <t>8755543444</t>
         </is>
       </c>
       <c r="F611" s="19" t="inlineStr">
@@ -44867,34 +44867,34 @@
       </c>
       <c r="G611" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H611" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I611" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J611" s="21" t="n">
-        <v>1079</v>
+        <v>6402</v>
       </c>
       <c r="K611" s="21" t="n">
-        <v>6277</v>
+        <v>6402</v>
       </c>
       <c r="L611" s="22" t="n">
-        <v>1828</v>
+        <v>6402</v>
       </c>
       <c r="M611" s="19" t="inlineStr">
         <is>
-          <t>682da517feb3b90013a268f5</t>
+          <t>63249943c41a79755468f965</t>
         </is>
       </c>
       <c r="N611" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/682da517feb3b90013a268f5</t>
+          <t>https://superprofile.bio/vig/63249943c41a79755468f965</t>
         </is>
       </c>
       <c r="O611" s="24" t="inlineStr">
@@ -44914,22 +44914,22 @@
       </c>
       <c r="B612" s="13" t="inlineStr">
         <is>
-          <t>664f08d3c2ede400130aeded</t>
+          <t>67d0f64dfac4900013face06</t>
         </is>
       </c>
       <c r="C612" s="13" t="inlineStr">
         <is>
-          <t>stockverse</t>
+          <t>traderswealth1</t>
         </is>
       </c>
       <c r="D612" s="12" t="inlineStr">
         <is>
-          <t>shahidk89007@gmail.com</t>
+          <t>traderswealth1@gmail.com</t>
         </is>
       </c>
       <c r="E612" s="12" t="inlineStr">
         <is>
-          <t>7302597556</t>
+          <t>9492340656</t>
         </is>
       </c>
       <c r="F612" s="12" t="inlineStr">
@@ -44939,34 +44939,34 @@
       </c>
       <c r="G612" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H612" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I612" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J612" s="14" t="n">
-        <v>1304</v>
+        <v>1079</v>
       </c>
       <c r="K612" s="14" t="n">
-        <v>6267</v>
+        <v>6277</v>
       </c>
       <c r="L612" s="15" t="n">
-        <v>4963</v>
+        <v>1828</v>
       </c>
       <c r="M612" s="12" t="inlineStr">
         <is>
-          <t>689a66a8aca0a500134fb5f1</t>
+          <t>682da517feb3b90013a268f5</t>
         </is>
       </c>
       <c r="N612" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/689a66a8aca0a500134fb5f1</t>
+          <t>https://superprofile.bio/vig/682da517feb3b90013a268f5</t>
         </is>
       </c>
       <c r="O612" s="17" t="inlineStr">
@@ -44986,22 +44986,22 @@
       </c>
       <c r="B613" s="20" t="inlineStr">
         <is>
-          <t>6a687488e5e89c0013c3ed1c</t>
+          <t>664f08d3c2ede400130aeded</t>
         </is>
       </c>
       <c r="C613" s="20" t="inlineStr">
         <is>
-          <t>star2693</t>
+          <t>stockverse</t>
         </is>
       </c>
       <c r="D613" s="19" t="inlineStr">
         <is>
-          <t>dipalipatil601160@gmail.com</t>
+          <t>shahidk89007@gmail.com</t>
         </is>
       </c>
       <c r="E613" s="19" t="inlineStr">
         <is>
-          <t>7567635030</t>
+          <t>7302597556</t>
         </is>
       </c>
       <c r="F613" s="19" t="inlineStr">
@@ -45011,34 +45011,34 @@
       </c>
       <c r="G613" s="19" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H613" s="19" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H613" s="19" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I613" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J613" s="21" t="n">
-        <v>2928</v>
+        <v>1304</v>
       </c>
       <c r="K613" s="21" t="n">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="L613" s="22" t="n">
-        <v>3334</v>
+        <v>4963</v>
       </c>
       <c r="M613" s="19" t="inlineStr">
         <is>
-          <t>6a688768eea28a0013597168</t>
+          <t>689a66a8aca0a500134fb5f1</t>
         </is>
       </c>
       <c r="N613" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a688768eea28a0013597168</t>
+          <t>https://superprofile.bio/vig/689a66a8aca0a500134fb5f1</t>
         </is>
       </c>
       <c r="O613" s="24" t="inlineStr">
@@ -45058,22 +45058,22 @@
       </c>
       <c r="B614" s="13" t="inlineStr">
         <is>
-          <t>65f03772c3be0800137389f9</t>
+          <t>6a687488e5e89c0013c3ed1c</t>
         </is>
       </c>
       <c r="C614" s="13" t="inlineStr">
         <is>
-          <t>evergreenprofit1</t>
+          <t>star2693</t>
         </is>
       </c>
       <c r="D614" s="12" t="inlineStr">
         <is>
-          <t>jtinvestment@yahoo.com</t>
+          <t>dipalipatil601160@gmail.com</t>
         </is>
       </c>
       <c r="E614" s="12" t="inlineStr">
         <is>
-          <t>9811359531</t>
+          <t>7567635030</t>
         </is>
       </c>
       <c r="F614" s="12" t="inlineStr">
@@ -45083,34 +45083,34 @@
       </c>
       <c r="G614" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H614" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I614" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J614" s="14" t="n">
-        <v>4793</v>
+        <v>2928</v>
       </c>
       <c r="K614" s="14" t="n">
-        <v>6248</v>
+        <v>6262</v>
       </c>
       <c r="L614" s="15" t="n">
-        <v>4793</v>
+        <v>3334</v>
       </c>
       <c r="M614" s="12" t="inlineStr">
         <is>
-          <t>68821d571a62d00013d94752</t>
+          <t>6a688768eea28a0013597168</t>
         </is>
       </c>
       <c r="N614" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68821d571a62d00013d94752</t>
+          <t>https://superprofile.bio/vig/6a688768eea28a0013597168</t>
         </is>
       </c>
       <c r="O614" s="17" t="inlineStr">
@@ -45130,22 +45130,22 @@
       </c>
       <c r="B615" s="20" t="inlineStr">
         <is>
-          <t>68037dbe74e41e0013a09d90</t>
+          <t>65f03772c3be0800137389f9</t>
         </is>
       </c>
       <c r="C615" s="20" t="inlineStr">
         <is>
-          <t>niftywaka</t>
+          <t>evergreenprofit1</t>
         </is>
       </c>
       <c r="D615" s="19" t="inlineStr">
         <is>
-          <t>navinravalsocial@gmail.com</t>
+          <t>jtinvestment@yahoo.com</t>
         </is>
       </c>
       <c r="E615" s="19" t="inlineStr">
         <is>
-          <t>8758021326</t>
+          <t>9811359531</t>
         </is>
       </c>
       <c r="F615" s="19" t="inlineStr">
@@ -45155,34 +45155,34 @@
       </c>
       <c r="G615" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H615" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I615" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J615" s="21" t="n">
-        <v>1748</v>
+        <v>4793</v>
       </c>
       <c r="K615" s="21" t="n">
-        <v>6213</v>
+        <v>6248</v>
       </c>
       <c r="L615" s="22" t="n">
-        <v>4465</v>
+        <v>4793</v>
       </c>
       <c r="M615" s="19" t="inlineStr">
         <is>
-          <t>6a2ff8193d7d2c001326919c</t>
+          <t>68821d571a62d00013d94752</t>
         </is>
       </c>
       <c r="N615" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a2ff8193d7d2c001326919c</t>
+          <t>https://superprofile.bio/vig/68821d571a62d00013d94752</t>
         </is>
       </c>
       <c r="O615" s="24" t="inlineStr">
@@ -45202,22 +45202,22 @@
       </c>
       <c r="B616" s="13" t="inlineStr">
         <is>
-          <t>6520f7847a624b001e93bb99</t>
+          <t>68037dbe74e41e0013a09d90</t>
         </is>
       </c>
       <c r="C616" s="13" t="inlineStr">
         <is>
-          <t>studyniftymalayalam</t>
+          <t>niftywaka</t>
         </is>
       </c>
       <c r="D616" s="12" t="inlineStr">
         <is>
-          <t>aidotechindia@gmail.com</t>
+          <t>navinravalsocial@gmail.com</t>
         </is>
       </c>
       <c r="E616" s="12" t="inlineStr">
         <is>
-          <t>8848066533</t>
+          <t>8758021326</t>
         </is>
       </c>
       <c r="F616" s="12" t="inlineStr">
@@ -45232,29 +45232,29 @@
       </c>
       <c r="H616" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I616" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J616" s="14" t="n">
-        <v>3687</v>
+        <v>1748</v>
       </c>
       <c r="K616" s="14" t="n">
-        <v>6193</v>
+        <v>6213</v>
       </c>
       <c r="L616" s="15" t="n">
-        <v>3687</v>
+        <v>4465</v>
       </c>
       <c r="M616" s="12" t="inlineStr">
         <is>
-          <t>6909a2491e2589001342a886</t>
+          <t>6a2ff8193d7d2c001326919c</t>
         </is>
       </c>
       <c r="N616" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6909a2491e2589001342a886</t>
+          <t>https://superprofile.bio/vig/6a2ff8193d7d2c001326919c</t>
         </is>
       </c>
       <c r="O616" s="17" t="inlineStr">
@@ -45274,22 +45274,22 @@
       </c>
       <c r="B617" s="20" t="inlineStr">
         <is>
-          <t>62fcd64e0031fa2b3302649b</t>
+          <t>6520f7847a624b001e93bb99</t>
         </is>
       </c>
       <c r="C617" s="20" t="inlineStr">
         <is>
-          <t>nmta-</t>
+          <t>studyniftymalayalam</t>
         </is>
       </c>
       <c r="D617" s="19" t="inlineStr">
         <is>
-          <t>Namdevmane23@gmail.com</t>
+          <t>aidotechindia@gmail.com</t>
         </is>
       </c>
       <c r="E617" s="19" t="inlineStr">
         <is>
-          <t>9850252283</t>
+          <t>8848066533</t>
         </is>
       </c>
       <c r="F617" s="19" t="inlineStr">
@@ -45299,7 +45299,7 @@
       </c>
       <c r="G617" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H617" s="19" t="inlineStr">
@@ -45311,22 +45311,22 @@
         <v>3</v>
       </c>
       <c r="J617" s="21" t="n">
-        <v>1952</v>
+        <v>3687</v>
       </c>
       <c r="K617" s="21" t="n">
-        <v>6142</v>
+        <v>6193</v>
       </c>
       <c r="L617" s="22" t="n">
-        <v>2238</v>
+        <v>3687</v>
       </c>
       <c r="M617" s="19" t="inlineStr">
         <is>
-          <t>62ff2e73bdd77b4291a5c288</t>
+          <t>6909a2491e2589001342a886</t>
         </is>
       </c>
       <c r="N617" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62ff2e73bdd77b4291a5c288</t>
+          <t>https://superprofile.bio/vig/6909a2491e2589001342a886</t>
         </is>
       </c>
       <c r="O617" s="24" t="inlineStr">
@@ -45346,22 +45346,22 @@
       </c>
       <c r="B618" s="13" t="inlineStr">
         <is>
-          <t>6a72f4beb6a36a0013d549fc</t>
+          <t>62fcd64e0031fa2b3302649b</t>
         </is>
       </c>
       <c r="C618" s="13" t="inlineStr">
         <is>
-          <t>tradewar11</t>
+          <t>nmta-</t>
         </is>
       </c>
       <c r="D618" s="12" t="inlineStr">
         <is>
-          <t>devangibheda77@gmail.com</t>
+          <t>Namdevmane23@gmail.com</t>
         </is>
       </c>
       <c r="E618" s="12" t="inlineStr">
         <is>
-          <t>9510353334</t>
+          <t>9850252283</t>
         </is>
       </c>
       <c r="F618" s="12" t="inlineStr">
@@ -45371,34 +45371,34 @@
       </c>
       <c r="G618" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H618" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I618" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J618" s="14" t="n">
-        <v>3007</v>
+        <v>1952</v>
       </c>
       <c r="K618" s="14" t="n">
-        <v>6014</v>
+        <v>6142</v>
       </c>
       <c r="L618" s="15" t="n">
-        <v>3007</v>
+        <v>2238</v>
       </c>
       <c r="M618" s="12" t="inlineStr">
         <is>
-          <t>6a9528eb9b645c0012b62d7b</t>
+          <t>62ff2e73bdd77b4291a5c288</t>
         </is>
       </c>
       <c r="N618" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9528eb9b645c0012b62d7b</t>
+          <t>https://superprofile.bio/vig/62ff2e73bdd77b4291a5c288</t>
         </is>
       </c>
       <c r="O618" s="17" t="inlineStr">
@@ -45418,22 +45418,22 @@
       </c>
       <c r="B619" s="20" t="inlineStr">
         <is>
-          <t>64c10e82985f36002a91518a</t>
+          <t>6a72f4beb6a36a0013d549fc</t>
         </is>
       </c>
       <c r="C619" s="20" t="inlineStr">
         <is>
-          <t>investwithsoumyadeep</t>
+          <t>tradewar11</t>
         </is>
       </c>
       <c r="D619" s="19" t="inlineStr">
         <is>
-          <t>soumyadeepsp@gmail.com</t>
+          <t>devangibheda77@gmail.com</t>
         </is>
       </c>
       <c r="E619" s="19" t="inlineStr">
         <is>
-          <t>7042006372</t>
+          <t>9510353334</t>
         </is>
       </c>
       <c r="F619" s="19" t="inlineStr">
@@ -45443,34 +45443,34 @@
       </c>
       <c r="G619" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H619" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I619" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J619" s="21" t="n">
-        <v>3285</v>
+        <v>3007</v>
       </c>
       <c r="K619" s="21" t="n">
-        <v>5985</v>
+        <v>6014</v>
       </c>
       <c r="L619" s="22" t="n">
-        <v>3285</v>
+        <v>3007</v>
       </c>
       <c r="M619" s="19" t="inlineStr">
         <is>
-          <t>66ffe626e0ec7e0013a396d5</t>
+          <t>6a9528eb9b645c0012b62d7b</t>
         </is>
       </c>
       <c r="N619" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ffe626e0ec7e0013a396d5</t>
+          <t>https://superprofile.bio/vig/6a9528eb9b645c0012b62d7b</t>
         </is>
       </c>
       <c r="O619" s="24" t="inlineStr">
@@ -45490,22 +45490,22 @@
       </c>
       <c r="B620" s="13" t="inlineStr">
         <is>
-          <t>67dade2683bbb700149ac687</t>
+          <t>64c10e82985f36002a91518a</t>
         </is>
       </c>
       <c r="C620" s="13" t="inlineStr">
         <is>
-          <t>studypoint45</t>
+          <t>investwithsoumyadeep</t>
         </is>
       </c>
       <c r="D620" s="12" t="inlineStr">
         <is>
-          <t>aspirentsx@gmail.com</t>
+          <t>soumyadeepsp@gmail.com</t>
         </is>
       </c>
       <c r="E620" s="12" t="inlineStr">
         <is>
-          <t>9454702803</t>
+          <t>7042006372</t>
         </is>
       </c>
       <c r="F620" s="12" t="inlineStr">
@@ -45515,34 +45515,34 @@
       </c>
       <c r="G620" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H620" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I620" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J620" s="14" t="n">
-        <v>1065</v>
+        <v>3285</v>
       </c>
       <c r="K620" s="14" t="n">
-        <v>5967</v>
+        <v>5985</v>
       </c>
       <c r="L620" s="15" t="n">
-        <v>1504</v>
+        <v>3285</v>
       </c>
       <c r="M620" s="12" t="inlineStr">
         <is>
-          <t>6a736ea6a22b2900141e43e1</t>
+          <t>66ffe626e0ec7e0013a396d5</t>
         </is>
       </c>
       <c r="N620" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a736ea6a22b2900141e43e1</t>
+          <t>https://superprofile.bio/vig/66ffe626e0ec7e0013a396d5</t>
         </is>
       </c>
       <c r="O620" s="17" t="inlineStr">
@@ -45562,22 +45562,22 @@
       </c>
       <c r="B621" s="20" t="inlineStr">
         <is>
-          <t>6617d1ae8da2380013d363c8</t>
+          <t>67dade2683bbb700149ac687</t>
         </is>
       </c>
       <c r="C621" s="20" t="inlineStr">
         <is>
-          <t>adminom</t>
+          <t>studypoint45</t>
         </is>
       </c>
       <c r="D621" s="19" t="inlineStr">
         <is>
-          <t>shahigaurav71@gmail.com</t>
+          <t>aspirentsx@gmail.com</t>
         </is>
       </c>
       <c r="E621" s="19" t="inlineStr">
         <is>
-          <t>9967768889</t>
+          <t>9454702803</t>
         </is>
       </c>
       <c r="F621" s="19" t="inlineStr">
@@ -45587,34 +45587,34 @@
       </c>
       <c r="G621" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H621" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I621" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J621" s="21" t="n">
-        <v>1976</v>
+        <v>1065</v>
       </c>
       <c r="K621" s="21" t="n">
-        <v>5928</v>
+        <v>5967</v>
       </c>
       <c r="L621" s="22" t="n">
-        <v>1976</v>
+        <v>1504</v>
       </c>
       <c r="M621" s="19" t="inlineStr">
         <is>
-          <t>66a4b3cb16743c00137d6124</t>
+          <t>6a736ea6a22b2900141e43e1</t>
         </is>
       </c>
       <c r="N621" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66a4b3cb16743c00137d6124</t>
+          <t>https://superprofile.bio/vig/6a736ea6a22b2900141e43e1</t>
         </is>
       </c>
       <c r="O621" s="24" t="inlineStr">
@@ -45634,22 +45634,22 @@
       </c>
       <c r="B622" s="13" t="inlineStr">
         <is>
-          <t>6652f73e17ab4600138327bc</t>
+          <t>6617d1ae8da2380013d363c8</t>
         </is>
       </c>
       <c r="C622" s="13" t="inlineStr">
         <is>
-          <t>aryashah</t>
+          <t>adminom</t>
         </is>
       </c>
       <c r="D622" s="12" t="inlineStr">
         <is>
-          <t>arya80226@gmail.com</t>
+          <t>shahigaurav71@gmail.com</t>
         </is>
       </c>
       <c r="E622" s="12" t="inlineStr">
         <is>
-          <t>9316096699</t>
+          <t>9967768889</t>
         </is>
       </c>
       <c r="F622" s="12" t="inlineStr">
@@ -45659,34 +45659,34 @@
       </c>
       <c r="G622" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H622" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I622" s="13" t="n">
         <v>3</v>
       </c>
       <c r="J622" s="14" t="n">
-        <v>2246</v>
+        <v>1976</v>
       </c>
       <c r="K622" s="14" t="n">
-        <v>5844</v>
+        <v>5928</v>
       </c>
       <c r="L622" s="15" t="n">
-        <v>2249</v>
+        <v>1976</v>
       </c>
       <c r="M622" s="12" t="inlineStr">
         <is>
-          <t>6a3fac03f608d4001316288a</t>
+          <t>66a4b3cb16743c00137d6124</t>
         </is>
       </c>
       <c r="N622" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3fac03f608d4001316288a</t>
+          <t>https://superprofile.bio/vig/66a4b3cb16743c00137d6124</t>
         </is>
       </c>
       <c r="O622" s="17" t="inlineStr">
@@ -45706,22 +45706,22 @@
       </c>
       <c r="B623" s="20" t="inlineStr">
         <is>
-          <t>637a8fbf0a58eb0038127fba</t>
+          <t>6652f73e17ab4600138327bc</t>
         </is>
       </c>
       <c r="C623" s="20" t="inlineStr">
         <is>
-          <t>getzepixai</t>
+          <t>aryashah</t>
         </is>
       </c>
       <c r="D623" s="19" t="inlineStr">
         <is>
-          <t>zepix.falco@gmail.com</t>
+          <t>arya80226@gmail.com</t>
         </is>
       </c>
       <c r="E623" s="19" t="inlineStr">
         <is>
-          <t>7878747212</t>
+          <t>9316096699</t>
         </is>
       </c>
       <c r="F623" s="19" t="inlineStr">
@@ -45731,34 +45731,34 @@
       </c>
       <c r="G623" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H623" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I623" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J623" s="21" t="n">
-        <v>1496</v>
+        <v>2246</v>
       </c>
       <c r="K623" s="21" t="n">
-        <v>5790</v>
+        <v>5844</v>
       </c>
       <c r="L623" s="22" t="n">
-        <v>4294</v>
+        <v>2249</v>
       </c>
       <c r="M623" s="19" t="inlineStr">
         <is>
-          <t>6a5ce2158411290013cb4aa6</t>
+          <t>6a3fac03f608d4001316288a</t>
         </is>
       </c>
       <c r="N623" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5ce2158411290013cb4aa6</t>
+          <t>https://superprofile.bio/vig/6a3fac03f608d4001316288a</t>
         </is>
       </c>
       <c r="O623" s="24" t="inlineStr">
@@ -45778,22 +45778,22 @@
       </c>
       <c r="B624" s="13" t="inlineStr">
         <is>
-          <t>64365f2f30eaa9001f2d470c</t>
+          <t>637a8fbf0a58eb0038127fba</t>
         </is>
       </c>
       <c r="C624" s="13" t="inlineStr">
         <is>
-          <t>nitinrawat5252</t>
+          <t>getzepixai</t>
         </is>
       </c>
       <c r="D624" s="12" t="inlineStr">
         <is>
-          <t>overnighttraders@gmail.com</t>
+          <t>zepix.falco@gmail.com</t>
         </is>
       </c>
       <c r="E624" s="12" t="inlineStr">
         <is>
-          <t>7836088360</t>
+          <t>7878747212</t>
         </is>
       </c>
       <c r="F624" s="12" t="inlineStr">
@@ -45803,34 +45803,34 @@
       </c>
       <c r="G624" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H624" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I624" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J624" s="14" t="n">
-        <v>1929</v>
+        <v>1496</v>
       </c>
       <c r="K624" s="14" t="n">
-        <v>5787</v>
+        <v>5790</v>
       </c>
       <c r="L624" s="15" t="n">
-        <v>1929</v>
+        <v>4294</v>
       </c>
       <c r="M624" s="12" t="inlineStr">
         <is>
-          <t>6436661a2b2028001fbd9570</t>
+          <t>6a5ce2158411290013cb4aa6</t>
         </is>
       </c>
       <c r="N624" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6436661a2b2028001fbd9570</t>
+          <t>https://superprofile.bio/vig/6a5ce2158411290013cb4aa6</t>
         </is>
       </c>
       <c r="O624" s="17" t="inlineStr">
@@ -45850,22 +45850,22 @@
       </c>
       <c r="B625" s="20" t="inlineStr">
         <is>
-          <t>67454cd9b2b739001433e4a3</t>
+          <t>64365f2f30eaa9001f2d470c</t>
         </is>
       </c>
       <c r="C625" s="20" t="inlineStr">
         <is>
-          <t>BERIJ7127</t>
+          <t>nitinrawat5252</t>
         </is>
       </c>
       <c r="D625" s="19" t="inlineStr">
         <is>
-          <t>sushantdhere7777@gmail.com</t>
+          <t>overnighttraders@gmail.com</t>
         </is>
       </c>
       <c r="E625" s="19" t="inlineStr">
         <is>
-          <t>9209765239</t>
+          <t>7836088360</t>
         </is>
       </c>
       <c r="F625" s="19" t="inlineStr">
@@ -45875,7 +45875,7 @@
       </c>
       <c r="G625" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H625" s="19" t="inlineStr">
@@ -45884,25 +45884,25 @@
         </is>
       </c>
       <c r="I625" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J625" s="21" t="n">
-        <v>2893</v>
+        <v>1929</v>
       </c>
       <c r="K625" s="21" t="n">
-        <v>5786</v>
+        <v>5787</v>
       </c>
       <c r="L625" s="22" t="n">
-        <v>2893</v>
+        <v>1929</v>
       </c>
       <c r="M625" s="19" t="inlineStr">
         <is>
-          <t>6a4c9f7457c58f0013cd766f</t>
+          <t>6436661a2b2028001fbd9570</t>
         </is>
       </c>
       <c r="N625" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4c9f7457c58f0013cd766f</t>
+          <t>https://superprofile.bio/vig/6436661a2b2028001fbd9570</t>
         </is>
       </c>
       <c r="O625" s="24" t="inlineStr">
@@ -45922,22 +45922,22 @@
       </c>
       <c r="B626" s="13" t="inlineStr">
         <is>
-          <t>69a0993ea5de7e00140e28e4</t>
+          <t>67454cd9b2b739001433e4a3</t>
         </is>
       </c>
       <c r="C626" s="13" t="inlineStr">
         <is>
-          <t>STOCK5904</t>
+          <t>BERIJ7127</t>
         </is>
       </c>
       <c r="D626" s="12" t="inlineStr">
         <is>
-          <t>demonscrimspvt.ltd@gmail.com</t>
+          <t>sushantdhere7777@gmail.com</t>
         </is>
       </c>
       <c r="E626" s="12" t="inlineStr">
         <is>
-          <t>9516992339</t>
+          <t>9209765239</t>
         </is>
       </c>
       <c r="F626" s="12" t="inlineStr">
@@ -45947,34 +45947,34 @@
       </c>
       <c r="G626" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H626" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I626" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J626" s="14" t="n">
-        <v>5757</v>
+        <v>2893</v>
       </c>
       <c r="K626" s="14" t="n">
-        <v>5757</v>
+        <v>5786</v>
       </c>
       <c r="L626" s="15" t="n">
-        <v>5757</v>
+        <v>2893</v>
       </c>
       <c r="M626" s="12" t="inlineStr">
         <is>
-          <t>69a0a70b9471170013a5e1c3</t>
+          <t>6a4c9f7457c58f0013cd766f</t>
         </is>
       </c>
       <c r="N626" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a0a70b9471170013a5e1c3</t>
+          <t>https://superprofile.bio/vig/6a4c9f7457c58f0013cd766f</t>
         </is>
       </c>
       <c r="O626" s="17" t="inlineStr">
@@ -45994,22 +45994,22 @@
       </c>
       <c r="B627" s="20" t="inlineStr">
         <is>
-          <t>64e0dae67a1d8d001eee9f38</t>
+          <t>69a0993ea5de7e00140e28e4</t>
         </is>
       </c>
       <c r="C627" s="20" t="inlineStr">
         <is>
-          <t>mcxmaster11</t>
+          <t>STOCK5904</t>
         </is>
       </c>
       <c r="D627" s="19" t="inlineStr">
         <is>
-          <t>excellence.1160@gmail.com</t>
+          <t>demonscrimspvt.ltd@gmail.com</t>
         </is>
       </c>
       <c r="E627" s="19" t="inlineStr">
         <is>
-          <t>9033903959</t>
+          <t>9516992339</t>
         </is>
       </c>
       <c r="F627" s="19" t="inlineStr">
@@ -46019,34 +46019,34 @@
       </c>
       <c r="G627" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H627" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I627" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J627" s="21" t="n">
-        <v>5716</v>
+        <v>5757</v>
       </c>
       <c r="K627" s="21" t="n">
-        <v>5716</v>
+        <v>5757</v>
       </c>
       <c r="L627" s="22" t="n">
-        <v>5716</v>
+        <v>5757</v>
       </c>
       <c r="M627" s="19" t="inlineStr">
         <is>
-          <t>69a532a10d2a490013386252</t>
+          <t>69a0a70b9471170013a5e1c3</t>
         </is>
       </c>
       <c r="N627" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a532a10d2a490013386252</t>
+          <t>https://superprofile.bio/vig/69a0a70b9471170013a5e1c3</t>
         </is>
       </c>
       <c r="O627" s="24" t="inlineStr">
@@ -46066,22 +46066,22 @@
       </c>
       <c r="B628" s="13" t="inlineStr">
         <is>
-          <t>689198a6c335f30013327b00</t>
+          <t>64e0dae67a1d8d001eee9f38</t>
         </is>
       </c>
       <c r="C628" s="13" t="inlineStr">
         <is>
-          <t>devapokale9</t>
+          <t>mcxmaster11</t>
         </is>
       </c>
       <c r="D628" s="12" t="inlineStr">
         <is>
-          <t>devapokale9@gmail.com</t>
+          <t>excellence.1160@gmail.com</t>
         </is>
       </c>
       <c r="E628" s="12" t="inlineStr">
         <is>
-          <t>9579536482</t>
+          <t>9033903959</t>
         </is>
       </c>
       <c r="F628" s="12" t="inlineStr">
@@ -46091,34 +46091,34 @@
       </c>
       <c r="G628" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H628" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I628" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J628" s="14" t="n">
-        <v>5702</v>
+        <v>5716</v>
       </c>
       <c r="K628" s="14" t="n">
-        <v>5702</v>
+        <v>5716</v>
       </c>
       <c r="L628" s="15" t="n">
-        <v>5702</v>
+        <v>5716</v>
       </c>
       <c r="M628" s="12" t="inlineStr">
         <is>
-          <t>697acab5461b1600134065ce</t>
+          <t>69a532a10d2a490013386252</t>
         </is>
       </c>
       <c r="N628" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697acab5461b1600134065ce</t>
+          <t>https://superprofile.bio/vig/69a532a10d2a490013386252</t>
         </is>
       </c>
       <c r="O628" s="17" t="inlineStr">
@@ -46138,22 +46138,22 @@
       </c>
       <c r="B629" s="20" t="inlineStr">
         <is>
-          <t>67506cec64fe550013dd58c8</t>
+          <t>689198a6c335f30013327b00</t>
         </is>
       </c>
       <c r="C629" s="20" t="inlineStr">
         <is>
-          <t>level2traders</t>
+          <t>devapokale9</t>
         </is>
       </c>
       <c r="D629" s="19" t="inlineStr">
         <is>
-          <t>renjuu.pais@gmail.com</t>
+          <t>devapokale9@gmail.com</t>
         </is>
       </c>
       <c r="E629" s="19" t="inlineStr">
         <is>
-          <t>9995015768</t>
+          <t>9579536482</t>
         </is>
       </c>
       <c r="F629" s="19" t="inlineStr">
@@ -46163,34 +46163,34 @@
       </c>
       <c r="G629" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H629" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I629" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J629" s="21" t="n">
-        <v>3798</v>
+        <v>5702</v>
       </c>
       <c r="K629" s="21" t="n">
-        <v>5697</v>
+        <v>5702</v>
       </c>
       <c r="L629" s="22" t="n">
-        <v>3798</v>
+        <v>5702</v>
       </c>
       <c r="M629" s="19" t="inlineStr">
         <is>
-          <t>69035024a37225001314a9b9</t>
+          <t>697acab5461b1600134065ce</t>
         </is>
       </c>
       <c r="N629" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69035024a37225001314a9b9</t>
+          <t>https://superprofile.bio/vig/697acab5461b1600134065ce</t>
         </is>
       </c>
       <c r="O629" s="24" t="inlineStr">
@@ -46210,22 +46210,22 @@
       </c>
       <c r="B630" s="13" t="inlineStr">
         <is>
-          <t>656085ecaefd62001e722f4c</t>
+          <t>67506cec64fe550013dd58c8</t>
         </is>
       </c>
       <c r="C630" s="13" t="inlineStr">
         <is>
-          <t>tradewithsujeet</t>
+          <t>level2traders</t>
         </is>
       </c>
       <c r="D630" s="12" t="inlineStr">
         <is>
-          <t>guptasujeet44@gmail.com</t>
+          <t>renjuu.pais@gmail.com</t>
         </is>
       </c>
       <c r="E630" s="12" t="inlineStr">
         <is>
-          <t>8210227202</t>
+          <t>9995015768</t>
         </is>
       </c>
       <c r="F630" s="12" t="inlineStr">
@@ -46235,34 +46235,34 @@
       </c>
       <c r="G630" s="12" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H630" s="12" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="H630" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
       <c r="I630" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J630" s="14" t="n">
-        <v>5646</v>
+        <v>3798</v>
       </c>
       <c r="K630" s="14" t="n">
-        <v>5646</v>
+        <v>5697</v>
       </c>
       <c r="L630" s="15" t="n">
-        <v>5646</v>
+        <v>3798</v>
       </c>
       <c r="M630" s="12" t="inlineStr">
         <is>
-          <t>65609ad2aefd62001e732801</t>
+          <t>69035024a37225001314a9b9</t>
         </is>
       </c>
       <c r="N630" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65609ad2aefd62001e732801</t>
+          <t>https://superprofile.bio/vig/69035024a37225001314a9b9</t>
         </is>
       </c>
       <c r="O630" s="17" t="inlineStr">
@@ -46282,22 +46282,22 @@
       </c>
       <c r="B631" s="20" t="inlineStr">
         <is>
-          <t>62c7cff57d9e2d0f32342064</t>
+          <t>656085ecaefd62001e722f4c</t>
         </is>
       </c>
       <c r="C631" s="20" t="inlineStr">
         <is>
-          <t>rpanwarstox</t>
+          <t>tradewithsujeet</t>
         </is>
       </c>
       <c r="D631" s="19" t="inlineStr">
         <is>
-          <t>ramcpanwar@gmail.com</t>
+          <t>guptasujeet44@gmail.com</t>
         </is>
       </c>
       <c r="E631" s="19" t="inlineStr">
         <is>
-          <t>9988003250</t>
+          <t>8210227202</t>
         </is>
       </c>
       <c r="F631" s="19" t="inlineStr">
@@ -46307,34 +46307,34 @@
       </c>
       <c r="G631" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H631" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I631" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J631" s="21" t="n">
-        <v>2822</v>
+        <v>5646</v>
       </c>
       <c r="K631" s="21" t="n">
-        <v>5644</v>
+        <v>5646</v>
       </c>
       <c r="L631" s="22" t="n">
-        <v>2822</v>
+        <v>5646</v>
       </c>
       <c r="M631" s="19" t="inlineStr">
         <is>
-          <t>66d6f2026e56ec001373ed15</t>
+          <t>65609ad2aefd62001e732801</t>
         </is>
       </c>
       <c r="N631" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66d6f2026e56ec001373ed15</t>
+          <t>https://superprofile.bio/vig/65609ad2aefd62001e732801</t>
         </is>
       </c>
       <c r="O631" s="24" t="inlineStr">
@@ -46354,22 +46354,22 @@
       </c>
       <c r="B632" s="13" t="inlineStr">
         <is>
-          <t>68fcd1a1390a76001310259f</t>
+          <t>62c7cff57d9e2d0f32342064</t>
         </is>
       </c>
       <c r="C632" s="13" t="inlineStr">
         <is>
-          <t>hindustantrader985</t>
+          <t>rpanwarstox</t>
         </is>
       </c>
       <c r="D632" s="12" t="inlineStr">
         <is>
-          <t>vivekpatel75364@gmail.com</t>
+          <t>ramcpanwar@gmail.com</t>
         </is>
       </c>
       <c r="E632" s="12" t="inlineStr">
         <is>
-          <t>8003683727</t>
+          <t>9988003250</t>
         </is>
       </c>
       <c r="F632" s="12" t="inlineStr">
@@ -46379,12 +46379,12 @@
       </c>
       <c r="G632" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H632" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I632" s="13" t="n">
@@ -46401,12 +46401,12 @@
       </c>
       <c r="M632" s="12" t="inlineStr">
         <is>
-          <t>69328fb31485a2001397c7ac</t>
+          <t>66d6f2026e56ec001373ed15</t>
         </is>
       </c>
       <c r="N632" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69328fb31485a2001397c7ac</t>
+          <t>https://superprofile.bio/vig/66d6f2026e56ec001373ed15</t>
         </is>
       </c>
       <c r="O632" s="17" t="inlineStr">
@@ -46426,22 +46426,22 @@
       </c>
       <c r="B633" s="20" t="inlineStr">
         <is>
-          <t>6515aeec9433d3001ef9f2a2</t>
+          <t>68fcd1a1390a76001310259f</t>
         </is>
       </c>
       <c r="C633" s="20" t="inlineStr">
         <is>
-          <t>markethunterr</t>
+          <t>hindustantrader985</t>
         </is>
       </c>
       <c r="D633" s="19" t="inlineStr">
         <is>
-          <t>querymarketunterr@gmail.com</t>
+          <t>vivekpatel75364@gmail.com</t>
         </is>
       </c>
       <c r="E633" s="19" t="inlineStr">
         <is>
-          <t>9579525336</t>
+          <t>8003683727</t>
         </is>
       </c>
       <c r="F633" s="19" t="inlineStr">
@@ -46451,34 +46451,34 @@
       </c>
       <c r="G633" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H633" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I633" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J633" s="21" t="n">
-        <v>1411</v>
+        <v>2822</v>
       </c>
       <c r="K633" s="21" t="n">
         <v>5644</v>
       </c>
       <c r="L633" s="22" t="n">
-        <v>1411</v>
+        <v>2822</v>
       </c>
       <c r="M633" s="19" t="inlineStr">
         <is>
-          <t>6a9292ec59d38a00131346fa</t>
+          <t>69328fb31485a2001397c7ac</t>
         </is>
       </c>
       <c r="N633" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9292ec59d38a00131346fa</t>
+          <t>https://superprofile.bio/vig/69328fb31485a2001397c7ac</t>
         </is>
       </c>
       <c r="O633" s="24" t="inlineStr">
@@ -46498,22 +46498,22 @@
       </c>
       <c r="B634" s="13" t="inlineStr">
         <is>
-          <t>66fcd933f178e60013c06440</t>
+          <t>6515aeec9433d3001ef9f2a2</t>
         </is>
       </c>
       <c r="C634" s="13" t="inlineStr">
         <is>
-          <t>drgoldsignal</t>
+          <t>markethunterr</t>
         </is>
       </c>
       <c r="D634" s="12" t="inlineStr">
         <is>
-          <t>rhonakmunot88@gmail.com</t>
+          <t>querymarketunterr@gmail.com</t>
         </is>
       </c>
       <c r="E634" s="12" t="inlineStr">
         <is>
-          <t>9623316888</t>
+          <t>9579525336</t>
         </is>
       </c>
       <c r="F634" s="12" t="inlineStr">
@@ -46523,34 +46523,34 @@
       </c>
       <c r="G634" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H634" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I634" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J634" s="14" t="n">
-        <v>1093</v>
+        <v>1411</v>
       </c>
       <c r="K634" s="14" t="n">
-        <v>5616</v>
+        <v>5644</v>
       </c>
       <c r="L634" s="15" t="n">
-        <v>1575</v>
+        <v>1411</v>
       </c>
       <c r="M634" s="12" t="inlineStr">
         <is>
-          <t>6a95128e5853160013932a82</t>
+          <t>6a9292ec59d38a00131346fa</t>
         </is>
       </c>
       <c r="N634" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a95128e5853160013932a82</t>
+          <t>https://superprofile.bio/vig/6a9292ec59d38a00131346fa</t>
         </is>
       </c>
       <c r="O634" s="17" t="inlineStr">
@@ -46570,22 +46570,22 @@
       </c>
       <c r="B635" s="20" t="inlineStr">
         <is>
-          <t>65897ce155e4ed001eaf2d96</t>
+          <t>66fcd933f178e60013c06440</t>
         </is>
       </c>
       <c r="C635" s="20" t="inlineStr">
         <is>
-          <t>legaltrader</t>
+          <t>drgoldsignal</t>
         </is>
       </c>
       <c r="D635" s="19" t="inlineStr">
         <is>
-          <t>legaltradergroup@gmail.com</t>
+          <t>rhonakmunot88@gmail.com</t>
         </is>
       </c>
       <c r="E635" s="19" t="inlineStr">
         <is>
-          <t>9337833196</t>
+          <t>9623316888</t>
         </is>
       </c>
       <c r="F635" s="19" t="inlineStr">
@@ -46595,34 +46595,34 @@
       </c>
       <c r="G635" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H635" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I635" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J635" s="21" t="n">
-        <v>1800</v>
+        <v>1093</v>
       </c>
       <c r="K635" s="21" t="n">
-        <v>5575</v>
+        <v>5616</v>
       </c>
       <c r="L635" s="22" t="n">
-        <v>3775</v>
+        <v>1575</v>
       </c>
       <c r="M635" s="19" t="inlineStr">
         <is>
-          <t>69dfd975b0686800146e02db</t>
+          <t>6a95128e5853160013932a82</t>
         </is>
       </c>
       <c r="N635" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69dfd975b0686800146e02db</t>
+          <t>https://superprofile.bio/vig/6a95128e5853160013932a82</t>
         </is>
       </c>
       <c r="O635" s="24" t="inlineStr">
@@ -46642,22 +46642,22 @@
       </c>
       <c r="B636" s="13" t="inlineStr">
         <is>
-          <t>6475a085f68c8e0020340ef5</t>
+          <t>65897ce155e4ed001eaf2d96</t>
         </is>
       </c>
       <c r="C636" s="13" t="inlineStr">
         <is>
-          <t>jd24education</t>
+          <t>legaltrader</t>
         </is>
       </c>
       <c r="D636" s="12" t="inlineStr">
         <is>
-          <t>jd24education@gmail.com</t>
+          <t>legaltradergroup@gmail.com</t>
         </is>
       </c>
       <c r="E636" s="12" t="inlineStr">
         <is>
-          <t>8002550026</t>
+          <t>9337833196</t>
         </is>
       </c>
       <c r="F636" s="12" t="inlineStr">
@@ -46667,34 +46667,34 @@
       </c>
       <c r="G636" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H636" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I636" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J636" s="14" t="n">
-        <v>1971</v>
+        <v>1800</v>
       </c>
       <c r="K636" s="14" t="n">
-        <v>5469</v>
+        <v>5575</v>
       </c>
       <c r="L636" s="15" t="n">
-        <v>1971</v>
+        <v>3775</v>
       </c>
       <c r="M636" s="12" t="inlineStr">
         <is>
-          <t>6582cd2325f8a7001ebe8d03</t>
+          <t>69dfd975b0686800146e02db</t>
         </is>
       </c>
       <c r="N636" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6582cd2325f8a7001ebe8d03</t>
+          <t>https://superprofile.bio/vig/69dfd975b0686800146e02db</t>
         </is>
       </c>
       <c r="O636" s="17" t="inlineStr">
@@ -46714,22 +46714,22 @@
       </c>
       <c r="B637" s="20" t="inlineStr">
         <is>
-          <t>6a8fc75235fd0000136b34a2</t>
+          <t>6475a085f68c8e0020340ef5</t>
         </is>
       </c>
       <c r="C637" s="20" t="inlineStr">
         <is>
-          <t>themodernmanager</t>
+          <t>jd24education</t>
         </is>
       </c>
       <c r="D637" s="19" t="inlineStr">
         <is>
-          <t>adityaughade88@gmail.com</t>
+          <t>jd24education@gmail.com</t>
         </is>
       </c>
       <c r="E637" s="19" t="inlineStr">
         <is>
-          <t>8087886280</t>
+          <t>8002550026</t>
         </is>
       </c>
       <c r="F637" s="19" t="inlineStr">
@@ -46739,34 +46739,34 @@
       </c>
       <c r="G637" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H637" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I637" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J637" s="21" t="n">
-        <v>1411</v>
+        <v>1971</v>
       </c>
       <c r="K637" s="21" t="n">
-        <v>5453</v>
+        <v>5469</v>
       </c>
       <c r="L637" s="22" t="n">
-        <v>1411</v>
+        <v>1971</v>
       </c>
       <c r="M637" s="19" t="inlineStr">
         <is>
-          <t>6a95b5659b39bd001394fa5c</t>
+          <t>6582cd2325f8a7001ebe8d03</t>
         </is>
       </c>
       <c r="N637" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a95b5659b39bd001394fa5c</t>
+          <t>https://superprofile.bio/vig/6582cd2325f8a7001ebe8d03</t>
         </is>
       </c>
       <c r="O637" s="24" t="inlineStr">
@@ -46786,22 +46786,22 @@
       </c>
       <c r="B638" s="13" t="inlineStr">
         <is>
-          <t>66baf10ae40f0000134d0562</t>
+          <t>6a8fc75235fd0000136b34a2</t>
         </is>
       </c>
       <c r="C638" s="13" t="inlineStr">
         <is>
-          <t>tradingwithguru</t>
+          <t>themodernmanager</t>
         </is>
       </c>
       <c r="D638" s="12" t="inlineStr">
         <is>
-          <t>tradingwithgujarati@gmail.com</t>
+          <t>adityaughade88@gmail.com</t>
         </is>
       </c>
       <c r="E638" s="12" t="inlineStr">
         <is>
-          <t>+917990772956</t>
+          <t>8087886280</t>
         </is>
       </c>
       <c r="F638" s="12" t="inlineStr">
@@ -46816,29 +46816,29 @@
       </c>
       <c r="H638" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I638" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J638" s="14" t="n">
-        <v>1472</v>
+        <v>1411</v>
       </c>
       <c r="K638" s="14" t="n">
-        <v>5409</v>
+        <v>5453</v>
       </c>
       <c r="L638" s="15" t="n">
-        <v>3937</v>
+        <v>1411</v>
       </c>
       <c r="M638" s="12" t="inlineStr">
         <is>
-          <t>67694af9e7dde20cdbeae7e3</t>
+          <t>6a95b5659b39bd001394fa5c</t>
         </is>
       </c>
       <c r="N638" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67694af9e7dde20cdbeae7e3</t>
+          <t>https://superprofile.bio/vig/6a95b5659b39bd001394fa5c</t>
         </is>
       </c>
       <c r="O638" s="17" t="inlineStr">
@@ -46858,22 +46858,22 @@
       </c>
       <c r="B639" s="20" t="inlineStr">
         <is>
-          <t>650abd0cf20ea4001dbfb6bb</t>
+          <t>66baf10ae40f0000134d0562</t>
         </is>
       </c>
       <c r="C639" s="20" t="inlineStr">
         <is>
-          <t>amyap</t>
+          <t>tradingwithguru</t>
         </is>
       </c>
       <c r="D639" s="19" t="inlineStr">
         <is>
-          <t>amit.parate97@gmail.com</t>
+          <t>tradingwithgujarati@gmail.com</t>
         </is>
       </c>
       <c r="E639" s="19" t="inlineStr">
         <is>
-          <t>9967928698</t>
+          <t>+917990772956</t>
         </is>
       </c>
       <c r="F639" s="19" t="inlineStr">
@@ -46883,34 +46883,34 @@
       </c>
       <c r="G639" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H639" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I639" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J639" s="21" t="n">
-        <v>5399</v>
+        <v>1472</v>
       </c>
       <c r="K639" s="21" t="n">
-        <v>5399</v>
+        <v>5409</v>
       </c>
       <c r="L639" s="22" t="n">
-        <v>5399</v>
+        <v>3937</v>
       </c>
       <c r="M639" s="19" t="inlineStr">
         <is>
-          <t>6a8fd3dd717b7000133592b6</t>
+          <t>67694af9e7dde20cdbeae7e3</t>
         </is>
       </c>
       <c r="N639" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8fd3dd717b7000133592b6</t>
+          <t>https://superprofile.bio/vig/67694af9e7dde20cdbeae7e3</t>
         </is>
       </c>
       <c r="O639" s="24" t="inlineStr">
@@ -46930,22 +46930,22 @@
       </c>
       <c r="B640" s="13" t="inlineStr">
         <is>
-          <t>66b5bdc0a0cb2f0013752847</t>
+          <t>650abd0cf20ea4001dbfb6bb</t>
         </is>
       </c>
       <c r="C640" s="13" t="inlineStr">
         <is>
-          <t>stockmarketpremium85</t>
+          <t>amyap</t>
         </is>
       </c>
       <c r="D640" s="12" t="inlineStr">
         <is>
-          <t>yogeshkumar635720@gmail.com</t>
+          <t>amit.parate97@gmail.com</t>
         </is>
       </c>
       <c r="E640" s="12" t="inlineStr">
         <is>
-          <t>6398573385</t>
+          <t>9967928698</t>
         </is>
       </c>
       <c r="F640" s="12" t="inlineStr">
@@ -46955,34 +46955,34 @@
       </c>
       <c r="G640" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H640" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I640" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J640" s="14" t="n">
-        <v>3149</v>
+        <v>5399</v>
       </c>
       <c r="K640" s="14" t="n">
-        <v>5396</v>
+        <v>5399</v>
       </c>
       <c r="L640" s="15" t="n">
-        <v>3149</v>
+        <v>5399</v>
       </c>
       <c r="M640" s="12" t="inlineStr">
         <is>
-          <t>6a41297e035268001316a24d</t>
+          <t>6a8fd3dd717b7000133592b6</t>
         </is>
       </c>
       <c r="N640" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a41297e035268001316a24d</t>
+          <t>https://superprofile.bio/vig/6a8fd3dd717b7000133592b6</t>
         </is>
       </c>
       <c r="O640" s="17" t="inlineStr">
@@ -47002,22 +47002,22 @@
       </c>
       <c r="B641" s="20" t="inlineStr">
         <is>
-          <t>6633a3eb4265dc0014959b3e</t>
+          <t>66b5bdc0a0cb2f0013752847</t>
         </is>
       </c>
       <c r="C641" s="20" t="inlineStr">
         <is>
-          <t>investmentworks</t>
+          <t>stockmarketpremium85</t>
         </is>
       </c>
       <c r="D641" s="19" t="inlineStr">
         <is>
-          <t>startwithinvestment@gmail.com</t>
+          <t>yogeshkumar635720@gmail.com</t>
         </is>
       </c>
       <c r="E641" s="19" t="inlineStr">
         <is>
-          <t>7010993728</t>
+          <t>6398573385</t>
         </is>
       </c>
       <c r="F641" s="19" t="inlineStr">
@@ -47027,34 +47027,34 @@
       </c>
       <c r="G641" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H641" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I641" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J641" s="21" t="n">
-        <v>5395</v>
+        <v>3149</v>
       </c>
       <c r="K641" s="21" t="n">
-        <v>5395</v>
+        <v>5396</v>
       </c>
       <c r="L641" s="22" t="n">
-        <v>5395</v>
+        <v>3149</v>
       </c>
       <c r="M641" s="19" t="inlineStr">
         <is>
-          <t>687cd87b4e9a4b00131ae969</t>
+          <t>6a41297e035268001316a24d</t>
         </is>
       </c>
       <c r="N641" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687cd87b4e9a4b00131ae969</t>
+          <t>https://superprofile.bio/vig/6a41297e035268001316a24d</t>
         </is>
       </c>
       <c r="O641" s="24" t="inlineStr">
@@ -47074,22 +47074,22 @@
       </c>
       <c r="B642" s="13" t="inlineStr">
         <is>
-          <t>6734e7af9db116001323f973</t>
+          <t>6633a3eb4265dc0014959b3e</t>
         </is>
       </c>
       <c r="C642" s="13" t="inlineStr">
         <is>
-          <t>simitrade</t>
+          <t>investmentworks</t>
         </is>
       </c>
       <c r="D642" s="12" t="inlineStr">
         <is>
-          <t>Deepak.khatri9585@gmail.com</t>
+          <t>startwithinvestment@gmail.com</t>
         </is>
       </c>
       <c r="E642" s="12" t="inlineStr">
         <is>
-          <t>8503914118</t>
+          <t>7010993728</t>
         </is>
       </c>
       <c r="F642" s="12" t="inlineStr">
@@ -47099,34 +47099,34 @@
       </c>
       <c r="G642" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H642" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I642" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J642" s="14" t="n">
-        <v>2441</v>
+        <v>5395</v>
       </c>
       <c r="K642" s="14" t="n">
-        <v>5371</v>
+        <v>5395</v>
       </c>
       <c r="L642" s="15" t="n">
-        <v>2441</v>
+        <v>5395</v>
       </c>
       <c r="M642" s="12" t="inlineStr">
         <is>
-          <t>65cca8c4dffb4239e9ccf794</t>
+          <t>687cd87b4e9a4b00131ae969</t>
         </is>
       </c>
       <c r="N642" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65cca8c4dffb4239e9ccf794</t>
+          <t>https://superprofile.bio/vig/687cd87b4e9a4b00131ae969</t>
         </is>
       </c>
       <c r="O642" s="17" t="inlineStr">
@@ -47146,22 +47146,22 @@
       </c>
       <c r="B643" s="20" t="inlineStr">
         <is>
-          <t>64ad63228adbd60020406bd9</t>
+          <t>6734e7af9db116001323f973</t>
         </is>
       </c>
       <c r="C643" s="20" t="inlineStr">
         <is>
-          <t>tradewithvikas</t>
+          <t>simitrade</t>
         </is>
       </c>
       <c r="D643" s="19" t="inlineStr">
         <is>
-          <t>saniyaroksarkhan@gmail.com</t>
+          <t>Deepak.khatri9585@gmail.com</t>
         </is>
       </c>
       <c r="E643" s="19" t="inlineStr">
         <is>
-          <t>7004676482</t>
+          <t>8503914118</t>
         </is>
       </c>
       <c r="F643" s="19" t="inlineStr">
@@ -47171,34 +47171,34 @@
       </c>
       <c r="G643" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H643" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I643" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J643" s="21" t="n">
-        <v>2823</v>
+        <v>2441</v>
       </c>
       <c r="K643" s="21" t="n">
-        <v>5270</v>
+        <v>5371</v>
       </c>
       <c r="L643" s="22" t="n">
-        <v>2823</v>
+        <v>2441</v>
       </c>
       <c r="M643" s="19" t="inlineStr">
         <is>
-          <t>68f893647b56730013ac653b</t>
+          <t>65cca8c4dffb4239e9ccf794</t>
         </is>
       </c>
       <c r="N643" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f893647b56730013ac653b</t>
+          <t>https://superprofile.bio/vig/65cca8c4dffb4239e9ccf794</t>
         </is>
       </c>
       <c r="O643" s="24" t="inlineStr">
@@ -47218,22 +47218,22 @@
       </c>
       <c r="B644" s="13" t="inlineStr">
         <is>
-          <t>69b5fcdb5e3ff20013757539</t>
+          <t>64ad63228adbd60020406bd9</t>
         </is>
       </c>
       <c r="C644" s="13" t="inlineStr">
         <is>
-          <t>adityatare</t>
+          <t>tradewithvikas</t>
         </is>
       </c>
       <c r="D644" s="12" t="inlineStr">
         <is>
-          <t>adityatare13@gmail.com</t>
+          <t>saniyaroksarkhan@gmail.com</t>
         </is>
       </c>
       <c r="E644" s="12" t="inlineStr">
         <is>
-          <t>9833309475</t>
+          <t>7004676482</t>
         </is>
       </c>
       <c r="F644" s="12" t="inlineStr">
@@ -47243,34 +47243,34 @@
       </c>
       <c r="G644" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H644" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I644" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J644" s="14" t="n">
-        <v>1126</v>
+        <v>2823</v>
       </c>
       <c r="K644" s="14" t="n">
-        <v>5266</v>
+        <v>5270</v>
       </c>
       <c r="L644" s="15" t="n">
-        <v>2070</v>
+        <v>2823</v>
       </c>
       <c r="M644" s="12" t="inlineStr">
         <is>
-          <t>69b7b761425b080013c0c91f</t>
+          <t>68f893647b56730013ac653b</t>
         </is>
       </c>
       <c r="N644" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b7b761425b080013c0c91f</t>
+          <t>https://superprofile.bio/vig/68f893647b56730013ac653b</t>
         </is>
       </c>
       <c r="O644" s="17" t="inlineStr">
@@ -47290,22 +47290,22 @@
       </c>
       <c r="B645" s="20" t="inlineStr">
         <is>
-          <t>65c05cddd5ea93001f37a5b4</t>
+          <t>69b5fcdb5e3ff20013757539</t>
         </is>
       </c>
       <c r="C645" s="20" t="inlineStr">
         <is>
-          <t>vlogsbysachinn</t>
+          <t>adityatare</t>
         </is>
       </c>
       <c r="D645" s="19" t="inlineStr">
         <is>
-          <t>sachinprsnl12@gmail.com</t>
+          <t>adityatare13@gmail.com</t>
         </is>
       </c>
       <c r="E645" s="19" t="inlineStr">
         <is>
-          <t>9315724186</t>
+          <t>9833309475</t>
         </is>
       </c>
       <c r="F645" s="19" t="inlineStr">
@@ -47315,7 +47315,7 @@
       </c>
       <c r="G645" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H645" s="19" t="inlineStr">
@@ -47327,22 +47327,22 @@
         <v>3</v>
       </c>
       <c r="J645" s="21" t="n">
-        <v>1881</v>
+        <v>1126</v>
       </c>
       <c r="K645" s="21" t="n">
-        <v>5173</v>
+        <v>5266</v>
       </c>
       <c r="L645" s="22" t="n">
-        <v>1881</v>
+        <v>2070</v>
       </c>
       <c r="M645" s="19" t="inlineStr">
         <is>
-          <t>68c2b6158f67740013f45471</t>
+          <t>69b7b761425b080013c0c91f</t>
         </is>
       </c>
       <c r="N645" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c2b6158f67740013f45471</t>
+          <t>https://superprofile.bio/vig/69b7b761425b080013c0c91f</t>
         </is>
       </c>
       <c r="O645" s="24" t="inlineStr">
@@ -47362,22 +47362,22 @@
       </c>
       <c r="B646" s="13" t="inlineStr">
         <is>
-          <t>68ec9b285044ba0013a9ca08</t>
+          <t>65c05cddd5ea93001f37a5b4</t>
         </is>
       </c>
       <c r="C646" s="13" t="inlineStr">
         <is>
-          <t>anvithbala</t>
+          <t>vlogsbysachinn</t>
         </is>
       </c>
       <c r="D646" s="12" t="inlineStr">
         <is>
-          <t>balakumar_dba@yahoo.co.in</t>
+          <t>sachinprsnl12@gmail.com</t>
         </is>
       </c>
       <c r="E646" s="12" t="inlineStr">
         <is>
-          <t>7299994911</t>
+          <t>9315724186</t>
         </is>
       </c>
       <c r="F646" s="12" t="inlineStr">
@@ -47387,34 +47387,34 @@
       </c>
       <c r="G646" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H646" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I646" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J646" s="14" t="n">
-        <v>5125</v>
+        <v>1881</v>
       </c>
       <c r="K646" s="14" t="n">
-        <v>5125</v>
+        <v>5173</v>
       </c>
       <c r="L646" s="15" t="n">
-        <v>5125</v>
+        <v>1881</v>
       </c>
       <c r="M646" s="12" t="inlineStr">
         <is>
-          <t>68ec9dd6a5316700137cfb07</t>
+          <t>68c2b6158f67740013f45471</t>
         </is>
       </c>
       <c r="N646" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68ec9dd6a5316700137cfb07</t>
+          <t>https://superprofile.bio/vig/68c2b6158f67740013f45471</t>
         </is>
       </c>
       <c r="O646" s="17" t="inlineStr">
@@ -47434,22 +47434,22 @@
       </c>
       <c r="B647" s="20" t="inlineStr">
         <is>
-          <t>65e02894261def001368f6b5</t>
+          <t>68ec9b285044ba0013a9ca08</t>
         </is>
       </c>
       <c r="C647" s="20" t="inlineStr">
         <is>
-          <t>crude</t>
+          <t>anvithbala</t>
         </is>
       </c>
       <c r="D647" s="19" t="inlineStr">
         <is>
-          <t>sunder21032009@gmail.com</t>
+          <t>balakumar_dba@yahoo.co.in</t>
         </is>
       </c>
       <c r="E647" s="19" t="inlineStr">
         <is>
-          <t>9486114296</t>
+          <t>7299994911</t>
         </is>
       </c>
       <c r="F647" s="19" t="inlineStr">
@@ -47471,22 +47471,22 @@
         <v>1</v>
       </c>
       <c r="J647" s="21" t="n">
-        <v>5101</v>
+        <v>5125</v>
       </c>
       <c r="K647" s="21" t="n">
-        <v>5101</v>
+        <v>5125</v>
       </c>
       <c r="L647" s="22" t="n">
-        <v>5101</v>
+        <v>5125</v>
       </c>
       <c r="M647" s="19" t="inlineStr">
         <is>
-          <t>65e02b19014d340013d435f2</t>
+          <t>68ec9dd6a5316700137cfb07</t>
         </is>
       </c>
       <c r="N647" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65e02b19014d340013d435f2</t>
+          <t>https://superprofile.bio/vig/68ec9dd6a5316700137cfb07</t>
         </is>
       </c>
       <c r="O647" s="24" t="inlineStr">
@@ -47506,22 +47506,22 @@
       </c>
       <c r="B648" s="13" t="inlineStr">
         <is>
-          <t>66a0d61217d88e001378fe44</t>
+          <t>65e02894261def001368f6b5</t>
         </is>
       </c>
       <c r="C648" s="13" t="inlineStr">
         <is>
-          <t>akash17971</t>
+          <t>crude</t>
         </is>
       </c>
       <c r="D648" s="12" t="inlineStr">
         <is>
-          <t>ytakash1995@gmail.com</t>
+          <t>sunder21032009@gmail.com</t>
         </is>
       </c>
       <c r="E648" s="12" t="inlineStr">
         <is>
-          <t>9548424304</t>
+          <t>9486114296</t>
         </is>
       </c>
       <c r="F648" s="12" t="inlineStr">
@@ -47531,34 +47531,34 @@
       </c>
       <c r="G648" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H648" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I648" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J648" s="14" t="n">
-        <v>3639</v>
+        <v>5101</v>
       </c>
       <c r="K648" s="14" t="n">
-        <v>5094</v>
+        <v>5101</v>
       </c>
       <c r="L648" s="15" t="n">
-        <v>3639</v>
+        <v>5101</v>
       </c>
       <c r="M648" s="12" t="inlineStr">
         <is>
-          <t>69e0bfe6e15a4d0013443f17</t>
+          <t>65e02b19014d340013d435f2</t>
         </is>
       </c>
       <c r="N648" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e0bfe6e15a4d0013443f17</t>
+          <t>https://superprofile.bio/vig/65e02b19014d340013d435f2</t>
         </is>
       </c>
       <c r="O648" s="17" t="inlineStr">
@@ -47578,22 +47578,22 @@
       </c>
       <c r="B649" s="20" t="inlineStr">
         <is>
-          <t>62d00252cbddc27faede3c84</t>
+          <t>66a0d61217d88e001378fe44</t>
         </is>
       </c>
       <c r="C649" s="20" t="inlineStr">
         <is>
-          <t>Dhaval34</t>
+          <t>akash17971</t>
         </is>
       </c>
       <c r="D649" s="19" t="inlineStr">
         <is>
-          <t>darjidhaval107@gmail.com</t>
+          <t>ytakash1995@gmail.com</t>
         </is>
       </c>
       <c r="E649" s="19" t="inlineStr">
         <is>
-          <t>6353369890</t>
+          <t>9548424304</t>
         </is>
       </c>
       <c r="F649" s="19" t="inlineStr">
@@ -47603,34 +47603,34 @@
       </c>
       <c r="G649" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H649" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I649" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J649" s="21" t="n">
-        <v>5045</v>
+        <v>3639</v>
       </c>
       <c r="K649" s="21" t="n">
-        <v>5045</v>
+        <v>5094</v>
       </c>
       <c r="L649" s="22" t="n">
-        <v>5045</v>
+        <v>3639</v>
       </c>
       <c r="M649" s="19" t="inlineStr">
         <is>
-          <t>6418359714826b001f6b31d0</t>
+          <t>69e0bfe6e15a4d0013443f17</t>
         </is>
       </c>
       <c r="N649" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6418359714826b001f6b31d0</t>
+          <t>https://superprofile.bio/vig/69e0bfe6e15a4d0013443f17</t>
         </is>
       </c>
       <c r="O649" s="24" t="inlineStr">
@@ -47650,22 +47650,22 @@
       </c>
       <c r="B650" s="13" t="inlineStr">
         <is>
-          <t>67502164ce765e0013d8cd9d</t>
+          <t>62d00252cbddc27faede3c84</t>
         </is>
       </c>
       <c r="C650" s="13" t="inlineStr">
         <is>
-          <t>thetradingscholarr</t>
+          <t>Dhaval34</t>
         </is>
       </c>
       <c r="D650" s="12" t="inlineStr">
         <is>
-          <t>thetradingscholar@gmail.com</t>
+          <t>darjidhaval107@gmail.com</t>
         </is>
       </c>
       <c r="E650" s="12" t="inlineStr">
         <is>
-          <t>8182838192</t>
+          <t>6353369890</t>
         </is>
       </c>
       <c r="F650" s="12" t="inlineStr">
@@ -47675,34 +47675,34 @@
       </c>
       <c r="G650" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H650" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I650" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J650" s="14" t="n">
-        <v>4933</v>
+        <v>5045</v>
       </c>
       <c r="K650" s="14" t="n">
-        <v>4933</v>
+        <v>5045</v>
       </c>
       <c r="L650" s="15" t="n">
-        <v>4933</v>
+        <v>5045</v>
       </c>
       <c r="M650" s="12" t="inlineStr">
         <is>
-          <t>67c21063a514640013661b84</t>
+          <t>6418359714826b001f6b31d0</t>
         </is>
       </c>
       <c r="N650" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67c21063a514640013661b84</t>
+          <t>https://superprofile.bio/vig/6418359714826b001f6b31d0</t>
         </is>
       </c>
       <c r="O650" s="17" t="inlineStr">
@@ -47722,22 +47722,22 @@
       </c>
       <c r="B651" s="20" t="inlineStr">
         <is>
-          <t>6a1ec43f62b0ef00138bace2</t>
+          <t>67502164ce765e0013d8cd9d</t>
         </is>
       </c>
       <c r="C651" s="20" t="inlineStr">
         <is>
-          <t>mindsetshustlerin</t>
+          <t>thetradingscholarr</t>
         </is>
       </c>
       <c r="D651" s="19" t="inlineStr">
         <is>
-          <t>ihsanullhaque47@gmail.com</t>
+          <t>thetradingscholar@gmail.com</t>
         </is>
       </c>
       <c r="E651" s="19" t="inlineStr">
         <is>
-          <t>8086009090</t>
+          <t>8182838192</t>
         </is>
       </c>
       <c r="F651" s="19" t="inlineStr">
@@ -47747,34 +47747,34 @@
       </c>
       <c r="G651" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H651" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I651" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J651" s="21" t="n">
-        <v>3394</v>
+        <v>4933</v>
       </c>
       <c r="K651" s="21" t="n">
-        <v>4930</v>
+        <v>4933</v>
       </c>
       <c r="L651" s="22" t="n">
-        <v>3394</v>
+        <v>4933</v>
       </c>
       <c r="M651" s="19" t="inlineStr">
         <is>
-          <t>6a6c77be29b0260013e8d665</t>
+          <t>67c21063a514640013661b84</t>
         </is>
       </c>
       <c r="N651" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6c77be29b0260013e8d665</t>
+          <t>https://superprofile.bio/vig/67c21063a514640013661b84</t>
         </is>
       </c>
       <c r="O651" s="24" t="inlineStr">
@@ -47794,22 +47794,22 @@
       </c>
       <c r="B652" s="13" t="inlineStr">
         <is>
-          <t>66dbe80d2b3bba001336d1c9</t>
+          <t>6a1ec43f62b0ef00138bace2</t>
         </is>
       </c>
       <c r="C652" s="13" t="inlineStr">
         <is>
-          <t>hariomhiren</t>
+          <t>mindsetshustlerin</t>
         </is>
       </c>
       <c r="D652" s="12" t="inlineStr">
         <is>
-          <t>hirenpandya.hariom@gmail.com</t>
+          <t>ihsanullhaque47@gmail.com</t>
         </is>
       </c>
       <c r="E652" s="12" t="inlineStr">
         <is>
-          <t>7043574159</t>
+          <t>8086009090</t>
         </is>
       </c>
       <c r="F652" s="12" t="inlineStr">
@@ -47819,34 +47819,34 @@
       </c>
       <c r="G652" s="12" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H652" s="12" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H652" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="I652" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J652" s="14" t="n">
-        <v>4912</v>
+        <v>3394</v>
       </c>
       <c r="K652" s="14" t="n">
-        <v>4912</v>
+        <v>4930</v>
       </c>
       <c r="L652" s="15" t="n">
-        <v>4912</v>
+        <v>3394</v>
       </c>
       <c r="M652" s="12" t="inlineStr">
         <is>
-          <t>66dbedbfbd3b730013cb4a61</t>
+          <t>6a6c77be29b0260013e8d665</t>
         </is>
       </c>
       <c r="N652" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66dbedbfbd3b730013cb4a61</t>
+          <t>https://superprofile.bio/vig/6a6c77be29b0260013e8d665</t>
         </is>
       </c>
       <c r="O652" s="17" t="inlineStr">
@@ -47866,22 +47866,22 @@
       </c>
       <c r="B653" s="20" t="inlineStr">
         <is>
-          <t>67cc28bfa5b64a0013a9ab38</t>
+          <t>66dbe80d2b3bba001336d1c9</t>
         </is>
       </c>
       <c r="C653" s="20" t="inlineStr">
         <is>
-          <t>threestocksfx</t>
+          <t>hariomhiren</t>
         </is>
       </c>
       <c r="D653" s="19" t="inlineStr">
         <is>
-          <t>rajputankita586@gmail.com</t>
+          <t>hirenpandya.hariom@gmail.com</t>
         </is>
       </c>
       <c r="E653" s="19" t="inlineStr">
         <is>
-          <t>6232904159</t>
+          <t>7043574159</t>
         </is>
       </c>
       <c r="F653" s="19" t="inlineStr">
@@ -47903,22 +47903,22 @@
         <v>1</v>
       </c>
       <c r="J653" s="21" t="n">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="K653" s="21" t="n">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="L653" s="22" t="n">
-        <v>4911</v>
+        <v>4912</v>
       </c>
       <c r="M653" s="19" t="inlineStr">
         <is>
-          <t>67cacfc13c278d0013ff1db3</t>
+          <t>66dbedbfbd3b730013cb4a61</t>
         </is>
       </c>
       <c r="N653" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67cacfc13c278d0013ff1db3</t>
+          <t>https://superprofile.bio/vig/66dbedbfbd3b730013cb4a61</t>
         </is>
       </c>
       <c r="O653" s="24" t="inlineStr">
@@ -47938,22 +47938,22 @@
       </c>
       <c r="B654" s="13" t="inlineStr">
         <is>
-          <t>641344de24c7290020be7b2a</t>
+          <t>67cc28bfa5b64a0013a9ab38</t>
         </is>
       </c>
       <c r="C654" s="13" t="inlineStr">
         <is>
-          <t>JSS</t>
+          <t>threestocksfx</t>
         </is>
       </c>
       <c r="D654" s="12" t="inlineStr">
         <is>
-          <t>Dhavalpatal040@gmail.com</t>
+          <t>rajputankita586@gmail.com</t>
         </is>
       </c>
       <c r="E654" s="12" t="inlineStr">
         <is>
-          <t>7976450407</t>
+          <t>6232904159</t>
         </is>
       </c>
       <c r="F654" s="12" t="inlineStr">
@@ -47963,34 +47963,34 @@
       </c>
       <c r="G654" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H654" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I654" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J654" s="14" t="n">
-        <v>4882</v>
+        <v>4911</v>
       </c>
       <c r="K654" s="14" t="n">
-        <v>4882</v>
+        <v>4911</v>
       </c>
       <c r="L654" s="15" t="n">
-        <v>4882</v>
+        <v>4911</v>
       </c>
       <c r="M654" s="12" t="inlineStr">
         <is>
-          <t>65018a07e24de1001ea91d75</t>
+          <t>67cacfc13c278d0013ff1db3</t>
         </is>
       </c>
       <c r="N654" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65018a07e24de1001ea91d75</t>
+          <t>https://superprofile.bio/vig/67cacfc13c278d0013ff1db3</t>
         </is>
       </c>
       <c r="O654" s="17" t="inlineStr">
@@ -48010,22 +48010,22 @@
       </c>
       <c r="B655" s="20" t="inlineStr">
         <is>
-          <t>66289f88804eff00137227a2</t>
+          <t>641344de24c7290020be7b2a</t>
         </is>
       </c>
       <c r="C655" s="20" t="inlineStr">
         <is>
-          <t>valuetrader01</t>
+          <t>JSS</t>
         </is>
       </c>
       <c r="D655" s="19" t="inlineStr">
         <is>
-          <t>valuetrader41@gmail.com</t>
+          <t>Dhavalpatal040@gmail.com</t>
         </is>
       </c>
       <c r="E655" s="19" t="inlineStr">
         <is>
-          <t>9450049279</t>
+          <t>7976450407</t>
         </is>
       </c>
       <c r="F655" s="19" t="inlineStr">
@@ -48035,34 +48035,34 @@
       </c>
       <c r="G655" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H655" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I655" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J655" s="21" t="n">
-        <v>2441</v>
+        <v>4882</v>
       </c>
       <c r="K655" s="21" t="n">
         <v>4882</v>
       </c>
       <c r="L655" s="22" t="n">
-        <v>2441</v>
+        <v>4882</v>
       </c>
       <c r="M655" s="19" t="inlineStr">
         <is>
-          <t>6846b8cd771c3e001386f931</t>
+          <t>65018a07e24de1001ea91d75</t>
         </is>
       </c>
       <c r="N655" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6846b8cd771c3e001386f931</t>
+          <t>https://superprofile.bio/vig/65018a07e24de1001ea91d75</t>
         </is>
       </c>
       <c r="O655" s="24" t="inlineStr">
@@ -48082,22 +48082,22 @@
       </c>
       <c r="B656" s="13" t="inlineStr">
         <is>
-          <t>646b738daca3b2002055b959</t>
+          <t>66289f88804eff00137227a2</t>
         </is>
       </c>
       <c r="C656" s="13" t="inlineStr">
         <is>
-          <t>MBPREMIUMMEMBERSHIP</t>
+          <t>valuetrader01</t>
         </is>
       </c>
       <c r="D656" s="12" t="inlineStr">
         <is>
-          <t>jtneee06@gmail.com</t>
+          <t>valuetrader41@gmail.com</t>
         </is>
       </c>
       <c r="E656" s="12" t="inlineStr">
         <is>
-          <t>9495487644</t>
+          <t>9450049279</t>
         </is>
       </c>
       <c r="F656" s="12" t="inlineStr">
@@ -48107,34 +48107,34 @@
       </c>
       <c r="G656" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H656" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I656" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J656" s="14" t="n">
-        <v>4835</v>
+        <v>2441</v>
       </c>
       <c r="K656" s="14" t="n">
-        <v>4835</v>
+        <v>4882</v>
       </c>
       <c r="L656" s="15" t="n">
-        <v>4835</v>
+        <v>2441</v>
       </c>
       <c r="M656" s="12" t="inlineStr">
         <is>
-          <t>654109ebeebd4a001d9f7598</t>
+          <t>6846b8cd771c3e001386f931</t>
         </is>
       </c>
       <c r="N656" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/654109ebeebd4a001d9f7598</t>
+          <t>https://superprofile.bio/vig/6846b8cd771c3e001386f931</t>
         </is>
       </c>
       <c r="O656" s="17" t="inlineStr">
@@ -48154,22 +48154,22 @@
       </c>
       <c r="B657" s="20" t="inlineStr">
         <is>
-          <t>6475a095ab41f2001fa94c93</t>
+          <t>646b738daca3b2002055b959</t>
         </is>
       </c>
       <c r="C657" s="20" t="inlineStr">
         <is>
-          <t>thetradeblog</t>
+          <t>MBPREMIUMMEMBERSHIP</t>
         </is>
       </c>
       <c r="D657" s="19" t="inlineStr">
         <is>
-          <t>thetradeblog1991@gmail.com</t>
+          <t>jtneee06@gmail.com</t>
         </is>
       </c>
       <c r="E657" s="19" t="inlineStr">
         <is>
-          <t>9898095432</t>
+          <t>9495487644</t>
         </is>
       </c>
       <c r="F657" s="19" t="inlineStr">
@@ -48179,34 +48179,34 @@
       </c>
       <c r="G657" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H657" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I657" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J657" s="21" t="n">
-        <v>4822</v>
+        <v>4835</v>
       </c>
       <c r="K657" s="21" t="n">
-        <v>4822</v>
+        <v>4835</v>
       </c>
       <c r="L657" s="22" t="n">
-        <v>4822</v>
+        <v>4835</v>
       </c>
       <c r="M657" s="19" t="inlineStr">
         <is>
-          <t>647610311a9d6e001f8a6957</t>
+          <t>654109ebeebd4a001d9f7598</t>
         </is>
       </c>
       <c r="N657" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647610311a9d6e001f8a6957</t>
+          <t>https://superprofile.bio/vig/654109ebeebd4a001d9f7598</t>
         </is>
       </c>
       <c r="O657" s="24" t="inlineStr">
@@ -48226,22 +48226,22 @@
       </c>
       <c r="B658" s="13" t="inlineStr">
         <is>
-          <t>6964db232eccc10013d25121</t>
+          <t>6475a095ab41f2001fa94c93</t>
         </is>
       </c>
       <c r="C658" s="13" t="inlineStr">
         <is>
-          <t>projectwireorg</t>
+          <t>thetradeblog</t>
         </is>
       </c>
       <c r="D658" s="12" t="inlineStr">
         <is>
-          <t>hey@projectwire.org</t>
+          <t>thetradeblog1991@gmail.com</t>
         </is>
       </c>
       <c r="E658" s="12" t="inlineStr">
         <is>
-          <t>9821891084</t>
+          <t>9898095432</t>
         </is>
       </c>
       <c r="F658" s="12" t="inlineStr">
@@ -48251,34 +48251,34 @@
       </c>
       <c r="G658" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H658" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I658" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J658" s="14" t="n">
-        <v>4794</v>
+        <v>4822</v>
       </c>
       <c r="K658" s="14" t="n">
-        <v>4794</v>
+        <v>4822</v>
       </c>
       <c r="L658" s="15" t="n">
-        <v>4794</v>
+        <v>4822</v>
       </c>
       <c r="M658" s="12" t="inlineStr">
         <is>
-          <t>69fa07f8353a45001315a32e</t>
+          <t>647610311a9d6e001f8a6957</t>
         </is>
       </c>
       <c r="N658" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69fa07f8353a45001315a32e</t>
+          <t>https://superprofile.bio/vig/647610311a9d6e001f8a6957</t>
         </is>
       </c>
       <c r="O658" s="17" t="inlineStr">
@@ -48298,22 +48298,22 @@
       </c>
       <c r="B659" s="20" t="inlineStr">
         <is>
-          <t>6967aa5a048bfe0013028036</t>
+          <t>6964db232eccc10013d25121</t>
         </is>
       </c>
       <c r="C659" s="20" t="inlineStr">
         <is>
-          <t>mohituk18</t>
+          <t>projectwireorg</t>
         </is>
       </c>
       <c r="D659" s="19" t="inlineStr">
         <is>
-          <t>mohit.biz90@gmail.com</t>
+          <t>hey@projectwire.org</t>
         </is>
       </c>
       <c r="E659" s="19" t="inlineStr">
         <is>
-          <t>8791769602</t>
+          <t>9821891084</t>
         </is>
       </c>
       <c r="F659" s="19" t="inlineStr">
@@ -48323,7 +48323,7 @@
       </c>
       <c r="G659" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H659" s="19" t="inlineStr">
@@ -48332,25 +48332,25 @@
         </is>
       </c>
       <c r="I659" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J659" s="21" t="n">
-        <v>1446</v>
+        <v>4794</v>
       </c>
       <c r="K659" s="21" t="n">
-        <v>4772</v>
+        <v>4794</v>
       </c>
       <c r="L659" s="22" t="n">
-        <v>3326</v>
+        <v>4794</v>
       </c>
       <c r="M659" s="19" t="inlineStr">
         <is>
-          <t>67a4e26933228900147e6e23</t>
+          <t>69fa07f8353a45001315a32e</t>
         </is>
       </c>
       <c r="N659" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a4e26933228900147e6e23</t>
+          <t>https://superprofile.bio/vig/69fa07f8353a45001315a32e</t>
         </is>
       </c>
       <c r="O659" s="24" t="inlineStr">
@@ -48370,22 +48370,22 @@
       </c>
       <c r="B660" s="13" t="inlineStr">
         <is>
-          <t>6a36aba84cf49e0012657a09</t>
+          <t>6967aa5a048bfe0013028036</t>
         </is>
       </c>
       <c r="C660" s="13" t="inlineStr">
         <is>
-          <t>mohdzaidan</t>
+          <t>mohituk18</t>
         </is>
       </c>
       <c r="D660" s="12" t="inlineStr">
         <is>
-          <t>kingvlogs5126@gmail.com</t>
+          <t>mohit.biz90@gmail.com</t>
         </is>
       </c>
       <c r="E660" s="12" t="inlineStr">
         <is>
-          <t>7251095126</t>
+          <t>8791769602</t>
         </is>
       </c>
       <c r="F660" s="12" t="inlineStr">
@@ -48395,34 +48395,34 @@
       </c>
       <c r="G660" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H660" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I660" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J660" s="14" t="n">
-        <v>4764</v>
+        <v>1446</v>
       </c>
       <c r="K660" s="14" t="n">
-        <v>4764</v>
+        <v>4772</v>
       </c>
       <c r="L660" s="15" t="n">
-        <v>4764</v>
+        <v>3326</v>
       </c>
       <c r="M660" s="12" t="inlineStr">
         <is>
-          <t>6a3d6a4890d55600135e1a17</t>
+          <t>67a4e26933228900147e6e23</t>
         </is>
       </c>
       <c r="N660" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3d6a4890d55600135e1a17</t>
+          <t>https://superprofile.bio/vig/67a4e26933228900147e6e23</t>
         </is>
       </c>
       <c r="O660" s="17" t="inlineStr">
@@ -48442,22 +48442,22 @@
       </c>
       <c r="B661" s="20" t="inlineStr">
         <is>
-          <t>65c89053e0e11f001e822548</t>
+          <t>6a36aba84cf49e0012657a09</t>
         </is>
       </c>
       <c r="C661" s="20" t="inlineStr">
         <is>
-          <t>freshershunt</t>
+          <t>mohdzaidan</t>
         </is>
       </c>
       <c r="D661" s="19" t="inlineStr">
         <is>
-          <t>freshershunt.in@gmail.com</t>
+          <t>kingvlogs5126@gmail.com</t>
         </is>
       </c>
       <c r="E661" s="19" t="inlineStr">
         <is>
-          <t>9060803166</t>
+          <t>7251095126</t>
         </is>
       </c>
       <c r="F661" s="19" t="inlineStr">
@@ -48467,34 +48467,34 @@
       </c>
       <c r="G661" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H661" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I661" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J661" s="21" t="n">
-        <v>1007</v>
+        <v>4764</v>
       </c>
       <c r="K661" s="21" t="n">
-        <v>4763</v>
+        <v>4764</v>
       </c>
       <c r="L661" s="22" t="n">
-        <v>1878</v>
+        <v>4764</v>
       </c>
       <c r="M661" s="19" t="inlineStr">
         <is>
-          <t>65f84c6876f3550013a2920c</t>
+          <t>6a3d6a4890d55600135e1a17</t>
         </is>
       </c>
       <c r="N661" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
+          <t>https://superprofile.bio/vig/6a3d6a4890d55600135e1a17</t>
         </is>
       </c>
       <c r="O661" s="24" t="inlineStr">
@@ -48514,22 +48514,22 @@
       </c>
       <c r="B662" s="13" t="inlineStr">
         <is>
-          <t>64cc03e3836e48001ec44b6d</t>
+          <t>65c89053e0e11f001e822548</t>
         </is>
       </c>
       <c r="C662" s="13" t="inlineStr">
         <is>
-          <t>abstocks</t>
+          <t>freshershunt</t>
         </is>
       </c>
       <c r="D662" s="12" t="inlineStr">
         <is>
-          <t>fahadabu850@gmail.com</t>
+          <t>freshershunt.in@gmail.com</t>
         </is>
       </c>
       <c r="E662" s="12" t="inlineStr">
         <is>
-          <t>9756123437</t>
+          <t>9060803166</t>
         </is>
       </c>
       <c r="F662" s="12" t="inlineStr">
@@ -48539,34 +48539,34 @@
       </c>
       <c r="G662" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H662" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I662" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J662" s="14" t="n">
-        <v>4734</v>
+        <v>1007</v>
       </c>
       <c r="K662" s="14" t="n">
-        <v>4734</v>
+        <v>4763</v>
       </c>
       <c r="L662" s="15" t="n">
-        <v>4734</v>
+        <v>1878</v>
       </c>
       <c r="M662" s="12" t="inlineStr">
         <is>
-          <t>6a747aca7fbc090013754e37</t>
+          <t>65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="N662" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a747aca7fbc090013754e37</t>
+          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="O662" s="17" t="inlineStr">
@@ -48586,22 +48586,22 @@
       </c>
       <c r="B663" s="20" t="inlineStr">
         <is>
-          <t>677e1f8423805b0013390e5c</t>
+          <t>64cc03e3836e48001ec44b6d</t>
         </is>
       </c>
       <c r="C663" s="20" t="inlineStr">
         <is>
-          <t>nikhilkushwahaa</t>
+          <t>abstocks</t>
         </is>
       </c>
       <c r="D663" s="19" t="inlineStr">
         <is>
-          <t>nikhilkushwaha99777@gmail.com</t>
+          <t>fahadabu850@gmail.com</t>
         </is>
       </c>
       <c r="E663" s="19" t="inlineStr">
         <is>
-          <t>9977782457</t>
+          <t>9756123437</t>
         </is>
       </c>
       <c r="F663" s="19" t="inlineStr">
@@ -48611,34 +48611,34 @@
       </c>
       <c r="G663" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H663" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I663" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J663" s="21" t="n">
-        <v>4733</v>
+        <v>4734</v>
       </c>
       <c r="K663" s="21" t="n">
-        <v>4733</v>
+        <v>4734</v>
       </c>
       <c r="L663" s="22" t="n">
-        <v>4733</v>
+        <v>4734</v>
       </c>
       <c r="M663" s="19" t="inlineStr">
         <is>
-          <t>6a7566ca32fda30013666078</t>
+          <t>6a747aca7fbc090013754e37</t>
         </is>
       </c>
       <c r="N663" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7566ca32fda30013666078</t>
+          <t>https://superprofile.bio/vig/6a747aca7fbc090013754e37</t>
         </is>
       </c>
       <c r="O663" s="24" t="inlineStr">
@@ -48658,22 +48658,22 @@
       </c>
       <c r="B664" s="13" t="inlineStr">
         <is>
-          <t>64ccb84e04c302001d67cde6</t>
+          <t>677e1f8423805b0013390e5c</t>
         </is>
       </c>
       <c r="C664" s="13" t="inlineStr">
         <is>
-          <t>twopmtrader</t>
+          <t>nikhilkushwahaa</t>
         </is>
       </c>
       <c r="D664" s="12" t="inlineStr">
         <is>
-          <t>ausaf.zubair@gmail.com</t>
+          <t>nikhilkushwaha99777@gmail.com</t>
         </is>
       </c>
       <c r="E664" s="12" t="inlineStr">
         <is>
-          <t>9700965934</t>
+          <t>9977782457</t>
         </is>
       </c>
       <c r="F664" s="12" t="inlineStr">
@@ -48683,34 +48683,34 @@
       </c>
       <c r="G664" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H664" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I664" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J664" s="14" t="n">
-        <v>4704</v>
+        <v>4733</v>
       </c>
       <c r="K664" s="14" t="n">
-        <v>4704</v>
+        <v>4733</v>
       </c>
       <c r="L664" s="15" t="n">
-        <v>4704</v>
+        <v>4733</v>
       </c>
       <c r="M664" s="12" t="inlineStr">
         <is>
-          <t>6945e0dfd17c0800138f13d3</t>
+          <t>6a7566ca32fda30013666078</t>
         </is>
       </c>
       <c r="N664" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6945e0dfd17c0800138f13d3</t>
+          <t>https://superprofile.bio/vig/6a7566ca32fda30013666078</t>
         </is>
       </c>
       <c r="O664" s="17" t="inlineStr">
@@ -48730,22 +48730,22 @@
       </c>
       <c r="B665" s="20" t="inlineStr">
         <is>
-          <t>6788ca6493df9b001313bee5</t>
+          <t>64ccb84e04c302001d67cde6</t>
         </is>
       </c>
       <c r="C665" s="20" t="inlineStr">
         <is>
-          <t>compoundly</t>
+          <t>twopmtrader</t>
         </is>
       </c>
       <c r="D665" s="19" t="inlineStr">
         <is>
-          <t>shiwanilegal31@gmail.com</t>
+          <t>ausaf.zubair@gmail.com</t>
         </is>
       </c>
       <c r="E665" s="19" t="inlineStr">
         <is>
-          <t>9821037875</t>
+          <t>9700965934</t>
         </is>
       </c>
       <c r="F665" s="19" t="inlineStr">
@@ -48755,7 +48755,7 @@
       </c>
       <c r="G665" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H665" s="19" t="inlineStr">
@@ -48764,25 +48764,25 @@
         </is>
       </c>
       <c r="I665" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J665" s="21" t="n">
-        <v>3239</v>
+        <v>4704</v>
       </c>
       <c r="K665" s="21" t="n">
-        <v>4687</v>
+        <v>4704</v>
       </c>
       <c r="L665" s="22" t="n">
-        <v>3239</v>
+        <v>4704</v>
       </c>
       <c r="M665" s="19" t="inlineStr">
         <is>
-          <t>68f764d5f9db6f0013225489</t>
+          <t>6945e0dfd17c0800138f13d3</t>
         </is>
       </c>
       <c r="N665" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f764d5f9db6f0013225489</t>
+          <t>https://superprofile.bio/vig/6945e0dfd17c0800138f13d3</t>
         </is>
       </c>
       <c r="O665" s="24" t="inlineStr">
@@ -48802,22 +48802,22 @@
       </c>
       <c r="B666" s="13" t="inlineStr">
         <is>
-          <t>6836bfddf7680b00139f707c</t>
+          <t>6788ca6493df9b001313bee5</t>
         </is>
       </c>
       <c r="C666" s="13" t="inlineStr">
         <is>
-          <t>tradewithnikhil</t>
+          <t>compoundly</t>
         </is>
       </c>
       <c r="D666" s="12" t="inlineStr">
         <is>
-          <t>nikhilaroraet@gmail.com</t>
+          <t>shiwanilegal31@gmail.com</t>
         </is>
       </c>
       <c r="E666" s="12" t="inlineStr">
         <is>
-          <t>7898550453</t>
+          <t>9821037875</t>
         </is>
       </c>
       <c r="F666" s="12" t="inlineStr">
@@ -48827,34 +48827,34 @@
       </c>
       <c r="G666" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H666" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I666" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J666" s="14" t="n">
-        <v>4636</v>
+        <v>3239</v>
       </c>
       <c r="K666" s="14" t="n">
-        <v>4636</v>
+        <v>4687</v>
       </c>
       <c r="L666" s="15" t="n">
-        <v>4636</v>
+        <v>3239</v>
       </c>
       <c r="M666" s="12" t="inlineStr">
         <is>
-          <t>6836f7a42dfe1f0013fccdb9</t>
+          <t>68f764d5f9db6f0013225489</t>
         </is>
       </c>
       <c r="N666" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6836f7a42dfe1f0013fccdb9</t>
+          <t>https://superprofile.bio/vig/68f764d5f9db6f0013225489</t>
         </is>
       </c>
       <c r="O666" s="17" t="inlineStr">
@@ -48874,22 +48874,22 @@
       </c>
       <c r="B667" s="20" t="inlineStr">
         <is>
-          <t>642d36c8795bf4001f9eb7ac</t>
+          <t>6836bfddf7680b00139f707c</t>
         </is>
       </c>
       <c r="C667" s="20" t="inlineStr">
         <is>
-          <t>ssquareit</t>
+          <t>tradewithnikhil</t>
         </is>
       </c>
       <c r="D667" s="19" t="inlineStr">
         <is>
-          <t>ssquareitsolutionspune@gmail.com</t>
+          <t>nikhilaroraet@gmail.com</t>
         </is>
       </c>
       <c r="E667" s="19" t="inlineStr">
         <is>
-          <t>7020103785</t>
+          <t>7898550453</t>
         </is>
       </c>
       <c r="F667" s="19" t="inlineStr">
@@ -48899,34 +48899,34 @@
       </c>
       <c r="G667" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H667" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I667" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J667" s="21" t="n">
-        <v>1409</v>
+        <v>4636</v>
       </c>
       <c r="K667" s="21" t="n">
-        <v>4614</v>
+        <v>4636</v>
       </c>
       <c r="L667" s="22" t="n">
-        <v>1796</v>
+        <v>4636</v>
       </c>
       <c r="M667" s="19" t="inlineStr">
         <is>
-          <t>67482c5e514ba30013f7097e</t>
+          <t>6836f7a42dfe1f0013fccdb9</t>
         </is>
       </c>
       <c r="N667" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67482c5e514ba30013f7097e</t>
+          <t>https://superprofile.bio/vig/6836f7a42dfe1f0013fccdb9</t>
         </is>
       </c>
       <c r="O667" s="24" t="inlineStr">
@@ -48946,22 +48946,22 @@
       </c>
       <c r="B668" s="13" t="inlineStr">
         <is>
-          <t>65a85c95ac6382001e286a41</t>
+          <t>642d36c8795bf4001f9eb7ac</t>
         </is>
       </c>
       <c r="C668" s="13" t="inlineStr">
         <is>
-          <t>subhxtrading</t>
+          <t>ssquareit</t>
         </is>
       </c>
       <c r="D668" s="12" t="inlineStr">
         <is>
-          <t>subhashishlal19@gmail.com</t>
+          <t>ssquareitsolutionspune@gmail.com</t>
         </is>
       </c>
       <c r="E668" s="12" t="inlineStr">
         <is>
-          <t>8235660288</t>
+          <t>7020103785</t>
         </is>
       </c>
       <c r="F668" s="12" t="inlineStr">
@@ -48971,34 +48971,34 @@
       </c>
       <c r="G668" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H668" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I668" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J668" s="14" t="n">
-        <v>4523</v>
+        <v>1409</v>
       </c>
       <c r="K668" s="14" t="n">
-        <v>4523</v>
+        <v>4614</v>
       </c>
       <c r="L668" s="15" t="n">
-        <v>4523</v>
+        <v>1796</v>
       </c>
       <c r="M668" s="12" t="inlineStr">
         <is>
-          <t>6a55fc888c4f550014852580</t>
+          <t>67482c5e514ba30013f7097e</t>
         </is>
       </c>
       <c r="N668" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a55fc888c4f550014852580</t>
+          <t>https://superprofile.bio/vig/67482c5e514ba30013f7097e</t>
         </is>
       </c>
       <c r="O668" s="17" t="inlineStr">
@@ -49018,22 +49018,22 @@
       </c>
       <c r="B669" s="20" t="inlineStr">
         <is>
-          <t>63c92432b3a7fb002cbc75d0</t>
+          <t>65a85c95ac6382001e286a41</t>
         </is>
       </c>
       <c r="C669" s="20" t="inlineStr">
         <is>
-          <t>prakashpk</t>
+          <t>subhxtrading</t>
         </is>
       </c>
       <c r="D669" s="19" t="inlineStr">
         <is>
-          <t>pktradeinn5@gmail.com</t>
+          <t>subhashishlal19@gmail.com</t>
         </is>
       </c>
       <c r="E669" s="19" t="inlineStr">
         <is>
-          <t>9928429327</t>
+          <t>8235660288</t>
         </is>
       </c>
       <c r="F669" s="19" t="inlineStr">
@@ -49043,34 +49043,34 @@
       </c>
       <c r="G669" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H669" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I669" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J669" s="21" t="n">
-        <v>4505</v>
+        <v>4523</v>
       </c>
       <c r="K669" s="21" t="n">
-        <v>4505</v>
+        <v>4523</v>
       </c>
       <c r="L669" s="22" t="n">
-        <v>4505</v>
+        <v>4523</v>
       </c>
       <c r="M669" s="19" t="inlineStr">
         <is>
-          <t>65bbcccd4ac232001eb3ebfe</t>
+          <t>6a55fc888c4f550014852580</t>
         </is>
       </c>
       <c r="N669" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65bbcccd4ac232001eb3ebfe</t>
+          <t>https://superprofile.bio/vig/6a55fc888c4f550014852580</t>
         </is>
       </c>
       <c r="O669" s="24" t="inlineStr">
@@ -49090,22 +49090,22 @@
       </c>
       <c r="B670" s="13" t="inlineStr">
         <is>
-          <t>67513d9dd5b500001487cf5a</t>
+          <t>63c92432b3a7fb002cbc75d0</t>
         </is>
       </c>
       <c r="C670" s="13" t="inlineStr">
         <is>
-          <t>vighdfc087hh64rhu66</t>
+          <t>prakashpk</t>
         </is>
       </c>
       <c r="D670" s="12" t="inlineStr">
         <is>
-          <t>DKP.775504@GMAIL.COM</t>
+          <t>pktradeinn5@gmail.com</t>
         </is>
       </c>
       <c r="E670" s="12" t="inlineStr">
         <is>
-          <t>7733995504</t>
+          <t>9928429327</t>
         </is>
       </c>
       <c r="F670" s="12" t="inlineStr">
@@ -49115,34 +49115,34 @@
       </c>
       <c r="G670" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H670" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I670" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J670" s="14" t="n">
-        <v>4499</v>
+        <v>4505</v>
       </c>
       <c r="K670" s="14" t="n">
-        <v>4499</v>
+        <v>4505</v>
       </c>
       <c r="L670" s="15" t="n">
-        <v>4499</v>
+        <v>4505</v>
       </c>
       <c r="M670" s="12" t="inlineStr">
         <is>
-          <t>6759c63e8a553700132dc4d8</t>
+          <t>65bbcccd4ac232001eb3ebfe</t>
         </is>
       </c>
       <c r="N670" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6759c63e8a553700132dc4d8</t>
+          <t>https://superprofile.bio/vig/65bbcccd4ac232001eb3ebfe</t>
         </is>
       </c>
       <c r="O670" s="17" t="inlineStr">
@@ -49162,22 +49162,22 @@
       </c>
       <c r="B671" s="20" t="inlineStr">
         <is>
-          <t>645ca52a5f8e6f001f368197</t>
+          <t>67513d9dd5b500001487cf5a</t>
         </is>
       </c>
       <c r="C671" s="20" t="inlineStr">
         <is>
-          <t>tradingbullspvtltd</t>
+          <t>vighdfc087hh64rhu66</t>
         </is>
       </c>
       <c r="D671" s="19" t="inlineStr">
         <is>
-          <t>tradingbulls.j@gmail.com</t>
+          <t>DKP.775504@GMAIL.COM</t>
         </is>
       </c>
       <c r="E671" s="19" t="inlineStr">
         <is>
-          <t>9384917408</t>
+          <t>7733995504</t>
         </is>
       </c>
       <c r="F671" s="19" t="inlineStr">
@@ -49209,12 +49209,12 @@
       </c>
       <c r="M671" s="19" t="inlineStr">
         <is>
-          <t>645ca65dc550f8001f1e5ee5</t>
+          <t>6759c63e8a553700132dc4d8</t>
         </is>
       </c>
       <c r="N671" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/645ca65dc550f8001f1e5ee5</t>
+          <t>https://superprofile.bio/vig/6759c63e8a553700132dc4d8</t>
         </is>
       </c>
       <c r="O671" s="24" t="inlineStr">
@@ -49234,22 +49234,22 @@
       </c>
       <c r="B672" s="13" t="inlineStr">
         <is>
-          <t>64eccad3656bd0001dbc3cb0</t>
+          <t>645ca52a5f8e6f001f368197</t>
         </is>
       </c>
       <c r="C672" s="13" t="inlineStr">
         <is>
-          <t>virenderjakhar</t>
+          <t>tradingbullspvtltd</t>
         </is>
       </c>
       <c r="D672" s="12" t="inlineStr">
         <is>
-          <t>potentialvirender@gmail.com</t>
+          <t>tradingbulls.j@gmail.com</t>
         </is>
       </c>
       <c r="E672" s="12" t="inlineStr">
         <is>
-          <t>9053535631</t>
+          <t>9384917408</t>
         </is>
       </c>
       <c r="F672" s="12" t="inlineStr">
@@ -49264,29 +49264,29 @@
       </c>
       <c r="H672" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I672" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J672" s="14" t="n">
-        <v>2246</v>
+        <v>4499</v>
       </c>
       <c r="K672" s="14" t="n">
-        <v>4492</v>
+        <v>4499</v>
       </c>
       <c r="L672" s="15" t="n">
-        <v>2246</v>
+        <v>4499</v>
       </c>
       <c r="M672" s="12" t="inlineStr">
         <is>
-          <t>69ad428e575c1100139bee62</t>
+          <t>645ca65dc550f8001f1e5ee5</t>
         </is>
       </c>
       <c r="N672" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ad428e575c1100139bee62</t>
+          <t>https://superprofile.bio/vig/645ca65dc550f8001f1e5ee5</t>
         </is>
       </c>
       <c r="O672" s="17" t="inlineStr">
@@ -49306,22 +49306,22 @@
       </c>
       <c r="B673" s="20" t="inlineStr">
         <is>
-          <t>675325243cd5c300136686ad</t>
+          <t>64eccad3656bd0001dbc3cb0</t>
         </is>
       </c>
       <c r="C673" s="20" t="inlineStr">
         <is>
-          <t>awdhesh12</t>
+          <t>virenderjakhar</t>
         </is>
       </c>
       <c r="D673" s="19" t="inlineStr">
         <is>
-          <t>awdheshkumar787015@gmail.com</t>
+          <t>potentialvirender@gmail.com</t>
         </is>
       </c>
       <c r="E673" s="19" t="inlineStr">
         <is>
-          <t>7322081660</t>
+          <t>9053535631</t>
         </is>
       </c>
       <c r="F673" s="19" t="inlineStr">
@@ -49331,7 +49331,7 @@
       </c>
       <c r="G673" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H673" s="19" t="inlineStr">
@@ -49340,25 +49340,25 @@
         </is>
       </c>
       <c r="I673" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J673" s="21" t="n">
-        <v>1080</v>
+        <v>2246</v>
       </c>
       <c r="K673" s="21" t="n">
-        <v>4320</v>
+        <v>4492</v>
       </c>
       <c r="L673" s="22" t="n">
-        <v>1080</v>
+        <v>2246</v>
       </c>
       <c r="M673" s="19" t="inlineStr">
         <is>
-          <t>6753f5df88eada0013d4acd0</t>
+          <t>69ad428e575c1100139bee62</t>
         </is>
       </c>
       <c r="N673" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6753f5df88eada0013d4acd0</t>
+          <t>https://superprofile.bio/vig/69ad428e575c1100139bee62</t>
         </is>
       </c>
       <c r="O673" s="24" t="inlineStr">
@@ -49378,22 +49378,22 @@
       </c>
       <c r="B674" s="13" t="inlineStr">
         <is>
-          <t>63b92b9b856cac00322f2516</t>
+          <t>675325243cd5c300136686ad</t>
         </is>
       </c>
       <c r="C674" s="13" t="inlineStr">
         <is>
-          <t>tradewithshree</t>
+          <t>awdhesh12</t>
         </is>
       </c>
       <c r="D674" s="12" t="inlineStr">
         <is>
-          <t>shreyashgupta018@gmail.com</t>
+          <t>awdheshkumar787015@gmail.com</t>
         </is>
       </c>
       <c r="E674" s="12" t="inlineStr">
         <is>
-          <t>9529829925</t>
+          <t>7322081660</t>
         </is>
       </c>
       <c r="F674" s="12" t="inlineStr">
@@ -49403,34 +49403,34 @@
       </c>
       <c r="G674" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H674" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I674" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J674" s="14" t="n">
-        <v>4315</v>
+        <v>1080</v>
       </c>
       <c r="K674" s="14" t="n">
-        <v>4315</v>
+        <v>4320</v>
       </c>
       <c r="L674" s="15" t="n">
-        <v>4315</v>
+        <v>1080</v>
       </c>
       <c r="M674" s="12" t="inlineStr">
         <is>
-          <t>6a9690e65a0b9a001334b15b</t>
+          <t>6753f5df88eada0013d4acd0</t>
         </is>
       </c>
       <c r="N674" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9690e65a0b9a001334b15b</t>
+          <t>https://superprofile.bio/vig/6753f5df88eada0013d4acd0</t>
         </is>
       </c>
       <c r="O674" s="17" t="inlineStr">
@@ -49450,22 +49450,22 @@
       </c>
       <c r="B675" s="20" t="inlineStr">
         <is>
-          <t>6a4e3d2d04591d00135b9ac0</t>
+          <t>63b92b9b856cac00322f2516</t>
         </is>
       </c>
       <c r="C675" s="20" t="inlineStr">
         <is>
-          <t>shrii</t>
+          <t>tradewithshree</t>
         </is>
       </c>
       <c r="D675" s="19" t="inlineStr">
         <is>
-          <t>satyamlabade1171@gmail.com</t>
+          <t>shreyashgupta018@gmail.com</t>
         </is>
       </c>
       <c r="E675" s="19" t="inlineStr">
         <is>
-          <t>8101111171</t>
+          <t>9529829925</t>
         </is>
       </c>
       <c r="F675" s="19" t="inlineStr">
@@ -49487,22 +49487,22 @@
         <v>1</v>
       </c>
       <c r="J675" s="21" t="n">
-        <v>4260</v>
+        <v>4315</v>
       </c>
       <c r="K675" s="21" t="n">
-        <v>4260</v>
+        <v>4315</v>
       </c>
       <c r="L675" s="22" t="n">
-        <v>4260</v>
+        <v>4315</v>
       </c>
       <c r="M675" s="19" t="inlineStr">
         <is>
-          <t>6a4f2a4523614b00135a6835</t>
+          <t>6a9690e65a0b9a001334b15b</t>
         </is>
       </c>
       <c r="N675" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4f2a4523614b00135a6835</t>
+          <t>https://superprofile.bio/vig/6a9690e65a0b9a001334b15b</t>
         </is>
       </c>
       <c r="O675" s="24" t="inlineStr">
@@ -49522,22 +49522,22 @@
       </c>
       <c r="B676" s="13" t="inlineStr">
         <is>
-          <t>69c5265e2203a70013a81621</t>
+          <t>6a4e3d2d04591d00135b9ac0</t>
         </is>
       </c>
       <c r="C676" s="13" t="inlineStr">
         <is>
-          <t>Haresh9504</t>
+          <t>shrii</t>
         </is>
       </c>
       <c r="D676" s="12" t="inlineStr">
         <is>
-          <t>hareshbhata5623@gmail.com</t>
+          <t>satyamlabade1171@gmail.com</t>
         </is>
       </c>
       <c r="E676" s="12" t="inlineStr">
         <is>
-          <t>7046653069</t>
+          <t>8101111171</t>
         </is>
       </c>
       <c r="F676" s="12" t="inlineStr">
@@ -49547,34 +49547,34 @@
       </c>
       <c r="G676" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H676" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I676" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J676" s="14" t="n">
-        <v>1892</v>
+        <v>4260</v>
       </c>
       <c r="K676" s="14" t="n">
-        <v>4256</v>
+        <v>4260</v>
       </c>
       <c r="L676" s="15" t="n">
-        <v>2364</v>
+        <v>4260</v>
       </c>
       <c r="M676" s="12" t="inlineStr">
         <is>
-          <t>69ca1572e3c5910014470e51</t>
+          <t>6a4f2a4523614b00135a6835</t>
         </is>
       </c>
       <c r="N676" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca1572e3c5910014470e51</t>
+          <t>https://superprofile.bio/vig/6a4f2a4523614b00135a6835</t>
         </is>
       </c>
       <c r="O676" s="17" t="inlineStr">
@@ -49594,22 +49594,22 @@
       </c>
       <c r="B677" s="20" t="inlineStr">
         <is>
-          <t>6a364acc4cf49e001251bd8d</t>
+          <t>69c5265e2203a70013a81621</t>
         </is>
       </c>
       <c r="C677" s="20" t="inlineStr">
         <is>
-          <t>vishaltradingx</t>
+          <t>Haresh9504</t>
         </is>
       </c>
       <c r="D677" s="19" t="inlineStr">
         <is>
-          <t>vishalgupta992005@gmail.com</t>
+          <t>hareshbhata5623@gmail.com</t>
         </is>
       </c>
       <c r="E677" s="19" t="inlineStr">
         <is>
-          <t>8882180982</t>
+          <t>7046653069</t>
         </is>
       </c>
       <c r="F677" s="19" t="inlineStr">
@@ -49619,7 +49619,7 @@
       </c>
       <c r="G677" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H677" s="19" t="inlineStr">
@@ -49628,25 +49628,25 @@
         </is>
       </c>
       <c r="I677" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J677" s="21" t="n">
-        <v>1411</v>
+        <v>1892</v>
       </c>
       <c r="K677" s="21" t="n">
-        <v>4233</v>
+        <v>4256</v>
       </c>
       <c r="L677" s="22" t="n">
-        <v>1411</v>
+        <v>2364</v>
       </c>
       <c r="M677" s="19" t="inlineStr">
         <is>
-          <t>6a95d78d71d63e00139088dc</t>
+          <t>69ca1572e3c5910014470e51</t>
         </is>
       </c>
       <c r="N677" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a95d78d71d63e00139088dc</t>
+          <t>https://superprofile.bio/vig/69ca1572e3c5910014470e51</t>
         </is>
       </c>
       <c r="O677" s="24" t="inlineStr">
@@ -49666,22 +49666,22 @@
       </c>
       <c r="B678" s="13" t="inlineStr">
         <is>
-          <t>68496d1b267f07001316fae2</t>
+          <t>6a364acc4cf49e001251bd8d</t>
         </is>
       </c>
       <c r="C678" s="13" t="inlineStr">
         <is>
-          <t>Harsh3320</t>
+          <t>vishaltradingx</t>
         </is>
       </c>
       <c r="D678" s="12" t="inlineStr">
         <is>
-          <t>harshchhura1998@gmail.com</t>
+          <t>vishalgupta992005@gmail.com</t>
         </is>
       </c>
       <c r="E678" s="12" t="inlineStr">
         <is>
-          <t>9140171059</t>
+          <t>8882180982</t>
         </is>
       </c>
       <c r="F678" s="12" t="inlineStr">
@@ -49691,34 +49691,34 @@
       </c>
       <c r="G678" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H678" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I678" s="13" t="n">
         <v>3</v>
       </c>
       <c r="J678" s="14" t="n">
-        <v>1695</v>
+        <v>1411</v>
       </c>
       <c r="K678" s="14" t="n">
-        <v>4189</v>
+        <v>4233</v>
       </c>
       <c r="L678" s="15" t="n">
-        <v>2096</v>
+        <v>1411</v>
       </c>
       <c r="M678" s="12" t="inlineStr">
         <is>
-          <t>695779059b6b5d00139242b9</t>
+          <t>6a95d78d71d63e00139088dc</t>
         </is>
       </c>
       <c r="N678" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/695779059b6b5d00139242b9</t>
+          <t>https://superprofile.bio/vig/6a95d78d71d63e00139088dc</t>
         </is>
       </c>
       <c r="O678" s="17" t="inlineStr">
@@ -49738,22 +49738,22 @@
       </c>
       <c r="B679" s="20" t="inlineStr">
         <is>
-          <t>63398a142e52d546d6af08e9</t>
+          <t>68496d1b267f07001316fae2</t>
         </is>
       </c>
       <c r="C679" s="20" t="inlineStr">
         <is>
-          <t>tigerstrading</t>
+          <t>Harsh3320</t>
         </is>
       </c>
       <c r="D679" s="19" t="inlineStr">
         <is>
-          <t>tigertrading921@gmail.com</t>
+          <t>harshchhura1998@gmail.com</t>
         </is>
       </c>
       <c r="E679" s="19" t="inlineStr">
         <is>
-          <t>9209860503</t>
+          <t>9140171059</t>
         </is>
       </c>
       <c r="F679" s="19" t="inlineStr">
@@ -49768,29 +49768,29 @@
       </c>
       <c r="H679" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I679" s="20" t="n">
         <v>3</v>
       </c>
       <c r="J679" s="21" t="n">
-        <v>1124</v>
+        <v>1695</v>
       </c>
       <c r="K679" s="21" t="n">
-        <v>4072</v>
+        <v>4189</v>
       </c>
       <c r="L679" s="22" t="n">
-        <v>1591</v>
+        <v>2096</v>
       </c>
       <c r="M679" s="19" t="inlineStr">
         <is>
-          <t>6976addf599433001336b54b</t>
+          <t>695779059b6b5d00139242b9</t>
         </is>
       </c>
       <c r="N679" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6976addf599433001336b54b</t>
+          <t>https://superprofile.bio/vig/695779059b6b5d00139242b9</t>
         </is>
       </c>
       <c r="O679" s="24" t="inlineStr">
@@ -49810,22 +49810,22 @@
       </c>
       <c r="B680" s="13" t="inlineStr">
         <is>
-          <t>65323a8ded5efe001e1583c6</t>
+          <t>63398a142e52d546d6af08e9</t>
         </is>
       </c>
       <c r="C680" s="13" t="inlineStr">
         <is>
-          <t>stocksvedaofficial</t>
+          <t>tigerstrading</t>
         </is>
       </c>
       <c r="D680" s="12" t="inlineStr">
         <is>
-          <t>rajeshk4356@gmail.com</t>
+          <t>tigertrading921@gmail.com</t>
         </is>
       </c>
       <c r="E680" s="12" t="inlineStr">
         <is>
-          <t>9914773105</t>
+          <t>9209860503</t>
         </is>
       </c>
       <c r="F680" s="12" t="inlineStr">
@@ -49835,34 +49835,34 @@
       </c>
       <c r="G680" s="12" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H680" s="12" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="H680" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="I680" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J680" s="14" t="n">
-        <v>4050</v>
+        <v>1124</v>
       </c>
       <c r="K680" s="14" t="n">
-        <v>4050</v>
+        <v>4072</v>
       </c>
       <c r="L680" s="15" t="n">
-        <v>4050</v>
+        <v>1591</v>
       </c>
       <c r="M680" s="12" t="inlineStr">
         <is>
-          <t>69c397a2c716fb0013012df1</t>
+          <t>6976addf599433001336b54b</t>
         </is>
       </c>
       <c r="N680" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c397a2c716fb0013012df1</t>
+          <t>https://superprofile.bio/vig/6976addf599433001336b54b</t>
         </is>
       </c>
       <c r="O680" s="17" t="inlineStr">
@@ -49882,22 +49882,22 @@
       </c>
       <c r="B681" s="20" t="inlineStr">
         <is>
-          <t>6550fb1348d70d0a6565e5d3</t>
+          <t>65323a8ded5efe001e1583c6</t>
         </is>
       </c>
       <c r="C681" s="20" t="inlineStr">
         <is>
-          <t>vibhor-aw</t>
+          <t>stocksvedaofficial</t>
         </is>
       </c>
       <c r="D681" s="19" t="inlineStr">
         <is>
-          <t>vibhor.tomar@gmail.com</t>
+          <t>rajeshk4356@gmail.com</t>
         </is>
       </c>
       <c r="E681" s="19" t="inlineStr">
         <is>
-          <t>9986680598</t>
+          <t>9914773105</t>
         </is>
       </c>
       <c r="F681" s="19" t="inlineStr">
@@ -49907,34 +49907,34 @@
       </c>
       <c r="G681" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H681" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I681" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J681" s="21" t="n">
-        <v>1799</v>
+        <v>4050</v>
       </c>
       <c r="K681" s="21" t="n">
-        <v>4048</v>
+        <v>4050</v>
       </c>
       <c r="L681" s="22" t="n">
-        <v>2249</v>
+        <v>4050</v>
       </c>
       <c r="M681" s="19" t="inlineStr">
         <is>
-          <t>69db7be277163000147b374b</t>
+          <t>69c397a2c716fb0013012df1</t>
         </is>
       </c>
       <c r="N681" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69db7be277163000147b374b</t>
+          <t>https://superprofile.bio/vig/69c397a2c716fb0013012df1</t>
         </is>
       </c>
       <c r="O681" s="24" t="inlineStr">
@@ -49954,22 +49954,22 @@
       </c>
       <c r="B682" s="13" t="inlineStr">
         <is>
-          <t>64a1753cab80790020aadcfb</t>
+          <t>6550fb1348d70d0a6565e5d3</t>
         </is>
       </c>
       <c r="C682" s="13" t="inlineStr">
         <is>
-          <t>Gourav2696</t>
+          <t>vibhor-aw</t>
         </is>
       </c>
       <c r="D682" s="12" t="inlineStr">
         <is>
-          <t>gouravdangi830@gmail.com</t>
+          <t>vibhor.tomar@gmail.com</t>
         </is>
       </c>
       <c r="E682" s="12" t="inlineStr">
         <is>
-          <t>9340549395</t>
+          <t>9986680598</t>
         </is>
       </c>
       <c r="F682" s="12" t="inlineStr">
@@ -49979,34 +49979,34 @@
       </c>
       <c r="G682" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H682" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I682" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J682" s="14" t="n">
-        <v>1251</v>
+        <v>1799</v>
       </c>
       <c r="K682" s="14" t="n">
-        <v>4041</v>
+        <v>4048</v>
       </c>
       <c r="L682" s="15" t="n">
-        <v>1539</v>
+        <v>2249</v>
       </c>
       <c r="M682" s="12" t="inlineStr">
         <is>
-          <t>6a463f963e42370013afb7f9</t>
+          <t>69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="N682" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a463f963e42370013afb7f9</t>
+          <t>https://superprofile.bio/vig/69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="O682" s="17" t="inlineStr">
@@ -50026,22 +50026,22 @@
       </c>
       <c r="B683" s="20" t="inlineStr">
         <is>
-          <t>63257ee60a46af3e6e681d38</t>
+          <t>64a1753cab80790020aadcfb</t>
         </is>
       </c>
       <c r="C683" s="20" t="inlineStr">
         <is>
-          <t>tradelikemantra</t>
+          <t>Gourav2696</t>
         </is>
       </c>
       <c r="D683" s="19" t="inlineStr">
         <is>
-          <t>kunwarvishal241@gmail.com</t>
+          <t>gouravdangi830@gmail.com</t>
         </is>
       </c>
       <c r="E683" s="19" t="inlineStr">
         <is>
-          <t>8827370474</t>
+          <t>9340549395</t>
         </is>
       </c>
       <c r="F683" s="19" t="inlineStr">
@@ -50056,29 +50056,29 @@
       </c>
       <c r="H683" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I683" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J683" s="21" t="n">
-        <v>2013</v>
+        <v>1251</v>
       </c>
       <c r="K683" s="21" t="n">
-        <v>4014</v>
+        <v>4041</v>
       </c>
       <c r="L683" s="22" t="n">
-        <v>2013</v>
+        <v>1539</v>
       </c>
       <c r="M683" s="19" t="inlineStr">
         <is>
-          <t>632582d30a46af3e6e6822f1</t>
+          <t>6a463f963e42370013afb7f9</t>
         </is>
       </c>
       <c r="N683" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/632582d30a46af3e6e6822f1</t>
+          <t>https://superprofile.bio/vig/6a463f963e42370013afb7f9</t>
         </is>
       </c>
       <c r="O683" s="24" t="inlineStr">
@@ -50098,22 +50098,22 @@
       </c>
       <c r="B684" s="13" t="inlineStr">
         <is>
-          <t>65dedb00c9a3280013f2b031</t>
+          <t>63257ee60a46af3e6e681d38</t>
         </is>
       </c>
       <c r="C684" s="13" t="inlineStr">
         <is>
-          <t>rahulhans</t>
+          <t>tradelikemantra</t>
         </is>
       </c>
       <c r="D684" s="12" t="inlineStr">
         <is>
-          <t>rahulhns41@gmail.com</t>
+          <t>kunwarvishal241@gmail.com</t>
         </is>
       </c>
       <c r="E684" s="12" t="inlineStr">
         <is>
-          <t>9138601433</t>
+          <t>8827370474</t>
         </is>
       </c>
       <c r="F684" s="12" t="inlineStr">
@@ -50132,25 +50132,25 @@
         </is>
       </c>
       <c r="I684" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J684" s="14" t="n">
-        <v>1141</v>
+        <v>2013</v>
       </c>
       <c r="K684" s="14" t="n">
-        <v>3993</v>
+        <v>4014</v>
       </c>
       <c r="L684" s="15" t="n">
-        <v>1426</v>
+        <v>2013</v>
       </c>
       <c r="M684" s="12" t="inlineStr">
         <is>
-          <t>691966f3892ce60013fb6617</t>
+          <t>632582d30a46af3e6e6822f1</t>
         </is>
       </c>
       <c r="N684" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/691966f3892ce60013fb6617</t>
+          <t>https://superprofile.bio/vig/632582d30a46af3e6e6822f1</t>
         </is>
       </c>
       <c r="O684" s="17" t="inlineStr">
@@ -50170,22 +50170,22 @@
       </c>
       <c r="B685" s="20" t="inlineStr">
         <is>
-          <t>64773578c6f07c0020e42d96</t>
+          <t>65dedb00c9a3280013f2b031</t>
         </is>
       </c>
       <c r="C685" s="20" t="inlineStr">
         <is>
-          <t>MVSTOCKK</t>
+          <t>rahulhans</t>
         </is>
       </c>
       <c r="D685" s="19" t="inlineStr">
         <is>
-          <t>mmmphasis18@gmail.com</t>
+          <t>rahulhns41@gmail.com</t>
         </is>
       </c>
       <c r="E685" s="19" t="inlineStr">
         <is>
-          <t>9601677233</t>
+          <t>9138601433</t>
         </is>
       </c>
       <c r="F685" s="19" t="inlineStr">
@@ -50195,34 +50195,34 @@
       </c>
       <c r="G685" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H685" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I685" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J685" s="21" t="n">
-        <v>3952</v>
+        <v>1141</v>
       </c>
       <c r="K685" s="21" t="n">
-        <v>3952</v>
+        <v>3993</v>
       </c>
       <c r="L685" s="22" t="n">
-        <v>3952</v>
+        <v>1426</v>
       </c>
       <c r="M685" s="19" t="inlineStr">
         <is>
-          <t>64783e3e4c76b10020ea2fb0</t>
+          <t>691966f3892ce60013fb6617</t>
         </is>
       </c>
       <c r="N685" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64783e3e4c76b10020ea2fb0</t>
+          <t>https://superprofile.bio/vig/691966f3892ce60013fb6617</t>
         </is>
       </c>
       <c r="O685" s="24" t="inlineStr">
@@ -50242,22 +50242,22 @@
       </c>
       <c r="B686" s="13" t="inlineStr">
         <is>
-          <t>68398bfb4039280013cfc3f9</t>
+          <t>64773578c6f07c0020e42d96</t>
         </is>
       </c>
       <c r="C686" s="13" t="inlineStr">
         <is>
-          <t>ebookvip</t>
+          <t>MVSTOCKK</t>
         </is>
       </c>
       <c r="D686" s="12" t="inlineStr">
         <is>
-          <t>sarangtilekar02@gmail.com</t>
+          <t>mmmphasis18@gmail.com</t>
         </is>
       </c>
       <c r="E686" s="12" t="inlineStr">
         <is>
-          <t>7219594765</t>
+          <t>9601677233</t>
         </is>
       </c>
       <c r="F686" s="12" t="inlineStr">
@@ -50267,34 +50267,34 @@
       </c>
       <c r="G686" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H686" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I686" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J686" s="14" t="n">
-        <v>1958</v>
+        <v>3952</v>
       </c>
       <c r="K686" s="14" t="n">
-        <v>3918</v>
+        <v>3952</v>
       </c>
       <c r="L686" s="15" t="n">
-        <v>1959</v>
+        <v>3952</v>
       </c>
       <c r="M686" s="12" t="inlineStr">
         <is>
-          <t>6a4132a346bff6001346419f</t>
+          <t>64783e3e4c76b10020ea2fb0</t>
         </is>
       </c>
       <c r="N686" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4132a346bff6001346419f</t>
+          <t>https://superprofile.bio/vig/64783e3e4c76b10020ea2fb0</t>
         </is>
       </c>
       <c r="O686" s="17" t="inlineStr">
@@ -50314,22 +50314,22 @@
       </c>
       <c r="B687" s="20" t="inlineStr">
         <is>
-          <t>67933de51dcd31001388e565</t>
+          <t>68398bfb4039280013cfc3f9</t>
         </is>
       </c>
       <c r="C687" s="20" t="inlineStr">
         <is>
-          <t>asuraxs</t>
+          <t>ebookvip</t>
         </is>
       </c>
       <c r="D687" s="19" t="inlineStr">
         <is>
-          <t>l3150akhan@gmail.com</t>
+          <t>sarangtilekar02@gmail.com</t>
         </is>
       </c>
       <c r="E687" s="19" t="inlineStr">
         <is>
-          <t>8958504836</t>
+          <t>7219594765</t>
         </is>
       </c>
       <c r="F687" s="19" t="inlineStr">
@@ -50339,34 +50339,34 @@
       </c>
       <c r="G687" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H687" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I687" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J687" s="21" t="n">
-        <v>1242</v>
+        <v>1958</v>
       </c>
       <c r="K687" s="21" t="n">
-        <v>3911</v>
+        <v>3918</v>
       </c>
       <c r="L687" s="22" t="n">
-        <v>1536</v>
+        <v>1959</v>
       </c>
       <c r="M687" s="19" t="inlineStr">
         <is>
-          <t>68ce2d8badc9cb0013079773</t>
+          <t>6a4132a346bff6001346419f</t>
         </is>
       </c>
       <c r="N687" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68ce2d8badc9cb0013079773</t>
+          <t>https://superprofile.bio/vig/6a4132a346bff6001346419f</t>
         </is>
       </c>
       <c r="O687" s="24" t="inlineStr">
@@ -50386,22 +50386,22 @@
       </c>
       <c r="B688" s="13" t="inlineStr">
         <is>
-          <t>6184db07e7713d065649d3e1</t>
+          <t>67933de51dcd31001388e565</t>
         </is>
       </c>
       <c r="C688" s="13" t="inlineStr">
         <is>
-          <t>jayneshkasliwal</t>
+          <t>asuraxs</t>
         </is>
       </c>
       <c r="D688" s="12" t="inlineStr">
         <is>
-          <t>jayneshkasliwal1@gmail.com</t>
+          <t>l3150akhan@gmail.com</t>
         </is>
       </c>
       <c r="E688" s="12" t="inlineStr">
         <is>
-          <t>7674007938</t>
+          <t>8958504836</t>
         </is>
       </c>
       <c r="F688" s="12" t="inlineStr">
@@ -50416,29 +50416,29 @@
       </c>
       <c r="H688" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I688" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J688" s="14" t="n">
-        <v>3858</v>
+        <v>1242</v>
       </c>
       <c r="K688" s="14" t="n">
-        <v>3858</v>
+        <v>3911</v>
       </c>
       <c r="L688" s="15" t="n">
-        <v>3858</v>
+        <v>1536</v>
       </c>
       <c r="M688" s="12" t="inlineStr">
         <is>
-          <t>683c0af42f436800130fedf0</t>
+          <t>68ce2d8badc9cb0013079773</t>
         </is>
       </c>
       <c r="N688" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/683c0af42f436800130fedf0</t>
+          <t>https://superprofile.bio/vig/68ce2d8badc9cb0013079773</t>
         </is>
       </c>
       <c r="O688" s="17" t="inlineStr">
@@ -50458,22 +50458,22 @@
       </c>
       <c r="B689" s="20" t="inlineStr">
         <is>
-          <t>67b9dd1184fb2700139c9e20</t>
+          <t>6184db07e7713d065649d3e1</t>
         </is>
       </c>
       <c r="C689" s="20" t="inlineStr">
         <is>
-          <t>vippremium1</t>
+          <t>jayneshkasliwal</t>
         </is>
       </c>
       <c r="D689" s="19" t="inlineStr">
         <is>
-          <t>bhairwaramkesh445@gmail.com</t>
+          <t>jayneshkasliwal1@gmail.com</t>
         </is>
       </c>
       <c r="E689" s="19" t="inlineStr">
         <is>
-          <t>7339731575</t>
+          <t>7674007938</t>
         </is>
       </c>
       <c r="F689" s="19" t="inlineStr">
@@ -50483,34 +50483,34 @@
       </c>
       <c r="G689" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H689" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I689" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J689" s="21" t="n">
-        <v>3834</v>
+        <v>3858</v>
       </c>
       <c r="K689" s="21" t="n">
-        <v>3834</v>
+        <v>3858</v>
       </c>
       <c r="L689" s="22" t="n">
-        <v>3834</v>
+        <v>3858</v>
       </c>
       <c r="M689" s="19" t="inlineStr">
         <is>
-          <t>68bdc091613da1001336d6fa</t>
+          <t>683c0af42f436800130fedf0</t>
         </is>
       </c>
       <c r="N689" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68bdc091613da1001336d6fa</t>
+          <t>https://superprofile.bio/vig/683c0af42f436800130fedf0</t>
         </is>
       </c>
       <c r="O689" s="24" t="inlineStr">
@@ -50530,22 +50530,22 @@
       </c>
       <c r="B690" s="13" t="inlineStr">
         <is>
-          <t>653d2bce423d4e001ee4dd1d</t>
+          <t>67b9dd1184fb2700139c9e20</t>
         </is>
       </c>
       <c r="C690" s="13" t="inlineStr">
         <is>
-          <t>cainvestor</t>
+          <t>vippremium1</t>
         </is>
       </c>
       <c r="D690" s="12" t="inlineStr">
         <is>
-          <t>multibaggerinvestor11@gmail.com</t>
+          <t>bhairwaramkesh445@gmail.com</t>
         </is>
       </c>
       <c r="E690" s="12" t="inlineStr">
         <is>
-          <t>8830932954</t>
+          <t>7339731575</t>
         </is>
       </c>
       <c r="F690" s="12" t="inlineStr">
@@ -50555,34 +50555,34 @@
       </c>
       <c r="G690" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H690" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I690" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J690" s="14" t="n">
-        <v>1904</v>
+        <v>3834</v>
       </c>
       <c r="K690" s="14" t="n">
-        <v>3808</v>
+        <v>3834</v>
       </c>
       <c r="L690" s="15" t="n">
-        <v>1904</v>
+        <v>3834</v>
       </c>
       <c r="M690" s="12" t="inlineStr">
         <is>
-          <t>6794368b20a3e90013310b49</t>
+          <t>68bdc091613da1001336d6fa</t>
         </is>
       </c>
       <c r="N690" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6794368b20a3e90013310b49</t>
+          <t>https://superprofile.bio/vig/68bdc091613da1001336d6fa</t>
         </is>
       </c>
       <c r="O690" s="17" t="inlineStr">
@@ -50602,22 +50602,22 @@
       </c>
       <c r="B691" s="20" t="inlineStr">
         <is>
-          <t>6346a07d2e23523c0ba15601</t>
+          <t>653d2bce423d4e001ee4dd1d</t>
         </is>
       </c>
       <c r="C691" s="20" t="inlineStr">
         <is>
-          <t>smartmcx</t>
+          <t>cainvestor</t>
         </is>
       </c>
       <c r="D691" s="19" t="inlineStr">
         <is>
-          <t>tradingprofitway@gmail.com</t>
+          <t>multibaggerinvestor11@gmail.com</t>
         </is>
       </c>
       <c r="E691" s="19" t="inlineStr">
         <is>
-          <t>8120940096</t>
+          <t>8830932954</t>
         </is>
       </c>
       <c r="F691" s="19" t="inlineStr">
@@ -50632,29 +50632,29 @@
       </c>
       <c r="H691" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I691" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J691" s="21" t="n">
-        <v>3806</v>
+        <v>1904</v>
       </c>
       <c r="K691" s="21" t="n">
-        <v>3806</v>
+        <v>3808</v>
       </c>
       <c r="L691" s="22" t="n">
-        <v>3806</v>
+        <v>1904</v>
       </c>
       <c r="M691" s="19" t="inlineStr">
         <is>
-          <t>64ae81808c16d0001fb4a7b0</t>
+          <t>6794368b20a3e90013310b49</t>
         </is>
       </c>
       <c r="N691" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64ae81808c16d0001fb4a7b0</t>
+          <t>https://superprofile.bio/vig/6794368b20a3e90013310b49</t>
         </is>
       </c>
       <c r="O691" s="24" t="inlineStr">
@@ -50674,22 +50674,22 @@
       </c>
       <c r="B692" s="13" t="inlineStr">
         <is>
-          <t>68183a34d8071400136f352e</t>
+          <t>6346a07d2e23523c0ba15601</t>
         </is>
       </c>
       <c r="C692" s="13" t="inlineStr">
         <is>
-          <t>slisgod</t>
+          <t>smartmcx</t>
         </is>
       </c>
       <c r="D692" s="12" t="inlineStr">
         <is>
-          <t>sinha0802@gmail.com</t>
+          <t>tradingprofitway@gmail.com</t>
         </is>
       </c>
       <c r="E692" s="12" t="inlineStr">
         <is>
-          <t>9899926451</t>
+          <t>8120940096</t>
         </is>
       </c>
       <c r="F692" s="12" t="inlineStr">
@@ -50699,34 +50699,34 @@
       </c>
       <c r="G692" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H692" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I692" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J692" s="14" t="n">
-        <v>3804</v>
+        <v>3806</v>
       </c>
       <c r="K692" s="14" t="n">
-        <v>3804</v>
+        <v>3806</v>
       </c>
       <c r="L692" s="15" t="n">
-        <v>3804</v>
+        <v>3806</v>
       </c>
       <c r="M692" s="12" t="inlineStr">
         <is>
-          <t>697e0ceef207ab0013d4c2f5</t>
+          <t>64ae81808c16d0001fb4a7b0</t>
         </is>
       </c>
       <c r="N692" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697e0ceef207ab0013d4c2f5</t>
+          <t>https://superprofile.bio/vig/64ae81808c16d0001fb4a7b0</t>
         </is>
       </c>
       <c r="O692" s="17" t="inlineStr">
@@ -50746,22 +50746,22 @@
       </c>
       <c r="B693" s="20" t="inlineStr">
         <is>
-          <t>69157f06e3a0e3001373be01</t>
+          <t>68183a34d8071400136f352e</t>
         </is>
       </c>
       <c r="C693" s="20" t="inlineStr">
         <is>
-          <t>ayushmarda</t>
+          <t>slisgod</t>
         </is>
       </c>
       <c r="D693" s="19" t="inlineStr">
         <is>
-          <t>ayushmarda000@gmail.com</t>
+          <t>sinha0802@gmail.com</t>
         </is>
       </c>
       <c r="E693" s="19" t="inlineStr">
         <is>
-          <t>8007790099</t>
+          <t>9899926451</t>
         </is>
       </c>
       <c r="F693" s="19" t="inlineStr">
@@ -50771,34 +50771,34 @@
       </c>
       <c r="G693" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H693" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I693" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J693" s="21" t="n">
-        <v>1259</v>
+        <v>3804</v>
       </c>
       <c r="K693" s="21" t="n">
-        <v>3777</v>
+        <v>3804</v>
       </c>
       <c r="L693" s="22" t="n">
-        <v>1259</v>
+        <v>3804</v>
       </c>
       <c r="M693" s="19" t="inlineStr">
         <is>
-          <t>692e8f7a0454370012d339a1</t>
+          <t>697e0ceef207ab0013d4c2f5</t>
         </is>
       </c>
       <c r="N693" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692e8f7a0454370012d339a1</t>
+          <t>https://superprofile.bio/vig/697e0ceef207ab0013d4c2f5</t>
         </is>
       </c>
       <c r="O693" s="24" t="inlineStr">
@@ -50818,22 +50818,22 @@
       </c>
       <c r="B694" s="13" t="inlineStr">
         <is>
-          <t>69830243c90cd7001368eaad</t>
+          <t>69157f06e3a0e3001373be01</t>
         </is>
       </c>
       <c r="C694" s="13" t="inlineStr">
         <is>
-          <t>coachrahulkharbanda</t>
+          <t>ayushmarda</t>
         </is>
       </c>
       <c r="D694" s="12" t="inlineStr">
         <is>
-          <t>contactrahulkharbanda@gmail.com</t>
+          <t>ayushmarda000@gmail.com</t>
         </is>
       </c>
       <c r="E694" s="12" t="inlineStr">
         <is>
-          <t>9891181914</t>
+          <t>8007790099</t>
         </is>
       </c>
       <c r="F694" s="12" t="inlineStr">
@@ -50843,34 +50843,34 @@
       </c>
       <c r="G694" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H694" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I694" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J694" s="14" t="n">
-        <v>3774</v>
+        <v>1259</v>
       </c>
       <c r="K694" s="14" t="n">
-        <v>3774</v>
+        <v>3777</v>
       </c>
       <c r="L694" s="15" t="n">
-        <v>3774</v>
+        <v>1259</v>
       </c>
       <c r="M694" s="12" t="inlineStr">
         <is>
-          <t>6a5b28a846f9d500149d11f9</t>
+          <t>692e8f7a0454370012d339a1</t>
         </is>
       </c>
       <c r="N694" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5b28a846f9d500149d11f9</t>
+          <t>https://superprofile.bio/vig/692e8f7a0454370012d339a1</t>
         </is>
       </c>
       <c r="O694" s="17" t="inlineStr">
@@ -50890,22 +50890,22 @@
       </c>
       <c r="B695" s="20" t="inlineStr">
         <is>
-          <t>645b82c0d3d3c4002092b8d6</t>
+          <t>69830243c90cd7001368eaad</t>
         </is>
       </c>
       <c r="C695" s="20" t="inlineStr">
         <is>
-          <t>niftybanknifty777</t>
+          <t>coachrahulkharbanda</t>
         </is>
       </c>
       <c r="D695" s="19" t="inlineStr">
         <is>
-          <t>devanshsharma999@gmail.com</t>
+          <t>contactrahulkharbanda@gmail.com</t>
         </is>
       </c>
       <c r="E695" s="19" t="inlineStr">
         <is>
-          <t>7302521682</t>
+          <t>9891181914</t>
         </is>
       </c>
       <c r="F695" s="19" t="inlineStr">
@@ -50915,34 +50915,34 @@
       </c>
       <c r="G695" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H695" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I695" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J695" s="21" t="n">
-        <v>3763</v>
+        <v>3774</v>
       </c>
       <c r="K695" s="21" t="n">
-        <v>3763</v>
+        <v>3774</v>
       </c>
       <c r="L695" s="22" t="n">
-        <v>3763</v>
+        <v>3774</v>
       </c>
       <c r="M695" s="19" t="inlineStr">
         <is>
-          <t>660e5fc79e824b0013c602ce</t>
+          <t>6a5b28a846f9d500149d11f9</t>
         </is>
       </c>
       <c r="N695" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/660e5fc79e824b0013c602ce</t>
+          <t>https://superprofile.bio/vig/6a5b28a846f9d500149d11f9</t>
         </is>
       </c>
       <c r="O695" s="24" t="inlineStr">
@@ -50962,22 +50962,22 @@
       </c>
       <c r="B696" s="13" t="inlineStr">
         <is>
-          <t>67cc33d5f2990900135f1213</t>
+          <t>645b82c0d3d3c4002092b8d6</t>
         </is>
       </c>
       <c r="C696" s="13" t="inlineStr">
         <is>
-          <t>tradevixofficial123</t>
+          <t>niftybanknifty777</t>
         </is>
       </c>
       <c r="D696" s="12" t="inlineStr">
         <is>
-          <t>tradewithsandeep8@gmail.com</t>
+          <t>devanshsharma999@gmail.com</t>
         </is>
       </c>
       <c r="E696" s="12" t="inlineStr">
         <is>
-          <t>6367327619</t>
+          <t>7302521682</t>
         </is>
       </c>
       <c r="F696" s="12" t="inlineStr">
@@ -50999,22 +50999,22 @@
         <v>1</v>
       </c>
       <c r="J696" s="14" t="n">
-        <v>3717</v>
+        <v>3763</v>
       </c>
       <c r="K696" s="14" t="n">
-        <v>3717</v>
+        <v>3763</v>
       </c>
       <c r="L696" s="15" t="n">
-        <v>3717</v>
+        <v>3763</v>
       </c>
       <c r="M696" s="12" t="inlineStr">
         <is>
-          <t>67cc69c2f926d700136ec846</t>
+          <t>660e5fc79e824b0013c602ce</t>
         </is>
       </c>
       <c r="N696" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67cc69c2f926d700136ec846</t>
+          <t>https://superprofile.bio/vig/660e5fc79e824b0013c602ce</t>
         </is>
       </c>
       <c r="O696" s="17" t="inlineStr">
@@ -51034,22 +51034,22 @@
       </c>
       <c r="B697" s="20" t="inlineStr">
         <is>
-          <t>67739d2d7eefc3001394e8f2</t>
+          <t>67cc33d5f2990900135f1213</t>
         </is>
       </c>
       <c r="C697" s="20" t="inlineStr">
         <is>
-          <t>o4ohari</t>
+          <t>tradevixofficial123</t>
         </is>
       </c>
       <c r="D697" s="19" t="inlineStr">
         <is>
-          <t>nicholasnelo2017@gmail.com</t>
+          <t>tradewithsandeep8@gmail.com</t>
         </is>
       </c>
       <c r="E697" s="19" t="inlineStr">
         <is>
-          <t>8848943849</t>
+          <t>6367327619</t>
         </is>
       </c>
       <c r="F697" s="19" t="inlineStr">
@@ -51059,34 +51059,34 @@
       </c>
       <c r="G697" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H697" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I697" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J697" s="21" t="n">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="K697" s="21" t="n">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="L697" s="22" t="n">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="M697" s="19" t="inlineStr">
         <is>
-          <t>6a51e8876879160013d44c08</t>
+          <t>67cc69c2f926d700136ec846</t>
         </is>
       </c>
       <c r="N697" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a51e8876879160013d44c08</t>
+          <t>https://superprofile.bio/vig/67cc69c2f926d700136ec846</t>
         </is>
       </c>
       <c r="O697" s="24" t="inlineStr">
@@ -51106,22 +51106,22 @@
       </c>
       <c r="B698" s="13" t="inlineStr">
         <is>
-          <t>650ff72bf8c83a001d33ca7c</t>
+          <t>67739d2d7eefc3001394e8f2</t>
         </is>
       </c>
       <c r="C698" s="13" t="inlineStr">
         <is>
-          <t>optionmaster02</t>
+          <t>o4ohari</t>
         </is>
       </c>
       <c r="D698" s="12" t="inlineStr">
         <is>
-          <t>kaushikmekdar@gmail.com</t>
+          <t>nicholasnelo2017@gmail.com</t>
         </is>
       </c>
       <c r="E698" s="12" t="inlineStr">
         <is>
-          <t>9599339897</t>
+          <t>8848943849</t>
         </is>
       </c>
       <c r="F698" s="12" t="inlineStr">
@@ -51131,34 +51131,34 @@
       </c>
       <c r="G698" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H698" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I698" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J698" s="14" t="n">
-        <v>1952</v>
+        <v>3716</v>
       </c>
       <c r="K698" s="14" t="n">
-        <v>3709</v>
+        <v>3716</v>
       </c>
       <c r="L698" s="15" t="n">
-        <v>1952</v>
+        <v>3716</v>
       </c>
       <c r="M698" s="12" t="inlineStr">
         <is>
-          <t>69ca0c4617aeb10013e7d804</t>
+          <t>6a51e8876879160013d44c08</t>
         </is>
       </c>
       <c r="N698" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca0c4617aeb10013e7d804</t>
+          <t>https://superprofile.bio/vig/6a51e8876879160013d44c08</t>
         </is>
       </c>
       <c r="O698" s="17" t="inlineStr">
@@ -51178,59 +51178,59 @@
       </c>
       <c r="B699" s="20" t="inlineStr">
         <is>
-          <t>67ad63172703020013099918</t>
+          <t>650ff72bf8c83a001d33ca7c</t>
         </is>
       </c>
       <c r="C699" s="20" t="inlineStr">
         <is>
-          <t>stockwithshreyash</t>
+          <t>optionmaster02</t>
         </is>
       </c>
       <c r="D699" s="19" t="inlineStr">
         <is>
-          <t>shreyashphanase@gmail.com</t>
+          <t>kaushikmekdar@gmail.com</t>
         </is>
       </c>
       <c r="E699" s="19" t="inlineStr">
         <is>
-          <t>7066533150</t>
+          <t>9599339897</t>
         </is>
       </c>
       <c r="F699" s="19" t="inlineStr">
         <is>
-          <t>Kkabir John</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G699" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H699" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I699" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J699" s="21" t="n">
-        <v>1410</v>
+        <v>1952</v>
       </c>
       <c r="K699" s="21" t="n">
-        <v>3666</v>
+        <v>3709</v>
       </c>
       <c r="L699" s="22" t="n">
-        <v>2256</v>
+        <v>1952</v>
       </c>
       <c r="M699" s="19" t="inlineStr">
         <is>
-          <t>6a6cb50933211a0013f61a2e</t>
+          <t>69ca0c4617aeb10013e7d804</t>
         </is>
       </c>
       <c r="N699" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6cb50933211a0013f61a2e</t>
+          <t>https://superprofile.bio/vig/69ca0c4617aeb10013e7d804</t>
         </is>
       </c>
       <c r="O699" s="24" t="inlineStr">
@@ -51250,59 +51250,59 @@
       </c>
       <c r="B700" s="13" t="inlineStr">
         <is>
-          <t>66d329848007d20013cda7e5</t>
+          <t>67ad63172703020013099918</t>
         </is>
       </c>
       <c r="C700" s="13" t="inlineStr">
         <is>
-          <t>madan21</t>
+          <t>stockwithshreyash</t>
         </is>
       </c>
       <c r="D700" s="12" t="inlineStr">
         <is>
-          <t>madanlal010123@gmail.com</t>
+          <t>shreyashphanase@gmail.com</t>
         </is>
       </c>
       <c r="E700" s="12" t="inlineStr">
         <is>
-          <t>9140204389</t>
+          <t>7066533150</t>
         </is>
       </c>
       <c r="F700" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kkabir John</t>
         </is>
       </c>
       <c r="G700" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H700" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I700" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J700" s="14" t="n">
-        <v>3600</v>
+        <v>1410</v>
       </c>
       <c r="K700" s="14" t="n">
-        <v>3600</v>
+        <v>3666</v>
       </c>
       <c r="L700" s="15" t="n">
-        <v>3600</v>
+        <v>2256</v>
       </c>
       <c r="M700" s="12" t="inlineStr">
         <is>
-          <t>6a5737d04ca9e200136e06b8</t>
+          <t>6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="N700" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5737d04ca9e200136e06b8</t>
+          <t>https://superprofile.bio/vig/6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="O700" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 10:40:46 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 12:38:21 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 12:38:21 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 14:07:56 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 14:07:56 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 15:49:41 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 15:49:41 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 17:41:07 | Daily Audits Logged: 13</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-11 17:41:07 | Daily Audits Logged: 13</t>
+          <t>Generated On: 2026-09-11 18:47:11 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹51,011,186.00</t>
+          <t>₹51,013,541.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -866,6 +866,24 @@
         <v>3482918</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Logged &amp; Deduplicated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Logged &amp; Deduplicated</t>
         </is>
@@ -28714,22 +28732,22 @@
       </c>
       <c r="B387" s="20" t="inlineStr">
         <is>
-          <t>691abf335bc13900136c119c</t>
+          <t>62115e4a6bd738258707c0e9</t>
         </is>
       </c>
       <c r="C387" s="20" t="inlineStr">
         <is>
-          <t>hami7778</t>
+          <t>aditya</t>
         </is>
       </c>
       <c r="D387" s="19" t="inlineStr">
         <is>
-          <t>monuvarma86908@gmail.com</t>
+          <t>imavschoudhary@gmail.com</t>
         </is>
       </c>
       <c r="E387" s="19" t="inlineStr">
         <is>
-          <t>6378701766</t>
+          <t>9717115749</t>
         </is>
       </c>
       <c r="F387" s="19" t="inlineStr">
@@ -28739,34 +28757,34 @@
       </c>
       <c r="G387" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H387" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I387" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J387" s="21" t="n">
-        <v>1881</v>
+        <v>2355</v>
       </c>
       <c r="K387" s="21" t="n">
-        <v>23706</v>
+        <v>24075</v>
       </c>
       <c r="L387" s="22" t="n">
-        <v>5268</v>
+        <v>4379</v>
       </c>
       <c r="M387" s="19" t="inlineStr">
         <is>
-          <t>691c16bc5dd8b600132d7867</t>
+          <t>6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="N387" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/691c16bc5dd8b600132d7867</t>
+          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
         </is>
       </c>
       <c r="O387" s="24" t="inlineStr">
@@ -28786,22 +28804,22 @@
       </c>
       <c r="B388" s="13" t="inlineStr">
         <is>
-          <t>69b3c1dd02fef30013b6cf7d</t>
+          <t>691abf335bc13900136c119c</t>
         </is>
       </c>
       <c r="C388" s="13" t="inlineStr">
         <is>
-          <t>gravitasedge</t>
+          <t>hami7778</t>
         </is>
       </c>
       <c r="D388" s="12" t="inlineStr">
         <is>
-          <t>gravitasedgeconsultant@gmail.com</t>
+          <t>monuvarma86908@gmail.com</t>
         </is>
       </c>
       <c r="E388" s="12" t="inlineStr">
         <is>
-          <t>9999774266</t>
+          <t>6378701766</t>
         </is>
       </c>
       <c r="F388" s="12" t="inlineStr">
@@ -28811,7 +28829,7 @@
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H388" s="12" t="inlineStr">
@@ -28820,25 +28838,25 @@
         </is>
       </c>
       <c r="I388" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J388" s="14" t="n">
-        <v>3597</v>
+        <v>1881</v>
       </c>
       <c r="K388" s="14" t="n">
-        <v>23527</v>
+        <v>23706</v>
       </c>
       <c r="L388" s="15" t="n">
-        <v>6890</v>
+        <v>5268</v>
       </c>
       <c r="M388" s="12" t="inlineStr">
         <is>
-          <t>69f5c5a44741f60013d5059c</t>
+          <t>691c16bc5dd8b600132d7867</t>
         </is>
       </c>
       <c r="N388" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f5c5a44741f60013d5059c</t>
+          <t>https://superprofile.bio/vig/691c16bc5dd8b600132d7867</t>
         </is>
       </c>
       <c r="O388" s="17" t="inlineStr">
@@ -28858,22 +28876,22 @@
       </c>
       <c r="B389" s="20" t="inlineStr">
         <is>
-          <t>65c3663e3dcad5001eb93f97</t>
+          <t>69b3c1dd02fef30013b6cf7d</t>
         </is>
       </c>
       <c r="C389" s="20" t="inlineStr">
         <is>
-          <t>shhelja</t>
+          <t>gravitasedge</t>
         </is>
       </c>
       <c r="D389" s="19" t="inlineStr">
         <is>
-          <t>artbyshelja@gmail.com</t>
+          <t>gravitasedgeconsultant@gmail.com</t>
         </is>
       </c>
       <c r="E389" s="19" t="inlineStr">
         <is>
-          <t>9891233375</t>
+          <t>9999774266</t>
         </is>
       </c>
       <c r="F389" s="19" t="inlineStr">
@@ -28883,34 +28901,34 @@
       </c>
       <c r="G389" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H389" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I389" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J389" s="21" t="n">
-        <v>11763</v>
+        <v>3597</v>
       </c>
       <c r="K389" s="21" t="n">
-        <v>23526</v>
+        <v>23527</v>
       </c>
       <c r="L389" s="22" t="n">
-        <v>11763</v>
+        <v>6890</v>
       </c>
       <c r="M389" s="19" t="inlineStr">
         <is>
-          <t>68c056c3fe96b40013738bc6</t>
+          <t>69f5c5a44741f60013d5059c</t>
         </is>
       </c>
       <c r="N389" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c056c3fe96b40013738bc6</t>
+          <t>https://superprofile.bio/vig/69f5c5a44741f60013d5059c</t>
         </is>
       </c>
       <c r="O389" s="24" t="inlineStr">
@@ -28930,22 +28948,22 @@
       </c>
       <c r="B390" s="13" t="inlineStr">
         <is>
-          <t>667c078d8a21550013342f58</t>
+          <t>65c3663e3dcad5001eb93f97</t>
         </is>
       </c>
       <c r="C390" s="13" t="inlineStr">
         <is>
-          <t>Piyush5796</t>
+          <t>shhelja</t>
         </is>
       </c>
       <c r="D390" s="12" t="inlineStr">
         <is>
-          <t>piyushkumarpmiisc2022@gmail.com</t>
+          <t>artbyshelja@gmail.com</t>
         </is>
       </c>
       <c r="E390" s="12" t="inlineStr">
         <is>
-          <t>6202485259</t>
+          <t>9891233375</t>
         </is>
       </c>
       <c r="F390" s="12" t="inlineStr">
@@ -28955,34 +28973,34 @@
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H390" s="12" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H390" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I390" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J390" s="14" t="n">
-        <v>9409</v>
+        <v>11763</v>
       </c>
       <c r="K390" s="14" t="n">
-        <v>23523</v>
+        <v>23526</v>
       </c>
       <c r="L390" s="15" t="n">
-        <v>14114</v>
+        <v>11763</v>
       </c>
       <c r="M390" s="12" t="inlineStr">
         <is>
-          <t>684d5a341e8e5a0013e23f5e</t>
+          <t>68c056c3fe96b40013738bc6</t>
         </is>
       </c>
       <c r="N390" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/684d5a341e8e5a0013e23f5e</t>
+          <t>https://superprofile.bio/vig/68c056c3fe96b40013738bc6</t>
         </is>
       </c>
       <c r="O390" s="17" t="inlineStr">
@@ -29002,22 +29020,22 @@
       </c>
       <c r="B391" s="20" t="inlineStr">
         <is>
-          <t>666576a165fdc20013ba3ce8</t>
+          <t>667c078d8a21550013342f58</t>
         </is>
       </c>
       <c r="C391" s="20" t="inlineStr">
         <is>
-          <t>bullishview</t>
+          <t>Piyush5796</t>
         </is>
       </c>
       <c r="D391" s="19" t="inlineStr">
         <is>
-          <t>chetanchopra012@gmail.com</t>
+          <t>piyushkumarpmiisc2022@gmail.com</t>
         </is>
       </c>
       <c r="E391" s="19" t="inlineStr">
         <is>
-          <t>9664390569</t>
+          <t>6202485259</t>
         </is>
       </c>
       <c r="F391" s="19" t="inlineStr">
@@ -29027,34 +29045,34 @@
       </c>
       <c r="G391" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H391" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I391" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J391" s="21" t="n">
-        <v>8468</v>
+        <v>9409</v>
       </c>
       <c r="K391" s="21" t="n">
-        <v>23192</v>
+        <v>23523</v>
       </c>
       <c r="L391" s="22" t="n">
-        <v>8468</v>
+        <v>14114</v>
       </c>
       <c r="M391" s="19" t="inlineStr">
         <is>
-          <t>68507ed473e5cd00133520c1</t>
+          <t>684d5a341e8e5a0013e23f5e</t>
         </is>
       </c>
       <c r="N391" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68507ed473e5cd00133520c1</t>
+          <t>https://superprofile.bio/vig/684d5a341e8e5a0013e23f5e</t>
         </is>
       </c>
       <c r="O391" s="24" t="inlineStr">
@@ -29074,22 +29092,22 @@
       </c>
       <c r="B392" s="13" t="inlineStr">
         <is>
-          <t>66f153fcbce5f30013159b4a</t>
+          <t>666576a165fdc20013ba3ce8</t>
         </is>
       </c>
       <c r="C392" s="13" t="inlineStr">
         <is>
-          <t>investway</t>
+          <t>bullishview</t>
         </is>
       </c>
       <c r="D392" s="12" t="inlineStr">
         <is>
-          <t>harickstewart@gmail.com</t>
+          <t>chetanchopra012@gmail.com</t>
         </is>
       </c>
       <c r="E392" s="12" t="inlineStr">
         <is>
-          <t>9724245588</t>
+          <t>9664390569</t>
         </is>
       </c>
       <c r="F392" s="12" t="inlineStr">
@@ -29099,34 +29117,34 @@
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H392" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I392" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J392" s="14" t="n">
-        <v>8861</v>
+        <v>8468</v>
       </c>
       <c r="K392" s="14" t="n">
-        <v>22916</v>
+        <v>23192</v>
       </c>
       <c r="L392" s="15" t="n">
-        <v>10117</v>
+        <v>8468</v>
       </c>
       <c r="M392" s="12" t="inlineStr">
         <is>
-          <t>66f26b26befc8e0013688a1f</t>
+          <t>68507ed473e5cd00133520c1</t>
         </is>
       </c>
       <c r="N392" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66f26b26befc8e0013688a1f</t>
+          <t>https://superprofile.bio/vig/68507ed473e5cd00133520c1</t>
         </is>
       </c>
       <c r="O392" s="17" t="inlineStr">
@@ -29146,22 +29164,22 @@
       </c>
       <c r="B393" s="20" t="inlineStr">
         <is>
-          <t>6a0739870374d70013f4a6da</t>
+          <t>66f153fcbce5f30013159b4a</t>
         </is>
       </c>
       <c r="C393" s="20" t="inlineStr">
         <is>
-          <t>algoxofficial</t>
+          <t>investway</t>
         </is>
       </c>
       <c r="D393" s="19" t="inlineStr">
         <is>
-          <t>sayhelloplux@gmail.com</t>
+          <t>harickstewart@gmail.com</t>
         </is>
       </c>
       <c r="E393" s="19" t="inlineStr">
         <is>
-          <t>8529451480</t>
+          <t>9724245588</t>
         </is>
       </c>
       <c r="F393" s="19" t="inlineStr">
@@ -29176,29 +29194,29 @@
       </c>
       <c r="H393" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I393" s="20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J393" s="21" t="n">
-        <v>1031</v>
+        <v>8861</v>
       </c>
       <c r="K393" s="21" t="n">
-        <v>22598</v>
+        <v>22916</v>
       </c>
       <c r="L393" s="22" t="n">
-        <v>6554</v>
+        <v>10117</v>
       </c>
       <c r="M393" s="19" t="inlineStr">
         <is>
-          <t>6a40b76b8552d90013a86043</t>
+          <t>66f26b26befc8e0013688a1f</t>
         </is>
       </c>
       <c r="N393" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
+          <t>https://superprofile.bio/vig/66f26b26befc8e0013688a1f</t>
         </is>
       </c>
       <c r="O393" s="24" t="inlineStr">
@@ -29218,22 +29236,22 @@
       </c>
       <c r="B394" s="13" t="inlineStr">
         <is>
-          <t>687f538e23947700130cd9cc</t>
+          <t>6a0739870374d70013f4a6da</t>
         </is>
       </c>
       <c r="C394" s="13" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>algoxofficial</t>
         </is>
       </c>
       <c r="D394" s="12" t="inlineStr">
         <is>
-          <t>mastermindteam051@gmail.com</t>
+          <t>sayhelloplux@gmail.com</t>
         </is>
       </c>
       <c r="E394" s="12" t="inlineStr">
         <is>
-          <t>9936556941</t>
+          <t>8529451480</t>
         </is>
       </c>
       <c r="F394" s="12" t="inlineStr">
@@ -29243,34 +29261,34 @@
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H394" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I394" s="13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J394" s="14" t="n">
-        <v>2633</v>
+        <v>1031</v>
       </c>
       <c r="K394" s="14" t="n">
-        <v>22504</v>
+        <v>22598</v>
       </c>
       <c r="L394" s="15" t="n">
-        <v>5857</v>
+        <v>6554</v>
       </c>
       <c r="M394" s="12" t="inlineStr">
         <is>
-          <t>697998f47fac9d0013f74dfe</t>
+          <t>6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="N394" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
+          <t>https://superprofile.bio/vig/6a40b76b8552d90013a86043</t>
         </is>
       </c>
       <c r="O394" s="17" t="inlineStr">
@@ -29290,22 +29308,22 @@
       </c>
       <c r="B395" s="20" t="inlineStr">
         <is>
-          <t>63098a19ab5f30156adbd12b</t>
+          <t>687f538e23947700130cd9cc</t>
         </is>
       </c>
       <c r="C395" s="20" t="inlineStr">
         <is>
-          <t>ankitjain1</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="D395" s="19" t="inlineStr">
         <is>
-          <t>ankitjain9590@gmail.com</t>
+          <t>mastermindteam051@gmail.com</t>
         </is>
       </c>
       <c r="E395" s="19" t="inlineStr">
         <is>
-          <t>7004488186</t>
+          <t>9936556941</t>
         </is>
       </c>
       <c r="F395" s="19" t="inlineStr">
@@ -29315,7 +29333,7 @@
       </c>
       <c r="G395" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H395" s="19" t="inlineStr">
@@ -29324,25 +29342,25 @@
         </is>
       </c>
       <c r="I395" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J395" s="21" t="n">
-        <v>2699</v>
+        <v>2633</v>
       </c>
       <c r="K395" s="21" t="n">
-        <v>22494</v>
+        <v>22504</v>
       </c>
       <c r="L395" s="22" t="n">
-        <v>9898</v>
+        <v>5857</v>
       </c>
       <c r="M395" s="19" t="inlineStr">
         <is>
-          <t>69ef37d0844a2100138b0bd0</t>
+          <t>697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="N395" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ef37d0844a2100138b0bd0</t>
+          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="O395" s="24" t="inlineStr">
@@ -29362,22 +29380,22 @@
       </c>
       <c r="B396" s="13" t="inlineStr">
         <is>
-          <t>6527fd70b28945001db6257f</t>
+          <t>63098a19ab5f30156adbd12b</t>
         </is>
       </c>
       <c r="C396" s="13" t="inlineStr">
         <is>
-          <t>stockhotspotkeypad</t>
+          <t>ankitjain1</t>
         </is>
       </c>
       <c r="D396" s="12" t="inlineStr">
         <is>
-          <t>stockhotspotkeypad@gmail.com</t>
+          <t>ankitjain9590@gmail.com</t>
         </is>
       </c>
       <c r="E396" s="12" t="inlineStr">
         <is>
-          <t>7690889673</t>
+          <t>7004488186</t>
         </is>
       </c>
       <c r="F396" s="12" t="inlineStr">
@@ -29387,34 +29405,34 @@
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H396" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I396" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J396" s="14" t="n">
-        <v>14852</v>
+        <v>2699</v>
       </c>
       <c r="K396" s="14" t="n">
-        <v>22422</v>
+        <v>22494</v>
       </c>
       <c r="L396" s="15" t="n">
-        <v>14852</v>
+        <v>9898</v>
       </c>
       <c r="M396" s="12" t="inlineStr">
         <is>
-          <t>6309df1a9a9138163a6a17a0</t>
+          <t>69ef37d0844a2100138b0bd0</t>
         </is>
       </c>
       <c r="N396" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6309df1a9a9138163a6a17a0</t>
+          <t>https://superprofile.bio/vig/69ef37d0844a2100138b0bd0</t>
         </is>
       </c>
       <c r="O396" s="17" t="inlineStr">
@@ -29434,22 +29452,22 @@
       </c>
       <c r="B397" s="20" t="inlineStr">
         <is>
-          <t>64b9e87f61918e00206df90d</t>
+          <t>6527fd70b28945001db6257f</t>
         </is>
       </c>
       <c r="C397" s="20" t="inlineStr">
         <is>
-          <t>zerotoherovipcalls</t>
+          <t>stockhotspotkeypad</t>
         </is>
       </c>
       <c r="D397" s="19" t="inlineStr">
         <is>
-          <t>bhaiajay5168@gmail.com</t>
+          <t>stockhotspotkeypad@gmail.com</t>
         </is>
       </c>
       <c r="E397" s="19" t="inlineStr">
         <is>
-          <t>7023193476</t>
+          <t>7690889673</t>
         </is>
       </c>
       <c r="F397" s="19" t="inlineStr">
@@ -29459,7 +29477,7 @@
       </c>
       <c r="G397" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H397" s="19" t="inlineStr">
@@ -29468,25 +29486,25 @@
         </is>
       </c>
       <c r="I397" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J397" s="21" t="n">
-        <v>2822</v>
+        <v>14852</v>
       </c>
       <c r="K397" s="21" t="n">
-        <v>22413</v>
+        <v>22422</v>
       </c>
       <c r="L397" s="22" t="n">
-        <v>6585</v>
+        <v>14852</v>
       </c>
       <c r="M397" s="19" t="inlineStr">
         <is>
-          <t>6a579cc484e30d0013ecd94d</t>
+          <t>6309df1a9a9138163a6a17a0</t>
         </is>
       </c>
       <c r="N397" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a579cc484e30d0013ecd94d</t>
+          <t>https://superprofile.bio/vig/6309df1a9a9138163a6a17a0</t>
         </is>
       </c>
       <c r="O397" s="24" t="inlineStr">
@@ -29506,22 +29524,22 @@
       </c>
       <c r="B398" s="13" t="inlineStr">
         <is>
-          <t>6386bcb126d3b5003c5dc980</t>
+          <t>64b9e87f61918e00206df90d</t>
         </is>
       </c>
       <c r="C398" s="13" t="inlineStr">
         <is>
-          <t>bankniftypremiumgroups</t>
+          <t>zerotoherovipcalls</t>
         </is>
       </c>
       <c r="D398" s="12" t="inlineStr">
         <is>
-          <t>vt3677264@gmail.com</t>
+          <t>bhaiajay5168@gmail.com</t>
         </is>
       </c>
       <c r="E398" s="12" t="inlineStr">
         <is>
-          <t>9557597328</t>
+          <t>7023193476</t>
         </is>
       </c>
       <c r="F398" s="12" t="inlineStr">
@@ -29531,34 +29549,34 @@
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H398" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I398" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J398" s="14" t="n">
-        <v>2249</v>
+        <v>2822</v>
       </c>
       <c r="K398" s="14" t="n">
-        <v>22406</v>
+        <v>22413</v>
       </c>
       <c r="L398" s="15" t="n">
-        <v>4860</v>
+        <v>6585</v>
       </c>
       <c r="M398" s="12" t="inlineStr">
         <is>
-          <t>6a85ca0eac362100135c2de3</t>
+          <t>6a579cc484e30d0013ecd94d</t>
         </is>
       </c>
       <c r="N398" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a85ca0eac362100135c2de3</t>
+          <t>https://superprofile.bio/vig/6a579cc484e30d0013ecd94d</t>
         </is>
       </c>
       <c r="O398" s="17" t="inlineStr">
@@ -29578,22 +29596,22 @@
       </c>
       <c r="B399" s="20" t="inlineStr">
         <is>
-          <t>6a0493243a48f800134b7d4b</t>
+          <t>6386bcb126d3b5003c5dc980</t>
         </is>
       </c>
       <c r="C399" s="20" t="inlineStr">
         <is>
-          <t>meenarahulzz</t>
+          <t>bankniftypremiumgroups</t>
         </is>
       </c>
       <c r="D399" s="19" t="inlineStr">
         <is>
-          <t>tmind4460@gmail.com</t>
+          <t>vt3677264@gmail.com</t>
         </is>
       </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
-          <t>9672238460</t>
+          <t>9557597328</t>
         </is>
       </c>
       <c r="F399" s="19" t="inlineStr">
@@ -29603,34 +29621,34 @@
       </c>
       <c r="G399" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H399" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I399" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J399" s="21" t="n">
-        <v>4233</v>
+        <v>2249</v>
       </c>
       <c r="K399" s="21" t="n">
-        <v>22138</v>
+        <v>22406</v>
       </c>
       <c r="L399" s="22" t="n">
-        <v>7428</v>
+        <v>4860</v>
       </c>
       <c r="M399" s="19" t="inlineStr">
         <is>
-          <t>68d0ebe0adc9cb00133eccaf</t>
+          <t>6a85ca0eac362100135c2de3</t>
         </is>
       </c>
       <c r="N399" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
+          <t>https://superprofile.bio/vig/6a85ca0eac362100135c2de3</t>
         </is>
       </c>
       <c r="O399" s="24" t="inlineStr">
@@ -29650,22 +29668,22 @@
       </c>
       <c r="B400" s="13" t="inlineStr">
         <is>
-          <t>67113f1b17d5ab001325c3a7</t>
+          <t>6a0493243a48f800134b7d4b</t>
         </is>
       </c>
       <c r="C400" s="13" t="inlineStr">
         <is>
-          <t>anshika7566</t>
+          <t>meenarahulzz</t>
         </is>
       </c>
       <c r="D400" s="12" t="inlineStr">
         <is>
-          <t>suhani93991@gmail.com</t>
+          <t>tmind4460@gmail.com</t>
         </is>
       </c>
       <c r="E400" s="12" t="inlineStr">
         <is>
-          <t>9399158129</t>
+          <t>9672238460</t>
         </is>
       </c>
       <c r="F400" s="12" t="inlineStr">
@@ -29675,7 +29693,7 @@
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H400" s="12" t="inlineStr">
@@ -29684,25 +29702,25 @@
         </is>
       </c>
       <c r="I400" s="13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J400" s="14" t="n">
-        <v>6709</v>
+        <v>4233</v>
       </c>
       <c r="K400" s="14" t="n">
-        <v>22046</v>
+        <v>22138</v>
       </c>
       <c r="L400" s="15" t="n">
-        <v>11982</v>
+        <v>7428</v>
       </c>
       <c r="M400" s="12" t="inlineStr">
         <is>
-          <t>676154f99babf600134329a6</t>
+          <t>68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="N400" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676154f99babf600134329a6</t>
+          <t>https://superprofile.bio/vig/68d0ebe0adc9cb00133eccaf</t>
         </is>
       </c>
       <c r="O400" s="17" t="inlineStr">
@@ -29722,22 +29740,22 @@
       </c>
       <c r="B401" s="20" t="inlineStr">
         <is>
-          <t>676cf61fae833e001322e4d4</t>
+          <t>67113f1b17d5ab001325c3a7</t>
         </is>
       </c>
       <c r="C401" s="20" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>anshika7566</t>
         </is>
       </c>
       <c r="D401" s="19" t="inlineStr">
         <is>
-          <t>rahulstock11@gmail.com</t>
+          <t>suhani93991@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="19" t="inlineStr">
         <is>
-          <t>8305763595</t>
+          <t>9399158129</t>
         </is>
       </c>
       <c r="F401" s="19" t="inlineStr">
@@ -29747,34 +29765,34 @@
       </c>
       <c r="G401" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H401" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I401" s="20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J401" s="21" t="n">
-        <v>3493</v>
+        <v>6709</v>
       </c>
       <c r="K401" s="21" t="n">
-        <v>21768</v>
+        <v>22046</v>
       </c>
       <c r="L401" s="22" t="n">
-        <v>4374</v>
+        <v>11982</v>
       </c>
       <c r="M401" s="19" t="inlineStr">
         <is>
-          <t>676d0ccf8e79b600130eb896</t>
+          <t>676154f99babf600134329a6</t>
         </is>
       </c>
       <c r="N401" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
+          <t>https://superprofile.bio/vig/676154f99babf600134329a6</t>
         </is>
       </c>
       <c r="O401" s="24" t="inlineStr">
@@ -29794,22 +29812,22 @@
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>62115e4a6bd738258707c0e9</t>
+          <t>676cf61fae833e001322e4d4</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
         <is>
-          <t>aditya</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="D402" s="12" t="inlineStr">
         <is>
-          <t>imavschoudhary@gmail.com</t>
+          <t>rahulstock11@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr">
         <is>
-          <t>9717115749</t>
+          <t>8305763595</t>
         </is>
       </c>
       <c r="F402" s="12" t="inlineStr">
@@ -29819,34 +29837,34 @@
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H402" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I402" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J402" s="14" t="n">
-        <v>2044</v>
+        <v>3493</v>
       </c>
       <c r="K402" s="14" t="n">
-        <v>21720</v>
+        <v>21768</v>
       </c>
       <c r="L402" s="15" t="n">
-        <v>4379</v>
+        <v>4374</v>
       </c>
       <c r="M402" s="12" t="inlineStr">
         <is>
-          <t>6511690d55ae1b0058703c86</t>
+          <t>676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="N402" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6511690d55ae1b0058703c86</t>
+          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="O402" s="17" t="inlineStr">

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 02:36:54 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 05:26:52 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 05:26:52 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 06:22:16 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 06:22:16 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 12:17:42 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 12:17:42 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 06:54:41 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 06:54:41 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 06:56:45 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 06:56:45 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 08:18:55 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>
@@ -593,11 +593,11 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹53,997,610.00</t>
+          <t>₹53,999,077.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>2988779</v>
+        <v>2990246</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P829"/>
+  <dimension ref="A1:P830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -59188,22 +59188,22 @@
       </c>
       <c r="B810" s="13" t="inlineStr">
         <is>
-          <t>62bad2a8dc07ec6e742c8cd2</t>
+          <t>6891f2a547882e0013794da9</t>
         </is>
       </c>
       <c r="C810" s="13" t="inlineStr">
         <is>
-          <t>tradexculture</t>
+          <t>11starteam</t>
         </is>
       </c>
       <c r="D810" s="12" t="inlineStr">
         <is>
-          <t>itstradeculture@gmail.com</t>
+          <t>lokeshgurjar0930@gmail.com</t>
         </is>
       </c>
       <c r="E810" s="12" t="inlineStr">
         <is>
-          <t>9098432281</t>
+          <t>9509698741</t>
         </is>
       </c>
       <c r="F810" s="12" t="inlineStr">
@@ -59213,34 +59213,34 @@
       </c>
       <c r="G810" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H810" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I810" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J810" s="14" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="K810" s="14" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="L810" s="15" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="M810" s="12" t="inlineStr">
         <is>
-          <t>63515a0aa785512f19f504e7</t>
+          <t>669e46c778795600130d6fac</t>
         </is>
       </c>
       <c r="N810" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
+          <t>https://superprofile.bio/vig/669e46c778795600130d6fac</t>
         </is>
       </c>
       <c r="O810" s="17" t="inlineStr">
@@ -59260,22 +59260,22 @@
       </c>
       <c r="B811" s="20" t="inlineStr">
         <is>
-          <t>62fce0e4560a1b2b3a724948</t>
+          <t>62bad2a8dc07ec6e742c8cd2</t>
         </is>
       </c>
       <c r="C811" s="20" t="inlineStr">
         <is>
-          <t>stockmarketwindow</t>
+          <t>tradexculture</t>
         </is>
       </c>
       <c r="D811" s="19" t="inlineStr">
         <is>
-          <t>stockmarketwindow2020@gmail.com</t>
+          <t>itstradeculture@gmail.com</t>
         </is>
       </c>
       <c r="E811" s="19" t="inlineStr">
         <is>
-          <t>9702609090</t>
+          <t>9098432281</t>
         </is>
       </c>
       <c r="F811" s="19" t="inlineStr">
@@ -59285,34 +59285,34 @@
       </c>
       <c r="G811" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H811" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I811" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J811" s="21" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="K811" s="21" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="L811" s="22" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="M811" s="19" t="inlineStr">
         <is>
-          <t>62fceac39275d45cb6f4f9b0</t>
+          <t>63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="N811" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62fceac39275d45cb6f4f9b0</t>
+          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="O811" s="24" t="inlineStr">
@@ -59332,22 +59332,22 @@
       </c>
       <c r="B812" s="13" t="inlineStr">
         <is>
-          <t>694b73fb58a19500131a05fc</t>
+          <t>62fce0e4560a1b2b3a724948</t>
         </is>
       </c>
       <c r="C812" s="13" t="inlineStr">
         <is>
-          <t>UPSC1109</t>
+          <t>stockmarketwindow</t>
         </is>
       </c>
       <c r="D812" s="12" t="inlineStr">
         <is>
-          <t>upsccurrentaffairs2026@gmail.com</t>
+          <t>stockmarketwindow2020@gmail.com</t>
         </is>
       </c>
       <c r="E812" s="12" t="inlineStr">
         <is>
-          <t>7840849825</t>
+          <t>9702609090</t>
         </is>
       </c>
       <c r="F812" s="12" t="inlineStr">
@@ -59357,34 +59357,34 @@
       </c>
       <c r="G812" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H812" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I812" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J812" s="14" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="K812" s="14" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L812" s="15" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="M812" s="12" t="inlineStr">
         <is>
-          <t>694bc7f749716f00136386dd</t>
+          <t>62fceac39275d45cb6f4f9b0</t>
         </is>
       </c>
       <c r="N812" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/694bc7f749716f00136386dd</t>
+          <t>https://superprofile.bio/vig/62fceac39275d45cb6f4f9b0</t>
         </is>
       </c>
       <c r="O812" s="17" t="inlineStr">
@@ -59404,22 +59404,22 @@
       </c>
       <c r="B813" s="20" t="inlineStr">
         <is>
-          <t>67c5f49ae74b1d0013ea0111</t>
+          <t>694b73fb58a19500131a05fc</t>
         </is>
       </c>
       <c r="C813" s="20" t="inlineStr">
         <is>
-          <t>jayb2427</t>
+          <t>UPSC1109</t>
         </is>
       </c>
       <c r="D813" s="19" t="inlineStr">
         <is>
-          <t>astutetrader24@gmail.com</t>
+          <t>upsccurrentaffairs2026@gmail.com</t>
         </is>
       </c>
       <c r="E813" s="19" t="inlineStr">
         <is>
-          <t>9879002427</t>
+          <t>7840849825</t>
         </is>
       </c>
       <c r="F813" s="19" t="inlineStr">
@@ -59429,34 +59429,34 @@
       </c>
       <c r="G813" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H813" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I813" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J813" s="21" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="K813" s="21" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="L813" s="22" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="M813" s="19" t="inlineStr">
         <is>
-          <t>67ecc370d9f0a5001309bd71</t>
+          <t>694bc7f749716f00136386dd</t>
         </is>
       </c>
       <c r="N813" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
+          <t>https://superprofile.bio/vig/694bc7f749716f00136386dd</t>
         </is>
       </c>
       <c r="O813" s="24" t="inlineStr">
@@ -59476,22 +59476,22 @@
       </c>
       <c r="B814" s="13" t="inlineStr">
         <is>
-          <t>65a74951ac6382001e161d60</t>
+          <t>67c5f49ae74b1d0013ea0111</t>
         </is>
       </c>
       <c r="C814" s="13" t="inlineStr">
         <is>
-          <t>ltt</t>
+          <t>jayb2427</t>
         </is>
       </c>
       <c r="D814" s="12" t="inlineStr">
         <is>
-          <t>ageshgowdom@gmail.com</t>
+          <t>astutetrader24@gmail.com</t>
         </is>
       </c>
       <c r="E814" s="12" t="inlineStr">
         <is>
-          <t>9952320729</t>
+          <t>9879002427</t>
         </is>
       </c>
       <c r="F814" s="12" t="inlineStr">
@@ -59501,12 +59501,12 @@
       </c>
       <c r="G814" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H814" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I814" s="13" t="n">
@@ -59523,12 +59523,12 @@
       </c>
       <c r="M814" s="12" t="inlineStr">
         <is>
-          <t>6a7b1ef9b038ca00137d7652</t>
+          <t>67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="N814" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7b1ef9b038ca00137d7652</t>
+          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="O814" s="17" t="inlineStr">
@@ -59548,22 +59548,22 @@
       </c>
       <c r="B815" s="20" t="inlineStr">
         <is>
-          <t>62b02cfe05ee3a0f33197b51</t>
+          <t>65a74951ac6382001e161d60</t>
         </is>
       </c>
       <c r="C815" s="20" t="inlineStr">
         <is>
-          <t>ssbfix</t>
+          <t>ltt</t>
         </is>
       </c>
       <c r="D815" s="19" t="inlineStr">
         <is>
-          <t>dantedmc4005@gmail.com</t>
+          <t>ageshgowdom@gmail.com</t>
         </is>
       </c>
       <c r="E815" s="19" t="inlineStr">
         <is>
-          <t>8492898406</t>
+          <t>9952320729</t>
         </is>
       </c>
       <c r="F815" s="19" t="inlineStr">
@@ -59573,12 +59573,12 @@
       </c>
       <c r="G815" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H815" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I815" s="20" t="n">
@@ -59595,12 +59595,12 @@
       </c>
       <c r="M815" s="19" t="inlineStr">
         <is>
-          <t>69b2db3479da0a0013c60582</t>
+          <t>6a7b1ef9b038ca00137d7652</t>
         </is>
       </c>
       <c r="N815" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b2db3479da0a0013c60582</t>
+          <t>https://superprofile.bio/vig/6a7b1ef9b038ca00137d7652</t>
         </is>
       </c>
       <c r="O815" s="24" t="inlineStr">
@@ -59620,22 +59620,22 @@
       </c>
       <c r="B816" s="13" t="inlineStr">
         <is>
-          <t>635b7f0025aca400328ae08f</t>
+          <t>62b02cfe05ee3a0f33197b51</t>
         </is>
       </c>
       <c r="C816" s="13" t="inlineStr">
         <is>
-          <t>gj20</t>
+          <t>ssbfix</t>
         </is>
       </c>
       <c r="D816" s="12" t="inlineStr">
         <is>
-          <t>gauravjetty2020@gmail.com</t>
+          <t>dantedmc4005@gmail.com</t>
         </is>
       </c>
       <c r="E816" s="12" t="inlineStr">
         <is>
-          <t>9049483124</t>
+          <t>8492898406</t>
         </is>
       </c>
       <c r="F816" s="12" t="inlineStr">
@@ -59645,34 +59645,34 @@
       </c>
       <c r="G816" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H816" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I816" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J816" s="14" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="K816" s="14" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="L816" s="15" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="M816" s="12" t="inlineStr">
         <is>
-          <t>6a5b01ec7929600013224a5b</t>
+          <t>69b2db3479da0a0013c60582</t>
         </is>
       </c>
       <c r="N816" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5b01ec7929600013224a5b</t>
+          <t>https://superprofile.bio/vig/69b2db3479da0a0013c60582</t>
         </is>
       </c>
       <c r="O816" s="17" t="inlineStr">
@@ -59692,22 +59692,22 @@
       </c>
       <c r="B817" s="20" t="inlineStr">
         <is>
-          <t>647578b824c9b30020e932b3</t>
+          <t>635b7f0025aca400328ae08f</t>
         </is>
       </c>
       <c r="C817" s="20" t="inlineStr">
         <is>
-          <t>prajustockmarket</t>
+          <t>gj20</t>
         </is>
       </c>
       <c r="D817" s="19" t="inlineStr">
         <is>
-          <t>kkurzekar16@gmail.com</t>
+          <t>gauravjetty2020@gmail.com</t>
         </is>
       </c>
       <c r="E817" s="19" t="inlineStr">
         <is>
-          <t>9112441997</t>
+          <t>9049483124</t>
         </is>
       </c>
       <c r="F817" s="19" t="inlineStr">
@@ -59739,12 +59739,12 @@
       </c>
       <c r="M817" s="19" t="inlineStr">
         <is>
-          <t>66b1ef098817a000134de2a4</t>
+          <t>6a5b01ec7929600013224a5b</t>
         </is>
       </c>
       <c r="N817" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66b1ef098817a000134de2a4</t>
+          <t>https://superprofile.bio/vig/6a5b01ec7929600013224a5b</t>
         </is>
       </c>
       <c r="O817" s="24" t="inlineStr">
@@ -59764,22 +59764,22 @@
       </c>
       <c r="B818" s="13" t="inlineStr">
         <is>
-          <t>655c2b17f2c0c5001e80dc5c</t>
+          <t>647578b824c9b30020e932b3</t>
         </is>
       </c>
       <c r="C818" s="13" t="inlineStr">
         <is>
-          <t>uday08</t>
+          <t>prajustockmarket</t>
         </is>
       </c>
       <c r="D818" s="12" t="inlineStr">
         <is>
-          <t>joguudaykiran4i@gmail.com</t>
+          <t>kkurzekar16@gmail.com</t>
         </is>
       </c>
       <c r="E818" s="12" t="inlineStr">
         <is>
-          <t>7569057147</t>
+          <t>9112441997</t>
         </is>
       </c>
       <c r="F818" s="12" t="inlineStr">
@@ -59789,34 +59789,34 @@
       </c>
       <c r="G818" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H818" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I818" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J818" s="14" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="K818" s="14" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="L818" s="15" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="M818" s="12" t="inlineStr">
         <is>
-          <t>6a97085d5a0b9a00134a57d9</t>
+          <t>66b1ef098817a000134de2a4</t>
         </is>
       </c>
       <c r="N818" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
+          <t>https://superprofile.bio/vig/66b1ef098817a000134de2a4</t>
         </is>
       </c>
       <c r="O818" s="17" t="inlineStr">
@@ -59836,22 +59836,22 @@
       </c>
       <c r="B819" s="20" t="inlineStr">
         <is>
-          <t>6a2a3b18739da100136db6f1</t>
+          <t>655c2b17f2c0c5001e80dc5c</t>
         </is>
       </c>
       <c r="C819" s="20" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>uday08</t>
         </is>
       </c>
       <c r="D819" s="19" t="inlineStr">
         <is>
-          <t>mr.perfect.official018@gmail.com</t>
+          <t>joguudaykiran4i@gmail.com</t>
         </is>
       </c>
       <c r="E819" s="19" t="inlineStr">
         <is>
-          <t>9116087897</t>
+          <t>7569057147</t>
         </is>
       </c>
       <c r="F819" s="19" t="inlineStr">
@@ -59861,34 +59861,34 @@
       </c>
       <c r="G819" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H819" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I819" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J819" s="21" t="n">
-        <v>1172</v>
+        <v>1259</v>
       </c>
       <c r="K819" s="21" t="n">
-        <v>1220</v>
+        <v>1259</v>
       </c>
       <c r="L819" s="22" t="n">
-        <v>1220</v>
+        <v>1259</v>
       </c>
       <c r="M819" s="19" t="inlineStr">
         <is>
-          <t>6a7d364eb62576001374f10c</t>
+          <t>6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="N819" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
+          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="O819" s="24" t="inlineStr">
@@ -59908,22 +59908,22 @@
       </c>
       <c r="B820" s="13" t="inlineStr">
         <is>
-          <t>6613b382df40ae0013ce2e06</t>
+          <t>6a2a3b18739da100136db6f1</t>
         </is>
       </c>
       <c r="C820" s="13" t="inlineStr">
         <is>
-          <t>thebullzonetrading</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="D820" s="12" t="inlineStr">
         <is>
-          <t>adityajangir22@gmail.com</t>
+          <t>mr.perfect.official018@gmail.com</t>
         </is>
       </c>
       <c r="E820" s="12" t="inlineStr">
         <is>
-          <t>9029547188</t>
+          <t>9116087897</t>
         </is>
       </c>
       <c r="F820" s="12" t="inlineStr">
@@ -59933,34 +59933,34 @@
       </c>
       <c r="G820" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H820" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I820" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J820" s="14" t="n">
-        <v>1213</v>
+        <v>1172</v>
       </c>
       <c r="K820" s="14" t="n">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="L820" s="15" t="n">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="M820" s="12" t="inlineStr">
         <is>
-          <t>66698a6464d3b00013ffe2cc</t>
+          <t>6a7d364eb62576001374f10c</t>
         </is>
       </c>
       <c r="N820" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66698a6464d3b00013ffe2cc</t>
+          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
         </is>
       </c>
       <c r="O820" s="17" t="inlineStr">
@@ -59980,22 +59980,22 @@
       </c>
       <c r="B821" s="20" t="inlineStr">
         <is>
-          <t>6867eeeeec727a00135b607b</t>
+          <t>6613b382df40ae0013ce2e06</t>
         </is>
       </c>
       <c r="C821" s="20" t="inlineStr">
         <is>
-          <t>speaksaurabh</t>
+          <t>thebullzonetrading</t>
         </is>
       </c>
       <c r="D821" s="19" t="inlineStr">
         <is>
-          <t>saurabhjs120@gmail.com</t>
+          <t>adityajangir22@gmail.com</t>
         </is>
       </c>
       <c r="E821" s="19" t="inlineStr">
         <is>
-          <t>7865522553</t>
+          <t>9029547188</t>
         </is>
       </c>
       <c r="F821" s="19" t="inlineStr">
@@ -60005,34 +60005,34 @@
       </c>
       <c r="G821" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H821" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I821" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J821" s="21" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="K821" s="21" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="L821" s="22" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="M821" s="19" t="inlineStr">
         <is>
-          <t>69d51deb76619c0014716500</t>
+          <t>66698a6464d3b00013ffe2cc</t>
         </is>
       </c>
       <c r="N821" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d51deb76619c0014716500</t>
+          <t>https://superprofile.bio/vig/66698a6464d3b00013ffe2cc</t>
         </is>
       </c>
       <c r="O821" s="24" t="inlineStr">
@@ -60052,22 +60052,22 @@
       </c>
       <c r="B822" s="13" t="inlineStr">
         <is>
-          <t>62b00d08d794090f2ca8d918</t>
+          <t>6867eeeeec727a00135b607b</t>
         </is>
       </c>
       <c r="C822" s="13" t="inlineStr">
         <is>
-          <t>rinkesh2076</t>
+          <t>speaksaurabh</t>
         </is>
       </c>
       <c r="D822" s="12" t="inlineStr">
         <is>
-          <t>rinkeshagrawal52@gmail.com</t>
+          <t>saurabhjs120@gmail.com</t>
         </is>
       </c>
       <c r="E822" s="12" t="inlineStr">
         <is>
-          <t>7247035512</t>
+          <t>7865522553</t>
         </is>
       </c>
       <c r="F822" s="12" t="inlineStr">
@@ -60077,34 +60077,34 @@
       </c>
       <c r="G822" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H822" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I822" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J822" s="14" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="K822" s="14" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="L822" s="15" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="M822" s="12" t="inlineStr">
         <is>
-          <t>6a8a70729ac5d90013fd1d86</t>
+          <t>69d51deb76619c0014716500</t>
         </is>
       </c>
       <c r="N822" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8a70729ac5d90013fd1d86</t>
+          <t>https://superprofile.bio/vig/69d51deb76619c0014716500</t>
         </is>
       </c>
       <c r="O822" s="17" t="inlineStr">
@@ -60124,22 +60124,22 @@
       </c>
       <c r="B823" s="20" t="inlineStr">
         <is>
-          <t>67fe57009043de0013589892</t>
+          <t>62b00d08d794090f2ca8d918</t>
         </is>
       </c>
       <c r="C823" s="20" t="inlineStr">
         <is>
-          <t>onestopmedicoo</t>
+          <t>rinkesh2076</t>
         </is>
       </c>
       <c r="D823" s="19" t="inlineStr">
         <is>
-          <t>gayathrinukalapati@gmail.com</t>
+          <t>rinkeshagrawal52@gmail.com</t>
         </is>
       </c>
       <c r="E823" s="19" t="inlineStr">
         <is>
-          <t>6281889512</t>
+          <t>7247035512</t>
         </is>
       </c>
       <c r="F823" s="19" t="inlineStr">
@@ -60149,34 +60149,34 @@
       </c>
       <c r="G823" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H823" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I823" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J823" s="21" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="K823" s="21" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="L823" s="22" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="M823" s="19" t="inlineStr">
         <is>
-          <t>67fe5d9fd3f9cd0013838092</t>
+          <t>6a8a70729ac5d90013fd1d86</t>
         </is>
       </c>
       <c r="N823" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67fe5d9fd3f9cd0013838092</t>
+          <t>https://superprofile.bio/vig/6a8a70729ac5d90013fd1d86</t>
         </is>
       </c>
       <c r="O823" s="24" t="inlineStr">
@@ -60196,22 +60196,22 @@
       </c>
       <c r="B824" s="13" t="inlineStr">
         <is>
-          <t>671a5a67c711890013a079f3</t>
+          <t>67fe57009043de0013589892</t>
         </is>
       </c>
       <c r="C824" s="13" t="inlineStr">
         <is>
-          <t>investing123</t>
+          <t>onestopmedicoo</t>
         </is>
       </c>
       <c r="D824" s="12" t="inlineStr">
         <is>
-          <t>gk8295311@gmail.com</t>
+          <t>gayathrinukalapati@gmail.com</t>
         </is>
       </c>
       <c r="E824" s="12" t="inlineStr">
         <is>
-          <t>7564911925</t>
+          <t>6281889512</t>
         </is>
       </c>
       <c r="F824" s="12" t="inlineStr">
@@ -60221,34 +60221,34 @@
       </c>
       <c r="G824" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H824" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I824" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J824" s="14" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="K824" s="14" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="L824" s="15" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="M824" s="12" t="inlineStr">
         <is>
-          <t>678540efacb5430013f405f9</t>
+          <t>67fe5d9fd3f9cd0013838092</t>
         </is>
       </c>
       <c r="N824" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/678540efacb5430013f405f9</t>
+          <t>https://superprofile.bio/vig/67fe5d9fd3f9cd0013838092</t>
         </is>
       </c>
       <c r="O824" s="17" t="inlineStr">
@@ -60268,22 +60268,22 @@
       </c>
       <c r="B825" s="20" t="inlineStr">
         <is>
-          <t>6436d5892b2028001fbf607b</t>
+          <t>671a5a67c711890013a079f3</t>
         </is>
       </c>
       <c r="C825" s="20" t="inlineStr">
         <is>
-          <t>Livelonghari</t>
+          <t>investing123</t>
         </is>
       </c>
       <c r="D825" s="19" t="inlineStr">
         <is>
-          <t>livelongwealth@gmail.com</t>
+          <t>gk8295311@gmail.com</t>
         </is>
       </c>
       <c r="E825" s="19" t="inlineStr">
         <is>
-          <t>9544085264</t>
+          <t>7564911925</t>
         </is>
       </c>
       <c r="F825" s="19" t="inlineStr">
@@ -60293,34 +60293,34 @@
       </c>
       <c r="G825" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H825" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I825" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J825" s="21" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="K825" s="21" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="L825" s="22" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="M825" s="19" t="inlineStr">
         <is>
-          <t>653e68ea423d4e001eef5b19</t>
+          <t>678540efacb5430013f405f9</t>
         </is>
       </c>
       <c r="N825" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
+          <t>https://superprofile.bio/vig/678540efacb5430013f405f9</t>
         </is>
       </c>
       <c r="O825" s="24" t="inlineStr">
@@ -60340,22 +60340,22 @@
       </c>
       <c r="B826" s="13" t="inlineStr">
         <is>
-          <t>67e424ccab747f00135495b4</t>
+          <t>6436d5892b2028001fbf607b</t>
         </is>
       </c>
       <c r="C826" s="13" t="inlineStr">
         <is>
-          <t>jobposting</t>
+          <t>Livelonghari</t>
         </is>
       </c>
       <c r="D826" s="12" t="inlineStr">
         <is>
-          <t>sagarruttare@gmail.com</t>
+          <t>livelongwealth@gmail.com</t>
         </is>
       </c>
       <c r="E826" s="12" t="inlineStr">
         <is>
-          <t>7796716569</t>
+          <t>9544085264</t>
         </is>
       </c>
       <c r="F826" s="12" t="inlineStr">
@@ -60377,22 +60377,22 @@
         <v>1</v>
       </c>
       <c r="J826" s="14" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="K826" s="14" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L826" s="15" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="M826" s="12" t="inlineStr">
         <is>
-          <t>692dae30d42b600013b13d78</t>
+          <t>653e68ea423d4e001eef5b19</t>
         </is>
       </c>
       <c r="N826" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
+          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
         </is>
       </c>
       <c r="O826" s="17" t="inlineStr">
@@ -60412,22 +60412,22 @@
       </c>
       <c r="B827" s="20" t="inlineStr">
         <is>
-          <t>64de1b2ce570b0001ed8a14d</t>
+          <t>67e424ccab747f00135495b4</t>
         </is>
       </c>
       <c r="C827" s="20" t="inlineStr">
         <is>
-          <t>azit</t>
+          <t>jobposting</t>
         </is>
       </c>
       <c r="D827" s="19" t="inlineStr">
         <is>
-          <t>adshree6@gmail.com</t>
+          <t>sagarruttare@gmail.com</t>
         </is>
       </c>
       <c r="E827" s="19" t="inlineStr">
         <is>
-          <t>9664914880</t>
+          <t>7796716569</t>
         </is>
       </c>
       <c r="F827" s="19" t="inlineStr">
@@ -60437,12 +60437,12 @@
       </c>
       <c r="G827" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H827" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I827" s="20" t="n">
@@ -60459,12 +60459,12 @@
       </c>
       <c r="M827" s="19" t="inlineStr">
         <is>
-          <t>68fe2dfaa6c0dd0013399d00</t>
+          <t>692dae30d42b600013b13d78</t>
         </is>
       </c>
       <c r="N827" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68fe2dfaa6c0dd0013399d00</t>
+          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
         </is>
       </c>
       <c r="O827" s="24" t="inlineStr">
@@ -60484,22 +60484,22 @@
       </c>
       <c r="B828" s="13" t="inlineStr">
         <is>
-          <t>6273b90a908af834792d0f70</t>
+          <t>64de1b2ce570b0001ed8a14d</t>
         </is>
       </c>
       <c r="C828" s="13" t="inlineStr">
         <is>
-          <t>otwa</t>
+          <t>azit</t>
         </is>
       </c>
       <c r="D828" s="12" t="inlineStr">
         <is>
-          <t>reshmanandyadav@gmail.com</t>
+          <t>adshree6@gmail.com</t>
         </is>
       </c>
       <c r="E828" s="12" t="inlineStr">
         <is>
-          <t>9792053659</t>
+          <t>9664914880</t>
         </is>
       </c>
       <c r="F828" s="12" t="inlineStr">
@@ -60509,34 +60509,34 @@
       </c>
       <c r="G828" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H828" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I828" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J828" s="14" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="K828" s="14" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="L828" s="15" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="M828" s="12" t="inlineStr">
         <is>
-          <t>680e309d146ab000130197f0</t>
+          <t>68fe2dfaa6c0dd0013399d00</t>
         </is>
       </c>
       <c r="N828" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/680e309d146ab000130197f0</t>
+          <t>https://superprofile.bio/vig/68fe2dfaa6c0dd0013399d00</t>
         </is>
       </c>
       <c r="O828" s="17" t="inlineStr">
@@ -60556,22 +60556,22 @@
       </c>
       <c r="B829" s="20" t="inlineStr">
         <is>
-          <t>69ad496eafc0e100130d7f09</t>
+          <t>6273b90a908af834792d0f70</t>
         </is>
       </c>
       <c r="C829" s="20" t="inlineStr">
         <is>
-          <t>sunoaudiobook</t>
+          <t>otwa</t>
         </is>
       </c>
       <c r="D829" s="19" t="inlineStr">
         <is>
-          <t>devrajstudio09@gmail.com</t>
+          <t>reshmanandyadav@gmail.com</t>
         </is>
       </c>
       <c r="E829" s="19" t="inlineStr">
         <is>
-          <t>7869490714</t>
+          <t>9792053659</t>
         </is>
       </c>
       <c r="F829" s="19" t="inlineStr">
@@ -60581,42 +60581,114 @@
       </c>
       <c r="G829" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H829" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I829" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J829" s="21" t="n">
+        <v>1049</v>
+      </c>
+      <c r="K829" s="21" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L829" s="22" t="n">
+        <v>1049</v>
+      </c>
+      <c r="M829" s="19" t="inlineStr">
+        <is>
+          <t>680e309d146ab000130197f0</t>
+        </is>
+      </c>
+      <c r="N829" s="23" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/680e309d146ab000130197f0</t>
+        </is>
+      </c>
+      <c r="O829" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P829" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="12" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" s="13" t="inlineStr">
+        <is>
+          <t>69ad496eafc0e100130d7f09</t>
+        </is>
+      </c>
+      <c r="C830" s="13" t="inlineStr">
+        <is>
+          <t>sunoaudiobook</t>
+        </is>
+      </c>
+      <c r="D830" s="12" t="inlineStr">
+        <is>
+          <t>devrajstudio09@gmail.com</t>
+        </is>
+      </c>
+      <c r="E830" s="12" t="inlineStr">
+        <is>
+          <t>7869490714</t>
+        </is>
+      </c>
+      <c r="F830" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G830" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H830" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I830" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J830" s="14" t="n">
         <v>1031</v>
       </c>
-      <c r="K829" s="21" t="n">
+      <c r="K830" s="14" t="n">
         <v>1031</v>
       </c>
-      <c r="L829" s="22" t="n">
+      <c r="L830" s="15" t="n">
         <v>1031</v>
       </c>
-      <c r="M829" s="19" t="inlineStr">
+      <c r="M830" s="12" t="inlineStr">
         <is>
           <t>6a4684b13604a700135096e1</t>
         </is>
       </c>
-      <c r="N829" s="23" t="inlineStr">
+      <c r="N830" s="16" t="inlineStr">
         <is>
           <t>https://superprofile.bio/vig/6a4684b13604a700135096e1</t>
         </is>
       </c>
-      <c r="O829" s="24" t="inlineStr">
-        <is>
-          <t>Not Verified</t>
-        </is>
-      </c>
-      <c r="P829" s="18" t="inlineStr">
+      <c r="O830" s="17" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P830" s="18" t="inlineStr">
         <is>
           <t>HOLD - RELEASE RESTRICTED</t>
         </is>
@@ -61452,6 +61524,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N827" r:id="rId826"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N828" r:id="rId827"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N829" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N830" r:id="rId829"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 08:18:55 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 10:09:45 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>
@@ -593,11 +593,11 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>₹53,999,077.00</t>
+          <t>₹54,002,773.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>2990246</v>
+        <v>2993942</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P830"/>
+  <dimension ref="A1:P831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -52204,59 +52204,59 @@
       </c>
       <c r="B713" s="20" t="inlineStr">
         <is>
-          <t>67ad63172703020013099918</t>
+          <t>69ec81771a704100130f824d</t>
         </is>
       </c>
       <c r="C713" s="20" t="inlineStr">
         <is>
-          <t>stockwithshreyash</t>
+          <t>confession</t>
         </is>
       </c>
       <c r="D713" s="19" t="inlineStr">
         <is>
-          <t>shreyashphanase@gmail.com</t>
+          <t>confession229@gmail.com</t>
         </is>
       </c>
       <c r="E713" s="19" t="inlineStr">
         <is>
-          <t>7066533150</t>
+          <t>9462003290</t>
         </is>
       </c>
       <c r="F713" s="19" t="inlineStr">
         <is>
-          <t>Kkabir John</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G713" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H713" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I713" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J713" s="21" t="n">
-        <v>1410</v>
+        <v>3696</v>
       </c>
       <c r="K713" s="21" t="n">
-        <v>3666</v>
+        <v>3696</v>
       </c>
       <c r="L713" s="22" t="n">
-        <v>2256</v>
+        <v>3696</v>
       </c>
       <c r="M713" s="19" t="inlineStr">
         <is>
-          <t>6a6cb50933211a0013f61a2e</t>
+          <t>69ec90975fe24c0013a3dbcc</t>
         </is>
       </c>
       <c r="N713" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6cb50933211a0013f61a2e</t>
+          <t>https://superprofile.bio/vig/69ec90975fe24c0013a3dbcc</t>
         </is>
       </c>
       <c r="O713" s="24" t="inlineStr">
@@ -52276,59 +52276,59 @@
       </c>
       <c r="B714" s="13" t="inlineStr">
         <is>
-          <t>679cb6eadcec620013a67618</t>
+          <t>67ad63172703020013099918</t>
         </is>
       </c>
       <c r="C714" s="13" t="inlineStr">
         <is>
-          <t>sharifftradingview</t>
+          <t>stockwithshreyash</t>
         </is>
       </c>
       <c r="D714" s="12" t="inlineStr">
         <is>
-          <t>omershrff@gmail.com</t>
+          <t>shreyashphanase@gmail.com</t>
         </is>
       </c>
       <c r="E714" s="12" t="inlineStr">
         <is>
-          <t>9848448771</t>
+          <t>7066533150</t>
         </is>
       </c>
       <c r="F714" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kkabir John</t>
         </is>
       </c>
       <c r="G714" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H714" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I714" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J714" s="14" t="n">
-        <v>1799</v>
+        <v>1410</v>
       </c>
       <c r="K714" s="14" t="n">
-        <v>3598</v>
+        <v>3666</v>
       </c>
       <c r="L714" s="15" t="n">
-        <v>1799</v>
+        <v>2256</v>
       </c>
       <c r="M714" s="12" t="inlineStr">
         <is>
-          <t>67a1b929a7465a001211b390</t>
+          <t>6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="N714" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a1b929a7465a001211b390</t>
+          <t>https://superprofile.bio/vig/6a6cb50933211a0013f61a2e</t>
         </is>
       </c>
       <c r="O714" s="17" t="inlineStr">
@@ -52348,22 +52348,22 @@
       </c>
       <c r="B715" s="20" t="inlineStr">
         <is>
-          <t>67866c436b549100138a3ed7</t>
+          <t>679cb6eadcec620013a67618</t>
         </is>
       </c>
       <c r="C715" s="20" t="inlineStr">
         <is>
-          <t>Quality0634</t>
+          <t>sharifftradingview</t>
         </is>
       </c>
       <c r="D715" s="19" t="inlineStr">
         <is>
-          <t>intraday.paisa@gmail.com</t>
+          <t>omershrff@gmail.com</t>
         </is>
       </c>
       <c r="E715" s="19" t="inlineStr">
         <is>
-          <t>8050416936</t>
+          <t>9848448771</t>
         </is>
       </c>
       <c r="F715" s="19" t="inlineStr">
@@ -52373,7 +52373,7 @@
       </c>
       <c r="G715" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H715" s="19" t="inlineStr">
@@ -52395,12 +52395,12 @@
       </c>
       <c r="M715" s="19" t="inlineStr">
         <is>
-          <t>692083d0709dbc001334eee9</t>
+          <t>67a1b929a7465a001211b390</t>
         </is>
       </c>
       <c r="N715" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692083d0709dbc001334eee9</t>
+          <t>https://superprofile.bio/vig/67a1b929a7465a001211b390</t>
         </is>
       </c>
       <c r="O715" s="24" t="inlineStr">
@@ -52420,22 +52420,22 @@
       </c>
       <c r="B716" s="13" t="inlineStr">
         <is>
-          <t>64ff537ad876e8001ee96fcf</t>
+          <t>67866c436b549100138a3ed7</t>
         </is>
       </c>
       <c r="C716" s="13" t="inlineStr">
         <is>
-          <t>elitecharttraders</t>
+          <t>Quality0634</t>
         </is>
       </c>
       <c r="D716" s="12" t="inlineStr">
         <is>
-          <t>shubhamkothari2808@gmail.com</t>
+          <t>intraday.paisa@gmail.com</t>
         </is>
       </c>
       <c r="E716" s="12" t="inlineStr">
         <is>
-          <t>9096316155</t>
+          <t>8050416936</t>
         </is>
       </c>
       <c r="F716" s="12" t="inlineStr">
@@ -52445,34 +52445,34 @@
       </c>
       <c r="G716" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H716" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I716" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J716" s="14" t="n">
-        <v>3517</v>
+        <v>1799</v>
       </c>
       <c r="K716" s="14" t="n">
-        <v>3517</v>
+        <v>3598</v>
       </c>
       <c r="L716" s="15" t="n">
-        <v>3517</v>
+        <v>1799</v>
       </c>
       <c r="M716" s="12" t="inlineStr">
         <is>
-          <t>69f82837bbbbcd0013ea8ddc</t>
+          <t>692083d0709dbc001334eee9</t>
         </is>
       </c>
       <c r="N716" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f82837bbbbcd0013ea8ddc</t>
+          <t>https://superprofile.bio/vig/692083d0709dbc001334eee9</t>
         </is>
       </c>
       <c r="O716" s="17" t="inlineStr">
@@ -52492,22 +52492,22 @@
       </c>
       <c r="B717" s="20" t="inlineStr">
         <is>
-          <t>663c8fbea3dd2a0013f1c1e4</t>
+          <t>64ff537ad876e8001ee96fcf</t>
         </is>
       </c>
       <c r="C717" s="20" t="inlineStr">
         <is>
-          <t>medrocket</t>
+          <t>elitecharttraders</t>
         </is>
       </c>
       <c r="D717" s="19" t="inlineStr">
         <is>
-          <t>medrocketofficial@gmail.com</t>
+          <t>shubhamkothari2808@gmail.com</t>
         </is>
       </c>
       <c r="E717" s="19" t="inlineStr">
         <is>
-          <t>8250617057</t>
+          <t>9096316155</t>
         </is>
       </c>
       <c r="F717" s="19" t="inlineStr">
@@ -52517,34 +52517,34 @@
       </c>
       <c r="G717" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H717" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I717" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J717" s="21" t="n">
-        <v>1169</v>
+        <v>3517</v>
       </c>
       <c r="K717" s="21" t="n">
-        <v>3507</v>
+        <v>3517</v>
       </c>
       <c r="L717" s="22" t="n">
-        <v>1169</v>
+        <v>3517</v>
       </c>
       <c r="M717" s="19" t="inlineStr">
         <is>
-          <t>66694f5004c49a001383e065</t>
+          <t>69f82837bbbbcd0013ea8ddc</t>
         </is>
       </c>
       <c r="N717" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66694f5004c49a001383e065</t>
+          <t>https://superprofile.bio/vig/69f82837bbbbcd0013ea8ddc</t>
         </is>
       </c>
       <c r="O717" s="24" t="inlineStr">
@@ -52564,22 +52564,22 @@
       </c>
       <c r="B718" s="13" t="inlineStr">
         <is>
-          <t>68ca4207823cd100138ea912</t>
+          <t>663c8fbea3dd2a0013f1c1e4</t>
         </is>
       </c>
       <c r="C718" s="13" t="inlineStr">
         <is>
-          <t>futuresfyndtelugu</t>
+          <t>medrocket</t>
         </is>
       </c>
       <c r="D718" s="12" t="inlineStr">
         <is>
-          <t>avanchavamshi8464@gmail.com</t>
+          <t>medrocketofficial@gmail.com</t>
         </is>
       </c>
       <c r="E718" s="12" t="inlineStr">
         <is>
-          <t>8886476331</t>
+          <t>8250617057</t>
         </is>
       </c>
       <c r="F718" s="12" t="inlineStr">
@@ -52589,34 +52589,34 @@
       </c>
       <c r="G718" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H718" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I718" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J718" s="14" t="n">
-        <v>2068</v>
+        <v>1169</v>
       </c>
       <c r="K718" s="14" t="n">
-        <v>3479</v>
+        <v>3507</v>
       </c>
       <c r="L718" s="15" t="n">
-        <v>2068</v>
+        <v>1169</v>
       </c>
       <c r="M718" s="12" t="inlineStr">
         <is>
-          <t>69bfce0243e38300139c4e6b</t>
+          <t>66694f5004c49a001383e065</t>
         </is>
       </c>
       <c r="N718" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bfce0243e38300139c4e6b</t>
+          <t>https://superprofile.bio/vig/66694f5004c49a001383e065</t>
         </is>
       </c>
       <c r="O718" s="17" t="inlineStr">
@@ -52636,22 +52636,22 @@
       </c>
       <c r="B719" s="20" t="inlineStr">
         <is>
-          <t>6767d31506ebeb001395b550</t>
+          <t>68ca4207823cd100138ea912</t>
         </is>
       </c>
       <c r="C719" s="20" t="inlineStr">
         <is>
-          <t>tradershub786</t>
+          <t>futuresfyndtelugu</t>
         </is>
       </c>
       <c r="D719" s="19" t="inlineStr">
         <is>
-          <t>cryptopandit7@gmail.com</t>
+          <t>avanchavamshi8464@gmail.com</t>
         </is>
       </c>
       <c r="E719" s="19" t="inlineStr">
         <is>
-          <t>7041627786</t>
+          <t>8886476331</t>
         </is>
       </c>
       <c r="F719" s="19" t="inlineStr">
@@ -52666,29 +52666,29 @@
       </c>
       <c r="H719" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I719" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J719" s="21" t="n">
-        <v>3416</v>
+        <v>2068</v>
       </c>
       <c r="K719" s="21" t="n">
-        <v>3416</v>
+        <v>3479</v>
       </c>
       <c r="L719" s="22" t="n">
-        <v>3416</v>
+        <v>2068</v>
       </c>
       <c r="M719" s="19" t="inlineStr">
         <is>
-          <t>691041745bdf5d00139c3ff4</t>
+          <t>69bfce0243e38300139c4e6b</t>
         </is>
       </c>
       <c r="N719" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/691041745bdf5d00139c3ff4</t>
+          <t>https://superprofile.bio/vig/69bfce0243e38300139c4e6b</t>
         </is>
       </c>
       <c r="O719" s="24" t="inlineStr">
@@ -52708,22 +52708,22 @@
       </c>
       <c r="B720" s="13" t="inlineStr">
         <is>
-          <t>62b1aa9416250451563f5842</t>
+          <t>6767d31506ebeb001395b550</t>
         </is>
       </c>
       <c r="C720" s="13" t="inlineStr">
         <is>
-          <t>gj123456</t>
+          <t>tradershub786</t>
         </is>
       </c>
       <c r="D720" s="12" t="inlineStr">
         <is>
-          <t>saroj.hirdayraj@gmail.com</t>
+          <t>cryptopandit7@gmail.com</t>
         </is>
       </c>
       <c r="E720" s="12" t="inlineStr">
         <is>
-          <t>9028236615</t>
+          <t>7041627786</t>
         </is>
       </c>
       <c r="F720" s="12" t="inlineStr">
@@ -52733,12 +52733,12 @@
       </c>
       <c r="G720" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H720" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I720" s="13" t="n">
@@ -52755,12 +52755,12 @@
       </c>
       <c r="M720" s="12" t="inlineStr">
         <is>
-          <t>64b631aadc0c5d001ff7ee42</t>
+          <t>691041745bdf5d00139c3ff4</t>
         </is>
       </c>
       <c r="N720" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64b631aadc0c5d001ff7ee42</t>
+          <t>https://superprofile.bio/vig/691041745bdf5d00139c3ff4</t>
         </is>
       </c>
       <c r="O720" s="17" t="inlineStr">
@@ -52780,22 +52780,22 @@
       </c>
       <c r="B721" s="20" t="inlineStr">
         <is>
-          <t>6651c35e1abe2000136fc7bc</t>
+          <t>62b1aa9416250451563f5842</t>
         </is>
       </c>
       <c r="C721" s="20" t="inlineStr">
         <is>
-          <t>sankar777</t>
+          <t>gj123456</t>
         </is>
       </c>
       <c r="D721" s="19" t="inlineStr">
         <is>
-          <t>sankarsutradhar.grp@gmail.com</t>
+          <t>saroj.hirdayraj@gmail.com</t>
         </is>
       </c>
       <c r="E721" s="19" t="inlineStr">
         <is>
-          <t>7002416396</t>
+          <t>9028236615</t>
         </is>
       </c>
       <c r="F721" s="19" t="inlineStr">
@@ -52805,34 +52805,34 @@
       </c>
       <c r="G721" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H721" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I721" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J721" s="21" t="n">
-        <v>1693</v>
+        <v>3416</v>
       </c>
       <c r="K721" s="21" t="n">
-        <v>3386</v>
+        <v>3416</v>
       </c>
       <c r="L721" s="22" t="n">
-        <v>1693</v>
+        <v>3416</v>
       </c>
       <c r="M721" s="19" t="inlineStr">
         <is>
-          <t>690de1efc4b63c0013a32b39</t>
+          <t>64b631aadc0c5d001ff7ee42</t>
         </is>
       </c>
       <c r="N721" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/690de1efc4b63c0013a32b39</t>
+          <t>https://superprofile.bio/vig/64b631aadc0c5d001ff7ee42</t>
         </is>
       </c>
       <c r="O721" s="24" t="inlineStr">
@@ -52852,22 +52852,22 @@
       </c>
       <c r="B722" s="13" t="inlineStr">
         <is>
-          <t>6a8c54406c483000139db29a</t>
+          <t>6651c35e1abe2000136fc7bc</t>
         </is>
       </c>
       <c r="C722" s="13" t="inlineStr">
         <is>
-          <t>ishita1m</t>
+          <t>sankar777</t>
         </is>
       </c>
       <c r="D722" s="12" t="inlineStr">
         <is>
-          <t>ishitasharma97349@gmail.com</t>
+          <t>sankarsutradhar.grp@gmail.com</t>
         </is>
       </c>
       <c r="E722" s="12" t="inlineStr">
         <is>
-          <t>9580414759</t>
+          <t>7002416396</t>
         </is>
       </c>
       <c r="F722" s="12" t="inlineStr">
@@ -52877,34 +52877,34 @@
       </c>
       <c r="G722" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H722" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I722" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J722" s="14" t="n">
-        <v>3382</v>
+        <v>1693</v>
       </c>
       <c r="K722" s="14" t="n">
-        <v>3382</v>
+        <v>3386</v>
       </c>
       <c r="L722" s="15" t="n">
-        <v>3382</v>
+        <v>1693</v>
       </c>
       <c r="M722" s="12" t="inlineStr">
         <is>
-          <t>6a9aecf5d960420013f7296f</t>
+          <t>690de1efc4b63c0013a32b39</t>
         </is>
       </c>
       <c r="N722" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a9aecf5d960420013f7296f</t>
+          <t>https://superprofile.bio/vig/690de1efc4b63c0013a32b39</t>
         </is>
       </c>
       <c r="O722" s="17" t="inlineStr">
@@ -52924,22 +52924,22 @@
       </c>
       <c r="B723" s="20" t="inlineStr">
         <is>
-          <t>6367eccd3e0974002eeec331</t>
+          <t>6a8c54406c483000139db29a</t>
         </is>
       </c>
       <c r="C723" s="20" t="inlineStr">
         <is>
-          <t>iborntotrade</t>
+          <t>ishita1m</t>
         </is>
       </c>
       <c r="D723" s="19" t="inlineStr">
         <is>
-          <t>dhirajsoni2412@gmail.com</t>
+          <t>ishitasharma97349@gmail.com</t>
         </is>
       </c>
       <c r="E723" s="19" t="inlineStr">
         <is>
-          <t>8108279968</t>
+          <t>9580414759</t>
         </is>
       </c>
       <c r="F723" s="19" t="inlineStr">
@@ -52949,34 +52949,34 @@
       </c>
       <c r="G723" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H723" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I723" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J723" s="21" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="K723" s="21" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="L723" s="22" t="n">
-        <v>3376</v>
+        <v>3382</v>
       </c>
       <c r="M723" s="19" t="inlineStr">
         <is>
-          <t>67ff6bee9043de001369580e</t>
+          <t>6a9aecf5d960420013f7296f</t>
         </is>
       </c>
       <c r="N723" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ff6bee9043de001369580e</t>
+          <t>https://superprofile.bio/vig/6a9aecf5d960420013f7296f</t>
         </is>
       </c>
       <c r="O723" s="24" t="inlineStr">
@@ -52996,22 +52996,22 @@
       </c>
       <c r="B724" s="13" t="inlineStr">
         <is>
-          <t>6a8e9befe4f3b80013c1a1ad</t>
+          <t>6367eccd3e0974002eeec331</t>
         </is>
       </c>
       <c r="C724" s="13" t="inlineStr">
         <is>
-          <t>madiflame</t>
+          <t>iborntotrade</t>
         </is>
       </c>
       <c r="D724" s="12" t="inlineStr">
         <is>
-          <t>coasterdice@gmail.com</t>
+          <t>dhirajsoni2412@gmail.com</t>
         </is>
       </c>
       <c r="E724" s="12" t="inlineStr">
         <is>
-          <t>6367975952</t>
+          <t>8108279968</t>
         </is>
       </c>
       <c r="F724" s="12" t="inlineStr">
@@ -53021,34 +53021,34 @@
       </c>
       <c r="G724" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H724" s="12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I724" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J724" s="14" t="n">
-        <v>1311</v>
+        <v>3376</v>
       </c>
       <c r="K724" s="14" t="n">
-        <v>3371</v>
+        <v>3376</v>
       </c>
       <c r="L724" s="15" t="n">
-        <v>2060</v>
+        <v>3376</v>
       </c>
       <c r="M724" s="12" t="inlineStr">
         <is>
-          <t>6a8e9f943215800013082fa8</t>
+          <t>67ff6bee9043de001369580e</t>
         </is>
       </c>
       <c r="N724" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8e9f943215800013082fa8</t>
+          <t>https://superprofile.bio/vig/67ff6bee9043de001369580e</t>
         </is>
       </c>
       <c r="O724" s="17" t="inlineStr">
@@ -53068,22 +53068,22 @@
       </c>
       <c r="B725" s="20" t="inlineStr">
         <is>
-          <t>647611e15fce50002086d43b</t>
+          <t>6a8e9befe4f3b80013c1a1ad</t>
         </is>
       </c>
       <c r="C725" s="20" t="inlineStr">
         <is>
-          <t>theindiantrading</t>
+          <t>madiflame</t>
         </is>
       </c>
       <c r="D725" s="19" t="inlineStr">
         <is>
-          <t>jaydeepsolanki123@gmail.com</t>
+          <t>coasterdice@gmail.com</t>
         </is>
       </c>
       <c r="E725" s="19" t="inlineStr">
         <is>
-          <t>7818009758</t>
+          <t>6367975952</t>
         </is>
       </c>
       <c r="F725" s="19" t="inlineStr">
@@ -53093,34 +53093,34 @@
       </c>
       <c r="G725" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H725" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I725" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J725" s="21" t="n">
-        <v>3355</v>
+        <v>1311</v>
       </c>
       <c r="K725" s="21" t="n">
-        <v>3355</v>
+        <v>3371</v>
       </c>
       <c r="L725" s="22" t="n">
-        <v>3355</v>
+        <v>2060</v>
       </c>
       <c r="M725" s="19" t="inlineStr">
         <is>
-          <t>64774adfaf783e0020bba577</t>
+          <t>6a8e9f943215800013082fa8</t>
         </is>
       </c>
       <c r="N725" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64774adfaf783e0020bba577</t>
+          <t>https://superprofile.bio/vig/6a8e9f943215800013082fa8</t>
         </is>
       </c>
       <c r="O725" s="24" t="inlineStr">
@@ -53140,22 +53140,22 @@
       </c>
       <c r="B726" s="13" t="inlineStr">
         <is>
-          <t>648c4eaa394394002a2e9d34</t>
+          <t>647611e15fce50002086d43b</t>
         </is>
       </c>
       <c r="C726" s="13" t="inlineStr">
         <is>
-          <t>anil4</t>
+          <t>theindiantrading</t>
         </is>
       </c>
       <c r="D726" s="12" t="inlineStr">
         <is>
-          <t>commoditytrading04@gmail.com</t>
+          <t>jaydeepsolanki123@gmail.com</t>
         </is>
       </c>
       <c r="E726" s="12" t="inlineStr">
         <is>
-          <t>9888881448</t>
+          <t>7818009758</t>
         </is>
       </c>
       <c r="F726" s="12" t="inlineStr">
@@ -53165,34 +53165,34 @@
       </c>
       <c r="G726" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H726" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I726" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J726" s="14" t="n">
-        <v>3315</v>
+        <v>3355</v>
       </c>
       <c r="K726" s="14" t="n">
-        <v>3315</v>
+        <v>3355</v>
       </c>
       <c r="L726" s="15" t="n">
-        <v>3315</v>
+        <v>3355</v>
       </c>
       <c r="M726" s="12" t="inlineStr">
         <is>
-          <t>648da40331b882002043c286</t>
+          <t>64774adfaf783e0020bba577</t>
         </is>
       </c>
       <c r="N726" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/648da40331b882002043c286</t>
+          <t>https://superprofile.bio/vig/64774adfaf783e0020bba577</t>
         </is>
       </c>
       <c r="O726" s="17" t="inlineStr">
@@ -53212,22 +53212,22 @@
       </c>
       <c r="B727" s="20" t="inlineStr">
         <is>
-          <t>659e3ca9c1f5ad001ec16b7a</t>
+          <t>648c4eaa394394002a2e9d34</t>
         </is>
       </c>
       <c r="C727" s="20" t="inlineStr">
         <is>
-          <t>vinay1207</t>
+          <t>anil4</t>
         </is>
       </c>
       <c r="D727" s="19" t="inlineStr">
         <is>
-          <t>vinaykumar.parasa@gmail.com</t>
+          <t>commoditytrading04@gmail.com</t>
         </is>
       </c>
       <c r="E727" s="19" t="inlineStr">
         <is>
-          <t>7036657719</t>
+          <t>9888881448</t>
         </is>
       </c>
       <c r="F727" s="19" t="inlineStr">
@@ -53242,29 +53242,29 @@
       </c>
       <c r="H727" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I727" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J727" s="21" t="n">
-        <v>1849</v>
+        <v>3315</v>
       </c>
       <c r="K727" s="21" t="n">
-        <v>3243</v>
+        <v>3315</v>
       </c>
       <c r="L727" s="22" t="n">
-        <v>1849</v>
+        <v>3315</v>
       </c>
       <c r="M727" s="19" t="inlineStr">
         <is>
-          <t>685e46711afd4f00137187f1</t>
+          <t>648da40331b882002043c286</t>
         </is>
       </c>
       <c r="N727" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/685e46711afd4f00137187f1</t>
+          <t>https://superprofile.bio/vig/648da40331b882002043c286</t>
         </is>
       </c>
       <c r="O727" s="24" t="inlineStr">
@@ -53284,22 +53284,22 @@
       </c>
       <c r="B728" s="13" t="inlineStr">
         <is>
-          <t>660d53978aa7cf0013775a08</t>
+          <t>659e3ca9c1f5ad001ec16b7a</t>
         </is>
       </c>
       <c r="C728" s="13" t="inlineStr">
         <is>
-          <t>rkroshansharma61</t>
+          <t>vinay1207</t>
         </is>
       </c>
       <c r="D728" s="12" t="inlineStr">
         <is>
-          <t>rkroshansharma61@gmail.com</t>
+          <t>vinaykumar.parasa@gmail.com</t>
         </is>
       </c>
       <c r="E728" s="12" t="inlineStr">
         <is>
-          <t>7033021747</t>
+          <t>7036657719</t>
         </is>
       </c>
       <c r="F728" s="12" t="inlineStr">
@@ -53309,34 +53309,34 @@
       </c>
       <c r="G728" s="12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H728" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I728" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J728" s="14" t="n">
-        <v>2680</v>
+        <v>1849</v>
       </c>
       <c r="K728" s="14" t="n">
-        <v>3230</v>
+        <v>3243</v>
       </c>
       <c r="L728" s="15" t="n">
-        <v>2680</v>
+        <v>1849</v>
       </c>
       <c r="M728" s="12" t="inlineStr">
         <is>
-          <t>6a977e55ead5440013c7ef96</t>
+          <t>685e46711afd4f00137187f1</t>
         </is>
       </c>
       <c r="N728" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a977e55ead5440013c7ef96</t>
+          <t>https://superprofile.bio/vig/685e46711afd4f00137187f1</t>
         </is>
       </c>
       <c r="O728" s="17" t="inlineStr">
@@ -53356,22 +53356,22 @@
       </c>
       <c r="B729" s="20" t="inlineStr">
         <is>
-          <t>646373ce6cbb8200207efe77</t>
+          <t>660d53978aa7cf0013775a08</t>
         </is>
       </c>
       <c r="C729" s="20" t="inlineStr">
         <is>
-          <t>godfather01</t>
+          <t>rkroshansharma61</t>
         </is>
       </c>
       <c r="D729" s="19" t="inlineStr">
         <is>
-          <t>vikkysharma4032@gmail.com</t>
+          <t>rkroshansharma61@gmail.com</t>
         </is>
       </c>
       <c r="E729" s="19" t="inlineStr">
         <is>
-          <t>9839384032</t>
+          <t>7033021747</t>
         </is>
       </c>
       <c r="F729" s="19" t="inlineStr">
@@ -53381,34 +53381,34 @@
       </c>
       <c r="G729" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H729" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I729" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J729" s="21" t="n">
-        <v>1552</v>
+        <v>2680</v>
       </c>
       <c r="K729" s="21" t="n">
-        <v>3193</v>
+        <v>3230</v>
       </c>
       <c r="L729" s="22" t="n">
-        <v>1641</v>
+        <v>2680</v>
       </c>
       <c r="M729" s="19" t="inlineStr">
         <is>
-          <t>68459b8cb2cccb0013dabf4c</t>
+          <t>6a977e55ead5440013c7ef96</t>
         </is>
       </c>
       <c r="N729" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
+          <t>https://superprofile.bio/vig/6a977e55ead5440013c7ef96</t>
         </is>
       </c>
       <c r="O729" s="24" t="inlineStr">
@@ -53428,22 +53428,22 @@
       </c>
       <c r="B730" s="13" t="inlineStr">
         <is>
-          <t>688affc53978d60013770389</t>
+          <t>646373ce6cbb8200207efe77</t>
         </is>
       </c>
       <c r="C730" s="13" t="inlineStr">
         <is>
-          <t>finanxialfreedomclub</t>
+          <t>godfather01</t>
         </is>
       </c>
       <c r="D730" s="12" t="inlineStr">
         <is>
-          <t>shubhammishrax03@gmail.com</t>
+          <t>vikkysharma4032@gmail.com</t>
         </is>
       </c>
       <c r="E730" s="12" t="inlineStr">
         <is>
-          <t>9812857854</t>
+          <t>9839384032</t>
         </is>
       </c>
       <c r="F730" s="12" t="inlineStr">
@@ -53453,34 +53453,34 @@
       </c>
       <c r="G730" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H730" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I730" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J730" s="14" t="n">
-        <v>3169</v>
+        <v>1552</v>
       </c>
       <c r="K730" s="14" t="n">
-        <v>3169</v>
+        <v>3193</v>
       </c>
       <c r="L730" s="15" t="n">
-        <v>3169</v>
+        <v>1641</v>
       </c>
       <c r="M730" s="12" t="inlineStr">
         <is>
-          <t>6a6791558d035c00136ca57a</t>
+          <t>68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="N730" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6791558d035c00136ca57a</t>
+          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="O730" s="17" t="inlineStr">
@@ -53500,22 +53500,22 @@
       </c>
       <c r="B731" s="20" t="inlineStr">
         <is>
-          <t>64899e94adbaf8002a667e2a</t>
+          <t>688affc53978d60013770389</t>
         </is>
       </c>
       <c r="C731" s="20" t="inlineStr">
         <is>
-          <t>rastogitrading</t>
+          <t>finanxialfreedomclub</t>
         </is>
       </c>
       <c r="D731" s="19" t="inlineStr">
         <is>
-          <t>umangrastogi12345@gmail.com</t>
+          <t>shubhammishrax03@gmail.com</t>
         </is>
       </c>
       <c r="E731" s="19" t="inlineStr">
         <is>
-          <t>7017907943</t>
+          <t>9812857854</t>
         </is>
       </c>
       <c r="F731" s="19" t="inlineStr">
@@ -53525,34 +53525,34 @@
       </c>
       <c r="G731" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H731" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I731" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J731" s="21" t="n">
-        <v>3086</v>
+        <v>3169</v>
       </c>
       <c r="K731" s="21" t="n">
-        <v>3086</v>
+        <v>3169</v>
       </c>
       <c r="L731" s="22" t="n">
-        <v>3086</v>
+        <v>3169</v>
       </c>
       <c r="M731" s="19" t="inlineStr">
         <is>
-          <t>67f65f246919960013fdfd3e</t>
+          <t>6a6791558d035c00136ca57a</t>
         </is>
       </c>
       <c r="N731" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67f65f246919960013fdfd3e</t>
+          <t>https://superprofile.bio/vig/6a6791558d035c00136ca57a</t>
         </is>
       </c>
       <c r="O731" s="24" t="inlineStr">
@@ -53572,22 +53572,22 @@
       </c>
       <c r="B732" s="13" t="inlineStr">
         <is>
-          <t>645cb91fc8965700203aa836</t>
+          <t>64899e94adbaf8002a667e2a</t>
         </is>
       </c>
       <c r="C732" s="13" t="inlineStr">
         <is>
-          <t>kavyatrader</t>
+          <t>rastogitrading</t>
         </is>
       </c>
       <c r="D732" s="12" t="inlineStr">
         <is>
-          <t>Singhabhishek59942@gmail.com</t>
+          <t>umangrastogi12345@gmail.com</t>
         </is>
       </c>
       <c r="E732" s="12" t="inlineStr">
         <is>
-          <t>8979006726</t>
+          <t>7017907943</t>
         </is>
       </c>
       <c r="F732" s="12" t="inlineStr">
@@ -53597,34 +53597,34 @@
       </c>
       <c r="G732" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H732" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I732" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J732" s="14" t="n">
-        <v>1534</v>
+        <v>3086</v>
       </c>
       <c r="K732" s="14" t="n">
-        <v>3068</v>
+        <v>3086</v>
       </c>
       <c r="L732" s="15" t="n">
-        <v>1534</v>
+        <v>3086</v>
       </c>
       <c r="M732" s="12" t="inlineStr">
         <is>
-          <t>69dc9e4d81ef030013e77b80</t>
+          <t>67f65f246919960013fdfd3e</t>
         </is>
       </c>
       <c r="N732" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
+          <t>https://superprofile.bio/vig/67f65f246919960013fdfd3e</t>
         </is>
       </c>
       <c r="O732" s="17" t="inlineStr">
@@ -53644,22 +53644,22 @@
       </c>
       <c r="B733" s="20" t="inlineStr">
         <is>
-          <t>61f364f28513970d4d61d7c2</t>
+          <t>645cb91fc8965700203aa836</t>
         </is>
       </c>
       <c r="C733" s="20" t="inlineStr">
         <is>
-          <t>lakhanikushal</t>
+          <t>kavyatrader</t>
         </is>
       </c>
       <c r="D733" s="19" t="inlineStr">
         <is>
-          <t>kushal9049@gmail.com</t>
+          <t>Singhabhishek59942@gmail.com</t>
         </is>
       </c>
       <c r="E733" s="19" t="inlineStr">
         <is>
-          <t>9638149519</t>
+          <t>8979006726</t>
         </is>
       </c>
       <c r="F733" s="19" t="inlineStr">
@@ -53669,34 +53669,34 @@
       </c>
       <c r="G733" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H733" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I733" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J733" s="21" t="n">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="K733" s="21" t="n">
-        <v>3054</v>
+        <v>3068</v>
       </c>
       <c r="L733" s="22" t="n">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="M733" s="19" t="inlineStr">
         <is>
-          <t>6565d90e912474001e53bbc5</t>
+          <t>69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="N733" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6565d90e912474001e53bbc5</t>
+          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="O733" s="24" t="inlineStr">
@@ -53716,22 +53716,22 @@
       </c>
       <c r="B734" s="13" t="inlineStr">
         <is>
-          <t>64e5125f74d92e001db1c863</t>
+          <t>61f364f28513970d4d61d7c2</t>
         </is>
       </c>
       <c r="C734" s="13" t="inlineStr">
         <is>
-          <t>stockincome</t>
+          <t>lakhanikushal</t>
         </is>
       </c>
       <c r="D734" s="12" t="inlineStr">
         <is>
-          <t>stockincomepremium@gmail.com</t>
+          <t>kushal9049@gmail.com</t>
         </is>
       </c>
       <c r="E734" s="12" t="inlineStr">
         <is>
-          <t>6360318605</t>
+          <t>9638149519</t>
         </is>
       </c>
       <c r="F734" s="12" t="inlineStr">
@@ -53741,34 +53741,34 @@
       </c>
       <c r="G734" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H734" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I734" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J734" s="14" t="n">
-        <v>2957</v>
+        <v>1527</v>
       </c>
       <c r="K734" s="14" t="n">
-        <v>2957</v>
+        <v>3054</v>
       </c>
       <c r="L734" s="15" t="n">
-        <v>2957</v>
+        <v>1527</v>
       </c>
       <c r="M734" s="12" t="inlineStr">
         <is>
-          <t>660c046ad850c90013078a88</t>
+          <t>6565d90e912474001e53bbc5</t>
         </is>
       </c>
       <c r="N734" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/660c046ad850c90013078a88</t>
+          <t>https://superprofile.bio/vig/6565d90e912474001e53bbc5</t>
         </is>
       </c>
       <c r="O734" s="17" t="inlineStr">
@@ -53788,22 +53788,22 @@
       </c>
       <c r="B735" s="20" t="inlineStr">
         <is>
-          <t>6683ff7b25fece0013581ba9</t>
+          <t>64e5125f74d92e001db1c863</t>
         </is>
       </c>
       <c r="C735" s="20" t="inlineStr">
         <is>
-          <t>stocknews12345</t>
+          <t>stockincome</t>
         </is>
       </c>
       <c r="D735" s="19" t="inlineStr">
         <is>
-          <t>mayankkalani1@gmail.com</t>
+          <t>stockincomepremium@gmail.com</t>
         </is>
       </c>
       <c r="E735" s="19" t="inlineStr">
         <is>
-          <t>9667476649</t>
+          <t>6360318605</t>
         </is>
       </c>
       <c r="F735" s="19" t="inlineStr">
@@ -53813,12 +53813,12 @@
       </c>
       <c r="G735" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H735" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I735" s="20" t="n">
@@ -53835,12 +53835,12 @@
       </c>
       <c r="M735" s="19" t="inlineStr">
         <is>
-          <t>68748d26e3c1b90013a1b865</t>
+          <t>660c046ad850c90013078a88</t>
         </is>
       </c>
       <c r="N735" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68748d26e3c1b90013a1b865</t>
+          <t>https://superprofile.bio/vig/660c046ad850c90013078a88</t>
         </is>
       </c>
       <c r="O735" s="24" t="inlineStr">
@@ -53860,22 +53860,22 @@
       </c>
       <c r="B736" s="13" t="inlineStr">
         <is>
-          <t>672365fabad6bf0013d98d77</t>
+          <t>6683ff7b25fece0013581ba9</t>
         </is>
       </c>
       <c r="C736" s="13" t="inlineStr">
         <is>
-          <t>parthoption</t>
+          <t>stocknews12345</t>
         </is>
       </c>
       <c r="D736" s="12" t="inlineStr">
         <is>
-          <t>tradingbillionaire05@gmail.com</t>
+          <t>mayankkalani1@gmail.com</t>
         </is>
       </c>
       <c r="E736" s="12" t="inlineStr">
         <is>
-          <t>9719333241</t>
+          <t>9667476649</t>
         </is>
       </c>
       <c r="F736" s="12" t="inlineStr">
@@ -53885,34 +53885,34 @@
       </c>
       <c r="G736" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H736" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I736" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J736" s="14" t="n">
-        <v>2947</v>
+        <v>2957</v>
       </c>
       <c r="K736" s="14" t="n">
-        <v>2947</v>
+        <v>2957</v>
       </c>
       <c r="L736" s="15" t="n">
-        <v>2947</v>
+        <v>2957</v>
       </c>
       <c r="M736" s="12" t="inlineStr">
         <is>
-          <t>6734903edeaa0b0013fed187</t>
+          <t>68748d26e3c1b90013a1b865</t>
         </is>
       </c>
       <c r="N736" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6734903edeaa0b0013fed187</t>
+          <t>https://superprofile.bio/vig/68748d26e3c1b90013a1b865</t>
         </is>
       </c>
       <c r="O736" s="17" t="inlineStr">
@@ -53932,22 +53932,22 @@
       </c>
       <c r="B737" s="20" t="inlineStr">
         <is>
-          <t>698c21f698c8af001374cda7</t>
+          <t>672365fabad6bf0013d98d77</t>
         </is>
       </c>
       <c r="C737" s="20" t="inlineStr">
         <is>
-          <t>advanceastrovastu</t>
+          <t>parthoption</t>
         </is>
       </c>
       <c r="D737" s="19" t="inlineStr">
         <is>
-          <t>graceenergy108@gmail.com</t>
+          <t>tradingbillionaire05@gmail.com</t>
         </is>
       </c>
       <c r="E737" s="19" t="inlineStr">
         <is>
-          <t>9409334468</t>
+          <t>9719333241</t>
         </is>
       </c>
       <c r="F737" s="19" t="inlineStr">
@@ -53957,34 +53957,34 @@
       </c>
       <c r="G737" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H737" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I737" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J737" s="21" t="n">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="K737" s="21" t="n">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="L737" s="22" t="n">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="M737" s="19" t="inlineStr">
         <is>
-          <t>698ca3b8648fed0013499cae</t>
+          <t>6734903edeaa0b0013fed187</t>
         </is>
       </c>
       <c r="N737" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698ca3b8648fed0013499cae</t>
+          <t>https://superprofile.bio/vig/6734903edeaa0b0013fed187</t>
         </is>
       </c>
       <c r="O737" s="24" t="inlineStr">
@@ -54004,22 +54004,22 @@
       </c>
       <c r="B738" s="13" t="inlineStr">
         <is>
-          <t>6551df78ce9bcc001e4a9b3b</t>
+          <t>698c21f698c8af001374cda7</t>
         </is>
       </c>
       <c r="C738" s="13" t="inlineStr">
         <is>
-          <t>premiumpaid</t>
+          <t>advanceastrovastu</t>
         </is>
       </c>
       <c r="D738" s="12" t="inlineStr">
         <is>
-          <t>devbharteliya74@gmail.com</t>
+          <t>graceenergy108@gmail.com</t>
         </is>
       </c>
       <c r="E738" s="12" t="inlineStr">
         <is>
-          <t>7470624461</t>
+          <t>9409334468</t>
         </is>
       </c>
       <c r="F738" s="12" t="inlineStr">
@@ -54029,34 +54029,34 @@
       </c>
       <c r="G738" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H738" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I738" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J738" s="14" t="n">
-        <v>2907</v>
+        <v>2941</v>
       </c>
       <c r="K738" s="14" t="n">
-        <v>2907</v>
+        <v>2941</v>
       </c>
       <c r="L738" s="15" t="n">
-        <v>2907</v>
+        <v>2941</v>
       </c>
       <c r="M738" s="12" t="inlineStr">
         <is>
-          <t>655e0455e3af71001edc4722</t>
+          <t>698ca3b8648fed0013499cae</t>
         </is>
       </c>
       <c r="N738" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/655e0455e3af71001edc4722</t>
+          <t>https://superprofile.bio/vig/698ca3b8648fed0013499cae</t>
         </is>
       </c>
       <c r="O738" s="17" t="inlineStr">
@@ -54076,22 +54076,22 @@
       </c>
       <c r="B739" s="20" t="inlineStr">
         <is>
-          <t>64768e451a9d6e001f8b9f98</t>
+          <t>6551df78ce9bcc001e4a9b3b</t>
         </is>
       </c>
       <c r="C739" s="20" t="inlineStr">
         <is>
-          <t>scalpingexpert</t>
+          <t>premiumpaid</t>
         </is>
       </c>
       <c r="D739" s="19" t="inlineStr">
         <is>
-          <t>pintum527@gmail.com</t>
+          <t>devbharteliya74@gmail.com</t>
         </is>
       </c>
       <c r="E739" s="19" t="inlineStr">
         <is>
-          <t>8446526519</t>
+          <t>7470624461</t>
         </is>
       </c>
       <c r="F739" s="19" t="inlineStr">
@@ -54113,22 +54113,22 @@
         <v>1</v>
       </c>
       <c r="J739" s="21" t="n">
-        <v>2893</v>
+        <v>2907</v>
       </c>
       <c r="K739" s="21" t="n">
-        <v>2893</v>
+        <v>2907</v>
       </c>
       <c r="L739" s="22" t="n">
-        <v>2893</v>
+        <v>2907</v>
       </c>
       <c r="M739" s="19" t="inlineStr">
         <is>
-          <t>69d34f3b4c70560013de119f</t>
+          <t>655e0455e3af71001edc4722</t>
         </is>
       </c>
       <c r="N739" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d34f3b4c70560013de119f</t>
+          <t>https://superprofile.bio/vig/655e0455e3af71001edc4722</t>
         </is>
       </c>
       <c r="O739" s="24" t="inlineStr">
@@ -54148,22 +54148,22 @@
       </c>
       <c r="B740" s="13" t="inlineStr">
         <is>
-          <t>6475f07e437344001f89c26d</t>
+          <t>64768e451a9d6e001f8b9f98</t>
         </is>
       </c>
       <c r="C740" s="13" t="inlineStr">
         <is>
-          <t>pewthuts</t>
+          <t>scalpingexpert</t>
         </is>
       </c>
       <c r="D740" s="12" t="inlineStr">
         <is>
-          <t>pewthuts@gmail.com</t>
+          <t>pintum527@gmail.com</t>
         </is>
       </c>
       <c r="E740" s="12" t="inlineStr">
         <is>
-          <t>8920803214</t>
+          <t>8446526519</t>
         </is>
       </c>
       <c r="F740" s="12" t="inlineStr">
@@ -54173,34 +54173,34 @@
       </c>
       <c r="G740" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H740" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I740" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J740" s="14" t="n">
-        <v>1439</v>
+        <v>2893</v>
       </c>
       <c r="K740" s="14" t="n">
-        <v>2878</v>
+        <v>2893</v>
       </c>
       <c r="L740" s="15" t="n">
-        <v>1439</v>
+        <v>2893</v>
       </c>
       <c r="M740" s="12" t="inlineStr">
         <is>
-          <t>647dd28a4bf3e90020377126</t>
+          <t>69d34f3b4c70560013de119f</t>
         </is>
       </c>
       <c r="N740" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/647dd28a4bf3e90020377126</t>
+          <t>https://superprofile.bio/vig/69d34f3b4c70560013de119f</t>
         </is>
       </c>
       <c r="O740" s="17" t="inlineStr">
@@ -54220,22 +54220,22 @@
       </c>
       <c r="B741" s="20" t="inlineStr">
         <is>
-          <t>6a3a795e7a585c0013785ad0</t>
+          <t>6475f07e437344001f89c26d</t>
         </is>
       </c>
       <c r="C741" s="20" t="inlineStr">
         <is>
-          <t>mahendrasinh18</t>
+          <t>pewthuts</t>
         </is>
       </c>
       <c r="D741" s="19" t="inlineStr">
         <is>
-          <t>mahendrasinhrajput869@gmail.com</t>
+          <t>pewthuts@gmail.com</t>
         </is>
       </c>
       <c r="E741" s="19" t="inlineStr">
         <is>
-          <t>9081586676</t>
+          <t>8920803214</t>
         </is>
       </c>
       <c r="F741" s="19" t="inlineStr">
@@ -54245,34 +54245,34 @@
       </c>
       <c r="G741" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H741" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I741" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J741" s="21" t="n">
-        <v>2875</v>
+        <v>1439</v>
       </c>
       <c r="K741" s="21" t="n">
-        <v>2875</v>
+        <v>2878</v>
       </c>
       <c r="L741" s="22" t="n">
-        <v>2875</v>
+        <v>1439</v>
       </c>
       <c r="M741" s="19" t="inlineStr">
         <is>
-          <t>6a3a7c3334158200138768eb</t>
+          <t>647dd28a4bf3e90020377126</t>
         </is>
       </c>
       <c r="N741" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3a7c3334158200138768eb</t>
+          <t>https://superprofile.bio/vig/647dd28a4bf3e90020377126</t>
         </is>
       </c>
       <c r="O741" s="24" t="inlineStr">
@@ -54292,59 +54292,59 @@
       </c>
       <c r="B742" s="13" t="inlineStr">
         <is>
-          <t>6a4bf7f1f111810013cba5ce</t>
+          <t>6a3a795e7a585c0013785ad0</t>
         </is>
       </c>
       <c r="C742" s="13" t="inlineStr">
         <is>
-          <t>insiderpedia</t>
+          <t>mahendrasinh18</t>
         </is>
       </c>
       <c r="D742" s="12" t="inlineStr">
         <is>
-          <t>insiderpedia@gmail.com</t>
+          <t>mahendrasinhrajput869@gmail.com</t>
         </is>
       </c>
       <c r="E742" s="12" t="inlineStr">
         <is>
-          <t>8439150506</t>
+          <t>9081586676</t>
         </is>
       </c>
       <c r="F742" s="12" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G742" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H742" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I742" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J742" s="14" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="K742" s="14" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="L742" s="15" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="M742" s="12" t="inlineStr">
         <is>
-          <t>68d3c6acdab36c001342c601</t>
+          <t>6a3a7c3334158200138768eb</t>
         </is>
       </c>
       <c r="N742" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d3c6acdab36c001342c601</t>
+          <t>https://superprofile.bio/vig/6a3a7c3334158200138768eb</t>
         </is>
       </c>
       <c r="O742" s="17" t="inlineStr">
@@ -54364,59 +54364,59 @@
       </c>
       <c r="B743" s="20" t="inlineStr">
         <is>
-          <t>6856668cc5a2ba00132de15a</t>
+          <t>6a4bf7f1f111810013cba5ce</t>
         </is>
       </c>
       <c r="C743" s="20" t="inlineStr">
         <is>
-          <t>eaglesclub</t>
+          <t>insiderpedia</t>
         </is>
       </c>
       <c r="D743" s="19" t="inlineStr">
         <is>
-          <t>thelionstradingclub@gmail.com</t>
+          <t>insiderpedia@gmail.com</t>
         </is>
       </c>
       <c r="E743" s="19" t="inlineStr">
         <is>
-          <t>8708868105</t>
+          <t>8439150506</t>
         </is>
       </c>
       <c r="F743" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="G743" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H743" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I743" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J743" s="21" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="K743" s="21" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="L743" s="22" t="n">
-        <v>2857</v>
+        <v>2874</v>
       </c>
       <c r="M743" s="19" t="inlineStr">
         <is>
-          <t>6857f6d6c357ae0013fa2b9d</t>
+          <t>68d3c6acdab36c001342c601</t>
         </is>
       </c>
       <c r="N743" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6857f6d6c357ae0013fa2b9d</t>
+          <t>https://superprofile.bio/vig/68d3c6acdab36c001342c601</t>
         </is>
       </c>
       <c r="O743" s="24" t="inlineStr">
@@ -54436,22 +54436,22 @@
       </c>
       <c r="B744" s="13" t="inlineStr">
         <is>
-          <t>647d9398dd6b3d0020306128</t>
+          <t>6856668cc5a2ba00132de15a</t>
         </is>
       </c>
       <c r="C744" s="13" t="inlineStr">
         <is>
-          <t>kpinvestment</t>
+          <t>eaglesclub</t>
         </is>
       </c>
       <c r="D744" s="12" t="inlineStr">
         <is>
-          <t>help.kpinvestment@gmail.com</t>
+          <t>thelionstradingclub@gmail.com</t>
         </is>
       </c>
       <c r="E744" s="12" t="inlineStr">
         <is>
-          <t>8160490424</t>
+          <t>8708868105</t>
         </is>
       </c>
       <c r="F744" s="12" t="inlineStr">
@@ -54461,34 +54461,34 @@
       </c>
       <c r="G744" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H744" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I744" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J744" s="14" t="n">
-        <v>2823</v>
+        <v>2857</v>
       </c>
       <c r="K744" s="14" t="n">
-        <v>2823</v>
+        <v>2857</v>
       </c>
       <c r="L744" s="15" t="n">
-        <v>2823</v>
+        <v>2857</v>
       </c>
       <c r="M744" s="12" t="inlineStr">
         <is>
-          <t>64d6fa8fedf0ae001ee54c49</t>
+          <t>6857f6d6c357ae0013fa2b9d</t>
         </is>
       </c>
       <c r="N744" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64d6fa8fedf0ae001ee54c49</t>
+          <t>https://superprofile.bio/vig/6857f6d6c357ae0013fa2b9d</t>
         </is>
       </c>
       <c r="O744" s="17" t="inlineStr">
@@ -54508,22 +54508,22 @@
       </c>
       <c r="B745" s="20" t="inlineStr">
         <is>
-          <t>65535c55ad8cfd001e27b0e3</t>
+          <t>647d9398dd6b3d0020306128</t>
         </is>
       </c>
       <c r="C745" s="20" t="inlineStr">
         <is>
-          <t>derivativetradersameer</t>
+          <t>kpinvestment</t>
         </is>
       </c>
       <c r="D745" s="19" t="inlineStr">
         <is>
-          <t>Samnit573@gmail.com</t>
+          <t>help.kpinvestment@gmail.com</t>
         </is>
       </c>
       <c r="E745" s="19" t="inlineStr">
         <is>
-          <t>7004760817</t>
+          <t>8160490424</t>
         </is>
       </c>
       <c r="F745" s="19" t="inlineStr">
@@ -54533,12 +54533,12 @@
       </c>
       <c r="G745" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H745" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I745" s="20" t="n">
@@ -54555,12 +54555,12 @@
       </c>
       <c r="M745" s="19" t="inlineStr">
         <is>
-          <t>681acdaf8684e10013d2bd41</t>
+          <t>64d6fa8fedf0ae001ee54c49</t>
         </is>
       </c>
       <c r="N745" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/681acdaf8684e10013d2bd41</t>
+          <t>https://superprofile.bio/vig/64d6fa8fedf0ae001ee54c49</t>
         </is>
       </c>
       <c r="O745" s="24" t="inlineStr">
@@ -54580,22 +54580,22 @@
       </c>
       <c r="B746" s="13" t="inlineStr">
         <is>
-          <t>6965edf1903a5c0013d1ccbc</t>
+          <t>65535c55ad8cfd001e27b0e3</t>
         </is>
       </c>
       <c r="C746" s="13" t="inlineStr">
         <is>
-          <t>presenttradingintelugu</t>
+          <t>derivativetradersameer</t>
         </is>
       </c>
       <c r="D746" s="12" t="inlineStr">
         <is>
-          <t>techrepresenttelugu@gmail.com</t>
+          <t>Samnit573@gmail.com</t>
         </is>
       </c>
       <c r="E746" s="12" t="inlineStr">
         <is>
-          <t>9640474466</t>
+          <t>7004760817</t>
         </is>
       </c>
       <c r="F746" s="12" t="inlineStr">
@@ -54605,34 +54605,34 @@
       </c>
       <c r="G746" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H746" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I746" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J746" s="14" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="K746" s="14" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="L746" s="15" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="M746" s="12" t="inlineStr">
         <is>
-          <t>6965f72391331700133f6bae</t>
+          <t>681acdaf8684e10013d2bd41</t>
         </is>
       </c>
       <c r="N746" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6965f72391331700133f6bae</t>
+          <t>https://superprofile.bio/vig/681acdaf8684e10013d2bd41</t>
         </is>
       </c>
       <c r="O746" s="17" t="inlineStr">
@@ -54652,22 +54652,22 @@
       </c>
       <c r="B747" s="20" t="inlineStr">
         <is>
-          <t>64e334e14a24de002b802a74</t>
+          <t>6965edf1903a5c0013d1ccbc</t>
         </is>
       </c>
       <c r="C747" s="20" t="inlineStr">
         <is>
-          <t>sahilmothsra</t>
+          <t>presenttradingintelugu</t>
         </is>
       </c>
       <c r="D747" s="19" t="inlineStr">
         <is>
-          <t>choudharysahiljaat@gmail.com</t>
+          <t>techrepresenttelugu@gmail.com</t>
         </is>
       </c>
       <c r="E747" s="19" t="inlineStr">
         <is>
-          <t>8504924263</t>
+          <t>9640474466</t>
         </is>
       </c>
       <c r="F747" s="19" t="inlineStr">
@@ -54677,12 +54677,12 @@
       </c>
       <c r="G747" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H747" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I747" s="20" t="n">
@@ -54699,12 +54699,12 @@
       </c>
       <c r="M747" s="19" t="inlineStr">
         <is>
-          <t>68c10c093fdf1300136b8a9c</t>
+          <t>6965f72391331700133f6bae</t>
         </is>
       </c>
       <c r="N747" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c10c093fdf1300136b8a9c</t>
+          <t>https://superprofile.bio/vig/6965f72391331700133f6bae</t>
         </is>
       </c>
       <c r="O747" s="24" t="inlineStr">
@@ -54724,22 +54724,22 @@
       </c>
       <c r="B748" s="13" t="inlineStr">
         <is>
-          <t>69f5b2c3bd98df00136c0003</t>
+          <t>64e334e14a24de002b802a74</t>
         </is>
       </c>
       <c r="C748" s="13" t="inlineStr">
         <is>
-          <t>24xaumagnumclub</t>
+          <t>sahilmothsra</t>
         </is>
       </c>
       <c r="D748" s="12" t="inlineStr">
         <is>
-          <t>naturaltaste24@gmail.com</t>
+          <t>choudharysahiljaat@gmail.com</t>
         </is>
       </c>
       <c r="E748" s="12" t="inlineStr">
         <is>
-          <t>7066934772</t>
+          <t>8504924263</t>
         </is>
       </c>
       <c r="F748" s="12" t="inlineStr">
@@ -54749,34 +54749,34 @@
       </c>
       <c r="G748" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H748" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I748" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J748" s="14" t="n">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="K748" s="14" t="n">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="L748" s="15" t="n">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="M748" s="12" t="inlineStr">
         <is>
-          <t>6a91cddf92ea850013003836</t>
+          <t>68c10c093fdf1300136b8a9c</t>
         </is>
       </c>
       <c r="N748" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a91cddf92ea850013003836</t>
+          <t>https://superprofile.bio/vig/68c10c093fdf1300136b8a9c</t>
         </is>
       </c>
       <c r="O748" s="17" t="inlineStr">
@@ -54796,22 +54796,22 @@
       </c>
       <c r="B749" s="20" t="inlineStr">
         <is>
-          <t>673784dcb657dd0013e67533</t>
+          <t>69f5b2c3bd98df00136c0003</t>
         </is>
       </c>
       <c r="C749" s="20" t="inlineStr">
         <is>
-          <t>financewithahujaa</t>
+          <t>24xaumagnumclub</t>
         </is>
       </c>
       <c r="D749" s="19" t="inlineStr">
         <is>
-          <t>ahujarounak4@gmail.com</t>
+          <t>naturaltaste24@gmail.com</t>
         </is>
       </c>
       <c r="E749" s="19" t="inlineStr">
         <is>
-          <t>8847226008</t>
+          <t>7066934772</t>
         </is>
       </c>
       <c r="F749" s="19" t="inlineStr">
@@ -54821,34 +54821,34 @@
       </c>
       <c r="G749" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H749" s="19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I749" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J749" s="21" t="n">
-        <v>2776</v>
+        <v>2820</v>
       </c>
       <c r="K749" s="21" t="n">
-        <v>2776</v>
+        <v>2820</v>
       </c>
       <c r="L749" s="22" t="n">
-        <v>2776</v>
+        <v>2820</v>
       </c>
       <c r="M749" s="19" t="inlineStr">
         <is>
-          <t>6a2ff50665186a00138554e8</t>
+          <t>6a91cddf92ea850013003836</t>
         </is>
       </c>
       <c r="N749" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a2ff50665186a00138554e8</t>
+          <t>https://superprofile.bio/vig/6a91cddf92ea850013003836</t>
         </is>
       </c>
       <c r="O749" s="24" t="inlineStr">
@@ -54868,22 +54868,22 @@
       </c>
       <c r="B750" s="13" t="inlineStr">
         <is>
-          <t>69fb20dbfae26e0013229a6c</t>
+          <t>673784dcb657dd0013e67533</t>
         </is>
       </c>
       <c r="C750" s="13" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>financewithahujaa</t>
         </is>
       </c>
       <c r="D750" s="12" t="inlineStr">
         <is>
-          <t>rupeshbhagat1445@gmail.com</t>
+          <t>ahujarounak4@gmail.com</t>
         </is>
       </c>
       <c r="E750" s="12" t="inlineStr">
         <is>
-          <t>6397113270</t>
+          <t>8847226008</t>
         </is>
       </c>
       <c r="F750" s="12" t="inlineStr">
@@ -54893,34 +54893,34 @@
       </c>
       <c r="G750" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H750" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I750" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J750" s="14" t="n">
-        <v>1061</v>
+        <v>2776</v>
       </c>
       <c r="K750" s="14" t="n">
-        <v>2749</v>
+        <v>2776</v>
       </c>
       <c r="L750" s="15" t="n">
-        <v>1688</v>
+        <v>2776</v>
       </c>
       <c r="M750" s="12" t="inlineStr">
         <is>
-          <t>6a40e3e946bff60013350d9d</t>
+          <t>6a2ff50665186a00138554e8</t>
         </is>
       </c>
       <c r="N750" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
+          <t>https://superprofile.bio/vig/6a2ff50665186a00138554e8</t>
         </is>
       </c>
       <c r="O750" s="17" t="inlineStr">
@@ -54940,22 +54940,22 @@
       </c>
       <c r="B751" s="20" t="inlineStr">
         <is>
-          <t>68efa32deb549e001385d2c4</t>
+          <t>69fb20dbfae26e0013229a6c</t>
         </is>
       </c>
       <c r="C751" s="20" t="inlineStr">
         <is>
-          <t>Mahbub0954</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="D751" s="19" t="inlineStr">
         <is>
-          <t>helperofficial786@gmail.com</t>
+          <t>rupeshbhagat1445@gmail.com</t>
         </is>
       </c>
       <c r="E751" s="19" t="inlineStr">
         <is>
-          <t>7667937751</t>
+          <t>6397113270</t>
         </is>
       </c>
       <c r="F751" s="19" t="inlineStr">
@@ -54965,34 +54965,34 @@
       </c>
       <c r="G751" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H751" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I751" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J751" s="21" t="n">
-        <v>1690</v>
+        <v>1061</v>
       </c>
       <c r="K751" s="21" t="n">
-        <v>2707</v>
+        <v>2749</v>
       </c>
       <c r="L751" s="22" t="n">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="M751" s="19" t="inlineStr">
         <is>
-          <t>68f1b5ebaacf8d0013e01c1e</t>
+          <t>6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="N751" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68f1b5ebaacf8d0013e01c1e</t>
+          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="O751" s="24" t="inlineStr">
@@ -55012,22 +55012,22 @@
       </c>
       <c r="B752" s="13" t="inlineStr">
         <is>
-          <t>6772d84a573cf00013c60e1b</t>
+          <t>68efa32deb549e001385d2c4</t>
         </is>
       </c>
       <c r="C752" s="13" t="inlineStr">
         <is>
-          <t>elliottmasti</t>
+          <t>Mahbub0954</t>
         </is>
       </c>
       <c r="D752" s="12" t="inlineStr">
         <is>
-          <t>vijayvsawant1997@gmail.com</t>
+          <t>helperofficial786@gmail.com</t>
         </is>
       </c>
       <c r="E752" s="12" t="inlineStr">
         <is>
-          <t>9766884324</t>
+          <t>7667937751</t>
         </is>
       </c>
       <c r="F752" s="12" t="inlineStr">
@@ -55037,34 +55037,34 @@
       </c>
       <c r="G752" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H752" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I752" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J752" s="14" t="n">
-        <v>2700</v>
+        <v>1690</v>
       </c>
       <c r="K752" s="14" t="n">
-        <v>2700</v>
+        <v>2707</v>
       </c>
       <c r="L752" s="15" t="n">
-        <v>2700</v>
+        <v>1690</v>
       </c>
       <c r="M752" s="12" t="inlineStr">
         <is>
-          <t>69f1aa36808e890013cacb09</t>
+          <t>68f1b5ebaacf8d0013e01c1e</t>
         </is>
       </c>
       <c r="N752" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f1aa36808e890013cacb09</t>
+          <t>https://superprofile.bio/vig/68f1b5ebaacf8d0013e01c1e</t>
         </is>
       </c>
       <c r="O752" s="17" t="inlineStr">
@@ -55084,22 +55084,22 @@
       </c>
       <c r="B753" s="20" t="inlineStr">
         <is>
-          <t>65ff2645cdd7340013f558ba</t>
+          <t>6772d84a573cf00013c60e1b</t>
         </is>
       </c>
       <c r="C753" s="20" t="inlineStr">
         <is>
-          <t>dgcametpapers</t>
+          <t>elliottmasti</t>
         </is>
       </c>
       <c r="D753" s="19" t="inlineStr">
         <is>
-          <t>examairways@gmail.com</t>
+          <t>vijayvsawant1997@gmail.com</t>
         </is>
       </c>
       <c r="E753" s="19" t="inlineStr">
         <is>
-          <t>9978638833</t>
+          <t>9766884324</t>
         </is>
       </c>
       <c r="F753" s="19" t="inlineStr">
@@ -55109,12 +55109,12 @@
       </c>
       <c r="G753" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H753" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I753" s="20" t="n">
@@ -55131,12 +55131,12 @@
       </c>
       <c r="M753" s="19" t="inlineStr">
         <is>
-          <t>65ff2831cf68d10013420bf5</t>
+          <t>69f1aa36808e890013cacb09</t>
         </is>
       </c>
       <c r="N753" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65ff2831cf68d10013420bf5</t>
+          <t>https://superprofile.bio/vig/69f1aa36808e890013cacb09</t>
         </is>
       </c>
       <c r="O753" s="24" t="inlineStr">
@@ -55156,22 +55156,22 @@
       </c>
       <c r="B754" s="13" t="inlineStr">
         <is>
-          <t>67828321a7f0570013af854a</t>
+          <t>65ff2645cdd7340013f558ba</t>
         </is>
       </c>
       <c r="C754" s="13" t="inlineStr">
         <is>
-          <t>paisavasooltrading</t>
+          <t>dgcametpapers</t>
         </is>
       </c>
       <c r="D754" s="12" t="inlineStr">
         <is>
-          <t>rajkaranrandhawa040@gmail.com</t>
+          <t>examairways@gmail.com</t>
         </is>
       </c>
       <c r="E754" s="12" t="inlineStr">
         <is>
-          <t>8437696904</t>
+          <t>9978638833</t>
         </is>
       </c>
       <c r="F754" s="12" t="inlineStr">
@@ -55181,34 +55181,34 @@
       </c>
       <c r="G754" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H754" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I754" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J754" s="14" t="n">
-        <v>1350</v>
+        <v>2700</v>
       </c>
       <c r="K754" s="14" t="n">
         <v>2700</v>
       </c>
       <c r="L754" s="15" t="n">
-        <v>1350</v>
+        <v>2700</v>
       </c>
       <c r="M754" s="12" t="inlineStr">
         <is>
-          <t>67dd719d04bc180013c1dda8</t>
+          <t>65ff2831cf68d10013420bf5</t>
         </is>
       </c>
       <c r="N754" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67dd719d04bc180013c1dda8</t>
+          <t>https://superprofile.bio/vig/65ff2831cf68d10013420bf5</t>
         </is>
       </c>
       <c r="O754" s="17" t="inlineStr">
@@ -55228,22 +55228,22 @@
       </c>
       <c r="B755" s="20" t="inlineStr">
         <is>
-          <t>68c10b0bfe96b400137da7ed</t>
+          <t>67828321a7f0570013af854a</t>
         </is>
       </c>
       <c r="C755" s="20" t="inlineStr">
         <is>
-          <t>tradewitharvind</t>
+          <t>paisavasooltrading</t>
         </is>
       </c>
       <c r="D755" s="19" t="inlineStr">
         <is>
-          <t>dharmpalverma612@gmail.com</t>
+          <t>rajkaranrandhawa040@gmail.com</t>
         </is>
       </c>
       <c r="E755" s="19" t="inlineStr">
         <is>
-          <t>6375584399</t>
+          <t>8437696904</t>
         </is>
       </c>
       <c r="F755" s="19" t="inlineStr">
@@ -55253,34 +55253,34 @@
       </c>
       <c r="G755" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H755" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I755" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J755" s="21" t="n">
-        <v>2699</v>
+        <v>1350</v>
       </c>
       <c r="K755" s="21" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="L755" s="22" t="n">
-        <v>2699</v>
+        <v>1350</v>
       </c>
       <c r="M755" s="19" t="inlineStr">
         <is>
-          <t>68c11258fe96b400137e95cd</t>
+          <t>67dd719d04bc180013c1dda8</t>
         </is>
       </c>
       <c r="N755" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68c11258fe96b400137e95cd</t>
+          <t>https://superprofile.bio/vig/67dd719d04bc180013c1dda8</t>
         </is>
       </c>
       <c r="O755" s="24" t="inlineStr">
@@ -55300,22 +55300,22 @@
       </c>
       <c r="B756" s="13" t="inlineStr">
         <is>
-          <t>68727633c835ab00139080d1</t>
+          <t>68c10b0bfe96b400137da7ed</t>
         </is>
       </c>
       <c r="C756" s="13" t="inlineStr">
         <is>
-          <t>disciplinetrader</t>
+          <t>tradewitharvind</t>
         </is>
       </c>
       <c r="D756" s="12" t="inlineStr">
         <is>
-          <t>rajesh25129@gmail.com</t>
+          <t>dharmpalverma612@gmail.com</t>
         </is>
       </c>
       <c r="E756" s="12" t="inlineStr">
         <is>
-          <t>7887205206</t>
+          <t>6375584399</t>
         </is>
       </c>
       <c r="F756" s="12" t="inlineStr">
@@ -55325,34 +55325,34 @@
       </c>
       <c r="G756" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H756" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I756" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J756" s="14" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="K756" s="14" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="L756" s="15" t="n">
-        <v>2682</v>
+        <v>2699</v>
       </c>
       <c r="M756" s="12" t="inlineStr">
         <is>
-          <t>696b5f6c469b4600134e3e96</t>
+          <t>68c11258fe96b400137e95cd</t>
         </is>
       </c>
       <c r="N756" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696b5f6c469b4600134e3e96</t>
+          <t>https://superprofile.bio/vig/68c11258fe96b400137e95cd</t>
         </is>
       </c>
       <c r="O756" s="17" t="inlineStr">
@@ -55372,22 +55372,22 @@
       </c>
       <c r="B757" s="20" t="inlineStr">
         <is>
-          <t>6a8352777b63ce00137c8364</t>
+          <t>68727633c835ab00139080d1</t>
         </is>
       </c>
       <c r="C757" s="20" t="inlineStr">
         <is>
-          <t>bootcampadsfusionacademy</t>
+          <t>disciplinetrader</t>
         </is>
       </c>
       <c r="D757" s="19" t="inlineStr">
         <is>
-          <t>hakeemkp111@gmail.com</t>
+          <t>rajesh25129@gmail.com</t>
         </is>
       </c>
       <c r="E757" s="19" t="inlineStr">
         <is>
-          <t>7356250713</t>
+          <t>7887205206</t>
         </is>
       </c>
       <c r="F757" s="19" t="inlineStr">
@@ -55397,34 +55397,34 @@
       </c>
       <c r="G757" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H757" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I757" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J757" s="21" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="K757" s="21" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="L757" s="22" t="n">
-        <v>2538</v>
+        <v>2682</v>
       </c>
       <c r="M757" s="19" t="inlineStr">
         <is>
-          <t>6a8463b0d51eef001369a03c</t>
+          <t>696b5f6c469b4600134e3e96</t>
         </is>
       </c>
       <c r="N757" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8463b0d51eef001369a03c</t>
+          <t>https://superprofile.bio/vig/696b5f6c469b4600134e3e96</t>
         </is>
       </c>
       <c r="O757" s="24" t="inlineStr">
@@ -55444,22 +55444,22 @@
       </c>
       <c r="B758" s="13" t="inlineStr">
         <is>
-          <t>65132965f4d0b1001eba9b70</t>
+          <t>6a8352777b63ce00137c8364</t>
         </is>
       </c>
       <c r="C758" s="13" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>bootcampadsfusionacademy</t>
         </is>
       </c>
       <c r="D758" s="12" t="inlineStr">
         <is>
-          <t>biswalfc@gmail.com</t>
+          <t>hakeemkp111@gmail.com</t>
         </is>
       </c>
       <c r="E758" s="12" t="inlineStr">
         <is>
-          <t>9658251426</t>
+          <t>7356250713</t>
         </is>
       </c>
       <c r="F758" s="12" t="inlineStr">
@@ -55469,7 +55469,7 @@
       </c>
       <c r="G758" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H758" s="12" t="inlineStr">
@@ -55478,25 +55478,25 @@
         </is>
       </c>
       <c r="I758" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J758" s="14" t="n">
-        <v>1134</v>
+        <v>2538</v>
       </c>
       <c r="K758" s="14" t="n">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="L758" s="15" t="n">
-        <v>1401</v>
+        <v>2538</v>
       </c>
       <c r="M758" s="12" t="inlineStr">
         <is>
-          <t>6724fcbd76412b00139f3f43</t>
+          <t>6a8463b0d51eef001369a03c</t>
         </is>
       </c>
       <c r="N758" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
+          <t>https://superprofile.bio/vig/6a8463b0d51eef001369a03c</t>
         </is>
       </c>
       <c r="O758" s="17" t="inlineStr">
@@ -55516,22 +55516,22 @@
       </c>
       <c r="B759" s="20" t="inlineStr">
         <is>
-          <t>64c5ffb8cabc14001e87cfb9</t>
+          <t>65132965f4d0b1001eba9b70</t>
         </is>
       </c>
       <c r="C759" s="20" t="inlineStr">
         <is>
-          <t>StudyNiftyMalayalam</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="D759" s="19" t="inlineStr">
         <is>
-          <t>nairjkrishnan@gmail.com</t>
+          <t>biswalfc@gmail.com</t>
         </is>
       </c>
       <c r="E759" s="19" t="inlineStr">
         <is>
-          <t>7200822228</t>
+          <t>9658251426</t>
         </is>
       </c>
       <c r="F759" s="19" t="inlineStr">
@@ -55541,34 +55541,34 @@
       </c>
       <c r="G759" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H759" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I759" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J759" s="21" t="n">
-        <v>1261</v>
+        <v>1134</v>
       </c>
       <c r="K759" s="21" t="n">
-        <v>2522</v>
+        <v>2535</v>
       </c>
       <c r="L759" s="22" t="n">
-        <v>1261</v>
+        <v>1401</v>
       </c>
       <c r="M759" s="19" t="inlineStr">
         <is>
-          <t>64c60188903653001d97606e</t>
+          <t>6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="N759" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64c60188903653001d97606e</t>
+          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="O759" s="24" t="inlineStr">
@@ -55588,22 +55588,22 @@
       </c>
       <c r="B760" s="13" t="inlineStr">
         <is>
-          <t>667d25dd8fa7f30013731fe4</t>
+          <t>64c5ffb8cabc14001e87cfb9</t>
         </is>
       </c>
       <c r="C760" s="13" t="inlineStr">
         <is>
-          <t>shivayindex</t>
+          <t>StudyNiftyMalayalam</t>
         </is>
       </c>
       <c r="D760" s="12" t="inlineStr">
         <is>
-          <t>shivayindex@gmail.com</t>
+          <t>nairjkrishnan@gmail.com</t>
         </is>
       </c>
       <c r="E760" s="12" t="inlineStr">
         <is>
-          <t>7760026001</t>
+          <t>7200822228</t>
         </is>
       </c>
       <c r="F760" s="12" t="inlineStr">
@@ -55618,29 +55618,29 @@
       </c>
       <c r="H760" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I760" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J760" s="14" t="n">
-        <v>2471</v>
+        <v>1261</v>
       </c>
       <c r="K760" s="14" t="n">
-        <v>2471</v>
+        <v>2522</v>
       </c>
       <c r="L760" s="15" t="n">
-        <v>2471</v>
+        <v>1261</v>
       </c>
       <c r="M760" s="12" t="inlineStr">
         <is>
-          <t>667d3662cdab3f0014414ffe</t>
+          <t>64c60188903653001d97606e</t>
         </is>
       </c>
       <c r="N760" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/667d3662cdab3f0014414ffe</t>
+          <t>https://superprofile.bio/vig/64c60188903653001d97606e</t>
         </is>
       </c>
       <c r="O760" s="17" t="inlineStr">
@@ -55660,22 +55660,22 @@
       </c>
       <c r="B761" s="20" t="inlineStr">
         <is>
-          <t>69955dcab7a14d00134f6967</t>
+          <t>667d25dd8fa7f30013731fe4</t>
         </is>
       </c>
       <c r="C761" s="20" t="inlineStr">
         <is>
-          <t>Kapil4688</t>
+          <t>shivayindex</t>
         </is>
       </c>
       <c r="D761" s="19" t="inlineStr">
         <is>
-          <t>kapilchitroda6@gmail.com</t>
+          <t>shivayindex@gmail.com</t>
         </is>
       </c>
       <c r="E761" s="19" t="inlineStr">
         <is>
-          <t>9913641472</t>
+          <t>7760026001</t>
         </is>
       </c>
       <c r="F761" s="19" t="inlineStr">
@@ -55697,22 +55697,22 @@
         <v>1</v>
       </c>
       <c r="J761" s="21" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="K761" s="21" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="L761" s="22" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="M761" s="19" t="inlineStr">
         <is>
-          <t>69956ec366f1840013fb1972</t>
+          <t>667d3662cdab3f0014414ffe</t>
         </is>
       </c>
       <c r="N761" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69956ec366f1840013fb1972</t>
+          <t>https://superprofile.bio/vig/667d3662cdab3f0014414ffe</t>
         </is>
       </c>
       <c r="O761" s="24" t="inlineStr">
@@ -55732,22 +55732,22 @@
       </c>
       <c r="B762" s="13" t="inlineStr">
         <is>
-          <t>68da3bdc97a50f0013bbbc8e</t>
+          <t>69955dcab7a14d00134f6967</t>
         </is>
       </c>
       <c r="C762" s="13" t="inlineStr">
         <is>
-          <t>KUCH4962</t>
+          <t>Kapil4688</t>
         </is>
       </c>
       <c r="D762" s="12" t="inlineStr">
         <is>
-          <t>ravsahebmarathe55@gmail.com</t>
+          <t>kapilchitroda6@gmail.com</t>
         </is>
       </c>
       <c r="E762" s="12" t="inlineStr">
         <is>
-          <t>9373026105</t>
+          <t>9913641472</t>
         </is>
       </c>
       <c r="F762" s="12" t="inlineStr">
@@ -55757,34 +55757,34 @@
       </c>
       <c r="G762" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H762" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I762" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J762" s="14" t="n">
-        <v>2396</v>
+        <v>2470</v>
       </c>
       <c r="K762" s="14" t="n">
-        <v>2396</v>
+        <v>2470</v>
       </c>
       <c r="L762" s="15" t="n">
-        <v>2396</v>
+        <v>2470</v>
       </c>
       <c r="M762" s="12" t="inlineStr">
         <is>
-          <t>648c4f68a1f806002b0e6ef8</t>
+          <t>69956ec366f1840013fb1972</t>
         </is>
       </c>
       <c r="N762" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/648c4f68a1f806002b0e6ef8</t>
+          <t>https://superprofile.bio/vig/69956ec366f1840013fb1972</t>
         </is>
       </c>
       <c r="O762" s="17" t="inlineStr">
@@ -55804,22 +55804,22 @@
       </c>
       <c r="B763" s="20" t="inlineStr">
         <is>
-          <t>648706794454f1002a6d3e57</t>
+          <t>68da3bdc97a50f0013bbbc8e</t>
         </is>
       </c>
       <c r="C763" s="20" t="inlineStr">
         <is>
-          <t>marketmonks</t>
+          <t>KUCH4962</t>
         </is>
       </c>
       <c r="D763" s="19" t="inlineStr">
         <is>
-          <t>kumarbutsu@gmail.com</t>
+          <t>ravsahebmarathe55@gmail.com</t>
         </is>
       </c>
       <c r="E763" s="19" t="inlineStr">
         <is>
-          <t>9361438983</t>
+          <t>9373026105</t>
         </is>
       </c>
       <c r="F763" s="19" t="inlineStr">
@@ -55829,34 +55829,34 @@
       </c>
       <c r="G763" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H763" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I763" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J763" s="21" t="n">
-        <v>2353</v>
+        <v>2396</v>
       </c>
       <c r="K763" s="21" t="n">
-        <v>2353</v>
+        <v>2396</v>
       </c>
       <c r="L763" s="22" t="n">
-        <v>2353</v>
+        <v>2396</v>
       </c>
       <c r="M763" s="19" t="inlineStr">
         <is>
-          <t>66ec201da9ab8500130442c8</t>
+          <t>648c4f68a1f806002b0e6ef8</t>
         </is>
       </c>
       <c r="N763" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ec201da9ab8500130442c8</t>
+          <t>https://superprofile.bio/vig/648c4f68a1f806002b0e6ef8</t>
         </is>
       </c>
       <c r="O763" s="24" t="inlineStr">
@@ -55876,22 +55876,22 @@
       </c>
       <c r="B764" s="13" t="inlineStr">
         <is>
-          <t>6614c807442e34001b427d04</t>
+          <t>648706794454f1002a6d3e57</t>
         </is>
       </c>
       <c r="C764" s="13" t="inlineStr">
         <is>
-          <t>learningskills2024</t>
+          <t>marketmonks</t>
         </is>
       </c>
       <c r="D764" s="12" t="inlineStr">
         <is>
-          <t>sureshbhobria@gmail.com</t>
+          <t>kumarbutsu@gmail.com</t>
         </is>
       </c>
       <c r="E764" s="12" t="inlineStr">
         <is>
-          <t>9493980572</t>
+          <t>9361438983</t>
         </is>
       </c>
       <c r="F764" s="12" t="inlineStr">
@@ -55901,34 +55901,34 @@
       </c>
       <c r="G764" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H764" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I764" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J764" s="14" t="n">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="K764" s="14" t="n">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="L764" s="15" t="n">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="M764" s="12" t="inlineStr">
         <is>
-          <t>6625fc1f9ef1d500139994c9</t>
+          <t>66ec201da9ab8500130442c8</t>
         </is>
       </c>
       <c r="N764" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6625fc1f9ef1d500139994c9</t>
+          <t>https://superprofile.bio/vig/66ec201da9ab8500130442c8</t>
         </is>
       </c>
       <c r="O764" s="17" t="inlineStr">
@@ -55948,22 +55948,22 @@
       </c>
       <c r="B765" s="20" t="inlineStr">
         <is>
-          <t>637dc4e34f7c40002b76bbc0</t>
+          <t>6614c807442e34001b427d04</t>
         </is>
       </c>
       <c r="C765" s="20" t="inlineStr">
         <is>
-          <t>k989</t>
+          <t>learningskills2024</t>
         </is>
       </c>
       <c r="D765" s="19" t="inlineStr">
         <is>
-          <t>limbachiyakaushik3@gmail.com</t>
+          <t>sureshbhobria@gmail.com</t>
         </is>
       </c>
       <c r="E765" s="19" t="inlineStr">
         <is>
-          <t>9879402061</t>
+          <t>9493980572</t>
         </is>
       </c>
       <c r="F765" s="19" t="inlineStr">
@@ -55973,34 +55973,34 @@
       </c>
       <c r="G765" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H765" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I765" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J765" s="21" t="n">
-        <v>2248</v>
+        <v>2352</v>
       </c>
       <c r="K765" s="21" t="n">
-        <v>2248</v>
+        <v>2352</v>
       </c>
       <c r="L765" s="22" t="n">
-        <v>2248</v>
+        <v>2352</v>
       </c>
       <c r="M765" s="19" t="inlineStr">
         <is>
-          <t>65b26a00d9f5df001eb963f4</t>
+          <t>6625fc1f9ef1d500139994c9</t>
         </is>
       </c>
       <c r="N765" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65b26a00d9f5df001eb963f4</t>
+          <t>https://superprofile.bio/vig/6625fc1f9ef1d500139994c9</t>
         </is>
       </c>
       <c r="O765" s="24" t="inlineStr">
@@ -56020,22 +56020,22 @@
       </c>
       <c r="B766" s="13" t="inlineStr">
         <is>
-          <t>67ec127cbca74f0013a6db1b</t>
+          <t>637dc4e34f7c40002b76bbc0</t>
         </is>
       </c>
       <c r="C766" s="13" t="inlineStr">
         <is>
-          <t>financewithajay</t>
+          <t>k989</t>
         </is>
       </c>
       <c r="D766" s="12" t="inlineStr">
         <is>
-          <t>contact.financewithajay@gmail.com</t>
+          <t>limbachiyakaushik3@gmail.com</t>
         </is>
       </c>
       <c r="E766" s="12" t="inlineStr">
         <is>
-          <t>9772539711</t>
+          <t>9879402061</t>
         </is>
       </c>
       <c r="F766" s="12" t="inlineStr">
@@ -56045,34 +56045,34 @@
       </c>
       <c r="G766" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H766" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I766" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J766" s="14" t="n">
-        <v>2241</v>
+        <v>2248</v>
       </c>
       <c r="K766" s="14" t="n">
-        <v>2241</v>
+        <v>2248</v>
       </c>
       <c r="L766" s="15" t="n">
-        <v>2241</v>
+        <v>2248</v>
       </c>
       <c r="M766" s="12" t="inlineStr">
         <is>
-          <t>6a23e5e47e49330013137085</t>
+          <t>65b26a00d9f5df001eb963f4</t>
         </is>
       </c>
       <c r="N766" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a23e5e47e49330013137085</t>
+          <t>https://superprofile.bio/vig/65b26a00d9f5df001eb963f4</t>
         </is>
       </c>
       <c r="O766" s="17" t="inlineStr">
@@ -56092,22 +56092,22 @@
       </c>
       <c r="B767" s="20" t="inlineStr">
         <is>
-          <t>659208105c801e06f023a189</t>
+          <t>67ec127cbca74f0013a6db1b</t>
         </is>
       </c>
       <c r="C767" s="20" t="inlineStr">
         <is>
-          <t>upscnewspaper</t>
+          <t>financewithajay</t>
         </is>
       </c>
       <c r="D767" s="19" t="inlineStr">
         <is>
-          <t>lokizircon@gmail.com</t>
+          <t>contact.financewithajay@gmail.com</t>
         </is>
       </c>
       <c r="E767" s="19" t="inlineStr">
         <is>
-          <t>8076501613</t>
+          <t>9772539711</t>
         </is>
       </c>
       <c r="F767" s="19" t="inlineStr">
@@ -56122,29 +56122,29 @@
       </c>
       <c r="H767" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I767" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J767" s="21" t="n">
-        <v>1156</v>
+        <v>2241</v>
       </c>
       <c r="K767" s="21" t="n">
-        <v>2223</v>
+        <v>2241</v>
       </c>
       <c r="L767" s="22" t="n">
-        <v>1156</v>
+        <v>2241</v>
       </c>
       <c r="M767" s="19" t="inlineStr">
         <is>
-          <t>678b74430410b00014115634</t>
+          <t>6a23e5e47e49330013137085</t>
         </is>
       </c>
       <c r="N767" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/678b74430410b00014115634</t>
+          <t>https://superprofile.bio/vig/6a23e5e47e49330013137085</t>
         </is>
       </c>
       <c r="O767" s="24" t="inlineStr">
@@ -56164,22 +56164,22 @@
       </c>
       <c r="B768" s="13" t="inlineStr">
         <is>
-          <t>62f60f34678fd77b3dabf980</t>
+          <t>659208105c801e06f023a189</t>
         </is>
       </c>
       <c r="C768" s="13" t="inlineStr">
         <is>
-          <t>fogyan</t>
+          <t>upscnewspaper</t>
         </is>
       </c>
       <c r="D768" s="12" t="inlineStr">
         <is>
-          <t>mayur22295@gmail.com</t>
+          <t>lokizircon@gmail.com</t>
         </is>
       </c>
       <c r="E768" s="12" t="inlineStr">
         <is>
-          <t>7041087129</t>
+          <t>8076501613</t>
         </is>
       </c>
       <c r="F768" s="12" t="inlineStr">
@@ -56189,34 +56189,34 @@
       </c>
       <c r="G768" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H768" s="12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I768" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J768" s="14" t="n">
-        <v>2194</v>
+        <v>1156</v>
       </c>
       <c r="K768" s="14" t="n">
-        <v>2194</v>
+        <v>2223</v>
       </c>
       <c r="L768" s="15" t="n">
-        <v>2194</v>
+        <v>1156</v>
       </c>
       <c r="M768" s="12" t="inlineStr">
         <is>
-          <t>6676bedfcfd9310013c8a087</t>
+          <t>678b74430410b00014115634</t>
         </is>
       </c>
       <c r="N768" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6676bedfcfd9310013c8a087</t>
+          <t>https://superprofile.bio/vig/678b74430410b00014115634</t>
         </is>
       </c>
       <c r="O768" s="17" t="inlineStr">
@@ -56236,22 +56236,22 @@
       </c>
       <c r="B769" s="20" t="inlineStr">
         <is>
-          <t>64a6df40de08fb0020605733</t>
+          <t>62f60f34678fd77b3dabf980</t>
         </is>
       </c>
       <c r="C769" s="20" t="inlineStr">
         <is>
-          <t>priyanka8090</t>
+          <t>fogyan</t>
         </is>
       </c>
       <c r="D769" s="19" t="inlineStr">
         <is>
-          <t>drtarunkashyap123@gmail.com</t>
+          <t>mayur22295@gmail.com</t>
         </is>
       </c>
       <c r="E769" s="19" t="inlineStr">
         <is>
-          <t>9355701148</t>
+          <t>7041087129</t>
         </is>
       </c>
       <c r="F769" s="19" t="inlineStr">
@@ -56261,34 +56261,34 @@
       </c>
       <c r="G769" s="19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H769" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I769" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J769" s="21" t="n">
-        <v>1080</v>
+        <v>2194</v>
       </c>
       <c r="K769" s="21" t="n">
-        <v>2160</v>
+        <v>2194</v>
       </c>
       <c r="L769" s="22" t="n">
-        <v>1080</v>
+        <v>2194</v>
       </c>
       <c r="M769" s="19" t="inlineStr">
         <is>
-          <t>64a8db7aee58cc002a13fe63</t>
+          <t>6676bedfcfd9310013c8a087</t>
         </is>
       </c>
       <c r="N769" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64a8db7aee58cc002a13fe63</t>
+          <t>https://superprofile.bio/vig/6676bedfcfd9310013c8a087</t>
         </is>
       </c>
       <c r="O769" s="24" t="inlineStr">
@@ -56308,22 +56308,22 @@
       </c>
       <c r="B770" s="13" t="inlineStr">
         <is>
-          <t>659b990d57f865001e1efa98</t>
+          <t>64a6df40de08fb0020605733</t>
         </is>
       </c>
       <c r="C770" s="13" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>priyanka8090</t>
         </is>
       </c>
       <c r="D770" s="12" t="inlineStr">
         <is>
-          <t>vishalgaikwad91888@gmail.com</t>
+          <t>drtarunkashyap123@gmail.com</t>
         </is>
       </c>
       <c r="E770" s="12" t="inlineStr">
         <is>
-          <t>7040119684</t>
+          <t>9355701148</t>
         </is>
       </c>
       <c r="F770" s="12" t="inlineStr">
@@ -56333,34 +56333,34 @@
       </c>
       <c r="G770" s="12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H770" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I770" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J770" s="14" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="K770" s="14" t="n">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="L770" s="15" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="M770" s="12" t="inlineStr">
         <is>
-          <t>69f59765a8c2c60013505029</t>
+          <t>64a8db7aee58cc002a13fe63</t>
         </is>
       </c>
       <c r="N770" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
+          <t>https://superprofile.bio/vig/64a8db7aee58cc002a13fe63</t>
         </is>
       </c>
       <c r="O770" s="17" t="inlineStr">
@@ -56380,22 +56380,22 @@
       </c>
       <c r="B771" s="20" t="inlineStr">
         <is>
-          <t>6845179e4fe31b001365bac0</t>
+          <t>659b990d57f865001e1efa98</t>
         </is>
       </c>
       <c r="C771" s="20" t="inlineStr">
         <is>
-          <t>lucifer0182</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="D771" s="19" t="inlineStr">
         <is>
-          <t>lucifer927974@gmail.com</t>
+          <t>vishalgaikwad91888@gmail.com</t>
         </is>
       </c>
       <c r="E771" s="19" t="inlineStr">
         <is>
-          <t>7781981785</t>
+          <t>7040119684</t>
         </is>
       </c>
       <c r="F771" s="19" t="inlineStr">
@@ -56405,34 +56405,34 @@
       </c>
       <c r="G771" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H771" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I771" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J771" s="21" t="n">
-        <v>2135</v>
+        <v>1078</v>
       </c>
       <c r="K771" s="21" t="n">
-        <v>2135</v>
+        <v>2156</v>
       </c>
       <c r="L771" s="22" t="n">
-        <v>2135</v>
+        <v>1078</v>
       </c>
       <c r="M771" s="19" t="inlineStr">
         <is>
-          <t>69cb2a436442e6001351a223</t>
+          <t>69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="N771" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69cb2a436442e6001351a223</t>
+          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="O771" s="24" t="inlineStr">
@@ -56452,22 +56452,22 @@
       </c>
       <c r="B772" s="13" t="inlineStr">
         <is>
-          <t>6790d7e59cdd18001364c325</t>
+          <t>6845179e4fe31b001365bac0</t>
         </is>
       </c>
       <c r="C772" s="13" t="inlineStr">
         <is>
-          <t>tga</t>
+          <t>lucifer0182</t>
         </is>
       </c>
       <c r="D772" s="12" t="inlineStr">
         <is>
-          <t>traders.guide2025@gmail.com</t>
+          <t>lucifer927974@gmail.com</t>
         </is>
       </c>
       <c r="E772" s="12" t="inlineStr">
         <is>
-          <t>9106193633</t>
+          <t>7781981785</t>
         </is>
       </c>
       <c r="F772" s="12" t="inlineStr">
@@ -56477,34 +56477,34 @@
       </c>
       <c r="G772" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H772" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I772" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J772" s="14" t="n">
-        <v>2128</v>
+        <v>2135</v>
       </c>
       <c r="K772" s="14" t="n">
-        <v>2128</v>
+        <v>2135</v>
       </c>
       <c r="L772" s="15" t="n">
-        <v>2128</v>
+        <v>2135</v>
       </c>
       <c r="M772" s="12" t="inlineStr">
         <is>
-          <t>69e73f8208572d0014eb9576</t>
+          <t>69cb2a436442e6001351a223</t>
         </is>
       </c>
       <c r="N772" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e73f8208572d0014eb9576</t>
+          <t>https://superprofile.bio/vig/69cb2a436442e6001351a223</t>
         </is>
       </c>
       <c r="O772" s="17" t="inlineStr">
@@ -56524,22 +56524,22 @@
       </c>
       <c r="B773" s="20" t="inlineStr">
         <is>
-          <t>636c3a1fac6bc6003dbb97c3</t>
+          <t>6790d7e59cdd18001364c325</t>
         </is>
       </c>
       <c r="C773" s="20" t="inlineStr">
         <is>
-          <t>pisignals</t>
+          <t>tga</t>
         </is>
       </c>
       <c r="D773" s="19" t="inlineStr">
         <is>
-          <t>support@pisignals.com</t>
+          <t>traders.guide2025@gmail.com</t>
         </is>
       </c>
       <c r="E773" s="19" t="inlineStr">
         <is>
-          <t>8087686830</t>
+          <t>9106193633</t>
         </is>
       </c>
       <c r="F773" s="19" t="inlineStr">
@@ -56549,34 +56549,34 @@
       </c>
       <c r="G773" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H773" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I773" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J773" s="21" t="n">
-        <v>2100</v>
+        <v>2128</v>
       </c>
       <c r="K773" s="21" t="n">
-        <v>2100</v>
+        <v>2128</v>
       </c>
       <c r="L773" s="22" t="n">
-        <v>2100</v>
+        <v>2128</v>
       </c>
       <c r="M773" s="19" t="inlineStr">
         <is>
-          <t>6371e1aeb9bdd4003d6c0bdf</t>
+          <t>69e73f8208572d0014eb9576</t>
         </is>
       </c>
       <c r="N773" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6371e1aeb9bdd4003d6c0bdf</t>
+          <t>https://superprofile.bio/vig/69e73f8208572d0014eb9576</t>
         </is>
       </c>
       <c r="O773" s="24" t="inlineStr">
@@ -56596,22 +56596,22 @@
       </c>
       <c r="B774" s="13" t="inlineStr">
         <is>
-          <t>6aa24ef0091d0900138c1b5c</t>
+          <t>636c3a1fac6bc6003dbb97c3</t>
         </is>
       </c>
       <c r="C774" s="13" t="inlineStr">
         <is>
-          <t>Rinku8687</t>
+          <t>pisignals</t>
         </is>
       </c>
       <c r="D774" s="12" t="inlineStr">
         <is>
-          <t>aaravboss7339@gmail.com</t>
+          <t>support@pisignals.com</t>
         </is>
       </c>
       <c r="E774" s="12" t="inlineStr">
         <is>
-          <t>7891541147</t>
+          <t>8087686830</t>
         </is>
       </c>
       <c r="F774" s="12" t="inlineStr">
@@ -56621,34 +56621,34 @@
       </c>
       <c r="G774" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H774" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I774" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J774" s="14" t="n">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="K774" s="14" t="n">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="L774" s="15" t="n">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="M774" s="12" t="inlineStr">
         <is>
-          <t>6aa25748b9d37a00131b442b</t>
+          <t>6371e1aeb9bdd4003d6c0bdf</t>
         </is>
       </c>
       <c r="N774" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6aa25748b9d37a00131b442b</t>
+          <t>https://superprofile.bio/vig/6371e1aeb9bdd4003d6c0bdf</t>
         </is>
       </c>
       <c r="O774" s="17" t="inlineStr">
@@ -56668,22 +56668,22 @@
       </c>
       <c r="B775" s="20" t="inlineStr">
         <is>
-          <t>699f1e6675134300132e01e6</t>
+          <t>6aa24ef0091d0900138c1b5c</t>
         </is>
       </c>
       <c r="C775" s="20" t="inlineStr">
         <is>
-          <t>traderpihuu</t>
+          <t>Rinku8687</t>
         </is>
       </c>
       <c r="D775" s="19" t="inlineStr">
         <is>
-          <t>pihulearningjoin@gmail.com</t>
+          <t>aaravboss7339@gmail.com</t>
         </is>
       </c>
       <c r="E775" s="19" t="inlineStr">
         <is>
-          <t>6393912567</t>
+          <t>7891541147</t>
         </is>
       </c>
       <c r="F775" s="19" t="inlineStr">
@@ -56693,34 +56693,34 @@
       </c>
       <c r="G775" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H775" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I775" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J775" s="21" t="n">
-        <v>2057</v>
+        <v>2097</v>
       </c>
       <c r="K775" s="21" t="n">
-        <v>2057</v>
+        <v>2097</v>
       </c>
       <c r="L775" s="22" t="n">
-        <v>2057</v>
+        <v>2097</v>
       </c>
       <c r="M775" s="19" t="inlineStr">
         <is>
-          <t>69bbaa83098b8c00135db027</t>
+          <t>6aa25748b9d37a00131b442b</t>
         </is>
       </c>
       <c r="N775" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69bbaa83098b8c00135db027</t>
+          <t>https://superprofile.bio/vig/6aa25748b9d37a00131b442b</t>
         </is>
       </c>
       <c r="O775" s="24" t="inlineStr">
@@ -56740,22 +56740,22 @@
       </c>
       <c r="B776" s="13" t="inlineStr">
         <is>
-          <t>64968e0c486e6b0020225310</t>
+          <t>699f1e6675134300132e01e6</t>
         </is>
       </c>
       <c r="C776" s="13" t="inlineStr">
         <is>
-          <t>radhikabhabhi</t>
+          <t>traderpihuu</t>
         </is>
       </c>
       <c r="D776" s="12" t="inlineStr">
         <is>
-          <t>jakhasar.2020@gmail.com</t>
+          <t>pihulearningjoin@gmail.com</t>
         </is>
       </c>
       <c r="E776" s="12" t="inlineStr">
         <is>
-          <t>8239505550</t>
+          <t>6393912567</t>
         </is>
       </c>
       <c r="F776" s="12" t="inlineStr">
@@ -56765,34 +56765,34 @@
       </c>
       <c r="G776" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H776" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I776" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J776" s="14" t="n">
-        <v>2050</v>
+        <v>2057</v>
       </c>
       <c r="K776" s="14" t="n">
-        <v>2050</v>
+        <v>2057</v>
       </c>
       <c r="L776" s="15" t="n">
-        <v>2050</v>
+        <v>2057</v>
       </c>
       <c r="M776" s="12" t="inlineStr">
         <is>
-          <t>6a87e7b179d74e0013dcd3e5</t>
+          <t>69bbaa83098b8c00135db027</t>
         </is>
       </c>
       <c r="N776" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a87e7b179d74e0013dcd3e5</t>
+          <t>https://superprofile.bio/vig/69bbaa83098b8c00135db027</t>
         </is>
       </c>
       <c r="O776" s="17" t="inlineStr">
@@ -56812,22 +56812,22 @@
       </c>
       <c r="B777" s="20" t="inlineStr">
         <is>
-          <t>69b99c4bd4535b00137cb627</t>
+          <t>64968e0c486e6b0020225310</t>
         </is>
       </c>
       <c r="C777" s="20" t="inlineStr">
         <is>
-          <t>lunarkio</t>
+          <t>radhikabhabhi</t>
         </is>
       </c>
       <c r="D777" s="19" t="inlineStr">
         <is>
-          <t>ahujadaksh2000@gmail.com</t>
+          <t>jakhasar.2020@gmail.com</t>
         </is>
       </c>
       <c r="E777" s="19" t="inlineStr">
         <is>
-          <t>7986554065</t>
+          <t>8239505550</t>
         </is>
       </c>
       <c r="F777" s="19" t="inlineStr">
@@ -56837,34 +56837,34 @@
       </c>
       <c r="G777" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H777" s="19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I777" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J777" s="21" t="n">
-        <v>2021</v>
+        <v>2050</v>
       </c>
       <c r="K777" s="21" t="n">
-        <v>2021</v>
+        <v>2050</v>
       </c>
       <c r="L777" s="22" t="n">
-        <v>2021</v>
+        <v>2050</v>
       </c>
       <c r="M777" s="19" t="inlineStr">
         <is>
-          <t>6a5e8c86b4f0e8001420ee62</t>
+          <t>6a87e7b179d74e0013dcd3e5</t>
         </is>
       </c>
       <c r="N777" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5e8c86b4f0e8001420ee62</t>
+          <t>https://superprofile.bio/vig/6a87e7b179d74e0013dcd3e5</t>
         </is>
       </c>
       <c r="O777" s="24" t="inlineStr">
@@ -56884,22 +56884,22 @@
       </c>
       <c r="B778" s="13" t="inlineStr">
         <is>
-          <t>634fc5237ae31a1e35705dde</t>
+          <t>69b99c4bd4535b00137cb627</t>
         </is>
       </c>
       <c r="C778" s="13" t="inlineStr">
         <is>
-          <t>alix48</t>
+          <t>lunarkio</t>
         </is>
       </c>
       <c r="D778" s="12" t="inlineStr">
         <is>
-          <t>hhkdhhkskdj@gmail.com</t>
+          <t>ahujadaksh2000@gmail.com</t>
         </is>
       </c>
       <c r="E778" s="12" t="inlineStr">
         <is>
-          <t>8317008716</t>
+          <t>7986554065</t>
         </is>
       </c>
       <c r="F778" s="12" t="inlineStr">
@@ -56909,34 +56909,34 @@
       </c>
       <c r="G778" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H778" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I778" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J778" s="14" t="n">
-        <v>1992</v>
+        <v>2021</v>
       </c>
       <c r="K778" s="14" t="n">
-        <v>1992</v>
+        <v>2021</v>
       </c>
       <c r="L778" s="15" t="n">
-        <v>1992</v>
+        <v>2021</v>
       </c>
       <c r="M778" s="12" t="inlineStr">
         <is>
-          <t>64976f84a4a91600204f143b</t>
+          <t>6a5e8c86b4f0e8001420ee62</t>
         </is>
       </c>
       <c r="N778" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64976f84a4a91600204f143b</t>
+          <t>https://superprofile.bio/vig/6a5e8c86b4f0e8001420ee62</t>
         </is>
       </c>
       <c r="O778" s="17" t="inlineStr">
@@ -56956,22 +56956,22 @@
       </c>
       <c r="B779" s="20" t="inlineStr">
         <is>
-          <t>69072bb4ae00150013d00d28</t>
+          <t>634fc5237ae31a1e35705dde</t>
         </is>
       </c>
       <c r="C779" s="20" t="inlineStr">
         <is>
-          <t>thelearning</t>
+          <t>alix48</t>
         </is>
       </c>
       <c r="D779" s="19" t="inlineStr">
         <is>
-          <t>xenik31898@lovleo.com</t>
+          <t>hhkdhhkskdj@gmail.com</t>
         </is>
       </c>
       <c r="E779" s="19" t="inlineStr">
         <is>
-          <t>9669648431</t>
+          <t>8317008716</t>
         </is>
       </c>
       <c r="F779" s="19" t="inlineStr">
@@ -56981,34 +56981,34 @@
       </c>
       <c r="G779" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H779" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I779" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J779" s="21" t="n">
-        <v>1977</v>
+        <v>1992</v>
       </c>
       <c r="K779" s="21" t="n">
-        <v>1977</v>
+        <v>1992</v>
       </c>
       <c r="L779" s="22" t="n">
-        <v>1977</v>
+        <v>1992</v>
       </c>
       <c r="M779" s="19" t="inlineStr">
         <is>
-          <t>67ee600f6cfba0001396a350</t>
+          <t>64976f84a4a91600204f143b</t>
         </is>
       </c>
       <c r="N779" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ee600f6cfba0001396a350</t>
+          <t>https://superprofile.bio/vig/64976f84a4a91600204f143b</t>
         </is>
       </c>
       <c r="O779" s="24" t="inlineStr">
@@ -57028,22 +57028,22 @@
       </c>
       <c r="B780" s="13" t="inlineStr">
         <is>
-          <t>67dd417c2e848e001306dae2</t>
+          <t>69072bb4ae00150013d00d28</t>
         </is>
       </c>
       <c r="C780" s="13" t="inlineStr">
         <is>
-          <t>kamakshiraheja</t>
+          <t>thelearning</t>
         </is>
       </c>
       <c r="D780" s="12" t="inlineStr">
         <is>
-          <t>kamakshidhameja@gmail.com</t>
+          <t>xenik31898@lovleo.com</t>
         </is>
       </c>
       <c r="E780" s="12" t="inlineStr">
         <is>
-          <t>9819908232</t>
+          <t>9669648431</t>
         </is>
       </c>
       <c r="F780" s="12" t="inlineStr">
@@ -57065,22 +57065,22 @@
         <v>1</v>
       </c>
       <c r="J780" s="14" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="K780" s="14" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="L780" s="15" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="M780" s="12" t="inlineStr">
         <is>
-          <t>693a7b20cd08d200134e762f</t>
+          <t>67ee600f6cfba0001396a350</t>
         </is>
       </c>
       <c r="N780" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/693a7b20cd08d200134e762f</t>
+          <t>https://superprofile.bio/vig/67ee600f6cfba0001396a350</t>
         </is>
       </c>
       <c r="O780" s="17" t="inlineStr">
@@ -57100,22 +57100,22 @@
       </c>
       <c r="B781" s="20" t="inlineStr">
         <is>
-          <t>66461a4a2526160013e088af</t>
+          <t>67dd417c2e848e001306dae2</t>
         </is>
       </c>
       <c r="C781" s="20" t="inlineStr">
         <is>
-          <t>vanaantmultiverse</t>
+          <t>kamakshiraheja</t>
         </is>
       </c>
       <c r="D781" s="19" t="inlineStr">
         <is>
-          <t>divinetarot808@gmail.com</t>
+          <t>kamakshidhameja@gmail.com</t>
         </is>
       </c>
       <c r="E781" s="19" t="inlineStr">
         <is>
-          <t>7017530919</t>
+          <t>9819908232</t>
         </is>
       </c>
       <c r="F781" s="19" t="inlineStr">
@@ -57125,12 +57125,12 @@
       </c>
       <c r="G781" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H781" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I781" s="20" t="n">
@@ -57147,12 +57147,12 @@
       </c>
       <c r="M781" s="19" t="inlineStr">
         <is>
-          <t>66e80a09e49fa70013df7e9f</t>
+          <t>693a7b20cd08d200134e762f</t>
         </is>
       </c>
       <c r="N781" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66e80a09e49fa70013df7e9f</t>
+          <t>https://superprofile.bio/vig/693a7b20cd08d200134e762f</t>
         </is>
       </c>
       <c r="O781" s="24" t="inlineStr">
@@ -57172,22 +57172,22 @@
       </c>
       <c r="B782" s="13" t="inlineStr">
         <is>
-          <t>67fdc8680a272d0013949011</t>
+          <t>66461a4a2526160013e088af</t>
         </is>
       </c>
       <c r="C782" s="13" t="inlineStr">
         <is>
-          <t>madhavbanknifty</t>
+          <t>vanaantmultiverse</t>
         </is>
       </c>
       <c r="D782" s="12" t="inlineStr">
         <is>
-          <t>ashvinbarot92@gmail.com</t>
+          <t>divinetarot808@gmail.com</t>
         </is>
       </c>
       <c r="E782" s="12" t="inlineStr">
         <is>
-          <t>7698089313</t>
+          <t>7017530919</t>
         </is>
       </c>
       <c r="F782" s="12" t="inlineStr">
@@ -57197,34 +57197,34 @@
       </c>
       <c r="G782" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H782" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I782" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J782" s="14" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="K782" s="14" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="L782" s="15" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
       <c r="M782" s="12" t="inlineStr">
         <is>
-          <t>68073ef7f0df960013f5afe4</t>
+          <t>66e80a09e49fa70013df7e9f</t>
         </is>
       </c>
       <c r="N782" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68073ef7f0df960013f5afe4</t>
+          <t>https://superprofile.bio/vig/66e80a09e49fa70013df7e9f</t>
         </is>
       </c>
       <c r="O782" s="17" t="inlineStr">
@@ -57244,59 +57244,59 @@
       </c>
       <c r="B783" s="20" t="inlineStr">
         <is>
-          <t>69a2adacccc9e60013257a64</t>
+          <t>67fdc8680a272d0013949011</t>
         </is>
       </c>
       <c r="C783" s="20" t="inlineStr">
         <is>
-          <t>teyesi</t>
+          <t>madhavbanknifty</t>
         </is>
       </c>
       <c r="D783" s="19" t="inlineStr">
         <is>
-          <t>stocktrader0050@gmail.com</t>
+          <t>ashvinbarot92@gmail.com</t>
         </is>
       </c>
       <c r="E783" s="19" t="inlineStr">
         <is>
-          <t>9096857617</t>
+          <t>7698089313</t>
         </is>
       </c>
       <c r="F783" s="19" t="inlineStr">
         <is>
-          <t>Mohit Singh</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G783" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H783" s="19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I783" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J783" s="21" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="K783" s="21" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="L783" s="22" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="M783" s="19" t="inlineStr">
         <is>
-          <t>6a133abc88bf0a0013e0af7b</t>
+          <t>68073ef7f0df960013f5afe4</t>
         </is>
       </c>
       <c r="N783" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a133abc88bf0a0013e0af7b</t>
+          <t>https://superprofile.bio/vig/68073ef7f0df960013f5afe4</t>
         </is>
       </c>
       <c r="O783" s="24" t="inlineStr">
@@ -57316,59 +57316,59 @@
       </c>
       <c r="B784" s="13" t="inlineStr">
         <is>
-          <t>650d7d75f8c83a001d1a9b22</t>
+          <t>69a2adacccc9e60013257a64</t>
         </is>
       </c>
       <c r="C784" s="13" t="inlineStr">
         <is>
-          <t>priceactioncourse</t>
+          <t>teyesi</t>
         </is>
       </c>
       <c r="D784" s="12" t="inlineStr">
         <is>
-          <t>theplutotv@gmail.com</t>
+          <t>stocktrader0050@gmail.com</t>
         </is>
       </c>
       <c r="E784" s="12" t="inlineStr">
         <is>
-          <t>9625222340</t>
+          <t>9096857617</t>
         </is>
       </c>
       <c r="F784" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mohit Singh</t>
         </is>
       </c>
       <c r="G784" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H784" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I784" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J784" s="14" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="K784" s="14" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="L784" s="15" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="M784" s="12" t="inlineStr">
         <is>
-          <t>6627984036843f001375093b</t>
+          <t>6a133abc88bf0a0013e0af7b</t>
         </is>
       </c>
       <c r="N784" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6627984036843f001375093b</t>
+          <t>https://superprofile.bio/vig/6a133abc88bf0a0013e0af7b</t>
         </is>
       </c>
       <c r="O784" s="17" t="inlineStr">
@@ -57388,22 +57388,22 @@
       </c>
       <c r="B785" s="20" t="inlineStr">
         <is>
-          <t>656404ed5929eb0029d9df20</t>
+          <t>650d7d75f8c83a001d1a9b22</t>
         </is>
       </c>
       <c r="C785" s="20" t="inlineStr">
         <is>
-          <t>TheOutlook</t>
+          <t>priceactioncourse</t>
         </is>
       </c>
       <c r="D785" s="19" t="inlineStr">
         <is>
-          <t>Gdu1618@gmail.com</t>
+          <t>theplutotv@gmail.com</t>
         </is>
       </c>
       <c r="E785" s="19" t="inlineStr">
         <is>
-          <t>8360942366</t>
+          <t>9625222340</t>
         </is>
       </c>
       <c r="F785" s="19" t="inlineStr">
@@ -57425,22 +57425,22 @@
         <v>1</v>
       </c>
       <c r="J785" s="21" t="n">
-        <v>1928</v>
+        <v>1940</v>
       </c>
       <c r="K785" s="21" t="n">
-        <v>1928</v>
+        <v>1940</v>
       </c>
       <c r="L785" s="22" t="n">
-        <v>1928</v>
+        <v>1940</v>
       </c>
       <c r="M785" s="19" t="inlineStr">
         <is>
-          <t>6992e4fd0fc07c0013dceef5</t>
+          <t>6627984036843f001375093b</t>
         </is>
       </c>
       <c r="N785" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6992e4fd0fc07c0013dceef5</t>
+          <t>https://superprofile.bio/vig/6627984036843f001375093b</t>
         </is>
       </c>
       <c r="O785" s="24" t="inlineStr">
@@ -57460,22 +57460,22 @@
       </c>
       <c r="B786" s="13" t="inlineStr">
         <is>
-          <t>65142047830114001e03f40a</t>
+          <t>656404ed5929eb0029d9df20</t>
         </is>
       </c>
       <c r="C786" s="13" t="inlineStr">
         <is>
-          <t>experttrader8950</t>
+          <t>TheOutlook</t>
         </is>
       </c>
       <c r="D786" s="12" t="inlineStr">
         <is>
-          <t>ravideswal6693@gmail.com</t>
+          <t>Gdu1618@gmail.com</t>
         </is>
       </c>
       <c r="E786" s="12" t="inlineStr">
         <is>
-          <t>8076772077</t>
+          <t>8360942366</t>
         </is>
       </c>
       <c r="F786" s="12" t="inlineStr">
@@ -57485,12 +57485,12 @@
       </c>
       <c r="G786" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H786" s="12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I786" s="13" t="n">
@@ -57507,12 +57507,12 @@
       </c>
       <c r="M786" s="12" t="inlineStr">
         <is>
-          <t>65142310fafe6b001d7a5d54</t>
+          <t>6992e4fd0fc07c0013dceef5</t>
         </is>
       </c>
       <c r="N786" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65142310fafe6b001d7a5d54</t>
+          <t>https://superprofile.bio/vig/6992e4fd0fc07c0013dceef5</t>
         </is>
       </c>
       <c r="O786" s="17" t="inlineStr">
@@ -57532,22 +57532,22 @@
       </c>
       <c r="B787" s="20" t="inlineStr">
         <is>
-          <t>6799b5fe5229a200134ae372</t>
+          <t>65142047830114001e03f40a</t>
         </is>
       </c>
       <c r="C787" s="20" t="inlineStr">
         <is>
-          <t>zerohero110</t>
+          <t>experttrader8950</t>
         </is>
       </c>
       <c r="D787" s="19" t="inlineStr">
         <is>
-          <t>zerheropremium230@gmail.com</t>
+          <t>ravideswal6693@gmail.com</t>
         </is>
       </c>
       <c r="E787" s="19" t="inlineStr">
         <is>
-          <t>9166230130</t>
+          <t>8076772077</t>
         </is>
       </c>
       <c r="F787" s="19" t="inlineStr">
@@ -57557,34 +57557,34 @@
       </c>
       <c r="G787" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H787" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I787" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J787" s="21" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="K787" s="21" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="L787" s="22" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="M787" s="19" t="inlineStr">
         <is>
-          <t>687e0fcb5399a5001312665f</t>
+          <t>65142310fafe6b001d7a5d54</t>
         </is>
       </c>
       <c r="N787" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/687e0fcb5399a5001312665f</t>
+          <t>https://superprofile.bio/vig/65142310fafe6b001d7a5d54</t>
         </is>
       </c>
       <c r="O787" s="24" t="inlineStr">
@@ -57604,22 +57604,22 @@
       </c>
       <c r="B788" s="13" t="inlineStr">
         <is>
-          <t>66878b370bfc9f0013f8aab2</t>
+          <t>6799b5fe5229a200134ae372</t>
         </is>
       </c>
       <c r="C788" s="13" t="inlineStr">
         <is>
-          <t>thattraderstories</t>
+          <t>zerohero110</t>
         </is>
       </c>
       <c r="D788" s="12" t="inlineStr">
         <is>
-          <t>giksongeorge@gmail.com</t>
+          <t>zerheropremium230@gmail.com</t>
         </is>
       </c>
       <c r="E788" s="12" t="inlineStr">
         <is>
-          <t>9910419041</t>
+          <t>9166230130</t>
         </is>
       </c>
       <c r="F788" s="12" t="inlineStr">
@@ -57641,22 +57641,22 @@
         <v>1</v>
       </c>
       <c r="J788" s="14" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="K788" s="14" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="L788" s="15" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="M788" s="12" t="inlineStr">
         <is>
-          <t>6a5f4719c1ef5e00131e7d17</t>
+          <t>687e0fcb5399a5001312665f</t>
         </is>
       </c>
       <c r="N788" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5f4719c1ef5e00131e7d17</t>
+          <t>https://superprofile.bio/vig/687e0fcb5399a5001312665f</t>
         </is>
       </c>
       <c r="O788" s="17" t="inlineStr">
@@ -57676,22 +57676,22 @@
       </c>
       <c r="B789" s="20" t="inlineStr">
         <is>
-          <t>67600b1b39b60f0013d996e2</t>
+          <t>66878b370bfc9f0013f8aab2</t>
         </is>
       </c>
       <c r="C789" s="20" t="inlineStr">
         <is>
-          <t>saima0786</t>
+          <t>thattraderstories</t>
         </is>
       </c>
       <c r="D789" s="19" t="inlineStr">
         <is>
-          <t>Saimashahnawaz130@gmail.com</t>
+          <t>giksongeorge@gmail.com</t>
         </is>
       </c>
       <c r="E789" s="19" t="inlineStr">
         <is>
-          <t>8100541237</t>
+          <t>9910419041</t>
         </is>
       </c>
       <c r="F789" s="19" t="inlineStr">
@@ -57713,22 +57713,22 @@
         <v>1</v>
       </c>
       <c r="J789" s="21" t="n">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="K789" s="21" t="n">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="L789" s="22" t="n">
-        <v>1916</v>
+        <v>1926</v>
       </c>
       <c r="M789" s="19" t="inlineStr">
         <is>
-          <t>69c3dba01eb3cc001300f9a9</t>
+          <t>6a5f4719c1ef5e00131e7d17</t>
         </is>
       </c>
       <c r="N789" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69c3dba01eb3cc001300f9a9</t>
+          <t>https://superprofile.bio/vig/6a5f4719c1ef5e00131e7d17</t>
         </is>
       </c>
       <c r="O789" s="24" t="inlineStr">
@@ -57748,22 +57748,22 @@
       </c>
       <c r="B790" s="13" t="inlineStr">
         <is>
-          <t>64c7f6aa009c3c001e206fa4</t>
+          <t>67600b1b39b60f0013d996e2</t>
         </is>
       </c>
       <c r="C790" s="13" t="inlineStr">
         <is>
-          <t>deepakwadhwaguruji</t>
+          <t>saima0786</t>
         </is>
       </c>
       <c r="D790" s="12" t="inlineStr">
         <is>
-          <t>monumee966085@gmail.com</t>
+          <t>Saimashahnawaz130@gmail.com</t>
         </is>
       </c>
       <c r="E790" s="12" t="inlineStr">
         <is>
-          <t>9772977600</t>
+          <t>8100541237</t>
         </is>
       </c>
       <c r="F790" s="12" t="inlineStr">
@@ -57773,34 +57773,34 @@
       </c>
       <c r="G790" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H790" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I790" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J790" s="14" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="K790" s="14" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="L790" s="15" t="n">
-        <v>1890</v>
+        <v>1916</v>
       </c>
       <c r="M790" s="12" t="inlineStr">
         <is>
-          <t>6a5c7ae2002e310013423007</t>
+          <t>69c3dba01eb3cc001300f9a9</t>
         </is>
       </c>
       <c r="N790" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5c7ae2002e310013423007</t>
+          <t>https://superprofile.bio/vig/69c3dba01eb3cc001300f9a9</t>
         </is>
       </c>
       <c r="O790" s="17" t="inlineStr">
@@ -57820,22 +57820,22 @@
       </c>
       <c r="B791" s="20" t="inlineStr">
         <is>
-          <t>67429ceade3d6800130d625e</t>
+          <t>64c7f6aa009c3c001e206fa4</t>
         </is>
       </c>
       <c r="C791" s="20" t="inlineStr">
         <is>
-          <t>dharmveer2424</t>
+          <t>deepakwadhwaguruji</t>
         </is>
       </c>
       <c r="D791" s="19" t="inlineStr">
         <is>
-          <t>dharmveer24gv@gmail.com</t>
+          <t>monumee966085@gmail.com</t>
         </is>
       </c>
       <c r="E791" s="19" t="inlineStr">
         <is>
-          <t>8109610552</t>
+          <t>9772977600</t>
         </is>
       </c>
       <c r="F791" s="19" t="inlineStr">
@@ -57845,12 +57845,12 @@
       </c>
       <c r="G791" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H791" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I791" s="20" t="n">
@@ -57867,12 +57867,12 @@
       </c>
       <c r="M791" s="19" t="inlineStr">
         <is>
-          <t>69e1477f728d000013b4e37e</t>
+          <t>6a5c7ae2002e310013423007</t>
         </is>
       </c>
       <c r="N791" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69e1477f728d000013b4e37e</t>
+          <t>https://superprofile.bio/vig/6a5c7ae2002e310013423007</t>
         </is>
       </c>
       <c r="O791" s="24" t="inlineStr">
@@ -57892,22 +57892,22 @@
       </c>
       <c r="B792" s="13" t="inlineStr">
         <is>
-          <t>68a9fb5faf623900130c6ec7</t>
+          <t>67429ceade3d6800130d625e</t>
         </is>
       </c>
       <c r="C792" s="13" t="inlineStr">
         <is>
-          <t>tradewithharsh</t>
+          <t>dharmveer2424</t>
         </is>
       </c>
       <c r="D792" s="12" t="inlineStr">
         <is>
-          <t>chturbhujmeena@gmail.com</t>
+          <t>dharmveer24gv@gmail.com</t>
         </is>
       </c>
       <c r="E792" s="12" t="inlineStr">
         <is>
-          <t>6367371305</t>
+          <t>8109610552</t>
         </is>
       </c>
       <c r="F792" s="12" t="inlineStr">
@@ -57917,34 +57917,34 @@
       </c>
       <c r="G792" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H792" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I792" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J792" s="14" t="n">
-        <v>1882</v>
+        <v>1890</v>
       </c>
       <c r="K792" s="14" t="n">
-        <v>1882</v>
+        <v>1890</v>
       </c>
       <c r="L792" s="15" t="n">
-        <v>1882</v>
+        <v>1890</v>
       </c>
       <c r="M792" s="12" t="inlineStr">
         <is>
-          <t>69b01e963a21990013a6dc75</t>
+          <t>69e1477f728d000013b4e37e</t>
         </is>
       </c>
       <c r="N792" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b01e963a21990013a6dc75</t>
+          <t>https://superprofile.bio/vig/69e1477f728d000013b4e37e</t>
         </is>
       </c>
       <c r="O792" s="17" t="inlineStr">
@@ -57964,22 +57964,22 @@
       </c>
       <c r="B793" s="20" t="inlineStr">
         <is>
-          <t>64d0b757596d8a001d266a41</t>
+          <t>68a9fb5faf623900130c6ec7</t>
         </is>
       </c>
       <c r="C793" s="20" t="inlineStr">
         <is>
-          <t>kkstockbtacademy</t>
+          <t>tradewithharsh</t>
         </is>
       </c>
       <c r="D793" s="19" t="inlineStr">
         <is>
-          <t>prasunb34@gmail.com</t>
+          <t>chturbhujmeena@gmail.com</t>
         </is>
       </c>
       <c r="E793" s="19" t="inlineStr">
         <is>
-          <t>8348726471</t>
+          <t>6367371305</t>
         </is>
       </c>
       <c r="F793" s="19" t="inlineStr">
@@ -57989,34 +57989,34 @@
       </c>
       <c r="G793" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H793" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I793" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J793" s="21" t="n">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="K793" s="21" t="n">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="L793" s="22" t="n">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="M793" s="19" t="inlineStr">
         <is>
-          <t>6a91e241282ef200131da755</t>
+          <t>69b01e963a21990013a6dc75</t>
         </is>
       </c>
       <c r="N793" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a91e241282ef200131da755</t>
+          <t>https://superprofile.bio/vig/69b01e963a21990013a6dc75</t>
         </is>
       </c>
       <c r="O793" s="24" t="inlineStr">
@@ -58036,22 +58036,22 @@
       </c>
       <c r="B794" s="13" t="inlineStr">
         <is>
-          <t>65cd763e8b84610029a550ab</t>
+          <t>64d0b757596d8a001d266a41</t>
         </is>
       </c>
       <c r="C794" s="13" t="inlineStr">
         <is>
-          <t>pioneerws</t>
+          <t>kkstockbtacademy</t>
         </is>
       </c>
       <c r="D794" s="12" t="inlineStr">
         <is>
-          <t>shetevaibhav@gmail.com</t>
+          <t>prasunb34@gmail.com</t>
         </is>
       </c>
       <c r="E794" s="12" t="inlineStr">
         <is>
-          <t>9820489820</t>
+          <t>8348726471</t>
         </is>
       </c>
       <c r="F794" s="12" t="inlineStr">
@@ -58061,12 +58061,12 @@
       </c>
       <c r="G794" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H794" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I794" s="13" t="n">
@@ -58083,12 +58083,12 @@
       </c>
       <c r="M794" s="12" t="inlineStr">
         <is>
-          <t>65d8fcd412af0500144f83cc</t>
+          <t>6a91e241282ef200131da755</t>
         </is>
       </c>
       <c r="N794" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65d8fcd412af0500144f83cc</t>
+          <t>https://superprofile.bio/vig/6a91e241282ef200131da755</t>
         </is>
       </c>
       <c r="O794" s="17" t="inlineStr">
@@ -58108,22 +58108,22 @@
       </c>
       <c r="B795" s="20" t="inlineStr">
         <is>
-          <t>68f1b6db304ab30013ea9925</t>
+          <t>65cd763e8b84610029a550ab</t>
         </is>
       </c>
       <c r="C795" s="20" t="inlineStr">
         <is>
-          <t>primiumguruji</t>
+          <t>pioneerws</t>
         </is>
       </c>
       <c r="D795" s="19" t="inlineStr">
         <is>
-          <t>vivekluck0786@gmail.com</t>
+          <t>shetevaibhav@gmail.com</t>
         </is>
       </c>
       <c r="E795" s="19" t="inlineStr">
         <is>
-          <t>7014418865</t>
+          <t>9820489820</t>
         </is>
       </c>
       <c r="F795" s="19" t="inlineStr">
@@ -58133,34 +58133,34 @@
       </c>
       <c r="G795" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H795" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I795" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J795" s="21" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="K795" s="21" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="L795" s="22" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="M795" s="19" t="inlineStr">
         <is>
-          <t>6a65d893afc79b0014d986e0</t>
+          <t>65d8fcd412af0500144f83cc</t>
         </is>
       </c>
       <c r="N795" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a65d893afc79b0014d986e0</t>
+          <t>https://superprofile.bio/vig/65d8fcd412af0500144f83cc</t>
         </is>
       </c>
       <c r="O795" s="24" t="inlineStr">
@@ -58180,22 +58180,22 @@
       </c>
       <c r="B796" s="13" t="inlineStr">
         <is>
-          <t>6880988ef959ac0013076234</t>
+          <t>68f1b6db304ab30013ea9925</t>
         </is>
       </c>
       <c r="C796" s="13" t="inlineStr">
         <is>
-          <t>heyitspriyankasingh</t>
+          <t>primiumguruji</t>
         </is>
       </c>
       <c r="D796" s="12" t="inlineStr">
         <is>
-          <t>priyanka.singhmgnt@gmail.com</t>
+          <t>vivekluck0786@gmail.com</t>
         </is>
       </c>
       <c r="E796" s="12" t="inlineStr">
         <is>
-          <t>9399019263</t>
+          <t>7014418865</t>
         </is>
       </c>
       <c r="F796" s="12" t="inlineStr">
@@ -58205,34 +58205,34 @@
       </c>
       <c r="G796" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H796" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I796" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J796" s="14" t="n">
-        <v>1873</v>
+        <v>1880</v>
       </c>
       <c r="K796" s="14" t="n">
-        <v>1873</v>
+        <v>1880</v>
       </c>
       <c r="L796" s="15" t="n">
-        <v>1873</v>
+        <v>1880</v>
       </c>
       <c r="M796" s="12" t="inlineStr">
         <is>
-          <t>6a92e2b6f6013c00133e3e5d</t>
+          <t>6a65d893afc79b0014d986e0</t>
         </is>
       </c>
       <c r="N796" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a92e2b6f6013c00133e3e5d</t>
+          <t>https://superprofile.bio/vig/6a65d893afc79b0014d986e0</t>
         </is>
       </c>
       <c r="O796" s="17" t="inlineStr">
@@ -58252,22 +58252,22 @@
       </c>
       <c r="B797" s="20" t="inlineStr">
         <is>
-          <t>676682fa9b91bb001351dee2</t>
+          <t>6880988ef959ac0013076234</t>
         </is>
       </c>
       <c r="C797" s="20" t="inlineStr">
         <is>
-          <t>tradewithttx</t>
+          <t>heyitspriyankasingh</t>
         </is>
       </c>
       <c r="D797" s="19" t="inlineStr">
         <is>
-          <t>TechnicalTradeXpert@gmail.com</t>
+          <t>priyanka.singhmgnt@gmail.com</t>
         </is>
       </c>
       <c r="E797" s="19" t="inlineStr">
         <is>
-          <t>7088907280</t>
+          <t>9399019263</t>
         </is>
       </c>
       <c r="F797" s="19" t="inlineStr">
@@ -58277,34 +58277,34 @@
       </c>
       <c r="G797" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H797" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I797" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J797" s="21" t="n">
-        <v>1800</v>
+        <v>1873</v>
       </c>
       <c r="K797" s="21" t="n">
-        <v>1800</v>
+        <v>1873</v>
       </c>
       <c r="L797" s="22" t="n">
-        <v>1800</v>
+        <v>1873</v>
       </c>
       <c r="M797" s="19" t="inlineStr">
         <is>
-          <t>686e6b8d14bb7b00137b6b38</t>
+          <t>6a92e2b6f6013c00133e3e5d</t>
         </is>
       </c>
       <c r="N797" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/686e6b8d14bb7b00137b6b38</t>
+          <t>https://superprofile.bio/vig/6a92e2b6f6013c00133e3e5d</t>
         </is>
       </c>
       <c r="O797" s="24" t="inlineStr">
@@ -58324,22 +58324,22 @@
       </c>
       <c r="B798" s="13" t="inlineStr">
         <is>
-          <t>64d31140b49711001ee4cb72</t>
+          <t>676682fa9b91bb001351dee2</t>
         </is>
       </c>
       <c r="C798" s="13" t="inlineStr">
         <is>
-          <t>Learningtrade</t>
+          <t>tradewithttx</t>
         </is>
       </c>
       <c r="D798" s="12" t="inlineStr">
         <is>
-          <t>vishallakhvara@email.com</t>
+          <t>TechnicalTradeXpert@gmail.com</t>
         </is>
       </c>
       <c r="E798" s="12" t="inlineStr">
         <is>
-          <t>9427664410</t>
+          <t>7088907280</t>
         </is>
       </c>
       <c r="F798" s="12" t="inlineStr">
@@ -58349,34 +58349,34 @@
       </c>
       <c r="G798" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H798" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I798" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J798" s="14" t="n">
-        <v>1744</v>
+        <v>1800</v>
       </c>
       <c r="K798" s="14" t="n">
-        <v>1744</v>
+        <v>1800</v>
       </c>
       <c r="L798" s="15" t="n">
-        <v>1744</v>
+        <v>1800</v>
       </c>
       <c r="M798" s="12" t="inlineStr">
         <is>
-          <t>64f20be95b9b46001fea4819</t>
+          <t>686e6b8d14bb7b00137b6b38</t>
         </is>
       </c>
       <c r="N798" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/64f20be95b9b46001fea4819</t>
+          <t>https://superprofile.bio/vig/686e6b8d14bb7b00137b6b38</t>
         </is>
       </c>
       <c r="O798" s="17" t="inlineStr">
@@ -58396,22 +58396,22 @@
       </c>
       <c r="B799" s="20" t="inlineStr">
         <is>
-          <t>63bab66e73a489003e7526c9</t>
+          <t>64d31140b49711001ee4cb72</t>
         </is>
       </c>
       <c r="C799" s="20" t="inlineStr">
         <is>
-          <t>stockpremium</t>
+          <t>Learningtrade</t>
         </is>
       </c>
       <c r="D799" s="19" t="inlineStr">
         <is>
-          <t>kaish3185@gmail.com</t>
+          <t>vishallakhvara@email.com</t>
         </is>
       </c>
       <c r="E799" s="19" t="inlineStr">
         <is>
-          <t>9811477947</t>
+          <t>9427664410</t>
         </is>
       </c>
       <c r="F799" s="19" t="inlineStr">
@@ -58433,22 +58433,22 @@
         <v>1</v>
       </c>
       <c r="J799" s="21" t="n">
-        <v>1715</v>
+        <v>1744</v>
       </c>
       <c r="K799" s="21" t="n">
-        <v>1715</v>
+        <v>1744</v>
       </c>
       <c r="L799" s="22" t="n">
-        <v>1715</v>
+        <v>1744</v>
       </c>
       <c r="M799" s="19" t="inlineStr">
         <is>
-          <t>63baba5c8a32b9003d4baae2</t>
+          <t>64f20be95b9b46001fea4819</t>
         </is>
       </c>
       <c r="N799" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63baba5c8a32b9003d4baae2</t>
+          <t>https://superprofile.bio/vig/64f20be95b9b46001fea4819</t>
         </is>
       </c>
       <c r="O799" s="24" t="inlineStr">
@@ -58468,22 +58468,22 @@
       </c>
       <c r="B800" s="13" t="inlineStr">
         <is>
-          <t>670a35a446b3f5001315f409</t>
+          <t>63bab66e73a489003e7526c9</t>
         </is>
       </c>
       <c r="C800" s="13" t="inlineStr">
         <is>
-          <t>tradewithshiv00</t>
+          <t>stockpremium</t>
         </is>
       </c>
       <c r="D800" s="12" t="inlineStr">
         <is>
-          <t>sonu3322111@gmail.com</t>
+          <t>kaish3185@gmail.com</t>
         </is>
       </c>
       <c r="E800" s="12" t="inlineStr">
         <is>
-          <t>7419333111</t>
+          <t>9811477947</t>
         </is>
       </c>
       <c r="F800" s="12" t="inlineStr">
@@ -58505,22 +58505,22 @@
         <v>1</v>
       </c>
       <c r="J800" s="14" t="n">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="K800" s="14" t="n">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="L800" s="15" t="n">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="M800" s="12" t="inlineStr">
         <is>
-          <t>67c06d2dd4e3b4001314d20c</t>
+          <t>63baba5c8a32b9003d4baae2</t>
         </is>
       </c>
       <c r="N800" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67c06d2dd4e3b4001314d20c</t>
+          <t>https://superprofile.bio/vig/63baba5c8a32b9003d4baae2</t>
         </is>
       </c>
       <c r="O800" s="17" t="inlineStr">
@@ -58540,22 +58540,22 @@
       </c>
       <c r="B801" s="20" t="inlineStr">
         <is>
-          <t>68b03fb7687f420013c3f18b</t>
+          <t>670a35a446b3f5001315f409</t>
         </is>
       </c>
       <c r="C801" s="20" t="inlineStr">
         <is>
-          <t>sy01</t>
+          <t>tradewithshiv00</t>
         </is>
       </c>
       <c r="D801" s="19" t="inlineStr">
         <is>
-          <t>saurabhydv856@gmail.com</t>
+          <t>sonu3322111@gmail.com</t>
         </is>
       </c>
       <c r="E801" s="19" t="inlineStr">
         <is>
-          <t>6398689318</t>
+          <t>7419333111</t>
         </is>
       </c>
       <c r="F801" s="19" t="inlineStr">
@@ -58565,34 +58565,34 @@
       </c>
       <c r="G801" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H801" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I801" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J801" s="21" t="n">
-        <v>1646</v>
+        <v>1669</v>
       </c>
       <c r="K801" s="21" t="n">
-        <v>1646</v>
+        <v>1669</v>
       </c>
       <c r="L801" s="22" t="n">
-        <v>1646</v>
+        <v>1669</v>
       </c>
       <c r="M801" s="19" t="inlineStr">
         <is>
-          <t>6734586c512491001324475c</t>
+          <t>67c06d2dd4e3b4001314d20c</t>
         </is>
       </c>
       <c r="N801" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6734586c512491001324475c</t>
+          <t>https://superprofile.bio/vig/67c06d2dd4e3b4001314d20c</t>
         </is>
       </c>
       <c r="O801" s="24" t="inlineStr">
@@ -58612,22 +58612,22 @@
       </c>
       <c r="B802" s="13" t="inlineStr">
         <is>
-          <t>62dd3018f83d933bcd5bd23c</t>
+          <t>68b03fb7687f420013c3f18b</t>
         </is>
       </c>
       <c r="C802" s="13" t="inlineStr">
         <is>
-          <t>bullbearpremium</t>
+          <t>sy01</t>
         </is>
       </c>
       <c r="D802" s="12" t="inlineStr">
         <is>
-          <t>pradip.gund9@gmail.com</t>
+          <t>saurabhydv856@gmail.com</t>
         </is>
       </c>
       <c r="E802" s="12" t="inlineStr">
         <is>
-          <t>9503876571</t>
+          <t>6398689318</t>
         </is>
       </c>
       <c r="F802" s="12" t="inlineStr">
@@ -58649,22 +58649,22 @@
         <v>1</v>
       </c>
       <c r="J802" s="14" t="n">
-        <v>1620</v>
+        <v>1646</v>
       </c>
       <c r="K802" s="14" t="n">
-        <v>1620</v>
+        <v>1646</v>
       </c>
       <c r="L802" s="15" t="n">
-        <v>1620</v>
+        <v>1646</v>
       </c>
       <c r="M802" s="12" t="inlineStr">
         <is>
-          <t>68e7cafb27f3a100139ee425</t>
+          <t>6734586c512491001324475c</t>
         </is>
       </c>
       <c r="N802" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68e7cafb27f3a100139ee425</t>
+          <t>https://superprofile.bio/vig/6734586c512491001324475c</t>
         </is>
       </c>
       <c r="O802" s="17" t="inlineStr">
@@ -58684,22 +58684,22 @@
       </c>
       <c r="B803" s="20" t="inlineStr">
         <is>
-          <t>696bad3a78f3790013422449</t>
+          <t>62dd3018f83d933bcd5bd23c</t>
         </is>
       </c>
       <c r="C803" s="20" t="inlineStr">
         <is>
-          <t>zerotohero2</t>
+          <t>bullbearpremium</t>
         </is>
       </c>
       <c r="D803" s="19" t="inlineStr">
         <is>
-          <t>tmind4470@gmail.com</t>
+          <t>pradip.gund9@gmail.com</t>
         </is>
       </c>
       <c r="E803" s="19" t="inlineStr">
         <is>
-          <t>9602674910</t>
+          <t>9503876571</t>
         </is>
       </c>
       <c r="F803" s="19" t="inlineStr">
@@ -58709,34 +58709,34 @@
       </c>
       <c r="G803" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H803" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I803" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J803" s="21" t="n">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="K803" s="21" t="n">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="L803" s="22" t="n">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="M803" s="19" t="inlineStr">
         <is>
-          <t>696da8d346bf86001301fded</t>
+          <t>68e7cafb27f3a100139ee425</t>
         </is>
       </c>
       <c r="N803" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/696da8d346bf86001301fded</t>
+          <t>https://superprofile.bio/vig/68e7cafb27f3a100139ee425</t>
         </is>
       </c>
       <c r="O803" s="24" t="inlineStr">
@@ -58756,22 +58756,22 @@
       </c>
       <c r="B804" s="13" t="inlineStr">
         <is>
-          <t>65e556ff75a641001a90bf56</t>
+          <t>696bad3a78f3790013422449</t>
         </is>
       </c>
       <c r="C804" s="13" t="inlineStr">
         <is>
-          <t>tradewithraj</t>
+          <t>zerotohero2</t>
         </is>
       </c>
       <c r="D804" s="12" t="inlineStr">
         <is>
-          <t>cmsprimesuport@gmail.com</t>
+          <t>tmind4470@gmail.com</t>
         </is>
       </c>
       <c r="E804" s="12" t="inlineStr">
         <is>
-          <t>6367105395</t>
+          <t>9602674910</t>
         </is>
       </c>
       <c r="F804" s="12" t="inlineStr">
@@ -58781,34 +58781,34 @@
       </c>
       <c r="G804" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H804" s="12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I804" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J804" s="14" t="n">
-        <v>1599</v>
+        <v>1619</v>
       </c>
       <c r="K804" s="14" t="n">
-        <v>1599</v>
+        <v>1619</v>
       </c>
       <c r="L804" s="15" t="n">
-        <v>1599</v>
+        <v>1619</v>
       </c>
       <c r="M804" s="12" t="inlineStr">
         <is>
-          <t>68fde49cad2e290012df50ba</t>
+          <t>696da8d346bf86001301fded</t>
         </is>
       </c>
       <c r="N804" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68fde49cad2e290012df50ba</t>
+          <t>https://superprofile.bio/vig/696da8d346bf86001301fded</t>
         </is>
       </c>
       <c r="O804" s="17" t="inlineStr">
@@ -58828,22 +58828,22 @@
       </c>
       <c r="B805" s="20" t="inlineStr">
         <is>
-          <t>69eeed4b09e8f10012d998bb</t>
+          <t>65e556ff75a641001a90bf56</t>
         </is>
       </c>
       <c r="C805" s="20" t="inlineStr">
         <is>
-          <t>preparationkit</t>
+          <t>tradewithraj</t>
         </is>
       </c>
       <c r="D805" s="19" t="inlineStr">
         <is>
-          <t>pranavvpatel25@gmail.com</t>
+          <t>cmsprimesuport@gmail.com</t>
         </is>
       </c>
       <c r="E805" s="19" t="inlineStr">
         <is>
-          <t>8469655210</t>
+          <t>6367105395</t>
         </is>
       </c>
       <c r="F805" s="19" t="inlineStr">
@@ -58853,34 +58853,34 @@
       </c>
       <c r="G805" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H805" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I805" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J805" s="21" t="n">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="K805" s="21" t="n">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="L805" s="22" t="n">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="M805" s="19" t="inlineStr">
         <is>
-          <t>6a90770994d8730013b824d6</t>
+          <t>68fde49cad2e290012df50ba</t>
         </is>
       </c>
       <c r="N805" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a90770994d8730013b824d6</t>
+          <t>https://superprofile.bio/vig/68fde49cad2e290012df50ba</t>
         </is>
       </c>
       <c r="O805" s="24" t="inlineStr">
@@ -58900,59 +58900,59 @@
       </c>
       <c r="B806" s="13" t="inlineStr">
         <is>
-          <t>68cf7b40aaa4c30013596288</t>
+          <t>69eeed4b09e8f10012d998bb</t>
         </is>
       </c>
       <c r="C806" s="13" t="inlineStr">
         <is>
-          <t>httpswwwcareerswavein</t>
+          <t>preparationkit</t>
         </is>
       </c>
       <c r="D806" s="12" t="inlineStr">
         <is>
-          <t>njawaharrenuka@gmail.com</t>
+          <t>pranavvpatel25@gmail.com</t>
         </is>
       </c>
       <c r="E806" s="12" t="inlineStr">
         <is>
-          <t>9010106560</t>
+          <t>8469655210</t>
         </is>
       </c>
       <c r="F806" s="12" t="inlineStr">
         <is>
-          <t>Aayush Sethi</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G806" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H806" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I806" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J806" s="14" t="n">
-        <v>1529</v>
+        <v>1572</v>
       </c>
       <c r="K806" s="14" t="n">
-        <v>1529</v>
+        <v>1572</v>
       </c>
       <c r="L806" s="15" t="n">
-        <v>1529</v>
+        <v>1572</v>
       </c>
       <c r="M806" s="12" t="inlineStr">
         <is>
-          <t>68d0ed81287cca00135e7910</t>
+          <t>6a90770994d8730013b824d6</t>
         </is>
       </c>
       <c r="N806" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68d0ed81287cca00135e7910</t>
+          <t>https://superprofile.bio/vig/6a90770994d8730013b824d6</t>
         </is>
       </c>
       <c r="O806" s="17" t="inlineStr">
@@ -58972,59 +58972,59 @@
       </c>
       <c r="B807" s="20" t="inlineStr">
         <is>
-          <t>6613ee30d6ac80001afadce9</t>
+          <t>68cf7b40aaa4c30013596288</t>
         </is>
       </c>
       <c r="C807" s="20" t="inlineStr">
         <is>
-          <t>httpstmet1uilphv4taxymm1</t>
+          <t>httpswwwcareerswavein</t>
         </is>
       </c>
       <c r="D807" s="19" t="inlineStr">
         <is>
-          <t>abinash543211@gmail.com</t>
+          <t>njawaharrenuka@gmail.com</t>
         </is>
       </c>
       <c r="E807" s="19" t="inlineStr">
         <is>
-          <t>9589592337</t>
+          <t>9010106560</t>
         </is>
       </c>
       <c r="F807" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aayush Sethi</t>
         </is>
       </c>
       <c r="G807" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H807" s="19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I807" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J807" s="21" t="n">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="K807" s="21" t="n">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="L807" s="22" t="n">
-        <v>1515</v>
+        <v>1529</v>
       </c>
       <c r="M807" s="19" t="inlineStr">
         <is>
-          <t>6994990e6e580f00133a8ce5</t>
+          <t>68d0ed81287cca00135e7910</t>
         </is>
       </c>
       <c r="N807" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6994990e6e580f00133a8ce5</t>
+          <t>https://superprofile.bio/vig/68d0ed81287cca00135e7910</t>
         </is>
       </c>
       <c r="O807" s="24" t="inlineStr">
@@ -59044,22 +59044,22 @@
       </c>
       <c r="B808" s="13" t="inlineStr">
         <is>
-          <t>669fa0a435c0ce00132e1976</t>
+          <t>6613ee30d6ac80001afadce9</t>
         </is>
       </c>
       <c r="C808" s="13" t="inlineStr">
         <is>
-          <t>stock123</t>
+          <t>httpstmet1uilphv4taxymm1</t>
         </is>
       </c>
       <c r="D808" s="12" t="inlineStr">
         <is>
-          <t>bhagwatrohit081@gmail.com</t>
+          <t>abinash543211@gmail.com</t>
         </is>
       </c>
       <c r="E808" s="12" t="inlineStr">
         <is>
-          <t>9021347462</t>
+          <t>9589592337</t>
         </is>
       </c>
       <c r="F808" s="12" t="inlineStr">
@@ -59069,34 +59069,34 @@
       </c>
       <c r="G808" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H808" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I808" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J808" s="14" t="n">
-        <v>1472</v>
+        <v>1515</v>
       </c>
       <c r="K808" s="14" t="n">
-        <v>1472</v>
+        <v>1515</v>
       </c>
       <c r="L808" s="15" t="n">
-        <v>1472</v>
+        <v>1515</v>
       </c>
       <c r="M808" s="12" t="inlineStr">
         <is>
-          <t>6a12baf5253c3a001372e45c</t>
+          <t>6994990e6e580f00133a8ce5</t>
         </is>
       </c>
       <c r="N808" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a12baf5253c3a001372e45c</t>
+          <t>https://superprofile.bio/vig/6994990e6e580f00133a8ce5</t>
         </is>
       </c>
       <c r="O808" s="17" t="inlineStr">
@@ -59116,22 +59116,22 @@
       </c>
       <c r="B809" s="20" t="inlineStr">
         <is>
-          <t>6619645537982d001350dd29</t>
+          <t>669fa0a435c0ce00132e1976</t>
         </is>
       </c>
       <c r="C809" s="20" t="inlineStr">
         <is>
-          <t>praveen511</t>
+          <t>stock123</t>
         </is>
       </c>
       <c r="D809" s="19" t="inlineStr">
         <is>
-          <t>praveenchoudhary5016@gmail.com</t>
+          <t>bhagwatrohit081@gmail.com</t>
         </is>
       </c>
       <c r="E809" s="19" t="inlineStr">
         <is>
-          <t>7891641511</t>
+          <t>9021347462</t>
         </is>
       </c>
       <c r="F809" s="19" t="inlineStr">
@@ -59141,12 +59141,12 @@
       </c>
       <c r="G809" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H809" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I809" s="20" t="n">
@@ -59163,12 +59163,12 @@
       </c>
       <c r="M809" s="19" t="inlineStr">
         <is>
-          <t>69eefe125fe24c0013092e92</t>
+          <t>6a12baf5253c3a001372e45c</t>
         </is>
       </c>
       <c r="N809" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69eefe125fe24c0013092e92</t>
+          <t>https://superprofile.bio/vig/6a12baf5253c3a001372e45c</t>
         </is>
       </c>
       <c r="O809" s="24" t="inlineStr">
@@ -59188,22 +59188,22 @@
       </c>
       <c r="B810" s="13" t="inlineStr">
         <is>
-          <t>6891f2a547882e0013794da9</t>
+          <t>6619645537982d001350dd29</t>
         </is>
       </c>
       <c r="C810" s="13" t="inlineStr">
         <is>
-          <t>11starteam</t>
+          <t>praveen511</t>
         </is>
       </c>
       <c r="D810" s="12" t="inlineStr">
         <is>
-          <t>lokeshgurjar0930@gmail.com</t>
+          <t>praveenchoudhary5016@gmail.com</t>
         </is>
       </c>
       <c r="E810" s="12" t="inlineStr">
         <is>
-          <t>9509698741</t>
+          <t>7891641511</t>
         </is>
       </c>
       <c r="F810" s="12" t="inlineStr">
@@ -59213,34 +59213,34 @@
       </c>
       <c r="G810" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H810" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I810" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J810" s="14" t="n">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="K810" s="14" t="n">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="L810" s="15" t="n">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="M810" s="12" t="inlineStr">
         <is>
-          <t>669e46c778795600130d6fac</t>
+          <t>69eefe125fe24c0013092e92</t>
         </is>
       </c>
       <c r="N810" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/669e46c778795600130d6fac</t>
+          <t>https://superprofile.bio/vig/69eefe125fe24c0013092e92</t>
         </is>
       </c>
       <c r="O810" s="17" t="inlineStr">
@@ -59260,22 +59260,22 @@
       </c>
       <c r="B811" s="20" t="inlineStr">
         <is>
-          <t>62bad2a8dc07ec6e742c8cd2</t>
+          <t>6891f2a547882e0013794da9</t>
         </is>
       </c>
       <c r="C811" s="20" t="inlineStr">
         <is>
-          <t>tradexculture</t>
+          <t>11starteam</t>
         </is>
       </c>
       <c r="D811" s="19" t="inlineStr">
         <is>
-          <t>itstradeculture@gmail.com</t>
+          <t>lokeshgurjar0930@gmail.com</t>
         </is>
       </c>
       <c r="E811" s="19" t="inlineStr">
         <is>
-          <t>9098432281</t>
+          <t>9509698741</t>
         </is>
       </c>
       <c r="F811" s="19" t="inlineStr">
@@ -59285,34 +59285,34 @@
       </c>
       <c r="G811" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H811" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I811" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J811" s="21" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="K811" s="21" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="L811" s="22" t="n">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="M811" s="19" t="inlineStr">
         <is>
-          <t>63515a0aa785512f19f504e7</t>
+          <t>669e46c778795600130d6fac</t>
         </is>
       </c>
       <c r="N811" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
+          <t>https://superprofile.bio/vig/669e46c778795600130d6fac</t>
         </is>
       </c>
       <c r="O811" s="24" t="inlineStr">
@@ -59332,22 +59332,22 @@
       </c>
       <c r="B812" s="13" t="inlineStr">
         <is>
-          <t>62fce0e4560a1b2b3a724948</t>
+          <t>62bad2a8dc07ec6e742c8cd2</t>
         </is>
       </c>
       <c r="C812" s="13" t="inlineStr">
         <is>
-          <t>stockmarketwindow</t>
+          <t>tradexculture</t>
         </is>
       </c>
       <c r="D812" s="12" t="inlineStr">
         <is>
-          <t>stockmarketwindow2020@gmail.com</t>
+          <t>itstradeculture@gmail.com</t>
         </is>
       </c>
       <c r="E812" s="12" t="inlineStr">
         <is>
-          <t>9702609090</t>
+          <t>9098432281</t>
         </is>
       </c>
       <c r="F812" s="12" t="inlineStr">
@@ -59357,34 +59357,34 @@
       </c>
       <c r="G812" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H812" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I812" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J812" s="14" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="K812" s="14" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="L812" s="15" t="n">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="M812" s="12" t="inlineStr">
         <is>
-          <t>62fceac39275d45cb6f4f9b0</t>
+          <t>63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="N812" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/62fceac39275d45cb6f4f9b0</t>
+          <t>https://superprofile.bio/vig/63515a0aa785512f19f504e7</t>
         </is>
       </c>
       <c r="O812" s="17" t="inlineStr">
@@ -59404,22 +59404,22 @@
       </c>
       <c r="B813" s="20" t="inlineStr">
         <is>
-          <t>694b73fb58a19500131a05fc</t>
+          <t>62fce0e4560a1b2b3a724948</t>
         </is>
       </c>
       <c r="C813" s="20" t="inlineStr">
         <is>
-          <t>UPSC1109</t>
+          <t>stockmarketwindow</t>
         </is>
       </c>
       <c r="D813" s="19" t="inlineStr">
         <is>
-          <t>upsccurrentaffairs2026@gmail.com</t>
+          <t>stockmarketwindow2020@gmail.com</t>
         </is>
       </c>
       <c r="E813" s="19" t="inlineStr">
         <is>
-          <t>7840849825</t>
+          <t>9702609090</t>
         </is>
       </c>
       <c r="F813" s="19" t="inlineStr">
@@ -59429,34 +59429,34 @@
       </c>
       <c r="G813" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H813" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I813" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J813" s="21" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="K813" s="21" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L813" s="22" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="M813" s="19" t="inlineStr">
         <is>
-          <t>694bc7f749716f00136386dd</t>
+          <t>62fceac39275d45cb6f4f9b0</t>
         </is>
       </c>
       <c r="N813" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/694bc7f749716f00136386dd</t>
+          <t>https://superprofile.bio/vig/62fceac39275d45cb6f4f9b0</t>
         </is>
       </c>
       <c r="O813" s="24" t="inlineStr">
@@ -59476,22 +59476,22 @@
       </c>
       <c r="B814" s="13" t="inlineStr">
         <is>
-          <t>67c5f49ae74b1d0013ea0111</t>
+          <t>694b73fb58a19500131a05fc</t>
         </is>
       </c>
       <c r="C814" s="13" t="inlineStr">
         <is>
-          <t>jayb2427</t>
+          <t>UPSC1109</t>
         </is>
       </c>
       <c r="D814" s="12" t="inlineStr">
         <is>
-          <t>astutetrader24@gmail.com</t>
+          <t>upsccurrentaffairs2026@gmail.com</t>
         </is>
       </c>
       <c r="E814" s="12" t="inlineStr">
         <is>
-          <t>9879002427</t>
+          <t>7840849825</t>
         </is>
       </c>
       <c r="F814" s="12" t="inlineStr">
@@ -59501,34 +59501,34 @@
       </c>
       <c r="G814" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H814" s="12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I814" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J814" s="14" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="K814" s="14" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="L814" s="15" t="n">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="M814" s="12" t="inlineStr">
         <is>
-          <t>67ecc370d9f0a5001309bd71</t>
+          <t>694bc7f749716f00136386dd</t>
         </is>
       </c>
       <c r="N814" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
+          <t>https://superprofile.bio/vig/694bc7f749716f00136386dd</t>
         </is>
       </c>
       <c r="O814" s="17" t="inlineStr">
@@ -59548,22 +59548,22 @@
       </c>
       <c r="B815" s="20" t="inlineStr">
         <is>
-          <t>65a74951ac6382001e161d60</t>
+          <t>67c5f49ae74b1d0013ea0111</t>
         </is>
       </c>
       <c r="C815" s="20" t="inlineStr">
         <is>
-          <t>ltt</t>
+          <t>jayb2427</t>
         </is>
       </c>
       <c r="D815" s="19" t="inlineStr">
         <is>
-          <t>ageshgowdom@gmail.com</t>
+          <t>astutetrader24@gmail.com</t>
         </is>
       </c>
       <c r="E815" s="19" t="inlineStr">
         <is>
-          <t>9952320729</t>
+          <t>9879002427</t>
         </is>
       </c>
       <c r="F815" s="19" t="inlineStr">
@@ -59573,12 +59573,12 @@
       </c>
       <c r="G815" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H815" s="19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I815" s="20" t="n">
@@ -59595,12 +59595,12 @@
       </c>
       <c r="M815" s="19" t="inlineStr">
         <is>
-          <t>6a7b1ef9b038ca00137d7652</t>
+          <t>67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="N815" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7b1ef9b038ca00137d7652</t>
+          <t>https://superprofile.bio/vig/67ecc370d9f0a5001309bd71</t>
         </is>
       </c>
       <c r="O815" s="24" t="inlineStr">
@@ -59620,22 +59620,22 @@
       </c>
       <c r="B816" s="13" t="inlineStr">
         <is>
-          <t>62b02cfe05ee3a0f33197b51</t>
+          <t>65a74951ac6382001e161d60</t>
         </is>
       </c>
       <c r="C816" s="13" t="inlineStr">
         <is>
-          <t>ssbfix</t>
+          <t>ltt</t>
         </is>
       </c>
       <c r="D816" s="12" t="inlineStr">
         <is>
-          <t>dantedmc4005@gmail.com</t>
+          <t>ageshgowdom@gmail.com</t>
         </is>
       </c>
       <c r="E816" s="12" t="inlineStr">
         <is>
-          <t>8492898406</t>
+          <t>9952320729</t>
         </is>
       </c>
       <c r="F816" s="12" t="inlineStr">
@@ -59645,12 +59645,12 @@
       </c>
       <c r="G816" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H816" s="12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I816" s="13" t="n">
@@ -59667,12 +59667,12 @@
       </c>
       <c r="M816" s="12" t="inlineStr">
         <is>
-          <t>69b2db3479da0a0013c60582</t>
+          <t>6a7b1ef9b038ca00137d7652</t>
         </is>
       </c>
       <c r="N816" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b2db3479da0a0013c60582</t>
+          <t>https://superprofile.bio/vig/6a7b1ef9b038ca00137d7652</t>
         </is>
       </c>
       <c r="O816" s="17" t="inlineStr">
@@ -59692,22 +59692,22 @@
       </c>
       <c r="B817" s="20" t="inlineStr">
         <is>
-          <t>635b7f0025aca400328ae08f</t>
+          <t>62b02cfe05ee3a0f33197b51</t>
         </is>
       </c>
       <c r="C817" s="20" t="inlineStr">
         <is>
-          <t>gj20</t>
+          <t>ssbfix</t>
         </is>
       </c>
       <c r="D817" s="19" t="inlineStr">
         <is>
-          <t>gauravjetty2020@gmail.com</t>
+          <t>dantedmc4005@gmail.com</t>
         </is>
       </c>
       <c r="E817" s="19" t="inlineStr">
         <is>
-          <t>9049483124</t>
+          <t>8492898406</t>
         </is>
       </c>
       <c r="F817" s="19" t="inlineStr">
@@ -59717,34 +59717,34 @@
       </c>
       <c r="G817" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H817" s="19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I817" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J817" s="21" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="K817" s="21" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="L817" s="22" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="M817" s="19" t="inlineStr">
         <is>
-          <t>6a5b01ec7929600013224a5b</t>
+          <t>69b2db3479da0a0013c60582</t>
         </is>
       </c>
       <c r="N817" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5b01ec7929600013224a5b</t>
+          <t>https://superprofile.bio/vig/69b2db3479da0a0013c60582</t>
         </is>
       </c>
       <c r="O817" s="24" t="inlineStr">
@@ -59764,22 +59764,22 @@
       </c>
       <c r="B818" s="13" t="inlineStr">
         <is>
-          <t>647578b824c9b30020e932b3</t>
+          <t>635b7f0025aca400328ae08f</t>
         </is>
       </c>
       <c r="C818" s="13" t="inlineStr">
         <is>
-          <t>prajustockmarket</t>
+          <t>gj20</t>
         </is>
       </c>
       <c r="D818" s="12" t="inlineStr">
         <is>
-          <t>kkurzekar16@gmail.com</t>
+          <t>gauravjetty2020@gmail.com</t>
         </is>
       </c>
       <c r="E818" s="12" t="inlineStr">
         <is>
-          <t>9112441997</t>
+          <t>9049483124</t>
         </is>
       </c>
       <c r="F818" s="12" t="inlineStr">
@@ -59811,12 +59811,12 @@
       </c>
       <c r="M818" s="12" t="inlineStr">
         <is>
-          <t>66b1ef098817a000134de2a4</t>
+          <t>6a5b01ec7929600013224a5b</t>
         </is>
       </c>
       <c r="N818" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66b1ef098817a000134de2a4</t>
+          <t>https://superprofile.bio/vig/6a5b01ec7929600013224a5b</t>
         </is>
       </c>
       <c r="O818" s="17" t="inlineStr">
@@ -59836,22 +59836,22 @@
       </c>
       <c r="B819" s="20" t="inlineStr">
         <is>
-          <t>655c2b17f2c0c5001e80dc5c</t>
+          <t>647578b824c9b30020e932b3</t>
         </is>
       </c>
       <c r="C819" s="20" t="inlineStr">
         <is>
-          <t>uday08</t>
+          <t>prajustockmarket</t>
         </is>
       </c>
       <c r="D819" s="19" t="inlineStr">
         <is>
-          <t>joguudaykiran4i@gmail.com</t>
+          <t>kkurzekar16@gmail.com</t>
         </is>
       </c>
       <c r="E819" s="19" t="inlineStr">
         <is>
-          <t>7569057147</t>
+          <t>9112441997</t>
         </is>
       </c>
       <c r="F819" s="19" t="inlineStr">
@@ -59861,34 +59861,34 @@
       </c>
       <c r="G819" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H819" s="19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I819" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J819" s="21" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="K819" s="21" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="L819" s="22" t="n">
-        <v>1259</v>
+        <v>1349</v>
       </c>
       <c r="M819" s="19" t="inlineStr">
         <is>
-          <t>6a97085d5a0b9a00134a57d9</t>
+          <t>66b1ef098817a000134de2a4</t>
         </is>
       </c>
       <c r="N819" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
+          <t>https://superprofile.bio/vig/66b1ef098817a000134de2a4</t>
         </is>
       </c>
       <c r="O819" s="24" t="inlineStr">
@@ -59908,22 +59908,22 @@
       </c>
       <c r="B820" s="13" t="inlineStr">
         <is>
-          <t>6a2a3b18739da100136db6f1</t>
+          <t>655c2b17f2c0c5001e80dc5c</t>
         </is>
       </c>
       <c r="C820" s="13" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>uday08</t>
         </is>
       </c>
       <c r="D820" s="12" t="inlineStr">
         <is>
-          <t>mr.perfect.official018@gmail.com</t>
+          <t>joguudaykiran4i@gmail.com</t>
         </is>
       </c>
       <c r="E820" s="12" t="inlineStr">
         <is>
-          <t>9116087897</t>
+          <t>7569057147</t>
         </is>
       </c>
       <c r="F820" s="12" t="inlineStr">
@@ -59933,34 +59933,34 @@
       </c>
       <c r="G820" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H820" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I820" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J820" s="14" t="n">
-        <v>1172</v>
+        <v>1259</v>
       </c>
       <c r="K820" s="14" t="n">
-        <v>1220</v>
+        <v>1259</v>
       </c>
       <c r="L820" s="15" t="n">
-        <v>1220</v>
+        <v>1259</v>
       </c>
       <c r="M820" s="12" t="inlineStr">
         <is>
-          <t>6a7d364eb62576001374f10c</t>
+          <t>6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="N820" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
+          <t>https://superprofile.bio/vig/6a97085d5a0b9a00134a57d9</t>
         </is>
       </c>
       <c r="O820" s="17" t="inlineStr">
@@ -59980,22 +59980,22 @@
       </c>
       <c r="B821" s="20" t="inlineStr">
         <is>
-          <t>6613b382df40ae0013ce2e06</t>
+          <t>6a2a3b18739da100136db6f1</t>
         </is>
       </c>
       <c r="C821" s="20" t="inlineStr">
         <is>
-          <t>thebullzonetrading</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="D821" s="19" t="inlineStr">
         <is>
-          <t>adityajangir22@gmail.com</t>
+          <t>mr.perfect.official018@gmail.com</t>
         </is>
       </c>
       <c r="E821" s="19" t="inlineStr">
         <is>
-          <t>9029547188</t>
+          <t>9116087897</t>
         </is>
       </c>
       <c r="F821" s="19" t="inlineStr">
@@ -60005,34 +60005,34 @@
       </c>
       <c r="G821" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H821" s="19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I821" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J821" s="21" t="n">
-        <v>1213</v>
+        <v>1172</v>
       </c>
       <c r="K821" s="21" t="n">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="L821" s="22" t="n">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="M821" s="19" t="inlineStr">
         <is>
-          <t>66698a6464d3b00013ffe2cc</t>
+          <t>6a7d364eb62576001374f10c</t>
         </is>
       </c>
       <c r="N821" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66698a6464d3b00013ffe2cc</t>
+          <t>https://superprofile.bio/vig/6a7d364eb62576001374f10c</t>
         </is>
       </c>
       <c r="O821" s="24" t="inlineStr">
@@ -60052,22 +60052,22 @@
       </c>
       <c r="B822" s="13" t="inlineStr">
         <is>
-          <t>6867eeeeec727a00135b607b</t>
+          <t>6613b382df40ae0013ce2e06</t>
         </is>
       </c>
       <c r="C822" s="13" t="inlineStr">
         <is>
-          <t>speaksaurabh</t>
+          <t>thebullzonetrading</t>
         </is>
       </c>
       <c r="D822" s="12" t="inlineStr">
         <is>
-          <t>saurabhjs120@gmail.com</t>
+          <t>adityajangir22@gmail.com</t>
         </is>
       </c>
       <c r="E822" s="12" t="inlineStr">
         <is>
-          <t>7865522553</t>
+          <t>9029547188</t>
         </is>
       </c>
       <c r="F822" s="12" t="inlineStr">
@@ -60077,34 +60077,34 @@
       </c>
       <c r="G822" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H822" s="12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I822" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J822" s="14" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="K822" s="14" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="L822" s="15" t="n">
-        <v>1188</v>
+        <v>1213</v>
       </c>
       <c r="M822" s="12" t="inlineStr">
         <is>
-          <t>69d51deb76619c0014716500</t>
+          <t>66698a6464d3b00013ffe2cc</t>
         </is>
       </c>
       <c r="N822" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d51deb76619c0014716500</t>
+          <t>https://superprofile.bio/vig/66698a6464d3b00013ffe2cc</t>
         </is>
       </c>
       <c r="O822" s="17" t="inlineStr">
@@ -60124,22 +60124,22 @@
       </c>
       <c r="B823" s="20" t="inlineStr">
         <is>
-          <t>62b00d08d794090f2ca8d918</t>
+          <t>6867eeeeec727a00135b607b</t>
         </is>
       </c>
       <c r="C823" s="20" t="inlineStr">
         <is>
-          <t>rinkesh2076</t>
+          <t>speaksaurabh</t>
         </is>
       </c>
       <c r="D823" s="19" t="inlineStr">
         <is>
-          <t>rinkeshagrawal52@gmail.com</t>
+          <t>saurabhjs120@gmail.com</t>
         </is>
       </c>
       <c r="E823" s="19" t="inlineStr">
         <is>
-          <t>7247035512</t>
+          <t>7865522553</t>
         </is>
       </c>
       <c r="F823" s="19" t="inlineStr">
@@ -60149,34 +60149,34 @@
       </c>
       <c r="G823" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H823" s="19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I823" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J823" s="21" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="K823" s="21" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="L823" s="22" t="n">
-        <v>1169</v>
+        <v>1188</v>
       </c>
       <c r="M823" s="19" t="inlineStr">
         <is>
-          <t>6a8a70729ac5d90013fd1d86</t>
+          <t>69d51deb76619c0014716500</t>
         </is>
       </c>
       <c r="N823" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a8a70729ac5d90013fd1d86</t>
+          <t>https://superprofile.bio/vig/69d51deb76619c0014716500</t>
         </is>
       </c>
       <c r="O823" s="24" t="inlineStr">
@@ -60196,22 +60196,22 @@
       </c>
       <c r="B824" s="13" t="inlineStr">
         <is>
-          <t>67fe57009043de0013589892</t>
+          <t>62b00d08d794090f2ca8d918</t>
         </is>
       </c>
       <c r="C824" s="13" t="inlineStr">
         <is>
-          <t>onestopmedicoo</t>
+          <t>rinkesh2076</t>
         </is>
       </c>
       <c r="D824" s="12" t="inlineStr">
         <is>
-          <t>gayathrinukalapati@gmail.com</t>
+          <t>rinkeshagrawal52@gmail.com</t>
         </is>
       </c>
       <c r="E824" s="12" t="inlineStr">
         <is>
-          <t>6281889512</t>
+          <t>7247035512</t>
         </is>
       </c>
       <c r="F824" s="12" t="inlineStr">
@@ -60221,34 +60221,34 @@
       </c>
       <c r="G824" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H824" s="12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I824" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J824" s="14" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="K824" s="14" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="L824" s="15" t="n">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="M824" s="12" t="inlineStr">
         <is>
-          <t>67fe5d9fd3f9cd0013838092</t>
+          <t>6a8a70729ac5d90013fd1d86</t>
         </is>
       </c>
       <c r="N824" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67fe5d9fd3f9cd0013838092</t>
+          <t>https://superprofile.bio/vig/6a8a70729ac5d90013fd1d86</t>
         </is>
       </c>
       <c r="O824" s="17" t="inlineStr">
@@ -60268,22 +60268,22 @@
       </c>
       <c r="B825" s="20" t="inlineStr">
         <is>
-          <t>671a5a67c711890013a079f3</t>
+          <t>67fe57009043de0013589892</t>
         </is>
       </c>
       <c r="C825" s="20" t="inlineStr">
         <is>
-          <t>investing123</t>
+          <t>onestopmedicoo</t>
         </is>
       </c>
       <c r="D825" s="19" t="inlineStr">
         <is>
-          <t>gk8295311@gmail.com</t>
+          <t>gayathrinukalapati@gmail.com</t>
         </is>
       </c>
       <c r="E825" s="19" t="inlineStr">
         <is>
-          <t>7564911925</t>
+          <t>6281889512</t>
         </is>
       </c>
       <c r="F825" s="19" t="inlineStr">
@@ -60293,34 +60293,34 @@
       </c>
       <c r="G825" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H825" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I825" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J825" s="21" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="K825" s="21" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="L825" s="22" t="n">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="M825" s="19" t="inlineStr">
         <is>
-          <t>678540efacb5430013f405f9</t>
+          <t>67fe5d9fd3f9cd0013838092</t>
         </is>
       </c>
       <c r="N825" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/678540efacb5430013f405f9</t>
+          <t>https://superprofile.bio/vig/67fe5d9fd3f9cd0013838092</t>
         </is>
       </c>
       <c r="O825" s="24" t="inlineStr">
@@ -60340,22 +60340,22 @@
       </c>
       <c r="B826" s="13" t="inlineStr">
         <is>
-          <t>6436d5892b2028001fbf607b</t>
+          <t>671a5a67c711890013a079f3</t>
         </is>
       </c>
       <c r="C826" s="13" t="inlineStr">
         <is>
-          <t>Livelonghari</t>
+          <t>investing123</t>
         </is>
       </c>
       <c r="D826" s="12" t="inlineStr">
         <is>
-          <t>livelongwealth@gmail.com</t>
+          <t>gk8295311@gmail.com</t>
         </is>
       </c>
       <c r="E826" s="12" t="inlineStr">
         <is>
-          <t>9544085264</t>
+          <t>7564911925</t>
         </is>
       </c>
       <c r="F826" s="12" t="inlineStr">
@@ -60365,34 +60365,34 @@
       </c>
       <c r="G826" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H826" s="12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I826" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J826" s="14" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="K826" s="14" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="L826" s="15" t="n">
-        <v>1080</v>
+        <v>1143</v>
       </c>
       <c r="M826" s="12" t="inlineStr">
         <is>
-          <t>653e68ea423d4e001eef5b19</t>
+          <t>678540efacb5430013f405f9</t>
         </is>
       </c>
       <c r="N826" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
+          <t>https://superprofile.bio/vig/678540efacb5430013f405f9</t>
         </is>
       </c>
       <c r="O826" s="17" t="inlineStr">
@@ -60412,22 +60412,22 @@
       </c>
       <c r="B827" s="20" t="inlineStr">
         <is>
-          <t>67e424ccab747f00135495b4</t>
+          <t>6436d5892b2028001fbf607b</t>
         </is>
       </c>
       <c r="C827" s="20" t="inlineStr">
         <is>
-          <t>jobposting</t>
+          <t>Livelonghari</t>
         </is>
       </c>
       <c r="D827" s="19" t="inlineStr">
         <is>
-          <t>sagarruttare@gmail.com</t>
+          <t>livelongwealth@gmail.com</t>
         </is>
       </c>
       <c r="E827" s="19" t="inlineStr">
         <is>
-          <t>7796716569</t>
+          <t>9544085264</t>
         </is>
       </c>
       <c r="F827" s="19" t="inlineStr">
@@ -60449,22 +60449,22 @@
         <v>1</v>
       </c>
       <c r="J827" s="21" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="K827" s="21" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L827" s="22" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="M827" s="19" t="inlineStr">
         <is>
-          <t>692dae30d42b600013b13d78</t>
+          <t>653e68ea423d4e001eef5b19</t>
         </is>
       </c>
       <c r="N827" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
+          <t>https://superprofile.bio/vig/653e68ea423d4e001eef5b19</t>
         </is>
       </c>
       <c r="O827" s="24" t="inlineStr">
@@ -60484,22 +60484,22 @@
       </c>
       <c r="B828" s="13" t="inlineStr">
         <is>
-          <t>64de1b2ce570b0001ed8a14d</t>
+          <t>67e424ccab747f00135495b4</t>
         </is>
       </c>
       <c r="C828" s="13" t="inlineStr">
         <is>
-          <t>azit</t>
+          <t>jobposting</t>
         </is>
       </c>
       <c r="D828" s="12" t="inlineStr">
         <is>
-          <t>adshree6@gmail.com</t>
+          <t>sagarruttare@gmail.com</t>
         </is>
       </c>
       <c r="E828" s="12" t="inlineStr">
         <is>
-          <t>9664914880</t>
+          <t>7796716569</t>
         </is>
       </c>
       <c r="F828" s="12" t="inlineStr">
@@ -60509,12 +60509,12 @@
       </c>
       <c r="G828" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H828" s="12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I828" s="13" t="n">
@@ -60531,12 +60531,12 @@
       </c>
       <c r="M828" s="12" t="inlineStr">
         <is>
-          <t>68fe2dfaa6c0dd0013399d00</t>
+          <t>692dae30d42b600013b13d78</t>
         </is>
       </c>
       <c r="N828" s="16" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68fe2dfaa6c0dd0013399d00</t>
+          <t>https://superprofile.bio/vig/692dae30d42b600013b13d78</t>
         </is>
       </c>
       <c r="O828" s="17" t="inlineStr">
@@ -60556,22 +60556,22 @@
       </c>
       <c r="B829" s="20" t="inlineStr">
         <is>
-          <t>6273b90a908af834792d0f70</t>
+          <t>64de1b2ce570b0001ed8a14d</t>
         </is>
       </c>
       <c r="C829" s="20" t="inlineStr">
         <is>
-          <t>otwa</t>
+          <t>azit</t>
         </is>
       </c>
       <c r="D829" s="19" t="inlineStr">
         <is>
-          <t>reshmanandyadav@gmail.com</t>
+          <t>adshree6@gmail.com</t>
         </is>
       </c>
       <c r="E829" s="19" t="inlineStr">
         <is>
-          <t>9792053659</t>
+          <t>9664914880</t>
         </is>
       </c>
       <c r="F829" s="19" t="inlineStr">
@@ -60581,34 +60581,34 @@
       </c>
       <c r="G829" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H829" s="19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I829" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J829" s="21" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="K829" s="21" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="L829" s="22" t="n">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="M829" s="19" t="inlineStr">
         <is>
-          <t>680e309d146ab000130197f0</t>
+          <t>68fe2dfaa6c0dd0013399d00</t>
         </is>
       </c>
       <c r="N829" s="23" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/680e309d146ab000130197f0</t>
+          <t>https://superprofile.bio/vig/68fe2dfaa6c0dd0013399d00</t>
         </is>
       </c>
       <c r="O829" s="24" t="inlineStr">
@@ -60628,22 +60628,22 @@
       </c>
       <c r="B830" s="13" t="inlineStr">
         <is>
-          <t>69ad496eafc0e100130d7f09</t>
+          <t>6273b90a908af834792d0f70</t>
         </is>
       </c>
       <c r="C830" s="13" t="inlineStr">
         <is>
-          <t>sunoaudiobook</t>
+          <t>otwa</t>
         </is>
       </c>
       <c r="D830" s="12" t="inlineStr">
         <is>
-          <t>devrajstudio09@gmail.com</t>
+          <t>reshmanandyadav@gmail.com</t>
         </is>
       </c>
       <c r="E830" s="12" t="inlineStr">
         <is>
-          <t>7869490714</t>
+          <t>9792053659</t>
         </is>
       </c>
       <c r="F830" s="12" t="inlineStr">
@@ -60653,42 +60653,114 @@
       </c>
       <c r="G830" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H830" s="12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I830" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J830" s="14" t="n">
+        <v>1049</v>
+      </c>
+      <c r="K830" s="14" t="n">
+        <v>1049</v>
+      </c>
+      <c r="L830" s="15" t="n">
+        <v>1049</v>
+      </c>
+      <c r="M830" s="12" t="inlineStr">
+        <is>
+          <t>680e309d146ab000130197f0</t>
+        </is>
+      </c>
+      <c r="N830" s="16" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/680e309d146ab000130197f0</t>
+        </is>
+      </c>
+      <c r="O830" s="17" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P830" s="18" t="inlineStr">
+        <is>
+          <t>HOLD - RELEASE RESTRICTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="19" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" s="20" t="inlineStr">
+        <is>
+          <t>69ad496eafc0e100130d7f09</t>
+        </is>
+      </c>
+      <c r="C831" s="20" t="inlineStr">
+        <is>
+          <t>sunoaudiobook</t>
+        </is>
+      </c>
+      <c r="D831" s="19" t="inlineStr">
+        <is>
+          <t>devrajstudio09@gmail.com</t>
+        </is>
+      </c>
+      <c r="E831" s="19" t="inlineStr">
+        <is>
+          <t>7869490714</t>
+        </is>
+      </c>
+      <c r="F831" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G831" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="H831" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I831" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J831" s="21" t="n">
         <v>1031</v>
       </c>
-      <c r="K830" s="14" t="n">
+      <c r="K831" s="21" t="n">
         <v>1031</v>
       </c>
-      <c r="L830" s="15" t="n">
+      <c r="L831" s="22" t="n">
         <v>1031</v>
       </c>
-      <c r="M830" s="12" t="inlineStr">
+      <c r="M831" s="19" t="inlineStr">
         <is>
           <t>6a4684b13604a700135096e1</t>
         </is>
       </c>
-      <c r="N830" s="16" t="inlineStr">
+      <c r="N831" s="23" t="inlineStr">
         <is>
           <t>https://superprofile.bio/vig/6a4684b13604a700135096e1</t>
         </is>
       </c>
-      <c r="O830" s="17" t="inlineStr">
-        <is>
-          <t>Not Verified</t>
-        </is>
-      </c>
-      <c r="P830" s="18" t="inlineStr">
+      <c r="O831" s="24" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P831" s="18" t="inlineStr">
         <is>
           <t>HOLD - RELEASE RESTRICTED</t>
         </is>
@@ -61525,6 +61597,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N828" r:id="rId827"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N829" r:id="rId828"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N830" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N831" r:id="rId830"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 10:09:45 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 11:59:38 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 11:59:38 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 13:25:53 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 13:25:53 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 14:56:48 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 14:56:48 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 16:53:31 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-12 16:53:31 | Daily Audits Logged: 14</t>
+          <t>Generated On: 2026-09-12 17:54:27 | Daily Audits Logged: 14</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-13 02:43:45 | Daily Audits Logged: 15</t>
+          <t>Generated On: 2026-09-13 05:56:49 | Daily Audits Logged: 15</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-13 11:48:16 | Daily Audits Logged: 15</t>
+          <t>Generated On: 2026-09-13 11:50:33 | Daily Audits Logged: 15</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-SEBI Master Registry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-13 11:50:33 | Daily Audits Logged: 15</t>
+          <t>Generated On: 2026-09-13 06:21:43 | Daily Audits Logged: 15</t>
         </is>
       </c>
     </row>

--- a/data/non_sebi_creators_cumulative.xlsx
+++ b/data/non_sebi_creators_cumulative.xlsx
@@ -569,7 +569,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Generated On: 2026-09-13 06:21:43 | Daily Audits Logged: 15</t>
+          <t>Generated On: 2026-09-13 08:42:51 | Daily Audits Logged: 15</t>
         </is>
       </c>
     </row>
